--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -10,6 +10,7 @@
     <sheet name="종합이슈_누적" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="주식추천_누적" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="시장지표_누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="코인추천_누적" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -462,7 +463,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3609,6 +3610,6188 @@
       <c r="G85" s="3" t="inlineStr">
         <is>
           <t>https://www.yna.co.kr/view/AKR20261013058200005</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”  경향신문[전국 주요 신문 톱뉴스](14일 조간)  연합뉴스금융위·법무부 등 44개 기관 9929명, 내년부터 세종 본격 이전  정책브리핑대사관들 모두 서울 있는데… 법 고쳐 외교안보 부처까지 세종으로  조선일보...</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBMeFo1WV9RWkgyZDc5OXRoaXJ1bFpqQXpITG9QQmxicVNnbnNKSHAzWUNXZjF0bVJ3VmExV2t0ZUtnQTNzc1lEZXlNYlY3R3podHp0d2JRTVJlZ9IBX0FVX3lxTE8tam1RNHk4a2JrTHJFd0FRWExJSlNWeU1UeEs5MnNqbGdUYkFFSVpqRnYyX0VVbV9sUHJBbmY4TkJueFBPQlhxRkwwczlWMU1neC1Ga3lOUm4wa2FPVzlV?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>헌재 사무처장 “조희대 국감 불러 대법관 제청 물은 건 위헌 아냐”</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>헌재 사무처장 “조희대 국감 불러 대법관 제청 물은 건 위헌 아냐”  한겨레여당 "조희대 문제 있다" 주장에…헌재 사무처장 "네" 답변  JTBC“조희대, 사법 독립 가장해 1인 정치 행동”…헌법학자들, ‘대법원장 제청권 독점’ 비판  경향신문[칼럼] ‘이진관 기피신청’ 인용이 조희대 ...</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>한겨레</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5mTm5HdFlNUG5nQkhqYU5SQUJJRUJQa2c4M3ZKSlZrWlU3RkI2ZWE4akg5OHRRVnc1YTFPbzdVWXZPMlFBRHBobV85eG5EQnVWT2RvWG54SmJySUd2bktSTzJ1VUl2U1RKclA4aXpTa25SQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>李대통령, '부캉이' 친수공원 찾아 시민 소통…HMM 제막식도 참석</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>李대통령, '부캉이' 친수공원 찾아 시민 소통…HMM 제막식도 참석  연합뉴스"부캉이 보러 왔다가 대통령까지"...부산 북항 찾은 이재명 대통령  KBC광주방송이 대통령, HMM 본사 제막식 '부산시대 개막'  뉴시스HMM 부산 시대 개막...이재명 대통령, 본사 사옥 제막식 참석  전...</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE15VnhEX2ZlYS1may05U3NMU29IOUFaR2F5dEZlVGJuN05zQzRsZnl2VEVFOXhValhIdEZ1UVByRDNWYkpGZ2ZZaUZ5NEQwQ0llUmVTdEpMbFVCTVdib0lDU9IBYEFVX3lxTE15VnhEX2ZlYS1may05U3NMU29IOUFaR2F5dEZlVGJuN05zQzRsZnl2VEVFOXhValhIdEZ1UVByRDNWYkpGZ2ZZaUZ5NEQwQ0llUmVTdEpMbFVCTVdib0lDUw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>[정우상 칼럼] 친문은 극혐하고 대통령은 극찬하는 인사처장</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>[정우상 칼럼] 친문은 극혐하고 대통령은 극찬하는 인사처장  조선일보</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxObElacC1uZUxRX0I2RmVOVjBoOFBRUGNYZUpSZWw0dXdhUWEtdHIxX2NPRnBEZXcxbWJJdS0yeGMzLTA0cktoZ1gyWnMtbTZDbWhCWlgzWEx1RkhXVE54WTBEX2pjNkI4WXlUOXcxSmhiTEtyUEF0NDFnZ3o1SlVTMmRB?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>청와대, '한·미 골프외교 TF' 구성‥실무 준비 착수</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>청와대, '한·미 골프외교 TF' 구성‥실무 준비 착수  MBC 뉴스[윤영호의 게임의 시선] 트럼프와 골프 라운드를 앞둔 이 대통령께  조선일보靑, 李-트럼프 골프 대비 TF 꾸려… 12월 G20 美회의 계기 성사 전망  동아일보靑, 트럼프와 골프회동 실무대응팀 구성…12월 성사 가능성...</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>MBC 뉴스</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9kaXQzajR4VFFPV04wMkh0a3N6V0xiQTRUV0tJbnBGR1NKTlIyT1pWTWk5UjVQaGFnMDRRczloX0VlRWJHTzZIMVlHX1pzd0JBVDhsNHZzQTJVZXpuZFZ3cWJOellmcG1SOEF3elhnZFpteDBENDhuM9IBeEFVX3lxTE83YXpQNFhmZm5RY2ZIX0RuWjI3Tnp2RlllbjZfamVMa2FseGVRd2xNSHhULThYaEhqR0dGUTZJN2JwTHdJaW4tZ2FKU3Q3V3RkeHNiNWhlNkFjNEpXU2NPdVBpVEJnTjh4YjhMZnJRbFNUaENMY210cA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>백악관 새 대변인, 첫 브리핑서 “한국, 알래스카 LNG 투자” 언급</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>백악관 새 대변인, 첫 브리핑서 “한국, 알래스카 LNG 투자” 언급  KBS 뉴스백악관 "한국, 알래스카에 540억 달러 투자할 것”...트럼프, 알래스카 유세  YTN백악관 “한국 최대 2천억 달러 에너지 투자 계획” 재강조  VOA 한국어 홈페이지트럼프의 에너지 압박 맞서는 한국…...</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9EVlBUeDhWZ040aUxiNlpQZmFNUUhPUW81MTJGMDdtVFlMbUN2TEhZVlFIUTZpY0tleUd3ejl0b3FIeDRuaUxIZjk5N2x4LXB3LTlRMEFYV1Rsa0k?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>[단독]검찰총장 후보 추천위원 2명이 같은 로펌 소속···위원 구성 놓고 공정성 우려 제기</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>[단독]검찰총장 후보 추천위원 2명이 같은 로펌 소속···위원 구성 놓고 공정성 우려 제기  경향신문속보 법무부, 검찰총장 후보추천위 구성...공소청 초대 수장 인선 착수  YTN공소청 초대 수장 인선 착수‥내일부터 국민 추천  MBC 뉴스이재명정부 첫 검찰총장 추천위 구성…초대 공소청...</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE02bXAtLVFINEhnUUdqSkxqSVlRV2ZkbUk0RW9HVHhXV3d1ME1uYUU1SzNUbGxZeUlNanNNNG4zNWZXektmNDdYek9QR19zWk5wX1VSdkdwZVVKZ9IBX0FVX3lxTE9qQWUxUlBic3U1ZU16aFVZSkRMczdwSzc1NTVsb1pSSWhkbXF2VEc2NzhPSGMyUWZ3eFIyMHh2blJzNF9JbmJOUFIxM1pjeEFsSlpaSEU1MjBfbWNfbGYw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>농진청, 5년간 기술이전 6천여건…제품화 성공률은 40%대 불과</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>(전주=연합뉴스) 김동철 기자 = 농촌진흥청이 최근 5년간 2천건이 넘는 특허를 내고 6천건이 넘는 기술이전 계약을 체결했지만, 실제 제품·서비...</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014030900055</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>김민석, '김지용 비판' 추미애에 "자기 역할에 집중해야"</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김정진 기자 = 더불어민주당 김민석 대표는 14일 추미애 경기도지사를 겨냥, "각자의 처지와 역할에 맞게 정확하게 하는 것, ...</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014020700001</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>"소진공, 베트남 매장 일방 폐점에 소상공인 업체 43곳 피해"</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 조다운 기자 = 소상공인시장진흥공단이 베트남에서 운영하던 화장품 상설 매장의 문을 일방적으로 닫으면서, 입점을 기다리던 소공인...</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013150700001</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>[오늘의 국회일정](14일·수)</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 위원회</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013187700001</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>정태호 "올해 공급망기금 91% 대기업에…지원체계 보완해야"</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 박재하 기자 = 글로벌 공급망 위기 대응을 위해 국내 기업에 지원하는 '공급망안정화기금'이 대기업에 편중되고 있어 이를 재조정...</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013181600001</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>주미대사관 "강경화 'DMZ 지뢰 발언', 정전협정 위반 강조 취지"</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>(워싱턴=연합뉴스) 홍정규 특파원 = 주미한국대사관은 최근 비무장지대(DMZ) 북한 지뢰 폭발에 대한 강경화 주미대사의 국정감사 발언이 "우리 ...</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014010200071</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>방송사 협찬고지 위반 처분 29건…9개월 만에 작년 추월</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 유현민 기자 = 방송사의 협찬고지 법규 위반에 따른 처분 건수가 올해 9월까지 29건으로 집계돼 지난해 연간 처분 건수(16건...</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013135700017</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>이양수 "aT 칭다오 물류센터, 거약 예산 투입에도 활용률 저하"</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 한주홍 기자 = 우리 농식품의 중국 수출을 지원하기 위해 거액의 재정을 투입해 설립한 한국농수산식품유통공사(aT) 칭다오 물류...</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013134700030</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>"LH 공공임대주택서 7년간 화재 1천여건…사망자 절반은 영구임대"</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 노선웅 기자 = 한국토지주택공사(LH) 공공임대주택에서 최근 7년간 1천100건이 넘는 화재가 발생해 250명이 넘는 사상자가...</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013187900001</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>박성훈 "대테러센터, 올 2월 이후 공유받은 중동 정보 0건"</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이정현 기자 = 국가 대테러 업무를 총괄하는 국무조정실 대테러센터가 올해 2월 이후 중동·호르무즈 관련 정보를 관계기관으로부터...</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261012144600001</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>서범수 "수학여행 가는 초등학교 2년새 724곳 줄어"</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김연정 기자 = 수학여행, 수련 활동 등 숙박형 현장체험학습을 실시한 초등학교가 최근 2년 새 700곳 넘게 줄어든 것으로 나...</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013177200001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>野최수진 "석탄공사 직원, 민주당 명함 들고 정치활동하다 징계"</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 조다운 기자 = 산업통상부 산하 대한석탄공사 직원이 더불어민주당 당직 이력이 적힌 명함을 만들어 정치 활동을 하다가 징계받았다...</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013131100001</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>"농어촌공사, 동일직종 뽑는데도 본부 심사기준 제각각"</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 박수윤 기자 = 한국농어촌공사가 동일 직종의 임직원을 뽑는데 지사별로 심사 기준을 달리하는 등 채용 절차를 주먹구구로 운영하고...</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013027300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>이양수 "농수산식품유통공사 새 비축기지 활용률 60%로 저조"</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이정현 기자 = 한국농수산식품유통공사(aT)가 비축시설 노후화와 분산 문제를 해결하기 위해 비축기지를 신축했지만, 활용률이 저...</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013113000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>정치</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>"한전, 호남산단 전력망건설 '2년반 안에 완료' 계획 비현실적"</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 권희원 기자 = 한국전력공사가 통상 9년이 소요되는 전력망 건설을 호남 반도체 국가산업단지 사업에서는 불과 2년 반 만에 완료...</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013183000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>이 대통령, 인천 찾아 ‘흉기난동 사건’ 보고받아…“엄정 수사” 지시</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>이 대통령, 인천 찾아 ‘흉기난동 사건’ 보고받아…“엄정 수사” 지시  한겨레[이시각헤드라인] 10월 14일 라이브투데이  연합뉴스TV인천경찰청 찾은 이 대통령, 흉기 난동 사건에 “엄정 수사···전자발찌 관리대책 마련해야”  경향신문인천서 전자발찌 찬 50대 흉기난동…시민들, 의자로 ...</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>한겨레</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE43eEgyQkpJTnFsbjkxYUxOX1IzT0NaT1BnaVpjM1ZadVFtby1nSXFVOTlmeHFLaWZRM1VGNzB0WGtUVUxOMFBCQ2lMeEZvVU1fbXJLQUFNU3d5QTVuTlNMejdDNWJ3TF8zTkNR?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>‘불의의 사고’ 아니란 강경화 대사 발언 해명 나선 주미 대사관···“기존 표현 맞는지와 무관”</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>‘불의의 사고’ 아니란 강경화 대사 발언 해명 나선 주미 대사관···“기존 표현 맞는지와 무관”  경향신문"불의의 사고 아니다" 강경화 발언 수습에… 한동훈 "국민이 우습나"  조선일보北 지뢰 도발 대응 놓고 유엔 국감서 공방… 차지훈 “어떻게 접근할지는 미정”  천지일보[뉴스광장 헤드...</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1hUkZwRHNSeXV0bVNkck15ZmpyckxlXzBLaUwxLUY5V3V0TEUzYUVuN040UndrYllabFM0NUdUTXpQVjRzb2xUQThFNG9sVUlVc1hSbWFqYUhYQdIBX0FVX3lxTFA5NklMWW96TDM3Nl9iejRueXhpakJxZjNNSEpIdzdMT3Z2ZUtqVjJCdk9VYUlaNzljdkRORW9wZXJYSmFnMVQzMUpiOWluUHVobkVMdnAwVW52S04wM20w?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>양육권 뺏긴 40대男, 딸과 함께 차에서 숨진채 발견</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>양육권 뺏긴 40대男, 딸과 함께 차에서 숨진채 발견  동아일보“경찰에 ‘안전 확인’ 수차례 요청했지만 결국”···제주서 40대 아버지·네 살 딸 숨진 채 발견  경향신문[속보]“찾아달라” 호소했지만 제주서 4살 딸 숨진 채 발견  문화일보“딸이 위험하다” 수차례 도움 요청했지만…4살 ...</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBuempJUmN5Q1dHYU1VZHVUemoxRURfVE1KWjFpRnVkbTFVUFVkZTFNNHY0LU9IaGwtaWM3YlV0bDJKMUVRYTNzWnlZSGZtcU9CSjNmVXVtQURkRTQyRzJhZ2xjY0J6bzdsbFpxRmYtbWc5UnhJYlHSAWZBVV95cUxNY1N6TzU3UVRHdzEtLThrQnZyWktTZzJwdl8xU0ZuU0FkX2txT0FxMWk2VDJnX1lsazNXeG9tRmpSMlNXX1loVDNzSkNhdDRaeXdpZjBRUjhCUEVNQUd6Nm1nbVJzNWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>추미애 "김지용은 친윤 검사‥공직에 부적합" 거듭 주장</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>추미애 "김지용은 친윤 검사‥공직에 부적합" 거듭 주장  MBC 뉴스靑이 해야 할 말, 하지 말아야 할 말[오늘과 내일/장원재]  동아일보김민석, '김지용 비판' 추미애에 "자기 역할에 집중해야"  연합뉴스“윤석열과 최근 10년간 사적 만남 없었다” 김지용 중수청장 후보 오늘 청문회  ...</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>MBC 뉴스</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5jRlcwUGcyM2MzcEpMSWxyOWg0YzJyYWtJQzJOQVRpdU9KVml0TGppbzJFVWZKSVJRZXVVSWE3UkJMNF9EMnp4c0JDWEFlV2VxVVN0WF9vV0Fndm5HcDRQc1NwczQxcFhBeUZMcnlUR0N3cU9LUEFTaNIBeEFVX3lxTE0xYnFEVHNfZFBzMTBJdUdGRl9WQVZ1allWVEdiZFRBcjNfbkxpN3REYm5rakwzYkZ6VkllX1NSeWxUMXlLQklKRFYxdE9qZm84ZWV5LWVRRk5LSXNxUV91YTJNd3cwUG1EWDRPYlktVnhhcl9KSkpQQw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>남은 중앙부처 모두 세종行…'행정수도 완성' 가시화</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>남은 중앙부처 모두 세종行…'행정수도 완성' 가시화  한국경제안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”  경향신문[전국 주요 신문 톱뉴스](14일 조간)  연합뉴스금융위·법무부 등 44개 기관 9929명, 내년부터 세종 본격 이전  정책브리핑대사관들 모두...</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE43TW4tcGZ5YWVBbmdpYVNlX18tYVJzSkpWSlRrek1YNFBnc2hKTlJmc2NINWtWZ1I1b2UtU1RSMTV3U05UWUhPWWs3MF9DcWdxNGdNNDdLM3lEQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>“한반도 다영역부대로 다층감지…지도서 베이징·서울 선그어보라”</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>“한반도 다영역부대로 다층감지…지도서 베이징·서울 선그어보라”  KBS 뉴스주한미군사령관 "더 넓은 작전환경 이해… 지도서 베이징·서울 선 그어보라"  조선일보"北도 실전경험… 한미 연합훈련 기존틀 벗어나야" - 머니투데이  머니투데이"한반도 다영역부대로 다층감지…지도서 베이징·서울 선...</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1aQnNfaV9oa0E3WTNwRkZUTDI4TDdseXM2ckVHYXV4TlhGcmVlelRwMFRidFBsRXJDeVM0MzlfV1N3eUpzUWZQUlZzTGRoVEdpLWZYMnNYX0NsREE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>‘1억 공천헌금’ 강선우·김경 오늘 1심 선고</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>‘1억 공천헌금’ 강선우·김경 오늘 1심 선고  KBS 뉴스Google 뉴스에서 헤드라인 및 의견 더보기</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9OMTJjTVhPZGVoOGRvak5nSXZ5eFEtZjNaVVJmaVJPSHV1OUpCczlucVNqdTBYZjZLbHo4d1U5aDJpUFAzTmIyYnJtS0RjUGZYV2g3Y2N2OG1CWFk?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>이 대통령 "북극항로 시대 대비, 부산·동남권 미래 함께 열어가겠다"</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>이 대통령 "북극항로 시대 대비, 부산·동남권 미래 함께 열어가겠다"  정책브리핑북극항로 시범운항선 시찰 - 포토 | 멀티미디어  정책브리핑이 대통령 “국제사회 신뢰 속 북극항로 열어갈 것…해양강국 대한민국”  KBS 뉴스이재명대통령이 북극항로에 진심인 이유! (261013 화요일 클립...</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>정책브리핑</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE81Q1ZoM2JvZTlBNWE0akI2UlpodWZtWlZyaGV1eEtHLWllWjBtRkcwdDhhMmhycWF4bl9CbE1lVzczZzhWbU9RZHdydlo2QlA0WGd5ei1KWU5pU0ZBbHliY1pGQ1gxVVRMZzR4SA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>[단독] ‘장모 살인’ 다음날 접근금지…경찰 6일 늑장, 공소청 2일, 법원 4일 걸려</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>[단독] ‘장모 살인’ 다음날 접근금지…경찰 6일 늑장, 공소청 2일, 법원 4일 걸려  한겨레[단독] 장모 살해범, 이미 ‘수차례 전과’…상습범의 계획범죄 정황  JTBC‘장모 살해’ 20대 과거 수배 이력까지…‘장모 살해’ 경찰 대응 적절했나  KBS 뉴스[단독]가정폭력 검거 절반은...</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>한겨레</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBEaERuWjVGMEt6UjJLeUlLTjItWHpCdkFiV21sRkZFM1pkOUtmN2RoWXg4dklPTWNMNHRJbVQtcmJ6WG5GdnczTEVLbFgyNTFXMzVUbFhaYzhhdTczNFFVN0g3QUFoUnNwLVZvaDNOb2VJUQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>추미애 "李대통령 '호의호식' SNS, 날 겨냥했다 보지 않아"</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>추미애 "李대통령 '호의호식' SNS, 날 겨냥했다 보지 않아"  MBC 뉴스경기도 아닌 ‘추미애 국정감사’?…여야, ‘예산 삭감’·‘SNS 정치’ 질타  KBS 뉴스"일방독주" "여의도지사" 與도 野도 秋 난타  조선일보秋국감서 與공세성 질의에 '내분 분수령'…김지용 청문회도 주목(종...</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>MBC 뉴스</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE94c3JuajRENkN6ZHdXM3piWHJzMUJnRGhkM3BoNjFPejZ0UDRMeVc2bFh3eFFpd0RFUkIzOURzSjc3aUh2MHVIREg2bEZDYVFvZEhtNmt2LTZmaFVKb0NBQUF5RFZTMFVMbXRTN2lEQ2k3R0Q4a0ZMa9IBeEFVX3lxTFB4Vi1HN0VFSGNxakxlVmdTb1J0ODFWOVZndFdVdmpqZjl2aERoMC1Ub1l6Rm5IMzk3bC1oSGRzZFN2ZkNlWXRqQVhkSVUtbEpabDJFTndVSGtTYUxXQXZKb2tSZmowM1hQUjRxSHdMZ2EzNEtFNEk3YQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>정동영 "한미동맹 이상 없다"는데…강경화 "백악관과 소통 답답"</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>정동영 "한미동맹 이상 없다"는데…강경화 "백악관과 소통 답답"  조선일보[사설]더 막 나가는 鄭 장관과 남 얘기하듯 하는 康 대사  동아일보강경화 '돌발 국감 발언'에 靑 당혹…李 "굴종·사대적 태도 지양"  데일리안국정감사 계속…주미대사관·헌재·식약처·경기도 등  연합뉴스주미대사관 ...</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNUzFnQnp1UXFnZHlUaXQ3RGtadVVQM1BnQlJfbnpPODRjU2NScmFRLWo2T1VGa2R5VzUyUU9iUXpONXhmNHFoaEpzbllhV0QyODdkb0g2T0ktajVBUTF1OWlBbkV4UkU1WV9XcWhpeU9WTWRJMXQtekxmdUNaUVhtNWJqbTRXZlBNMHlWSVZrN21Xd21IV04xN1BPSkI3QQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>“내일 출근길엔 패딩 입어야겠네”…비 그친 뒤 기온 ‘뚝’ 최저 5도</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>“내일 출근길엔 패딩 입어야겠네”…비 그친 뒤 기온 ‘뚝’ 최저 5도  매일경제[날씨] 서울 9.5℃, 올가을 최저...찬바람 불며 종일 쌀쌀  YTN올가을 들어 가장 쌀쌀한 아침…찬바람에 체감온도 ‘뚝’  경향신문대전·세종·충남 출근길 쌀쌀…바람도 강해 체감기온 뚝  연합뉴스쌀쌀한 가...</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1qaGxTc0dhTEYxTDE1ZVZ3alA4TGd6WXhYdkhvckxmTlFiYmNxbllCNWwtdEJmTmtURjdld2pzY0Y1c3EtYWdmQWE1QW96MlJ4NUxPWQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>이 대통령 "주택·일자리·포용금융 정책 속도…성장 온기 함께 해야"</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>이 대통령 "주택·일자리·포용금융 정책 속도…성장 온기 함께 해야"  정책브리핑이재명 대통령 "양극화 골 메우고 불평등 벽 낮춰야"  경상일보李대통령 “올해 韓 성장률 4%까지 예측…성장 그늘도 세심히 살펴야”  전자신문李대통령 "엎드릴 각오로"…장·차관·LH 사장 현장行, 착공 시험대...</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>정책브리핑</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9TZXJHcVA5SDY5NVVLWmRSZEhMNUl1WUNxTmg5T3A2SjhsRGxZNkhSSC1uLXJtbUs3cUwxWlg0TGFZRUR1Q0YxQ0xNSE9KV292bDl3QnBNSElxcExJT1NwTG9kNS1SNTRxOGIySg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>전경국 선린대 총장 취임…"미래사회 필요 전문인재 양성"</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>(포항=연합뉴스) 손대성 기자 = 전경국(46) 신임 선린대 총장이 14일 취임해 업무를 시작했다.</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014038700053</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>강원경제자유구역청, 동해 북평지구 수소기업 투자 유치 나서</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>(춘천=연합뉴스) 이재현 기자 = 강원경제자유구역청이 동해 북평지구의 수소산업 육성을 위해 관련 기업 유치에 나섰다.</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014035600062</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>강원산 감자로 만든 '감자전맛 감자칩' 15일부터 전국 판매</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>(춘천=연합뉴스) 이재현 기자 = 강원에서 생산한 감자로 만든 '감자전맛 감자칩'이 전국 대형마트와 편의점에서 판매된다.</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014032500062</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>태안군의원 내년 의정비 4천364만2천원…올해보다 2.0% 인상</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>(태안=연합뉴스) 정윤덕 기자 = 충남 태안군은 내년 군의원 의정비가 올해보다 2.0% 인상된다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014039200063</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>스포츠박물관 도서관 15일 개관…송파구-체육공단 운영 협약</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 정준영 기자 = 서울 송파구(구청장 서강석)는 서울올림픽기념국민체육진흥공단(이사장 하형주)과 지난 12일 '국립스포츠박물관 도...</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014037500004</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>현대차그룹, 학대피해 아동 돕는 '아이케어 카' 20대 기증</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 홍규빈 기자 = 현대차그룹은 학대 피해 아동을 지원하는 '아이케어 카'(i-CARE CAR) 20대를 기증한다고 14일 밝혔다...</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014031700003</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>함안 남해고속도서 덤프트럭이 통근버스 추돌…12명 병원 이송</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>(함안=연합뉴스) 박영민 기자 = 14일 오전 7시 44분께 경남 함안군 군북면 남해고속도로 순천 방향 군북IC 인근에서 40대 남성 A씨가 몰...</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014034800052</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>제주 펜션 풀장에 16개월 여아 빠져 중태</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>(제주=연합뉴스) 고성식 기자 = 13일 오후 6시 2분께 제주 서귀포시 대정읍의 한 펜션 풀장에서 16개월 된 여아가 물에 빠져 구조됐지만 중...</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014035300056</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>인천 백령도·대청도 강풍주의보 해제…서해에 풍랑주의보 해제</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>(인천=연합뉴스) 기상청은 인천 백령도·대청도에 발령했던 강풍주의보를 14일 오전 9시를 기해 해제했다고 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014036300527</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>울산 시내버스 노선 개편 설문서 '배차시간 단축' 요구 최다</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>(울산=연합뉴스) 김용태 기자 = 울산시가 시내버스 노선 개편을 위해 실시 중인 시민 설문 조사의 중간 집계 결과 '배차 시간 단축' 요구가 가...</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014024500057</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>24억원어치 암표 판매업자 검거 경찰팀에 1천500만원 포상금</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 한지은 기자 = 경찰청은 전문 암표업자 검거와 자살시도자 등을 위한 일시보호센터 도입 추진 등 20건을 특별성과 포상 대상으로...</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013179100004</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>쌍용C&amp;B "태국 수출 물량 두배 확대…'한국산' 높은 신뢰 덕분"</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>(세종=연합뉴스) 이상서 기자 = MSS홀딩스(이하 MSS)의 쌍용C&amp;amp;B가 최근 주요 제품을 태국에 수출하기 시작하면서 수출 비중을 지속...</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013148400030</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>[내일날씨] 전국 맑고 일교차 커…경기·강원 북부 늦은 오후 비</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 조현영 기자 = 목요일인 15일은 전국이 대체로 맑고 일교차 큰 날씨가 이어지겠다.</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014011600004</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>[부산소식] 동의대, 재난관리 전문인력 양성사업에 선정</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>(부산=연합뉴스) ▲ 동의대, 재난관리 전문인력 양성사업에 선정 = 동의대학교는 행정안전부의 '재난관리 분야 전문인력 양성사업'에 선정됐다고 1...</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014031500051</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>“코스피 6천 겨우 턱걸이”…범인은 중국 반도체? [잇슈 머니]</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>“코스피 6천 겨우 턱걸이”…범인은 중국 반도체? [잇슈 머니]  KBS 뉴스센터장도 '당황' 삼전 잘 나가는데 도대체 왜 떨어지나 "이유 굳이 굳이 꼽자면…"  YTN대신證 "PER 5배 이하서 매도 실익 없어...분할매수 유효"  마켓인[오늘의 증시]코스피 야간선물 1.7%↑…'검은...</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE81LTZBQkc1a0xKWXZmaUxsUXNOenBBcERySmFId2dndW94MjBtLXZWOURVUkZ0WVpQYXluc0hydTdvcjAwSHhoWlhsU3VPZGd1YlFvU1dfckxfUFE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>IMF, 올해 韓 1인당 GDP 4만弗 돌파 전망…명목 GDP 2.2조달러 관측</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>IMF, 올해 韓 1인당 GDP 4만弗 돌파 전망…명목 GDP 2.2조달러 관측  연합인포맥스IMF, 올해 한국 경제성장률 3.3% 전망…7월 대비 0.7%↑  정책브리핑성장률 전망 3.3%로 오른 날, 코스피는 5% 폭락  조선일보IMF "선진국 재정적자 GDP의 5.2%…코로나 이후...</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1sTGQ3OGV4TW55VElfaEZWN0FWak8tLTVXZHpOY0VKTVZkTzNCOXNHcEIzejFEYWYyVnU0d2dBQURsMlBIYWdKZ21ZenkwQlNCT0g0NkJLNGx3LVAxWWo5VERwZUJvTGtRcG5RYXd3SVg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>홍라희, 또 이재용에 지분 넘겼다…이번엔 삼성전자 2.6조</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>홍라희, 또 이재용에 지분 넘겼다…이번엔 삼성전자 2.6조  비즈워치이재용, 장외매수로 삼성전자 766만주 매수…1.9조 규모  연합인포맥스[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여  문화일보홍라희 관장, 이재용 회장에 삼성전자 지분 2.6조 증여  조선일보홍...</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>비즈워치</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwN01xRjFiRF9ZMjJUUG1PUWlGaWRHV2hsLWNCY2ZnYnRTREtGcXYxMFF6X0k3YXRXM3Z1dW04Qm1IbE9rdUY5cm1IVG9FVDZ5M29GNXA2VFgxS0VLT0RtTW1rTW5wWHFJTXZ1Ng?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>뉴욕증시 일제히 하락…美은행 실적 혼조·반도체 약세 여파</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>뉴욕증시 일제히 하락…美은행 실적 혼조·반도체 약세 여파  연합뉴스TV은행 실적 기대 못 미치고 반도체 약세…뉴욕증시 일제히 하락  조선일보[뉴욕증시] 출발이 살짝 불안한 어닝 시즌…하락 마감  연합인포맥스[속보] 삼전닉스 프리장 2%대 상승 … 중국발 쇼크에 美 반도체는 약세  뉴데일...</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스TV</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBqenprbEMybXJmWVh1eUpDekswMGNoaGZ6WjhUU2hpRVRYUF8xNXRGWEFaLWdlY2F2VGxMVEtscTJPOGViQ1p5SnRCUzBvVTRGSVN4SzJxWTVqdWpEUzFORFlNZ0JseDA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>주주환원 늘었는데 세금은 제각각…입법조사처 "배당세제 정합성 손봐야"</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>주주환원 늘었는데 세금은 제각각…입법조사처 "배당세제 정합성 손봐야"  연합인포맥스상장사, 자사주 62조 소각해 1년 새 156%↑…삼전닉스가 절반  매일경제 마켓자사주 소각 1년 새 156% 급증⋯삼성전자•SK하이닉스가 절반  브릿지경제"상법 개정의 역설"…유증 부담에 PRS·신종자본...</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5tQlNOUERvNU54YVhIN2xOQ0lVdThfZmptd3AzY05SdlZxZ2FuZ0dvcXhnRXNqVEpBTk9yY3lNbkphd1pRVklkbTVtVnl2czZEWG0yZUdkS2tUNlJ5WXdyOTBPUWhvRDlXMlBMRDZPMUE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>가족 연계 회사에 수년간 자문료…전 LG엔솔 사장 ‘배임’ 수사</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>가족 연계 회사에 수년간 자문료…전 LG엔솔 사장 ‘배임’ 수사  KBS 뉴스[단독]가족 연계된 中컨설팅사에 10여년 자문료… 100억 손해 혐의 LG엔솔 前사장 압수수색  동아일보'가족 연계 中업체에 100억 자문료'…경찰, LG엔솔 전 사장 '배임' 수사 - 머니투데이  머니투데이경...</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE51dUxwVzFJQWd3UkxSOHlLWTZvVS0wQnltS0RwNnlYaHZjS1pod0pqQWpqZ0RvcVU5MUVJeG1XSnpBZTVsSk9DOXhJN1hkTFg1M3BrSXo5MWM3Uzg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>거침없는 외인 매도...반도체 역대급 실적에도 급락, 왜?</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>거침없는 외인 매도...반도체 역대급 실적에도 급락, 왜?  YTN100조원 벌었지만 증가율은 반토막…외국인 올들어 232조원 ‘엑소더스’  한국경제삼성전자·SK하이닉스, 두번째 바닥 찍었나…“W자 반등 기대”  마켓인"내년도 삼전닉스 성장동력은 HBM4…엔비디아 루빈 출하 본격화"  ...</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>YTN</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE84MU9jNnEweUVaeWZ5emd5RFNjQmdEd3N2RDUweDViQnBKTVJsbnJXWGlHaDQ1TmY2VzFyMm1aUkFoLVktTUJFY0pLcXlIREtSQ1dveEwxYVpUNDdiZWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>[단독]망분리 완화 금융사 10곳, 보안계획만 세우고 이행 안해···내부망 해킹 노출될 뻔</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>[단독]망분리 완화 금융사 10곳, 보안계획만 세우고 이행 안해···내부망 해킹 노출될 뻔  경향신문경찰, 금융권 해킹수사 美 FBI와 공조…공격자 신원·활동 추적  연합뉴스“보안 담당임원, 경영진 제동 걸 정도 힘 실려야” [해킹에 뚫린 금융 ⑦]  IT조선[금융현미경]AI·해킹 위협...</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5IT2RzRnhNZmloc0luUTFHMi1iTnpuZWdra0NXdlFOdFBReEpLUFJtdkdOMV9reGJnaDZmTmJNVEdrbjZvbjczVndMZWhfajR5N201NF80bVZsUdIBX0FVX3lxTE1OclA5Q2EwWDN3b3paSUYwck9BRE5HM0doUE9ZWFladzduUlNuQVRNSExWWVgwR3dxbjVsR2tfZ1pKTEdUcEs5T1RTUTBKNHJ6X1gtTk54dTkzalI1SkZF?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>원화값 1330원대 강세…삼성전자 배당·美 금리가 변수</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>원화값 1330원대 강세…삼성전자 배당·美 금리가 변수  매일경제Google 뉴스에서 헤드라인 및 의견 더보기</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Jb0NSMmpTSnZzMHVwOEloSWZmRlBNcDEwN2RZTGwzcE5TV2FaZC1JS0FqaGgwdGlqTVpxMjh2aGRpYmp1d1hYcmY2amRiaXN6cXNfcg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>靑, 초과세수 활용 국채 발행 축소에 "부처간 이견 無"</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>靑, 초과세수 활용 국채 발행 축소에 "부처간 이견 無"  연합인포맥스靑 "'초과세수' 활용 국채 축소 범위 이견 없다…토론 통해 정리" - 머니투데이  머니투데이국고채 금리, 코스피 급락·외인 매수에 이틀째 큰 폭 하락  연합뉴스"그게 네 거냐?"…'63조 제로섬 게임' 벌이는 재경부...</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5jWi11SE4zRENIUHh1UmF3OS1ZYWN3XzZvLUVpcGs0enlWRncyRXd3UzFUT1JmNVkwVDZUUEdxU3VCNlRnOEFYeFQ0b1dacTVMWGdWZFdNT19MNzdVQ3RVbXBKSVhtYk5yRkZjUnRuU3M?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>[잇슈 SNS] 미 놀이공원서 또 롤러코스터 사고 “1명 사망·4명 부상”</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>[잇슈 SNS] 미 놀이공원서 또 롤러코스터 사고 “1명 사망·4명 부상”  KBS 뉴스美 테마파크 또 롤러코스터 사망 사고…연이은 안전 논란[이런일이]  노컷뉴스공중에 멈춘 롤러코스터, 1명 추락사…美 놀이공원서 또 사고 - 머니투데이  머니투데이Six Flags Entertainme...</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5CZTBncGdVYzRQTHdTQjZWMHk0R3FRdmJ5X1k0VzdrYVpubXZJMW9wN1hfa0RvV0FvSU5qM0xjNERLR0FybVctb00xbURGLTduZ3dfYWxmeTNISzdnOENpVF9RaEVJUQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>노동부 장관 “포스코 교섭 적극 지도…신안산선 사고 엄중 조치”</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>노동부 장관 “포스코 교섭 적극 지도…신안산선 사고 엄중 조치”  KBS 뉴스[기자수첩] 포스코 노사, 철강업·지역경제 위기 극복이 먼저다!… 대승적 자세로 합의점 찾기를  폴리뉴스 Polinews김영훈 "포스코 교섭 적극 지도"…직고용 갈등엔 "현장 찾겠다"  뉴스1포스코 노사 14일...</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5GdV9XNUJWZmtFQW82N2xHcVV5V184ZzFzcGVrdGVUVzJlZm1haWFPb2NXc0ZZRGtGWUQ2MmpNYTNlR3dyNldOQ1BkSnhieUdrZmhmNnR2aG9yWjQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>연준 '매파' 해맥 "제약적 정책 기조 필요"…이달 관련 언급은 안해</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>연준 '매파' 해맥 "제약적 정책 기조 필요"…이달 관련 언급은 안해  연합인포맥스뉴욕 연은 윌리엄스 “내년에 금리 추가 인상 필요 없어”  KBS 뉴스美연준 해맥 "금리 소폭·잦은 조정 바람직…인플레 고착 위험"  연합뉴스시카고 연은 총재 "금리 인하경로로 복귀하려면 진전 필요"  연...</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5DamUzb21IazZqXzNRQVlIYTc0VWxaVzRTTnhLNnJNRklseE1VYmdOelpFZEVxdWx0QkZoR0NPeEdXQlhHZDgwMGtGRHhXall1clo4elEtcFV1a3BQbWxiTjBlRHByalY0QTVrZmE3U2c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>임광현 “이 대통령 아파트 거래, 과세 대상 아냐”…증여세 과세기준 이하 판단</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>임광현 “이 대통령 아파트 거래, 과세 대상 아냐”…증여세 과세기준 이하 판단  한겨레임광현 국세청장 “이재명 대통령 아파트 거래, 과세 대상 아니다”  경향신문“대통령처럼 아파트 거래했더니 세무조사 받았다” 국세청장의 답변은  문화일보의사봉 두드리는 조승래 국회 재경위원장  뉴시스[2...</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>한겨레</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFAyS1lBbEg0RFVvNVIzZVlfSjBGU3dTNzM1aUtISEpjc3dCQ2lvNEZXOGQzV3E1MjdBeEhUU1MwdGtkQW8yNXc2WlFMdk05T0ltZVlJX2tNMVF0b0NlQUI2QlBXWXVtOG04anlpNWM2bmRIZw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>코오롱인더스트리, 채용전환형 인턴 모집…19일까지 접수</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 조성흠 기자 = 화학소재 기업 코오롱인더스트리는 제조 부문에서 2026년 채용전환형 인턴 채용을 실시한다고 13일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014039100003</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>한투운용, 펀드 한곳에서 검색·비교…'투자플러스' 출시</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 고은지 기자 = 한국투자신탁운용은 상장지수펀드(ETF)를 비롯해 공모펀드를 한곳에서 검색·비교해볼 수 있는 투자 플랫폼 '투자...</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014033800008</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>[특징주] 철강주, 백악관 대변인 알래스카 LNG 언급에 상승</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 임은진 기자 = 철강주가 백악관 신임 대변인의 알래스카 액화천연가스(LNG) 개발 사업에 대한 한국 투자 언급에 14일 장 초...</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014038300008</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>전날 급락했던 코스피, 상승 출발…1%대 오름세</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김유향 기자 = 전날 급락했던 코스피가 14일 장 초반 1% 내 상승세를 나타내고 있다.</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014037100008</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>[게시판] NH농협은행 금융투자자문, 키움증권 영웅문S에서도 이용</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>▲ NH농협은행은 13일 서울 중구 NH농협은행 본사에서 키움증권[039490]과 '금융투자자문 서비스 활성화를 위한 업무협약'을 체결했다고 1...</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014035100002</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>유통업계, 김장철 앞두고 절임배추 사전 예약 판매…할인 행사도(종합)</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 정수연 김세린 기자 = 유통업계가 김장철을 앞두고 절임배추 사전 예약 판매에 나서고 김장 재료 할인 행사를 진행한다.</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013159551030</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>오는 22일 '증평 일자리 이음 취업박람회'…212명 채용 추진</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>(증평=연합뉴스) 박재천 기자 = 충북 증평군은 지역 기업의 인력난 해소와 구직자 취업 기회 제공을 위해 오는 22일 증평생활체육관 1층 로비에...</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014036400064</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약, 마이크로니들 무균 제조소 구축한다</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 신선미 기자 = 대웅제약[069620]은 경기 화성시 향남 대웅바이오 3공장에 마이크로니들(Microneedle) 제조 인프라...</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014031000017</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>이형일 "반도체 다음은 서비스산업…입법 협조 요청드린다"</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>(세종=연합뉴스) 이세원 기자 = 이형일 부총리 겸 재정경제부 장관은 반도체에 이어 한국 경제를 견인하도록 서비스산업을 집중적으로 육성하겠다고 ...</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014029000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>유진투자증권, 현대오토에버 목표가↓…"피지컬 AI 매출 지연"</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 정회인 기자 = 유진투자증권[001200]은 현대오토에버[307950]에 대해 피지컬 인공지능(AI) 관련 매출이 본격화되는 ...</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014028200008</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>금감원 "韓, 바젤위원회 LEV 규제 평가서 최고등급 획득"</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 강류나 기자 = 금융감독원은 한국이 바젤은행감독위원회(BCBS)의 단순기본자본비율(LEV) 규제이행평가(RCAP)에서 최고 등...</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014028100002</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>하나증권 "신한 '롯데손보 인수' 이익불확실…보수적 접근해야"</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김유아 기자 = 하나증권은 신한지주[055550]가 롯데손해보험[000400]을 인수하기로 한 결정에 대해 향후 자본 추가 투...</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014024600008</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>SK증권, 한화오션 목표가↓…"상선 부문 피크아웃 우려"</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 곽윤아 기자 = SK증권[001510]은 14일 한화오션[042660]의 목표주가를 13만4천원에서 11만원으로 하향 조정했다...</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014025700008</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>롯데손보 인수 신한금융…증권가 “최선인지 의문” [오늘 나온 보고서]</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>NH證·iM證 보고서  주주환원 악영향 제한적이나 보험사 빠른 회수 가능성 낮아 추가 증자 가능성도 부담으로증권가가 신한금융지주의 롯데손해보험 인수를 두고 기대와 우려 섞인 시선을..</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/stock/12175145</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>“코스피 급락했는데 괜찮나요?”…국민참여성장펀드, 손실 방어 어디까지</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>2차 국민참여성장펀드가 오는 15일 판매를 마감하는 가운데 최근 코스피 하락세가 두드러지면서 손실을 우려해 가입을 망설인다는 목소리가 일부에서 나온다. 국민참여성장펀드는 지수를 그..</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12175134</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>“지갑사정 나만 힘든가요?”…IMF, 한국 경제성장률 3.3%로 확 올렸다</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>7월 2.6%서 0.7%P 높여 반도체 수출 호조로 성장세 “중동전쟁發 리스크도 상쇄” 美성장률 4년만에 넘어설듯 고물가 대응책 마련은 숙제국제통화기금(IMF)이 올해 우리나라 성..</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12175070</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>공동명의가 불리할 수도 있다? … 세금폭탄 피하는 1주택자 ‘꿀팁’</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>잘못 알려진 부동산 세금상식 Q&amp;A부동산 세금에서 경계해야 할 것은 복잡한 규정만이 아닙니다. 일부 요건을 생략한 채 널리 알려진 설명도 잘못된 의사결정의 원인이 될 수 있습니다...</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174610</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>“회의하시죠, KTX 시간 좀 볼게요”…금융사는 서울, 금융위는 세종</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>중앙행정기관 44곳 이전 금융위 등 27곳 내년 이전 외교·통일부 등 17개 기관은 2031년까지 청사 지어 이동 공무원 주거·통근 부담 커져 민간 이직 등 인력 유출 우려 정부,..</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174867</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>삼전닉스 자사주 매입 끝나자 주가 와르르 … 코스피 사줄 사람이 없다 [머니닥터 시장진단]</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>코스피 수급 여건 심층분석코스피가 12일 6500선이 무너진데 이어 13일에는 장중에 6000선까지 무너졌다. 반도체 기업들의 실적 개선에도 국내 증시가 오히려 뒷걸음질 치면서 시..</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/stock/12174815</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>"시민 지켜라"… 로봇개, 첫 도심순찰 나선다</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>앞으로 네 발로 걷는 로봇이 공원과 산책로를 순찰하고, 편의점에서는 성인 인증을 거쳐 무인 자동판매기로 주류를 구매할 수 있게 된다. 반도체와 자동차, 조선 등 제조 현장에는 사람..</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174772</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>석달만에 … IMF, 올 韓성장률 3.3%로 상향</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>국제통화기금(IMF)이 올해 우리나라 성장률 전망치를 2.6%에서 3.3%로 석 달 만에 0.7%포인트 높였다. 중동전쟁 충격에도 강력한 반도체 수출에 성장률이 높아질 것으로 본 ..</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174769</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>[단독] 정부, 수소차 늘린다더니 보조금은 9년만에 줄인다</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>내년부터 수소승용차 한 대당 국비 보조금이 올해보다 11.1% 줄어든 2000만원으로 인하된다. 정부가 수소승용차 국비 보조금을 인하하는 것은 2018년 이후 9년 만이다.
+13일..</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174770</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>韓기업 해외원화 조달 숨통 … 신고기준 10억→500억 완화</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>재정경제부가 국내 기업이 해외 금융기관 등에서 원화를 빌릴 때 적용되는 사전신고 기준을 연간 10억원 초과에서 500억원 초과로 높이는 내용을 담은 외국환거래규정 개정안을 13일 ..</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174771</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>시중은행 '골목 사장님 비대면 대출' 경쟁</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>시중은행들이 개인사업자 부동산담보대출을 비대면으로 내놓고 있다. 영업점을 찾기 어려운 자영업자의 대출 문턱은 낮추고, 담보를 잡아 건전성 부담은 줄이겠다는 계산이다.
+13일 금융권..</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174757</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>[포토] 수출입銀, 고립청년 자립지원</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>[포토] 수출입銀, 고립청년 자립지원</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174758</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>'7000억 승부수' 신한금융…롯데손보 품고 '리딩금융' 탈환나서</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>신한금융그룹이 롯데손해보험을 인수하며 '리딩금융' 탈환에 나섰다. 그간 취약했던 비은행 포트폴리오인 손해보험 사업을 강화해 KB금융에 3년 연속 내줬던 금융지주 1위 자리를 되찾겠..</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174755</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>카카오뱅크 'AI적금' 출시…저축목표 따라 맞춤형 조언</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>카카오뱅크가 금융권 최초로 인공지능(AI) 코칭 기능을 적용한 저축 상품을 출시했다.
+13일 카카오뱅크는 'AI 목표적금'을 출시했다고 밝혔다. '부모님께 드리는 안마의자' '내년..</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12174756</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>교황, 폐 결절 제거술 위해 로마 병원에 입원</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>교황, 폐 결절 제거술 위해 로마 병원에 입원  연합뉴스교황 레오 14세, 폐 절제 수술 뒤 ‘암 진단’ 받아  한겨레바티칸 "교황 레오 14세 폐암 진단…수술 성공적" - 머니투데이  머니투데이교황청 "레오 14세, 폐 결절 수술 성공적 완료"…남미순방 갈듯  마켓인[속보]교황 레오1...</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9Hb1JpRG41NHJVQXNSYW9sbWpMOTVTajJUX1V2a05YNUE1X01ZTUh2WUpWcXk3R3lJWDhwZG5qQTQ5NXNCa1V1WnVTTTZSSHNOaUpEZVhVUHlHS03SAWBBVV95cUxNbk50bmV5RXN0NkZYN2tCa1d6dXFlVzJMYXJCOUl1Ylo2WTZjLXVSUkpkOTYyV1ByYkJiNmlZc0E4RjFjYzVsTFE4TTJ2Q3FSQ2JaclJxdVNwNHcta0d4M0M?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>프랑스 "냉장고 해킹 피해 슈퍼 700곳…식량안보 건드려"</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>프랑스 "냉장고 해킹 피해 슈퍼 700곳…식량안보 건드려"  연합뉴스TV佛 마트 냉장고들 해킹당했다... 온도 50도 폭주 ‘먹거리 테러’  조선일보냉장고 속 음식 다 버렸다…프랑스 슈퍼마켓 700곳 날벼락  마켓인50도로 달궈진 냉동고…프랑스 마트 뚫린 날 "AI, 곧 가전제품 점거"...</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스TV</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1VemdGcUxiaE9yMGZ0STFwTkE5QVJFNzBsRjBONkJiWUdBSzBVX3BPQ2xmLURGUVp5YjM4emFPQzhVcVlwMV82eW5QTk9ONmc5dGQxd19qY2VocWlobzVUN2FoTzFJQnM?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>트럼프 “미국, 우크라이나와 정보 공유 중단 안 했다”</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>트럼프 “미국, 우크라이나와 정보 공유 중단 안 했다”  VOA 한국어 홈페이지‘경유 딜’ 우크라 반발에… “美, 종전 협상단 방러 보류”  동아일보젤렌스키 "트럼프 '휴전' 언급에 공격 자제했지만 러는 계속"  연합뉴스"이런 기름값 처음" 비상 걸린 미국…트럼프 ‘푸틴과 딜’ 발칵  ...</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>VOA 한국어 홈페이지</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFB6WDNka1BrSklyOWxFNlRBdnR0WTB1UGtCd0xSYnlJUXlZQXBrcDR0MTFZZGh6YkxaZDBfVnlIQ2JrSXZJd3BTNWhpa0YxS0NkeDNFZTFILUhicjN2LVp6dVgwR3BOdW5tSVpYejd4d3pHME3SAXZBVV95cUxPaFY5MjIydVg3N3RsVV8ya1dUeUtiNkdRSjdWeFBIUXpvTEFWYkpOeUxFVUZ6S2Nqd2tFQXFHelNKbkk5LVBzSGUwTm1IV2hPelBLVTljY0F5WV9yQTY1Qzk5M0pHbG9XMkYtMXhMQVNMNnNPQmN3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>러시아, ICBM급 초장거리 6500km 순항 미사일 32기 도입…원거리 타격망 확충</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>러시아, ICBM급 초장거리 6500km 순항 미사일 32기 도입…원거리 타격망 확충  글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNMHN2OGtVRDdiM3VIVUNYQUNSbjd5bVVyd2h0c0RTYVJFTU1GQXBqeTNZLXlndTEzY1FmY3pjSHpfbGpxeEhfS1lyOXJEYW1YQUxTNFFpWWtNemZvMWwydE1FaUxsclZXUkdLVGx3a0UxZk52YjVFcWJjeUx6QmFaT0FhQUZJMExQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>이란 지원 받은 후티, 사우디 공항 연일 공습…미사일·드론 섞어쏴</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>이란 지원 받은 후티, 사우디 공항 연일 공습…미사일·드론 섞어쏴  한겨레트럼프 "이란, 후티에 사우디 공격 지시…의도적으로 유가 올리려 해"  연합인포맥스사우디 아람코 본사 미사일 공격받아 화재…후티 공격 추정  연합뉴스사우디, 후티 석유 시설 보복 타격...후티, 재보복 '난타전' ...</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>한겨레</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBjc0haenYteU8yYzY1bndkWlh4blFwVkRybmUtWThwTGZtWldFQkRuZWhYVWMwX3FCWHJWWVZ1Q1lXTDkzNjBtZFNzN0VEck9rNGJwYUpnUF9BeGxZNVpjeE54VVVubUU5RVI0XzY4YWJLNE0?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>'트럼프 장남 前연인' 그리스 美대사 잘린다… 백악관 "사퇴 요구"</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>'트럼프 장남 前연인' 그리스 美대사 잘린다… 백악관 "사퇴 요구"  한국일보‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임  경향신문"가족은 아니었다"…트럼프, '아들 전 약혼녀' 그리스 대사 해임  마켓인백악관, '각종 비위 의혹' 그리스 대사에 "사퇴 요구했다"  연...</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>한국일보</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1xaVhYRWVHcGIxR0RMUkVBV0dLZkZXWUk0Nl9GbUNFZFlhOVJGdkhMSjdFTEZHRVpoZzVnbXFQTHN1RG5Wd0VNMENxMTA4MmVJRklBbnZXcUtDTmpObU1TNzZYQXlZUlZYaWw4YmhB0gFzQVVfeXFMUG9JWWtSRURaRUJFZW1kMVZrOHFCSXZlVERlUkxoOS1maU8tNlFwT3Jmc1Jsc1hxYkR4OGxORkxIUmpyOTZWMnZlUUtob0FPVnRoYzFybU96Z3hjQVNfaldBRUZQZlpPVHJJQ1RYWUhXa1NNdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>北中 국기 내걸린 신압록강대교…12년 만에 개통 임박 관측 - 조선비즈</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>北中 국기 내걸린 신압록강대교…12년 만에 개통 임박 관측 - 조선비즈  Chosunbiz北中신압록강대교 개통 임박했나…북측 관문 북중 대형국기 포착  연합뉴스12년 멈춘 신압록강대교, 왜 지금?…"북중 경제적 타협 신호"  뉴스1[특파원리포트] 두 개의 다리와 북한의 몸값  세계일보북...</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeHltSzRtbUs3Z2FuNVRObkZKOGdhbDZneWRxLWFxY3dXSWwxSHdCdDFXd3ExUFVLRm4yVXJqejBRT1FRa0VlcmRzeWdTZjZTS1R0Z3Z3WkRreFJuUmt5QVpJRkwwNkRzMVQ2dTJqQ2sxVWpHT2J0VHhfd19WLW9EUndSdGpuZktmQjZIYl8yR21rMGxCNkxaRFBQMDR6QdIBsgFBVV95cUxNNlYtZUNUQUhiMnd2U3d6eVBjNHhSRXdGWmlwREhQQ0ZSclFMUXRtQXI5OVZrbWtzNG1nOUZKSFBWTkx3MzJjclBxVmpkNW9yX1lTLW9EVGVOQlFPSGQyVW9kTFU5d1FKY0k5bHZRUU03TmFkMnVXWDdzWXRXU1ZsbDIwbmVrY1lfNThrVzZFN2l4aHd2alhBLS1yOGxGTnV3OWFQWjZHQTFsTVR0QlVmU0Fn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>러 데이터센터 드론 피습에 중앙아시아 앱 장애..."우크라 공격"</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>러 데이터센터 드론 피습에 중앙아시아 앱 장애..."우크라 공격"  YTN우크라 드론이 러시아 데이터센터 때리자 중앙아시아 앱 '멈춤'  연합뉴스러 미사일 공격으로 부상한 여성 옮기는 구조대  뉴시스러 데이터센터 피격에 카자흐 주요 플랫폼 마비…디지털 인프라 의존 한계  아시아투데이美 ...</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>YTN</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9PdERfa2JGWlk1clhEZ2xqV0JFeHN3ZXV5bFVFLUxyNndlUU9qblBZa0hQN0dfX0ZnaVowZnFUWUNBRi02OTFLRV84ODFwdVZrZ1NNakF5WExCLThGeHc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>이란군 "호르무즈 동부 선박 주시…금지구역서 유조선 화재"</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>이란군 "호르무즈 동부 선박 주시…금지구역서 유조선 화재"  연합뉴스"호르무즈 선박 피격 2주간 24건…개전 이후 최다"  연합뉴스이란군 “호르무즈 동부 선박 주시…금지 구역서 유조선 화재”  KBS 뉴스호르무즈 유조선 연쇄 공격… '중동 원유' 수출 회복세 또 꺾이나  마켓인호르무즈 ...</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5yTm14NmI1c1RXcXk2WWhfOUlTRWp3ZDNsZFlLdjhLRkprd09jQXd0dFZuZ1BxdExBZG9IUjByVDZ1VGY3VW9nTUNWVUhnbkxnN1Y3SjVDNnkyZG_SAWBBVV95cUxPTlhjMkFldm5rWXJ5UUc1eFphTTdBekU2MVpmVy1vYmNZOVRmQUluekc4SXUyc25Wd1ppUnRxWE9HYU9lUmRnaFZ5WFkzWEhjRThRRjduSXU4OENnanBENU0?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>트럼프 “내달 亞 방문중 김정은 만날수도”</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>트럼프 “내달 亞 방문중 김정은 만날수도”  동아일보트럼프 "다음 달 김정은 위원장과 만날 수도...흥미진진할 것"  YTN 사이언스[열린세상] 북미 정상회담이 불러올 후폭풍  서울신문트럼프, 북한에 또 러브콜…“김정은 만날 수도”  KBS 뉴스트럼프 “내달 김정은 만날 수도”… 북한은...</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9QektUZlgyUXJqZ2VnZEt2WnE1WUtqU1JLR3BWREMzWGxXQlBJS29zMjFDTlcyVHRfRzNpcHdzbkdVbVFQcU9LTjc1WlRWb010SWpidGZXVDFwdmlKWC1pQ1BRVEN1SFh5WjM4VEdINjNIczjSAWZBVV95cUxOejRBaUpONWo0MWs1RDk2UVphSjE3RHNOdUVtOHoybTNzWnBSaTUxcnduRUhsdE5VZENQRnZOdXBVdXRVa01YdUVpT2pUTkFEMmJhNDBxUjNmQ2FsblhEc0FtNGFzTVE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>[브라질증시] 이보베스파 1.04% 하락…룰라·플라비우 지지율 격차 주시</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>[브라질증시] 이보베스파 1.04% 하락…룰라·플라비우 지지율 격차 주시  뉴스핌다급한 룰라, '소상공인 부채탕감' 대선 결선용 선심법안  연합뉴스브라질 대법원, 보우소나루에 부친 면회 허용  문화일보트럼프 ‘블루 타이드’ 마지막 퍼즐 완성하나…‘보우소나루 정치 왕조’ 계승자 [더 비저...</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>뉴스핌</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9RUFJfV095U1NUblZMUnNrUGFGem94aU5Pb2xuT1cyd0lJcGdvWXFjdHo4VzVvelV1Qi1yRTBnRGNreldkNzMyUFQ5Q2VPdFNTaDdLM1dldG1aa0t2?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>러시아 '페스트 의심 사망'‥국내 위험도 낮지만 검역 강화</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>러시아 '페스트 의심 사망'‥국내 위험도 낮지만 검역 강화  MBC 뉴스국내 페스트 종합위험도 '낮음' 유지…러 입국자 감시는 강화  연합뉴스[크랩] “치료 안하면 100% 사망” 미국·WHO도 러시아에 정보 공개 요구  KBS 뉴스[한마당] ‘원인불명 폐렴’ 미스터리  국민일보질병청 ...</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>MBC 뉴스</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1ld25YY1JGSC1SSDMyTVVvSW5RRmNLcHJqVDVZOVdVSFh3bHNQNXF6ZkJZeXcwd2VGUjM3NTdCclNhMHF3MnAxdEp0WW5DcVJjZ21DaDg2WGFPNTNvWWphaTgwdTFVaG16QzdaaVBqNkxaelotODl30gF3QVVfeXFMUFhRZXdDaXltSThQRklGZ0dKdDNrLXFiRzBPcnRhVVhUUEVJNjFkc3pqaWQzTl83VTFUM0FwbUtFVVJqNVFlM3hGeXI3YW5aV3NzREZJbXN4S19YbTNKWm9FZnQwU0FFRmFKaC1HQ25nLTYxWnYwSVE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>WSJ "이란, 美 중간선거 후 전쟁 대비…지상전 시사"</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>WSJ "이란, 美 중간선거 후 전쟁 대비…지상전 시사"  한국경제이란, 인접국 지상군 투입도 시사…美중간선거 이후 공세 대비  연합뉴스美재공습 나설라…이란, 핵시설 방어·전시태세 전환 '집중'  마켓인이란 외무부 "미국 답변 검토 후 중재국에 입장 전달"  MBC 뉴스이란, 美의 이란...</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB3eFNlRFh5ZHpLUUZfejczSXM2bmlpLWRHVkJrYi1RSS1KM1pFTTM0ZXAxQlBJVkNuN2Z1cXpNczBVSmdPaTBNb21OcjNTY01rV1g0SUM4eXhtZw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>구글, 최상위 AI모델 '제미나이 4 아르곤' 정식 출시</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>(샌프란시스코=연합뉴스) 권영전 특파원 = 구글이 최상위 인공지능(AI) 모델 '제미나이 4 아르곤'을 일반에 공개했다.</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014033100091</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>세계의 날씨(10월14일)</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>(09:00)</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014035400009</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>유엔 국감서 '北지뢰' 대응 공방…유엔대사 "안보리 대응 미정"(종합2보)</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>(뉴욕=연합뉴스) 임수정 김연숙 특파원 = 13일(현지시간) 미국 뉴욕 주유엔 한국대표부에서 열린 국회 외교통일위원회 국정감사에서는 북한의 비무...</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014003052072</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>"트럼프, 지난주 네타냐후와 '중간선거 전 이란 공격' 논의"</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 고일환 기자 = 도널드 트럼프 미국 대통령이 중간선거 이전에는 이란 공격이 없을 것이라고 밝히기 앞서 대규모 군사작전 가능성을...</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014036700009</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>日정부, 경제·재정 소개 영문책자 발간…"해외 우려 잠재우기"</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>(도쿄=연합뉴스) 조성미 특파원 = 확장 재정을 통한 경제 성장을 추진하는 다카이치 사나에 일본 총리가 내각의 경제·재정 정책을 중점적으로 소개...</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014032700073</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>사우디 아람코 본사 미사일 공격받아 화재…후티 공격 추정</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 강훈상 기자 = 사우디아라비아 국영 석유사 아람코의 본사 단지 내 건물이 13일(현지시간) 밤 공격을 받아 불이 났다고 사우디...</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014026500009</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>'자금세탁 방치' BofA에 1.6조원 벌금</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이성한 기자 = 미국 재무부가 자금 세탁 방지 및 제재 준수 의무를 심각하고 반복적으로 위반한 책임을 물어 뱅크오브아메리카(B...</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014025100009</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>알바니아 '플라밍고 시위' 넉달째 격화…대학생들도 화염병 가세</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김용래 기자 = 동유럽 발칸반도 알바니아에서 도널드 트럼프 미국 대통령 사위의 리조트 개발에 맞서 불거진 거리 시위가 대학생들...</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014024300009</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>뉴욕 연은 윌리엄스 "내년에 금리 올릴 필요 없어"</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 주종국 기자 = 존 윌리엄스 뉴욕 연방준비은행(연은) 총재는 연방준비제도(Fed·연준)가 올해 한 차례 더 기준금리를 올리는 ...</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014023500009</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>후티 공격에 사우디 진땀…간판급 투자회의 원격참여도 허용</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이신영 기자 = 사우디아라비아가 이달 말 열기로 한 간판급 투자 콘퍼런스 '미래투자이니셔티브'(FII)를 원격으로도 개최하기로...</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014022900009</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>BBC, 13조원 손배소 낸 트럼프 상대로 '강제 증언녹취' 요청</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장재은 기자 = 영국 공영방송 BBC가 자사를 상대로 도널드 트럼프 미국 대통령이 제기한 손해배상 청구소송에서 트럼프 대통령 ...</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014022800009</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>뉴욕 센트럴파크 마차, 150년 역사 뒤로…내후년부터 금지 전망</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>(뉴욕=연합뉴스) 김연숙 특파원 = 미국 뉴욕 센트럴파크의 명물이자 관광 상품이었던 마차 운행이 2028년부터 금지될 전망이다.</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014016100072</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>교황, 오른쪽 폐 일부 절제 수술…폐암 진단 확인</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이지헌 기자 = 레오 14세 교황이 예정대로 흉부 수술을 받은 뒤 폐암 진단을 받았다고 로이터 통신이 교황청 발표를 인용해 1...</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014017800009</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>엘니뇨에 남미 강 수위 상승…이타이푸·야시레타 댐 수문 개방</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>(부에노스아이레스=연합뉴스) 김선정 통신원 = 엘니뇨와 관련한 집중호우로 남미 파라나강 유역의 물이 불어나면서 브라질·파라과이·아르헨티나 접경 ...</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014015700009</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>美 금리 급등 충격 월가로 번지나…대형은행 실적 '희비 교차'</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>(뉴욕=연합뉴스) 임수정 특파원 = 미국의 금리 급등으로 채권시장이 요동치는 상황에서 3분기 실적을 발표한 대형은행들의 희비가 엇갈렸다.</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014009700072</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>NASA 화성탐사 차량 45.2km 주행...지구밖 최장 기록</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>NASA 화성탐사 차량 45.2km 주행...지구밖 최장 기록  YTN화성서 45.2㎞ 달린 퍼서비어런스… 지구 밖 로버 최장 주행 - 조선비즈  Chosunbiz“지구밖 가장 많이 달려“…NASA 화성 탐사선 ’신기록’  연합뉴스TVNASA 화성탐사 로버 퍼서비어런스, 지구밖 최장 주...</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>YTN</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE91bGwzNEthTTN2bWNHYzFkTTF4RjAwNDdBN1gyNVo2cjhXdUEyYnJXMm94NUZMZERkY3A1QWtVZ2ZPUzYyNjUwWDBuLVdUekRfb19zUkUwUWhmZGpUc3c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>발러 모티스 - 리뷰</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>발러 모티스 - 리뷰  IGN Korea발러 모티스  IGN Korea</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>IGN Korea</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1hTmVoMVhXX0JDTXBWdUFOekRGaFUzWVlpU0JfN28zNFlmNlNzT1JUNE1SUGtkVjlFNFhBdGlCTEVFVWtfam9iMkVtOWtnN1ZqNXVGNkdxRFdUc0pvUDRZUTZyXzloSEdhVlE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>포스텍·DGIST 연구팀, 가시광선으로 상온의 물에서 고결정성 MOF 합성</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>포스텍·DGIST 연구팀, 가시광선으로 상온의 물에서 고결정성 MOF 합성  전자신문</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>전자신문</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5ScWtpZWR5bm9wdzVFSHNuWXlZM0xKbUN0WXpvZlFSb0ptUEVLUHNxeTZQaEdkZG9qNVdmMFAwN2lkdUtaczZ5a2lOZw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>애플, 4년만 A19 탑재한 신형 애플TV 4K 공개···가격 44만 원</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>애플, 4년만 A19 탑재한 신형 애플TV 4K 공개···가격 44만 원  글로벌EApple, 새로운 Apple TV 4K 공개  Apple애플, AI 기반 Siri 탑재한 신형 애플 TV 4K 발표…사전 주문 시작  Investing.com 한국어애플, 2017년 출시 애플TV 4K ...</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>글로벌E</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1rSnVVaE04eVBDM1V6Tzl3czRMUEFFZ3BZRXlwUk5td1BrWjJ1WDNUUkhwbWotblY0cU53azJaTHpPblIzM1FTcWt5NHdieTNmYkZibmFGWVhZVDdYUS1mZE1jWGlVVGNKZ1HSAW9BVV95cUxQaUxEYmQ2SWJUR1YtTEhlVWl3bGxuRzR6X21idmoyT0pKQklRT0luV0c1dXN2enFUUmVjLS1udjlRN2tWeHluX3d6REFQRllmTW45d3pfVkhGZUhqSFotSmdlSEtnMVJndmhUWU81VVU?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>원플러스 16, 9,000mAh 배터리·2억 화소 카메라 얹고 시작가 1,700위안 올렸다</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>원플러스 16, 9,000mAh 배터리·2억 화소 카메라 얹고 시작가 1,700위안 올렸다  위키트리</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>위키트리</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBYcm45OGNsR0RfV3owZE5sTTRiVVpfSU12UkhqbGM5d2gwV1QzWFZxei1YUV9iMnlnbTdaWF82cEQzREtVRV9pWTR6QVJIbGg4UF9uaUx3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>“노벨상이 다음 연구제안서 채택에 도움 됐으면”</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>“노벨상이 다음 연구제안서 채택에 도움 됐으면”  문화일보남극 빙하를 거대 망원경으로...'유령 입자'로 노벨상  YTN 사이언스[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상  한국아이닷컴한국 중성미자 연구, 20년의 성과와 남은 숙제  이로운넷벨기에 13년 만에 또 노벨 ...</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>문화일보</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1TY2ZCNzFXa1FuWExSX1B0R0lNZ1NrWmtLdFdEWkJDYVZpVmZ5SlZCdXdBZ0NEZGg1NGJqMFgxMlg4LWxrd3VCYlc4NUVTSkNN?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>[영상] 스튜피드 네버 다이즈, ‘DEEP BITE’ 아트 편 공개</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>[영상] 스튜피드 네버 다이즈, ‘DEEP BITE’ 아트 편 공개  게임뷰'스튜피드 네버 다이즈', 독특한 비주얼 소개하는 개발자 해설 영상 공개  인벤[게임뉴스] 펄어비스 및 그리프라인 소식 외  게임뷰음악부터 만들고 게임을 설계했다... 고바야시 히로유키가 밝힌 '스투피드 네버 다...</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>게임뷰</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFA2amxrUE9tWEROM0xheVpOMktXeWtzc0RQc2F3OTZMbWp1VkJYMmJTWV9ZaUFjUUxlN3lOV09Sa2sxRjRTQTFYZnNJdFBqREZMdF8zdjhEaUJDTk83N3FFNlNfWHc2NXVZcUE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>ARCTIC BioniX P12 A-RGB 쿨링팬 서린 [써보니]</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>ARCTIC BioniX P12 A-RGB 쿨링팬 서린 [써보니]  위클리포스트</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>위클리포스트</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBDMXVkU2R0QVpLM1dpMGY1azZVVmV1bUxvQkd5QXNucExsRmVGbm1oaWZzZGNVdHdCSzVpSHFfUnlfaGJoZkIwbm9JV0NZQlBwWXRkTzRCcUg3WDFHeGpZRW9UOUV4VjVBRjIw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>페이커·제우스 사인 품었다… GALAX 지포스 RTX 50 시리즈 ‘아시안게임 국대 패키지’</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>페이커·제우스 사인 품었다… GALAX 지포스 RTX 50 시리즈 ‘아시안게임 국대 패키지’  디지털포스트클릭나라, GALAX 지포스 RTX 50 시리즈 ‘아시안게임 국대 패키지’ 적용  위클리포스트</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>디지털포스트</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBCdTdmYnhiZVhiZVpBMm82b0FjQ3h0TFdVQnVKUUVyMzR2UVBVMkpHWFpKcFFuQVJoT1hfczNjU2hObmw0dHZ3T0p3MWFxTXEySlRpMnhYZ1pYVzA5VGxYbmYtMHNaSUpIYXJV?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>헬다이버스 2에 프리미엄 저격총 배틀 패스인 '권한의 범위(Scope of Authority)'가 발표되었습니다.</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>헬다이버스 2에 프리미엄 저격총 배틀 패스인 '권한의 범위(Scope of Authority)'가 발표되었습니다.  GameGPU</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>GameGPU</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNME92UVZIa0ExWVYzMlJJamhNTXhqeGctNU9SUXN6VGJIelZoMFAwbGhXNjJ4NGxVQkdlazF0dkpHcFM5Vjh3M3hNa2c2dk93X0JqU1l5eWtFNEZMUHpNeVpmN3hIUmo0SHl6MEotSWYwNzRvMUY3OTVNRFFmZzlDZkd3TUdxbGVaUEktWGYxMXRJNHdZSW9IZ0pWZE10ZHlQd2ZodHRGbmxELTJBTnVCMXVEQUdvT2JtRy1IMA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>목성 탐사선 주스 정밀위치 추적에 한국천문연 나선다</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>목성 탐사선 주스 정밀위치 추적에 한국천문연 나선다  중도일보유럽 목성 탐사선 '주스' 추적에 韓 우주전파관측망 투입  뉴시스“목성 얼음위성 생명체 비밀 푼다”…韓 전파망원경, 유럽 탐사선 정밀 추적  헤럴드경제천문연, ‘한국우주전파관측망’으로 목성 탐사선 ‘주스’ 위치 쫓는다  Don...</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>중도일보</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9HRlhzVy1hY2Y1RjFicDNVWlhGTEI0YTBrMHhDWGhWOWF5ZTQ1UHFJbkRIVFNsQ0xJa05LajB6T0tZSmJDYUV4d1hkbjNiMFVNYzV2U0ZUR3Q4eDh5MUMybnRqZUw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>캐슬바니아: 벨몬트의 저주 - 리뷰</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>캐슬바니아: 벨몬트의 저주 - 리뷰  IGN Korea[리뷰] 채찍으로 날아다니는 화려한 악마성, '캐슬바니아: 벨몬트의 저주'  디스이즈게임캐슬바니아신작 '벨몬트의 저주' 10월 15일 출시, 무료 데모 이미 공개  디지털포커스18년 만에 정사로 복귀, 캐슬바니아: 벨몬트의 저주  게...</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>IGN Korea</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNeTJ4NVdEQnVvWkNEdFJTZVZQTUVIVUgtMElWaVBTT0hVTnBHTmRDQmRxNTVIYm9iSmxWOFRqUEJ0dWw1ZnhUbHlyQWxfellrWWdsRnBwV0diQkpWbExUUk1qa1FYMDBNVG1Lbm9jLU9xemtvS1Faa0FuMlRzMl9BQzRPUGwya0FoaGRXZjZkWTdHdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>'하우 투 피시', 출시 두 달 만에 이용자 1,000만 명</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>'하우 투 피시', 출시 두 달 만에 이용자 1,000만 명  인벤</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>인벤</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBKWWQ3eVBxdXZBdHFxeXNOb0M2ZnJueXlDQlFFU21xblpuNnFwNVpBTFNwcTZkRk15WlEwUlcyWnpiaTliS290RS1WM3ZNYmViX2pGNUN3OU5nS1pHY1E?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Battlefield 6가 시즌 5 보너스와 함께 EA Play의 플레이리스트에 추가되었습니다.</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Battlefield 6가 시즌 5 보너스와 함께 EA Play의 플레이리스트에 추가되었습니다.  GameGPU다음 주에 Xbox 콘솔에 40개의 새로운 게임이 출시됩니다.  GameGPU라스베이거스에 데드스페이스 콜라보까지, 배틀필드6 시즌5  인벤배틀필드6, 출시 1년 만에 게임패스...</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>GameGPU</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbTI2aTZHYVRSMkd1MDhteFVEOHkzdGpyb2ttMVFfc281NnhTbG1SdHRXaVBhczZOekhTcG9LSXhyV3Zrb0xfLUcxcUNPcm8wdm53N3JTNXFhUTRKXzZqdHV0S0lzdE5MQ2xOd2ZocGMyTzZnclp1N3RXaGdWVDJNeTZqaXVZVjRJQUNteUE1WVBqU21XM0VZeTRnX0RMZ2hYRkNVNU1sLTVOdUN3Rzl0TmtJeTRwOG9jRXJTLWdTQ3BLV3RnYUZn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>AMD Radeon RX 9070 XT AMDLSS5를 사용할 때 FPS가 70% 감소했습니다. Resident Evil Requiem</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>AMD Radeon RX 9070 XT AMDLSS5를 사용할 때 FPS가 70% 감소했습니다. Resident Evil Requiem  GameGPUAssetto Corsa에서 DLSS 5 출시 Radeon RX 9060 XT 4K 해상도에서 30FPS로 재생 가능  GameGPUCy...</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>GameGPU</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNk95eFZMLUhTRDFyQVpOZVZsVkU1SzQxTVRPdEhxRmV1M2xNUkg4R0xzWEdSb3ZUZE9VOXVxXzlnaEpnWGswV2YtbTg1RFVEQW90TE5CYzdPYy0zVFdUQ2NwNGdqQnhpcXBPQnJsaDgwdkhEZXYyU2RWckRDNDFkXzVRcXRnaXlpd2dITDFqNVBEeUQzX25zczR2Y0h5NnFWVEFuSklsekdoVDNSZUVqLWJ1SU1ueVVzS0ZaZg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>세계철강협회 내년 총회 서울 개최…포스코 회장, 유치 앞장</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장보인 기자 = 내년 세계철강협회 총회가 25년 만에 서울에서 열린다.</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014033700003</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>에이피알 "美아마존 행사서 역대 최대 성과…유럽서 검색어 1위"</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이상서 기자 = 에이피알[278470]의 메디큐브는 아마존의 대규모 할인행사인 '프라임 빅딜데이즈'에서 큰 성장세를 기록하며 ...</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014033000030</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>쿠팡, 유명 먹거리 모은 '미식관' 출시…로켓프레시 배송</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 조민정 기자 = 쿠팡 로켓프레시는 인기 셰프와 전국 맛집, 트렌드 먹거리를 모은 미식 전문관 '하우스 오브 테이스트'를 오픈했...</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014031400030</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>AI 반도체 성능·전력 한계 넘는다…'K-문샷' 위원회 출범</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 조승한 기자 = 과학기술정보통신부는 14일 서울 중구 달개비에서 K-문샷 반도체 분야 운영위원회와 기술위원회를 출범한다고 밝혔...</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013169500017</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>물길·양식장까지 한눈에…충남도, 드론으로 갯벌지도 구축</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>(홍성=연합뉴스) 김준범 기자 = 충남도는 드론을 활용해 가로림만 갯벌의 지형과 물길 등을 디지털 지도로 구축한다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014034100063</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>"시그니엘 이불 집으로"…롯데호텔, 침구·욕실용품 백화점 판매</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 구정모 기자 = 롯데호텔앤리조트는 송파구 롯데백화점 잠실점 9층에 '해온'(HEON)을 비롯한 자체 브랜드(PB) 상품을 판매...</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014026200030</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>'♥박위' 발목잡힌 송지은-잘나가는 한선화-3크릿, 엇갈린 시크릿 17주년[SC이슈]</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>'♥박위' 발목잡힌 송지은-잘나가는 한선화-3크릿, 엇갈린 시크릿 17주년[SC이슈]  조선일보Google 뉴스에서 헤드라인 및 의견 더보기</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQc1poUno5RWpuUUo2YUFCMVlLbHhDMl9hci1rTS0yZFVGYnBualBBRXZ6T3RocVNqU1lURE1GNzRiZmNoSHBuTHEwblNIdlY4UWNNbWNpUnk2dDJkZHlGdjZ0dUI4VTViSnJfWWlmRTlLRXJIVVJXdHEtVHN0eGpLcERZS1BSVWdJZ1lzRUtSQnN4Q0hx?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>[주간! 대중문화] 연상호 신작 ‘실낙원’…류혜영, ‘킬링타임’에서 액션 도전</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>[주간! 대중문화] 연상호 신작 ‘실낙원’…류혜영, ‘킬링타임’에서 액션 도전  KBS 뉴스AI로 되살린 아들 vs 9년 만에 돌아온 아들…연상호 '실낙원'  연합뉴스김현주, 10월 스크린과 안방극장 동시 정조준...N차 전성기 예감 - 머니투데이  머니투데이BIFF #8호 [씨네초이스...</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9OMmhEY2xPdlU2S1ZPLU1UcWVCaFVaNHl2YkxNaUs4UHFtQXJuQUtjVmVzY25wcWRQQTFsZFZpcXRmYjJZV2FEUzUtUFBIMmp2V0JBQmx3WlMzdjQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>유재석, 또 시청률 1위…서강대 심리학과 출신 남지현 모교 가더니(‘틈만나면’)</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>유재석, 또 시청률 1위…서강대 심리학과 출신 남지현 모교 가더니(‘틈만나면’)  조선일보‘틈만나면,’ 남지현 “공부가 재밌었다”…퀴즈 프로그램 나갔다가 데뷔한 사연  YTN'틈만나면' 유재석, 김재영 등장에 "역시 미남은 장발…장발은 미남밖에 안 어울려"  SBS 뉴스'틈만나면' 대흥...</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUW44eDJtdGlOTk1JR0lCb3JMTUZpcVlxQnNlY1k1QXB0TFlNSFBGRHZKMFQyVE9qUGJ1QXhCelpmekM0RW1tQkJXVThyTDBqcnNManVwS0s0YWZvM253Tm9OWFdDME1mOEtnYU9HMmRUWGh0eTVRSjE3UEtBcGJWRnRiWXp4OHZWN0tYenNmMA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>[지윤철학원의 오늘의 운세] 2026년 10월 14일 수요일 띠별 운세</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>[지윤철학원의 오늘의 운세] 2026년 10월 14일 수요일 띠별 운세  뉴스투데이[오늘의 운세] 2026년 10월 14일 띠별 운세  YTN[오늘의 운세] 10월 14일 수요일 (음력 9월 4일) 띠별 운세  경기일보[오늘의 운세/10월 14일]  동아일보[김동완의 오늘의 운세] 20...</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>뉴스투데이</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFAzUFI5MzhPWGFDdlRBQTdrNUlpRVVuRi1MRlEtNE5sODVFU1lHNDByM3BQVkkwcjY5RDhFVmVPRDNQWjdfMnlTMFY4Rml6OTRpSGNQSW5tdVFmdkFUTnc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>경찰, '암살자(들)' 역사 왜곡 논란 고발인 조사… 본격 수사 착수</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>경찰, '암살자(들)' 역사 왜곡 논란 고발인 조사… 본격 수사 착수  한국경제[시론담론] 사실과 진실 사이  제민일보[기고]표현의 자유 뒤에 숨겨진 역사적 책임  경상일보‘암살자(들)’ 논란 어디까지 가나…이젠 ‘100분 토론’까지  매일경제“300만 넘고 또 뛰었다..개싸라기” ‘암...</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE40OFpPTlVwUmtKWk5sSFY5WC1IaGkwbUFhTGpnS0R3d3pCZ21KcEM5VTMwVElyZFhhNVVnWUE5MVpfTkxudDNaMEt4UHBZZE5xNlE1dmphOXdLUQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>경찰, '역사왜곡 논란' 영화 암살자(들) 제작진 고발 사건 수사 착수…고발인 조사</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>경찰, '역사왜곡 논란' 영화 암살자(들) 제작진 고발 사건 수사 착수…고발인 조사  데일리안Google 뉴스에서 헤드라인 및 의견 더보기</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>데일리안</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFBDLTl1VkJtRkVaMlJQbFZ3cHlLY2JUQ3FaNzNKdFNLUHNuSWRfMGRqU1UybGdFVGxvMDc4M080WFZGNEVNTjF6c3BRNGppeVhwampsTlZTSQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>[핌in현장] '킬링타임' 류혜영·남윤수, 자극 좇는 인터넷 방송 속 생존 스릴러</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>[핌in현장] '킬링타임' 류혜영·남윤수, 자극 좇는 인터넷 방송 속 생존 스릴러  뉴스핌몰카가 진짜 살인 현장으로 바뀌었다…공포액션 영화 '킬링타임'  연합뉴스[Y현장] "가짜 공포가 현실로"…'킬링타임' 류혜영·남윤수, 핏빛 사투극(종합)  YTN[영상] 죽어야 끝나는 라이브…‘킬링...</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>뉴스핌</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9CbTdpT1FHeFFvcDF2a3RzeENKdFpkODRFRmhqRUM2XzdPM2ZBbThCV3pQdGdHM3hhLVR2NjhyWFJLYzkwV3NqTXBId2pGZkxtZUVrb1N2c05jdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>기안84, 잘 안씻는 뜻밖의 이유 "군대서 자꾸 씻으라고, 반발심 생겼다"(기안장)</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>기안84, 잘 안씻는 뜻밖의 이유 "군대서 자꾸 씻으라고, 반발심 생겼다"(기안장)  스포츠조선"보다가 더러워서 껐다"…팬티 사흘간 안 갈아입은 기안84 '시끌' - 머니투데이  머니투데이"팬티 3일간 안갈아입어"..'기안장2' 기안84 위생논란, 김연경 "군대서 못배웠나" 정색[Oh!...</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>스포츠조선</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPRmxPWjQ2UFF2WWo0TFdpZmQ1TWhpQ3F1d1U4eF9fYTNzMVVFeEJ2Vk5JNlJ6blpaaURPVDNydWpjdHZ0LXU5MFQ1eWROSTNMZ1VsV1FHN3lYMEFaaV9QdlQ3MU5mYTd4NXJ3My1tb09HcGlUYXU1NEVpSFJoU0Y4cE5BRGU?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>천재 의사 활약 그린 '닥터X', 넷플릭스 비영어쇼 1위 직행</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>천재 의사 활약 그린 '닥터X', 넷플릭스 비영어쇼 1위 직행  연합뉴스의사 가운 입은 김지원, '시청률의 여왕'…'닥터X', 첫 주 주말극 평정  YTN'닥터X' 의료 고증 논란…자문 교수 남궁인 "제작진과 싸우다 의사가 패배"  뉴스1[스경연예연구소] ‘닥터X’ 김지원·‘100일의 ...</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5FOTNiSHdfNXFpNldxdi1jLUlfSGNYV1YxVmg3cXBFeGFKeHNQRGpmeTluMldiTFNUUzNseGRGajVGWHVHODRveHlKd1RGQnNZY0tubXNOMnoybTTSAWBBVV95cUxPVk14VUNQQlYzR3pFZFNmSFZhaExYS2YwRHd5b1RoamtiODFaUzg1SE52WS0xSVhROXVxRG4xaXB1SWdGZXpOTFBJX2xXYWk4ak1rb1pmZXRqOC1pdmpHcEs?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>이준혁 “로또 5천 원이 최고 당첨금..30억 당첨되면 제작비로 쓸듯” [인터뷰②] - 조선비즈</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>이준혁 “로또 5천 원이 최고 당첨금..30억 당첨되면 제작비로 쓸듯” [인터뷰②] - 조선비즈  Chosunbiz"하루 반 끼 '로또 1등의 삶'"...알잖아요. 배우 이준혁이 어떻게 했는지, 뭘 했는지, 얼마나 열심히 했는지  조선일보윤영빈 감독 "열심히 산 사람에게 행운이 있길 바...</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPU3FmamZ4REUxN3FfOWd2R3pBYnF3bFZTc3VqNllvc1BXQUJ3b1hxTjRzUWczTmhvWFk1TGYzOV84ckgzMkZNeXdWNmwyWUpjYmtNcDNjc1Q4d2xvc0lVU0JKWFVYSmhMZVEwZkVOeUNmdXc1Mmdzd2t0UTNHT05TRzdSa1AteGQyeUVycEpXcEc2NHPSAacBQVVfeXFMUHhGUm9XR0NMM0liU1dCZ214ZjQ4RDZnVi1Ta2lpMjVzWGZWOERmeXZtekc5ajR0d2JlZEc3ZlljbHYzbjFBWHdqSW9zUVU1ODZQR0d3QnJVdERoUkptbFliRjVaVTl4bjNuWTloOGRiOHJfOVhqZTRWUlI4NWNwSWN1eWVSSDlfSGpIM1F5QlpQdjkxWmJDQ1FlZjJFSEpzUnVtQkhsRzg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>리센느 ‘PULSE’ 심장이 뛴다</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>리센느 ‘PULSE’ 심장이 뛴다  스포츠경향리센느, 차트 역주행 넘어 새 도약…신보 'PULSE' 프로모션 일정 공개  YTN[단독] 배민에서 아이돌 앨범까지...‘리센느’ 컴백 앨범 사전 예약 받는다  조선일보리센느, 첫 지상파 뉴스에 떴다!…역주행→대중 존재감 각인  전자신문‘안원...</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>스포츠경향</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9lRUlCa1NUZ3RXRS1PNjl0M3BHNTJvdXBocnJOS0dxcU1ZQWRPWU9iYTZERHFycnNCZXBQVHFPNG1wcC11OHYxaFRueUJUMG9vS09ZR2RrTGZhcTAtWHfSAWNBVV95cUxOVHIxb3k1dGJYMjZZRk5XNDVpWGVjYl9BQ05fLWpqS0Y3OTFCWTRDUk93NU5lalZpMklfRnI1Wjg4UWt0T09FeUQ0blFOU0FsdlgyUVBzZXVld2p4WGdpRmEzMFk?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>성유리, 바쁘다 바빠 ‘이중생활’..핑클 안무 연습 끝나니 쌍둥이 딸 수영 케어</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>성유리, 바쁘다 바빠 ‘이중생활’..핑클 안무 연습 끝나니 쌍둥이 딸 수영 케어  조선일보Google 뉴스에서 헤드라인 및 의견 더보기</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOWDNIXzFYWk1QS3Zfd2p2akZOWXFtOFJ0UVRhWDQ5R0pQdXFEbEpaaktqNDlQaE1GbHN5eDVEOExBY1Bka1hUakw3RURIbU91NDExdXFYUnRLT1hsV3UwQ3BWZHI0QjdQV1p2TmZxeVNlZkw2ZTFRN3hsVDZsSGczdklQYzF3S3ZBTWczZzR6MA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>[영상] 올해도 낙담한 일본 하루키팬들…내년엔 환호할 수 있을까?</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>[영상] 올해도 낙담한 일본 하루키팬들…내년엔 환호할 수 있을까?  KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RcnBueXBsU1pfRU5ZUUNHeEpXNFNvT1kzSWdJbG5ueXB1LWw5a0p1N3RneHFJZWxYb2h2Z1ItT0hGU3VXNEhPbmJZMm10QUlsOVhIZDMzU1pHZWM?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>2026 노벨 문학상 수상자, 앤 카슨의 대표작 5</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>2026 노벨 문학상 수상자, 앤 카슨의 대표작 5  Vogue korea[속보]전국 경찰서장 242명 중 절반 교체…'향피제' 전면 적용  노컷뉴스[세상 읽기]사랑이 사라지는 사회  경향신문[대중문화칼럼] ‘노벨문학상’ 앤 카슨의 문화적 신드롬이 주는 메시지  천지일보병도 나이도 막지...</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>Vogue korea</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxOSG12YS1PX3psQnhRMmlncEFGQ1RLMVVXY2g0dXVGdGpMeGxRZGhlSDZLQWlYNG1kNHJJTTl6cHBZVTJSNVJnbF83VmhzZ2V6dFFUSnJPakpFVkZiV3gxdkNBa05CZU40dUt6M2M0bWphd2VmcVFDSjlyU0Q3VTVpMUxmVWtSUlZOaFkySm1zcEhsQXBSV01TX0hQMW16QkZVVkoyc2podUNjY0I3ZlUyTlQyWDhvWGhyNV9Wc0hIRnIxNkpRU2RERUZzYzd6ZW1KWmthN0FsM0xtVkoxZ1NMdTdScXNnTEhOSUVxX2RWMlRFUVZDSzBWbDRDUUNwMmo1NjVudkx2bW1pQXVXX0VqQw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>차장으로 승진한 이준혁…'로또 1등' 6.2% 종영</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장진리 기자 = 로또 1등에 당첨된 직장인의 삶을 그린 오피스물 '로또 1등도 출근합니다'가 6%대 시청률로 종영했다.</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014032000005</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>손호영 "5년 만에 신곡, 솔로 데뷔 20주년에 마음 먹었죠"</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김선우 기자 = "손호영이란 이름으로 신곡을 내기까지 5년이나 걸렸네요. 솔로 데뷔 20주년 만큼은 절대 피하면 안 된다는 생...</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261012182400005</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>'투팍 살해지시' 갱단 두목에 사실상 종신형…30년만의 단죄</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>(샌프란시스코=연합뉴스) 권영전 특파원 = 미국 힙합계의 전설적인 래퍼 투팍(2Pac·투팍 샤쿠르)의 살해를 지시·공모한 갱단 두목이 범행 30...</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014009400091</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>천재 의사 활약 그린 '닥터X', 넷플릭스 비영어쇼 1위 직행</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장진리 기자 = 천재 외과의사의 활약을 그린 의학물 '닥터X: 하얀 마피아의 시대'(이하 '닥터X')가 전 세계 넷플릭스 이용...</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014017900005</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>단편선 순간들 "좋아하는 재료 다 넣어 맛있는 음악 만들었죠"</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이태수 기자 = "사랑을 한다는 건 모험 가운데에서도 가장 어려운 모험이라고 생각해요."</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013136400005</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>이준혁 "20년 만에 첫 원톱 주인공, 연기가 재즈 같았죠"</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장진리 기자 = 배우 이준혁(42)에게 주연작인 티빙 시리즈 '로또 1등도 출근합니다'는 재즈 같은 작품이었다.</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013160100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>인피니트 남우현 "16곡 꽉 채운 정규 2집, 그만큼 자신 있어요"</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김선우 기자 = "정규 2집에 댄스, 록, 알앤비(R&amp;amp;B) 등 다양한 장르가 담겨있어요. 제가 10년 동안 선보인 음악...</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013133700005</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>윤영빈 감독 "열심히 산 사람에게 행운이 있길 바랐죠"</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장진리 기자 = 티빙 시리즈 '로또 1등도 출근합니다'에서 배우 이준혁이 연기한 주인공인 직장인 공은태는 편의점에 갔다가 잔돈...</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013179700005</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>"아일릿이 뉴진스 표절" 민희진, 명예훼손·업무방해 혐의로 송치</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 양수연 기자 = 하이브 산하 레이블 빌리프랩의 걸그룹 아일릿이 어도어 소속의 뉴진스를 표절했다는 의혹을 제기해 온 민희진 전 ...</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013180200004</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>AI로 되살린 아들 vs 9년 만에 돌아온 아들…연상호 '실낙원'</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 정래원 기자 = 9년 만에 살아 돌아온 아들보다 인공지능(AI)으로 재현한 아들이 더 진짜처럼 느껴질 수 있을까.</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013177600005</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>최휘영 장관 "영화 '홀드백' 아직 숙의 중…고민할 지점 생겨"</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 임순현 기자 = 최휘영 문화체육관광부 장관이 영화계 '홀드백' 논의가 참여자 간 이견으로 아직 숙의 과정 중에 있다고 밝혔다....</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013175300005</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>티빙 대표 "AI 기반 해킹 추정"…개인정보위 "연내 처분 마무리"</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 차민지 기자 = 최주희 티빙 대표가 대규모 개인정보 유출 사고와 관련해 인공지능(AI) 기반 해킹에 따른 사고로 추정하고 있다...</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013173300530</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>몰카가 진짜 살인 현장으로 바뀌었다…공포액션 영화 '킬링타임'</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 박원희 기자 = 연우(류혜영 분)와 주원(남윤수)이 운영하는 인터넷 방송 채널 '킬링타임'은 몰래카메라 콘텐츠를 생중계해 돈을...</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013171800005</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>[가요소식] NCT 위시, 신보 발매 하루 만에 밀리언셀러</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김선우 기자 = ▲ NCT 위시, 4연속 밀리언셀러 달성 = 그룹 NCT 위시가 지난 12일 공개한 미니 4집 '아이 스파이'...</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013168900005</t>
         </is>
       </c>
     </row>
@@ -3623,7 +9806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4908,6 +11091,1176 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>005930.KS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>반도체/IT</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>232,000원</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>+25,500.0원 (+12.35%)</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>229,500원</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>258,500원</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>224,000원</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>+12.6%</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>RSI 34.4로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>-12.1%</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>"한전, 호남산단 전력망건설 '2년반 안에 완료' 계획 비현실적" (주요언론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>000660.KS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>반도체/AI</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1,443,000원</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>+340,000.0원 (+30.83%)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>1,371,000원</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>1,428,500원</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>1,399,500원</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>+4.2%</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>🔴 단기 비중 축소 (악재 주의)</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>48.3%</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>주주환원 늘었는데 세금은 제각각…입법조사처 "배당세제 정합성 손봐야" (연합인포맥스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>005380.KS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>자동차/모빌리티</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>315,000원</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>-176,500.0원 (-35.91%)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>312,000원</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>346,000원</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>304,000원</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>+11.0%</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>RSI 21.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>-10.8%</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>40.2%</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>현대차그룹, 학대피해 아동 돕는 '아이케어 카' 20대 기증 (주요언론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>000270.KS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>자동차/모빌리티</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>108,500원</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>-40,900.0원 (-27.41%)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>107,000원</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>115,000원</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>104,500원</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>RSI 29.0로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>-7.2%</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>51.0%</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>035420.KS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>인터넷/AI</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>178,000원</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>-23,500.0원 (-11.66%)</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>176,000원</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>191,500원</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>172,000원</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>+8.7%</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>RSI 26.7로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>-8.9%</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>58.6%</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>035720.KS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>인터넷/플랫폼</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>31,300원</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>-16,800.0원 (-34.93%)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>31,000원</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>30,200원</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>RSI 27.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>44.9%</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>카카오뱅크 'AI적금' 출시…저축목표 따라 맞춤형 조언 (주요언론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>068270.KS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>바이오/헬스케어</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>179,500원</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>-9,919.049999999988원 (-5.23%)</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>176,000원</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>188,500원</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>170,500원</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>관망 (HOLD)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>중립 구간 유지 중</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>75.2%</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>012450.KS</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>방산/우주</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>839,000원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>-684,000.0원 (-44.91%)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>830,500원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>1,003,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>809,500원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>+20.8%</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>RSI 29.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>50.7%</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>373220.KS</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2차전지/배터리</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>410,000원</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>+10,000.0원 (+2.50%)</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>369,500원</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>410,000원</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>402,000원</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>+11.0%</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>RSI 67.8, 20일선 이격도 +11.0%로 단기 과열권, 분할 차익 실현 권고</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>+11.0%</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>가족 연계 회사에 수년간 자문료…전 LG엔솔 사장 ‘배임’ 수사 (KBS 뉴스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>POSCO홀딩스</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>005490.KS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>철강/이차전지소재</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>299,000원</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>-62,500.0원 (-17.29%)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>296,000원</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>317,000원</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>288,500원</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>RSI 37.2로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>55.2%</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>노동부 장관 “포스코 교섭 적극 지도…신안산선 사고 엄중 조치” (KBS 뉴스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>엔비디아 (NVIDIA)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>글로벌 AI/반도체</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>$228.52</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>+39.21000000000001$ (+20.71%)</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>$201.56</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>$226.23</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>$221.66</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>+12.2%</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>🔴 단기 비중 축소 (악재 주의)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>81.2%</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>거침없는 외인 매도...반도체 역대급 실적에도 급락, 왜? (YTN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>애플 (Apple)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>글로벌 빅테크</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>$341.27</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>+82.07$ (+31.66%)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>$334.44</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>$358.33</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>$324.21</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>관망 (HOLD)</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>중립 구간 유지 중</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>+1.6%</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>93.4%</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>애플, 4년만 A19 탑재한 신형 애플TV 4K 공개···가격 44만 원 (글로벌E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>테슬라 (Tesla)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>전기차/자율주행</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>$375.23</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>+22.810000000000002$ (+6.47%)</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>$367.73</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>$393.99</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>$356.47</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>관망 (HOLD)</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>중립 구간 유지 중</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>+1.5%</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>38.6%</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4919,7 +12272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5118,6 +12471,423 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>증시 지수</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>코스피 (KOSPI)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>6,035.35</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-348.89 (-5.46%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>증시 지수</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>코스닥 (KOSDAQ)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>837.03</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>-55.24 (-6.19%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>미국 달러 (USD)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1,340.88원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>매매기준율</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>일본 100엔 (JPY)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>847.01원</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>100엔 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>유로 (EUR)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1,500.84원</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>매매기준율</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>중국 위안 (CNY)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>199.98원</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>매매기준율</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="53" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>분석일자</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>코인명</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>심볼</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>현재가</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>24시간등락</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>매수_추천금액</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>목표_매도금액</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>손절_기준가</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>기대_수익률</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>투자신호</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>전망및근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>비트코인</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>112,886,000원</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>112,322,000원</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>121,917,000원</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>110,592,000원</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>+8.5%</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>⭐ 지지선 안착 매수 (눌림목)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>20일 이동평균선 지지선 안착, 상승 추세 지속 전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>이더리움</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3,393,000원</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+0.35%</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>3,366,000원</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>3,596,500원</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>3,274,000원</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>+6.9%</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>🟢 단기 매수 유망 (과매도 반등)</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>RSI 47.5로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>솔라나</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>145,200원</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>144,000원</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>155,800원</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>140,100원</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>+8.2%</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>🟢 단기 매수 유망 (과매도 반등)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>RSI 47.6로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -463,7 +463,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3626,27 +3626,27 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”</t>
+          <t>김지용 중수청장 후보자 오늘 청문회…‘친윤 논란·개혁 적합성’ 시험대</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”  경향신문[전국 주요 신문 톱뉴스](14일 조간)  연합뉴스금융위·법무부 등 44개 기관 9929명, 내년부터 세종 본격 이전  정책브리핑대사관들 모두 서울 있는데… 법 고쳐 외교안보 부처까지 세종으로  조선일보...</t>
+          <t>김지용 중수청장 후보자 오늘 청문회…‘친윤 논란·개혁 적합성’ 시험대  한겨레‘친윤’ 딱지에 임은정 감찰까지…김지용, 중수청장 문턱서 여권 시험대  매일경제김민석, '김지용 비판' 추미애에 "자기 역할에 집중해야"  연합뉴스靑이 해야 할 말, 하지 말아야 할 말[오늘과 내일/장원재]  ...</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBMeFo1WV9RWkgyZDc5OXRoaXJ1bFpqQXpITG9QQmxicVNnbnNKSHAzWUNXZjF0bVJ3VmExV2t0ZUtnQTNzc1lEZXlNYlY3R3podHp0d2JRTVJlZ9IBX0FVX3lxTE8tam1RNHk4a2JrTHJFd0FRWExJSlNWeU1UeEs5MnNqbGdUYkFFSVpqRnYyX0VVbV9sUHJBbmY4TkJueFBPQlhxRkwwczlWMU1neC1Ga3lOUm4wa2FPVzlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5oYjdZdVl0MTNLWE1zWVI3QWw3aVpjNlpkaklQV2dYVUMwOUFkTXVycmRFNFN1Xy1pSFFDYUZzR3pPamxzUzMwYkQtWW5FRVllOWg0SkQ3TTluWmN4TWdBVFhRdGQxbUVWRzR5YXNTN2YtZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3668,22 +3668,22 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>헌재 사무처장 “조희대 국감 불러 대법관 제청 물은 건 위헌 아냐”</t>
+          <t>첫발 뗀 '북극항로' 개척…사업성 확보가 최대 관건</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>헌재 사무처장 “조희대 국감 불러 대법관 제청 물은 건 위헌 아냐”  한겨레여당 "조희대 문제 있다" 주장에…헌재 사무처장 "네" 답변  JTBC“조희대, 사법 독립 가장해 1인 정치 행동”…헌법학자들, ‘대법원장 제청권 독점’ 비판  경향신문[칼럼] ‘이진관 기피신청’ 인용이 조희대 ...</t>
+          <t>첫발 뗀 '북극항로' 개척…사업성 확보가 최대 관건  한국경제[대통령 이재명 말모이] 대한민국의 북극항로 항해일지는 이제 첫 장을 열게 됩니다 - 카드/한컷 | 멀티미디어  정책브리핑이 대통령 “국제사회 신뢰 속 북극항로 열어갈 것…해양강국 대한민국”  KBS 뉴스북극항로 부산 허브화 ...</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5mTm5HdFlNUG5nQkhqYU5SQUJJRUJQa2c4M3ZKSlZrWlU3RkI2ZWE4akg5OHRRVnc1YTFPbzdVWXZPMlFBRHBobV85eG5EQnVWT2RvWG54SmJySUd2bktSTzJ1VUl2U1RKclA4aXpTa25SQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE82ZDF3clBYNzVHVFA3NUd4NTRGUnpPSXVoZ1AwTFhPVUdMSGZGeDdDbzBOaTZSeHhVVkEzTHpMVjUzMWxZR3BwcWMxa09hZXBnUWgxQV9Qbm5aZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3700,27 +3700,27 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>李대통령, '부캉이' 친수공원 찾아 시민 소통…HMM 제막식도 참석</t>
+          <t>국감서 배제된 이진숙… '尹정부 방통위원장 출신' 이해충돌 공방</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>李대통령, '부캉이' 친수공원 찾아 시민 소통…HMM 제막식도 참석  연합뉴스"부캉이 보러 왔다가 대통령까지"...부산 북항 찾은 이재명 대통령  KBC광주방송이 대통령, HMM 본사 제막식 '부산시대 개막'  뉴시스HMM 부산 시대 개막...이재명 대통령, 본사 사옥 제막식 참석  전...</t>
+          <t>국감서 배제된 이진숙… '尹정부 방통위원장 출신' 이해충돌 공방  한국일보“투쟁 선봉” “선 넘는다” 이진숙·주진우에 국힘서도 이견  경향신문‘사상 초유’ 발언권 2명 정지·위원 제척까지…국감서 위원장 칼 휘두르는 與  서울경제국힘 "與, 억지 프레임 씌워 이진숙 제척…내로남불·의회폭거...</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>한국일보</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE15VnhEX2ZlYS1may05U3NMU29IOUFaR2F5dEZlVGJuN05zQzRsZnl2VEVFOXhValhIdEZ1UVByRDNWYkpGZ2ZZaUZ5NEQwQ0llUmVTdEpMbFVCTVdib0lDU9IBYEFVX3lxTE15VnhEX2ZlYS1may05U3NMU29IOUFaR2F5dEZlVGJuN05zQzRsZnl2VEVFOXhValhIdEZ1UVByRDNWYkpGZ2ZZaUZ5NEQwQ0llUmVTdEpMbFVCTVdib0lDUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9kYVNBRVlPNnliZTREaWdUT3doR0lrWVRTUlVHbmNJT1R5ZEpjS3VIazFrYWpPRkwyZlNiVkFCRlE0MUNYd1pSdVQ3MGdpLUQ4dGxsSkxINzV5bUZnaE9RMndMTE1nNU9IcmFIbUJR0gFzQVVfeXFMTV9ybWJfNmZzNDRBNmlyVkZIVnRUd1JzNGVqcV9TMDJoVjhCTHdOT2lEZjRjTlN1VzZRaWdrU2FyMWRwNjgwUVVBbUM0R2Y3RlV3NFNoMmZpdXdQNnI2MElnb2dBcjdTcUdQQ2FWWFY1RkJiQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3742,22 +3742,22 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>[정우상 칼럼] 친문은 극혐하고 대통령은 극찬하는 인사처장</t>
+          <t>지난해 아파트 관리비 최고는 나인원 한남…"월 평균 170만원"</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>[정우상 칼럼] 친문은 극혐하고 대통령은 극찬하는 인사처장  조선일보</t>
+          <t>(서울=연합뉴스) 노선웅 기자 = 지난해 전국 아파트 가운데 서울 용산구 '나인원 한남'의 세대당 월평균 관리비가 월평균 170만1천847원으로...</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxObElacC1uZUxRX0I2RmVOVjBoOFBRUGNYZUpSZWw0dXdhUWEtdHIxX2NPRnBEZXcxbWJJdS0yeGMzLTA0cktoZ1gyWnMtbTZDbWhCWlgzWEx1RkhXVE54WTBEX2pjNkI4WXlUOXcxSmhiTEtyUEF0NDFnZ3o1SlVTMmRB?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014047900001</t>
         </is>
       </c>
     </row>
@@ -3779,22 +3779,22 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>청와대, '한·미 골프외교 TF' 구성‥실무 준비 착수</t>
+          <t>한병도 "중수청, 리더십 절실…김지용, 소신·비전 제시해달라"</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>청와대, '한·미 골프외교 TF' 구성‥실무 준비 착수  MBC 뉴스[윤영호의 게임의 시선] 트럼프와 골프 라운드를 앞둔 이 대통령께  조선일보靑, 李-트럼프 골프 대비 TF 꾸려… 12월 G20 美회의 계기 성사 전망  동아일보靑, 트럼프와 골프회동 실무대응팀 구성…12월 성사 가능성...</t>
+          <t>(서울=연합뉴스) 박경준 안정훈 기자 = 더불어민주당 한병도 원내대표는 주진우 의원이 SNS에 '이재 명을 끊을 때'라는 댓글을 적는 등 국민의...</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9kaXQzajR4VFFPV04wMkh0a3N6V0xiQTRUV0tJbnBGR1NKTlIyT1pWTWk5UjVQaGFnMDRRczloX0VlRWJHTzZIMVlHX1pzd0JBVDhsNHZzQTJVZXpuZFZ3cWJOellmcG1SOEF3elhnZFpteDBENDhuM9IBeEFVX3lxTE83YXpQNFhmZm5RY2ZIX0RuWjI3Tnp2RlllbjZfamVMa2FseGVRd2xNSHhULThYaEhqR0dGUTZJN2JwTHdJaW4tZ2FKU3Q3V3RkeHNiNWhlNkFjNEpXU2NPdVBpVEJnTjh4YjhMZnJRbFNUaENMY210cA?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014044800001</t>
         </is>
       </c>
     </row>
@@ -3811,27 +3811,27 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>백악관 새 대변인, 첫 브리핑서 “한국, 알래스카 LNG 투자” 언급</t>
+          <t>주진우, 2026 여수 세계섬박람회 국민감사 청구</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>백악관 새 대변인, 첫 브리핑서 “한국, 알래스카 LNG 투자” 언급  KBS 뉴스백악관 "한국, 알래스카에 540억 달러 투자할 것”...트럼프, 알래스카 유세  YTN백악관 “한국 최대 2천억 달러 에너지 투자 계획” 재강조  VOA 한국어 홈페이지트럼프의 에너지 압박 맞서는 한국…...</t>
+          <t>(여수=연합뉴스) 손상원 기자 = 국민의힘 주진우 의원이 부실 지적을 받아온 2026 여수 세계섬박람회에 대한 국민감사를 청구한다.</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9EVlBUeDhWZ040aUxiNlpQZmFNUUhPUW81MTJGMDdtVFlMbUN2TEhZVlFIUTZpY0tleUd3ejl0b3FIeDRuaUxIZjk5N2x4LXB3LTlRMEFYV1Rsa0k?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014048400054</t>
         </is>
       </c>
     </row>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>[단독]검찰총장 후보 추천위원 2명이 같은 로펌 소속···위원 구성 놓고 공정성 우려 제기</t>
+          <t>어기구 "가습기살균제 피해 재심사 결과 받는 데 최장 4년 반"</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>[단독]검찰총장 후보 추천위원 2명이 같은 로펌 소속···위원 구성 놓고 공정성 우려 제기  경향신문속보 법무부, 검찰총장 후보추천위 구성...공소청 초대 수장 인선 착수  YTN공소청 초대 수장 인선 착수‥내일부터 국민 추천  MBC 뉴스이재명정부 첫 검찰총장 추천위 구성…초대 공소청...</t>
+          <t>(당진=연합뉴스) 정윤덕 기자 = 가습기살균제 피해 재심사를 신청한 뒤 결과를 받기까지 길게는 4년 반이 걸린 것으로 나타났다.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE02bXAtLVFINEhnUUdqSkxqSVlRV2ZkbUk0RW9HVHhXV3d1ME1uYUU1SzNUbGxZeUlNanNNNG4zNWZXektmNDdYek9QR19zWk5wX1VSdkdwZVVKZ9IBX0FVX3lxTE9qQWUxUlBic3U1ZU16aFVZSkRMczdwSzc1NTVsb1pSSWhkbXF2VEc2NzhPSGMyUWZ3eFIyMHh2blJzNF9JbmJOUFIxM1pjeEFsSlpaSEU1MjBfbWNfbGYw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014044600063</t>
         </is>
       </c>
     </row>
@@ -3885,17 +3885,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>농진청, 5년간 기술이전 6천여건…제품화 성공률은 40%대 불과</t>
+          <t>전작권 조건충족 이견 속…한미 국방장관 이달말 첫 대면 가능성</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>(전주=연합뉴스) 김동철 기자 = 농촌진흥청이 최근 5년간 2천건이 넘는 특허를 내고 6천건이 넘는 기술이전 계약을 체결했지만, 실제 제품·서비...</t>
+          <t>(서울=연합뉴스) 김효정 기자 = 전시작전통제권(전작권) 전환 조건 충족 여부를 두고 한미가 이견을 보이는 가운데 이달 말 국제회의를 계기로 강...</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014030900055</t>
+          <t>https://www.yna.co.kr/view/AKR20261014039900504</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3922,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>김민석, '김지용 비판' 추미애에 "자기 역할에 집중해야"</t>
+          <t>조의장, 그리스서 경제협력 간담회…방산·첨단산업 세일즈외교</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김정진 기자 = 더불어민주당 김민석 대표는 14일 추미애 경기도지사를 겨냥, "각자의 처지와 역할에 맞게 정확하게 하는 것, ...</t>
+          <t>(아테네=연합뉴스) 오규진 기자 = 그리스를 공식 방문 중인 조정식 국회의장은 13일(현지시간) 그리스 의원들과 경제협력 오찬 간담회를 열어 방...</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014020700001</t>
+          <t>https://www.yna.co.kr/view/AKR20261013189300001</t>
         </is>
       </c>
     </row>
@@ -3964,12 +3964,12 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>"소진공, 베트남 매장 일방 폐점에 소상공인 업체 43곳 피해"</t>
+          <t>김민석 "曺 헌법훼손 차고 넘쳐…잘못 바로잡는 모든 방안 검토"</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 조다운 기자 = 소상공인시장진흥공단이 베트남에서 운영하던 화장품 상설 매장의 문을 일방적으로 닫으면서, 입점을 기다리던 소공인...</t>
+          <t>(서울=연합뉴스) 김남권 안정훈 기자 = 더불어민주당 김민석 대표는 14일 조희대 대법원장의 대법관 후보자 재제청 거부와 대법관 격려금 지급 논...</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013150700001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014044000001</t>
         </is>
       </c>
     </row>
@@ -3996,17 +3996,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>[오늘의 국회일정](14일·수)</t>
+          <t>"농진청, '57만명 개인정보 유출' 제재받은 업체와 재계약"</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>▲ 위원회</t>
+          <t>(서울=연합뉴스) 노선웅 기자 = 농촌진흥청이 농민 57만여명의 개인정보 유출 사고에 책임이 있는 업체와 별도의 보안 강화 조치 없이 계약을 유...</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013187700001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014035700001</t>
         </is>
       </c>
     </row>
@@ -4028,32 +4028,32 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>정태호 "올해 공급망기금 91% 대기업에…지원체계 보완해야"</t>
+          <t>유엔 국감장서도 北 지뢰 논쟁… 野 “유엔대표부 할 일 하고 있나” 공세</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 박재하 기자 = 글로벌 공급망 위기 대응을 위해 국내 기업에 지원하는 '공급망안정화기금'이 대기업에 편중되고 있어 이를 재조정...</t>
+          <t>유엔 국감장서도 北 지뢰 논쟁… 野 “유엔대표부 할 일 하고 있나” 공세  동아일보‘불의의 사고’ 아니란 강경화 대사 발언 해명 나선 주미 대사관···“기존 표현 맞는지와 무관”  경향신문‘북 DMZ 지뢰’ 대처 공방…“안보리 차원 대응 검토 중”  KBS 뉴스[연합뉴스 이 시각 헤드라...</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013181600001</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE00bXFtc1dxeWdEWG9yY0o1WWVYeUNqUVZhc0Q2djhFT1pfdEtaaUdIemQyQWJnMkdfVTZwNDFULV9jYWszR2FuT0EwVjU3dWZJWUdoMFZMVFVuOE5sQ2NsREpqMDE3ek9aT29UaDUxNWxJOXfSAWZBVV95cUxOdktGVFlUOGNCOXhINTh2YWVEQ3k0RDFERDlJbVFVNmdGTTVTaHNPaGxQY0h4a3F2RE85eGN4VzltZDI2a2lYenNsbFh0YldmS2VNUENXNnJHVWdnZlA3cVpIWDhtN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -4065,32 +4065,32 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>주미대사관 "강경화 'DMZ 지뢰 발언', 정전협정 위반 강조 취지"</t>
+          <t>마라톤 결승선 앞두고 숨진 카이스트 대학원생…SNS 추모 물결</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>(워싱턴=연합뉴스) 홍정규 특파원 = 주미한국대사관은 최근 비무장지대(DMZ) 북한 지뢰 폭발에 대한 강경화 주미대사의 국정감사 발언이 "우리 ...</t>
+          <t>마라톤 결승선 앞두고 숨진 카이스트 대학원생…SNS 추모 물결  한국경제'서울 달리기' 마라톤대회 참가했던 20대 여성 사망  연합뉴스황영조 “사망에 이르는 러닝” 경고···SNS 과시형 기록 문화도 지적  경향신문“SNS 인증샷 찍다 죽습니다”…마라톤 기록 경쟁 과열에 황영조 당부 -...</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014010200071</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1nRG1XbzVKbGFySjZMU1FFZ1FHOHNKYjVQNk1nbGdVeE1WYnhXWTdZNGVORlFMMnp1YVppbTZXVDVOY2JJTG96MjhrVkhVN0ZGMmVqUWZOZ05jUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4102,32 +4102,32 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>방송사 협찬고지 위반 처분 29건…9개월 만에 작년 추월</t>
+          <t>[단독] 美 DNI가 ‘정보공유 제한’ 결정… 李, 정동영·이종석 경질론 선 그어</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 유현민 기자 = 방송사의 협찬고지 법규 위반에 따른 처분 건수가 올해 9월까지 29건으로 집계돼 지난해 연간 처분 건수(16건...</t>
+          <t>[단독] 美 DNI가 ‘정보공유 제한’ 결정… 李, 정동영·이종석 경질론 선 그어  조선일보국민의힘 “동맹 지키자는게 굴종?…이재명 정부 백해무익 외교”  KBS 뉴스조갑제 “李대통령, 김정은엔 굴종적·美엔 당당하게? 말이 되나”  문화일보한·미 정보 갈등에도 “국익 최우선”… 이 대통...</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013135700017</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxORUxjVnJDQjk3WU9KdllpN3hRcnRSUWNGUDlKc1NQSlZtaHBVWVlGTW1zQ1ROQUJzal9kS1ZJUFF0eGhzS0xEQVZETXpGN1pNTTVxUEtyRlFrYkxLV1MtQ3QtY1Vld0pJbGQ0SWtvMkdCWWYxX0hJNkNmdEhYTURDRDhyaktRSjJGZTJOMUpobkg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4139,32 +4139,32 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>이양수 "aT 칭다오 물류센터, 거약 예산 투입에도 활용률 저하"</t>
+          <t>민간건물 임차 27곳 내년 이전…‘행정수도 세종’ 2031년 완성</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 한주홍 기자 = 우리 농식품의 중국 수출을 지원하기 위해 거액의 재정을 투입해 설립한 한국농수산식품유통공사(aT) 칭다오 물류...</t>
+          <t>민간건물 임차 27곳 내년 이전…‘행정수도 세종’ 2031년 완성  한겨레안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”  경향신문[전국 주요 신문 톱뉴스](14일 조간)  연합뉴스금융위·법무부 등 44개 기관 9929명, 내년부터 세종 본격 이전  정책브리핑...</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013134700030</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5nRVl0ZVdQRld3OGtSZFp3WmdOZWFmRk1HWkNFZTMtVDJvYWRfQURGNUFLRUFYRVFtVC1wU1VJSGZrR01sMXBsZ2g1eTQ5aldSY0xydHhiUHl3dmpqOTJPLTN2Wl9CdzdLTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4186,22 +4186,22 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>"LH 공공임대주택서 7년간 화재 1천여건…사망자 절반은 영구임대"</t>
+          <t>혼인무효 소송 중 장모 살해·아내 납치한 20대 남성 구속영장심사</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 노선웅 기자 = 한국토지주택공사(LH) 공공임대주택에서 최근 7년간 1천100건이 넘는 화재가 발생해 250명이 넘는 사상자가...</t>
+          <t>혼인무효 소송 중 장모 살해·아내 납치한 20대 남성 구속영장심사  MBC 뉴스[단독] 장모 살해범, 이미 ‘수차례 전과’…상습범의 계획범죄 정황  JTBC[단독] “경찰 신고 전에 뭐라 했어”…송파 ‘장모 살해범’ 보복 범죄 정황  KBS 뉴스장모 살해 20대, 가족 신변 볼모로 아내...</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013187900001</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JM3lPYzJGVjJJclh2cUx3cFdzby1sOHF1Q1ktQnIyWkVRVmRPcWdhOEhMTHNUYTNpSDNMWUwyR2NZRnRRc19OMDVHMG1rS2NEYUkzTndob3JxZHk4Wk5FUFp6LTA5Sy1SZzE4UFpvX0ZLWG9sWlRJ0gF3QVVfeXFMTVMwZVl2TXltUlZXd2dwUzVaRXlpOVJuUnlYMHlQLXk5NTBQb2oyNG9PR0xQb1djRGJnd1dtbzQ3ZlJvWmdwVnoxSEhrbmdhVUFxYV9ZcmdoUENGOUtINTBUVXlVcmVEXzY5aXkzVzVZYkNZTDd4c00?oc=5</t>
         </is>
       </c>
     </row>
@@ -4213,32 +4213,32 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>박성훈 "대테러센터, 올 2월 이후 공유받은 중동 정보 0건"</t>
+          <t>추미애 “관사 계약, 사치라 보기 어려워”···이재명 대통령 SNS글엔 “저라고 생각 안 해”</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 이정현 기자 = 국가 대테러 업무를 총괄하는 국무조정실 대테러센터가 올해 2월 이후 중동·호르무즈 관련 정보를 관계기관으로부터...</t>
+          <t>추미애 “관사 계약, 사치라 보기 어려워”···이재명 대통령 SNS글엔 “저라고 생각 안 해”  경향신문경기도 아닌 ‘추미애 국정감사’?…여야, ‘예산 삭감’·‘SNS 정치’ 질타  KBS 뉴스"일방독주" "여의도지사" 與도 野도 秋 난타  조선일보秋국감서 與공세성 질의에 '내분 분수령...</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261012144600001</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1ZMXNSbkp5MlNtcXZuQ3R4TjBqek1vQ0NYa1IyRDFKaTBrdXZpZE9SSWVycGVsNHlkRVZCcnpVV2RfZEgxaWdYQV92d05Ja0pUbk04eDlhOGhDd9IBX0FVX3lxTE9lTmFkSV9mNWpFX210TXBZelIzOXU3NF9zQ0w3T25rcjFUbzRBTFhtelpGQlR0QUpCcm9WYW9EaVpxbG9CaUNhZkxEOGdhbzBOS24zMXZ3WGJwdGZnZURZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>서범수 "수학여행 가는 초등학교 2년새 724곳 줄어"</t>
+          <t>뇌동맥류 수술 후 사망…법원 "대안 치료 설명 의무 위반"</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김연정 기자 = 수학여행, 수련 활동 등 숙박형 현장체험학습을 실시한 초등학교가 최근 2년 새 700곳 넘게 줄어든 것으로 나...</t>
+          <t>(부산=연합뉴스) 차근호 기자 = 별다른 증상이 없던 환자가 비파열성 뇌동맥류 수술을 받은 뒤 뇌출혈로 숨진 사건에서 의료진의 수술상 과실은 인...</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013177200001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014049500051</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>野최수진 "석탄공사 직원, 민주당 명함 들고 정치활동하다 징계"</t>
+          <t>강북구, 고령자 운전면허 반납지원 확대…차 없애면 20만원 추가</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 조다운 기자 = 산업통상부 산하 대한석탄공사 직원이 더불어민주당 당직 이력이 적힌 명함을 만들어 정치 활동을 하다가 징계받았다...</t>
+          <t>(서울=연합뉴스) 정준영 기자 = 서울 강북구(구청장 정창수)는 고령운전자의 교통사고를 예방하고자 오는 15일부터 '고령운전자 운전면허 자진반납...</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013131100001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014054900004</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>"농어촌공사, 동일직종 뽑는데도 본부 심사기준 제각각"</t>
+          <t>광주 온 도시철도 2호선 전동차…내년부터 시운전</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 박수윤 기자 = 한국농어촌공사가 동일 직종의 임직원을 뽑는데 지사별로 심사 기준을 달리하는 등 채용 절차를 주먹구구로 운영하고...</t>
+          <t>(전남광주=연합뉴스) 장덕종 기자 = 광주도시철도 2호선 1단계(시청∼월드컵경기장∼백운광장∼조선대∼광주역)를 달릴 전동차가 14일 첫 입고돼 본...</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013027300001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014044500054</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>이양수 "농수산식품유통공사 새 비축기지 활용률 60%로 저조"</t>
+          <t>저소득층 '실명 예방' 공로…강동구, 보건복지부장관 표창</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 이정현 기자 = 한국농수산식품유통공사(aT)가 비축시설 노후화와 분산 문제를 해결하기 위해 비축기지를 신축했지만, 활용률이 저...</t>
+          <t>(서울=연합뉴스) 김준태 기자 = 강동구는 지난 8일 송파여성문화회관에서 열린 '제56회 눈의 날 기념식'에서 보건복지부장관 표창을 받았다고 1...</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013113000001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014048800004</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>"한전, 호남산단 전력망건설 '2년반 안에 완료' 계획 비현실적"</t>
+          <t>음성 사정리 동학군·항일의병 추정 묘소 보존·활용 방향은</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 권희원 기자 = 한국전력공사가 통상 9년이 소요되는 전력망 건설을 호남 반도체 국가산업단지 사업에서는 불과 2년 반 만에 완료...</t>
+          <t>(음성=연합뉴스) 박재천 기자 = 충북 음성군은 충북역사문화연구원과 함께 오는 16일 오전 10시 30분 음성생활문화센터에서 사정리 동학군(항일...</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013183000001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014053100064</t>
         </is>
       </c>
     </row>
@@ -4440,27 +4440,27 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>이 대통령, 인천 찾아 ‘흉기난동 사건’ 보고받아…“엄정 수사” 지시</t>
+          <t>[바이오스냅] 셀트리온, 미국 처방집 추가 등재 추진</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>이 대통령, 인천 찾아 ‘흉기난동 사건’ 보고받아…“엄정 수사” 지시  한겨레[이시각헤드라인] 10월 14일 라이브투데이  연합뉴스TV인천경찰청 찾은 이 대통령, 흉기 난동 사건에 “엄정 수사···전자발찌 관리대책 마련해야”  경향신문인천서 전자발찌 찬 50대 흉기난동…시민들, 의자로 ...</t>
+          <t>(서울=연합뉴스) 박상현 기자 = 셀트리온[068270]이 미국에서 대형 처방약급여관리업체(PBM) 처방집 추가 등재를 추진하며 매출 확대를 모...</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE43eEgyQkpJTnFsbjkxYUxOX1IzT0NaT1BnaVpjM1ZadVFtby1nSXFVOTlmeHFLaWZRM1VGNzB0WGtUVUxOMFBCQ2lMeEZvVU1fbXJLQUFNU3d5QTVuTlNMejdDNWJ3TF8zTkNR?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014055200017</t>
         </is>
       </c>
     </row>
@@ -4477,27 +4477,27 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>‘불의의 사고’ 아니란 강경화 대사 발언 해명 나선 주미 대사관···“기존 표현 맞는지와 무관”</t>
+          <t>서울대 80주년 유홍림총장 "왜 대학이어야 하는가 다시 물어야"</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>‘불의의 사고’ 아니란 강경화 대사 발언 해명 나선 주미 대사관···“기존 표현 맞는지와 무관”  경향신문"불의의 사고 아니다" 강경화 발언 수습에… 한동훈 "국민이 우습나"  조선일보北 지뢰 도발 대응 놓고 유엔 국감서 공방… 차지훈 “어떻게 접근할지는 미정”  천지일보[뉴스광장 헤드...</t>
+          <t>(서울=연합뉴스) 윤민혁 기자 = 유홍림 서울대 총장은 14일 제80주년 개교기념사에서 대학의 위상과 의미가 근본적으로 도전받고 있다며 "왜 대...</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1hUkZwRHNSeXV0bVNkck15ZmpyckxlXzBLaUwxLUY5V3V0TEUzYUVuN040UndrYllabFM0NUdUTXpQVjRzb2xUQThFNG9sVUlVc1hSbWFqYUhYQdIBX0FVX3lxTFA5NklMWW96TDM3Nl9iejRueXhpakJxZjNNSEpIdzdMT3Z2ZUtqVjJCdk9VYUlaNzljdkRORW9wZXJYSmFnMVQzMUpiOWluUHVobkVMdnAwVW52S04wM20w?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014048000004</t>
         </is>
       </c>
     </row>
@@ -4514,27 +4514,27 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>양육권 뺏긴 40대男, 딸과 함께 차에서 숨진채 발견</t>
+          <t>[게시판] 소진공, 대전 종합사회복지관 등에 '로컬푸드 꾸러미' 전달</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>양육권 뺏긴 40대男, 딸과 함께 차에서 숨진채 발견  동아일보“경찰에 ‘안전 확인’ 수차례 요청했지만 결국”···제주서 40대 아버지·네 살 딸 숨진 채 발견  경향신문[속보]“찾아달라” 호소했지만 제주서 4살 딸 숨진 채 발견  문화일보“딸이 위험하다” 수차례 도움 요청했지만…4살 ...</t>
+          <t>▲ 소상공인시장진흥공단은 지역 농가의 소득 증대와 지역경제 활성화를 돕고자 대전 유성구 종합사회복지관과 그냥드림센터에 '로컬푸드 꾸러미'를 전달...</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBuempJUmN5Q1dHYU1VZHVUemoxRURfVE1KWjFpRnVkbTFVUFVkZTFNNHY0LU9IaGwtaWM3YlV0bDJKMUVRYTNzWnlZSGZtcU9CSjNmVXVtQURkRTQyRzJhZ2xjY0J6bzdsbFpxRmYtbWc5UnhJYlHSAWZBVV95cUxNY1N6TzU3UVRHdzEtLThrQnZyWktTZzJwdl8xU0ZuU0FkX2txT0FxMWk2VDJnX1lsazNXeG9tRmpSMlNXX1loVDNzSkNhdDRaeXdpZjBRUjhCUEVNQUd6Nm1nbVJzNWc?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014022600030</t>
         </is>
       </c>
     </row>
@@ -4556,22 +4556,22 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>추미애 "김지용은 친윤 검사‥공직에 부적합" 거듭 주장</t>
+          <t>[부고] 홍성권(강원대학교병원 외과 과장)씨 부친상</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>추미애 "김지용은 친윤 검사‥공직에 부적합" 거듭 주장  MBC 뉴스靑이 해야 할 말, 하지 말아야 할 말[오늘과 내일/장원재]  동아일보김민석, '김지용 비판' 추미애에 "자기 역할에 집중해야"  연합뉴스“윤석열과 최근 10년간 사적 만남 없었다” 김지용 중수청장 후보 오늘 청문회  ...</t>
+          <t>▲ 홍홍표(향년 86세)씨 별세, 홍성권(강원대학교병원 외과 과장)씨 부친상 = 14일 오전, 강원대학교병원장례식장 2호실, 발인 16일 오전 ...</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5jRlcwUGcyM2MzcEpMSWxyOWg0YzJyYWtJQzJOQVRpdU9KVml0TGppbzJFVWZKSVJRZXVVSWE3UkJMNF9EMnp4c0JDWEFlV2VxVVN0WF9vV0Fndm5HcDRQc1NwczQxcFhBeUZMcnlUR0N3cU9LUEFTaNIBeEFVX3lxTE0xYnFEVHNfZFBzMTBJdUdGRl9WQVZ1allWVEdiZFRBcjNfbkxpN3REYm5rakwzYkZ6VkllX1NSeWxUMXlLQklKRFYxdE9qZm84ZWV5LWVRRk5LSXNxUV91YTJNd3cwUG1EWDRPYlktVnhhcl9KSkpQQw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014051800062</t>
         </is>
       </c>
     </row>
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>남은 중앙부처 모두 세종行…'행정수도 완성' 가시화</t>
+          <t>속초시, 상반기 사업체·청년 창업기업 증가세… 지역경제 활기</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>남은 중앙부처 모두 세종行…'행정수도 완성' 가시화  한국경제안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”  경향신문[전국 주요 신문 톱뉴스](14일 조간)  연합뉴스금융위·법무부 등 44개 기관 9929명, 내년부터 세종 본격 이전  정책브리핑대사관들 모두...</t>
+          <t>(속초=연합뉴스) 류호준 기자 = 강원 속초지역 전체 사업체 수와 청년 창업기업 수가 올해 상반기 매월 증가한 것으로 나타났다.</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE43TW4tcGZ5YWVBbmdpYVNlX18tYVJzSkpWSlRrek1YNFBnc2hKTlJmc2NINWtWZ1I1b2UtU1RSMTV3U05UWUhPWWs3MF9DcWdxNGdNNDdLM3lEQQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014051100062</t>
         </is>
       </c>
     </row>
@@ -4630,22 +4630,22 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>“한반도 다영역부대로 다층감지…지도서 베이징·서울 선그어보라”</t>
+          <t>순천향대-국군대전병원, 미래 군 의료 및 과학기술 융합 협약</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>“한반도 다영역부대로 다층감지…지도서 베이징·서울 선그어보라”  KBS 뉴스주한미군사령관 "더 넓은 작전환경 이해… 지도서 베이징·서울 선 그어보라"  조선일보"北도 실전경험… 한미 연합훈련 기존틀 벗어나야" - 머니투데이  머니투데이"한반도 다영역부대로 다층감지…지도서 베이징·서울 선...</t>
+          <t>(아산=연합뉴스) 유의주 기자 = 순천향대는 최근 국군대전병원과 '미래 군 의료 및 과학기술 융합을 위한 업무협약'을 맺었다고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1aQnNfaV9oa0E3WTNwRkZUTDI4TDdseXM2ckVHYXV4TlhGcmVlelRwMFRidFBsRXJDeVM0MzlfV1N3eUpzUWZQUlZzTGRoVEdpLWZYMnNYX0NsREE?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014051400063</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>‘1억 공천헌금’ 강선우·김경 오늘 1심 선고</t>
+          <t>다천 김종원, 추사 김정희 '충효가전' 편액 국립창원대에 기증</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>‘1억 공천헌금’ 강선우·김경 오늘 1심 선고  KBS 뉴스Google 뉴스에서 헤드라인 및 의견 더보기</t>
+          <t>(창원=연합뉴스) 박영민 기자 = 국립창원대학교는 경남도립미술관장을 지낸 서예가 다천 김종원이 추사 김정희(1786∼1856)의 '충효가전'(忠...</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9OMTJjTVhPZGVoOGRvak5nSXZ5eFEtZjNaVVJmaVJPSHV1OUpCczlucVNqdTBYZjZLbHo4d1U5aDJpUFAzTmIyYnJtS0RjUGZYV2g3Y2N2OG1CWFk?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014052700052</t>
         </is>
       </c>
     </row>
@@ -4699,27 +4699,27 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 "북극항로 시대 대비, 부산·동남권 미래 함께 열어가겠다"</t>
+          <t>전자발찌 차고 또 흉기난동…이상동기범죄자 80% '전과 있음'</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 "북극항로 시대 대비, 부산·동남권 미래 함께 열어가겠다"  정책브리핑북극항로 시범운항선 시찰 - 포토 | 멀티미디어  정책브리핑이 대통령 “국제사회 신뢰 속 북극항로 열어갈 것…해양강국 대한민국”  KBS 뉴스이재명대통령이 북극항로에 진심인 이유! (261013 화요일 클립...</t>
+          <t>(서울=연합뉴스) 한지은 기자 = 인천에서 전자발찌를 착용한 출소자가 불특정 다수를 상대로 흉기를 휘두르면서 고위험 범죄자의 재범을 막기 위한 ...</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>정책브리핑</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE81Q1ZoM2JvZTlBNWE0akI2UlpodWZtWlZyaGV1eEtHLWllWjBtRkcwdDhhMmhycWF4bl9CbE1lVzczZzhWbU9RZHdydlo2QlA0WGd5ei1KWU5pU0ZBbHliY1pGQ1gxVVRMZzR4SA?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014042000004</t>
         </is>
       </c>
     </row>
@@ -4736,27 +4736,27 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>[단독] ‘장모 살인’ 다음날 접근금지…경찰 6일 늑장, 공소청 2일, 법원 4일 걸려</t>
+          <t>'8명 부상' 인천 흉기난동 사건에 프로파일러 3명 투입</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>[단독] ‘장모 살인’ 다음날 접근금지…경찰 6일 늑장, 공소청 2일, 법원 4일 걸려  한겨레[단독] 장모 살해범, 이미 ‘수차례 전과’…상습범의 계획범죄 정황  JTBC‘장모 살해’ 20대 과거 수배 이력까지…‘장모 살해’ 경찰 대응 적절했나  KBS 뉴스[단독]가정폭력 검거 절반은...</t>
+          <t>(인천=연합뉴스) 홍현기 기자 = 인천 대형 상업시설에서 흉기를 휘둘러 8명을 다치게 한 50대 남성을 상대로 경찰이 범행 동기를 밝히기 위해 ...</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBEaERuWjVGMEt6UjJLeUlLTjItWHpCdkFiV21sRkZFM1pkOUtmN2RoWXg4dklPTWNMNHRJbVQtcmJ6WG5GdnczTEVLbFgyNTFXMzVUbFhaYzhhdTczNFFVN0g3QUFoUnNwLVZvaDNOb2VJUQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014050800065</t>
         </is>
       </c>
     </row>
@@ -4773,27 +4773,27 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>추미애 "李대통령 '호의호식' SNS, 날 겨냥했다 보지 않아"</t>
+          <t>농민 매년 300명 사망에도…농진청, 안전장비 보급사업 중단</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>추미애 "李대통령 '호의호식' SNS, 날 겨냥했다 보지 않아"  MBC 뉴스경기도 아닌 ‘추미애 국정감사’?…여야, ‘예산 삭감’·‘SNS 정치’ 질타  KBS 뉴스"일방독주" "여의도지사" 與도 野도 秋 난타  조선일보秋국감서 與공세성 질의에 '내분 분수령'…김지용 청문회도 주목(종...</t>
+          <t>(전주=연합뉴스) 김진방 기자 = 농업인의 재해율이 전체 산업 대비 8배를 웃도는 상황에서 농촌진흥청이 'IoT 농기계 교통안전 및 사고 감지 ...</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE94c3JuajRENkN6ZHdXM3piWHJzMUJnRGhkM3BoNjFPejZ0UDRMeVc2bFh3eFFpd0RFUkIzOURzSjc3aUh2MHVIREg2bEZDYVFvZEhtNmt2LTZmaFVKb0NBQUF5RFZTMFVMbXRTN2lEQ2k3R0Q4a0ZMa9IBeEFVX3lxTFB4Vi1HN0VFSGNxakxlVmdTb1J0ODFWOVZndFdVdmpqZjl2aERoMC1Ub1l6Rm5IMzk3bC1oSGRzZFN2ZkNlWXRqQVhkSVUtbEpabDJFTndVSGtTYUxXQXZKb2tSZmowM1hQUjRxSHdMZ2EzNEtFNEk3YQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014048200055</t>
         </is>
       </c>
     </row>
@@ -4805,32 +4805,32 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>정동영 "한미동맹 이상 없다"는데…강경화 "백악관과 소통 답답"</t>
+          <t>[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>정동영 "한미동맹 이상 없다"는데…강경화 "백악관과 소통 답답"  조선일보[사설]더 막 나가는 鄭 장관과 남 얘기하듯 하는 康 대사  동아일보강경화 '돌발 국감 발언'에 靑 당혹…李 "굴종·사대적 태도 지양"  데일리안국정감사 계속…주미대사관·헌재·식약처·경기도 등  연합뉴스주미대사관 ...</t>
+          <t>[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여  문화일보이재용, 장외매수로 삼성전자 766만주 매수…1.9조 규모  연합인포맥스홍라희 관장, 이재용 회장에 삼성전자 지분 2.6조 증여  조선일보홍라희, 이재용에 삼성전자 주식 1천115만주 증여…이재용 지분율 1....</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>문화일보</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNUzFnQnp1UXFnZHlUaXQ3RGtadVVQM1BnQlJfbnpPODRjU2NScmFRLWo2T1VGa2R5VzUyUU9iUXpONXhmNHFoaEpzbllhV0QyODdkb0g2T0ktajVBUTF1OWlBbkV4UkU1WV9XcWhpeU9WTWRJMXQtekxmdUNaUVhtNWJqbTRXZlBNMHlWSVZrN21Xd21IV04xN1BPSkI3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBGRllSNUNuOTVwTGl2OXM5a1RKazk3NnRwR2I2Z1ZqOTdveWpNZHYtLUZpVlZTOFlWS2FMNnNYLWpZbkFjTkM3RGNhY0I1UHgy?oc=5</t>
         </is>
       </c>
     </row>
@@ -4842,32 +4842,32 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>“내일 출근길엔 패딩 입어야겠네”…비 그친 뒤 기온 ‘뚝’ 최저 5도</t>
+          <t>[은행이 뚫린다-진단③] 보안업계 제안은? “IP 차단은 임시... 자산식별·행위분석·접점 숨기기 필요”</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>“내일 출근길엔 패딩 입어야겠네”…비 그친 뒤 기온 ‘뚝’ 최저 5도  매일경제[날씨] 서울 9.5℃, 올가을 최저...찬바람 불며 종일 쌀쌀  YTN올가을 들어 가장 쌀쌀한 아침…찬바람에 체감온도 ‘뚝’  경향신문대전·세종·충남 출근길 쌀쌀…바람도 강해 체감기온 뚝  연합뉴스쌀쌀한 가...</t>
+          <t>[은행이 뚫린다-진단③] 보안업계 제안은? “IP 차단은 임시... 자산식별·행위분석·접점 숨기기 필요”  보안뉴스[금융현미경]AI·해킹 위협에 금융권 내부통제 경고등…커지는 '임원 책임' 강화론  아시아경제[단독]망분리 완화 금융사 10곳, 보안계획만 세우고 이행 안해···내부망 해킹...</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>보안뉴스</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1qaGxTc0dhTEYxTDE1ZVZ3alA4TGd6WXhYdkhvckxmTlFiYmNxbllCNWwtdEJmTmtURjdld2pzY0Y1c3EtYWdmQWE1QW96MlJ4NUxPWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9ESmY2WkEzNVVwVGNGWm9GZjhVUVpRMXp4UWlWMDhwY0ZxTHJ6VllQUXpiOXFEUUtqbFdERk9ERDNzYUt4UklRelNWWEk3TGNFZ2szZDFxb2F0ODlzYm0tT05aVzBLbVdHZGVz?oc=5</t>
         </is>
       </c>
     </row>
@@ -4879,32 +4879,32 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 "주택·일자리·포용금융 정책 속도…성장 온기 함께 해야"</t>
+          <t>반도체, 이익 전망 대비 과도한 하락…"분할매수 대응“</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 "주택·일자리·포용금융 정책 속도…성장 온기 함께 해야"  정책브리핑이재명 대통령 "양극화 골 메우고 불평등 벽 낮춰야"  경상일보李대통령 “올해 韓 성장률 4%까지 예측…성장 그늘도 세심히 살펴야”  전자신문李대통령 "엎드릴 각오로"…장·차관·LH 사장 현장行, 착공 시험대...</t>
+          <t>반도체, 이익 전망 대비 과도한 하락…"분할매수 대응“  비즈워치“이젠 반도체 미련 버려야?”...내년 증시 주도주 바뀌나  매일경제반도체주 반등 언제쯤…“소부장이 투자 대안”  마켓인메모리 호황인데 '삼전닉스' 왜 떨어지나…"공급 과잉 우려·환율이 발목"  뉴시스반도체 미련 버릴까요?...</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>정책브리핑</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9TZXJHcVA5SDY5NVVLWmRSZEhMNUl1WUNxTmg5T3A2SjhsRGxZNkhSSC1uLXJtbUs3cUwxWlg0TGFZRUR1Q0YxQ0xNSE9KV292bDl3QnBNSElxcExJT1NwTG9kNS1SNTRxOGIySg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE8zZUN5TmF3dXFaQktYdkxDdlV6SUFTRndrcnVFZG1PcW92SUhkMzZpa3BLRDVZTFdHNzFRbDNfSWFjbEdUNnhZb2V0Zld6QmI0c3JjNzNPVWZCMXNpc2lpZTg3Y3BPSVRjTFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -4916,32 +4916,32 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>전경국 선린대 총장 취임…"미래사회 필요 전문인재 양성"</t>
+          <t>삼성·LG, 일상·산업 속 AI 기술 한눈에…’KES 2026’ 개최</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>(포항=연합뉴스) 손대성 기자 = 전경국(46) 신임 선린대 총장이 14일 취임해 업무를 시작했다.</t>
+          <t>삼성·LG, 일상·산업 속 AI 기술 한눈에…’KES 2026’ 개최  연합뉴스TVKTC, 한국전자전서 AI·소프트웨어·스마트가전 역량 선보여  전기신문산업부, 2030년까지 국가·지역 대표 전시회 5개 이상 육성  연합뉴스허공 위 버튼에 로봇손 학습까지...한국판 CES 개막  YTN...</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014038700053</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBfbWtIOGxCdFNuNW9Eb1lhaG9uMVlRNmVxRHJSSE1zTUlwdFY1bV9ORmI2NFkxcVhFSWlRZGwwSm11RVNzZGJKYkRWNm5kTFVnMGJCY0J1MEtwcmhaekp6NUQ4eWZrdU0?oc=5</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4963,22 +4963,22 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>강원경제자유구역청, 동해 북평지구 수소기업 투자 유치 나서</t>
+          <t>NDF, 1,341.90/ 1,342.30원…2.05원↓</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>(춘천=연합뉴스) 이재현 기자 = 강원경제자유구역청이 동해 북평지구의 수소산업 육성을 위해 관련 기업 유치에 나섰다.</t>
+          <t>NDF, 1,341.90/ 1,342.30원…2.05원↓  연합인포맥스중동발 유가상승·증시 급락에…환율 10원 오른 1,345.1원  연합뉴스반도체 호황에 ‘센’ 원화…1200이냐, 다시 1400이냐  경향신문원·달러 환율, 1340원대 초반 등락  뉴시스외인 증시 순매수 전환에…달러·...</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014035600062</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5HaGJxTHJkaTFEM1JDS09WTkNEX1ZMLUNuZEpYQ0Vjb0VhN1ZDb1FZeGo2S1hXM08yZDh6RTFqQUVxek9sVXNXUElXQnMwbGg0eGkyMDhOSmVFYUdjSDdjOGQxS0dycEJjYm8xXzZLaHXSAXRBVV95cUxQNjVRWjlpWDJNa1RiZVljNW5mOTQ4QjhmT1JkdXlfRU4tUEJEOE9XUTlTX1JGbmhBTFRRb1FtVUdnVVdHeTBpQ1ljNkRfRTBqQ19falEyN0thbmZiNHNtaTlab0JtREJnZHU0Wk5UdnBUVldzeQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -5000,22 +5000,22 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>강원산 감자로 만든 '감자전맛 감자칩' 15일부터 전국 판매</t>
+          <t>中 차세대 D램, 삼전닉스 주도판 흔든다?…"기술격차 3년" 업계 선긋기 - 머니투데이</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>(춘천=연합뉴스) 이재현 기자 = 강원에서 생산한 감자로 만든 '감자전맛 감자칩'이 전국 대형마트와 편의점에서 판매된다.</t>
+          <t>中 차세대 D램, 삼전닉스 주도판 흔든다?…"기술격차 3년" 업계 선긋기 - 머니투데이  머니투데이삼성證 "中 CXMT 리스크, 더 반영할 이유 없어…반도체 소부장 주목"  뉴시스창신메모리, 사실이면 "삼전닉스보다 빠르다"…긴장  JTBC애널리스트, 중국 CXMT의 주장이 마이크론 테크...</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014032500062</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBGZE5NWFB1MmgwZjZ2YWdqYl9XamNORTBzS2Zxb3ZwdHhqWWJRc0U2a2t5ZlE2VUFDT1l5YUxLTEQ0Z05kMXk0ODZ6OUxUTTlyMWxOWVpoQWpmVWwwUUI4akYzMDdzZDVY0gFuQVVfeXFMTkc5Rnc2ek9rNy00amdwbFBaZDU1blI1ODBoclpMUzVOQy0xTWlscENENUhJUjVJbU93UzV0UzNoMk11dm1WaTZuRzBkN1FVRHlELThlWkVJVUU0enFxQldEUnI3WkEtNmZTdTR6dGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5027,22 +5027,22 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>태안군의원 내년 의정비 4천364만2천원…올해보다 2.0% 인상</t>
+          <t>한화생명, '필요할 때 쓰는 종신보험' 출시</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>(태안=연합뉴스) 정윤덕 기자 = 충남 태안군은 내년 군의원 의정비가 올해보다 2.0% 인상된다고 14일 밝혔다.</t>
+          <t>(서울=연합뉴스) 강수련 기자 = 한화생명[088350]은 14일 보장이 필요할 때는 사망보험금을, 생애 자금이 필요할 때는 납입보험료 전액을 ...</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014039200063</t>
+          <t>https://www.yna.co.kr/view/AKR20261014053900002</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>스포츠박물관 도서관 15일 개관…송파구-체육공단 운영 협약</t>
+          <t>[게시판] CJ프레시웨이, 상생협력 아카데미 개최</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 정준영 기자 = 서울 송파구(구청장 서강석)는 서울올림픽기념국민체육진흥공단(이사장 하형주)과 지난 12일 '국립스포츠박물관 도...</t>
+          <t>▲ CJ프레시웨이[051500]는 지난 13일 서울 마포구 본사에서 중소식품 협력사의 식품안전 역량 강화를 위한 프로그램 '상생협력 아카데미'를...</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014037500004</t>
+          <t>https://www.yna.co.kr/view/AKR20261014026300030</t>
         </is>
       </c>
     </row>
@@ -5101,22 +5101,22 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>현대차그룹, 학대피해 아동 돕는 '아이케어 카' 20대 기증</t>
+          <t>카카오, 인적분할 앞두고 CEO 총출동…새 성장전략 공개</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 홍규빈 기자 = 현대차그룹은 학대 피해 아동을 지원하는 '아이케어 카'(i-CARE CAR) 20대를 기증한다고 14일 밝혔다...</t>
+          <t>(서울=연합뉴스) 한상용 기자 = 카카오[035720]는 인적분할을 앞두고 증권사 애널리스트 등을 대상으로 주요 계열사 최고경영자(CEO)들이 ...</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014031700003</t>
+          <t>https://www.yna.co.kr/view/AKR20261014055100017</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>함안 남해고속도서 덤프트럭이 통근버스 추돌…12명 병원 이송</t>
+          <t>[보령소식] 종합체육관서 20일 취·창업 박람회</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>(함안=연합뉴스) 박영민 기자 = 14일 오전 7시 44분께 경남 함안군 군북면 남해고속도로 순천 방향 군북IC 인근에서 40대 남성 A씨가 몰...</t>
+          <t>(보령=연합뉴스) ▲ 종합체육관서 20일 취·창업 박람회 = 충남 보령시는 아주자동차대학교와 함께 오는 20일 오후 1시 30분부터 보령종합체육...</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014034800052</t>
+          <t>https://www.yna.co.kr/view/AKR20261014050500063</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>제주 펜션 풀장에 16개월 여아 빠져 중태</t>
+          <t>카카오페이, 마이데이터 기반 '멤버십 사후 적립' 출시</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>(제주=연합뉴스) 고성식 기자 = 13일 오후 6시 2분께 제주 서귀포시 대정읍의 한 펜션 풀장에서 16개월 된 여아가 물에 빠져 구조됐지만 중...</t>
+          <t>(서울=연합뉴스) 오지은 기자 = 카카오페이[377300]가 마이데이터를 활용해 결제 당시 놓친 멤버십 포인트를 나중에 적립할 수 있는 서비스를...</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014035300056</t>
+          <t>https://www.yna.co.kr/view/AKR20261014043700017</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>인천 백령도·대청도 강풍주의보 해제…서해에 풍랑주의보 해제</t>
+          <t>hy "자체 개발 유산균, 알코올성 간손상 완화"…국제학술지 게재</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>(인천=연합뉴스) 기상청은 인천 백령도·대청도에 발령했던 강풍주의보를 14일 오전 9시를 기해 해제했다고 밝혔다.</t>
+          <t>(서울=연합뉴스) 한주홍 기자 = hy는 자체 개발한 프로바이오틱스 균주 'HY7804'의 알코올성 간손상 완화 가능성을 확인한 연구 논문이 국...</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014036300527</t>
+          <t>https://www.yna.co.kr/view/AKR20261014044100030</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>울산 시내버스 노선 개편 설문서 '배차시간 단축' 요구 최다</t>
+          <t>카이아, 490만개 KAIA 소각…JPYC도 기여보상 대상</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>(울산=연합뉴스) 김용태 기자 = 울산시가 시내버스 노선 개편을 위해 실시 중인 시민 설문 조사의 중간 집계 결과 '배차 시간 단축' 요구가 가...</t>
+          <t>(서울=연합뉴스) 유동현 기자 = 카이아 DLT 재단이 자체 블록체인 네트워크의 토큰인 카이아(KAIA) 490만개를 소각한다고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014024500057</t>
+          <t>https://www.yna.co.kr/view/AKR20261014051200002</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>24억원어치 암표 판매업자 검거 경찰팀에 1천500만원 포상금</t>
+          <t>[게시판] 토스증권, 앱에 '시장' 탭 신설…AI시황 요약 제공</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 한지은 기자 = 경찰청은 전문 암표업자 검거와 자살시도자 등을 위한 일시보호센터 도입 추진 등 20건을 특별성과 포상 대상으로...</t>
+          <t>▲ 토스증권은 앱 내 '시장' 탭을 새롭게 도입했다고 14일 밝혔다. 이 탭에서는 주요 국내외 지수와 수급 등을 확인할 수 있다. 특히 'AI(...</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013179100004</t>
+          <t>https://www.yna.co.kr/view/AKR20261014049900008</t>
         </is>
       </c>
     </row>
@@ -5323,22 +5323,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>쌍용C&amp;B "태국 수출 물량 두배 확대…'한국산' 높은 신뢰 덕분"</t>
+          <t>KB국민은행, 기업고객용 'KB B2B우대통장' 출시</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>(세종=연합뉴스) 이상서 기자 = MSS홀딩스(이하 MSS)의 쌍용C&amp;amp;B가 최근 주요 제품을 태국에 수출하기 시작하면서 수출 비중을 지속...</t>
+          <t>(서울=연합뉴스) 한지훈 기자 = KB국민은행은 14일 기업 전용 파킹통장 'KB B2B우대통장'을 출시했다.</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013148400030</t>
+          <t>https://www.yna.co.kr/view/AKR20261014051700002</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>[내일날씨] 전국 맑고 일교차 커…경기·강원 북부 늦은 오후 비</t>
+          <t>[게시판] LS증권, 국내 선물·옵션 수수료 할인 이벤트</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 조현영 기자 = 목요일인 15일은 전국이 대체로 맑고 일교차 큰 날씨가 이어지겠다.</t>
+          <t>▲ LS증권[078020]은 국내 선물·옵션 신규 및 휴면 고객을 대상으로 거래 수수료를 할인해주는 이벤트를 12월 31일까지 진행한다고 14일...</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014011600004</t>
+          <t>https://www.yna.co.kr/view/AKR20261014050100008</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>[부산소식] 동의대, 재난관리 전문인력 양성사업에 선정</t>
+          <t>메리츠증권, 캔톤 재단과 금융자산 토큰화 협약체결</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>(부산=연합뉴스) ▲ 동의대, 재난관리 전문인력 양성사업에 선정 = 동의대학교는 행정안전부의 '재난관리 분야 전문인력 양성사업'에 선정됐다고 1...</t>
+          <t>(서울=연합뉴스) 김유아 기자 = 메리츠증권은 캔톤 네트워크(Canton Network) 운영 재단인 캔톤 재단(CantonFoundation)...</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014031500051</t>
+          <t>https://www.yna.co.kr/view/AKR20261014050900008</t>
         </is>
       </c>
     </row>
@@ -5439,27 +5439,27 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>“코스피 6천 겨우 턱걸이”…범인은 중국 반도체? [잇슈 머니]</t>
+          <t>코람코라이프인프라리츠, 전국 주유소 19곳 매각 추진</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>“코스피 6천 겨우 턱걸이”…범인은 중국 반도체? [잇슈 머니]  KBS 뉴스센터장도 '당황' 삼전 잘 나가는데 도대체 왜 떨어지나 "이유 굳이 굳이 꼽자면…"  YTN대신證 "PER 5배 이하서 매도 실익 없어...분할매수 유효"  마켓인[오늘의 증시]코스피 야간선물 1.7%↑…'검은...</t>
+          <t>(서울=연합뉴스) 정회인 기자 = 코람코자산신탁이 운용하는 코람코라이프인프라리츠가 포트폴리오 재편과 신규 성장자산 투자를 위해 전국 주유소 19...</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE81LTZBQkc1a0xKWXZmaUxsUXNOenBBcERySmFId2dndW94MjBtLXZWOURVUkZ0WVpQYXluc0hydTdvcjAwSHhoWlhsU3VPZGd1YlFvU1dfckxfUFE?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014049700008</t>
         </is>
       </c>
     </row>
@@ -5476,27 +5476,27 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>IMF, 올해 韓 1인당 GDP 4만弗 돌파 전망…명목 GDP 2.2조달러 관측</t>
+          <t>관세청 "최근 5년 국회 반복지적 전면 점검…8건 개선 완료"</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>IMF, 올해 韓 1인당 GDP 4만弗 돌파 전망…명목 GDP 2.2조달러 관측  연합인포맥스IMF, 올해 한국 경제성장률 3.3% 전망…7월 대비 0.7%↑  정책브리핑성장률 전망 3.3%로 오른 날, 코스피는 5% 폭락  조선일보IMF "선진국 재정적자 GDP의 5.2%…코로나 이후...</t>
+          <t>(세종=연합뉴스) 안채원 기자 = 관세청은 최근 5년간 국정감사에서 반복적으로 지적돼온 사항을 전면 점검해 총 8건의 개선 조치를 완료했다고 1...</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1sTGQ3OGV4TW55VElfaEZWN0FWak8tLTVXZHpOY0VKTVZkTzNCOXNHcEIzejFEYWYyVnU0d2dBQURsMlBIYWdKZ21ZenkwQlNCT0g0NkJLNGx3LVAxWWo5VERwZUJvTGtRcG5RYXd3SVg?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014047700002</t>
         </is>
       </c>
     </row>
@@ -5513,27 +5513,27 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>홍라희, 또 이재용에 지분 넘겼다…이번엔 삼성전자 2.6조</t>
+          <t>LH, 공동주택 중대하자 4년새 90% 감소…"품질관리 강화"</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>홍라희, 또 이재용에 지분 넘겼다…이번엔 삼성전자 2.6조  비즈워치이재용, 장외매수로 삼성전자 766만주 매수…1.9조 규모  연합인포맥스[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여  문화일보홍라희 관장, 이재용 회장에 삼성전자 지분 2.6조 증여  조선일보홍...</t>
+          <t>(서울=연합뉴스) 오예진 기자 = 한국토지주택공사(LH)는 공동주택 품질 개선에 노력한 결과 올해 균열, 누수 등 중대하자 발생 건수가 크게 감...</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwN01xRjFiRF9ZMjJUUG1PUWlGaWRHV2hsLWNCY2ZnYnRTREtGcXYxMFF6X0k3YXRXM3Z1dW04Qm1IbE9rdUY5cm1IVG9FVDZ5M29GNXA2VFgxS0VLT0RtTW1rTW5wWHFJTXZ1Ng?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014047500003</t>
         </is>
       </c>
     </row>
@@ -5555,22 +5555,22 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>뉴욕증시 일제히 하락…美은행 실적 혼조·반도체 약세 여파</t>
+          <t>섬박람회 논란 큰데 이번엔 K컬처 전시회?…117억 투입 지역행사 키운다</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>뉴욕증시 일제히 하락…美은행 실적 혼조·반도체 약세 여파  연합뉴스TV은행 실적 기대 못 미치고 반도체 약세…뉴욕증시 일제히 하락  조선일보[뉴욕증시] 출발이 살짝 불안한 어닝 시즌…하락 마감  연합인포맥스[속보] 삼전닉스 프리장 2%대 상승 … 중국발 쇼크에 美 반도체는 약세  뉴데일...</t>
+          <t>2030년까지 전시회 5개 이상 육성 첨단 제조산업·K-컬처 등 연계 계획 기존 전시장들 낮은 가동률은 문제정부가 2030년까지 국가·지역 대표 전시회를 5개 이상 육성하고 관련 ..</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBqenprbEMybXJmWVh1eUpDekswMGNoaGZ6WjhUU2hpRVRYUF8xNXRGWEFaLWdlY2F2VGxMVEtscTJPOGViQ1p5SnRCUzBvVTRGSVN4SzJxWTVqdWpEUzFORFlNZ0JseDA?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12175201</t>
         </is>
       </c>
     </row>
@@ -5582,32 +5582,32 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>주주환원 늘었는데 세금은 제각각…입법조사처 "배당세제 정합성 손봐야"</t>
+          <t>교황 레오 14세 폐암 진단…“오른쪽 폐 일부 절제”</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>주주환원 늘었는데 세금은 제각각…입법조사처 "배당세제 정합성 손봐야"  연합인포맥스상장사, 자사주 62조 소각해 1년 새 156%↑…삼전닉스가 절반  매일경제 마켓자사주 소각 1년 새 156% 급증⋯삼성전자•SK하이닉스가 절반  브릿지경제"상법 개정의 역설"…유증 부담에 PRS·신종자본...</t>
+          <t>교황 레오 14세 폐암 진단…“오른쪽 폐 일부 절제”  한겨레교황청 "레오 14세, 폐 결절 수술 성공적 완료"…남미순방 갈듯  마켓인교황, 폐 결절 제거술 위해 로마 병원에 입원  연합뉴스바티칸 "교황 레오 14세 폐암 진단…수술 성공적" - 머니투데이  머니투데이[속보]교황 레오16...</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5tQlNOUERvNU54YVhIN2xOQ0lVdThfZmptd3AzY05SdlZxZ2FuZ0dvcXhnRXNqVEpBTk9yY3lNbkphd1pRVklkbTVtVnl2czZEWG0yZUdkS2tUNlJ5WXdyOTBPUWhvRDlXMlBMRDZPMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNSFNnUnVzUU4taDNoM1NEcmU5YlpXaVozdzFjT3N5UENKS2hTU3o4LW1hN0FtUzNYNDJ6WDBxVS0ydGFxSHJZUTd2LWpzbFFaZDNRMGM2X3hzRm5STUxLcmlHR2Y2M1FTQlBIa1AxbFRZazJpS0dmdHBEQWlyT0doM1h3?oc=5</t>
         </is>
       </c>
     </row>
@@ -5619,32 +5619,32 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>가족 연계 회사에 수년간 자문료…전 LG엔솔 사장 ‘배임’ 수사</t>
+          <t>여객기 납치경보에 교신까지 끊겨 독일 발칵…알고보니 시스템 오류</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>가족 연계 회사에 수년간 자문료…전 LG엔솔 사장 ‘배임’ 수사  KBS 뉴스[단독]가족 연계된 中컨설팅사에 10여년 자문료… 100억 손해 혐의 LG엔솔 前사장 압수수색  동아일보'가족 연계 中업체에 100억 자문료'…경찰, LG엔솔 전 사장 '배임' 수사 - 머니투데이  머니투데이경...</t>
+          <t>여객기 납치경보에 교신까지 끊겨 독일 발칵…알고보니 시스템 오류  연합뉴스TV“드론 추정 물체 목격, 항공 비상 상황”···독일 뉘른베르크 공항, 항공기 운항 중단  경향신문독일행 여객기 납치경보 잘못 보내 전투기 출격 소동  MBC 뉴스'7500' 여객기 하이재킹 오경보에 獨전투기 2...</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE51dUxwVzFJQWd3UkxSOHlLWTZvVS0wQnltS0RwNnlYaHZjS1pod0pqQWpqZ0RvcVU5MUVJeG1XSnpBZTVsSk9DOXhJN1hkTFg1M3BrSXo5MWM3Uzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE81QWVvWkFRaTBZYmdkb25GbnZyOWFoR2tCUzNhMWxoVHpsUkR6dzFnRm9ZSmZBemxLQW5ZNExNVnRqaWxjbWx4bldiamd6WmlXM0NrS3ZKd29mXy1zdW5tOG5JNVJnU1k?oc=5</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -5666,22 +5666,22 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>거침없는 외인 매도...반도체 역대급 실적에도 급락, 왜?</t>
+          <t>트럼프 "우크라이나와 정보 공유 중단 안 해…푸틴, 종전 더 원해"(종합)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>거침없는 외인 매도...반도체 역대급 실적에도 급락, 왜?  YTN100조원 벌었지만 증가율은 반토막…외국인 올들어 232조원 ‘엑소더스’  한국경제삼성전자·SK하이닉스, 두번째 바닥 찍었나…“W자 반등 기대”  마켓인"내년도 삼전닉스 성장동력은 HBM4…엔비디아 루빈 출하 본격화"  ...</t>
+          <t>트럼프 "우크라이나와 정보 공유 중단 안 해…푸틴, 종전 더 원해"(종합)  뉴스1‘경유 딜’ 우크라 반발에… “美, 종전 협상단 방러 보류”  동아일보트럼프 ‘에너지 휴전’ 후폭풍 속 침묵하는 푸틴…왜?  경향신문공화·민주 상원의원 12명 "러시아 경유 합의는 적국에 주는 선물"  뉴...</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE84MU9jNnEweUVaeWZ5emd5RFNjQmdEd3N2RDUweDViQnBKTVJsbnJXWGlHaDQ1TmY2VzFyMm1aUkFoLVktTUJFY0pLcXlIREtSQ1dveEwxYVpUNDdiZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCYmM0WHNQd01tM3A3MThrZ3FEbVBySlQ0OFVKZVVsSjg2SmVCYndZRXBLWGVOX201Ukhjd3ZwSzNJQnBGVVJITWRVdVRmYWFFdEdOMllZRHk?oc=5</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5703,22 +5703,22 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>[단독]망분리 완화 금융사 10곳, 보안계획만 세우고 이행 안해···내부망 해킹 노출될 뻔</t>
+          <t>美 정보공유 안했나?…러 미사일, 공습경보 발령 전 키이우 타격</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>[단독]망분리 완화 금융사 10곳, 보안계획만 세우고 이행 안해···내부망 해킹 노출될 뻔  경향신문경찰, 금융권 해킹수사 美 FBI와 공조…공격자 신원·활동 추적  연합뉴스“보안 담당임원, 경영진 제동 걸 정도 힘 실려야” [해킹에 뚫린 금융 ⑦]  IT조선[금융현미경]AI·해킹 위협...</t>
+          <t>美 정보공유 안했나?…러 미사일, 공습경보 발령 전 키이우 타격  뉴스1우크라 드론이 러시아 데이터센터 때리자 중앙아시아 앱 '멈춤'  연합뉴스러 미사일 공격으로 부상한 여성 옮기는 구조대  뉴시스러 데이터센터 피격에 카자흐 주요 플랫폼 마비…디지털 인프라 의존 한계  아시아투데이[포착...</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5IT2RzRnhNZmloc0luUTFHMi1iTnpuZWdra0NXdlFOdFBReEpLUFJtdkdOMV9reGJnaDZmTmJNVEdrbjZvbjczVndMZWhfajR5N201NF80bVZsUdIBX0FVX3lxTE1OclA5Q2EwWDN3b3paSUYwck9BRE5HM0doUE9ZWFladzduUlNuQVRNSExWWVgwR3dxbjVsR2tfZ1pKTEdUcEs5T1RTUTBKNHJ6X1gtTk54dTkzalI1SkZF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFA5cFVCdDlfQ1VyOFp0ZEpsRVh1MUxrVnM4SFlvYVl1WE5SRVJWWC14VXNQWXo2VnplQVk1ZFhqanNlcnd0NjQ1bklEV3RsV0FieEsw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5730,32 +5730,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>원화값 1330원대 강세…삼성전자 배당·美 금리가 변수</t>
+          <t>‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>원화값 1330원대 강세…삼성전자 배당·美 금리가 변수  매일경제Google 뉴스에서 헤드라인 및 의견 더보기</t>
+          <t>‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임  경향신문"가족은 아니었다"…트럼프, '아들 전 약혼녀' 그리스 대사 해임  마켓인백악관, '각종 비위 의혹' 그리스 대사에 "사퇴 요구했다"  연합뉴스트럼프와 측근 인사 부패 의혹, 미 중간선거 쟁점 부상  뉴시스"억대 빚...</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Jb0NSMmpTSnZzMHVwOEloSWZmRlBNcDEwN2RZTGwzcE5TV2FaZC1JS0FqaGgwdGlqTVpxMjh2aGRpYmp1d1hYcmY2amRiaXN6cXNfcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBsanNzT0RJMzI1SGI4b3ByWUJPUXRzdEgzTGtkZl90Wmo5dUhrSE53MmFpbDBuQmdEcXNUVy1vV1dFSGlQMG5EdVFfQmhTZHVOcG1taUVubS0yd9IBX0FVX3lxTE5nUV8yQUZXOUZ2SV9JeUpLa2lzc0t5QXlOREoyYmh6STFLX0VKd2hJTTg2WnllWTBRQ1JTdlZDbFVpT2VXa2k1MGE2N05qQjI5R1J0WTZZZmMweEJySnRz?oc=5</t>
         </is>
       </c>
     </row>
@@ -5767,32 +5767,32 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>靑, 초과세수 활용 국채 발행 축소에 "부처간 이견 無"</t>
+          <t>신압록강대교 북한 쪽 관문에 인공기·오성홍기 내걸려‥개통 임박 정황</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>靑, 초과세수 활용 국채 발행 축소에 "부처간 이견 無"  연합인포맥스靑 "'초과세수' 활용 국채 축소 범위 이견 없다…토론 통해 정리" - 머니투데이  머니투데이국고채 금리, 코스피 급락·외인 매수에 이틀째 큰 폭 하락  연합뉴스"그게 네 거냐?"…'63조 제로섬 게임' 벌이는 재경부...</t>
+          <t>신압록강대교 북한 쪽 관문에 인공기·오성홍기 내걸려‥개통 임박 정황  MBC 뉴스北中신압록강대교 개통 임박했나…북측 관문 북중 대형국기 포착  연합뉴스[특파원리포트] 두 개의 다리와 북한의 몸값  세계일보북한 남포항 컨테이너 단지를 촬영한 위성사진. 올해 10월 7일 촬영된 위성사진에서...</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5jWi11SE4zRENIUHh1UmF3OS1ZYWN3XzZvLUVpcGs0enlWRncyRXd3UzFUT1JmNVkwVDZUUEdxU3VCNlRnOEFYeFQ0b1dacTVMWGdWZFdNT19MNzdVQ3RVbXBKSVhtYk5yRkZjUnRuU3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1tYXFLZnE3VmpmekdBZnpWM2FfalNNejBfT2oxMTVYRUR5cEY4WFMtamE0X1pscGNvZ0x3VjRiN2JtbFEtTEFRbXdlR25xczVZemMwUHZqbVNZTzJMdzhBRWtKX1NSU1BjWUJVUzZqSHlSS2dx0gF0QVVfeXFMTjdRbDZnbU5wdFBtMVJQY1RMZjRwRS1JQjdmQVRNR2lDUFNPQzlZVEhEWURZb25wWGptQXNMR1lrT0czSmMxc1lEakhHNVVqYjJkdkM3OVFPUUQwU01lNUEzNk1EZUpZVkZhV3dJYkIzbDFRWmU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -5814,22 +5814,22 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>[잇슈 SNS] 미 놀이공원서 또 롤러코스터 사고 “1명 사망·4명 부상”</t>
+          <t>"호르무즈 선박 피격 2주간 24건…이란전 이후 최다"</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>[잇슈 SNS] 미 놀이공원서 또 롤러코스터 사고 “1명 사망·4명 부상”  KBS 뉴스美 테마파크 또 롤러코스터 사망 사고…연이은 안전 논란[이런일이]  노컷뉴스공중에 멈춘 롤러코스터, 1명 추락사…美 놀이공원서 또 사고 - 머니투데이  머니투데이Six Flags Entertainme...</t>
+          <t>"호르무즈 선박 피격 2주간 24건…이란전 이후 최다"  연합뉴스TV"호르무즈 선박 피격 2주간 24건…개전 이후 최다"  연합뉴스이란군 “호르무즈 동부 선박 주시…금지 구역서 유조선 화재”  KBS 뉴스호르무즈 유조선 연쇄 공격… '중동 원유' 수출 회복세 또 꺾이나  마켓인호르무즈 ...</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5CZTBncGdVYzRQTHdTQjZWMHk0R3FRdmJ5X1k0VzdrYVpubXZJMW9wN1hfa0RvV0FvSU5qM0xjNERLR0FybVctb00xbURGLTduZ3dfYWxmeTNISzdnOENpVF9RaEVJUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE80R1Ezc0hlaWJRSUNQUk1XWmNDU1JDYVNSOWxwWm1JY0lTblpSZ055YXNwWmhKcDJSN3VMUk9HcTk2dnluSkpkX1lLSXRYWTJhSmRXV2RCVGxlY1dva3NwRlBOa2hkMms?oc=5</t>
         </is>
       </c>
     </row>
@@ -5841,32 +5841,32 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>노동부 장관 “포스코 교섭 적극 지도…신안산선 사고 엄중 조치”</t>
+          <t>PAK DA 지연에 Kh-BD 부상…러시아 공중 핵억지력의 불확실성</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>노동부 장관 “포스코 교섭 적극 지도…신안산선 사고 엄중 조치”  KBS 뉴스[기자수첩] 포스코 노사, 철강업·지역경제 위기 극복이 먼저다!… 대승적 자세로 합의점 찾기를  폴리뉴스 Polinews김영훈 "포스코 교섭 적극 지도"…직고용 갈등엔 "현장 찾겠다"  뉴스1포스코 노사 14일...</t>
+          <t>PAK DA 지연에 Kh-BD 부상…러시아 공중 핵억지력의 불확실성  Meta-Defense</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>Meta-Defense</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5GdV9XNUJWZmtFQW82N2xHcVV5V184ZzFzcGVrdGVUVzJlZm1haWFPb2NXc0ZZRGtGWUQ2MmpNYTNlR3dyNldOQ1BkSnhieUdrZmhmNnR2aG9yWjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQbEEyUy02aDN4OG5KVVdhSUl2TkZzck83eVhHRFB2eHZqMEY0U21BemgtS3VKNDBZOHlmWHN2MTg1M2xsMWF1RENwNl9kbkJGUEx2V1dRcUMxLTRNSXBBUVY2UU1oYk01RWE0Vk94emxHQ3VWVzg4U1N3ZGVVeFFQRlJqY0ptR2Ez?oc=5</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -5888,22 +5888,22 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>연준 '매파' 해맥 "제약적 정책 기조 필요"…이달 관련 언급은 안해</t>
+          <t>다급한 룰라, '소상공인 부채탕감' 대선 결선용 선심법안</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>연준 '매파' 해맥 "제약적 정책 기조 필요"…이달 관련 언급은 안해  연합인포맥스뉴욕 연은 윌리엄스 “내년에 금리 추가 인상 필요 없어”  KBS 뉴스美연준 해맥 "금리 소폭·잦은 조정 바람직…인플레 고착 위험"  연합뉴스시카고 연은 총재 "금리 인하경로로 복귀하려면 진전 필요"  연...</t>
+          <t>다급한 룰라, '소상공인 부채탕감' 대선 결선용 선심법안  연합뉴스[브라질증시] 이보베스파 1.04% 하락…룰라·플라비우 지지율 격차 주시  뉴스핌트럼프 ‘블루 타이드’ 마지막 퍼즐 완성하나…‘보우소나루 정치 왕조’ 계승자 [더 비저너리-플라비우 보우소나루]  헤럴드경제브라질 대법원, ...</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5DamUzb21IazZqXzNRQVlIYTc0VWxaVzRTTnhLNnJNRklseE1VYmdOelpFZEVxdWx0QkZoR0NPeEdXQlhHZDgwMGtGRHhXall1clo4elEtcFV1a3BQbWxiTjBlRHByalY0QTVrZmE3U2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1QYjRyYU1pSUdDc2x4SVotMktwUTRfSk5XTEFIanI1UzVGWHdKeVZlWnpfQThvV3BNbTJ0X2t2SjBUa21UUnVaR0NDVWJGV2QyNlM4ZVM4TlBoY0nSAWBBVV95cUxOaTNpZ0FuR0plZ0k4ZE5GLTBlS2NaTjR2Vkp5M2Y3NExOZ0hoUmJ6cmQ1ZGZTc2l6bHNtbVh2dkZ2QjRZUENiVUlUM1NuQWp1bU9HTUQ3OV95UTJpRnRkcEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -5915,32 +5915,32 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>임광현 “이 대통령 아파트 거래, 과세 대상 아냐”…증여세 과세기준 이하 판단</t>
+          <t>"오픈AI, 사이버보안업체 '트레일오브비츠' 인수 추진"</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>임광현 “이 대통령 아파트 거래, 과세 대상 아냐”…증여세 과세기준 이하 판단  한겨레임광현 국세청장 “이재명 대통령 아파트 거래, 과세 대상 아니다”  경향신문“대통령처럼 아파트 거래했더니 세무조사 받았다” 국세청장의 답변은  문화일보의사봉 두드리는 조승래 국회 재경위원장  뉴시스[2...</t>
+          <t>(서울=연합뉴스) 이성한 기자 = 오픈AI가 사이버보안 업체인 '트레일 오브 비츠'를 인수하기 위한 협상을 진행하고 있다고 미국 IT전문매체 디...</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFAyS1lBbEg0RFVvNVIzZVlfSjBGU3dTNzM1aUtISEpjc3dCQ2lvNEZXOGQzV3E1MjdBeEhUU1MwdGtkQW8yNXc2WlFMdk05T0ltZVlJX2tNMVF0b0NlQUI2QlBXWXVtOG04anlpNWM2bmRIZw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014042500009</t>
         </is>
       </c>
     </row>
@@ -5952,22 +5952,22 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>코오롱인더스트리, 채용전환형 인턴 모집…19일까지 접수</t>
+          <t>앤트로픽, 14일 공식 재무상황 공개</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 조성흠 기자 = 화학소재 기업 코오롱인더스트리는 제조 부문에서 2026년 채용전환형 인턴 채용을 실시한다고 13일 밝혔다.</t>
+          <t>(서울=연합뉴스) 주종국 기자 = 기업공개(IPO)를 준비 중인 인공지능(AI) 모델 개발 기업 앤트로픽이 14일(이하 현지시간) 기관투자가들과...</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014039100003</t>
+          <t>https://www.yna.co.kr/view/AKR20261014050400009</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>한투운용, 펀드 한곳에서 검색·비교…'투자플러스' 출시</t>
+          <t>국방비 연 112조원 쓰고도 난타당하는 사우디…"지킬 게 많다"</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 고은지 기자 = 한국투자신탁운용은 상장지수펀드(ETF)를 비롯해 공모펀드를 한곳에서 검색·비교해볼 수 있는 투자 플랫폼 '투자...</t>
+          <t>(서울=연합뉴스) 임화섭 기자 = 사우디아라비아는 막대한 국방비 지출이 무색하게도 최근 예멘 후티 반군이 쏘는 미사일과 드론에 공항, 정유소, ...</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014033800008</t>
+          <t>https://www.yna.co.kr/view/AKR20261014046300009</t>
         </is>
       </c>
     </row>
@@ -6026,22 +6026,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>[특징주] 철강주, 백악관 대변인 알래스카 LNG 언급에 상승</t>
+          <t>다저스 감독 "오타니 3차전도 출전"…선발 제외 가능성 일축(종합)</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 임은진 기자 = 철강주가 백악관 신임 대변인의 알래스카 액화천연가스(LNG) 개발 사업에 대한 한국 투자 언급에 14일 장 초...</t>
+          <t>(서울=연합뉴스) 천병혁 기자 = 미국프로야구 메이저리그(MLB) 로스앤젤레스 다저스가 간판스타 오타니 쇼헤이(32)에 대한 신뢰를 재확인했다.</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014038300008</t>
+          <t>https://www.yna.co.kr/view/AKR20261014019651007</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>전날 급락했던 코스피, 상승 출발…1%대 오름세</t>
+          <t>베트남에 'K-문화유산 보존법' 전한다…22일까지 현지 교육</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김유향 기자 = 전날 급락했던 코스피가 14일 장 초반 1% 내 상승세를 나타내고 있다.</t>
+          <t>(서울=연합뉴스) 김예나 기자 = 한국의 문화유산 보존과학 전문가들이 베트남 현지에서 문화유산 보존·관리 노하우를 전한다.</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014037100008</t>
+          <t>https://www.yna.co.kr/view/AKR20261014042800005</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>[게시판] NH농협은행 금융투자자문, 키움증권 영웅문S에서도 이용</t>
+          <t>세레브라스 CEO "데이터센터 반발은 공포 마케팅 탓"</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>▲ NH농협은행은 13일 서울 중구 NH농협은행 본사에서 키움증권[039490]과 '금융투자자문 서비스 활성화를 위한 업무협약'을 체결했다고 1...</t>
+          <t>(샌프란시스코=연합뉴스) 권영전 특파원 = 엔비디아 대항마로 꼽히는 인공지능(AI) 칩 개발사 세레브라스의 앤드루 펠드먼 최고경영자(CEO)는 ...</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014035100002</t>
+          <t>https://www.yna.co.kr/view/AKR20261014022500091</t>
         </is>
       </c>
     </row>
@@ -6137,32 +6137,32 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>유통업계, 김장철 앞두고 절임배추 사전 예약 판매…할인 행사도(종합)</t>
+          <t>NASA 화성 로버, 45.22㎞ 주행 신기록…마라톤 풀코스보다 더 달려 [여기는 화성]</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 정수연 김세린 기자 = 유통업계가 김장철을 앞두고 절임배추 사전 예약 판매에 나서고 김장 재료 할인 행사를 진행한다.</t>
+          <t>NASA 화성 로버, 45.22㎞ 주행 신기록…마라톤 풀코스보다 더 달려 [여기는 화성]  지디넷코리아화성에서 45.2km…퍼시비런스, 지구 밖 천체 주행 신기록  한겨레NASA 화성탐사 로버 퍼서비어런스, 지구밖 최장 주행  연합뉴스화성서 45.2㎞ 달린 퍼서비어런스… 지구 밖 로버 ...</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>지디넷코리아</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013159551030</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1sV0ZxS09JU05rdnJhclRvVlFwbFR6X1p1ZWQ1WnFxSFdic1VzZXdubHhGVmhyVHpEaEhQNk1oQWsxbWQ3cXQ0akp1cldsR3A3RWR4TEdR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -6184,22 +6184,22 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>오는 22일 '증평 일자리 이음 취업박람회'…212명 채용 추진</t>
+          <t>XBOX, AI 에이전트와 게임 디컴파일을 탐구하는 XBOX LABS 출범</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>(증평=연합뉴스) 박재천 기자 = 충북 증평군은 지역 기업의 인력난 해소와 구직자 취업 기회 제공을 위해 오는 22일 증평생활체육관 1층 로비에...</t>
+          <t>XBOX, AI 에이전트와 게임 디컴파일을 탐구하는 XBOX LABS 출범  Unite.AI엑스박스, 신기술 실험조직 ‘엑스박스 랩스’ 출범  지디넷코리아게임 넘어 디즈니처럼… MS, 엑스박스 엔터 사업부 ‘XP’ 신설  IT조선Xbox, 영화, TV, 라이브 이벤트 및 소비재를 전담하...</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>Unite.AI</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014036400064</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPV1A1WUZhSVlvQnZxSlNLeG1xZFFROHVKVzc5YkJxTFVnVnR4Q0x4TS1GdXJ0QUEtOW54Ym1JaWVfVmlUZTNoWlZWVlp5SEhfaXo1cGpwbW1ESHhoUXhLLWJubXZRbW1KX1FnZnlWa190Y1padmc3bG04NGxYenp4dHFKUEFGbi1JVHRlaTdhTEJZWFlhMmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6211,32 +6211,32 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>대웅제약, 마이크로니들 무균 제조소 구축한다</t>
+          <t>[이슈] 컬렉터스 에디션인데 게임이 없다?</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 신선미 기자 = 대웅제약[069620]은 경기 화성시 향남 대웅바이오 3공장에 마이크로니들(Microneedle) 제조 인프라...</t>
+          <t>[이슈] 컬렉터스 에디션인데 게임이 없다?  인벤</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>인벤</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014031000017</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1WV3lvcVpSZTVFQ0lzNTZob1RNYVFmNUwwMGFVSHFnSWRQZndnNlhCdDF0T1cwSm5xbG9MUnl1dUVPelVNa1NrVThZcFRhWWxMQmVWd043NlhnU2JZRmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6248,32 +6248,32 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>이형일 "반도체 다음은 서비스산업…입법 협조 요청드린다"</t>
+          <t>메트로 2039 예약 판매가 시작되었으며, 동시에 컬렉터스 에디션 출시 소식도 발표되었습니다.</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>(세종=연합뉴스) 이세원 기자 = 이형일 부총리 겸 재정경제부 장관은 반도체에 이어 한국 경제를 견인하도록 서비스산업을 집중적으로 육성하겠다고 ...</t>
+          <t>메트로 2039 예약 판매가 시작되었으며, 동시에 컬렉터스 에디션 출시 소식도 발표되었습니다.  GameGPU</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>GameGPU</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014029000002</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPTXZTOVBsSVAyaXBaOW1DdmktV285RVpQbDlveGs3NUVnNkFDMlBVWFBSQXg0UWhBNjJuTG1HWjZkRmgteDk4aGtwYVdIUHNObFRyUGRabnUxY0F5RXgxOTMzN1FrNTU4Y3IzS0NjVXJPSFROY1MwUk1HSEtTekFRZk9GTHJOY2dNTUY1bFRaWnlEMm03NUE0SjNCbG1YdS0tajI1QUJFXzkyR2s?oc=5</t>
         </is>
       </c>
     </row>
@@ -6285,32 +6285,32 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>유진투자증권, 현대오토에버 목표가↓…"피지컬 AI 매출 지연"</t>
+          <t>독성 약품 투입량 5분의 1로 낮춰···'청정 원전 해체' 가능성</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 정회인 기자 = 유진투자증권[001200]은 현대오토에버[307950]에 대해 피지컬 인공지능(AI) 관련 매출이 본격화되는 ...</t>
+          <t>독성 약품 투입량 5분의 1로 낮춰···'청정 원전 해체' 가능성  이데일리</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014028200008</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNGxxUG1PSF8taVVIQXp0bGJteS1Ga3NkdkdmOGRqbEpBbGxaSDYzMTJDZUxPRjcyNTRvUzdiSWRBSlJaOFZPYTVkS3pZMEVrQTN5ZVlRYjF1NDdxTElsU1c0SG0xRnlJTU01SEhtRS1NYWZva0dWYVZWVlhWZ2c0bw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6322,32 +6322,32 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>금감원 "韓, 바젤위원회 LEV 규제 평가서 최고등급 획득"</t>
+          <t>“죽으면 전 재산 증발”…요즘 세상보다 더 살벌한 생존 게임 ‘빌로우 더 스톤’ 11/17 정식 출시</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 강류나 기자 = 금융감독원은 한국이 바젤은행감독위원회(BCBS)의 단순기본자본비율(LEV) 규제이행평가(RCAP)에서 최고 등...</t>
+          <t>“죽으면 전 재산 증발”…요즘 세상보다 더 살벌한 생존 게임 ‘빌로우 더 스톤’ 11/17 정식 출시  헝그리앱</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>헝그리앱</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014028100002</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9xUFY5bFV3Q1hidUJJVy1TajdHbnc5VjVqQzYwaEVUMVBIVUFvN1dvcjhFWkdUZkFvMnY0cFF2djRPcTNCS3BoOEdPWGF0Q0F1LXpnYzZWUXF6cW85RHo5UWxFU2stZklYNkc2WFRPSTJyWGJV?oc=5</t>
         </is>
       </c>
     </row>
@@ -6359,32 +6359,32 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>하나증권 "신한 '롯데손보 인수' 이익불확실…보수적 접근해야"</t>
+          <t>파페 산의 한국 식료점, 파리에서 비밀리에 열리는 콜 오브 듀티 팝업을 선보인다</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김유아 기자 = 하나증권은 신한지주[055550]가 롯데손해보험[000400]을 인수하기로 한 결정에 대해 향후 자본 추가 투...</t>
+          <t>파페 산의 한국 식료점, 파리에서 비밀리에 열리는 콜 오브 듀티 팝업을 선보인다  Sortir à Paris콜오브듀티: 모던 워페어4, 캠페인에 이어 'DMZ'도 미리 한다  인벤콜 오브 듀티: 모던 워페어 4의 DMZ 모드에 대해 알아야 할 모든 것  PlayStationDMZ 모드에...</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>Sortir à Paris</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014024600008</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOS3dMSHNXSGFZaV9uV3d0ZTFLaldzWG9zcW1XRnBwczRpaUladnZWcjNqZU5DeWJwV2lDamtGY1FVek1SQkdnNW03ZVV5ckpOMzZMWFFNRjhtekVKMHRzY3RKNVVZQ1dEZE80cU1SZnUxWFhCUDJQY0FBcEVvY0MxSEM3c01uX25MT1RWR0FiaXNoc0ZPVkVtSHFxWF9Mc2FHU2VrV2RDeWpZeFVOc1NOTmdEeTdMZEItWjFSNXJCNWZuOFdsT3IwQVBIcXFZTkVyWXNCcTE4ZzRPejkzQU02cldhalZnREprSkR4QzlFZE5vRHNKN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -6396,32 +6396,32 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>SK증권, 한화오션 목표가↓…"상선 부문 피크아웃 우려"</t>
+          <t>남극 얼음에 탐지기 심어 우주 중성미자 잡았다…할젠 교수 노벨 물리학상 수상</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 곽윤아 기자 = SK증권[001510]은 14일 한화오션[042660]의 목표주가를 13만4천원에서 11만원으로 하향 조정했다...</t>
+          <t>남극 얼음에 탐지기 심어 우주 중성미자 잡았다…할젠 교수 노벨 물리학상 수상  교수신문남극 빙하를 거대 망원경으로...'유령 입자'로 노벨상  YTN 사이언스[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상  한국아이닷컴벨기에 13년 만에 또 노벨 물리학상…과학 강소국 저력 과...</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>교수신문</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014025700008</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE92WF9yMDViT0RjQjNiWHA0c19DVnBPSHRnRGdWbXhJRElzMEZpM05Fdmd2dlJreURYS2V4VGtwMVBhSGozdDZFNkRPMVViMkd5dmxGbXRUNmp5cEg0ZkhkVDlPN3ptclk?oc=5</t>
         </is>
       </c>
     </row>
@@ -6433,32 +6433,32 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>롯데손보 인수 신한금융…증권가 “최선인지 의문” [오늘 나온 보고서]</t>
+          <t>[리뷰] 채찍으로 날아다니는 화려한 악마성, '캐슬바니아: 벨몬트의 저주'</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>NH證·iM證 보고서  주주환원 악영향 제한적이나 보험사 빠른 회수 가능성 낮아 추가 증자 가능성도 부담으로증권가가 신한금융지주의 롯데손해보험 인수를 두고 기대와 우려 섞인 시선을..</t>
+          <t>[리뷰] 채찍으로 날아다니는 화려한 악마성, '캐슬바니아: 벨몬트의 저주'  디스이즈게임캐슬바니아신작 '벨몬트의 저주' 10월 15일 출시, 무료 데모 이미 공개  디지털포커스캐슬바니아: 벨몬트의 저주 - 리뷰  IGN Korea18년 만에 정사로 복귀, 캐슬바니아: 벨몬트의 저주  게...</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>디스이즈게임</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/stock/12175145</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45bEhmaWlTVDMxUW1hMjV6RzltOFRHeV9VZTdoc0p6am5JcUJiY1NBaGVmeFYyZEk3WHUydWJRcGlUS0ZpWWk0YlBwclJrcVEzZWJXMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6480,22 +6480,22 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>“코스피 급락했는데 괜찮나요?”…국민참여성장펀드, 손실 방어 어디까지</t>
+          <t>Mafia Definitive Edition이 10월 22일까지 PlayStation Store에서 85% 할인된 가격으로 판매됩니다.</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>2차 국민참여성장펀드가 오는 15일 판매를 마감하는 가운데 최근 코스피 하락세가 두드러지면서 손실을 우려해 가입을 망설인다는 목소리가 일부에서 나온다. 국민참여성장펀드는 지수를 그..</t>
+          <t>Mafia Definitive Edition이 10월 22일까지 PlayStation Store에서 85% 할인된 가격으로 판매됩니다.  GameGPUMafia III는 현재 고화질 HDR을 지원하며, 향후 DLSS 및 FSR도 지원할 예정입니다.  GameGPU마피아 3가 버그 수정 ...</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>GameGPU</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175134</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZUVrXzhrQmRqZE1Ia0RzM2lJaG5MYmdSdVZpQXNkMkNnbE15Vmt5eGw3REFBYlExOGt2em5nMGVUN2Y4dXBwUllnUk9Oa280SGlEYzBSUjRSMjhKMkNHUUFHZERDZDN5My1rbGtNTGotMm90M0tLanhzazYwLW1CaXBQM3JBR0FkQW9DWENNYXdkaWExYzgybTVGdk9HVFZRVTV6Z0NzdkdIM21GdWhVRzN3WQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6507,32 +6507,32 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>“지갑사정 나만 힘든가요?”…IMF, 한국 경제성장률 3.3%로 확 올렸다</t>
+          <t>새로운 보도에 따르면 소니는 플레이스테이션 6를 세 가지 구성으로 출시할 계획입니다.</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>7월 2.6%서 0.7%P 높여 반도체 수출 호조로 성장세 “중동전쟁發 리스크도 상쇄” 美성장률 4년만에 넘어설듯 고물가 대응책 마련은 숙제국제통화기금(IMF)이 올해 우리나라 성..</t>
+          <t>새로운 보도에 따르면 소니는 플레이스테이션 6를 세 가지 구성으로 출시할 계획입니다.  GameGPU플스5 소니의 잇단 '반 게이머' 정책에 소비자 불만 급증  글로벌EPS5 탈옥 스토어까지...소니 향한 게이머들의 '반란' 왜?  게임플“어차피 사라질 운명” 사이버커넥트2 대표 디스크...</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>GameGPU</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175070</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOdWJQZGg0bDQ2RTNsbjlDM0pIZnlFYmZnYnJza21KckdWWHVkZXYzRmhaaFFteHYzWEQwOG9GZ0wyV3QtbHE1ZktCQ29jczF6c1ZPWkJydTBjRE4zLWxRdGRlWi1OUjViajBsb1gzLWhPUVV6ZmR0d2Y2dXlNRnhvQzVjSjdDNmwtTG1UU0NDcmp6LVBPMzV4djBEVFRsSmdCaTRtWGwxbV9lVDRaYVpmMnU3MVU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>공동명의가 불리할 수도 있다? … 세금폭탄 피하는 1주택자 ‘꿀팁’</t>
+          <t>[속초소식] 착한가격업소 2곳 신규 선정…16일까지 신청</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>잘못 알려진 부동산 세금상식 Q&amp;A부동산 세금에서 경계해야 할 것은 복잡한 규정만이 아닙니다. 일부 요건을 생략한 채 널리 알려진 설명도 잘못된 의사결정의 원인이 될 수 있습니다...</t>
+          <t>(속초=연합뉴스) ▲ 착한가격업소 2곳 신규 선정…16일까지 신청 = 강원 속초시는 오는 16일까지 '2026년 2차 착한가격업소' 신규 지정 ...</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174610</t>
+          <t>https://www.yna.co.kr/view/AKR20261014054400062</t>
         </is>
       </c>
     </row>
@@ -6581,22 +6581,22 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>“회의하시죠, KTX 시간 좀 볼게요”…금융사는 서울, 금융위는 세종</t>
+          <t>소노인터내셔널, 비발디파크 스키장 '26·27 시즌패스' 판매</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>중앙행정기관 44곳 이전 금융위 등 27곳 내년 이전 외교·통일부 등 17개 기관은 2031년까지 청사 지어 이동 공무원 주거·통근 부담 커져 민간 이직 등 인력 유출 우려 정부,..</t>
+          <t>(서울=연합뉴스) 구정모 기자 = 소노인터내셔널은 2026∼2027년 겨울 시즌을 맞아 비발디파크 스키장 시즌패스를 판매한다고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174867</t>
+          <t>https://www.yna.co.kr/view/AKR20261014049100030</t>
         </is>
       </c>
     </row>
@@ -6618,22 +6618,22 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>삼전닉스 자사주 매입 끝나자 주가 와르르 … 코스피 사줄 사람이 없다 [머니닥터 시장진단]</t>
+          <t>파라다이스, 인천서 '넥스트 가스트로노미' 포럼…ESG 실천 모색</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>코스피 수급 여건 심층분석코스피가 12일 6500선이 무너진데 이어 13일에는 장중에 6000선까지 무너졌다. 반도체 기업들의 실적 개선에도 국내 증시가 오히려 뒷걸음질 치면서 시..</t>
+          <t>(서울=연합뉴스) 이상서 기자 = 파라다이스[034230]그룹은 지난 12일 인천 파라다이스시티에서 글로벌 미식 가이드인 '라 리스트 2027 ...</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/stock/12174815</t>
+          <t>https://www.yna.co.kr/view/AKR20261014048500030</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>"시민 지켜라"… 로봇개, 첫 도심순찰 나선다</t>
+          <t>신한은행, 모바일 신분증 발급 서비스 개시</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>앞으로 네 발로 걷는 로봇이 공원과 산책로를 순찰하고, 편의점에서는 성인 인증을 거쳐 무인 자동판매기로 주류를 구매할 수 있게 된다. 반도체와 자동차, 조선 등 제조 현장에는 사람..</t>
+          <t>(서울=연합뉴스) 한지훈 기자 = 신한은행은 14일 신한 슈퍼SOL에서 모바일 신분증을 발급하는 서비스를 시작했다.</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174772</t>
+          <t>https://www.yna.co.kr/view/AKR20261014052900002</t>
         </is>
       </c>
     </row>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>석달만에 … IMF, 올 韓성장률 3.3%로 상향</t>
+          <t>[인사] 한국방송광고진흥공사</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>국제통화기금(IMF)이 올해 우리나라 성장률 전망치를 2.6%에서 3.3%로 석 달 만에 0.7%포인트 높였다. 중동전쟁 충격에도 강력한 반도체 수출에 성장률이 높아질 것으로 본 ..</t>
+          <t>▲ 상임감사 이수호 (서울=연합뉴스)</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174769</t>
+          <t>https://www.yna.co.kr/view/AKR20261014051300017</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -6739,13 +6739,12 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>[단독] 정부, 수소차 늘린다더니 보조금은 9년만에 줄인다</t>
+          <t>위메이드, 서틱과 위믹스 3.0 보안 강화…최대 1만 달러 포상</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>내년부터 수소승용차 한 대당 국비 보조금이 올해보다 11.1% 줄어든 2000만원으로 인하된다. 정부가 수소승용차 국비 보조금을 인하하는 것은 2018년 이후 9년 만이다.
-13일..</t>
+          <t>(서울=연합뉴스) 김주환 기자 = 위메이드[112040]의 위믹스 재단은 미국 소재 블록체인 보안 기업 서틱(CertiK)과 함께 블록체인 메인...</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -6755,7 +6754,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174770</t>
+          <t>https://www.yna.co.kr/view/AKR20261014040300017</t>
         </is>
       </c>
     </row>
@@ -6767,32 +6766,32 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>韓기업 해외원화 조달 숨통 … 신고기준 10억→500억 완화</t>
+          <t>이수만 “새 문 열겠다” 3년 만에 K팝 복귀…보이·걸그룹 동시 공개</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>재정경제부가 국내 기업이 해외 금융기관 등에서 원화를 빌릴 때 적용되는 사전신고 기준을 연간 10억원 초과에서 500억원 초과로 높이는 내용을 담은 외국환거래규정 개정안을 13일 ..</t>
+          <t>이수만 “새 문 열겠다” 3년 만에 K팝 복귀…보이·걸그룹 동시 공개  국민일보이수만, 유영진과 돌아왔다…24명 아이돌로 K팝 흔들까  한겨레A20 LITE의 데뷔 쇼  뉴시스[ET포토] A2O 라이트 라다, '호수에서 백조가 발레하듯'  전자신문'이수만 표' 새 바람…A2O 소울·A2...</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>국민일보</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174771</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOamxndXRINVdISDF1N2VpMUdjM0R4dmVYR09fazVNYzExZTh1QXh6bk1DWEtUV21VcFhNTktOei0xYlp6aTlSYkZ5VjJ1WjE3ZUdzRGdmZTRjVEQxbmpuT0dhVkp0X3BzNDBhaHlfNHRfUDhVSHZLT0VFXy01REtPeEh0RHg4T3VPX3pyRWRna2Vzdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6804,33 +6803,32 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>시중은행 '골목 사장님 비대면 대출' 경쟁</t>
+          <t>'나를 충전해줘', 공개 3일 만에 글로벌 톱10 비영어 쇼 3위</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>시중은행들이 개인사업자 부동산담보대출을 비대면으로 내놓고 있다. 영업점을 찾기 어려운 자영업자의 대출 문턱은 낮추고, 담보를 잡아 건전성 부담은 줄이겠다는 계산이다.
-13일 금융권..</t>
+          <t>'나를 충전해줘', 공개 3일 만에 글로벌 톱10 비영어 쇼 3위  뉴스핌차우민, '최애의 사원' 이어 '나를 충전해줘'까지…로맨스 연타 흥행 예고  YTN김영광·채수빈 ‘나를 충전해줘’, 공개 3일 만에 넷플릭스 글로벌 비영어권 3위  스포츠동아‘국민엄마’ 김미경, 백발됐다…이번엔 재...</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>뉴스핌</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174757</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1PUG5VSTdieXRQZ0lrVmJGVWZieHdqRjhqYkZieWZ1cV9SN3Y2ZlBFdlBodzNORkNtbjh2Q1ZReklxQy1YR2l0aS1oYkROSDA1WVNkNjV3VXZTbFdm?oc=5</t>
         </is>
       </c>
     </row>
@@ -6842,32 +6840,32 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>[포토] 수출입銀, 고립청년 자립지원</t>
+          <t>[스브스夜] '틈만나면' 남지현, "전파견문록 출신, 출연 이후 드라마 캐스팅"…유재석 '사과 방송' 예고</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>[포토] 수출입銀, 고립청년 자립지원</t>
+          <t>[스브스夜] '틈만나면' 남지현, "전파견문록 출신, 출연 이후 드라마 캐스팅"…유재석 '사과 방송' 예고  news.sbs.co.krGoogle 뉴스에서 헤드라인 및 의견 더보기</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>news.sbs.co.kr</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174758</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPZ202a3RsUTFDVEJxU1A3eGpIT3lDZlhJbmdhank3dk8tRlVzVnVIcHZlUG9hWjRiSGxIdEpJVVZ5bjFHVUxvV1FkSlp0S2xCVWNQYUlhS2JYclZFampIcHRlVnlONGY0Wl9PSjBVR0RmNUozOFhQRGRHOUFIOE9XN1NDeTF6Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6879,32 +6877,32 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>'7000억 승부수' 신한금융…롯데손보 품고 '리딩금융' 탈환나서</t>
+          <t>시크릿, 17주년 자축…송지은, 박위 논란 불똥 속 '침묵' - 머니투데이</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>신한금융그룹이 롯데손해보험을 인수하며 '리딩금융' 탈환에 나섰다. 그간 취약했던 비은행 포트폴리오인 손해보험 사업을 강화해 KB금융에 3년 연속 내줬던 금융지주 1위 자리를 되찾겠..</t>
+          <t>시크릿, 17주년 자축…송지은, 박위 논란 불똥 속 '침묵' - 머니투데이  머니투데이'♥박위' 발목잡힌 송지은-잘나가는 한선화-3크릿, 엇갈린 시크릿 17주년[SC이슈]  조선일보전효성, 데뷔 17주년 생일 카페에서 전한 팬 사랑 다짐  톱스타뉴스시크릿, 송지은 없이 17주년 맞았다…...</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174755</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBuTXhMcGtwMGVIR3ZvQkVMMkh5Wjc1TDFNNUloenNzY1kxZVVNYnJrNXMxVjVvSjZrLUtMT2IzVVNIVndpRF9IdnItcEhhQjQ1RFVZN0xTWEZJa1owNWgwcUZ1ZGxjQlpGNG1hRTB6NHpkNVHSAXhBVV95cUxPNkptTVNtRWZxWDVYLU1NNXdzVTYybVVRWC1zYzhuYlpzQVh6dEluMEFRWVNSNUQ1b2VRZWlFbkt2ZDk1U0ZOa2RISUxMaVJxanRZT2pvRlZJbEVCLW83NE9DQ0NVenhWWUtWNVczeXJ3Mk9ZS01sUXY?oc=5</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6914,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -6926,23 +6924,22 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>카카오뱅크 'AI적금' 출시…저축목표 따라 맞춤형 조언</t>
+          <t>국힘 달성 군의회와 당원, \'암살자(들)\'영화 상영중지 촉구</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>카카오뱅크가 금융권 최초로 인공지능(AI) 코칭 기능을 적용한 저축 상품을 출시했다.
-13일 카카오뱅크는 'AI 목표적금'을 출시했다고 밝혔다. '부모님께 드리는 안마의자' '내년..</t>
+          <t>국힘 달성 군의회와 당원, \'암살자(들)\'영화 상영중지 촉구  세명일보‘암살자(들)’ 실제 기자 “우리 패던 중정…영화가 잘 그려”  한겨레‘암살자(들)’ 논란, 하다하다 ‘100분 토론’ 간다  스포츠경향‘기립박수받은 배우가 위협받고 있다’ 외신도 주목  JTBC[시론] 권력자의 ...</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>세명일보</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12174756</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBnSG5LUDhaVXZFcDR6ZE9fbUdhMDN6MnpmN0p3eUF0YUZLQUR4YkZIWldSMTloUm9ncWdWd2NEWVNfNkxBU1JwSFNuNG1Lbk1WMWk4YWgzbmszOEVON2hBNnZMaU1SQ3VsSlprTldUcWo?oc=5</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6951,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -6964,22 +6961,22 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>교황, 폐 결절 제거술 위해 로마 병원에 입원</t>
+          <t>김새론에 “언제 안고 잘 수 있어” 다른 연예인이었다…김수현 미성년 성착취 의혹 해소</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>교황, 폐 결절 제거술 위해 로마 병원에 입원  연합뉴스교황 레오 14세, 폐 절제 수술 뒤 ‘암 진단’ 받아  한겨레바티칸 "교황 레오 14세 폐암 진단…수술 성공적" - 머니투데이  머니투데이교황청 "레오 14세, 폐 결절 수술 성공적 완료"…남미순방 갈듯  마켓인[속보]교황 레오1...</t>
+          <t>김새론에 “언제 안고 잘 수 있어” 다른 연예인이었다…김수현 미성년 성착취 의혹 해소  헤럴드경제김수현 아니었다…"너 안고 잠들 수 있어" 발신자는 연예인 A씨  뉴시스‘누명 벗은’ 김수현 측, 허위사실 유포에 강경 대응…“합의 없이 형사 고소·민사소송”  스포츠동아“언제 안고 잘 수 ...</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9Hb1JpRG41NHJVQXNSYW9sbWpMOTVTajJUX1V2a05YNUE1X01ZTUh2WUpWcXk3R3lJWDhwZG5qQTQ5NXNCa1V1WnVTTTZSSHNOaUpEZVhVUHlHS03SAWBBVV95cUxNbk50bmV5RXN0NkZYN2tCa1d6dXFlVzJMYXJCOUl1Ylo2WTZjLXVSUkpkOTYyV1ByYkJiNmlZc0E4RjFjYzVsTFE4TTJ2Q3FSQ2JaclJxdVNwNHcta0d4M0M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE4wVEI2bnllQmlsZ2JUcmxBQ05mdmpGQnZLVW9ueXpPVTV2Q0VDaE5IX2lKV2tBY3R3NWQ0ZEU1TWMzVTU2RXA2aEt2NHVnSUtvRnhQcktWaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6991,32 +6988,32 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>프랑스 "냉장고 해킹 피해 슈퍼 700곳…식량안보 건드려"</t>
+          <t>베이비몬스터, 23일 신곡 ‘디저브’로 컴백…“강렬한 에너지”</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>프랑스 "냉장고 해킹 피해 슈퍼 700곳…식량안보 건드려"  연합뉴스TV佛 마트 냉장고들 해킹당했다... 온도 50도 폭주 ‘먹거리 테러’  조선일보냉장고 속 음식 다 버렸다…프랑스 슈퍼마켓 700곳 날벼락  마켓인50도로 달궈진 냉동고…프랑스 마트 뚫린 날 "AI, 곧 가전제품 점거"...</t>
+          <t>베이비몬스터, 23일 신곡 ‘디저브’로 컴백…“강렬한 에너지”  KBS 뉴스베이비몬스터, 23일 신곡 '디저브'로 컴백…"강렬한 에너지"  연합뉴스YG 5인조 보이그룹·4인조 걸그룹 데뷔 구체화..양현석 직접 밝혔다 - 조선비즈  Chosunbiz‘가창력 과시’ 베이비몬스터, ‘힙합 노...</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1VemdGcUxiaE9yMGZ0STFwTkE5QVJFNzBsRjBONkJiWUdBSzBVX3BPQ2xmLURGUVp5YjM4emFPQzhVcVlwMV82eW5QTk9ONmc5dGQxd19qY2VocWlobzVUN2FoTzFJQnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE00bjZ2YkUwcmZ3MW1GZjF5dnViZVpNbzdaYmpzSllMYnFpakNidzhMN3hyV0FMVERfcUR4em5pTHcwdkp2YXRYN09PaVBqRm1MbkxIN3ZtSmxzMjZiUEVFWWVqT0t3UQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7028,32 +7025,32 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>트럼프 “미국, 우크라이나와 정보 공유 중단 안 했다”</t>
+          <t>맨발로 비스듬히 느릿느릿… 차이밍량·이강생 “기존 영화 지겨워져 걸었다”</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>트럼프 “미국, 우크라이나와 정보 공유 중단 안 했다”  VOA 한국어 홈페이지‘경유 딜’ 우크라 반발에… “美, 종전 협상단 방러 보류”  동아일보젤렌스키 "트럼프 '휴전' 언급에 공격 자제했지만 러는 계속"  연합뉴스"이런 기름값 처음" 비상 걸린 미국…트럼프 ‘푸틴과 딜’ 발칵  ...</t>
+          <t>맨발로 비스듬히 느릿느릿… 차이밍량·이강생 “기존 영화 지겨워져 걸었다”  문화일보</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>VOA 한국어 홈페이지</t>
+          <t>문화일보</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFB6WDNka1BrSklyOWxFNlRBdnR0WTB1UGtCd0xSYnlJUXlZQXBrcDR0MTFZZGh6YkxaZDBfVnlIQ2JrSXZJd3BTNWhpa0YxS0NkeDNFZTFILUhicjN2LVp6dVgwR3BOdW5tSVpYejd4d3pHME3SAXZBVV95cUxPaFY5MjIydVg3N3RsVV8ya1dUeUtiNkdRSjdWeFBIUXpvTEFWYkpOeUxFVUZ6S2Nqd2tFQXFHelNKbkk5LVBzSGUwTm1IV2hPelBLVTljY0F5WV9yQTY1Qzk5M0pHbG9XMkYtMXhMQVNMNnNPQmN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE53dlVHR0diVUc0YTRVMHhBWXFDUXhlUnpIOXVBUVIxZGdtZHNNbG1FR3BST0FwdVAzUVBQY0FqUXUtQ2ZUT28yMGJZbmRHMlJJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7065,32 +7062,32 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>러시아, ICBM급 초장거리 6500km 순항 미사일 32기 도입…원거리 타격망 확충</t>
+          <t>[가요소식] '정엽 밴드' 코스믹 칩스, 2집 '테이스트'</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>러시아, ICBM급 초장거리 6500km 순항 미사일 32기 도입…원거리 타격망 확충  글로벌이코노믹</t>
+          <t>(서울=연합뉴스) 이태수 기자 = ▲ 코스믹 칩스 정규 2집 = 가수 정엽이 결성한 밴드 코스믹 칩스가 14일 오후 6시 두 번째 정규앨범 '테...</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>글로벌이코노믹</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNMHN2OGtVRDdiM3VIVUNYQUNSbjd5bVVyd2h0c0RTYVJFTU1GQXBqeTNZLXlndTEzY1FmY3pjSHpfbGpxeEhfS1lyOXJEYW1YQUxTNFFpWWtNemZvMWwydE1FaUxsclZXUkdLVGx3a0UxZk52YjVFcWJjeUx6QmFaT0FhQUZJMExQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014054000005</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7099,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -7112,22 +7109,22 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>이란 지원 받은 후티, 사우디 공항 연일 공습…미사일·드론 섞어쏴</t>
+          <t>KBS '드라마스페셜 2026'…연말까지 단막극 8편 방송</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>이란 지원 받은 후티, 사우디 공항 연일 공습…미사일·드론 섞어쏴  한겨레트럼프 "이란, 후티에 사우디 공격 지시…의도적으로 유가 올리려 해"  연합인포맥스사우디 아람코 본사 미사일 공격받아 화재…후티 공격 추정  연합뉴스사우디, 후티 석유 시설 보복 타격...후티, 재보복 '난타전' ...</t>
+          <t>(서울=연합뉴스) 장진리 기자 = KBS는 2TV '드라마스페셜 2026'을 편성해 연말까지 단막극 8편을 방송한다고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBjc0haenYteU8yYzY1bndkWlh4blFwVkRybmUtWThwTGZtWldFQkRuZWhYVWMwX3FCWHJWWVZ1Q1lXTDkzNjBtZFNzN0VEck9rNGJwYUpnUF9BeGxZNVpjeE54VVVubUU5RVI0XzY4YWJLNE0?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014048100005</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7136,32 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>'트럼프 장남 前연인' 그리스 美대사 잘린다… 백악관 "사퇴 요구"</t>
+          <t>베이비몬스터, 23일 신곡 '디저브'로 컴백…"강렬한 에너지"</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>'트럼프 장남 前연인' 그리스 美대사 잘린다… 백악관 "사퇴 요구"  한국일보‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임  경향신문"가족은 아니었다"…트럼프, '아들 전 약혼녀' 그리스 대사 해임  마켓인백악관, '각종 비위 의혹' 그리스 대사에 "사퇴 요구했다"  연...</t>
+          <t>(서울=연합뉴스) 이태수 기자 = 걸그룹 베이비몬스터가 오는 23일 오후 1시 새 디지털 싱글 '디저브'(DESERVE)를 발매하고 가을 K팝 ...</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>한국일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1xaVhYRWVHcGIxR0RMUkVBV0dLZkZXWUk0Nl9GbUNFZFlhOVJGdkhMSjdFTEZHRVpoZzVnbXFQTHN1RG5Wd0VNMENxMTA4MmVJRklBbnZXcUtDTmpObU1TNzZYQXlZUlZYaWw4YmhB0gFzQVVfeXFMUG9JWWtSRURaRUJFZW1kMVZrOHFCSXZlVERlUkxoOS1maU8tNlFwT3Jmc1Jsc1hxYkR4OGxORkxIUmpyOTZWMnZlUUtob0FPVnRoYzFybU96Z3hjQVNfaldBRUZQZlpPVHJJQ1RYWUhXa1NNdw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014047000005</t>
         </is>
       </c>
     </row>
@@ -7176,2622 +7173,32 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>北中 국기 내걸린 신압록강대교…12년 만에 개통 임박 관측 - 조선비즈</t>
+          <t>BTS '아리랑', 스포티파이 50억 스트리밍…올해 발매 최고 기록</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>北中 국기 내걸린 신압록강대교…12년 만에 개통 임박 관측 - 조선비즈  Chosunbiz北中신압록강대교 개통 임박했나…북측 관문 북중 대형국기 포착  연합뉴스12년 멈춘 신압록강대교, 왜 지금?…"북중 경제적 타협 신호"  뉴스1[특파원리포트] 두 개의 다리와 북한의 몸값  세계일보북...</t>
+          <t>(서울=연합뉴스) 이태수 기자 = 그룹 방탄소년단(BTS)의 정규 5집 '아리랑'(ARIRANG)이 세계 최대 음원 플랫폼 스포티파이에서 누적 ...</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeHltSzRtbUs3Z2FuNVRObkZKOGdhbDZneWRxLWFxY3dXSWwxSHdCdDFXd3ExUFVLRm4yVXJqejBRT1FRa0VlcmRzeWdTZjZTS1R0Z3Z3WkRreFJuUmt5QVpJRkwwNkRzMVQ2dTJqQ2sxVWpHT2J0VHhfd19WLW9EUndSdGpuZktmQjZIYl8yR21rMGxCNkxaRFBQMDR6QdIBsgFBVV95cUxNNlYtZUNUQUhiMnd2U3d6eVBjNHhSRXdGWmlwREhQQ0ZSclFMUXRtQXI5OVZrbWtzNG1nOUZKSFBWTkx3MzJjclBxVmpkNW9yX1lTLW9EVGVOQlFPSGQyVW9kTFU5d1FKY0k5bHZRUU03TmFkMnVXWDdzWXRXU1ZsbDIwbmVrY1lfNThrVzZFN2l4aHd2alhBLS1yOGxGTnV3OWFQWjZHQTFsTVR0QlVmU0Fn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>러 데이터센터 드론 피습에 중앙아시아 앱 장애..."우크라 공격"</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>러 데이터센터 드론 피습에 중앙아시아 앱 장애..."우크라 공격"  YTN우크라 드론이 러시아 데이터센터 때리자 중앙아시아 앱 '멈춤'  연합뉴스러 미사일 공격으로 부상한 여성 옮기는 구조대  뉴시스러 데이터센터 피격에 카자흐 주요 플랫폼 마비…디지털 인프라 의존 한계  아시아투데이美 ...</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>YTN</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9PdERfa2JGWlk1clhEZ2xqV0JFeHN3ZXV5bFVFLUxyNndlUU9qblBZa0hQN0dfX0ZnaVowZnFUWUNBRi02OTFLRV84ODFwdVZrZ1NNakF5WExCLThGeHc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>이란군 "호르무즈 동부 선박 주시…금지구역서 유조선 화재"</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>이란군 "호르무즈 동부 선박 주시…금지구역서 유조선 화재"  연합뉴스"호르무즈 선박 피격 2주간 24건…개전 이후 최다"  연합뉴스이란군 “호르무즈 동부 선박 주시…금지 구역서 유조선 화재”  KBS 뉴스호르무즈 유조선 연쇄 공격… '중동 원유' 수출 회복세 또 꺾이나  마켓인호르무즈 ...</t>
-        </is>
-      </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G184" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5yTm14NmI1c1RXcXk2WWhfOUlTRWp3ZDNsZFlLdjhLRkprd09jQXd0dFZuZ1BxdExBZG9IUjByVDZ1VGY3VW9nTUNWVUhnbkxnN1Y3SjVDNnkyZG_SAWBBVV95cUxPTlhjMkFldm5rWXJ5UUc1eFphTTdBekU2MVpmVy1vYmNZOVRmQUluekc4SXUyc25Wd1ppUnRxWE9HYU9lUmRnaFZ5WFkzWEhjRThRRjduSXU4OENnanBENU0?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 “내달 亞 방문중 김정은 만날수도”</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 “내달 亞 방문중 김정은 만날수도”  동아일보트럼프 "다음 달 김정은 위원장과 만날 수도...흥미진진할 것"  YTN 사이언스[열린세상] 북미 정상회담이 불러올 후폭풍  서울신문트럼프, 북한에 또 러브콜…“김정은 만날 수도”  KBS 뉴스트럼프 “내달 김정은 만날 수도”… 북한은...</t>
-        </is>
-      </c>
-      <c r="F185" s="3" t="inlineStr">
-        <is>
-          <t>동아일보</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9QektUZlgyUXJqZ2VnZEt2WnE1WUtqU1JLR3BWREMzWGxXQlBJS29zMjFDTlcyVHRfRzNpcHdzbkdVbVFQcU9LTjc1WlRWb010SWpidGZXVDFwdmlKWC1pQ1BRVEN1SFh5WjM4VEdINjNIczjSAWZBVV95cUxOejRBaUpONWo0MWs1RDk2UVphSjE3RHNOdUVtOHoybTNzWnBSaTUxcnduRUhsdE5VZENQRnZOdXBVdXRVa01YdUVpT2pUTkFEMmJhNDBxUjNmQ2FsblhEc0FtNGFzTVE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>[브라질증시] 이보베스파 1.04% 하락…룰라·플라비우 지지율 격차 주시</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>[브라질증시] 이보베스파 1.04% 하락…룰라·플라비우 지지율 격차 주시  뉴스핌다급한 룰라, '소상공인 부채탕감' 대선 결선용 선심법안  연합뉴스브라질 대법원, 보우소나루에 부친 면회 허용  문화일보트럼프 ‘블루 타이드’ 마지막 퍼즐 완성하나…‘보우소나루 정치 왕조’ 계승자 [더 비저...</t>
-        </is>
-      </c>
-      <c r="F186" s="3" t="inlineStr">
-        <is>
-          <t>뉴스핌</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9RUFJfV095U1NUblZMUnNrUGFGem94aU5Pb2xuT1cyd0lJcGdvWXFjdHo4VzVvelV1Qi1yRTBnRGNreldkNzMyUFQ5Q2VPdFNTaDdLM1dldG1aa0t2?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>러시아 '페스트 의심 사망'‥국내 위험도 낮지만 검역 강화</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>러시아 '페스트 의심 사망'‥국내 위험도 낮지만 검역 강화  MBC 뉴스국내 페스트 종합위험도 '낮음' 유지…러 입국자 감시는 강화  연합뉴스[크랩] “치료 안하면 100% 사망” 미국·WHO도 러시아에 정보 공개 요구  KBS 뉴스[한마당] ‘원인불명 폐렴’ 미스터리  국민일보질병청 ...</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="inlineStr">
-        <is>
-          <t>MBC 뉴스</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1ld25YY1JGSC1SSDMyTVVvSW5RRmNLcHJqVDVZOVdVSFh3bHNQNXF6ZkJZeXcwd2VGUjM3NTdCclNhMHF3MnAxdEp0WW5DcVJjZ21DaDg2WGFPNTNvWWphaTgwdTFVaG16QzdaaVBqNkxaelotODl30gF3QVVfeXFMUFhRZXdDaXltSThQRklGZ0dKdDNrLXFiRzBPcnRhVVhUUEVJNjFkc3pqaWQzTl83VTFUM0FwbUtFVVJqNVFlM3hGeXI3YW5aV3NzREZJbXN4S19YbTNKWm9FZnQwU0FFRmFKaC1HQ25nLTYxWnYwSVE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>WSJ "이란, 美 중간선거 후 전쟁 대비…지상전 시사"</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>WSJ "이란, 美 중간선거 후 전쟁 대비…지상전 시사"  한국경제이란, 인접국 지상군 투입도 시사…美중간선거 이후 공세 대비  연합뉴스美재공습 나설라…이란, 핵시설 방어·전시태세 전환 '집중'  마켓인이란 외무부 "미국 답변 검토 후 중재국에 입장 전달"  MBC 뉴스이란, 美의 이란...</t>
-        </is>
-      </c>
-      <c r="F188" s="3" t="inlineStr">
-        <is>
-          <t>한국경제</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB3eFNlRFh5ZHpLUUZfejczSXM2bmlpLWRHVkJrYi1RSS1KM1pFTTM0ZXAxQlBJVkNuN2Z1cXpNczBVSmdPaTBNb21OcjNTY01rV1g0SUM4eXhtZw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>구글, 최상위 AI모델 '제미나이 4 아르곤' 정식 출시</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>(샌프란시스코=연합뉴스) 권영전 특파원 = 구글이 최상위 인공지능(AI) 모델 '제미나이 4 아르곤'을 일반에 공개했다.</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014033100091</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>세계의 날씨(10월14일)</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>(09:00)</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G190" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014035400009</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>유엔 국감서 '北지뢰' 대응 공방…유엔대사 "안보리 대응 미정"(종합2보)</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>(뉴욕=연합뉴스) 임수정 김연숙 특파원 = 13일(현지시간) 미국 뉴욕 주유엔 한국대표부에서 열린 국회 외교통일위원회 국정감사에서는 북한의 비무...</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014003052072</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>"트럼프, 지난주 네타냐후와 '중간선거 전 이란 공격' 논의"</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 고일환 기자 = 도널드 트럼프 미국 대통령이 중간선거 이전에는 이란 공격이 없을 것이라고 밝히기 앞서 대규모 군사작전 가능성을...</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014036700009</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>日정부, 경제·재정 소개 영문책자 발간…"해외 우려 잠재우기"</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>(도쿄=연합뉴스) 조성미 특파원 = 확장 재정을 통한 경제 성장을 추진하는 다카이치 사나에 일본 총리가 내각의 경제·재정 정책을 중점적으로 소개...</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014032700073</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>사우디 아람코 본사 미사일 공격받아 화재…후티 공격 추정</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 강훈상 기자 = 사우디아라비아 국영 석유사 아람코의 본사 단지 내 건물이 13일(현지시간) 밤 공격을 받아 불이 났다고 사우디...</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014026500009</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>'자금세탁 방치' BofA에 1.6조원 벌금</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이성한 기자 = 미국 재무부가 자금 세탁 방지 및 제재 준수 의무를 심각하고 반복적으로 위반한 책임을 물어 뱅크오브아메리카(B...</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014025100009</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>알바니아 '플라밍고 시위' 넉달째 격화…대학생들도 화염병 가세</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김용래 기자 = 동유럽 발칸반도 알바니아에서 도널드 트럼프 미국 대통령 사위의 리조트 개발에 맞서 불거진 거리 시위가 대학생들...</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014024300009</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>뉴욕 연은 윌리엄스 "내년에 금리 올릴 필요 없어"</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 주종국 기자 = 존 윌리엄스 뉴욕 연방준비은행(연은) 총재는 연방준비제도(Fed·연준)가 올해 한 차례 더 기준금리를 올리는 ...</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014023500009</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>후티 공격에 사우디 진땀…간판급 투자회의 원격참여도 허용</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이신영 기자 = 사우디아라비아가 이달 말 열기로 한 간판급 투자 콘퍼런스 '미래투자이니셔티브'(FII)를 원격으로도 개최하기로...</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014022900009</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>BBC, 13조원 손배소 낸 트럼프 상대로 '강제 증언녹취' 요청</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장재은 기자 = 영국 공영방송 BBC가 자사를 상대로 도널드 트럼프 미국 대통령이 제기한 손해배상 청구소송에서 트럼프 대통령 ...</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014022800009</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>뉴욕 센트럴파크 마차, 150년 역사 뒤로…내후년부터 금지 전망</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>(뉴욕=연합뉴스) 김연숙 특파원 = 미국 뉴욕 센트럴파크의 명물이자 관광 상품이었던 마차 운행이 2028년부터 금지될 전망이다.</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014016100072</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>교황, 오른쪽 폐 일부 절제 수술…폐암 진단 확인</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이지헌 기자 = 레오 14세 교황이 예정대로 흉부 수술을 받은 뒤 폐암 진단을 받았다고 로이터 통신이 교황청 발표를 인용해 1...</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014017800009</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>엘니뇨에 남미 강 수위 상승…이타이푸·야시레타 댐 수문 개방</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>(부에노스아이레스=연합뉴스) 김선정 통신원 = 엘니뇨와 관련한 집중호우로 남미 파라나강 유역의 물이 불어나면서 브라질·파라과이·아르헨티나 접경 ...</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G202" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014015700009</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>美 금리 급등 충격 월가로 번지나…대형은행 실적 '희비 교차'</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>(뉴욕=연합뉴스) 임수정 특파원 = 미국의 금리 급등으로 채권시장이 요동치는 상황에서 3분기 실적을 발표한 대형은행들의 희비가 엇갈렸다.</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014009700072</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>NASA 화성탐사 차량 45.2km 주행...지구밖 최장 기록</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>NASA 화성탐사 차량 45.2km 주행...지구밖 최장 기록  YTN화성서 45.2㎞ 달린 퍼서비어런스… 지구 밖 로버 최장 주행 - 조선비즈  Chosunbiz“지구밖 가장 많이 달려“…NASA 화성 탐사선 ’신기록’  연합뉴스TVNASA 화성탐사 로버 퍼서비어런스, 지구밖 최장 주...</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>YTN</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE91bGwzNEthTTN2bWNHYzFkTTF4RjAwNDdBN1gyNVo2cjhXdUEyYnJXMm94NUZMZERkY3A1QWtVZ2ZPUzYyNjUwWDBuLVdUekRfb19zUkUwUWhmZGpUc3c?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>발러 모티스 - 리뷰</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>발러 모티스 - 리뷰  IGN Korea발러 모티스  IGN Korea</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>IGN Korea</t>
-        </is>
-      </c>
-      <c r="G205" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1hTmVoMVhXX0JDTXBWdUFOekRGaFUzWVlpU0JfN28zNFlmNlNzT1JUNE1SUGtkVjlFNFhBdGlCTEVFVWtfam9iMkVtOWtnN1ZqNXVGNkdxRFdUc0pvUDRZUTZyXzloSEdhVlE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>포스텍·DGIST 연구팀, 가시광선으로 상온의 물에서 고결정성 MOF 합성</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>포스텍·DGIST 연구팀, 가시광선으로 상온의 물에서 고결정성 MOF 합성  전자신문</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>전자신문</t>
-        </is>
-      </c>
-      <c r="G206" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5ScWtpZWR5bm9wdzVFSHNuWXlZM0xKbUN0WXpvZlFSb0ptUEVLUHNxeTZQaEdkZG9qNVdmMFAwN2lkdUtaczZ5a2lOZw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>애플, 4년만 A19 탑재한 신형 애플TV 4K 공개···가격 44만 원</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>애플, 4년만 A19 탑재한 신형 애플TV 4K 공개···가격 44만 원  글로벌EApple, 새로운 Apple TV 4K 공개  Apple애플, AI 기반 Siri 탑재한 신형 애플 TV 4K 발표…사전 주문 시작  Investing.com 한국어애플, 2017년 출시 애플TV 4K ...</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>글로벌E</t>
-        </is>
-      </c>
-      <c r="G207" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1rSnVVaE04eVBDM1V6Tzl3czRMUEFFZ3BZRXlwUk5td1BrWjJ1WDNUUkhwbWotblY0cU53azJaTHpPblIzM1FTcWt5NHdieTNmYkZibmFGWVhZVDdYUS1mZE1jWGlVVGNKZ1HSAW9BVV95cUxQaUxEYmQ2SWJUR1YtTEhlVWl3bGxuRzR6X21idmoyT0pKQklRT0luV0c1dXN2enFUUmVjLS1udjlRN2tWeHluX3d6REFQRllmTW45d3pfVkhGZUhqSFotSmdlSEtnMVJndmhUWU81VVU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>원플러스 16, 9,000mAh 배터리·2억 화소 카메라 얹고 시작가 1,700위안 올렸다</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>원플러스 16, 9,000mAh 배터리·2억 화소 카메라 얹고 시작가 1,700위안 올렸다  위키트리</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>위키트리</t>
-        </is>
-      </c>
-      <c r="G208" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBYcm45OGNsR0RfV3owZE5sTTRiVVpfSU12UkhqbGM5d2gwV1QzWFZxei1YUV9iMnlnbTdaWF82cEQzREtVRV9pWTR6QVJIbGg4UF9uaUx3?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>“노벨상이 다음 연구제안서 채택에 도움 됐으면”</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>“노벨상이 다음 연구제안서 채택에 도움 됐으면”  문화일보남극 빙하를 거대 망원경으로...'유령 입자'로 노벨상  YTN 사이언스[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상  한국아이닷컴한국 중성미자 연구, 20년의 성과와 남은 숙제  이로운넷벨기에 13년 만에 또 노벨 ...</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr">
-        <is>
-          <t>문화일보</t>
-        </is>
-      </c>
-      <c r="G209" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1TY2ZCNzFXa1FuWExSX1B0R0lNZ1NrWmtLdFdEWkJDYVZpVmZ5SlZCdXdBZ0NEZGg1NGJqMFgxMlg4LWxrd3VCYlc4NUVTSkNN?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>[영상] 스튜피드 네버 다이즈, ‘DEEP BITE’ 아트 편 공개</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>[영상] 스튜피드 네버 다이즈, ‘DEEP BITE’ 아트 편 공개  게임뷰'스튜피드 네버 다이즈', 독특한 비주얼 소개하는 개발자 해설 영상 공개  인벤[게임뉴스] 펄어비스 및 그리프라인 소식 외  게임뷰음악부터 만들고 게임을 설계했다... 고바야시 히로유키가 밝힌 '스투피드 네버 다...</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>게임뷰</t>
-        </is>
-      </c>
-      <c r="G210" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFA2amxrUE9tWEROM0xheVpOMktXeWtzc0RQc2F3OTZMbWp1VkJYMmJTWV9ZaUFjUUxlN3lOV09Sa2sxRjRTQTFYZnNJdFBqREZMdF8zdjhEaUJDTk83N3FFNlNfWHc2NXVZcUE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>ARCTIC BioniX P12 A-RGB 쿨링팬 서린 [써보니]</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>ARCTIC BioniX P12 A-RGB 쿨링팬 서린 [써보니]  위클리포스트</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="inlineStr">
-        <is>
-          <t>위클리포스트</t>
-        </is>
-      </c>
-      <c r="G211" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBDMXVkU2R0QVpLM1dpMGY1azZVVmV1bUxvQkd5QXNucExsRmVGbm1oaWZzZGNVdHdCSzVpSHFfUnlfaGJoZkIwbm9JV0NZQlBwWXRkTzRCcUg3WDFHeGpZRW9UOUV4VjVBRjIw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>페이커·제우스 사인 품었다… GALAX 지포스 RTX 50 시리즈 ‘아시안게임 국대 패키지’</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>페이커·제우스 사인 품었다… GALAX 지포스 RTX 50 시리즈 ‘아시안게임 국대 패키지’  디지털포스트클릭나라, GALAX 지포스 RTX 50 시리즈 ‘아시안게임 국대 패키지’ 적용  위클리포스트</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>디지털포스트</t>
-        </is>
-      </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBCdTdmYnhiZVhiZVpBMm82b0FjQ3h0TFdVQnVKUUVyMzR2UVBVMkpHWFpKcFFuQVJoT1hfczNjU2hObmw0dHZ3T0p3MWFxTXEySlRpMnhYZ1pYVzA5VGxYbmYtMHNaSUpIYXJV?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>헬다이버스 2에 프리미엄 저격총 배틀 패스인 '권한의 범위(Scope of Authority)'가 발표되었습니다.</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>헬다이버스 2에 프리미엄 저격총 배틀 패스인 '권한의 범위(Scope of Authority)'가 발표되었습니다.  GameGPU</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>GameGPU</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNME92UVZIa0ExWVYzMlJJamhNTXhqeGctNU9SUXN6VGJIelZoMFAwbGhXNjJ4NGxVQkdlazF0dkpHcFM5Vjh3M3hNa2c2dk93X0JqU1l5eWtFNEZMUHpNeVpmN3hIUmo0SHl6MEotSWYwNzRvMUY3OTVNRFFmZzlDZkd3TUdxbGVaUEktWGYxMXRJNHdZSW9IZ0pWZE10ZHlQd2ZodHRGbmxELTJBTnVCMXVEQUdvT2JtRy1IMA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>목성 탐사선 주스 정밀위치 추적에 한국천문연 나선다</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>목성 탐사선 주스 정밀위치 추적에 한국천문연 나선다  중도일보유럽 목성 탐사선 '주스' 추적에 韓 우주전파관측망 투입  뉴시스“목성 얼음위성 생명체 비밀 푼다”…韓 전파망원경, 유럽 탐사선 정밀 추적  헤럴드경제천문연, ‘한국우주전파관측망’으로 목성 탐사선 ‘주스’ 위치 쫓는다  Don...</t>
-        </is>
-      </c>
-      <c r="F214" s="3" t="inlineStr">
-        <is>
-          <t>중도일보</t>
-        </is>
-      </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9HRlhzVy1hY2Y1RjFicDNVWlhGTEI0YTBrMHhDWGhWOWF5ZTQ1UHFJbkRIVFNsQ0xJa05LajB6T0tZSmJDYUV4d1hkbjNiMFVNYzV2U0ZUR3Q4eDh5MUMybnRqZUw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>캐슬바니아: 벨몬트의 저주 - 리뷰</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>캐슬바니아: 벨몬트의 저주 - 리뷰  IGN Korea[리뷰] 채찍으로 날아다니는 화려한 악마성, '캐슬바니아: 벨몬트의 저주'  디스이즈게임캐슬바니아신작 '벨몬트의 저주' 10월 15일 출시, 무료 데모 이미 공개  디지털포커스18년 만에 정사로 복귀, 캐슬바니아: 벨몬트의 저주  게...</t>
-        </is>
-      </c>
-      <c r="F215" s="3" t="inlineStr">
-        <is>
-          <t>IGN Korea</t>
-        </is>
-      </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNeTJ4NVdEQnVvWkNEdFJTZVZQTUVIVUgtMElWaVBTT0hVTnBHTmRDQmRxNTVIYm9iSmxWOFRqUEJ0dWw1ZnhUbHlyQWxfellrWWdsRnBwV0diQkpWbExUUk1qa1FYMDBNVG1Lbm9jLU9xemtvS1Faa0FuMlRzMl9BQzRPUGwya0FoaGRXZjZkWTdHdw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>'하우 투 피시', 출시 두 달 만에 이용자 1,000만 명</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>'하우 투 피시', 출시 두 달 만에 이용자 1,000만 명  인벤</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>인벤</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBKWWQ3eVBxdXZBdHFxeXNOb0M2ZnJueXlDQlFFU21xblpuNnFwNVpBTFNwcTZkRk15WlEwUlcyWnpiaTliS290RS1WM3ZNYmViX2pGNUN3OU5nS1pHY1E?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>Battlefield 6가 시즌 5 보너스와 함께 EA Play의 플레이리스트에 추가되었습니다.</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>Battlefield 6가 시즌 5 보너스와 함께 EA Play의 플레이리스트에 추가되었습니다.  GameGPU다음 주에 Xbox 콘솔에 40개의 새로운 게임이 출시됩니다.  GameGPU라스베이거스에 데드스페이스 콜라보까지, 배틀필드6 시즌5  인벤배틀필드6, 출시 1년 만에 게임패스...</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>GameGPU</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbTI2aTZHYVRSMkd1MDhteFVEOHkzdGpyb2ttMVFfc281NnhTbG1SdHRXaVBhczZOekhTcG9LSXhyV3Zrb0xfLUcxcUNPcm8wdm53N3JTNXFhUTRKXzZqdHV0S0lzdE5MQ2xOd2ZocGMyTzZnclp1N3RXaGdWVDJNeTZqaXVZVjRJQUNteUE1WVBqU21XM0VZeTRnX0RMZ2hYRkNVNU1sLTVOdUN3Rzl0TmtJeTRwOG9jRXJTLWdTQ3BLV3RnYUZn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>AMD Radeon RX 9070 XT AMDLSS5를 사용할 때 FPS가 70% 감소했습니다. Resident Evil Requiem</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>AMD Radeon RX 9070 XT AMDLSS5를 사용할 때 FPS가 70% 감소했습니다. Resident Evil Requiem  GameGPUAssetto Corsa에서 DLSS 5 출시 Radeon RX 9060 XT 4K 해상도에서 30FPS로 재생 가능  GameGPUCy...</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>GameGPU</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNk95eFZMLUhTRDFyQVpOZVZsVkU1SzQxTVRPdEhxRmV1M2xNUkg4R0xzWEdSb3ZUZE9VOXVxXzlnaEpnWGswV2YtbTg1RFVEQW90TE5CYzdPYy0zVFdUQ2NwNGdqQnhpcXBPQnJsaDgwdkhEZXYyU2RWckRDNDFkXzVRcXRnaXlpd2dITDFqNVBEeUQzX25zczR2Y0h5NnFWVEFuSklsekdoVDNSZUVqLWJ1SU1ueVVzS0ZaZg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>세계철강협회 내년 총회 서울 개최…포스코 회장, 유치 앞장</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장보인 기자 = 내년 세계철강협회 총회가 25년 만에 서울에서 열린다.</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014033700003</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>에이피알 "美아마존 행사서 역대 최대 성과…유럽서 검색어 1위"</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이상서 기자 = 에이피알[278470]의 메디큐브는 아마존의 대규모 할인행사인 '프라임 빅딜데이즈'에서 큰 성장세를 기록하며 ...</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014033000030</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>쿠팡, 유명 먹거리 모은 '미식관' 출시…로켓프레시 배송</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 조민정 기자 = 쿠팡 로켓프레시는 인기 셰프와 전국 맛집, 트렌드 먹거리를 모은 미식 전문관 '하우스 오브 테이스트'를 오픈했...</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014031400030</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="inlineStr">
-        <is>
-          <t>AI 반도체 성능·전력 한계 넘는다…'K-문샷' 위원회 출범</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 조승한 기자 = 과학기술정보통신부는 14일 서울 중구 달개비에서 K-문샷 반도체 분야 운영위원회와 기술위원회를 출범한다고 밝혔...</t>
-        </is>
-      </c>
-      <c r="F222" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013169500017</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>물길·양식장까지 한눈에…충남도, 드론으로 갯벌지도 구축</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>(홍성=연합뉴스) 김준범 기자 = 충남도는 드론을 활용해 가로림만 갯벌의 지형과 물길 등을 디지털 지도로 구축한다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G223" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014034100063</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>"시그니엘 이불 집으로"…롯데호텔, 침구·욕실용품 백화점 판매</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 구정모 기자 = 롯데호텔앤리조트는 송파구 롯데백화점 잠실점 9층에 '해온'(HEON)을 비롯한 자체 브랜드(PB) 상품을 판매...</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014026200030</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>'♥박위' 발목잡힌 송지은-잘나가는 한선화-3크릿, 엇갈린 시크릿 17주년[SC이슈]</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>'♥박위' 발목잡힌 송지은-잘나가는 한선화-3크릿, 엇갈린 시크릿 17주년[SC이슈]  조선일보Google 뉴스에서 헤드라인 및 의견 더보기</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQc1poUno5RWpuUUo2YUFCMVlLbHhDMl9hci1rTS0yZFVGYnBualBBRXZ6T3RocVNqU1lURE1GNzRiZmNoSHBuTHEwblNIdlY4UWNNbWNpUnk2dDJkZHlGdjZ0dUI4VTViSnJfWWlmRTlLRXJIVVJXdHEtVHN0eGpLcERZS1BSVWdJZ1lzRUtSQnN4Q0hx?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>[주간! 대중문화] 연상호 신작 ‘실낙원’…류혜영, ‘킬링타임’에서 액션 도전</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>[주간! 대중문화] 연상호 신작 ‘실낙원’…류혜영, ‘킬링타임’에서 액션 도전  KBS 뉴스AI로 되살린 아들 vs 9년 만에 돌아온 아들…연상호 '실낙원'  연합뉴스김현주, 10월 스크린과 안방극장 동시 정조준...N차 전성기 예감 - 머니투데이  머니투데이BIFF #8호 [씨네초이스...</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>KBS 뉴스</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9OMmhEY2xPdlU2S1ZPLU1UcWVCaFVaNHl2YkxNaUs4UHFtQXJuQUtjVmVzY25wcWRQQTFsZFZpcXRmYjJZV2FEUzUtUFBIMmp2V0JBQmx3WlMzdjQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>유재석, 또 시청률 1위…서강대 심리학과 출신 남지현 모교 가더니(‘틈만나면’)</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>유재석, 또 시청률 1위…서강대 심리학과 출신 남지현 모교 가더니(‘틈만나면’)  조선일보‘틈만나면,’ 남지현 “공부가 재밌었다”…퀴즈 프로그램 나갔다가 데뷔한 사연  YTN'틈만나면' 유재석, 김재영 등장에 "역시 미남은 장발…장발은 미남밖에 안 어울려"  SBS 뉴스'틈만나면' 대흥...</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="G227" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUW44eDJtdGlOTk1JR0lCb3JMTUZpcVlxQnNlY1k1QXB0TFlNSFBGRHZKMFQyVE9qUGJ1QXhCelpmekM0RW1tQkJXVThyTDBqcnNManVwS0s0YWZvM253Tm9OWFdDME1mOEtnYU9HMmRUWGh0eTVRSjE3UEtBcGJWRnRiWXp4OHZWN0tYenNmMA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>[지윤철학원의 오늘의 운세] 2026년 10월 14일 수요일 띠별 운세</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>[지윤철학원의 오늘의 운세] 2026년 10월 14일 수요일 띠별 운세  뉴스투데이[오늘의 운세] 2026년 10월 14일 띠별 운세  YTN[오늘의 운세] 10월 14일 수요일 (음력 9월 4일) 띠별 운세  경기일보[오늘의 운세/10월 14일]  동아일보[김동완의 오늘의 운세] 20...</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>뉴스투데이</t>
-        </is>
-      </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFAzUFI5MzhPWGFDdlRBQTdrNUlpRVVuRi1MRlEtNE5sODVFU1lHNDByM3BQVkkwcjY5RDhFVmVPRDNQWjdfMnlTMFY4Rml6OTRpSGNQSW5tdVFmdkFUTnc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>경찰, '암살자(들)' 역사 왜곡 논란 고발인 조사… 본격 수사 착수</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>경찰, '암살자(들)' 역사 왜곡 논란 고발인 조사… 본격 수사 착수  한국경제[시론담론] 사실과 진실 사이  제민일보[기고]표현의 자유 뒤에 숨겨진 역사적 책임  경상일보‘암살자(들)’ 논란 어디까지 가나…이젠 ‘100분 토론’까지  매일경제“300만 넘고 또 뛰었다..개싸라기” ‘암...</t>
-        </is>
-      </c>
-      <c r="F229" s="3" t="inlineStr">
-        <is>
-          <t>한국경제</t>
-        </is>
-      </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE40OFpPTlVwUmtKWk5sSFY5WC1IaGkwbUFhTGpnS0R3d3pCZ21KcEM5VTMwVElyZFhhNVVnWUE5MVpfTkxudDNaMEt4UHBZZE5xNlE1dmphOXdLUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>경찰, '역사왜곡 논란' 영화 암살자(들) 제작진 고발 사건 수사 착수…고발인 조사</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>경찰, '역사왜곡 논란' 영화 암살자(들) 제작진 고발 사건 수사 착수…고발인 조사  데일리안Google 뉴스에서 헤드라인 및 의견 더보기</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>데일리안</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFBDLTl1VkJtRkVaMlJQbFZ3cHlLY2JUQ3FaNzNKdFNLUHNuSWRfMGRqU1UybGdFVGxvMDc4M080WFZGNEVNTjF6c3BRNGppeVhwampsTlZTSQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>[핌in현장] '킬링타임' 류혜영·남윤수, 자극 좇는 인터넷 방송 속 생존 스릴러</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>[핌in현장] '킬링타임' 류혜영·남윤수, 자극 좇는 인터넷 방송 속 생존 스릴러  뉴스핌몰카가 진짜 살인 현장으로 바뀌었다…공포액션 영화 '킬링타임'  연합뉴스[Y현장] "가짜 공포가 현실로"…'킬링타임' 류혜영·남윤수, 핏빛 사투극(종합)  YTN[영상] 죽어야 끝나는 라이브…‘킬링...</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>뉴스핌</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9CbTdpT1FHeFFvcDF2a3RzeENKdFpkODRFRmhqRUM2XzdPM2ZBbThCV3pQdGdHM3hhLVR2NjhyWFJLYzkwV3NqTXBId2pGZkxtZUVrb1N2c05jdw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>기안84, 잘 안씻는 뜻밖의 이유 "군대서 자꾸 씻으라고, 반발심 생겼다"(기안장)</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>기안84, 잘 안씻는 뜻밖의 이유 "군대서 자꾸 씻으라고, 반발심 생겼다"(기안장)  스포츠조선"보다가 더러워서 껐다"…팬티 사흘간 안 갈아입은 기안84 '시끌' - 머니투데이  머니투데이"팬티 3일간 안갈아입어"..'기안장2' 기안84 위생논란, 김연경 "군대서 못배웠나" 정색[Oh!...</t>
-        </is>
-      </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>스포츠조선</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPRmxPWjQ2UFF2WWo0TFdpZmQ1TWhpQ3F1d1U4eF9fYTNzMVVFeEJ2Vk5JNlJ6blpaaURPVDNydWpjdHZ0LXU5MFQ1eWROSTNMZ1VsV1FHN3lYMEFaaV9QdlQ3MU5mYTd4NXJ3My1tb09HcGlUYXU1NEVpSFJoU0Y4cE5BRGU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>천재 의사 활약 그린 '닥터X', 넷플릭스 비영어쇼 1위 직행</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>천재 의사 활약 그린 '닥터X', 넷플릭스 비영어쇼 1위 직행  연합뉴스의사 가운 입은 김지원, '시청률의 여왕'…'닥터X', 첫 주 주말극 평정  YTN'닥터X' 의료 고증 논란…자문 교수 남궁인 "제작진과 싸우다 의사가 패배"  뉴스1[스경연예연구소] ‘닥터X’ 김지원·‘100일의 ...</t>
-        </is>
-      </c>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5FOTNiSHdfNXFpNldxdi1jLUlfSGNYV1YxVmg3cXBFeGFKeHNQRGpmeTluMldiTFNUUzNseGRGajVGWHVHODRveHlKd1RGQnNZY0tubXNOMnoybTTSAWBBVV95cUxPVk14VUNQQlYzR3pFZFNmSFZhaExYS2YwRHd5b1RoamtiODFaUzg1SE52WS0xSVhROXVxRG4xaXB1SWdGZXpOTFBJX2xXYWk4ak1rb1pmZXRqOC1pdmpHcEs?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>이준혁 “로또 5천 원이 최고 당첨금..30억 당첨되면 제작비로 쓸듯” [인터뷰②] - 조선비즈</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>이준혁 “로또 5천 원이 최고 당첨금..30억 당첨되면 제작비로 쓸듯” [인터뷰②] - 조선비즈  Chosunbiz"하루 반 끼 '로또 1등의 삶'"...알잖아요. 배우 이준혁이 어떻게 했는지, 뭘 했는지, 얼마나 열심히 했는지  조선일보윤영빈 감독 "열심히 산 사람에게 행운이 있길 바...</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPU3FmamZ4REUxN3FfOWd2R3pBYnF3bFZTc3VqNllvc1BXQUJ3b1hxTjRzUWczTmhvWFk1TGYzOV84ckgzMkZNeXdWNmwyWUpjYmtNcDNjc1Q4d2xvc0lVU0JKWFVYSmhMZVEwZkVOeUNmdXc1Mmdzd2t0UTNHT05TRzdSa1AteGQyeUVycEpXcEc2NHPSAacBQVVfeXFMUHhGUm9XR0NMM0liU1dCZ214ZjQ4RDZnVi1Ta2lpMjVzWGZWOERmeXZtekc5ajR0d2JlZEc3ZlljbHYzbjFBWHdqSW9zUVU1ODZQR0d3QnJVdERoUkptbFliRjVaVTl4bjNuWTloOGRiOHJfOVhqZTRWUlI4NWNwSWN1eWVSSDlfSGpIM1F5QlpQdjkxWmJDQ1FlZjJFSEpzUnVtQkhsRzg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>리센느 ‘PULSE’ 심장이 뛴다</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>리센느 ‘PULSE’ 심장이 뛴다  스포츠경향리센느, 차트 역주행 넘어 새 도약…신보 'PULSE' 프로모션 일정 공개  YTN[단독] 배민에서 아이돌 앨범까지...‘리센느’ 컴백 앨범 사전 예약 받는다  조선일보리센느, 첫 지상파 뉴스에 떴다!…역주행→대중 존재감 각인  전자신문‘안원...</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>스포츠경향</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9lRUlCa1NUZ3RXRS1PNjl0M3BHNTJvdXBocnJOS0dxcU1ZQWRPWU9iYTZERHFycnNCZXBQVHFPNG1wcC11OHYxaFRueUJUMG9vS09ZR2RrTGZhcTAtWHfSAWNBVV95cUxOVHIxb3k1dGJYMjZZRk5XNDVpWGVjYl9BQ05fLWpqS0Y3OTFCWTRDUk93NU5lalZpMklfRnI1Wjg4UWt0T09FeUQ0blFOU0FsdlgyUVBzZXVld2p4WGdpRmEzMFk?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>성유리, 바쁘다 바빠 ‘이중생활’..핑클 안무 연습 끝나니 쌍둥이 딸 수영 케어</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>성유리, 바쁘다 바빠 ‘이중생활’..핑클 안무 연습 끝나니 쌍둥이 딸 수영 케어  조선일보Google 뉴스에서 헤드라인 및 의견 더보기</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOWDNIXzFYWk1QS3Zfd2p2akZOWXFtOFJ0UVRhWDQ5R0pQdXFEbEpaaktqNDlQaE1GbHN5eDVEOExBY1Bka1hUakw3RURIbU91NDExdXFYUnRLT1hsV3UwQ3BWZHI0QjdQV1p2TmZxeVNlZkw2ZTFRN3hsVDZsSGczdklQYzF3S3ZBTWczZzR6MA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>[영상] 올해도 낙담한 일본 하루키팬들…내년엔 환호할 수 있을까?</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>[영상] 올해도 낙담한 일본 하루키팬들…내년엔 환호할 수 있을까?  KBS 뉴스</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>KBS 뉴스</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RcnBueXBsU1pfRU5ZUUNHeEpXNFNvT1kzSWdJbG5ueXB1LWw5a0p1N3RneHFJZWxYb2h2Z1ItT0hGU3VXNEhPbmJZMm10QUlsOVhIZDMzU1pHZWM?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>2026 노벨 문학상 수상자, 앤 카슨의 대표작 5</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>2026 노벨 문학상 수상자, 앤 카슨의 대표작 5  Vogue korea[속보]전국 경찰서장 242명 중 절반 교체…'향피제' 전면 적용  노컷뉴스[세상 읽기]사랑이 사라지는 사회  경향신문[대중문화칼럼] ‘노벨문학상’ 앤 카슨의 문화적 신드롬이 주는 메시지  천지일보병도 나이도 막지...</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>Vogue korea</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxOSG12YS1PX3psQnhRMmlncEFGQ1RLMVVXY2g0dXVGdGpMeGxRZGhlSDZLQWlYNG1kNHJJTTl6cHBZVTJSNVJnbF83VmhzZ2V6dFFUSnJPakpFVkZiV3gxdkNBa05CZU40dUt6M2M0bWphd2VmcVFDSjlyU0Q3VTVpMUxmVWtSUlZOaFkySm1zcEhsQXBSV01TX0hQMW16QkZVVkoyc2podUNjY0I3ZlUyTlQyWDhvWGhyNV9Wc0hIRnIxNkpRU2RERUZzYzd6ZW1KWmthN0FsM0xtVkoxZ1NMdTdScXNnTEhOSUVxX2RWMlRFUVZDSzBWbDRDUUNwMmo1NjVudkx2bW1pQXVXX0VqQw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>차장으로 승진한 이준혁…'로또 1등' 6.2% 종영</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장진리 기자 = 로또 1등에 당첨된 직장인의 삶을 그린 오피스물 '로또 1등도 출근합니다'가 6%대 시청률로 종영했다.</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014032000005</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>손호영 "5년 만에 신곡, 솔로 데뷔 20주년에 마음 먹었죠"</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김선우 기자 = "손호영이란 이름으로 신곡을 내기까지 5년이나 걸렸네요. 솔로 데뷔 20주년 만큼은 절대 피하면 안 된다는 생...</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261012182400005</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>'투팍 살해지시' 갱단 두목에 사실상 종신형…30년만의 단죄</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>(샌프란시스코=연합뉴스) 권영전 특파원 = 미국 힙합계의 전설적인 래퍼 투팍(2Pac·투팍 샤쿠르)의 살해를 지시·공모한 갱단 두목이 범행 30...</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014009400091</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>천재 의사 활약 그린 '닥터X', 넷플릭스 비영어쇼 1위 직행</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장진리 기자 = 천재 외과의사의 활약을 그린 의학물 '닥터X: 하얀 마피아의 시대'(이하 '닥터X')가 전 세계 넷플릭스 이용...</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014017900005</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>단편선 순간들 "좋아하는 재료 다 넣어 맛있는 음악 만들었죠"</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이태수 기자 = "사랑을 한다는 건 모험 가운데에서도 가장 어려운 모험이라고 생각해요."</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013136400005</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>이준혁 "20년 만에 첫 원톱 주인공, 연기가 재즈 같았죠"</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장진리 기자 = 배우 이준혁(42)에게 주연작인 티빙 시리즈 '로또 1등도 출근합니다'는 재즈 같은 작품이었다.</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013160100005</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>인피니트 남우현 "16곡 꽉 채운 정규 2집, 그만큼 자신 있어요"</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김선우 기자 = "정규 2집에 댄스, 록, 알앤비(R&amp;amp;B) 등 다양한 장르가 담겨있어요. 제가 10년 동안 선보인 음악...</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013133700005</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>윤영빈 감독 "열심히 산 사람에게 행운이 있길 바랐죠"</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장진리 기자 = 티빙 시리즈 '로또 1등도 출근합니다'에서 배우 이준혁이 연기한 주인공인 직장인 공은태는 편의점에 갔다가 잔돈...</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013179700005</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>"아일릿이 뉴진스 표절" 민희진, 명예훼손·업무방해 혐의로 송치</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 양수연 기자 = 하이브 산하 레이블 빌리프랩의 걸그룹 아일릿이 어도어 소속의 뉴진스를 표절했다는 의혹을 제기해 온 민희진 전 ...</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013180200004</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>AI로 되살린 아들 vs 9년 만에 돌아온 아들…연상호 '실낙원'</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 정래원 기자 = 9년 만에 살아 돌아온 아들보다 인공지능(AI)으로 재현한 아들이 더 진짜처럼 느껴질 수 있을까.</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013177600005</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>최휘영 장관 "영화 '홀드백' 아직 숙의 중…고민할 지점 생겨"</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 임순현 기자 = 최휘영 문화체육관광부 장관이 영화계 '홀드백' 논의가 참여자 간 이견으로 아직 숙의 과정 중에 있다고 밝혔다....</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013175300005</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>티빙 대표 "AI 기반 해킹 추정"…개인정보위 "연내 처분 마무리"</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 차민지 기자 = 최주희 티빙 대표가 대규모 개인정보 유출 사고와 관련해 인공지능(AI) 기반 해킹에 따른 사고로 추정하고 있다...</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013173300530</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>몰카가 진짜 살인 현장으로 바뀌었다…공포액션 영화 '킬링타임'</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 박원희 기자 = 연우(류혜영 분)와 주원(남윤수)이 운영하는 인터넷 방송 채널 '킬링타임'은 몰래카메라 콘텐츠를 생중계해 돈을...</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013171800005</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>[가요소식] NCT 위시, 신보 발매 하루 만에 밀리언셀러</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김선우 기자 = ▲ NCT 위시, 4연속 밀리언셀러 달성 = 그룹 NCT 위시가 지난 12일 공개한 미니 4집 '아이 스파이'...</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261013168900005</t>
+          <t>https://www.yna.co.kr/view/AKR20261014039500005</t>
         </is>
       </c>
     </row>
@@ -11114,32 +8521,32 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>232,000원</t>
+          <t>240,000원</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+25,500.0원 (+12.35%)</t>
+          <t>+33,500.0원 (+16.22%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>229,500원</t>
+          <t>237,500원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>258,500원</t>
+          <t>257,000원</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>224,000원</t>
+          <t>231,500원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+12.6%</t>
+          <t>+8.2%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -11149,7 +8556,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>RSI 34.4로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 39.3로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -11163,21 +8570,21 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>34.4</v>
+        <v>39.3</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>"한전, 호남산단 전력망건설 '2년반 안에 완료' 계획 비현실적" (주요언론)</t>
+          <t>[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여 (문화일보)</t>
         </is>
       </c>
     </row>
@@ -11204,42 +8611,42 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1,443,000원</t>
+          <t>1,487,000원</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+340,000.0원 (+30.83%)</t>
+          <t>+384,000.0원 (+34.81%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1,371,000원</t>
+          <t>1,472,000원</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1,428,500원</t>
+          <t>1,706,500원</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>1,399,500원</t>
+          <t>1,435,000원</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+15.9%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (악재 주의)</t>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
+          <t>RSI 35.1로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -11253,21 +8660,21 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>31.4</v>
+        <v>35.1</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>주주환원 늘었는데 세금은 제각각…입법조사처 "배당세제 정합성 손봐야" (연합인포맥스)</t>
+          <t>[개장시황] 코스피 1.29% 상승 출발…삼성전자·SK하이닉스 반등 (남도일보)</t>
         </is>
       </c>
     </row>
@@ -11294,32 +8701,32 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>315,000원</t>
+          <t>321,000원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-176,500.0원 (-35.91%)</t>
+          <t>-170,500.0원 (-34.69%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>312,000원</t>
+          <t>318,000원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>346,000원</t>
+          <t>342,500원</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>304,000원</t>
+          <t>310,000원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>+7.8%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -11329,35 +8736,35 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>RSI 21.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 27.4로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.9</v>
+        <v>27.4</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>현대차그룹, 학대피해 아동 돕는 '아이케어 카' 20대 기증 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -11384,27 +8791,27 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>108,500원</t>
+          <t>110,000원</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-40,900.0원 (-27.41%)</t>
+          <t>-39,100.0원 (-26.21%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>107,000원</t>
+          <t>109,000원</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>115,000원</t>
+          <t>116,500원</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>104,500원</t>
+          <t>106,000원</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -11419,30 +8826,30 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>RSI 29.0로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 34.0로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -11474,32 +8881,32 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>178,000원</t>
+          <t>182,000원</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-23,500.0원 (-11.66%)</t>
+          <t>-19,250.0원 (-9.55%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
+          <t>180,500원</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>193,000원</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
           <t>176,000원</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>191,500원</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>172,000원</t>
-        </is>
-      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+8.7%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -11509,30 +8916,30 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>RSI 26.7로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 33.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>26.7</v>
+        <v>33.6</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -11564,27 +8971,27 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>31,300원</t>
+          <t>32,000원</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-16,800.0원 (-34.93%)</t>
+          <t>-16,100.0원 (-33.47%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>31,000원</t>
+          <t>31,700원</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>33,900원</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>30,200원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -11599,35 +9006,35 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>RSI 27.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 35.4로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>27.9</v>
+        <v>35.4</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>카카오뱅크 'AI적금' 출시…저축목표 따라 맞춤형 조언 (주요언론)</t>
+          <t>카카오, 인적분할 앞두고 CEO 총출동…새 성장전략 공개 (주요언론)</t>
         </is>
       </c>
     </row>
@@ -11654,32 +9061,32 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>179,500원</t>
+          <t>183,500원</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-9,919.049999999988원 (-5.23%)</t>
+          <t>-5,919.049999999988원 (-3.12%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>176,000원</t>
+          <t>180,000원</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>188,500원</t>
+          <t>193,000원</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>170,500원</t>
+          <t>174,500원</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -11703,21 +9110,21 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>[바이오스냅] 셀트리온, 미국 처방집 추가 등재 추진 (주요언론)</t>
         </is>
       </c>
     </row>
@@ -11744,32 +9151,32 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>839,000원</t>
+          <t>832,000원</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-684,000.0원 (-44.91%)</t>
+          <t>-691,000.0원 (-45.37%)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>830,500원</t>
+          <t>823,500원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>1,003,000원</t>
+          <t>991,500원</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>809,500원</t>
+          <t>803,000원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>+20.8%</t>
+          <t>+20.4%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -11779,30 +9186,30 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>RSI 29.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 29.1로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>29.6</v>
+        <v>29.1</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -11834,32 +9241,32 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>410,000원</t>
+          <t>421,500원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+10,000.0원 (+2.50%)</t>
+          <t>+21,500.0원 (+5.38%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>369,500원</t>
+          <t>372,000원</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>410,000원</t>
+          <t>421,500원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>402,000원</t>
+          <t>413,000원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>+13.3%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -11869,7 +9276,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 67.8, 20일선 이격도 +11.0%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 70.9, 20일선 이격도 +13.2%로 단기 과열권, 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -11883,21 +9290,21 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>67.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>+13.2%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>가족 연계 회사에 수년간 자문료…전 LG엔솔 사장 ‘배임’ 수사 (KBS 뉴스)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -11924,42 +9331,42 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>299,000원</t>
+          <t>308,500원</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>-62,500.0원 (-17.29%)</t>
+          <t>-53,000.0원 (-14.66%)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>296,000원</t>
+          <t>302,500원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>317,000원</t>
+          <t>334,000원</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>288,500원</t>
+          <t>293,000원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+10.5%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>RSI 37.2로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -11973,21 +9380,21 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>37.2</v>
+        <v>45</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>노동부 장관 “포스코 교섭 적극 지도…신안산선 사고 엄중 조치” (KBS 뉴스)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -12024,32 +9431,32 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>$201.56</t>
+          <t>$223.95</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>$226.23</t>
+          <t>$239.95</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>$221.66</t>
+          <t>$217.09</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>+12.2%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (악재 주의)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -12077,7 +9484,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>거침없는 외인 매도...반도체 역대급 실적에도 급락, 왜? (YTN)</t>
+          <t>세레브라스 CEO "데이터센터 반발은 공포 마케팅 탓" (주요언론)</t>
         </is>
       </c>
     </row>
@@ -12167,7 +9574,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>애플, 4년만 A19 탑재한 신형 애플TV 4K 공개···가격 44만 원 (글로벌E)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -12489,12 +9896,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6,035.35</t>
+          <t>6,168.13</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>-348.89 (-5.46%)</t>
+          <t>+132.78 (+2.20%)</t>
         </is>
       </c>
     </row>
@@ -12516,12 +9923,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>837.03</t>
+          <t>845.03</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-55.24 (-6.19%)</t>
+          <t>+8.00 (+0.96%)</t>
         </is>
       </c>
     </row>
@@ -12735,27 +10142,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,886,000원</t>
+          <t>112,822,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>112,322,000원</t>
+          <t>112,258,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,917,000원</t>
+          <t>121,848,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,592,000원</t>
+          <t>110,586,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -12792,27 +10199,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3,393,000원</t>
+          <t>3,391,000원</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3,366,000원</t>
+          <t>3,364,000원</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3,596,500원</t>
+          <t>3,594,500원</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3,274,000원</t>
+          <t>3,272,500원</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -12827,7 +10234,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>RSI 47.5로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 47.2로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -12849,17 +10256,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>145,200원</t>
+          <t>145,300원</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>144,000원</t>
+          <t>144,100원</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -12869,12 +10276,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>140,100원</t>
+          <t>140,200원</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>+8.2%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -11,6 +11,7 @@
     <sheet name="주식추천_누적" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="시장지표_누적" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="코인추천_누적" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="공식리포트_누적" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -463,7 +464,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3626,27 +3627,27 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>김지용 중수청장 후보자 오늘 청문회…‘친윤 논란·개혁 적합성’ 시험대</t>
+          <t>태안군, 12월부터 참전명예수당 월 30만원→50만원</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>김지용 중수청장 후보자 오늘 청문회…‘친윤 논란·개혁 적합성’ 시험대  한겨레‘친윤’ 딱지에 임은정 감찰까지…김지용, 중수청장 문턱서 여권 시험대  매일경제김민석, '김지용 비판' 추미애에 "자기 역할에 집중해야"  연합뉴스靑이 해야 할 말, 하지 말아야 할 말[오늘과 내일/장원재]  ...</t>
+          <t>(태안=연합뉴스) 정윤덕 기자 = 충남 태안군은 현재 월 30만원인 참전명예수당을 오는 12월부터 50만원으로 인상할 계획이라고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5oYjdZdVl0MTNLWE1zWVI3QWw3aVpjNlpkaklQV2dYVUMwOUFkTXVycmRFNFN1Xy1pSFFDYUZzR3pPamxzUzMwYkQtWW5FRVllOWg0SkQ3TTluWmN4TWdBVFhRdGQxbUVWRzR5YXNTN2YtZw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014058000063</t>
         </is>
       </c>
     </row>
@@ -3668,22 +3669,22 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>첫발 뗀 '북극항로' 개척…사업성 확보가 최대 관건</t>
+          <t>與, 野주진우·이진숙·김태규 직격…"패륜으로 인지도 올리나"</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>첫발 뗀 '북극항로' 개척…사업성 확보가 최대 관건  한국경제[대통령 이재명 말모이] 대한민국의 북극항로 항해일지는 이제 첫 장을 열게 됩니다 - 카드/한컷 | 멀티미디어  정책브리핑이 대통령 “국제사회 신뢰 속 북극항로 열어갈 것…해양강국 대한민국”  KBS 뉴스북극항로 부산 허브화 ...</t>
+          <t>(서울=연합뉴스) 최주성 기자 = 더불어민주당은 14일 국민의힘 주진우·이진숙·김태규 의원의 국정감사 기간 중 발언을 놓고 "막말 정치인 양성소...</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE82ZDF3clBYNzVHVFA3NUd4NTRGUnpPSXVoZ1AwTFhPVUdMSGZGeDdDbzBOaTZSeHhVVkEzTHpMVjUzMWxZR3BwcWMxa09hZXBnUWgxQV9Qbm5aZw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014062800001</t>
         </is>
       </c>
     </row>
@@ -3695,32 +3696,32 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>국감서 배제된 이진숙… '尹정부 방통위원장 출신' 이해충돌 공방</t>
+          <t>주미대사관 “강경화 ‘불의의 사고 아니다’ 발언, 이 대통령 반박 아냐”</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>국감서 배제된 이진숙… '尹정부 방통위원장 출신' 이해충돌 공방  한국일보“투쟁 선봉” “선 넘는다” 이진숙·주진우에 국힘서도 이견  경향신문‘사상 초유’ 발언권 2명 정지·위원 제척까지…국감서 위원장 칼 휘두르는 與  서울경제국힘 "與, 억지 프레임 씌워 이진숙 제척…내로남불·의회폭거...</t>
+          <t>주미대사관 “강경화 ‘불의의 사고 아니다’ 발언, 이 대통령 반박 아냐”  한겨레"불의의 사고 아니다" 강경화 발언 수습에… 한동훈 "국민이 우습나"  조선일보‘북 DMZ 지뢰’ 대처 공방…“안보리 차원 대응 검토 중”  KBS 뉴스[연합뉴스 이 시각 헤드라인] - 07:30  연합뉴스...</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>한국일보</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9kYVNBRVlPNnliZTREaWdUT3doR0lrWVRTUlVHbmNJT1R5ZEpjS3VIazFrYWpPRkwyZlNiVkFCRlE0MUNYd1pSdVQ3MGdpLUQ4dGxsSkxINzV5bUZnaE9RMndMTE1nNU9IcmFIbUJR0gFzQVVfeXFMTV9ybWJfNmZzNDRBNmlyVkZIVnRUd1JzNGVqcV9TMDJoVjhCTHdOT2lEZjRjTlN1VzZRaWdrU2FyMWRwNjgwUVVBbUM0R2Y3RlV3NFNoMmZpdXdQNnI2MElnb2dBcjdTcUdQQ2FWWFY1RkJiQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBvaWlRcEhkSXFzQU56OW1VOEFZdjFYZGh1akJIVUkwOFE4Y2NweUVpaVVxQjhSaGd2bG9FZzZKSExzTU8zY0FocWZTS3diZHZlSGxBaW9TazZ2b1RtWXBhS09tYzRsTHFMNVBR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3733,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3742,12 +3743,12 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>지난해 아파트 관리비 최고는 나인원 한남…"월 평균 170만원"</t>
+          <t>경남도, 육상풍력 7개단지 48기 전수 점검…위험요인 사전 확인</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 노선웅 기자 = 지난해 전국 아파트 가운데 서울 용산구 '나인원 한남'의 세대당 월평균 관리비가 월평균 170만1천847원으로...</t>
+          <t>(창원=연합뉴스) 김선경 기자 = 경남도는 오는 30일까지 도내 육상풍력 발전단지 7곳을 전수 점검한다고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3757,7 +3758,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014047900001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014066600052</t>
         </is>
       </c>
     </row>
@@ -3769,22 +3770,22 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>한병도 "중수청, 리더십 절실…김지용, 소신·비전 제시해달라"</t>
+          <t>세종시-홍익대, 청년 창업·실험실 '금남대평시장 리빙랩' 운영</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 박경준 안정훈 기자 = 더불어민주당 한병도 원내대표는 주진우 의원이 SNS에 '이재 명을 끊을 때'라는 댓글을 적는 등 국민의...</t>
+          <t>(세종=연합뉴스) 양영석 기자 = 세종시와 홍익대학교 세종캠퍼스는 청년 창업·실험 공간인 '금남대평시장 가치회복 리빙랩'을 운영한다고 14일 밝...</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3794,7 +3795,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014044800001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014068900063</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3807,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3816,12 +3817,12 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>주진우, 2026 여수 세계섬박람회 국민감사 청구</t>
+          <t>AI 전환부터 수출까지…산업부·식약처, 바이오산업 전주기 협력</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>(여수=연합뉴스) 손상원 기자 = 국민의힘 주진우 의원이 부실 지적을 받아온 2026 여수 세계섬박람회에 대한 국민감사를 청구한다.</t>
+          <t>(서울=연합뉴스) 장보인 기자 = 바이오산업 육성을 담당하는 산업통상부와 의약품·의료기기 규제를 책임지는 식품의약품안전처가 바이오산업 전 주기에...</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3831,7 +3832,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014048400054</t>
+          <t>https://www.yna.co.kr/view/AKR20261014025800003</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3844,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3853,12 +3854,12 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>어기구 "가습기살균제 피해 재심사 결과 받는 데 최장 4년 반"</t>
+          <t>강원 고성군, 재난 안전상황실 전담 인력 배치…내달 본격 운영</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>(당진=연합뉴스) 정윤덕 기자 = 가습기살균제 피해 재심사를 신청한 뒤 결과를 받기까지 길게는 4년 반이 걸린 것으로 나타났다.</t>
+          <t>(강원 고성=연합뉴스) 류호준 기자 = 강원 고성군은 기후 변화와 각종 재난 사고에 신속하게 대응하기 위해 다음 달부터 재난 안전상황실 전담 운...</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3868,7 +3869,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014044600063</t>
+          <t>https://www.yna.co.kr/view/AKR20261014066400062</t>
         </is>
       </c>
     </row>
@@ -3880,22 +3881,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>전작권 조건충족 이견 속…한미 국방장관 이달말 첫 대면 가능성</t>
+          <t>설악권 현안 두고 머리 맞댄 속초시·고성군 의회…"상생 협력"</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김효정 기자 = 전시작전통제권(전작권) 전환 조건 충족 여부를 두고 한미가 이견을 보이는 가운데 이달 말 국제회의를 계기로 강...</t>
+          <t>(속초=연합뉴스) 류호준 기자 = 강원 속초시의회와 고성군의회 의장이 만나 울산바위 인근 공동주택 개발 문제 등 설악권 주요 현안과 관련해 지역...</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3905,7 +3906,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014039900504</t>
+          <t>https://www.yna.co.kr/view/AKR20261014065100062</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3918,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3927,12 +3928,12 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>조의장, 그리스서 경제협력 간담회…방산·첨단산업 세일즈외교</t>
+          <t>AI로 '옥외영업 인허가' 판단…고양시, 직원 아이디어 특허</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>(아테네=연합뉴스) 오규진 기자 = 그리스를 공식 방문 중인 조정식 국회의장은 13일(현지시간) 그리스 의원들과 경제협력 오찬 간담회를 열어 방...</t>
+          <t>(고양=연합뉴스) 노승혁 기자 = 경기 고양시는 현장 공무원이 직접 고안한 '인공지능(AI) 기반 옥외영업 가능 대상 자동 판단 및 인허가 검증...</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3942,7 +3943,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261013189300001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014064100060</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3955,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3964,12 +3965,12 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>김민석 "曺 헌법훼손 차고 넘쳐…잘못 바로잡는 모든 방안 검토"</t>
+          <t>AI 코딩부터 데이터 활용까지…'AI 체험 축제' 열린다</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김남권 안정훈 기자 = 더불어민주당 김민석 대표는 14일 조희대 대법원장의 대법관 후보자 재제청 거부와 대법관 격려금 지급 논...</t>
+          <t>(서울=연합뉴스) 권하영 기자 = 전 국민이 참여할 수 있는 인공지능(AI) 체험의 장이 열린다.</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -3979,7 +3980,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014044000001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014065400017</t>
         </is>
       </c>
     </row>
@@ -3991,22 +3992,22 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>"농진청, '57만명 개인정보 유출' 제재받은 업체와 재계약"</t>
+          <t>김해진영단감축제 30일 개막…사흘간 공연·체험 행사 풍성</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 노선웅 기자 = 농촌진흥청이 농민 57만여명의 개인정보 유출 사고에 책임이 있는 업체와 별도의 보안 강화 조치 없이 계약을 유...</t>
+          <t>(김해=연합뉴스) 이준영 기자 = 경남 김해시는 오는 30일부터 내달 1일까지 진영운동장 일원에서 '제42회 김해진영단감축제'를 개최한다고 14...</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4016,7 +4017,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014035700001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014065600052</t>
         </is>
       </c>
     </row>
@@ -4033,27 +4034,27 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>유엔 국감장서도 北 지뢰 논쟁… 野 “유엔대표부 할 일 하고 있나” 공세</t>
+          <t>목포해경, 안전사고 위험 '주의보' 발령</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>유엔 국감장서도 北 지뢰 논쟁… 野 “유엔대표부 할 일 하고 있나” 공세  동아일보‘불의의 사고’ 아니란 강경화 대사 발언 해명 나선 주미 대사관···“기존 표현 맞는지와 무관”  경향신문‘북 DMZ 지뢰’ 대처 공방…“안보리 차원 대응 검토 중”  KBS 뉴스[연합뉴스 이 시각 헤드라...</t>
+          <t>(목포=연합뉴스) 조근영 기자 = 목포해양경찰서는 14일 목포·신안·무안·진도 등 전남광주 8개 시·군 지역에 안전사고 위험예보제 '주의보' 단...</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE00bXFtc1dxeWdEWG9yY0o1WWVYeUNqUVZhc0Q2djhFT1pfdEtaaUdIemQyQWJnMkdfVTZwNDFULV9jYWszR2FuT0EwVjU3dWZJWUdoMFZMVFVuOE5sQ2NsREpqMDE3ek9aT29UaDUxNWxJOXfSAWZBVV95cUxOdktGVFlUOGNCOXhINTh2YWVEQ3k0RDFERDlJbVFVNmdGTTVTaHNPaGxQY0h4a3F2RE85eGN4VzltZDI2a2lYenNsbFh0YldmS2VNUENXNnJHVWdnZlA3cVpIWDhtN1E?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014065700054</t>
         </is>
       </c>
     </row>
@@ -4075,22 +4076,22 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>마라톤 결승선 앞두고 숨진 카이스트 대학원생…SNS 추모 물결</t>
+          <t>거래소·배출권시장協, 배출권거래제 정책·산업계 대응 논의</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>마라톤 결승선 앞두고 숨진 카이스트 대학원생…SNS 추모 물결  한국경제'서울 달리기' 마라톤대회 참가했던 20대 여성 사망  연합뉴스황영조 “사망에 이르는 러닝” 경고···SNS 과시형 기록 문화도 지적  경향신문“SNS 인증샷 찍다 죽습니다”…마라톤 기록 경쟁 과열에 황영조 당부 -...</t>
+          <t>(서울=연합뉴스) 임은진 기자 = 한국거래소는 14일 오후 서울 사옥에서 배출권시장협의회와 함께 '2026년 하반기 자문위원회 세미나'를 연다.</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1nRG1XbzVKbGFySjZMU1FFZ1FHOHNKYjVQNk1nbGdVeE1WYnhXWTdZNGVORlFMMnp1YVppbTZXVDVOY2JJTG96MjhrVkhVN0ZGMmVqUWZOZ05jUQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014066900008</t>
         </is>
       </c>
     </row>
@@ -4112,22 +4113,22 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>[단독] 美 DNI가 ‘정보공유 제한’ 결정… 李, 정동영·이종석 경질론 선 그어</t>
+          <t>법원, '푸틴 반대' 러시아인 체류연장 불허에 "취소해야"</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>[단독] 美 DNI가 ‘정보공유 제한’ 결정… 李, 정동영·이종석 경질론 선 그어  조선일보국민의힘 “동맹 지키자는게 굴종?…이재명 정부 백해무익 외교”  KBS 뉴스조갑제 “李대통령, 김정은엔 굴종적·美엔 당당하게? 말이 되나”  문화일보한·미 정보 갈등에도 “국익 최우선”… 이 대통...</t>
+          <t>(인천=연합뉴스) 김상연 기자 = 국내에서 러시아·우크라이나 전쟁 반대 시위에 수백회 참여한 러시아인에게 난민인정 신청 결과가 나올 때까지 임시...</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxORUxjVnJDQjk3WU9KdllpN3hRcnRSUWNGUDlKc1NQSlZtaHBVWVlGTW1zQ1ROQUJzal9kS1ZJUFF0eGhzS0xEQVZETXpGN1pNTTVxUEtyRlFrYkxLV1MtQ3QtY1Vld0pJbGQ0SWtvMkdCWWYxX0hJNkNmdEhYTURDRDhyaktRSjJGZTJOMUpobkg?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014065900065</t>
         </is>
       </c>
     </row>
@@ -4139,32 +4140,32 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>민간건물 임차 27곳 내년 이전…‘행정수도 세종’ 2031년 완성</t>
+          <t>산업부, 2030년까지 국가·지역 대표 전시회 5개 이상 육성</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>민간건물 임차 27곳 내년 이전…‘행정수도 세종’ 2031년 완성  한겨레안철수, 외교·통일·국방부 ‘세종 이전’ 발표에 “북한에 수도 헌납할건가”  경향신문[전국 주요 신문 톱뉴스](14일 조간)  연합뉴스금융위·법무부 등 44개 기관 9929명, 내년부터 세종 본격 이전  정책브리핑...</t>
+          <t>산업부, 2030년까지 국가·지역 대표 전시회 5개 이상 육성  KBS 뉴스Google 뉴스에서 헤드라인 및 의견 더보기</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5nRVl0ZVdQRld3OGtSZFp3WmdOZWFmRk1HWkNFZTMtVDJvYWRfQURGNUFLRUFYRVFtVC1wU1VJSGZrR01sMXBsZ2g1eTQ5aldSY0xydHhiUHl3dmpqOTJPLTN2Wl9CdzdLTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE0wbFFDM0djVl8tRTVjVUhwS0dfdjFGWkZYVURJNTZnaUZIeEVNdzUtMWZYRTY0VTFSYXMwdk9RVVVOR2FLMTFpSlQ2ZE1xRzFxa2pMdnBfT0pHa3M?oc=5</t>
         </is>
       </c>
     </row>
@@ -4176,32 +4177,32 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>혼인무효 소송 중 장모 살해·아내 납치한 20대 남성 구속영장심사</t>
+          <t>필라델피아 반도체 지수 5일 연속 하락...7월 말 이후 처음</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>혼인무효 소송 중 장모 살해·아내 납치한 20대 남성 구속영장심사  MBC 뉴스[단독] 장모 살해범, 이미 ‘수차례 전과’…상습범의 계획범죄 정황  JTBC[단독] “경찰 신고 전에 뭐라 했어”…송파 ‘장모 살해범’ 보복 범죄 정황  KBS 뉴스장모 살해 20대, 가족 신변 볼모로 아내...</t>
+          <t>필라델피아 반도체 지수 5일 연속 하락...7월 말 이후 처음  YTN메모리, 제2 소프트웨어?…"내년 정말 힘들 것" PTJ의 경고 [김현석의 월스트리트나우]  한국경제반도체 손실로 월가 하락 후 미국 증시 선물 보합세…CPI 발표 대기  Investing.com 한국어中 반도체 추격...</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JM3lPYzJGVjJJclh2cUx3cFdzby1sOHF1Q1ktQnIyWkVRVmRPcWdhOEhMTHNUYTNpSDNMWUwyR2NZRnRRc19OMDVHMG1rS2NEYUkzTndob3JxZHk4Wk5FUFp6LTA5Sy1SZzE4UFpvX0ZLWG9sWlRJ0gF3QVVfeXFMTVMwZVl2TXltUlZXd2dwUzVaRXlpOVJuUnlYMHlQLXk5NTBQb2oyNG9PR0xQb1djRGJnd1dtbzQ3ZlJvWmdwVnoxSEhrbmdhVUFxYV9ZcmdoUENGOUtINTBUVXlVcmVEXzY5aXkzVzVZYkNZTDd4c00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFByT3A4M2N1UEF1c211Rll3UHdCX2F6ZkttQ3YwY0U3OTlJSE00ZDlwR1Y2X1dRT09zakFLRnd6TEs0RlBCcVhUSURyNF9BLVBHeld6bERydDZUQmxLY1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -4213,32 +4214,32 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>추미애 “관사 계약, 사치라 보기 어려워”···이재명 대통령 SNS글엔 “저라고 생각 안 해”</t>
+          <t>삼성전자 '100조 잭팟' 뒤 서늘한 경고…"한국이 흔들린다" [테크로그]</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>추미애 “관사 계약, 사치라 보기 어려워”···이재명 대통령 SNS글엔 “저라고 생각 안 해”  경향신문경기도 아닌 ‘추미애 국정감사’?…여야, ‘예산 삭감’·‘SNS 정치’ 질타  KBS 뉴스"일방독주" "여의도지사" 與도 野도 秋 난타  조선일보秋국감서 與공세성 질의에 '내분 분수령...</t>
+          <t>삼성전자 '100조 잭팟' 뒤 서늘한 경고…"한국이 흔들린다" [테크로그]  한국경제100조원 벌었지만 증가율은 반토막…외국인 올들어 232조원 ‘엑소더스’  한국경제삼성전자·SK하이닉스, 두번째 바닥 찍었나…“W자 반등 기대”  마켓인거침없는 외인 매도...반도체 역대급 실적에도 급락...</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1ZMXNSbkp5MlNtcXZuQ3R4TjBqek1vQ0NYa1IyRDFKaTBrdXZpZE9SSWVycGVsNHlkRVZCcnpVV2RfZEgxaWdYQV92d05Ja0pUbk04eDlhOGhDd9IBX0FVX3lxTE9lTmFkSV9mNWpFX210TXBZelIzOXU3NF9zQ0w3T25rcjFUbzRBTFhtelpGQlR0QUpCcm9WYW9EaVpxbG9CaUNhZkxEOGdhbzBOS24zMXZ3WGJwdGZnZURZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE0ybTlfNDRfSnlTM3l0VzBjYm5QNmpPeW9wLWJ6UGE1dTF2ZEd3Nll1LTA4dW0wVFlneHNqaWlMTzFDY21VbEF3eDluN2FVSXAyR0FQcVRuVm1kUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4250,32 +4251,32 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>뇌동맥류 수술 후 사망…법원 "대안 치료 설명 의무 위반"</t>
+          <t>새마을금고·OK저축은행도 고객 정보 유출…금융당국에 신고</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>(부산=연합뉴스) 차근호 기자 = 별다른 증상이 없던 환자가 비파열성 뇌동맥류 수술을 받은 뒤 뇌출혈로 숨진 사건에서 의료진의 수술상 과실은 인...</t>
+          <t>새마을금고·OK저축은행도 고객 정보 유출…금융당국에 신고  조선일보새마을금고 400명대 개인정보 유출... 계좌정보도 포함  보안뉴스금융당국, 해킹 2금융권 확산에 긴급 점검  전자신문OK저축은행, 대출신청 페이지에서 정보 유출… 고객 183명 정보 유출 - 조선비즈  Chosunbiz...</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014049500051</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNdUg3TWo4c01LMHZnOXFZOFdfZDRXRWpuMld3TlRzTXBNdjdvQTJyUFZmcGRfOGJCc3dnRFZQbW9pLVYtWDNPSXFDQkR0dTR3ZnVud0NlbjhhYWVhTnpvYm85SUNncUJvYzVqY0FRRlVrU2pvQnhSaDJ6aGFWM0s1bUJwaFdrd3dvQzQw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4288,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4297,12 +4298,12 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>강북구, 고령자 운전면허 반납지원 확대…차 없애면 20만원 추가</t>
+          <t>횡성군, 임도 사면 녹화 기술 도입…식생 정착·시공 품질 향상</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 정준영 기자 = 서울 강북구(구청장 정창수)는 고령운전자의 교통사고를 예방하고자 오는 15일부터 '고령운전자 운전면허 자진반납...</t>
+          <t>(횡성=연합뉴스) 류호준 기자 = 강원 횡성군은 횡성군산림조합, 구루이엔티와 임도 사면 녹화 기술의 현장 적용과 기술 협력을 위한 업무협약(MO...</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4312,7 +4313,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014054900004</t>
+          <t>https://www.yna.co.kr/view/AKR20261014068000062</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4325,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4334,12 +4335,12 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>광주 온 도시철도 2호선 전동차…내년부터 시운전</t>
+          <t>충남도, 올해 마지막 '동네창업학교' 교육생 100명 모집</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>(전남광주=연합뉴스) 장덕종 기자 = 광주도시철도 2호선 1단계(시청∼월드컵경기장∼백운광장∼조선대∼광주역)를 달릴 전동차가 14일 첫 입고돼 본...</t>
+          <t>(홍성=연합뉴스) 김준범 기자 = 충남도는 청년 예비·초기 창업자를 대상으로 올해 마지막 '동네창업학교' 교육생 100명을 모집한다고 14일 밝...</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4349,7 +4350,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014044500054</t>
+          <t>https://www.yna.co.kr/view/AKR20261014068300063</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4362,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4371,12 +4372,12 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>저소득층 '실명 예방' 공로…강동구, 보건복지부장관 표창</t>
+          <t>공공수주 반등에도 민간 부진…8월 건설수주 8% 감소</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김준태 기자 = 강동구는 지난 8일 송파여성문화회관에서 열린 '제56회 눈의 날 기념식'에서 보건복지부장관 표창을 받았다고 1...</t>
+          <t>(세종=연합뉴스) 오진송 기자 = 올해 8월 국내 건설수주가 공공 부문의 반등에도 민간 부진이 이어지면서 3개월 연속 감소한 것으로 나타났다.</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4386,7 +4387,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014048800004</t>
+          <t>https://www.yna.co.kr/view/AKR20261014059000003</t>
         </is>
       </c>
     </row>
@@ -4398,32 +4399,32 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>음성 사정리 동학군·항일의병 추정 묘소 보존·활용 방향은</t>
+          <t>레오 14세 교황, 폐암 진단…오른쪽 폐 일부 절제 수술</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>(음성=연합뉴스) 박재천 기자 = 충북 음성군은 충북역사문화연구원과 함께 오는 16일 오전 10시 30분 음성생활문화센터에서 사정리 동학군(항일...</t>
+          <t>레오 14세 교황, 폐암 진단…오른쪽 폐 일부 절제 수술  한국경제71살 교황 레오 14세 폐암 진단…“오른쪽 폐 일부 절제”  한겨레레오 14세 교황, 폐 결절 아닌 폐암…오른쪽 폐 일부 절제 수술  동아일보교황청 "레오 14세, 폐 결절 수술 성공적 완료"…남미순방 갈듯  마켓인교황...</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014053100064</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE52ak40R0pZMTk1NVRHM3lZNGNsYnFsYW1Ud2RGbXYzRzJZbUZFRjlxb2V2ZGVVRm5MaVFLOW5HZmM2eE5iSTcyLVowc2cydUc5WS1XRG9uVU53dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4436,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4445,12 +4446,12 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>[바이오스냅] 셀트리온, 미국 처방집 추가 등재 추진</t>
+          <t>美검찰, '韓 정부 대리' 혐의 수미 테리 '기소유예 합의'</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 박상현 기자 = 셀트리온[068270]이 미국에서 대형 처방약급여관리업체(PBM) 처방집 추가 등재를 추진하며 매출 확대를 모...</t>
+          <t>(서울=연합뉴스) 임화섭 기자 = 한국 정부를 위해 비밀리에 활동하고 고가 선물을 수수했다는 혐의를 받아온 전직 미국 중앙정보국(CIA) 분석가...</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4460,7 +4461,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014055200017</t>
+          <t>https://www.yna.co.kr/view/AKR20261014067100009</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4473,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4482,12 +4483,12 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>서울대 80주년 유홍림총장 "왜 대학이어야 하는가 다시 물어야"</t>
+          <t>해양진흥공사, 지속가능경영보고서 최고 등급</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 윤민혁 기자 = 유홍림 서울대 총장은 14일 제80주년 개교기념사에서 대학의 위상과 의미가 근본적으로 도전받고 있다며 "왜 대...</t>
+          <t>(부산=연합뉴스) 박창수 기자 = 한국해양진흥공사는 지난 5월 발간한 '2025 지속가능경영보고서'가 미국 커뮤니케이션연맹(LACP)이 주관하는...</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4497,7 +4498,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014048000004</t>
+          <t>https://www.yna.co.kr/view/AKR20261014067400051</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4510,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4519,12 +4520,12 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>[게시판] 소진공, 대전 종합사회복지관 등에 '로컬푸드 꾸러미' 전달</t>
+          <t>1∼8월 배터리 분리막 적재량 25%↑…중국 제외 41% 성장</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>▲ 소상공인시장진흥공단은 지역 농가의 소득 증대와 지역경제 활성화를 돕고자 대전 유성구 종합사회복지관과 그냥드림센터에 '로컬푸드 꾸러미'를 전달...</t>
+          <t>(서울=연합뉴스) 김민지 기자 = 올해 1∼8월 글로벌 전기차용 배터리 분리막 적재량이 배터리 탑재량 증가와 중국 제외 시장의 빠른 성장에 힘입...</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4534,7 +4535,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014022600030</t>
+          <t>https://www.yna.co.kr/view/AKR20261014062600003</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4547,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4556,12 +4557,12 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>[부고] 홍성권(강원대학교병원 외과 과장)씨 부친상</t>
+          <t>음성군, '전통시장·상점가 활성화 유공' 중기부 장관상 수상</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>▲ 홍홍표(향년 86세)씨 별세, 홍성권(강원대학교병원 외과 과장)씨 부친상 = 14일 오전, 강원대학교병원장례식장 2호실, 발인 16일 오전 ...</t>
+          <t>(음성=연합뉴스) 박재천 기자 = 충북 음성군은 중소벤처기업부의 '2026년 전통시장 및 상점가 활성화 유공' 평가에서 우수 지방자치단체로 선정...</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -4571,2634 +4572,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014051800062</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>속초시, 상반기 사업체·청년 창업기업 증가세… 지역경제 활기</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>(속초=연합뉴스) 류호준 기자 = 강원 속초지역 전체 사업체 수와 청년 창업기업 수가 올해 상반기 매월 증가한 것으로 나타났다.</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014051100062</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>순천향대-국군대전병원, 미래 군 의료 및 과학기술 융합 협약</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>(아산=연합뉴스) 유의주 기자 = 순천향대는 최근 국군대전병원과 '미래 군 의료 및 과학기술 융합을 위한 업무협약'을 맺었다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014051400063</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>다천 김종원, 추사 김정희 '충효가전' 편액 국립창원대에 기증</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>(창원=연합뉴스) 박영민 기자 = 국립창원대학교는 경남도립미술관장을 지낸 서예가 다천 김종원이 추사 김정희(1786∼1856)의 '충효가전'(忠...</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014052700052</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>전자발찌 차고 또 흉기난동…이상동기범죄자 80% '전과 있음'</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 한지은 기자 = 인천에서 전자발찌를 착용한 출소자가 불특정 다수를 상대로 흉기를 휘두르면서 고위험 범죄자의 재범을 막기 위한 ...</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014042000004</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>'8명 부상' 인천 흉기난동 사건에 프로파일러 3명 투입</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>(인천=연합뉴스) 홍현기 기자 = 인천 대형 상업시설에서 흉기를 휘둘러 8명을 다치게 한 50대 남성을 상대로 경찰이 범행 동기를 밝히기 위해 ...</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014050800065</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>농민 매년 300명 사망에도…농진청, 안전장비 보급사업 중단</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>(전주=연합뉴스) 김진방 기자 = 농업인의 재해율이 전체 산업 대비 8배를 웃도는 상황에서 농촌진흥청이 'IoT 농기계 교통안전 및 사고 감지 ...</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014048200055</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여  문화일보이재용, 장외매수로 삼성전자 766만주 매수…1.9조 규모  연합인포맥스홍라희 관장, 이재용 회장에 삼성전자 지분 2.6조 증여  조선일보홍라희, 이재용에 삼성전자 주식 1천115만주 증여…이재용 지분율 1....</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>문화일보</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBGRllSNUNuOTVwTGl2OXM5a1RKazk3NnRwR2I2Z1ZqOTdveWpNZHYtLUZpVlZTOFlWS2FMNnNYLWpZbkFjTkM3RGNhY0I1UHgy?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>[은행이 뚫린다-진단③] 보안업계 제안은? “IP 차단은 임시... 자산식별·행위분석·접점 숨기기 필요”</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>[은행이 뚫린다-진단③] 보안업계 제안은? “IP 차단은 임시... 자산식별·행위분석·접점 숨기기 필요”  보안뉴스[금융현미경]AI·해킹 위협에 금융권 내부통제 경고등…커지는 '임원 책임' 강화론  아시아경제[단독]망분리 완화 금융사 10곳, 보안계획만 세우고 이행 안해···내부망 해킹...</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>보안뉴스</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9ESmY2WkEzNVVwVGNGWm9GZjhVUVpRMXp4UWlWMDhwY0ZxTHJ6VllQUXpiOXFEUUtqbFdERk9ERDNzYUt4UklRelNWWEk3TGNFZ2szZDFxb2F0ODlzYm0tT05aVzBLbVdHZGVz?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>반도체, 이익 전망 대비 과도한 하락…"분할매수 대응“</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>반도체, 이익 전망 대비 과도한 하락…"분할매수 대응“  비즈워치“이젠 반도체 미련 버려야?”...내년 증시 주도주 바뀌나  매일경제반도체주 반등 언제쯤…“소부장이 투자 대안”  마켓인메모리 호황인데 '삼전닉스' 왜 떨어지나…"공급 과잉 우려·환율이 발목"  뉴시스반도체 미련 버릴까요?...</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>비즈워치</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE8zZUN5TmF3dXFaQktYdkxDdlV6SUFTRndrcnVFZG1PcW92SUhkMzZpa3BLRDVZTFdHNzFRbDNfSWFjbEdUNnhZb2V0Zld6QmI0c3JjNzNPVWZCMXNpc2lpZTg3Y3BPSVRjTFE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>삼성·LG, 일상·산업 속 AI 기술 한눈에…’KES 2026’ 개최</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>삼성·LG, 일상·산업 속 AI 기술 한눈에…’KES 2026’ 개최  연합뉴스TVKTC, 한국전자전서 AI·소프트웨어·스마트가전 역량 선보여  전기신문산업부, 2030년까지 국가·지역 대표 전시회 5개 이상 육성  연합뉴스허공 위 버튼에 로봇손 학습까지...한국판 CES 개막  YTN...</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스TV</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBfbWtIOGxCdFNuNW9Eb1lhaG9uMVlRNmVxRHJSSE1zTUlwdFY1bV9ORmI2NFkxcVhFSWlRZGwwSm11RVNzZGJKYkRWNm5kTFVnMGJCY0J1MEtwcmhaekp6NUQ4eWZrdU0?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>NDF, 1,341.90/ 1,342.30원…2.05원↓</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>NDF, 1,341.90/ 1,342.30원…2.05원↓  연합인포맥스중동발 유가상승·증시 급락에…환율 10원 오른 1,345.1원  연합뉴스반도체 호황에 ‘센’ 원화…1200이냐, 다시 1400이냐  경향신문원·달러 환율, 1340원대 초반 등락  뉴시스외인 증시 순매수 전환에…달러·...</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>연합인포맥스</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5HaGJxTHJkaTFEM1JDS09WTkNEX1ZMLUNuZEpYQ0Vjb0VhN1ZDb1FZeGo2S1hXM08yZDh6RTFqQUVxek9sVXNXUElXQnMwbGg0eGkyMDhOSmVFYUdjSDdjOGQxS0dycEJjYm8xXzZLaHXSAXRBVV95cUxQNjVRWjlpWDJNa1RiZVljNW5mOTQ4QjhmT1JkdXlfRU4tUEJEOE9XUTlTX1JGbmhBTFRRb1FtVUdnVVdHeTBpQ1ljNkRfRTBqQ19falEyN0thbmZiNHNtaTlab0JtREJnZHU0Wk5UdnBUVldzeQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>中 차세대 D램, 삼전닉스 주도판 흔든다?…"기술격차 3년" 업계 선긋기 - 머니투데이</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>中 차세대 D램, 삼전닉스 주도판 흔든다?…"기술격차 3년" 업계 선긋기 - 머니투데이  머니투데이삼성證 "中 CXMT 리스크, 더 반영할 이유 없어…반도체 소부장 주목"  뉴시스창신메모리, 사실이면 "삼전닉스보다 빠르다"…긴장  JTBC애널리스트, 중국 CXMT의 주장이 마이크론 테크...</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>머니투데이</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBGZE5NWFB1MmgwZjZ2YWdqYl9XamNORTBzS2Zxb3ZwdHhqWWJRc0U2a2t5ZlE2VUFDT1l5YUxLTEQ0Z05kMXk0ODZ6OUxUTTlyMWxOWVpoQWpmVWwwUUI4akYzMDdzZDVY0gFuQVVfeXFMTkc5Rnc2ek9rNy00amdwbFBaZDU1blI1ODBoclpMUzVOQy0xTWlscENENUhJUjVJbU93UzV0UzNoMk11dm1WaTZuRzBkN1FVRHlELThlWkVJVUU0enFxQldEUnI3WkEtNmZTdTR6dGc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>한화생명, '필요할 때 쓰는 종신보험' 출시</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 강수련 기자 = 한화생명[088350]은 14일 보장이 필요할 때는 사망보험금을, 생애 자금이 필요할 때는 납입보험료 전액을 ...</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014053900002</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>[게시판] CJ프레시웨이, 상생협력 아카데미 개최</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>▲ CJ프레시웨이[051500]는 지난 13일 서울 마포구 본사에서 중소식품 협력사의 식품안전 역량 강화를 위한 프로그램 '상생협력 아카데미'를...</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014026300030</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>카카오, 인적분할 앞두고 CEO 총출동…새 성장전략 공개</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 한상용 기자 = 카카오[035720]는 인적분할을 앞두고 증권사 애널리스트 등을 대상으로 주요 계열사 최고경영자(CEO)들이 ...</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014055100017</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>[보령소식] 종합체육관서 20일 취·창업 박람회</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>(보령=연합뉴스) ▲ 종합체육관서 20일 취·창업 박람회 = 충남 보령시는 아주자동차대학교와 함께 오는 20일 오후 1시 30분부터 보령종합체육...</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014050500063</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>카카오페이, 마이데이터 기반 '멤버십 사후 적립' 출시</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 오지은 기자 = 카카오페이[377300]가 마이데이터를 활용해 결제 당시 놓친 멤버십 포인트를 나중에 적립할 수 있는 서비스를...</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014043700017</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>hy "자체 개발 유산균, 알코올성 간손상 완화"…국제학술지 게재</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 한주홍 기자 = hy는 자체 개발한 프로바이오틱스 균주 'HY7804'의 알코올성 간손상 완화 가능성을 확인한 연구 논문이 국...</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014044100030</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>카이아, 490만개 KAIA 소각…JPYC도 기여보상 대상</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 유동현 기자 = 카이아 DLT 재단이 자체 블록체인 네트워크의 토큰인 카이아(KAIA) 490만개를 소각한다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014051200002</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>[게시판] 토스증권, 앱에 '시장' 탭 신설…AI시황 요약 제공</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>▲ 토스증권은 앱 내 '시장' 탭을 새롭게 도입했다고 14일 밝혔다. 이 탭에서는 주요 국내외 지수와 수급 등을 확인할 수 있다. 특히 'AI(...</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014049900008</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>KB국민은행, 기업고객용 'KB B2B우대통장' 출시</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 한지훈 기자 = KB국민은행은 14일 기업 전용 파킹통장 'KB B2B우대통장'을 출시했다.</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014051700002</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>[게시판] LS증권, 국내 선물·옵션 수수료 할인 이벤트</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>▲ LS증권[078020]은 국내 선물·옵션 신규 및 휴면 고객을 대상으로 거래 수수료를 할인해주는 이벤트를 12월 31일까지 진행한다고 14일...</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014050100008</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>메리츠증권, 캔톤 재단과 금융자산 토큰화 협약체결</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김유아 기자 = 메리츠증권은 캔톤 네트워크(Canton Network) 운영 재단인 캔톤 재단(CantonFoundation)...</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014050900008</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>코람코라이프인프라리츠, 전국 주유소 19곳 매각 추진</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 정회인 기자 = 코람코자산신탁이 운용하는 코람코라이프인프라리츠가 포트폴리오 재편과 신규 성장자산 투자를 위해 전국 주유소 19...</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014049700008</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>관세청 "최근 5년 국회 반복지적 전면 점검…8건 개선 완료"</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>(세종=연합뉴스) 안채원 기자 = 관세청은 최근 5년간 국정감사에서 반복적으로 지적돼온 사항을 전면 점검해 총 8건의 개선 조치를 완료했다고 1...</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014047700002</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>LH, 공동주택 중대하자 4년새 90% 감소…"품질관리 강화"</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 오예진 기자 = 한국토지주택공사(LH)는 공동주택 품질 개선에 노력한 결과 올해 균열, 누수 등 중대하자 발생 건수가 크게 감...</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014047500003</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>섬박람회 논란 큰데 이번엔 K컬처 전시회?…117억 투입 지역행사 키운다</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>2030년까지 전시회 5개 이상 육성 첨단 제조산업·K-컬처 등 연계 계획 기존 전시장들 낮은 가동률은 문제정부가 2030년까지 국가·지역 대표 전시회를 5개 이상 육성하고 관련 ..</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12175201</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>교황 레오 14세 폐암 진단…“오른쪽 폐 일부 절제”</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>교황 레오 14세 폐암 진단…“오른쪽 폐 일부 절제”  한겨레교황청 "레오 14세, 폐 결절 수술 성공적 완료"…남미순방 갈듯  마켓인교황, 폐 결절 제거술 위해 로마 병원에 입원  연합뉴스바티칸 "교황 레오 14세 폐암 진단…수술 성공적" - 머니투데이  머니투데이[속보]교황 레오16...</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>한겨레</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNSFNnUnVzUU4taDNoM1NEcmU5YlpXaVozdzFjT3N5UENKS2hTU3o4LW1hN0FtUzNYNDJ6WDBxVS0ydGFxSHJZUTd2LWpzbFFaZDNRMGM2X3hzRm5STUxLcmlHR2Y2M1FTQlBIa1AxbFRZazJpS0dmdHBEQWlyT0doM1h3?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>여객기 납치경보에 교신까지 끊겨 독일 발칵…알고보니 시스템 오류</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>여객기 납치경보에 교신까지 끊겨 독일 발칵…알고보니 시스템 오류  연합뉴스TV“드론 추정 물체 목격, 항공 비상 상황”···독일 뉘른베르크 공항, 항공기 운항 중단  경향신문독일행 여객기 납치경보 잘못 보내 전투기 출격 소동  MBC 뉴스'7500' 여객기 하이재킹 오경보에 獨전투기 2...</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스TV</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE81QWVvWkFRaTBZYmdkb25GbnZyOWFoR2tCUzNhMWxoVHpsUkR6dzFnRm9ZSmZBemxLQW5ZNExNVnRqaWxjbWx4bldiamd6WmlXM0NrS3ZKd29mXy1zdW5tOG5JNVJnU1k?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 "우크라이나와 정보 공유 중단 안 해…푸틴, 종전 더 원해"(종합)</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 "우크라이나와 정보 공유 중단 안 해…푸틴, 종전 더 원해"(종합)  뉴스1‘경유 딜’ 우크라 반발에… “美, 종전 협상단 방러 보류”  동아일보트럼프 ‘에너지 휴전’ 후폭풍 속 침묵하는 푸틴…왜?  경향신문공화·민주 상원의원 12명 "러시아 경유 합의는 적국에 주는 선물"  뉴...</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>뉴스1</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCYmM0WHNQd01tM3A3MThrZ3FEbVBySlQ0OFVKZVVsSjg2SmVCYndZRXBLWGVOX201Ukhjd3ZwSzNJQnBGVVJITWRVdVRmYWFFdEdOMllZRHk?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>美 정보공유 안했나?…러 미사일, 공습경보 발령 전 키이우 타격</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>美 정보공유 안했나?…러 미사일, 공습경보 발령 전 키이우 타격  뉴스1우크라 드론이 러시아 데이터센터 때리자 중앙아시아 앱 '멈춤'  연합뉴스러 미사일 공격으로 부상한 여성 옮기는 구조대  뉴시스러 데이터센터 피격에 카자흐 주요 플랫폼 마비…디지털 인프라 의존 한계  아시아투데이[포착...</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>뉴스1</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFA5cFVCdDlfQ1VyOFp0ZEpsRVh1MUxrVnM4SFlvYVl1WE5SRVJWWC14VXNQWXo2VnplQVk1ZFhqanNlcnd0NjQ1bklEV3RsV0FieEsw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임  경향신문"가족은 아니었다"…트럼프, '아들 전 약혼녀' 그리스 대사 해임  마켓인백악관, '각종 비위 의혹' 그리스 대사에 "사퇴 요구했다"  연합뉴스트럼프와 측근 인사 부패 의혹, 미 중간선거 쟁점 부상  뉴시스"억대 빚...</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>경향신문</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBsanNzT0RJMzI1SGI4b3ByWUJPUXRzdEgzTGtkZl90Wmo5dUhrSE53MmFpbDBuQmdEcXNUVy1vV1dFSGlQMG5EdVFfQmhTZHVOcG1taUVubS0yd9IBX0FVX3lxTE5nUV8yQUZXOUZ2SV9JeUpLa2lzc0t5QXlOREoyYmh6STFLX0VKd2hJTTg2WnllWTBRQ1JTdlZDbFVpT2VXa2k1MGE2N05qQjI5R1J0WTZZZmMweEJySnRz?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>신압록강대교 북한 쪽 관문에 인공기·오성홍기 내걸려‥개통 임박 정황</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>신압록강대교 북한 쪽 관문에 인공기·오성홍기 내걸려‥개통 임박 정황  MBC 뉴스北中신압록강대교 개통 임박했나…북측 관문 북중 대형국기 포착  연합뉴스[특파원리포트] 두 개의 다리와 북한의 몸값  세계일보북한 남포항 컨테이너 단지를 촬영한 위성사진. 올해 10월 7일 촬영된 위성사진에서...</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>MBC 뉴스</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1tYXFLZnE3VmpmekdBZnpWM2FfalNNejBfT2oxMTVYRUR5cEY4WFMtamE0X1pscGNvZ0x3VjRiN2JtbFEtTEFRbXdlR25xczVZemMwUHZqbVNZTzJMdzhBRWtKX1NSU1BjWUJVUzZqSHlSS2dx0gF0QVVfeXFMTjdRbDZnbU5wdFBtMVJQY1RMZjRwRS1JQjdmQVRNR2lDUFNPQzlZVEhEWURZb25wWGptQXNMR1lrT0czSmMxc1lEakhHNVVqYjJkdkM3OVFPUUQwU01lNUEzNk1EZUpZVkZhV3dJYkIzbDFRWmU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>"호르무즈 선박 피격 2주간 24건…이란전 이후 최다"</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>"호르무즈 선박 피격 2주간 24건…이란전 이후 최다"  연합뉴스TV"호르무즈 선박 피격 2주간 24건…개전 이후 최다"  연합뉴스이란군 “호르무즈 동부 선박 주시…금지 구역서 유조선 화재”  KBS 뉴스호르무즈 유조선 연쇄 공격… '중동 원유' 수출 회복세 또 꺾이나  마켓인호르무즈 ...</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스TV</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE80R1Ezc0hlaWJRSUNQUk1XWmNDU1JDYVNSOWxwWm1JY0lTblpSZ055YXNwWmhKcDJSN3VMUk9HcTk2dnluSkpkX1lLSXRYWTJhSmRXV2RCVGxlY1dva3NwRlBOa2hkMms?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>PAK DA 지연에 Kh-BD 부상…러시아 공중 핵억지력의 불확실성</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>PAK DA 지연에 Kh-BD 부상…러시아 공중 핵억지력의 불확실성  Meta-Defense</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>Meta-Defense</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQbEEyUy02aDN4OG5KVVdhSUl2TkZzck83eVhHRFB2eHZqMEY0U21BemgtS3VKNDBZOHlmWHN2MTg1M2xsMWF1RENwNl9kbkJGUEx2V1dRcUMxLTRNSXBBUVY2UU1oYk01RWE0Vk94emxHQ3VWVzg4U1N3ZGVVeFFQRlJqY0ptR2Ez?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>다급한 룰라, '소상공인 부채탕감' 대선 결선용 선심법안</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>다급한 룰라, '소상공인 부채탕감' 대선 결선용 선심법안  연합뉴스[브라질증시] 이보베스파 1.04% 하락…룰라·플라비우 지지율 격차 주시  뉴스핌트럼프 ‘블루 타이드’ 마지막 퍼즐 완성하나…‘보우소나루 정치 왕조’ 계승자 [더 비저너리-플라비우 보우소나루]  헤럴드경제브라질 대법원, ...</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1QYjRyYU1pSUdDc2x4SVotMktwUTRfSk5XTEFIanI1UzVGWHdKeVZlWnpfQThvV3BNbTJ0X2t2SjBUa21UUnVaR0NDVWJGV2QyNlM4ZVM4TlBoY0nSAWBBVV95cUxOaTNpZ0FuR0plZ0k4ZE5GLTBlS2NaTjR2Vkp5M2Y3NExOZ0hoUmJ6cmQ1ZGZTc2l6bHNtbVh2dkZ2QjRZUENiVUlUM1NuQWp1bU9HTUQ3OV95UTJpRnRkcEE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>"오픈AI, 사이버보안업체 '트레일오브비츠' 인수 추진"</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이성한 기자 = 오픈AI가 사이버보안 업체인 '트레일 오브 비츠'를 인수하기 위한 협상을 진행하고 있다고 미국 IT전문매체 디...</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014042500009</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>앤트로픽, 14일 공식 재무상황 공개</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 주종국 기자 = 기업공개(IPO)를 준비 중인 인공지능(AI) 모델 개발 기업 앤트로픽이 14일(이하 현지시간) 기관투자가들과...</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014050400009</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>국방비 연 112조원 쓰고도 난타당하는 사우디…"지킬 게 많다"</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 임화섭 기자 = 사우디아라비아는 막대한 국방비 지출이 무색하게도 최근 예멘 후티 반군이 쏘는 미사일과 드론에 공항, 정유소, ...</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014046300009</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>다저스 감독 "오타니 3차전도 출전"…선발 제외 가능성 일축(종합)</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 천병혁 기자 = 미국프로야구 메이저리그(MLB) 로스앤젤레스 다저스가 간판스타 오타니 쇼헤이(32)에 대한 신뢰를 재확인했다.</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014019651007</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>베트남에 'K-문화유산 보존법' 전한다…22일까지 현지 교육</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김예나 기자 = 한국의 문화유산 보존과학 전문가들이 베트남 현지에서 문화유산 보존·관리 노하우를 전한다.</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014042800005</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>세레브라스 CEO "데이터센터 반발은 공포 마케팅 탓"</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>(샌프란시스코=연합뉴스) 권영전 특파원 = 엔비디아 대항마로 꼽히는 인공지능(AI) 칩 개발사 세레브라스의 앤드루 펠드먼 최고경영자(CEO)는 ...</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014022500091</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>NASA 화성 로버, 45.22㎞ 주행 신기록…마라톤 풀코스보다 더 달려 [여기는 화성]</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>NASA 화성 로버, 45.22㎞ 주행 신기록…마라톤 풀코스보다 더 달려 [여기는 화성]  지디넷코리아화성에서 45.2km…퍼시비런스, 지구 밖 천체 주행 신기록  한겨레NASA 화성탐사 로버 퍼서비어런스, 지구밖 최장 주행  연합뉴스화성서 45.2㎞ 달린 퍼서비어런스… 지구 밖 로버 ...</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>지디넷코리아</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1sV0ZxS09JU05rdnJhclRvVlFwbFR6X1p1ZWQ1WnFxSFdic1VzZXdubHhGVmhyVHpEaEhQNk1oQWsxbWQ3cXQ0akp1cldsR3A3RWR4TEdR?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>XBOX, AI 에이전트와 게임 디컴파일을 탐구하는 XBOX LABS 출범</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>XBOX, AI 에이전트와 게임 디컴파일을 탐구하는 XBOX LABS 출범  Unite.AI엑스박스, 신기술 실험조직 ‘엑스박스 랩스’ 출범  지디넷코리아게임 넘어 디즈니처럼… MS, 엑스박스 엔터 사업부 ‘XP’ 신설  IT조선Xbox, 영화, TV, 라이브 이벤트 및 소비재를 전담하...</t>
-        </is>
-      </c>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t>Unite.AI</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPV1A1WUZhSVlvQnZxSlNLeG1xZFFROHVKVzc5YkJxTFVnVnR4Q0x4TS1GdXJ0QUEtOW54Ym1JaWVfVmlUZTNoWlZWVlp5SEhfaXo1cGpwbW1ESHhoUXhLLWJubXZRbW1KX1FnZnlWa190Y1padmc3bG04NGxYenp4dHFKUEFGbi1JVHRlaTdhTEJZWFlhMmc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>[이슈] 컬렉터스 에디션인데 게임이 없다?</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>[이슈] 컬렉터스 에디션인데 게임이 없다?  인벤</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>인벤</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1WV3lvcVpSZTVFQ0lzNTZob1RNYVFmNUwwMGFVSHFnSWRQZndnNlhCdDF0T1cwSm5xbG9MUnl1dUVPelVNa1NrVThZcFRhWWxMQmVWd043NlhnU2JZRmc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>메트로 2039 예약 판매가 시작되었으며, 동시에 컬렉터스 에디션 출시 소식도 발표되었습니다.</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>메트로 2039 예약 판매가 시작되었으며, 동시에 컬렉터스 에디션 출시 소식도 발표되었습니다.  GameGPU</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>GameGPU</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPTXZTOVBsSVAyaXBaOW1DdmktV285RVpQbDlveGs3NUVnNkFDMlBVWFBSQXg0UWhBNjJuTG1HWjZkRmgteDk4aGtwYVdIUHNObFRyUGRabnUxY0F5RXgxOTMzN1FrNTU4Y3IzS0NjVXJPSFROY1MwUk1HSEtTekFRZk9GTHJOY2dNTUY1bFRaWnlEMm03NUE0SjNCbG1YdS0tajI1QUJFXzkyR2s?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>독성 약품 투입량 5분의 1로 낮춰···'청정 원전 해체' 가능성</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>독성 약품 투입량 5분의 1로 낮춰···'청정 원전 해체' 가능성  이데일리</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>이데일리</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNGxxUG1PSF8taVVIQXp0bGJteS1Ga3NkdkdmOGRqbEpBbGxaSDYzMTJDZUxPRjcyNTRvUzdiSWRBSlJaOFZPYTVkS3pZMEVrQTN5ZVlRYjF1NDdxTElsU1c0SG0xRnlJTU01SEhtRS1NYWZva0dWYVZWVlhWZ2c0bw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>“죽으면 전 재산 증발”…요즘 세상보다 더 살벌한 생존 게임 ‘빌로우 더 스톤’ 11/17 정식 출시</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>“죽으면 전 재산 증발”…요즘 세상보다 더 살벌한 생존 게임 ‘빌로우 더 스톤’ 11/17 정식 출시  헝그리앱</t>
-        </is>
-      </c>
-      <c r="F159" s="3" t="inlineStr">
-        <is>
-          <t>헝그리앱</t>
-        </is>
-      </c>
-      <c r="G159" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9xUFY5bFV3Q1hidUJJVy1TajdHbnc5VjVqQzYwaEVUMVBIVUFvN1dvcjhFWkdUZkFvMnY0cFF2djRPcTNCS3BoOEdPWGF0Q0F1LXpnYzZWUXF6cW85RHo5UWxFU2stZklYNkc2WFRPSTJyWGJV?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>파페 산의 한국 식료점, 파리에서 비밀리에 열리는 콜 오브 듀티 팝업을 선보인다</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>파페 산의 한국 식료점, 파리에서 비밀리에 열리는 콜 오브 듀티 팝업을 선보인다  Sortir à Paris콜오브듀티: 모던 워페어4, 캠페인에 이어 'DMZ'도 미리 한다  인벤콜 오브 듀티: 모던 워페어 4의 DMZ 모드에 대해 알아야 할 모든 것  PlayStationDMZ 모드에...</t>
-        </is>
-      </c>
-      <c r="F160" s="3" t="inlineStr">
-        <is>
-          <t>Sortir à Paris</t>
-        </is>
-      </c>
-      <c r="G160" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOS3dMSHNXSGFZaV9uV3d0ZTFLaldzWG9zcW1XRnBwczRpaUladnZWcjNqZU5DeWJwV2lDamtGY1FVek1SQkdnNW03ZVV5ckpOMzZMWFFNRjhtekVKMHRzY3RKNVVZQ1dEZE80cU1SZnUxWFhCUDJQY0FBcEVvY0MxSEM3c01uX25MT1RWR0FiaXNoc0ZPVkVtSHFxWF9Mc2FHU2VrV2RDeWpZeFVOc1NOTmdEeTdMZEItWjFSNXJCNWZuOFdsT3IwQVBIcXFZTkVyWXNCcTE4ZzRPejkzQU02cldhalZnREprSkR4QzlFZE5vRHNKN1E?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>남극 얼음에 탐지기 심어 우주 중성미자 잡았다…할젠 교수 노벨 물리학상 수상</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>남극 얼음에 탐지기 심어 우주 중성미자 잡았다…할젠 교수 노벨 물리학상 수상  교수신문남극 빙하를 거대 망원경으로...'유령 입자'로 노벨상  YTN 사이언스[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상  한국아이닷컴벨기에 13년 만에 또 노벨 물리학상…과학 강소국 저력 과...</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t>교수신문</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE92WF9yMDViT0RjQjNiWHA0c19DVnBPSHRnRGdWbXhJRElzMEZpM05Fdmd2dlJreURYS2V4VGtwMVBhSGozdDZFNkRPMVViMkd5dmxGbXRUNmp5cEg0ZkhkVDlPN3ptclk?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>[리뷰] 채찍으로 날아다니는 화려한 악마성, '캐슬바니아: 벨몬트의 저주'</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>[리뷰] 채찍으로 날아다니는 화려한 악마성, '캐슬바니아: 벨몬트의 저주'  디스이즈게임캐슬바니아신작 '벨몬트의 저주' 10월 15일 출시, 무료 데모 이미 공개  디지털포커스캐슬바니아: 벨몬트의 저주 - 리뷰  IGN Korea18년 만에 정사로 복귀, 캐슬바니아: 벨몬트의 저주  게...</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>디스이즈게임</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45bEhmaWlTVDMxUW1hMjV6RzltOFRHeV9VZTdoc0p6am5JcUJiY1NBaGVmeFYyZEk3WHUydWJRcGlUS0ZpWWk0YlBwclJrcVEzZWJXMg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Mafia Definitive Edition이 10월 22일까지 PlayStation Store에서 85% 할인된 가격으로 판매됩니다.</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>Mafia Definitive Edition이 10월 22일까지 PlayStation Store에서 85% 할인된 가격으로 판매됩니다.  GameGPUMafia III는 현재 고화질 HDR을 지원하며, 향후 DLSS 및 FSR도 지원할 예정입니다.  GameGPU마피아 3가 버그 수정 ...</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>GameGPU</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZUVrXzhrQmRqZE1Ia0RzM2lJaG5MYmdSdVZpQXNkMkNnbE15Vmt5eGw3REFBYlExOGt2em5nMGVUN2Y4dXBwUllnUk9Oa280SGlEYzBSUjRSMjhKMkNHUUFHZERDZDN5My1rbGtNTGotMm90M0tLanhzazYwLW1CaXBQM3JBR0FkQW9DWENNYXdkaWExYzgybTVGdk9HVFZRVTV6Z0NzdkdIM21GdWhVRzN3WQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>새로운 보도에 따르면 소니는 플레이스테이션 6를 세 가지 구성으로 출시할 계획입니다.</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>새로운 보도에 따르면 소니는 플레이스테이션 6를 세 가지 구성으로 출시할 계획입니다.  GameGPU플스5 소니의 잇단 '반 게이머' 정책에 소비자 불만 급증  글로벌EPS5 탈옥 스토어까지...소니 향한 게이머들의 '반란' 왜?  게임플“어차피 사라질 운명” 사이버커넥트2 대표 디스크...</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>GameGPU</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOdWJQZGg0bDQ2RTNsbjlDM0pIZnlFYmZnYnJza21KckdWWHVkZXYzRmhaaFFteHYzWEQwOG9GZ0wyV3QtbHE1ZktCQ29jczF6c1ZPWkJydTBjRE4zLWxRdGRlWi1OUjViajBsb1gzLWhPUVV6ZmR0d2Y2dXlNRnhvQzVjSjdDNmwtTG1UU0NDcmp6LVBPMzV4djBEVFRsSmdCaTRtWGwxbV9lVDRaYVpmMnU3MVU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>[속초소식] 착한가격업소 2곳 신규 선정…16일까지 신청</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>(속초=연합뉴스) ▲ 착한가격업소 2곳 신규 선정…16일까지 신청 = 강원 속초시는 오는 16일까지 '2026년 2차 착한가격업소' 신규 지정 ...</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014054400062</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>소노인터내셔널, 비발디파크 스키장 '26·27 시즌패스' 판매</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 구정모 기자 = 소노인터내셔널은 2026∼2027년 겨울 시즌을 맞아 비발디파크 스키장 시즌패스를 판매한다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014049100030</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>파라다이스, 인천서 '넥스트 가스트로노미' 포럼…ESG 실천 모색</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이상서 기자 = 파라다이스[034230]그룹은 지난 12일 인천 파라다이스시티에서 글로벌 미식 가이드인 '라 리스트 2027 ...</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014048500030</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>신한은행, 모바일 신분증 발급 서비스 개시</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 한지훈 기자 = 신한은행은 14일 신한 슈퍼SOL에서 모바일 신분증을 발급하는 서비스를 시작했다.</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014052900002</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>[인사] 한국방송광고진흥공사</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>▲ 상임감사 이수호 (서울=연합뉴스)</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014051300017</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>위메이드, 서틱과 위믹스 3.0 보안 강화…최대 1만 달러 포상</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김주환 기자 = 위메이드[112040]의 위믹스 재단은 미국 소재 블록체인 보안 기업 서틱(CertiK)과 함께 블록체인 메인...</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014040300017</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>이수만 “새 문 열겠다” 3년 만에 K팝 복귀…보이·걸그룹 동시 공개</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>이수만 “새 문 열겠다” 3년 만에 K팝 복귀…보이·걸그룹 동시 공개  국민일보이수만, 유영진과 돌아왔다…24명 아이돌로 K팝 흔들까  한겨레A20 LITE의 데뷔 쇼  뉴시스[ET포토] A2O 라이트 라다, '호수에서 백조가 발레하듯'  전자신문'이수만 표' 새 바람…A2O 소울·A2...</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>국민일보</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOamxndXRINVdISDF1N2VpMUdjM0R4dmVYR09fazVNYzExZTh1QXh6bk1DWEtUV21VcFhNTktOei0xYlp6aTlSYkZ5VjJ1WjE3ZUdzRGdmZTRjVEQxbmpuT0dhVkp0X3BzNDBhaHlfNHRfUDhVSHZLT0VFXy01REtPeEh0RHg4T3VPX3pyRWRna2Vzdw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>'나를 충전해줘', 공개 3일 만에 글로벌 톱10 비영어 쇼 3위</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>'나를 충전해줘', 공개 3일 만에 글로벌 톱10 비영어 쇼 3위  뉴스핌차우민, '최애의 사원' 이어 '나를 충전해줘'까지…로맨스 연타 흥행 예고  YTN김영광·채수빈 ‘나를 충전해줘’, 공개 3일 만에 넷플릭스 글로벌 비영어권 3위  스포츠동아‘국민엄마’ 김미경, 백발됐다…이번엔 재...</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>뉴스핌</t>
-        </is>
-      </c>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1PUG5VSTdieXRQZ0lrVmJGVWZieHdqRjhqYkZieWZ1cV9SN3Y2ZlBFdlBodzNORkNtbjh2Q1ZReklxQy1YR2l0aS1oYkROSDA1WVNkNjV3VXZTbFdm?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>[스브스夜] '틈만나면' 남지현, "전파견문록 출신, 출연 이후 드라마 캐스팅"…유재석 '사과 방송' 예고</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>[스브스夜] '틈만나면' 남지현, "전파견문록 출신, 출연 이후 드라마 캐스팅"…유재석 '사과 방송' 예고  news.sbs.co.krGoogle 뉴스에서 헤드라인 및 의견 더보기</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>news.sbs.co.kr</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPZ202a3RsUTFDVEJxU1A3eGpIT3lDZlhJbmdhank3dk8tRlVzVnVIcHZlUG9hWjRiSGxIdEpJVVZ5bjFHVUxvV1FkSlp0S2xCVWNQYUlhS2JYclZFampIcHRlVnlONGY0Wl9PSjBVR0RmNUozOFhQRGRHOUFIOE9XN1NDeTF6Zw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>시크릿, 17주년 자축…송지은, 박위 논란 불똥 속 '침묵' - 머니투데이</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>시크릿, 17주년 자축…송지은, 박위 논란 불똥 속 '침묵' - 머니투데이  머니투데이'♥박위' 발목잡힌 송지은-잘나가는 한선화-3크릿, 엇갈린 시크릿 17주년[SC이슈]  조선일보전효성, 데뷔 17주년 생일 카페에서 전한 팬 사랑 다짐  톱스타뉴스시크릿, 송지은 없이 17주년 맞았다…...</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>머니투데이</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBuTXhMcGtwMGVIR3ZvQkVMMkh5Wjc1TDFNNUloenNzY1kxZVVNYnJrNXMxVjVvSjZrLUtMT2IzVVNIVndpRF9IdnItcEhhQjQ1RFVZN0xTWEZJa1owNWgwcUZ1ZGxjQlpGNG1hRTB6NHpkNVHSAXhBVV95cUxPNkptTVNtRWZxWDVYLU1NNXdzVTYybVVRWC1zYzhuYlpzQVh6dEluMEFRWVNSNUQ1b2VRZWlFbkt2ZDk1U0ZOa2RISUxMaVJxanRZT2pvRlZJbEVCLW83NE9DQ0NVenhWWUtWNVczeXJ3Mk9ZS01sUXY?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>국힘 달성 군의회와 당원, \'암살자(들)\'영화 상영중지 촉구</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>국힘 달성 군의회와 당원, \'암살자(들)\'영화 상영중지 촉구  세명일보‘암살자(들)’ 실제 기자 “우리 패던 중정…영화가 잘 그려”  한겨레‘암살자(들)’ 논란, 하다하다 ‘100분 토론’ 간다  스포츠경향‘기립박수받은 배우가 위협받고 있다’ 외신도 주목  JTBC[시론] 권력자의 ...</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>세명일보</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBnSG5LUDhaVXZFcDR6ZE9fbUdhMDN6MnpmN0p3eUF0YUZLQUR4YkZIWldSMTloUm9ncWdWd2NEWVNfNkxBU1JwSFNuNG1Lbk1WMWk4YWgzbmszOEVON2hBNnZMaU1SQ3VsSlprTldUcWo?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>김새론에 “언제 안고 잘 수 있어” 다른 연예인이었다…김수현 미성년 성착취 의혹 해소</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>김새론에 “언제 안고 잘 수 있어” 다른 연예인이었다…김수현 미성년 성착취 의혹 해소  헤럴드경제김수현 아니었다…"너 안고 잠들 수 있어" 발신자는 연예인 A씨  뉴시스‘누명 벗은’ 김수현 측, 허위사실 유포에 강경 대응…“합의 없이 형사 고소·민사소송”  스포츠동아“언제 안고 잘 수 ...</t>
-        </is>
-      </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE4wVEI2bnllQmlsZ2JUcmxBQ05mdmpGQnZLVW9ueXpPVTV2Q0VDaE5IX2lKV2tBY3R3NWQ0ZEU1TWMzVTU2RXA2aEt2NHVnSUtvRnhQcktWaw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>베이비몬스터, 23일 신곡 ‘디저브’로 컴백…“강렬한 에너지”</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>베이비몬스터, 23일 신곡 ‘디저브’로 컴백…“강렬한 에너지”  KBS 뉴스베이비몬스터, 23일 신곡 '디저브'로 컴백…"강렬한 에너지"  연합뉴스YG 5인조 보이그룹·4인조 걸그룹 데뷔 구체화..양현석 직접 밝혔다 - 조선비즈  Chosunbiz‘가창력 과시’ 베이비몬스터, ‘힙합 노...</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>KBS 뉴스</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE00bjZ2YkUwcmZ3MW1GZjF5dnViZVpNbzdaYmpzSllMYnFpakNidzhMN3hyV0FMVERfcUR4em5pTHcwdkp2YXRYN09PaVBqRm1MbkxIN3ZtSmxzMjZiUEVFWWVqT0t3UQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>맨발로 비스듬히 느릿느릿… 차이밍량·이강생 “기존 영화 지겨워져 걸었다”</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>맨발로 비스듬히 느릿느릿… 차이밍량·이강생 “기존 영화 지겨워져 걸었다”  문화일보</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>문화일보</t>
-        </is>
-      </c>
-      <c r="G178" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE53dlVHR0diVUc0YTRVMHhBWXFDUXhlUnpIOXVBUVIxZGdtZHNNbG1FR3BST0FwdVAzUVBQY0FqUXUtQ2ZUT28yMGJZbmRHMlJJ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>[가요소식] '정엽 밴드' 코스믹 칩스, 2집 '테이스트'</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이태수 기자 = ▲ 코스믹 칩스 정규 2집 = 가수 정엽이 결성한 밴드 코스믹 칩스가 14일 오후 6시 두 번째 정규앨범 '테...</t>
-        </is>
-      </c>
-      <c r="F179" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G179" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014054000005</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>KBS '드라마스페셜 2026'…연말까지 단막극 8편 방송</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장진리 기자 = KBS는 2TV '드라마스페셜 2026'을 편성해 연말까지 단막극 8편을 방송한다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G180" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014048100005</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>베이비몬스터, 23일 신곡 '디저브'로 컴백…"강렬한 에너지"</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이태수 기자 = 걸그룹 베이비몬스터가 오는 23일 오후 1시 새 디지털 싱글 '디저브'(DESERVE)를 발매하고 가을 K팝 ...</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014047000005</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>BTS '아리랑', 스포티파이 50억 스트리밍…올해 발매 최고 기록</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이태수 기자 = 그룹 방탄소년단(BTS)의 정규 5집 '아리랑'(ARIRANG)이 세계 최대 음원 플랫폼 스포티파이에서 누적 ...</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014039500005</t>
+          <t>https://www.yna.co.kr/view/AKR20261014066300064</t>
         </is>
       </c>
     </row>
@@ -8521,42 +5895,42 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>240,000원</t>
+          <t>236,000원</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+33,500.0원 (+16.22%)</t>
+          <t>+29,500.0원 (+14.29%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>237,500원</t>
+          <t>220,500원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>257,000원</t>
+          <t>233,500원</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>231,500원</t>
+          <t>229,000원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+8.2%</t>
+          <t>+6.0%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>🔴 단기 비중 축소 (악재 주의)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>RSI 39.3로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -8570,21 +5944,21 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>39.3</v>
+        <v>37</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>[속보]홍라희 관장, 아들 이재용 회장에 삼성전자 주식 2.6조 증여 (문화일보)</t>
+          <t>필라델피아 반도체 지수 5일 연속 하락...7월 말 이후 처음 (YTN)</t>
         </is>
       </c>
     </row>
@@ -8611,42 +5985,42 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1,487,000원</t>
+          <t>1,458,000원</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+384,000.0원 (+34.81%)</t>
+          <t>+355,000.0원 (+32.18%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1,472,000원</t>
+          <t>1,371,000원</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1,706,500원</t>
+          <t>1,443,500원</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>1,435,000원</t>
+          <t>1,414,500원</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+15.9%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>🔴 단기 비중 축소 (악재 주의)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>RSI 35.1로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -8660,21 +6034,21 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>[개장시황] 코스피 1.29% 상승 출발…삼성전자·SK하이닉스 반등 (남도일보)</t>
+          <t>삼성전자 '100조 잭팟' 뒤 서늘한 경고…"한국이 흔들린다" [테크로그] (한국경제)</t>
         </is>
       </c>
     </row>
@@ -8701,17 +6075,17 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>321,000원</t>
+          <t>318,500원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-170,500.0원 (-34.69%)</t>
+          <t>-173,000.0원 (-35.20%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>318,000원</t>
+          <t>315,500원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -8721,12 +6095,12 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>310,000원</t>
+          <t>307,500원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+7.8%</t>
+          <t>+8.6%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -8736,7 +6110,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>RSI 27.4로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 25.2로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -8750,21 +6124,21 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>27.4</v>
+        <v>25.2</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>1∼8월 배터리 분리막 적재량 25%↑…중국 제외 41% 성장 (주요언론)</t>
         </is>
       </c>
     </row>
@@ -8796,7 +6170,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-39,100.0원 (-26.21%)</t>
+          <t>-39,300.0원 (-26.34%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -8826,7 +6200,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>RSI 34.0로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 33.5로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -8840,16 +6214,16 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -8886,7 +6260,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-19,250.0원 (-9.55%)</t>
+          <t>-19,400.0원 (-9.63%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -8901,7 +6275,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>176,000원</t>
+          <t>175,500원</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -8916,7 +6290,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>RSI 33.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 33.3로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -8930,16 +6304,16 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -8976,12 +6350,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-16,100.0원 (-33.47%)</t>
+          <t>-16,150.0원 (-33.58%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>31,700원</t>
+          <t>31,600원</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -8991,7 +6365,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>30,800원</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -9006,7 +6380,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>RSI 35.4로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 34.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -9020,21 +6394,21 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>35.4</v>
+        <v>34.9</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>카카오, 인적분할 앞두고 CEO 총출동…새 성장전략 공개 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -9066,7 +6440,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-5,919.049999999988원 (-3.12%)</t>
+          <t>-6,019.049999999988원 (-3.17%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -9086,7 +6460,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>+7.2%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -9110,21 +6484,21 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>[바이오스냅] 셀트리온, 미국 처방집 추가 등재 추진 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -9151,17 +6525,17 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>832,000원</t>
+          <t>828,000원</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-691,000.0원 (-45.37%)</t>
+          <t>-695,000.0원 (-45.63%)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>823,500원</t>
+          <t>819,500원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -9171,12 +6545,12 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>803,000원</t>
+          <t>799,000원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>+20.4%</t>
+          <t>+20.9%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -9186,7 +6560,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>RSI 29.1로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 28.8로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -9200,16 +6574,16 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -9241,12 +6615,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>421,500원</t>
+          <t>419,500원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+21,500.0원 (+5.38%)</t>
+          <t>+19,500.0원 (+4.88%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -9256,17 +6630,17 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>421,500원</t>
+          <t>419,500원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>413,000원</t>
+          <t>411,000원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>+12.7%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -9276,7 +6650,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 70.9, 20일선 이격도 +13.2%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 70.4, 20일선 이격도 +12.8%로 단기 과열권, 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -9290,21 +6664,21 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+13.2%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>1∼8월 배터리 분리막 적재량 25%↑…중국 제외 41% 성장 (주요언론)</t>
         </is>
       </c>
     </row>
@@ -9331,17 +6705,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>308,500원</t>
+          <t>309,500원</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>-53,000.0원 (-14.66%)</t>
+          <t>-52,000.0원 (-14.38%)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>302,500원</t>
+          <t>303,500원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -9351,12 +6725,12 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>293,000원</t>
+          <t>294,000원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+10.5%</t>
+          <t>+10.1%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -9380,16 +6754,16 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>45</v>
+        <v>45.7</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
@@ -9484,7 +6858,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>세레브라스 CEO "데이터센터 반발은 공포 마케팅 탓" (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -9896,12 +7270,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6,168.13</t>
+          <t>6,094.87</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+132.78 (+2.20%)</t>
+          <t>+59.52 (+0.99%)</t>
         </is>
       </c>
     </row>
@@ -9923,12 +7297,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>845.03</t>
+          <t>830.88</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>+8.00 (+0.96%)</t>
+          <t>-6.15 (-0.73%)</t>
         </is>
       </c>
     </row>
@@ -9950,7 +7324,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1,340.88원</t>
+          <t>1,340.88</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -9977,7 +7351,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>847.01원</t>
+          <t>847.01</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -10004,7 +7378,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1,500.84원</t>
+          <t>1,500.84</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -10031,7 +7405,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>199.98원</t>
+          <t>199.98</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -10142,27 +7516,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,822,000원</t>
+          <t>112,595,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>112,258,000원</t>
+          <t>112,032,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,848,000원</t>
+          <t>121,603,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,586,000원</t>
+          <t>110,576,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -10199,27 +7573,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3,391,000원</t>
+          <t>3,385,000원</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3,364,000원</t>
+          <t>3,358,000원</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3,594,500원</t>
+          <t>3,588,000원</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3,272,500원</t>
+          <t>3,266,500원</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -10234,7 +7608,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>RSI 47.2로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 46.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -10256,17 +7630,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>145,300원</t>
+          <t>144,900원</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>144,100원</t>
+          <t>143,700원</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -10276,12 +7650,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>140,200원</t>
+          <t>139,800원</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -10291,7 +7665,529 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>RSI 47.6로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 47.1로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>수집일자</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>신뢰도점수</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>증권사</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>리포트제목</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>목표주가</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>투자의견</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>핵심요약</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PDF파일명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>신한투자증권</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>빛을 보기 시작한 포트폴리오 변화</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>한 단계 진화한 실적, 한 단계 진화할 주가 레벨 수급 영향으로 단기 주가의 변동폭은 과거 대비 커졌으나 우호적인 벌크·탱커 시황 감안 시 중기 우상향 흐름 지속될 것으로 판단. 환율 방향성이원화 환산 실적에 부담이나 펀더멘털에 미치는 영향은 제한적</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_신한투자증권_팬오션_빛을 보기 시작한 포트폴리오 변화.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>신한투자증권</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>일진전기</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>가장 저평가된 전력기기</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>신한투자증권</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>HMM</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>우려도 있지만 너무 잠잠한 주가</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다 큰 이익 회복에 주목</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_신한투자증권_HMM_우려도 있지만 너무 잠잠한 주가.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>더 안정적인 성장을 위한 정비 작업(3Q26 Pre)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>선급금 4Q26 반영, 북경한미 정비 작업과 앱토즈 인수로 전체적인 실적은 부진 3Q26 실적은 연결기준 매출액 3,794억원(YoY+4.7%), 영업이익 381억원(YoY-30.8%, OPM 10.0%)으로 예상된다. 컨센서스와 크게 어긋나 보이지만, Genentech향 HM17321 L/O 선급금이 미국 HSR 행정절차가 10월 초 완료됨에 따라 4Q26에 인식되는데 컨센서스가 미리 3Q에 이를 반영했기 때문이다. 2Q에 Lilly향 L/O에 따른 선급금이 반영되었기 때문에 QoQ로 비교하는 것도 큰 의미가 없다. 선급금이 없던</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_하나증권_한미약품_더 안정적인 성장을 위한 정비 작업(3Q26 Pre).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>신한투자증권</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>현대글로비스</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>환율은 야속하지만 너무 좋은 해운 업황</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>자동차 밸류체인이지만 해운사이기도 함 단기 실적 가시성은 다소 낮아졌으나 이익 방향성은 여전히 긍정적. 비계열 고객 호조로 이익 개선이 뚜렷한 사업부를 가진 점은 차별화 포인트</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_신한투자증권_현대글로비스_환율은 야속하지만 너무 좋은 해운 업황.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>미래에셋증권</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다. 기존 유통사 재고 바이백으로 미국 매출은 마이너스가 예상된다. ASP가 높은 미국향 톡신 매출 공백으로 매출총이익률도 전년 동기 대비 6%p 하락이 </t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>삼성화재</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다. 장기보험손익은 3,560억원으로 YoY/QoQ 모두 감소할 것으로 예상하며, 사업비 부담 확대가 주요 원인이다. 자동차보험손익은 전분기대비 감소하겠으나 YoY </t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>세아베스틸지주</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>3분기는 다소 부진하겠지만 4분기부터 회복 기대</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3Q26 주력 자회사들 판매 감소와 스프레드 축소 2026년 3분기 세아베스틸지주의 매출액과 영업이익은 각각 1.0조원(YoY +10.3%, QoQ -10.6%)과 236억원(YoY -12.4%, QoQ -60.6%)으로 영업이익은 시장컨센서스인 398억원을 크게 하회할 것으로 예상된다. 계절적 비수기와 9월 추석 연휴 영향으로 세아베스틸의 특수강 판매는 41.2만톤(YoY +5.0%, QoQ -9.8%)에 그치며 고정비 부담이 확대될 전망이다. 원가 상승분 가격 전가를 위한 노력으로 8월초까지 적극적인 가격 인상을 시도한 결과, </t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_하나증권_세아베스틸지주_3분기는 다소 부진하겠지만 4분기부터 회복 기대.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>한화손해보험</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 Pre - 보험손익 개선세에 주목</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>2026년 3분기 실적은 컨센서스 소폭 하회 전망 3분기 별도 당기순이익은 903억원으로 컨센서스(939억원)를 소폭 하회할 것으로 전망한다. 증시 부진 및 금리 상승에 따른 투자손익 악화가 예상되나, 보험손익은 전반적으로 개선될 전망이다. [보험손익] 보험손익은 1,377억원(YoY +44.5%, QoQ +35.2%)으로 추정한다. 장기·자동차·일반보험손익 모두 예상대비 양호한 수준을 기록할 전망이다. 장기보험손익은 1,411억원으로 YoY/QoQ 모두 큰 폭 증가할 것으로 예상한다. 관리급여 효과에 따른 보험금 예실차 개선이 주</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_하나증권_한화손해보험_3Q26 Pre - 보험손익 개선세에 주목.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>어려운 영업환경!</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 내수와 수출 모두 수익성 악화 2026년 3분기 세아제강의 매출액과 영업이익은 각각 4,318억원(YoY +30.2%, QoQ -12.8%)과 195억원(YoY 흑.전, QoQ -44.2%)으로 영업이익은 시장컨센서스인 254억원을 하회할 것으로 예상된다. 3분기 내수 강관 시장은 계절적 비수기와 추석 연휴 영향으로 다소 부진할 것으로 예상되는 가운데 수출의 경우 캐나다 LNG와 같은 프로젝트 덕분에 소폭 증가한 것으로 추정되어 결과적으로 세아제강의 3분기 전체 강관 판매는 22.8만톤(YoY +21.4%, QoQ -6.8</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14_하나증권_세아제강_어려운 영업환경!.pdf</t>
         </is>
       </c>
     </row>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -12,6 +12,8 @@
     <sheet name="시장지표_누적" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="코인추천_누적" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="공식리포트_누적" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="추천성과_검증누적" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="특수공시_누적" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3632,12 +3634,12 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>태안군, 12월부터 참전명예수당 월 30만원→50만원</t>
+          <t>김용태 "은퇴봉사동물 지원예산 편성 2곳뿐…관리체계 개선해야"</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>(태안=연합뉴스) 정윤덕 기자 = 충남 태안군은 현재 월 30만원인 참전명예수당을 오는 12월부터 50만원으로 인상할 계획이라고 14일 밝혔다.</t>
+          <t>(서울=연합뉴스) 김세린 기자 = 국가봉사동물 운용 기관 대부분이 은퇴 동물에 대한 별도 지원 예산을 편성하지 않아 범부처 차원의 관리체계 개선...</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3647,7 +3649,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014058000063</t>
+          <t>https://www.yna.co.kr/view/AKR20261014083900030</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3661,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3669,22 +3671,22 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>與, 野주진우·이진숙·김태규 직격…"패륜으로 인지도 올리나"</t>
+          <t>달리기 대회서 20대女 사망에… '마라톤 거목' 황영조가 한 말</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 최주성 기자 = 더불어민주당은 14일 국민의힘 주진우·이진숙·김태규 의원의 국정감사 기간 중 발언을 놓고 "막말 정치인 양성소...</t>
+          <t>달리기 대회서 20대女 사망에… '마라톤 거목' 황영조가 한 말  한국일보황영조 ‘죽음에 이르는 러닝’ 경고···“욕심 부리지 말고, 필요하면 포기할 줄 알아야”  경향신문'서울 달리기' 마라톤대회 참가했던 20대 여성 사망  연합뉴스'서울달리기' 숨진 20대女는 '카이스트 대학원생' ...</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국일보</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014062800001</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBNT1l5LUxfQjNUOTIwSDRwdGt0MDBBZXZzVjQwa1RMV21NTTNxOHVMNS1ydjgzZ0wxRlJkY0xPSzVkcDYydUt1SWxRR1FBbVpmMjU0WkJFeW5La1NZSlREczBuVUJuU19vTVdQbGJn0gFzQVVfeXFMTzFCN2tGdVpYMjI0a1Z0emhBR3pPWUZjRXlnRTdpTlRwY0lxTnhPb1dpc2gwekFNYm9LVW1PRnFuRm12eDNzRDkzWkZSUVA2T0VsTUx6UDRHQ0dZM3Z2U2pSbzhWdUxUUXRHaEQ5UldldTFuTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3701,27 +3703,27 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>주미대사관 “강경화 ‘불의의 사고 아니다’ 발언, 이 대통령 반박 아냐”</t>
+          <t>울산 온산읍 제조업체서 불‥'대응 1단계'</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>주미대사관 “강경화 ‘불의의 사고 아니다’ 발언, 이 대통령 반박 아냐”  한겨레"불의의 사고 아니다" 강경화 발언 수습에… 한동훈 "국민이 우습나"  조선일보‘북 DMZ 지뢰’ 대처 공방…“안보리 차원 대응 검토 중”  KBS 뉴스[연합뉴스 이 시각 헤드라인] - 07:30  연합뉴스...</t>
+          <t>울산 온산읍 제조업체서 불‥'대응 1단계'  MBC 뉴스[속보] 울산 온산읍 제조업체 큰불...대응 1단계 발령  YTN울산 온산 화학공장서 폭발음 잇따라…공단 근로자 수천명 대피  부산일보울산 울주군 위험물 제조업체서 화재···소방 대응 1단계 발령  경향신문검은 연기 치솟는 울산 화...</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBvaWlRcEhkSXFzQU56OW1VOEFZdjFYZGh1akJIVUkwOFE4Y2NweUVpaVVxQjhSaGd2bG9FZzZKSExzTU8zY0FocWZTS3diZHZlSGxBaW9TazZ2b1RtWXBhS09tYzRsTHFMNVBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9xZ25EN3hYNlBZZE8yUmZCSHByRkdsbnMyNHA1eGt5VzdrUzV2djlqamdlUUVUWUlFT2k3cjVkSXFTY1hfVThBSGFDaHlTZC1GMlNHa09mQzJGMUxmNjUwYVhkbTdaOGhxS1ZDLTc1QmMyNzlTZkJN0gF3QVVfeXFMT0NFQ2FBa0JYcGdWUjZxSVhFQXZId3haTnNtOFFocExTUUR3R3Q3SWxFV2xaODdSUXNGdkd1bGtIMlRDZlVUYWNkZmxSU01DbXp1ZjVlRE9kaU84MXdIMlFzZElYSjBsMm5ySWZLdFdPLTVhVTk5c3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3738,17 +3740,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>경남도, 육상풍력 7개단지 48기 전수 점검…위험요인 사전 확인</t>
+          <t>무면허 중학생 공유 킥보드로 60대 여성 치여 하천 추락</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>(창원=연합뉴스) 김선경 기자 = 경남도는 오는 30일까지 도내 육상풍력 발전단지 7곳을 전수 점검한다고 14일 밝혔다.</t>
+          <t>(양주=연합뉴스) 심민규 기자 = 경기 양주시에서 중학생이 몰던 공유 전동킥보드에 60대 여성이 치여 하천으로 추락하는 사고가 발생했다.</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3758,7 +3760,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014066600052</t>
+          <t>https://www.yna.co.kr/view/AKR20261014083700060</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3782,12 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>세종시-홍익대, 청년 창업·실험실 '금남대평시장 리빙랩' 운영</t>
+          <t>흉기 난동범 재범 위험 '높음'이었는데…예견된 참극</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>(세종=연합뉴스) 양영석 기자 = 세종시와 홍익대학교 세종캠퍼스는 청년 창업·실험 공간인 '금남대평시장 가치회복 리빙랩'을 운영한다고 14일 밝...</t>
+          <t>(인천=연합뉴스) 최은지 기자 = 과거에도 재범 위험성 '높음' 판정을 받은 50대 살인미수 전과자가 도심 한복판에서 시민 8명을 찌르는 참극이...</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3795,7 +3797,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014068900063</t>
+          <t>https://www.yna.co.kr/view/AKR20261014081200065</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3809,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3817,22 +3819,22 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>AI 전환부터 수출까지…산업부·식약처, 바이오산업 전주기 협력</t>
+          <t>9월 ICT 수출 751억달러 '역대 최대'…반도체가 80% 견인</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 장보인 기자 = 바이오산업 육성을 담당하는 산업통상부와 의약품·의료기기 규제를 책임지는 식품의약품안전처가 바이오산업 전 주기에...</t>
+          <t>9월 ICT 수출 751억달러 '역대 최대'…반도체가 80% 견인  연합인포맥스지난달 ICT 수출 “사상 첫 700억 달러 돌파”  KBS 뉴스AI 열풍 탄 K-반도체 폭주…9월 ICT 수출 700억弗 첫 돌파  뉴시스2026년 9월 정보통신산업(ICT) 수출입 동향  서울PnKDI, ...</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014025800003</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBMdnFvTFQycG1RNDZHcWU3WncxMEpyZHB4Z3lHMlhFc0U1TUs0djFoZ3pLQ2lpZERDTThqXzNjeFNCdnpiOWxOZHFVVjFLeGlrWGNKNWpRLVRRbFRsTnM3TUlBN01iMTRzNXNtdlI5ck8?oc=5</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3846,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3854,12 +3856,12 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>강원 고성군, 재난 안전상황실 전담 인력 배치…내달 본격 운영</t>
+          <t>완주 테크노밸리 미니복합타운 2천884세대, 내년부터 순차 분양</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>(강원 고성=연합뉴스) 류호준 기자 = 강원 고성군은 기후 변화와 각종 재난 사고에 신속하게 대응하기 위해 다음 달부터 재난 안전상황실 전담 운...</t>
+          <t>(완주=연합뉴스) 최영수 기자 = 전북 완주군은 봉동읍 테크노밸리 제2일반산업단지 옆 미니복합타운을 내년 1월 첫 분양한다고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3869,7 +3871,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014066400062</t>
+          <t>https://www.yna.co.kr/view/AKR20261014082100055</t>
         </is>
       </c>
     </row>
@@ -3881,22 +3883,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>설악권 현안 두고 머리 맞댄 속초시·고성군 의회…"상생 협력"</t>
+          <t>한솔제지 등 대전 3개 기업, 공장 증설에 734억 투자</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>(속초=연합뉴스) 류호준 기자 = 강원 속초시의회와 고성군의회 의장이 만나 울산바위 인근 공동주택 개발 문제 등 설악권 주요 현안과 관련해 지역...</t>
+          <t>(대전=연합뉴스) 박주영 기자 = 대전시는 14일 대전 소재 기업 3곳과 734억원 규모의 투자 유치를 위한 업무협약을 했다.</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3906,7 +3908,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014065100062</t>
+          <t>https://www.yna.co.kr/view/AKR20261014083600063</t>
         </is>
       </c>
     </row>
@@ -3918,22 +3920,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>AI로 '옥외영업 인허가' 판단…고양시, 직원 아이디어 특허</t>
+          <t>이란, 레이더 파괴되자 '인간 레이더' 동원…미국과 '유가 전쟁'</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>(고양=연합뉴스) 노승혁 기자 = 경기 고양시는 현장 공무원이 직접 고안한 '인공지능(AI) 기반 옥외영업 가능 대상 자동 판단 및 인허가 검증...</t>
+          <t>(서울=연합뉴스) 임화섭 기자 = 미국 중간선거를 앞두고 이란이 호르무즈 해협을 지나는 선박을 공격하는 데에 '새 전술'을 동원하고 있다고 로이...</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3943,7 +3945,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014064100060</t>
+          <t>https://www.yna.co.kr/view/AKR20261014052400009</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3957,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3965,22 +3967,22 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>AI 코딩부터 데이터 활용까지…'AI 체험 축제' 열린다</t>
+          <t>불륜녀에게 칼 찔린 남편…살려달라 연락한 사람은 ‘아내’, 日 발칵 [핫이슈]</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 권하영 기자 = 전 국민이 참여할 수 있는 인공지능(AI) 체험의 장이 열린다.</t>
+          <t>불륜녀에게 칼 찔린 남편…살려달라 연락한 사람은 ‘아내’, 日 발칵 [핫이슈]  나우뉴스</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>나우뉴스</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014065400017</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5yYlFXd1pIRWNSakJjSmhDT1FGY0doR0NhYlNodFotVmZobWI4Uzh4dENKQnhqbFBoV1ZSNlFORTBxenpLbkh5MUpnN09VTjJPYmxRVWRQX3RRUjNhNnQ0aF9YU3htTUJLc0ZhWFRoMFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -3992,32 +3994,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>김해진영단감축제 30일 개막…사흘간 공연·체험 행사 풍성</t>
+          <t>트럼프, '장남 전 약혼녀' 길포일 주그리스 대사 전격 경질</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>(김해=연합뉴스) 이준영 기자 = 경남 김해시는 오는 30일부터 내달 1일까지 진영운동장 일원에서 '제42회 김해진영단감축제'를 개최한다고 14...</t>
+          <t>트럼프, '장남 전 약혼녀' 길포일 주그리스 대사 전격 경질  뉴스핌‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임  경향신문"가족은 아니었다"…트럼프, '아들 전 약혼녀' 그리스 대사 해임  마켓인백악관, '각종 비위 의혹' 그리스 대사에 "사퇴 요구했다"  연합뉴스트럼...</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>뉴스핌</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014065600052</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1FTFlBWGhjbXIyR01pc0Q4bGJGWWFyY01BTzdrS3hZdmlrQ3NzdHJheUV0Nmd2Y21fN3pabXR3YTlnUVZTZE90SWtmdGJYM0hKZGF3c2hlRk1rRlZP?oc=5</t>
         </is>
       </c>
     </row>
@@ -4029,32 +4031,32 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>목포해경, 안전사고 위험 '주의보' 발령</t>
+          <t>트럼프·네타냐후, 선거 전 이란 재공격 저울질…정치적 부담에 딜레마</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>(목포=연합뉴스) 조근영 기자 = 목포해양경찰서는 14일 목포·신안·무안·진도 등 전남광주 8개 시·군 지역에 안전사고 위험예보제 '주의보' 단...</t>
+          <t>트럼프·네타냐후, 선거 전 이란 재공격 저울질…정치적 부담에 딜레마  뉴스핌악시오스 "트럼프, 지난주 네타냐후와 중간선거 전 이란 공격 논의"  MBC 뉴스트럼프 "선거 끝나도 나는 대통령…후티 공격 잊지 않을 것" [이상은의 워싱턴나우]  한국경제트럼프, "러시아·중국이 이란 돕고 있...</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>뉴스핌</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014065700054</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5IeWdpMkUtOVZFQWRXQ0VERHJKVUNRSWE1M3JZSnB5Y1NfSWFVZHZwUGhiZ0ZqV05QNFdTZzlSNll1YTQyN0tLT0h2R3JEVEdXcVBfYnpJT1phRUFt?oc=5</t>
         </is>
       </c>
     </row>
@@ -4066,22 +4068,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>거래소·배출권시장協, 배출권거래제 정책·산업계 대응 논의</t>
+          <t>트럼프 새 대변인 변호사 경력 논란…"중국서 자격 취득" 주장</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 임은진 기자 = 한국거래소는 14일 오후 서울 사옥에서 배출권시장협의회와 함께 '2026년 하반기 자문위원회 세미나'를 연다.</t>
+          <t>(서울=연합뉴스) 이신영 기자 = 도널드 트럼프 미국 대통령이 새로 임명한 백악관 대변인 케이티 재커라이어가 경력 논란에 휩싸였다.</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4091,7 +4093,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014066900008</t>
+          <t>https://www.yna.co.kr/view/AKR20261014076000009</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4105,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4113,12 +4115,12 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>법원, '푸틴 반대' 러시아인 체류연장 불허에 "취소해야"</t>
+          <t>텐센트, AI 투자용 7.7조원 채권 발행…주문 4배 몰려</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>(인천=연합뉴스) 김상연 기자 = 국내에서 러시아·우크라이나 전쟁 반대 시위에 수백회 참여한 러시아인에게 난민인정 신청 결과가 나올 때까지 임시...</t>
+          <t>(서울=연합뉴스) 정주호 기자 = 중국 텐센트가 인공지능(AI) 투자 자금 마련을 위한 대규모 채권 발행에 4배가 넘는 투자 수요가 몰렸다.</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4128,7 +4130,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014065900065</t>
+          <t>https://www.yna.co.kr/view/AKR20261014082900009</t>
         </is>
       </c>
     </row>
@@ -4140,32 +4142,32 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>산업부, 2030년까지 국가·지역 대표 전시회 5개 이상 육성</t>
+          <t>조이시티, 12월 3일 신작 '프리스타일 풋볼 2' 글로벌 출시</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>산업부, 2030년까지 국가·지역 대표 전시회 5개 이상 육성  KBS 뉴스Google 뉴스에서 헤드라인 및 의견 더보기</t>
+          <t>조이시티, 12월 3일 신작 '프리스타일 풋볼 2' 글로벌 출시  아이뉴스24조이시티, '프리스타일 풋볼 2' 12월 3일 출시…사전 판매 시작  매일경제 마켓26년 9월 월간게임동향  게임트릭스'프리스타일 풋볼 2', 12월 3일 글로벌 출시…사전 판매 시작  인벤조이시티 ‘프리스타일...</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>아이뉴스24</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE0wbFFDM0djVl8tRTVjVUhwS0dfdjFGWkZYVURJNTZnaUZIeEVNdzUtMWZYRTY0VTFSYXMwdk9RVVVOR2FLMTFpSlQ2ZE1xRzFxa2pMdnBfT0pHa3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTFBLeDN5NXQ2U2xZdjRrYm1TSnJkRjdydDRPc19qbzZzU3E4ZnZMRW5DcWszNWNqRFA3aWp5YklNNG0zeVJyd2lEQ0N3NA?oc=5</t>
         </is>
       </c>
     </row>
@@ -4177,32 +4179,32 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>필라델피아 반도체 지수 5일 연속 하락...7월 말 이후 처음</t>
+          <t>RTX 5080 할인에 CPU 쿨러까지…조텍, 탁탁몰 특가 행사</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>필라델피아 반도체 지수 5일 연속 하락...7월 말 이후 처음  YTN메모리, 제2 소프트웨어?…"내년 정말 힘들 것" PTJ의 경고 [김현석의 월스트리트나우]  한국경제반도체 손실로 월가 하락 후 미국 증시 선물 보합세…CPI 발표 대기  Investing.com 한국어中 반도체 추격...</t>
+          <t>RTX 5080 할인에 CPU 쿨러까지…조텍, 탁탁몰 특가 행사  뉴스탭Google 뉴스에서 헤드라인 및 의견 더보기</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>뉴스탭</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFByT3A4M2N1UEF1c211Rll3UHdCX2F6ZkttQ3YwY0U3OTlJSE00ZDlwR1Y2X1dRT09zakFLRnd6TEs0RlBCcVhUSURyNF9BLVBHeld6bERydDZUQmxLY1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE92UmZLWFY0bG9iOEZPUjVtYTZjcnBNMkRteFZUY2ZkZ2xYaVlKS3lvRG5UMENyNGVMSkxaYUxIREo2ZjdSSjZlY2FFeEZuU1M4NF9EY0w5dU9wZWhBN1VucjB0ZGg5bmUtNmI4SA?oc=5</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4216,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4224,22 +4226,22 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>삼성전자 '100조 잭팟' 뒤 서늘한 경고…"한국이 흔들린다" [테크로그]</t>
+          <t>콘솔게임 보안까지 뚫은 AI, 해적판 등장에 업계 '발칵'</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>삼성전자 '100조 잭팟' 뒤 서늘한 경고…"한국이 흔들린다" [테크로그]  한국경제100조원 벌었지만 증가율은 반토막…외국인 올들어 232조원 ‘엑소더스’  한국경제삼성전자·SK하이닉스, 두번째 바닥 찍었나…“W자 반등 기대”  마켓인거침없는 외인 매도...반도체 역대급 실적에도 급락...</t>
+          <t>(서울=연합뉴스) 김주환 기자 = 인기 콘솔 게임과 플랫폼의 철통 같은 데이터 보안이 에이전틱 인공지능(AI) 고도화에 잇달아 뚫리며 해적판이 ...</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE0ybTlfNDRfSnlTM3l0VzBjYm5QNmpPeW9wLWJ6UGE1dTF2ZEd3Nll1LTA4dW0wVFlneHNqaWlMTzFDY21VbEF3eDluN2FVSXAyR0FQcVRuVm1kUQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014079700017</t>
         </is>
       </c>
     </row>
@@ -4251,32 +4253,32 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>새마을금고·OK저축은행도 고객 정보 유출…금융당국에 신고</t>
+          <t>'월가 족집게' 댄 아이브스 "테슬라·스페이스X 내년 합병 가능성 80%"</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>새마을금고·OK저축은행도 고객 정보 유출…금융당국에 신고  조선일보새마을금고 400명대 개인정보 유출... 계좌정보도 포함  보안뉴스금융당국, 해킹 2금융권 확산에 긴급 점검  전자신문OK저축은행, 대출신청 페이지에서 정보 유출… 고객 183명 정보 유출 - 조선비즈  Chosunbiz...</t>
+          <t>(서울=연합뉴스) 정회인 기자 = 월가의 대표적인 기술주 분석가인 댄 아이브스 '요크빌 아이브스' 파트너 겸 선임 전무는 엔비디아와 마이크로소프...</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNdUg3TWo4c01LMHZnOXFZOFdfZDRXRWpuMld3TlRzTXBNdjdvQTJyUFZmcGRfOGJCc3dnRFZQbW9pLVYtWDNPSXFDQkR0dTR3ZnVud0NlbjhhYWVhTnpvYm85SUNncUJvYzVqY0FRRlVrU2pvQnhSaDJ6aGFWM0s1bUJwaFdrd3dvQzQw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014080500008</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4290,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4298,22 +4300,22 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>횡성군, 임도 사면 녹화 기술 도입…식생 정착·시공 품질 향상</t>
+          <t>‘이병헌♥’ 이민정, 12살 초등학생 아들 사교육 언급..“농구·수학만 시켜”</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>(횡성=연합뉴스) 류호준 기자 = 강원 횡성군은 횡성군산림조합, 구루이엔티와 임도 사면 녹화 기술의 현장 적용과 기술 협력을 위한 업무협약(MO...</t>
+          <t>‘이병헌♥’ 이민정, 12살 초등학생 아들 사교육 언급..“농구·수학만 시켜”  조선일보이민정, 아들 사교육 질문에 "농구·수학 학원만 다녀"  뉴시스‘이병헌♥’ 이민정, 12살 초등학생 아들 사교육 언급..“농구·수학만 시켜” - 조선비즈  Chosunbiz'MJ' 이민정 "어렸을 때...</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014068000062</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZXdFa0RBNkNZYlBOZ1ZOUzlQWWJWbXlYbjJVUFdLeFBrSFhqcHVvMm5wWVRBMklsTm44MUJJRmMycjRCdzByYTdfTW8xLTFyaDVyN1RIdnZzSVRNOHdIeld1NW15Q2VibGZTUFE2eTlTXzR6MTdtakJ2MDZWRkk1UndvNy0xZUt0a2lRQ0dXbw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4325,32 +4327,32 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>충남도, 올해 마지막 '동네창업학교' 교육생 100명 모집</t>
+          <t>최수종, 모친상 후 끝내 눈물 “왜 쓴소리 했을까” (유퀴즈)</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>(홍성=연합뉴스) 김준범 기자 = 충남도는 청년 예비·초기 창업자를 대상으로 올해 마지막 '동네창업학교' 교육생 100명을 모집한다고 14일 밝...</t>
+          <t>최수종, 모친상 후 끝내 눈물 “왜 쓴소리 했을까” (유퀴즈)  매일경제최수종, 모친상 발인 다음 날 녹화…"엄마에게 쓴소리했던 게 후회"  뉴시스최수종, 모친상 심경.."쓴소리 더 기억나서 마음 아파" 눈물('유퀴즈')[핫피플] - 조선비즈  Chosunbiz“쓴소리했던 기억에 눈물”...</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014068300063</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE55YkFOMHFYNXc3S1c4MWY4T1ZHRGQxdmwzMjZFWS15d3dtaTZkdW1QbzgxUWlmaWpOcHFJVXN0RFlIcV9rU0dkX3ZpdGI5MG41ME9yeXdKVjF2Yi16cVBYZk1ic21vQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4362,32 +4364,32 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>공공수주 반등에도 민간 부진…8월 건설수주 8% 감소</t>
+          <t>김영광·채수빈 ‘나를 충전해줘’, 공개 3일 만에 넷플릭스 글로벌 비영어권 3위</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>(세종=연합뉴스) 오진송 기자 = 올해 8월 국내 건설수주가 공공 부문의 반등에도 민간 부진이 이어지면서 3개월 연속 감소한 것으로 나타났다.</t>
+          <t>김영광·채수빈 ‘나를 충전해줘’, 공개 3일 만에 넷플릭스 글로벌 비영어권 3위  스포츠동아차우민, '최애의 사원' 이어 '나를 충전해줘'까지…로맨스 연타 흥행 예고  YTN‘국민엄마’ 김미경, 백발됐다…이번엔 재벌가 회장 변신(‘나를 충전해줘’) - 조선비즈  Chosunbiz‘나를 ...</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>스포츠동아</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014059000003</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Ra1M4ZWNJS21PN3QtYnBCU3V4bnZoRm44Z2ZITHR1Z1lkUXZqZ2RVWTN1ZU0xWWRkZkJRVlVvOXQzanpDekVYcnBvWDJ0ekRlWElHZVFmVDVOT0IwWnpBbDlPNzk0WmtGdm1TTGZ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4399,180 +4401,32 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>레오 14세 교황, 폐암 진단…오른쪽 폐 일부 절제 수술</t>
+          <t>‘계약결혼’ 음주·흡연 갈등 시작</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>레오 14세 교황, 폐암 진단…오른쪽 폐 일부 절제 수술  한국경제71살 교황 레오 14세 폐암 진단…“오른쪽 폐 일부 절제”  한겨레레오 14세 교황, 폐 결절 아닌 폐암…오른쪽 폐 일부 절제 수술  동아일보교황청 "레오 14세, 폐 결절 수술 성공적 완료"…남미순방 갈듯  마켓인교황...</t>
+          <t>‘계약결혼’ 음주·흡연 갈등 시작  BNT뉴스'계약결혼' 남편 담배 냄새에 질색 "안대에서도 냄새나"  뉴시스흥행신화 PD도 0%대 굴욕...새 판 짠 남규홍 ‘계약결혼’ 아쉬운 초반 성적표 [SC이슈]  조선일보16기 상철, 암 수술한 영숙에 술 권유 "한 캔 정도는…"  파이낸셜뉴스...</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>BNT뉴스</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE52ak40R0pZMTk1NVRHM3lZNGNsYnFsYW1Ud2RGbXYzRzJZbUZFRjlxb2V2ZGVVRm5MaVFLOW5HZmM2eE5iSTcyLVowc2cydUc5WS1XRG9uVU53dw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>美검찰, '韓 정부 대리' 혐의 수미 테리 '기소유예 합의'</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 임화섭 기자 = 한국 정부를 위해 비밀리에 활동하고 고가 선물을 수수했다는 혐의를 받아온 전직 미국 중앙정보국(CIA) 분석가...</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014067100009</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>해양진흥공사, 지속가능경영보고서 최고 등급</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>(부산=연합뉴스) 박창수 기자 = 한국해양진흥공사는 지난 5월 발간한 '2025 지속가능경영보고서'가 미국 커뮤니케이션연맹(LACP)이 주관하는...</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014067400051</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>1∼8월 배터리 분리막 적재량 25%↑…중국 제외 41% 성장</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김민지 기자 = 올해 1∼8월 글로벌 전기차용 배터리 분리막 적재량이 배터리 탑재량 증가와 중국 제외 시장의 빠른 성장에 힘입...</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014062600003</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>음성군, '전통시장·상점가 활성화 유공' 중기부 장관상 수상</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>(음성=연합뉴스) 박재천 기자 = 충북 음성군은 중소벤처기업부의 '2026년 전통시장 및 상점가 활성화 유공' 평가에서 우수 지방자치단체로 선정...</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014066300064</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9RbjBZcjlhWHUtcDdJb3V3Q1VlWU9CVTBWSXNzaURtb05heENLNzJ1aHZJM3BqSFBjd2p0WTU0Ym5TODhVSjV5LWxvXzM3LWEyNmlBWVcyRVNhLTRLbEM3VzRpQ1M?oc=5</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4441,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
@@ -5895,42 +5749,42 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>236,000원</t>
+          <t>238,000원</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+29,500.0원 (+14.29%)</t>
+          <t>+31,250.0원 (+15.13%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>220,500원</t>
+          <t>235,500원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>233,500원</t>
+          <t>257,000원</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>229,000원</t>
+          <t>229,500원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+6.0%</t>
+          <t>+9.2%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (악재 주의)</t>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
+          <t>RSI 38.0로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5944,21 +5798,21 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>필라델피아 반도체 지수 5일 연속 하락...7월 말 이후 처음 (YTN)</t>
+          <t>9월 ICT 수출 751억달러 '역대 최대'…반도체가 80% 견인 (연합인포맥스)</t>
         </is>
       </c>
     </row>
@@ -5985,42 +5839,42 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1,458,000원</t>
+          <t>1,475,000원</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+355,000.0원 (+32.18%)</t>
+          <t>+372,000.0원 (+33.73%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1,371,000원</t>
+          <t>1,460,000원</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1,443,500원</t>
+          <t>1,706,000원</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>1,414,500원</t>
+          <t>1,423,500원</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (악재 주의)</t>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>악재 보도 및 5일 연속 약세로 단기 추가 하락 위험</t>
+          <t>RSI 34.2로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -6034,21 +5888,21 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>32.7</v>
+        <v>34.2</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>삼성전자 '100조 잭팟' 뒤 서늘한 경고…"한국이 흔들린다" [테크로그] (한국경제)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -6075,42 +5929,42 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>318,500원</t>
+          <t>319,500원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-173,000.0원 (-35.20%)</t>
+          <t>-172,000.0원 (-34.99%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>315,500원</t>
+          <t>313,000원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>342,500원</t>
+          <t>382,500원</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>307,500원</t>
+          <t>303,500원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+8.6%</t>
+          <t>+22.2%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>RSI 25.2로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -6124,21 +5978,21 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>25.2</v>
+        <v>26.1</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>1∼8월 배터리 분리막 적재량 25%↑…중국 제외 41% 성장 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -6165,42 +6019,42 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>110,000원</t>
+          <t>109,500원</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-39,300.0원 (-26.34%)</t>
+          <t>-39,500.0원 (-26.47%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>109,000원</t>
+          <t>107,500원</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>116,500원</t>
+          <t>126,500원</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>106,000원</t>
+          <t>104,000원</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+17.8%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>RSI 33.5로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -6214,16 +6068,16 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -6255,42 +6109,42 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>182,000원</t>
+          <t>181,500원</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-19,400.0원 (-9.63%)</t>
+          <t>-19,900.0원 (-9.88%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>180,500원</t>
+          <t>178,000원</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>193,000원</t>
+          <t>206,500원</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>175,500원</t>
+          <t>172,500원</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+16.0%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>RSI 33.3로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -6304,16 +6158,16 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>33.3</v>
+        <v>32.6</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -6345,42 +6199,42 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>32,000원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-16,150.0원 (-33.58%)</t>
+          <t>-16,200.0원 (-33.68%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>31,600원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>33,900원</t>
+          <t>34,600원</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>30,800원</t>
+          <t>30,300원</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+10.8%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>RSI 34.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -6394,16 +6248,16 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>34.9</v>
+        <v>34.4</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -6435,27 +6289,27 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>183,500원</t>
+          <t>182,000원</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-6,019.049999999988원 (-3.17%)</t>
+          <t>-7,419.049999999988원 (-3.91%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>180,000원</t>
+          <t>178,500원</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>193,000원</t>
+          <t>191,500원</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>174,500원</t>
+          <t>173,000원</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -6484,16 +6338,16 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>52.9</v>
+        <v>50.3</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -6525,42 +6379,42 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>828,000원</t>
+          <t>835,000원</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-695,000.0원 (-45.63%)</t>
+          <t>-688,000.0원 (-45.17%)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>819,500원</t>
+          <t>818,500원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>991,500원</t>
+          <t>1,137,000원</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>799,000원</t>
+          <t>793,000원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>+20.9%</t>
+          <t>+38.9%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>RSI 28.8로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -6574,16 +6428,16 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -6615,12 +6469,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>419,500원</t>
+          <t>422,500원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+19,500.0원 (+4.88%)</t>
+          <t>+22,500.0원 (+5.62%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -6630,17 +6484,17 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>419,500원</t>
+          <t>422,500원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>411,000원</t>
+          <t>414,000원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>+13.5%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -6650,7 +6504,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 70.4, 20일선 이격도 +12.8%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 71.1, 20일선 이격도 +13.5%로 단기 과열권, 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -6664,21 +6518,21 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+12.8%</t>
+          <t>+13.5%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>1∼8월 배터리 분리막 적재량 25%↑…중국 제외 41% 성장 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -6705,17 +6559,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>309,500원</t>
+          <t>309,000원</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>-52,000.0원 (-14.38%)</t>
+          <t>-52,500.0원 (-14.52%)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>303,500원</t>
+          <t>303,000원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -6725,12 +6579,12 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>294,000원</t>
+          <t>293,500원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+10.1%</t>
+          <t>+10.3%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -6754,16 +6608,16 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>45.7</v>
+        <v>45.3</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
@@ -6795,7 +6649,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>$228.52</t>
+          <t>$228.52 (약 306,417원)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -6805,12 +6659,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>$223.95</t>
+          <t>$223.95 (약 300,289원)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>$239.95</t>
+          <t>$239.95 (약 321,738원)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -6844,11 +6698,11 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>49.4</v>
+        <v>52</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6858,7 +6712,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>'월가 족집게' 댄 아이브스 "테슬라·스페이스X 내년 합병 가능성 80%" (주요언론)</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6739,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>$341.27</t>
+          <t>$341.27 (약 457,602원)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6895,12 +6749,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>$334.44</t>
+          <t>$334.44 (약 448,450원)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>$358.33</t>
+          <t>$358.33 (약 480,482원)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -6934,11 +6788,11 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>60.2</v>
+        <v>60.5</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6975,7 +6829,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>$375.23</t>
+          <t>$375.23 (약 503,138원)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -6985,12 +6839,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>$367.73</t>
+          <t>$367.73 (약 493,075원)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>$393.99</t>
+          <t>$393.99 (약 528,295원)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -7024,11 +6878,11 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>56.4</v>
+        <v>54.5</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -7037,6 +6891,96 @@
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>'월가 족집게' 댄 아이브스 "테슬라·스페이스X 내년 합병 가능성 80%" (주요언론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>마이크로소프트 (Microsoft)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>글로벌 AI/클라우드</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>$543.45 (약 728,701원)</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>+159.08000000000004$ (+41.39%)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>$514.20 (약 689,480원)</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>$543.45 (약 728,701원)</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>$532.58</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>+5.7%</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>RSI 70.7, 20일선 이격도 +5.7%로 단기 과열권, 분할 차익 실현 권고</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>+5.7%</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>95.0%</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
         </is>
@@ -7270,12 +7214,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6,094.87</t>
+          <t>6,123.61</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+59.52 (+0.99%)</t>
+          <t>+88.26 (+1.46%)</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7241,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>830.88</t>
+          <t>832.41</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-6.15 (-0.73%)</t>
+          <t>-4.62 (-0.55%)</t>
         </is>
       </c>
     </row>
@@ -7516,27 +7460,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,595,000원</t>
+          <t>112,538,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>112,032,000원</t>
+          <t>111,975,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,603,000원</t>
+          <t>121,541,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,576,000원</t>
+          <t>110,573,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7573,27 +7517,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3,385,000원</t>
+          <t>3,384,000원</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3,358,000원</t>
+          <t>3,357,000원</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3,588,000원</t>
+          <t>3,587,000원</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3,266,500원</t>
+          <t>3,265,500원</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -7630,17 +7574,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>144,900원</t>
+          <t>145,000원</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>143,700원</t>
+          <t>143,800원</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -7650,12 +7594,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>139,800원</t>
+          <t>139,900원</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>+8.4%</t>
+          <t>+8.3%</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -7665,7 +7609,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>RSI 47.1로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 47.3로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7692,6 +7636,11 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="65" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7740,6 +7689,31 @@
           <t>PDF파일명</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026F_예상매출</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026F_예상영업익</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2027F_예상매출</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2027F_예상영업익</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>실적전망요약</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7748,7 +7722,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -7783,6 +7757,31 @@
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2026-10-14_신한투자증권_팬오션_빛을 보기 시작한 포트폴리오 변화.pdf</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>7,426.1십억원</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>726.2십억원</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>7,662.9십억원</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>742.3십억원</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 영업이익 2,027억원(+61</t>
         </is>
       </c>
     </row>
@@ -7793,21 +7792,21 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>가장 저평가된 전력기기</t>
+          <t>더 안정적인 성장을 위한 정비 작업(3Q26 Pre)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -7817,17 +7816,42 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단</t>
+          <t>선급금 4Q26 반영, 북경한미 정비 작업과 앱토즈 인수로 전체적인 실적은 부진 3Q26 실적은 연결기준 매출액 3,794억원(YoY+4.7%), 영업이익 381억원(YoY-30.8%, OPM 10.0%)으로 예상된다. 컨센서스와 크게 어긋나 보이지만, Genentech향 HM17321 L/O 선급금이 미국 HSR 행정절차가 10월 초 완료됨에 따라 4Q26에 인식되는데 컨센서스가 미리 3Q에 이를 반영했기 때문이다. 2Q에 Lilly향 L/O에 따른 선급금이 반영되었기 때문에 QoQ로 비교하는 것도 큰 의미가 없다. 선급금이 없던</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
+          <t>2026-10-14_하나증권_한미약품_더 안정적인 성장을 위한 정비 작업(3Q26 Pre).pdf</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>1,895.0십억원</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>494.6십억원</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>1,844.1십억원</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>284.7십억원</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 실적은 연결기준 매출액 3,794억원(YoY+4</t>
         </is>
       </c>
     </row>
@@ -7847,12 +7871,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>일진전기</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>우려도 있지만 너무 잠잠한 주가</t>
+          <t>가장 저평가된 전력기기</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -7867,12 +7891,37 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다 큰 이익 회복에 주목</t>
+          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_HMM_우려도 있지만 너무 잠잠한 주가.pdf</t>
+          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2,350.8십억원</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>252.8십억원</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>2,595.2십억원</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>271.7십억원</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -7883,21 +7932,21 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>더 안정적인 성장을 위한 정비 작업(3Q26 Pre)</t>
+          <t>우려도 있지만 너무 잠잠한 주가</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -7907,17 +7956,42 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>선급금 4Q26 반영, 북경한미 정비 작업과 앱토즈 인수로 전체적인 실적은 부진 3Q26 실적은 연결기준 매출액 3,794억원(YoY+4.7%), 영업이익 381억원(YoY-30.8%, OPM 10.0%)으로 예상된다. 컨센서스와 크게 어긋나 보이지만, Genentech향 HM17321 L/O 선급금이 미국 HSR 행정절차가 10월 초 완료됨에 따라 4Q26에 인식되는데 컨센서스가 미리 3Q에 이를 반영했기 때문이다. 2Q에 Lilly향 L/O에 따른 선급금이 반영되었기 때문에 QoQ로 비교하는 것도 큰 의미가 없다. 선급금이 없던</t>
+          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다 큰 이익 회복에 주목</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_한미약품_더 안정적인 성장을 위한 정비 작업(3Q26 Pre).pdf</t>
+          <t>2026-10-14_신한투자증권_HMM_우려도 있지만 너무 잠잠한 주가.pdf</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>14,179.9십억원</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2,497.7십억원</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>14,293.1십억원</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1,812.7십억원</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 매출 4조 802억원(+51%, 이하 YoY) 및 영업이익 1조 42억원(+</t>
         </is>
       </c>
     </row>
@@ -7965,6 +8039,31 @@
           <t>2026-10-14_신한투자증권_현대글로비스_환율은 야속하지만 너무 좋은 해운 업황.pdf</t>
         </is>
       </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>33,217.4십억원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2,077.2십억원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>34,964.5십억원</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2,408.5십억원</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7977,17 +8076,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
+          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -7997,17 +8096,42 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다. 기존 유통사 재고 바이백으로 미국 매출은 마이너스가 예상된다. ASP가 높은 미국향 톡신 매출 공백으로 매출총이익률도 전년 동기 대비 6%p 하락이 </t>
+          <t xml:space="preserve">2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다. 장기보험손익은 3,560억원으로 YoY/QoQ 모두 감소할 것으로 예상하며, 사업비 부담 확대가 주요 원인이다. 자동차보험손익은 전분기대비 감소하겠으나 YoY </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
+          <t>2026-10-14_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>3,496십억원</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>4,566십억원</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -8018,21 +8142,21 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>휴젤</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
+          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -8042,17 +8166,42 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다. 장기보험손익은 3,560억원으로 YoY/QoQ 모두 감소할 것으로 예상하며, 사업비 부담 확대가 주요 원인이다. 자동차보험손익은 전분기대비 감소하겠으나 YoY </t>
+          <t xml:space="preserve">3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다. 기존 유통사 재고 바이백으로 미국 매출은 마이너스가 예상된다. ASP가 높은 미국향 톡신 매출 공백으로 매출총이익률도 전년 동기 대비 6%p 하락이 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
+          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>486십억원</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>174십억원</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>657십억원</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>272십억원</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 매출액은 1,009억원(-4</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8212,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -8098,6 +8247,31 @@
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t>2026-10-14_하나증권_세아베스틸지주_3분기는 다소 부진하겠지만 4분기부터 회복 기대.pdf</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>4,116.0십억원</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>140.6십억원</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>4,496.9십억원</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>223.3십억원</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>3Q26 영업이익 236억원(YoY -</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8282,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -8143,6 +8317,31 @@
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>2026-10-14_하나증권_한화손해보험_3Q26 Pre - 보험손익 개선세에 주목.pdf</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>465십억원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>595십억원</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8352,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -8188,6 +8387,991 @@
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>2026-10-14_하나증권_세아제강_어려운 영업환경!.pdf</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>1,822.7십억원</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>103.1십억원</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>1,852.8십억원</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>124.3십억원</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>2026년 3분기 세아제강의 매출액과 영업이익은 각각 4,318억원(YoY +30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>검증기준일</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>추천일자</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>티커</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>추천당시가</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>매수추천가</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>목표매도가</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>손절기준가</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>검증결과</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>실현수익률</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>최고도달가</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>소요일수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>005380.KS</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>315,000원</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>312,000원</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>349,500원</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>304,000원</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (보유 중)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>321,500원</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>1일 경과</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>000270.KS</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>108,500원</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>107,000원</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>115,500원</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>104,500원</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (보유 중)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>+2.5%</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>110,700원</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>1일 경과</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>035420.KS</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>178,000원</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>176,000원</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>193,000원</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>172,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (보유 중)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>183,200원</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>1일 경과</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>035720.KS</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>31,300원</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>31,000원</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>30,200원</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (보유 중)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>+2.9%</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>32,100원</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>1일 경과</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>012450.KS</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>839,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>830,500원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1,012,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>809,500원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (보유 중)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>839,000원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>1일 경과</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>POSCO홀딩스</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>005490.KS</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>299,000원</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>296,000원</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>317,000원</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>288,500원</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (보유 중)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>+4.4%</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>312,000원</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>1일 경과</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>000660.KS</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1,475,000원</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1,460,000원</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1,706,000원</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>1,423,500원</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (당일 포지션 구축)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>1,475,000원</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="53" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>수집일자</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>공시구분</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>공시배지</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>관련기업</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>공시제목</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>영향전망</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>언론사</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>공시일시</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>스틱인베스트먼트</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>[공시 Pick] 스틱인베스트먼트, 41억원 자사주 취득에 강세…장중 4%↑</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>뉴스투데이</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 05:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE41b0xlNUs4c2FxVTNMaENRVHJFM1prZDE0dWw0dy1CY1VYOVN3LVV4REtOUDJhTTFhU2lCS1RMcDlQeU8tVG8xSXVSbURwRW9oOHNaelhKdktwRjhmSWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>데스트라 멀티 대체 투자 펀드, 자사주 매입 프로그램 도입·월 배당금 주당 0.115달러로 인상</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>데이터투자</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 19:52:27 GMT</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1lemt2YTFaYUFFeVI4cVJZbjFYOHpWLVJmNTUxN3huQlRtYUVHYXplTUpvQktSZFdKenhkMl9PYXlNci1RbHNtTUdQdXgxelpjaEJVbWNjVmFndWFiaV9KZFAxd2ozbVZXVUd4MHFPNlZYT0U?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>“역시 주주환원은 뒷전입니까”…코스피 자사주 매입, 삼전닉스 뺐더니 줄었다</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>매일경제 마켓</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 11:51:10 GMT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE0zXzFYa0xGekFCVWtnODd6QVRIRmp1MnFLcXhBWWVadVdXQWZaY3lGcGg3WUl1dzY4M1R1cTBWV1h1a0JBbXdGV3Y0aC1KV25lRmc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>AZZ, 연간 실적 가이던스 상향…2000만 달러 규모 자사주 매입</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>데이터투자</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 20:20:27 GMT</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9QR3MyNXVOWndYaXJsdTF5Z2NaQnlGUVRFanBlUjhmN1U0TDNCMXNUZ2RrNTRselZhSGtXTW9YMUJGVWtvSTdDdFhCVVN6ZTVCcTZ0WnlkeUNsRTZlMGZBXzJnSnkxZ1Z3NjI5MlF0N0N3dw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>트러스트</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>선라이즈 리얼티 트러스트, 2000만 달러 자사주 매입 프로그램 승인</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>데이터투자</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 12:13:59 GMT</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1fQmV2cFR2OFA5M1B6UXE3NF83TmRrd2lGSE1QelFpZWFMUDhZT1lHWHJYUnFBcmtKNUJmRWlwRTU3ME1ydno4cmpDMnpWMTF0Q09HQ0dmOVVubFFIYXNWZ1FhWlRZaEp3dk4xcHd2TmdFQ00?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>아웃렛</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>올리스 바겐 아웃렛, 5억 달러 규모 신규 자사주 매입 승인</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>데이터투자</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 11:09:56 GMT</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5nZklvLUJYTTRmYUtlSnZGdWgzaE9aeExETGVnWDF1dXpLTGVMWWpSSEdodW1WMkprQW5oeEMxV0xtM0pIcndVZDVhVk5UWnIwcFNyMlI2X0hjb2M3UHBXME5sRGFCN0pYdDJWTEstSmpqVE0?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>엘컴텍</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>엘컴텍, 20억원 규모 자사주 취득 결정</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>데이터투자</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 07:22:52 GMT</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE13UXpQT2FyUjBQSkpSdFNtQVpJOHFGMExaeDFtajBra1h5dHl5S2dMbUV5TUdmMzFYZkF6b1RmSTd0TVk1NUZCOGN1Y1pWS3d1Rk50WmRUS19XZkJISzdJX3k1YXpPU2V3X3FhNkloOWs1QQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>💎 자사주 취득 (주가 부양)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>자사주 취득</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>더핑크퐁컴퍼니</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>더핑크퐁컴퍼니, 50억원 규모 자사주 취득 신탁계약 해지 결정</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>데이터투자</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 05:43:38 GMT</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1MVmRGS1NqcEJobXNpM01fNTlJbV9MeFZUeXBTVktGWV9XOWFlMHFET09BeW1rQ1RJdzVCR0I1OXM1UkpxM3Nnazk4RnBPbC1EaGFxM0FpVVpqYzZPRnlGb0plTEwyYmZDSXJXNW8yYmh5M0k?oc=5</t>
         </is>
       </c>
     </row>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -14,6 +14,7 @@
     <sheet name="공식리포트_누적" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="추천성과_검증누적" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="특수공시_누적" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="스토리딥다이브_누적" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3629,27 +3630,27 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>김용태 "은퇴봉사동물 지원예산 편성 2곳뿐…관리체계 개선해야"</t>
+          <t>김지용 "중수청, 외압 흔들림 없이 법·원칙 따라 공정 수사"</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김세린 기자 = 국가봉사동물 운용 기관 대부분이 은퇴 동물에 대한 별도 지원 예산을 편성하지 않아 범부처 차원의 관리체계 개선...</t>
+          <t>김지용 "중수청, 외압 흔들림 없이 법·원칙 따라 공정 수사"  MBC 뉴스김지용 중수청장 후보자 "약자 대상 범죄 보완수사 빈틈없이"  조선일보김민석 “각자 역할 집중해야”…‘김지용 비판’ 추미애에 [지금뉴스]  KBS 뉴스김지용 "김학의 불법출금 무리한 기소 인정…책임 없지 않아" ...</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014083900030</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFB5UDcySVc2Q3hrX1ZxUi1oOXVFTkJCSF9DUHZvVmVYY3BKeC0xdmN4RXVXcGxsRE45enFpYXNLcERDbVRBMWNWUHgydURaRkpTaV9KbHVqTGIwVEFTYkVXUHBzdVFMb1N3Zk80OUVzM1NRRGlNWVh30gF3QVVfeXFMUHgtOG9BQlprR3ZSc0JFeWthUFNsZ29BM0xyR2FmVm9iNkQxWm01REpPUmlPQzdHbUxobnpmVHp1ZE1ldHdRNHpZZ2h4YkFjWGREMzFWemcwUGFBY1JheDhOcHNlTzhsQ2VRUTIyWWRLbVMzZHZkU3M?oc=5</t>
         </is>
       </c>
     </row>
@@ -3661,32 +3662,32 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>달리기 대회서 20대女 사망에… '마라톤 거목' 황영조가 한 말</t>
+          <t>[사설]“대출 더 줄여야” “집값 급락 가능성”… LH 사장의 오지랖</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>달리기 대회서 20대女 사망에… '마라톤 거목' 황영조가 한 말  한국일보황영조 ‘죽음에 이르는 러닝’ 경고···“욕심 부리지 말고, 필요하면 포기할 줄 알아야”  경향신문'서울 달리기' 마라톤대회 참가했던 20대 여성 사망  연합뉴스'서울달리기' 숨진 20대女는 '카이스트 대학원생' ...</t>
+          <t>[사설]“대출 더 줄여야” “집값 급락 가능성”… LH 사장의 오지랖  동아일보이성훈 LH 사장, 고양창릉 첫마을 입주 준비 점검…공공임대 품질 강화 주문  전기신문유승민 “LH사장이 집값 예측할 때인가…주택공급이나 열심히 해야”  경기일보[기자수첩]대출 없이 집 산 LH 사장의 대출 ...</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>한국일보</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBNT1l5LUxfQjNUOTIwSDRwdGt0MDBBZXZzVjQwa1RMV21NTTNxOHVMNS1ydjgzZ0wxRlJkY0xPSzVkcDYydUt1SWxRR1FBbVpmMjU0WkJFeW5La1NZSlREczBuVUJuU19vTVdQbGJn0gFzQVVfeXFMTzFCN2tGdVpYMjI0a1Z0emhBR3pPWUZjRXlnRTdpTlRwY0lxTnhPb1dpc2gwekFNYm9LVW1PRnFuRm12eDNzRDkzWkZSUVA2T0VsTUx6UDRHQ0dZM3Z2U2pSbzhWdUxUUXRHaEQ5UldldTFuTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE43QTc0VC1rSWlsSzZteVRkOXNDYU5YbmlxVjJoeVV6bFZXNmw2V1NfSklHY2JHVHVLU0pja196Ml91MXhrN3ZxTHQ5SE5ZQUZuTkRHUHVrOGUxbEhuV2phcWF3MllveFEwVzlEaEMyUDFvMHVzMlHSAWZBVV95cUxQZTUtX0dhUVdyNmw0T1JCTzQzc1NtakNnWDJ4MXZ3Vk1SaVBvRmFFakE1MjA5a3NMT0FvTWplYjFBZWF4am5zUnhnQVFHSFNpTVUweHpQMkcxZzFCZnl4Wms1MVpiVkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -3698,32 +3699,32 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>울산 온산읍 제조업체서 불‥'대응 1단계'</t>
+          <t>국힘, 與 '신천지 의혹' 확인에 "특검·당원명부 압수수색 해야"</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>울산 온산읍 제조업체서 불‥'대응 1단계'  MBC 뉴스[속보] 울산 온산읍 제조업체 큰불...대응 1단계 발령  YTN울산 온산 화학공장서 폭발음 잇따라…공단 근로자 수천명 대피  부산일보울산 울주군 위험물 제조업체서 화재···소방 대응 1단계 발령  경향신문검은 연기 치솟는 울산 화...</t>
+          <t>(서울=연합뉴스) 박수윤 조다운 기자 = 국민의힘은 14일 더불어민주당이 신천지 교인의 집단 당원 가입 정황을 자체 조사로 공식 확인하자 당원 ...</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9xZ25EN3hYNlBZZE8yUmZCSHByRkdsbnMyNHA1eGt5VzdrUzV2djlqamdlUUVUWUlFT2k3cjVkSXFTY1hfVThBSGFDaHlTZC1GMlNHa09mQzJGMUxmNjUwYVhkbTdaOGhxS1ZDLTc1QmMyNzlTZkJN0gF3QVVfeXFMT0NFQ2FBa0JYcGdWUjZxSVhFQXZId3haTnNtOFFocExTUUR3R3Q3SWxFV2xaODdSUXNGdkd1bGtIMlRDZlVUYWNkZmxSU01DbXp1ZjVlRE9kaU84MXdIMlFzZElYSjBsMm5ySWZLdFdPLTVhVTk5c3c?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014089200001</t>
         </is>
       </c>
     </row>
@@ -3735,22 +3736,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>무면허 중학생 공유 킥보드로 60대 여성 치여 하천 추락</t>
+          <t>교육위서 교부금 개편 도마…여야 '김민석·한동훈 자녀' 겨냥도</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>(양주=연합뉴스) 심민규 기자 = 경기 양주시에서 중학생이 몰던 공유 전동킥보드에 60대 여성이 치여 하천으로 추락하는 사고가 발생했다.</t>
+          <t>(서울=연합뉴스) 류미나 이율립 기자 = 국회 교육위원회가 14일 서울·인천·경기 등 수도권 교육청을 대상으로 실시한 국정감사에서는 정부의 지방...</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3760,7 +3761,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014083700060</t>
+          <t>https://www.yna.co.kr/view/AKR20261014088200001</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3773,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3782,12 +3783,12 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>흉기 난동범 재범 위험 '높음'이었는데…예견된 참극</t>
+          <t>어린 딸 두고 입대한 6·25전쟁 두 호국영웅 유해 신원확인</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>(인천=연합뉴스) 최은지 기자 = 과거에도 재범 위험성 '높음' 판정을 받은 50대 살인미수 전과자가 도심 한복판에서 시민 8명을 찌르는 참극이...</t>
+          <t>(서울=연합뉴스) 김효정 기자 = 국방부 유해발굴감식단(이하 국유단)은 각기 어린 딸을 두고 입대했다 6·25전쟁에서 전사한 고(故) 진성대 이...</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3797,7 +3798,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014081200065</t>
+          <t>https://www.yna.co.kr/view/AKR20261014085600504</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3810,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3819,22 +3820,22 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>9월 ICT 수출 751억달러 '역대 최대'…반도체가 80% 견인</t>
+          <t>복지위 '리밸런싱' 충돌…"회의록 공개해야"·"시장영향 우려"</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>9월 ICT 수출 751억달러 '역대 최대'…반도체가 80% 견인  연합인포맥스지난달 ICT 수출 “사상 첫 700억 달러 돌파”  KBS 뉴스AI 열풍 탄 K-반도체 폭주…9월 ICT 수출 700억弗 첫 돌파  뉴시스2026년 9월 정보통신산업(ICT) 수출입 동향  서울PnKDI, ...</t>
+          <t>(서울=연합뉴스) 권희원 기자 = 여야는 14일 국회 보건복지위원회 국민연금공단 국정감사에서 국민연금의 리밸런싱(자산 비중 재조정) 유예 결정 ...</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBMdnFvTFQycG1RNDZHcWU3WncxMEpyZHB4Z3lHMlhFc0U1TUs0djFoZ3pLQ2lpZERDTThqXzNjeFNCdnpiOWxOZHFVVjFLeGlrWGNKNWpRLVRRbFRsTnM3TUlBN01iMTRzNXNtdlI5ck8?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014090800001</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3847,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3856,12 +3857,12 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>완주 테크노밸리 미니복합타운 2천884세대, 내년부터 순차 분양</t>
+          <t>국정원 '美, 국정원장 방문거부' 보도 정정신청…이례적 법적대응</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>(완주=연합뉴스) 최영수 기자 = 전북 완주군은 봉동읍 테크노밸리 제2일반산업단지 옆 미니복합타운을 내년 1월 첫 분양한다고 14일 밝혔다.</t>
+          <t>(서울=연합뉴스) 하채림 기자 = 국가정보원이 미국 국방부 산하 기관이 이종석 국정원장의 방문을 거부했다는 언론보도에 대해 이례적으로 법적 대응...</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3871,7 +3872,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014082100055</t>
+          <t>https://www.yna.co.kr/view/AKR20261014084800504</t>
         </is>
       </c>
     </row>
@@ -3883,22 +3884,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>한솔제지 등 대전 3개 기업, 공장 증설에 734억 투자</t>
+          <t>김창국 aT 사장대행 "브라질산 계란 수입, 수입선 다변화 측면"</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>(대전=연합뉴스) 박주영 기자 = 대전시는 14일 대전 소재 기업 3곳과 734억원 규모의 투자 유치를 위한 업무협약을 했다.</t>
+          <t>(서울=연합뉴스) 한주홍 기자 = 김창국 한국농수산식품유통공사(aT) 사장 직무대행은 14일 브라질산 신선란 수입과 관련해 "수입선 다변화 측면...</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3908,7 +3909,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014083600063</t>
+          <t>https://www.yna.co.kr/view/AKR20261014091000030</t>
         </is>
       </c>
     </row>
@@ -3920,22 +3921,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>이란, 레이더 파괴되자 '인간 레이더' 동원…미국과 '유가 전쟁'</t>
+          <t>특검, '선거용품 입찰비리' 중앙선관위 등 5곳 압수수색</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 임화섭 기자 = 미국 중간선거를 앞두고 이란이 호르무즈 해협을 지나는 선박을 공격하는 데에 '새 전술'을 동원하고 있다고 로이...</t>
+          <t>(서울=연합뉴스) 최원정 기자 = 이태한 선거관리위원회 특별검사팀이 중앙선관위의 선거 용품 입찰 비리 의혹과 관련해 강제수사에 착수했다.</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3945,7 +3946,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014052400009</t>
+          <t>https://www.yna.co.kr/view/AKR20261014090600004</t>
         </is>
       </c>
     </row>
@@ -3957,32 +3958,32 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>불륜녀에게 칼 찔린 남편…살려달라 연락한 사람은 ‘아내’, 日 발칵 [핫이슈]</t>
+          <t>김지용 "정치 편중되지 않게 일했다…부적격이라 생각지 않아"</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>불륜녀에게 칼 찔린 남편…살려달라 연락한 사람은 ‘아내’, 日 발칵 [핫이슈]  나우뉴스</t>
+          <t>(서울=연합뉴스) 황재하 기자 = 김지용 초대 중대범죄수사청장(중수청장) 후보자가 과거 검찰권 남용 사례들에 반대했었다고 재차 밝히면서 정치적 ...</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>나우뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5yYlFXd1pIRWNSakJjSmhDT1FGY0doR0NhYlNodFotVmZobWI4Uzh4dENKQnhqbFBoV1ZSNlFORTBxenpLbkh5MUpnN09VTjJPYmxRVWRQX3RRUjNhNnQ0aF9YU3htTUJLc0ZhWFRoMFE?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014089000004</t>
         </is>
       </c>
     </row>
@@ -3994,32 +3995,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>트럼프, '장남 전 약혼녀' 길포일 주그리스 대사 전격 경질</t>
+          <t>문체위, 이임생·이동국 국감증인 의결…암살자(들) 채택은 불발</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>트럼프, '장남 전 약혼녀' 길포일 주그리스 대사 전격 경질  뉴스핌‘트럼프 장남 전 연인’ 주그리스 미국 대사 비위 의혹에 사임  경향신문"가족은 아니었다"…트럼프, '아들 전 약혼녀' 그리스 대사 해임  마켓인백악관, '각종 비위 의혹' 그리스 대사에 "사퇴 요구했다"  연합뉴스트럼...</t>
+          <t>(서울=연합뉴스) 박경준 기자 = 국회 문화체육관광위원회는 14일 전체회의를 열어 이용수 대한축구협회 회장 직무대행, 이임생 전 대한축구협회 기...</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>뉴스핌</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1FTFlBWGhjbXIyR01pc0Q4bGJGWWFyY01BTzdrS3hZdmlrQ3NzdHJheUV0Nmd2Y21fN3pabXR3YTlnUVZTZE90SWtmdGJYM0hKZGF3c2hlRk1rRlZP?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014084500001</t>
         </is>
       </c>
     </row>
@@ -4031,32 +4032,32 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>트럼프·네타냐후, 선거 전 이란 재공격 저울질…정치적 부담에 딜레마</t>
+          <t>LIG D&amp;A, 미국 방산 스타트업과 유도로켓 추진체계 '맞손'</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>트럼프·네타냐후, 선거 전 이란 재공격 저울질…정치적 부담에 딜레마  뉴스핌악시오스 "트럼프, 지난주 네타냐후와 중간선거 전 이란 공격 논의"  MBC 뉴스트럼프 "선거 끝나도 나는 대통령…후티 공격 잊지 않을 것" [이상은의 워싱턴나우]  한국경제트럼프, "러시아·중국이 이란 돕고 있...</t>
+          <t>(서울=연합뉴스) 홍규빈 기자 = LIG 디펜스&amp;amp;에어로스페이스(LIG D&amp;amp;A)가 미국 방산 스타트업 '파이어호크'와 손잡고 미국 ...</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>뉴스핌</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5IeWdpMkUtOVZFQWRXQ0VERHJKVUNRSWE1M3JZSnB5Y1NfSWFVZHZwUGhiZ0ZqV05QNFdTZzlSNll1YTQyN0tLT0h2R3JEVEdXcVBfYnpJT1phRUFt?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014087800003</t>
         </is>
       </c>
     </row>
@@ -4068,22 +4069,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>트럼프 새 대변인 변호사 경력 논란…"중국서 자격 취득" 주장</t>
+          <t>육군 1군단, 19∼23일 파주·고양·양주서 호국훈련</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 이신영 기자 = 도널드 트럼프 미국 대통령이 새로 임명한 백악관 대변인 케이티 재커라이어가 경력 논란에 휩싸였다.</t>
+          <t>(고양=연합뉴스) 노승혁 기자 = 육군 1군단은 군사대비태세 유지와 합동 작전 수행 능력 향상을 위해 오는 19∼23일 파주·고양·양주 등 경기...</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4093,7 +4094,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014076000009</t>
+          <t>https://www.yna.co.kr/view/AKR20261014087900060</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4106,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4115,12 +4116,12 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>텐센트, AI 투자용 7.7조원 채권 발행…주문 4배 몰려</t>
+          <t>친청계 "허위면 책임져야"…與 '신천지 확인'에 갈등 재점화 조짐</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 정주호 기자 = 중국 텐센트가 인공지능(AI) 투자 자금 마련을 위한 대규모 채권 발행에 4배가 넘는 투자 수요가 몰렸다.</t>
+          <t>(서울=연합뉴스) 김정진 안정훈 기자 = 더불어민주당이 공식적으로 신천지 교인의 집단 당원 가입 사실을 확인하면서 당내 계파 갈등이 재점화하고 ...</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4130,7 +4131,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014082900009</t>
+          <t>https://www.yna.co.kr/view/AKR20261014078300001</t>
         </is>
       </c>
     </row>
@@ -4142,32 +4143,32 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>조이시티, 12월 3일 신작 '프리스타일 풋볼 2' 글로벌 출시</t>
+          <t>'카이스트 러너' 유지원, 마라톤 레이스 중 사망 ...500m 남기고 '심정지' 비보</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>조이시티, 12월 3일 신작 '프리스타일 풋볼 2' 글로벌 출시  아이뉴스24조이시티, '프리스타일 풋볼 2' 12월 3일 출시…사전 판매 시작  매일경제 마켓26년 9월 월간게임동향  게임트릭스'프리스타일 풋볼 2', 12월 3일 글로벌 출시…사전 판매 시작  인벤조이시티 ‘프리스타일...</t>
+          <t>'카이스트 러너' 유지원, 마라톤 레이스 중 사망 ...500m 남기고 '심정지' 비보  스포츠조선황영조 ‘죽음에 이르는 러닝’ 경고···“욕심 부리지 말고, 필요하면 포기할 줄 알아야”  경향신문'서울 달리기' 마라톤대회 참가했던 20대 여성 사망  연합뉴스'서울달리기' 숨진 20대女...</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>아이뉴스24</t>
+          <t>스포츠조선</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTFBLeDN5NXQ2U2xZdjRrYm1TSnJkRjdydDRPc19qbzZzU3E4ZnZMRW5DcWszNWNqRFA3aWp5YklNNG0zeVJyd2lEQ0N3NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQSTFXR09uYVhhTEJlb3BRQVg0RndvYkhVNThjcFB6VzNpdDhBa1o5dDFfbnFGXy1WYkFKTG1GOEtKUjBvS01Pc1VzTGtLbFBiYWR4U1dib01JdnZ1cnBfdlFxcGtObjdqSzZTRnE5Mml0WWZlMVJWLVJoVkl0Y3h1eXlJRDU?oc=5</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4180,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4189,22 +4190,22 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>RTX 5080 할인에 CPU 쿨러까지…조텍, 탁탁몰 특가 행사</t>
+          <t>생후 2개월 딸 때려 숨지게 한 친부 구속 갈림길‥"죄송하다"</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>RTX 5080 할인에 CPU 쿨러까지…조텍, 탁탁몰 특가 행사  뉴스탭Google 뉴스에서 헤드라인 및 의견 더보기</t>
+          <t>생후 2개월 딸 때려 숨지게 한 친부 구속 갈림길‥"죄송하다"  MBC 뉴스“잠투정한다고” 생후 2개월 딸 숨지게 한 40대 친부 구속 갈림길  경기일보2개월 영아 멍든 채 숨져..."안 자고 울어 때렸다" [뉴스퀘어 2PM]  YTN오산 2개월 여아 살해 사건 수사 중인 경찰, 고의 ...</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>뉴스탭</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE92UmZLWFY0bG9iOEZPUjVtYTZjcnBNMkRteFZUY2ZkZ2xYaVlKS3lvRG5UMENyNGVMSkxaYUxIREo2ZjdSSjZlY2FFeEZuU1M4NF9EY0w5dU9wZWhBN1VucjB0ZGg5bmUtNmI4SA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBnRzZabG1wTjhuTjNENmh4OGllVHB3bzJDMmdjWEhualNhYUFJNG9vN2ZyTGx5UjVHTWZBZ0E0bklWZnNBakhmVmVzbVJpaENwSl9sR25IRXpoSXQwLXp2a2RESmxEQ1RJUTRPeWtIaElvY1hadGNF0gF3QVVfeXFMUE5PNHVOWnU4N3NzNEdpR3pLMnlDWTk1NGRQWmdZeFEtU0JvMFdERTZwYnZXQ1Z5dEhQWVdaeTVrcXlXVFo4N2JfaG5sdEdNTGo4NWg5X1pwcUttN3p4OHhFZ1ptNnhHVEk0anJ5WW5JbEhTY0VJcUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4217,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4226,12 +4227,12 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>콘솔게임 보안까지 뚫은 AI, 해적판 등장에 업계 '발칵'</t>
+          <t>"학대 정황 없어 안전" 판단했지만…비극 못 막은 경찰</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김주환 기자 = 인기 콘솔 게임과 플랫폼의 철통 같은 데이터 보안이 에이전틱 인공지능(AI) 고도화에 잇달아 뚫리며 해적판이 ...</t>
+          <t>(제주=연합뉴스) 백나용 기자 = 제주에서 부녀가 차 안에서 숨진 채 발견된 사건과 관련해 경찰이 아동학대 의심과 실종 신고에 따른 조사·면담과...</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4241,7 +4242,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014079700017</t>
+          <t>https://www.yna.co.kr/view/AKR20261014088500056</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4254,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4263,12 +4264,12 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>'월가 족집게' 댄 아이브스 "테슬라·스페이스X 내년 합병 가능성 80%"</t>
+          <t>이진호 원자력환경공단 이사장 취임…"국민 신뢰받는 기관으로"</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 정회인 기자 = 월가의 대표적인 기술주 분석가인 댄 아이브스 '요크빌 아이브스' 파트너 겸 선임 전무는 엔비디아와 마이크로소프...</t>
+          <t>(경주=연합뉴스) 손대성 기자 = 이진호(61) 한국원자력환경공단 신임 이사장이 14일 경북 경주의 본사에서 취임식을 하고 업무에 들어갔다.</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4278,7 +4279,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014080500008</t>
+          <t>https://www.yna.co.kr/view/AKR20261014094000053</t>
         </is>
       </c>
     </row>
@@ -4290,32 +4291,32 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>‘이병헌♥’ 이민정, 12살 초등학생 아들 사교육 언급..“농구·수학만 시켜”</t>
+          <t>김지용 중수청장 후보 "정치검사 1호는 윤석열…한동훈도 포함"</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>‘이병헌♥’ 이민정, 12살 초등학생 아들 사교육 언급..“농구·수학만 시켜”  조선일보이민정, 아들 사교육 질문에 "농구·수학 학원만 다녀"  뉴시스‘이병헌♥’ 이민정, 12살 초등학생 아들 사교육 언급..“농구·수학만 시켜” - 조선비즈  Chosunbiz'MJ' 이민정 "어렸을 때...</t>
+          <t>(서울=연합뉴스) 이승연 기자 = 김지용 중대범죄수사청장(중수청장) 후보자가 검찰의 개혁 필요성에 동의한다는 입장을 재차 밝히며 그 배경에 윤석...</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZXdFa0RBNkNZYlBOZ1ZOUzlQWWJWbXlYbjJVUFdLeFBrSFhqcHVvMm5wWVRBMklsTm44MUJJRmMycjRCdzByYTdfTW8xLTFyaDVyN1RIdnZzSVRNOHdIeld1NW15Q2VibGZTUFE2eTlTXzR6MTdtakJ2MDZWRkk1UndvNy0xZUt0a2lRQ0dXbw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014093300004</t>
         </is>
       </c>
     </row>
@@ -4327,32 +4328,32 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>최수종, 모친상 후 끝내 눈물 “왜 쓴소리 했을까” (유퀴즈)</t>
+          <t>'채용대가 뇌물수수' 강서구의회 前의장·운영위원장 징역 5년</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>최수종, 모친상 후 끝내 눈물 “왜 쓴소리 했을까” (유퀴즈)  매일경제최수종, 모친상 발인 다음 날 녹화…"엄마에게 쓴소리했던 게 후회"  뉴시스최수종, 모친상 심경.."쓴소리 더 기억나서 마음 아파" 눈물('유퀴즈')[핫피플] - 조선비즈  Chosunbiz“쓴소리했던 기억에 눈물”...</t>
+          <t>(서울=연합뉴스) 김채린 기자 = 공무원 채용 및 계약 연장 대가로 금품을 수수한 혐의로 재판에 넘겨진 구의회 전직 의장과 운영위원장이 1심에서...</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE55YkFOMHFYNXc3S1c4MWY4T1ZHRGQxdmwzMjZFWS15d3dtaTZkdW1QbzgxUWlmaWpOcHFJVXN0RFlIcV9rU0dkX3ZpdGI5MG41ME9yeXdKVjF2Yi16cVBYZk1ic21vQQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014087100004</t>
         </is>
       </c>
     </row>
@@ -4364,32 +4365,32 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>김영광·채수빈 ‘나를 충전해줘’, 공개 3일 만에 넷플릭스 글로벌 비영어권 3위</t>
+          <t>평택 아파트 지하실 화재…2살 여아 등 11명 중경상(종합)</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>김영광·채수빈 ‘나를 충전해줘’, 공개 3일 만에 넷플릭스 글로벌 비영어권 3위  스포츠동아차우민, '최애의 사원' 이어 '나를 충전해줘'까지…로맨스 연타 흥행 예고  YTN‘국민엄마’ 김미경, 백발됐다…이번엔 재벌가 회장 변신(‘나를 충전해줘’) - 조선비즈  Chosunbiz‘나를 ...</t>
+          <t>(평택=연합뉴스) 김지원 기자 = 경기 평택시의 한 아파트 지하에서 불이 나 2살 여아를 포함한 11명이 중경상을 입었다.</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>스포츠동아</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Ra1M4ZWNJS21PN3QtYnBCU3V4bnZoRm44Z2ZITHR1Z1lkUXZqZ2RVWTN1ZU0xWWRkZkJRVlVvOXQzanpDekVYcnBvWDJ0ekRlWElHZVFmVDVOT0IwWnpBbDlPNzk0WmtGdm1TTGZ3?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014089151061</t>
         </is>
       </c>
     </row>
@@ -4401,32 +4402,1771 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>[게시판] 강남소방서, 서울시의원 '소방관의 하루' 체험 행사</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>▲ 강남소방서는 강신욱 서울시의원과 지난 9일 '소방관의 하루' 행사를 했다고 14일 밝혔다. 강 시의원이 화재 출동·주택 감지기 설치·산불 훈...</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014093200004</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>성동구, 가을 중랑천서 '걷고 듣는' 정원 프로그램 운영</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 정준영 기자 = 서울 성동구(구청장 유보화)는 가을을 맞아 '중랑천 정원투어'와 '중랑천 사운드캠프' 프로그램을 운영한다고 1...</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014092700004</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>[담양소식] 어린이 놀이공간 조성 국비 확보</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>(담양=연합뉴스) 전남광주통합특별시 담양군은 행정안전부의 '2026년 지역맞춤형 저출산 대응 공모사업'에 선정돼 특별교부세 5억원을 확보했다고 ...</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014093100054</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>'마약 투약 후 시내버스 운전' 40대 기사에 징역 2년 6개월</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>(안산=연합뉴스) 최해민 기자 = 필로폰을 투약한 채 수많은 시민이 타는 시내버스를 운전한 중국 국적의 40대 버스 기사에게 실형이 선고됐다.</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014075300061</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>전북도, 농기계 임대사업 예산 작년보다 16% 증가</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>(전주=연합뉴스) 임채두 기자 = 전북특별자치도는 올해 농기계 임대사업에 지난해보다 11억원(16%) 늘어난 78억원을 투입, 농기계 임대 기반...</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014090400055</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>곡성군, 하와이 교류 연계 고향사랑기부 사업 발굴</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>(전남광주=연합뉴스) 박철홍 기자 = 전남광주통합특별시 곡성군은 미국 하와이 카운티와의 자매결연을 활용해 청소년 교육 분야 고향사랑기부 사업과 ...</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014089600054</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>우상호 "원주 옛 종축장 부지, 시민 휴식 공간으로 우선 개방"</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>(춘천=연합뉴스) 이재현 기자 = 30년 가까이 개발계획만 반복된 강원 원주시 반곡동 옛 종축장 부지를 우선 시민 휴식 공간으로 개방하고, 향후...</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014088700062</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>"고객 마음을 훔쳐라"…온·오프 넘나드는 증권가 MTS '전면전'</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>"고객 마음을 훔쳐라"…온·오프 넘나드는 증권가 MTS '전면전'  연합인포맥스iM증권, MTS 새 단장…내 투자정보 한눈에 본다  뉴시스[게시판] 키움증권, MTS에 신규 국내주식 주문 화면 도입  연합뉴스키움증권, 국내주식 신규 주문 화면 오픈…차트·잔고·ETF 한눈에  전자신문iM...</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9oWi1hTHRMcW85NnlGU1pWSmZ2a1RiMS00VzhXTGxkbGVudTljV3Ywbzl0V3VxYV9adExGYVF1d0lZUVpXNEliYjVoVVA5b1p4ZnVaWDRNVkIxVlR0U2RLT0FNTnN2VWlTam1vc1VBemw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>삼전닉스 폭락에도 "지금이 저점"…'W자 반등' 전망한 이유 [분석+]</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>삼전닉스 폭락에도 "지금이 저점"…'W자 반등' 전망한 이유 [분석+]  한국경제“이젠 반도체 미련 버려야?”...내년 증시 주도주 바뀌나  매일경제삼성證 "메모리 가격 상승 둔화해도 이익 성장 가능…'삼전닉스' 매수 유지"  연합인포맥스반도체주 반등 언제쯤…“소부장이 투자 대안”  마...</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9vTllzX2VGdExfcjB2aUM4dG8zNVY3TmFLZVQxV3JxSzNqZ3lGX0sxMnRIUjRUNzZBaW9mdEtxM2RQNDVYYTI0eVB6dTNaQURQVEZwZE1LaTJYQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>부활한 '재계 저승사자' 1호 사건…대상·오뚜기·CJ제일제당(종합)</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>(세종=연합뉴스) 송정은 기자 = 새로 출범한 공정거래위원회 중점조사기획단이 1호 사건으로 식품업체 담합 사건을 조사하고 있다.</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014091451002</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>디지털엑스, 내달 미래에셋증권 본사 센터원으로 이전</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 유동현 기자 = 미래에셋그룹 가상자산 거래소 디지털엑스가 다음 달 미래에셋증권[006800] 본사로 사무실을 이전한다고 14일...</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014092600002</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>박홍근 "정책기획 역량이 조직 성패 좌우…체질 개선해야"</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>(세종=연합뉴스) 이대희 기자 = 박홍근 기획예산처 장관은 14일 "정책기획 역량이 조직의 성패를 좌우한다"며 강도 높은 조직체질 개선을 간부들...</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014092100002</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>[1보] 공정위 중점조사기획단 1호 대상·오뚜기·CJ제일제당 현장조사</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>(</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014091400002</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>국고채 금리 일제히 상승…3년물 장중 연 3.883%</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 14일 국고채 금리가 일제히 상승하고 있다.</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014091100008</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>삼성전자, 기후부 장관에 고효율·저탄소 주거 솔루션 제시</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 조성흠 기자 = 삼성전자는 14일 김성환 기후에너지환경부 장관에게 히트펌프 방식의 냉난방 솔루션과 인공지능(AI) 기반 에너지...</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014085100003</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>포천시-차의과학대학, 지역사회 건강증진 업무협약</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>(포천=연합뉴스) 노승혁 기자 = 경기 포천시보건소는 차의과학대학교 스포츠의학연구원과 '지역사회 건강증진 및 포CHA건강프로젝트 운영을 위한 업...</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014086500060</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>카카오뱅크 "18일 새벽 금융거래 일시 중단…전산시스템 점검"</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이도흔 기자 = 카카오뱅크[323410]는 오는 18일 새벽 전산시스템 정기 점검으로 금융거래를 일시 중단한다고 14일 밝혔다...</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014086400002</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>하나은행, 6억달러 규모 달러화 선순위채 발행</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 채새롬 기자 = 하나은행은 총 6억 달러 규모의 미 달러화 선순위 채권을 발행했다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014084900002</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>반도체산단 입지 용인 처인지역 '사통팔달' 도로망 구축 잰걸음</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>(용인=연합뉴스) 김광호 기자 = 원삼면과 남사·이동읍 일대에 초대형 반도체 산업단지가 조성 중인 경기 용인시 처인구의 주요 도로망 구축 사업이...</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014075200061</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>[단독] 금융권 비상인데…새마을금고, 해킹 당하고도 60시간 몰랐다</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>400여명 이름 등 개인정보 유출 외부서 공격 IP 공유받아 인지 금융권 해킹 경계령 내렸지만 계속되는 감독 사각지대 논란새마을금고가 해킹 공격을 당하고도 약 60시간 가까이 이를..</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12175452</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>임신 위한 ‘적절한 성관계 횟수’는?…“‘이 시기’ 놓치지 않아야” [라이프+]</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>임신 위한 ‘적절한 성관계 횟수’는?…“‘이 시기’ 놓치지 않아야” [라이프+]  나우뉴스</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>나우뉴스</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5iTEVvT21uTXFZT251dWVLUFg5Q0VGWnlKaEhhWmpjMUNhTi1ObzdyQ05DcjJNLUpHTXNCbHc5ekxrRFRma2p0S2FSRFBYUUtjS191MVdvNEZ1RG00ZVBxTV9jTmljbW1HQzUtRmdrRWM?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>인니 11년 만에 최악의 산불…연무로 항공 진화 1주일째 난항</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>인니 11년 만에 최악의 산불…연무로 항공 진화 1주일째 난항  연합뉴스인니 보르네오섬, 오랜 산불에 서식지 잃은 오랑우탄 46마리 구조  뉴시스인니 대규모 산불 연무에 말레이 조호르州 학교 1198곳 최소 16일까지 휴교  아시아투데이[포토] 인니 깨끗한 공기는 언제쯤  뉴스1집단 대...</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9acHV4TGVfM016VEJxMVlXeVNOVWNkMFM3aXBEamE4emhrOGlyeTB3NnRlSG13RUt4dlAza1FVT3NNYi1SMHh1cTh4UmtWY3ZmRGZ2LVY3MVlGdTDSAWBBVV95cUxQNHpFNHBZSUwtU2pZQjh4YXFGR1pDRnpMU3REcUdVOUp4dnlXU09oZ2I0bmRocTRLNk5ReHlMYWRmcWtRLU1DekxTRTVqdWc1X3FTdmJxMGR2U2tfUUNWZnE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>MLB 휴스턴 감독, 계약 기간 중 시애틀 구단 감독 면접</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장현구 기자 = 미국프로야구 메이저리그(MLB) 휴스턴 애스트로스의 조 에스파다 감독이 계약 기간 중 구단의 승낙을 받아 같은...</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014094100007</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>중국 9월 수출 36.3% 급증…수입은 31.0% 늘어</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>(상하이=연합뉴스) 차병섭 특파원 = 세계적인 인공지능(AI) 투자 붐 속에 지난달 중국의 수출이 30% 넘게 급증한 것으로 집계됐다.</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014092900089</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>미 대학서 '동료 음료에 독' 中유학생 도피하다 공항서 체포</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김승욱 기자 = 미국 대학교에서 동료 대학원생의 음료에 독극물을 타 중상을 입힌 뒤 중국으로 도피하려던 중국인 유학생이 경찰에...</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014091800009</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>오라클, 데이터센터용 가스관 승인 신속처리 촉구</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 설원태 기자 = 오라클은 미국 뉴멕시코주에서 추진중인 대규모데이터센터 구축 프로젝트에 필요한 천연가스관 건설을 신속하게 승인해...</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014083000009</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>中 9월 생산자물가 5% 올라 4년여만 최고…소비자물가는 0.9%↑</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 권숙희 기자 = 국제유가와 원자재 비용 상승 속 중국의 지난달 생산자 물가가 가파르게 올라 4년여만에 최고 수준을 기록했다.</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014088400009</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>반크 '아프리카인이 삶의 주체'인 후원 광고 찾는다</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 박성진 기자 = 사이버 외교사절단 반크(단장 박기태)가 아프리카 사람들을 외부의 도움을 기다리는 '수혜자'로만 반복해 보여주는...</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014087500898</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>외국인 인력 부족에 '정원 돌려막기' 나선 日…급식·요양 지원</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>(도쿄=연합뉴스) 조성미 특파원 = 일본 정부가 체류 허가를 내준 외국인 인력 쿼터의 관리를 강화하면서 일부 업종의 인력 확보에 차질이 빚어지자...</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014086300073</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>[영상] 해킹에 80도까지 치솟은 냉장고…"다 녹았다" 프랑스 '발칵'</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 냉장고 신선식품 칸이 텅텅 비었고 냉동고에서도 상품을 찾아볼 수 없습니다. '기술적인 문제로 냉장고 안의 신선식품을 제공할 수...</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014084300704</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>줘룽타이 대만 총리 "中 패권이 전 세계 반감 불러"</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>(타이베이=연합뉴스) 김철문 통신원 = 라이칭더 대만 총통의 지난 10일 건국기념일 연설 이후 중국이 군사적, 외교적 압박을 강화하는 가운데 줘...</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014079900009</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>인니 11년 만에 최악의 산불…연무로 항공 진화 1주일째 난항</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>(자카르타=연합뉴스) 손현규 특파원 = 11년 만에 최악의 산불로 몸살을 앓는 인도네시아에서 연무로 인해 항공 진화 작업이 1주일 넘게 차질을 ...</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014083800104</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>[영상] 사우디, 후티 연료·군사시설 전격 공습…"공항 피격 보복"</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 사우디 주도 연합군이 후티 반군 측이 장악한 예멘 수도 사나 등지의 주요 석유 시설과 군사 지원 시설을 전격 공습했습니다.</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014080700704</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>캐나다 전 부총리 "트럼프, 동맹 압박하려 CEO들 협박"</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 이성한 기자 = 미국 정부가 동맹국 기업의 최고경영자(CEO)와 비즈니스 리더들을 막후에서 위협하는 방식으로 동맹국을 백악관의...</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014082500009</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>코드 이식·AI 실험 전담… MS 엑스박스, R&amp;D 조직 신설</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>코드 이식·AI 실험 전담… MS 엑스박스, R&amp;D 조직 신설  IT조선엑스박스, 신기술 실험조직 ‘엑스박스 랩스’ 출범  지디넷코리아게임 넘어 디즈니처럼… MS, 엑스박스 엔터 사업부 ‘XP’ 신설  IT조선Xbox, 영화, TV, 라이브 이벤트 및 소비재를 전담하는 새로운 부서 'X...</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>IT조선</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE43aDVmbHg3OUM2aTA5clJXZXJIbDFjNGQyclpiLTJ6Ql9HaDJYTHktZkgtQkNhbHVjWi1ENlJ6bkl1QUZ6WEZEZFVBZmw5a3NtREVlMFc4UHNUd0FpTnppaWk4U1JHUDdray14S1FpM3rSAXRBVV95cUxORmZUbmMtYVlXUTNYSWxVUFhyLXlwazE2T1R6X0NjQUZYbm5NQVRXenBtcFR6eFZMa05Xd3AyMVN3VFExOTZYNVJOLVdrSkliN1ZHMFV0TjNVbEJ2SWkzRlBteDdrTnpaaEgybDctbk1wUkMwYg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상  주간한국Google 뉴스에서 헤드라인 및 의견 더보기</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>주간한국</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBfeGtUZl96V1ZLamFndzNRODRtVTdpRlQyV1g0VE5ZS3BBdlYwWkhGZk92VmxSeDJvLW1mWE9PTWl4VFgzM3p3UC1oTHZOWmZuX1N5M1pfNUQ2ME50dU1VWDNOY0lEeGNkcnJhSVNGUTfSAXRBVV95cUxNMFFsQS1KVzBucVd4Y2JGRTRCdWpOU2c5dkRXY2dRdkJ1Y1phV2FjSzg0Z2dfWUZUTS1NaW1wc3ZySUFhQkY5UU9EOW5KMXVEcVkxNU1yWktpRlBuN1RUWXpGTG4zZWRIOTNMa3ROaENtY05GeQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>삼성 반도체 부스 찾은 하정우 부위원장 "AI반도체 로드맵 확인"(종합)</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 김민지 강태우 기자 = 하정우 국가AI전략위원회 부위원장은 14일 서울 코엑스에서 열린 '제28회 반도체대전'(SEDEX 20...</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014042351003</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>[옥천소식] 15일 공설시장서 '우리동네 문화장날' 행사</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>(옥천=연합뉴스) 충북 옥천군은 이달 15일 옥천공설시장에서 '우리동네 문화장날' 행사를 연다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014091700064</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>아트광주 22일 개막…12개국 국내외 거장 작품 출품</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>(전남광주=연합뉴스) 장아름 기자 = 호남권 최대 미술시장인 제17회 광주국제아트페어 '아트광주'가 오는 22일부터 25일까지 전남광주 김대중컨...</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014089800054</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>[전남광주소식] 롯데백화점 11월8일까지 김장김치 예약</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>(전남광주=연합뉴스) 롯데백화점 광주점은 지하 1층 올가매장에서 11월8일까지 김장 김치 사전 예약행사를 한다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014088000054</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>말로 지시하면 AI가 광통신망 알아서 설정…'로컬LLM' 기술 확보</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>(대전=연합뉴스) 김준호 기자 = 한국전자통신연구원(ETRI)은 사용자가 자연어로 원하는 네트워크 동작을 지시하면 대규모언어모델(LLM)이 이를...</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014087300063</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>강릉커피거리 350m 노천카페로…21일 커피축제 개막</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>(강릉=연합뉴스) 유형재 기자 = '제18회 강릉커피축제'가 21∼25일 강릉커피거리와 강릉시 일원에서 열린다.</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014086200062</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>괴산군, 굴착기 등 불용 임대농기계 19대 공개 매각</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>(괴산=연합뉴스) 박재천 기자 = 충북 괴산군은 영농 자재비 상승 등으로 어려움을 겪는 농가들의 경영 부담을 덜어주고 농기계 활용을 극대화하기 ...</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014083200064</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>연예/대중문화</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>문체위, 이임생·이동국 국감증인 의결…암살자(들) 채택은 불발</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>문체위, 이임생·이동국 국감증인 의결…암살자(들) 채택은 불발  연합뉴스국민의힘 청년당원, 박정희대통령기념관에서 영화 '암살자(들)' 규탄  뉴시스[시론담론] 사실과 진실 사이  제민일보[기고]표현의 자유 뒤에 숨겨진 역사적 책임  경상일보'역사 왜곡' 암살자(들) 왜 보냐고 한 딸이 ...</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFB6ZjR1UU9sRTJ0djlRUTFyby0yeHNKWHNPNGVadEV1dTFiZTQ2VURiLTRKSUZnMnE1NjF0MDMtNFFjQzhIWTRqQ09CUUVFaTFoRENZbm94LXhBM0HSAWBBVV95cUxQdDZMM2dvcE5CeXd2Nkc2NThUWnZLTTQwNFJzamwtWWtiWUVFbThsOVZqc29uZ3Z4M25VZ25Fc29ZQVc3V04xMmRaUHZaY2VLMXZtRnppQVBUT3BtLUtqbEE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>박하선, 6년 만에 SBS 라디오 '씨네타운' 하차…"연기에 집중"</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>박하선, 6년 만에 SBS 라디오 '씨네타운' 하차…"연기에 집중"  연합뉴스[단독] 박하선, '씨네타운' DJ 6년만에 떠난다…본업 집중  뉴스1박하선, ‘박하선의 씨네타운’ 청취자들에게 작별 인사  스포츠경향박하선, 6년만에 아쉬운 이별 '씨네타운' 떠난다.."연기 집중" [공식] ...</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5LTDRGSEZFSnJlTk9qUnU0ZWVVZXlvczF2WU56TEp5RzR2NlVielBndUE5cjFQeWNjMGF6RGlnT0d0Vkg4clZPVVpiZk0zZ1l3VDA1SG9vb00yZWvSAWBBVV95cUxQNzdVUEdmWTAzRTVDM19CeUFYUWhwS2FfcHhVUVpQdDlEMjF0ZThUYVFTRUpJZEsxX1BMeDZvSTRhMzB5SzNNVUdXdDFxSS11TlpwazhJMzAzV09BTkE4YWU?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>‘계약결혼’ 음주·흡연 갈등 시작</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>‘계약결혼’ 음주·흡연 갈등 시작  BNT뉴스'계약결혼' 남편 담배 냄새에 질색 "안대에서도 냄새나"  뉴시스흥행신화 PD도 0%대 굴욕...새 판 짠 남규홍 ‘계약결혼’ 아쉬운 초반 성적표 [SC이슈]  조선일보16기 상철, 암 수술한 영숙에 술 권유 "한 캔 정도는…"  파이낸셜뉴스...</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>BNT뉴스</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9RbjBZcjlhWHUtcDdJb3V3Q1VlWU9CVTBWSXNzaURtb05heENLNzJ1aHZJM3BqSFBjd2p0WTU0Ym5TODhVSjV5LWxvXzM3LWEyNmlBWVcyRVNhLTRLbEM3VzRpQ1M?oc=5</t>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>콘진원, 뉴욕 코믹콘서 Ｋ-게임 알려…340만달러 수출 상담</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>콘진원, 뉴욕 코믹콘서 Ｋ-게임 알려…340만달러 수출 상담  지디넷코리아[르포] 뉴욕 달군 한국 웹툰…韓작가 사인회에 3시간 대기줄  연합뉴스콘진원, '뉴욕 코믹콘' 韓 공동관 성료…상담액 45억 기록  뉴스핌네이버웹툰, 뉴욕 코믹콘 5만명…'포그랜드' 부스  뉴스1"울버린으로 변신했...</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>지디넷코리아</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBOQ1U1TGNZQnA2RDlXWm1lUEcwendSV2FKVm5ZTUlXaVZDakhGX0Z3aVB6LUlwUmhlUzRsN2EzMXhGSHJ5aXppNzI3Q1lnTTVBTmxEbXJR?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>초소형 말 '윌리'·가수 추혁진, 이천시 홍보대사 위촉</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>(이천=연합뉴스) 김광호 기자 = 경기 이천시는 초소형 말 '윌리'와 가수 추혁진을 시 홍보대사로 위촉했다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014089900061</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>박하선, 6년 만에 SBS 라디오 '씨네타운' 하차…"연기에 집중"</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>(서울=연합뉴스) 장진리 기자 = 배우 박하선이 다음 달 1일 방송을 끝으로 6년간 진행한 SBS 라디오 파워FM '박하선의 씨네타운'에서 하차...</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014086700005</t>
         </is>
       </c>
     </row>
@@ -5754,12 +7494,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+31,250.0원 (+15.13%)</t>
+          <t>+31,750.0원 (+15.38%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>235,500원</t>
+          <t>236,000원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5769,12 +7509,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>229,500원</t>
+          <t>230,000원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+9.2%</t>
+          <t>+9.0%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -5784,7 +7524,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>RSI 38.0로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 38.3로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5798,21 +7538,21 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>38</v>
+        <v>38.3</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>9월 ICT 수출 751억달러 '역대 최대'…반도체가 80% 견인 (연합인포맥스)</t>
+          <t>삼전닉스 폭락에도 "지금이 저점"…'W자 반등' 전망한 이유 [분석+] (한국경제)</t>
         </is>
       </c>
     </row>
@@ -5839,32 +7579,32 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1,475,000원</t>
+          <t>1,470,000원</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+372,000.0원 (+33.73%)</t>
+          <t>+367,000.0원 (+33.27%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1,460,000원</t>
+          <t>1,455,500원</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1,706,000원</t>
+          <t>1,705,500원</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>1,423,500원</t>
+          <t>1,418,500원</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>+17.2%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -5874,7 +7614,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>RSI 34.2로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 33.7로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5888,16 +7628,16 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -5929,17 +7669,17 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>319,500원</t>
+          <t>320,000원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-172,000.0원 (-34.99%)</t>
+          <t>-171,500.0원 (-34.89%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>313,000원</t>
+          <t>313,500원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -5949,12 +7689,12 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>303,500원</t>
+          <t>304,000원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+22.2%</t>
+          <t>+22.0%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -5978,16 +7718,16 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>26.1</v>
+        <v>26.6</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
@@ -6019,12 +7759,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>109,500원</t>
+          <t>110,000원</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-39,500.0원 (-26.47%)</t>
+          <t>-39,300.0원 (-26.34%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -6039,12 +7779,12 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>104,000원</t>
+          <t>104,500원</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+17.8%</t>
+          <t>+17.5%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -6068,16 +7808,16 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -6114,7 +7854,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-19,900.0원 (-9.88%)</t>
+          <t>-19,850.0원 (-9.85%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -6158,7 +7898,7 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -6167,12 +7907,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>콘진원, 뉴욕 코믹콘서 Ｋ-게임 알려…340만달러 수출 상담 (지디넷코리아)</t>
         </is>
       </c>
     </row>
@@ -6199,17 +7939,17 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>32,000원</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-16,200.0원 (-33.68%)</t>
+          <t>-16,100.0원 (-33.47%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>31,300원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -6219,12 +7959,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>30,300원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>+10.8%</t>
+          <t>+10.5%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -6248,21 +7988,21 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>34.4</v>
+        <v>35.4</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>카카오뱅크 "18일 새벽 금융거래 일시 중단…전산시스템 점검" (주요언론)</t>
         </is>
       </c>
     </row>
@@ -6289,27 +8029,27 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>182,000원</t>
+          <t>182,500원</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-7,419.049999999988원 (-3.91%)</t>
+          <t>-6,919.049999999988원 (-3.65%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>178,500원</t>
+          <t>179,000원</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>191,500원</t>
+          <t>192,000원</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>173,000원</t>
+          <t>173,500원</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -6338,16 +8078,16 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>50.3</v>
+        <v>51.3</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -6379,17 +8119,17 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>835,000원</t>
+          <t>845,000원</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-688,000.0원 (-45.17%)</t>
+          <t>-678,000.0원 (-44.52%)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>818,500원</t>
+          <t>828,000원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -6399,12 +8139,12 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>793,000원</t>
+          <t>803,000원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>+38.9%</t>
+          <t>+37.3%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -6428,16 +8168,16 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>29.3</v>
+        <v>30.6</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -6469,32 +8209,32 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>422,500원</t>
+          <t>424,000원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+22,500.0원 (+5.62%)</t>
+          <t>+23,750.0원 (+5.94%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>372,000원</t>
+          <t>372,500원</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>422,500원</t>
+          <t>424,000원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>414,000원</t>
+          <t>415,500원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>+13.8%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -6504,7 +8244,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 71.1, 20일선 이격도 +13.5%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 71.4, 20일선 이격도 +13.8%로 단기 과열권, 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -6518,16 +8258,16 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>+13.8%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
@@ -6559,17 +8299,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>309,000원</t>
+          <t>310,000원</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>-52,500.0원 (-14.52%)</t>
+          <t>-51,500.0원 (-14.25%)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>303,000원</t>
+          <t>304,000원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -6579,12 +8319,12 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>293,500원</t>
+          <t>294,500원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+9.9%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -6608,16 +8348,16 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>45.3</v>
+        <v>46</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
@@ -6712,7 +8452,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>'월가 족집게' 댄 아이브스 "테슬라·스페이스X 내년 합병 가능성 80%" (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -6892,7 +8632,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>'월가 족집게' 댄 아이브스 "테슬라·스페이스X 내년 합병 가능성 80%" (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
     </row>
@@ -7214,12 +8954,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6,123.61</t>
+          <t>6,137.60</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+88.26 (+1.46%)</t>
+          <t>+102.25 (+1.69%)</t>
         </is>
       </c>
     </row>
@@ -7241,12 +8981,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>832.41</t>
+          <t>839.61</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-4.62 (-0.55%)</t>
+          <t>+2.58 (+0.31%)</t>
         </is>
       </c>
     </row>
@@ -7460,27 +9200,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,538,000원</t>
+          <t>112,951,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>111,975,000원</t>
+          <t>112,386,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,541,000원</t>
+          <t>121,987,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,573,000원</t>
+          <t>110,593,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7517,27 +9257,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3,384,000원</t>
+          <t>3,393,000원</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3,357,000원</t>
+          <t>3,366,000원</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3,587,000원</t>
+          <t>3,596,500원</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3,265,500원</t>
+          <t>3,274,000원</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -7552,7 +9292,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>RSI 46.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 47.6로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -7574,32 +9314,32 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>145,000원</t>
+          <t>145,600원</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>143,800원</t>
+          <t>144,400원</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>155,800원</t>
+          <t>155,900원</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>139,900원</t>
+          <t>140,500원</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>+8.3%</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -7609,7 +9349,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>RSI 47.3로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 48.2로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -7792,7 +9532,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -7862,7 +9602,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -7871,12 +9611,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>가장 저평가된 전력기기</t>
+          <t>우려도 있지만 너무 잠잠한 주가</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -7891,37 +9631,37 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단</t>
+          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다 큰 이익 회복에 주목</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
+          <t>2026-10-14_신한투자증권_HMM_우려도 있지만 너무 잠잠한 주가.pdf</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2,350.8십억원</t>
+          <t>14,179.9십억원</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>252.8십억원</t>
+          <t>2,497.7십억원</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2,595.2십억원</t>
+          <t>14,293.1십억원</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>271.7십억원</t>
+          <t>1,812.7십억원</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>3Q26 매출 4조 802억원(+51%, 이하 YoY) 및 영업이익 1조 42억원(+</t>
         </is>
       </c>
     </row>
@@ -7941,12 +9681,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>일진전기</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>우려도 있지만 너무 잠잠한 주가</t>
+          <t>가장 저평가된 전력기기</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -7961,37 +9701,37 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다 큰 이익 회복에 주목</t>
+          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_HMM_우려도 있지만 너무 잠잠한 주가.pdf</t>
+          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>14,179.9십억원</t>
+          <t>2,350.8십억원</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2,497.7십억원</t>
+          <t>252.8십억원</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>14,293.1십억원</t>
+          <t>2,595.2십억원</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1,812.7십억원</t>
+          <t>271.7십억원</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>3Q26 매출 4조 802억원(+51%, 이하 YoY) 및 영업이익 1조 42억원(+</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -8072,7 +9812,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -8142,7 +9882,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -8212,7 +9952,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -8282,7 +10022,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -8352,7 +10092,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -8426,7 +10166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8553,7 +10293,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -8615,7 +10355,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -8739,7 +10479,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -8801,12 +10541,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>839,000원</t>
+          <t>849,000원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -8863,7 +10603,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -8890,50 +10630,112 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>005930.KS</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>238,000원</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>235,500원</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>257,000원</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>229,500원</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 진행 중 (당일 포지션 구축)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>+1.3%</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>238,500원</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>000660.KS</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>1,475,000원</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>1,460,000원</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1,706,000원</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>1,423,500원</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>⏳ 진행 중 (당일 포지션 구축)</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>+1.0%</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>1,475,000원</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>1,470,000원</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
@@ -9077,7 +10879,7 @@
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>데스트라 멀티 대체 투자 펀드, 자사주 매입 프로그램 도입·월 배당금 주당 0.115달러로 인상</t>
+          <t>“역시 주주환원은 뒷전입니까”…코스피 자사주 매입, 삼전닉스 뺐더니 줄었다</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -9087,17 +10889,17 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>매일경제 마켓</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 19:52:27 GMT</t>
+          <t>Sun, 11 Oct 2026 11:51:10 GMT</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1lemt2YTFaYUFFeVI4cVJZbjFYOHpWLVJmNTUxN3huQlRtYUVHYXplTUpvQktSZFdKenhkMl9PYXlNci1RbHNtTUdQdXgxelpjaEJVbWNjVmFndWFiaV9KZFAxd2ozbVZXVUd4MHFPNlZYT0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE0zXzFYa0xGekFCVWtnODd6QVRIRmp1MnFLcXhBWWVadVdXQWZaY3lGcGg3WUl1dzY4M1R1cTBWV1h1a0JBbXdGV3Y0aC1KV25lRmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9120,7 +10922,7 @@
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>“역시 주주환원은 뒷전입니까”…코스피 자사주 매입, 삼전닉스 뺐더니 줄었다</t>
+          <t>데스트라 멀티 대체 투자 펀드, 자사주 매입 프로그램 도입·월 배당금 주당 0.115달러로 인상</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -9130,17 +10932,17 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>매일경제 마켓</t>
+          <t>데이터투자</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Sun, 11 Oct 2026 11:51:10 GMT</t>
+          <t>Tue, 13 Oct 2026 19:52:27 GMT</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE0zXzFYa0xGekFCVWtnODd6QVRIRmp1MnFLcXhBWWVadVdXQWZaY3lGcGg3WUl1dzY4M1R1cTBWV1h1a0JBbXdGV3Y0aC1KV25lRmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1lemt2YTFaYUFFeVI4cVJZbjFYOHpWLVJmNTUxN3huQlRtYUVHYXplTUpvQktSZFdKenhkMl9PYXlNci1RbHNtTUdQdXgxelpjaEJVbWNjVmFndWFiaV9KZFAxd2ozbVZXVUd4MHFPNlZYT0U?oc=5</t>
         </is>
       </c>
     </row>
@@ -9372,6 +11174,220 @@
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1MVmRGS1NqcEJobXNpM01fNTlJbV9MeFZUeXBTVktGWV9XOWFlMHFET09BeW1rQ1RJdzVCR0I1OXM1UkpxM3Nnazk4RnBPbC1EaGFxM0FpVVpqYzZPRnlGb0plTEwyYmZDSXJXNW8yYmh5M0k?oc=5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="53" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>수집일자</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>트랙구분</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>배지</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>스토리제목</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>핵심키워드</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>도입부훅</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>1막_발단현상</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2막_과거시초타임라인</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>3막_이면의속셈과심리</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>4막_파장과미래변화</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>언론사/출처</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>원문링크</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>경제·사회 딥다이브</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>아! 이래서 그런 거였어</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>🌐 [경제·사회 딥다이브] "아! 이래서 그런 거였어": 트럼프, 동맹 압박하려 CEO들 협박의 숨겨진 비하인드</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>트럼프, 동맹 압박하려 CEO들 협박</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>오늘 언론을 도배한 '트럼프, 동맹 압박하려 CEO들 협박' 뉴스, 겉보기엔 단순한 갈등 같지만 사실은 수년 전부터 시작된 거대한 판의 충돌입니다.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>오늘 언론사들이 일제히 보도한 사건: **[캐나다 전 부총리 "트럼프, 동맹 압박하려 CEO들 협박"]** 입니다. (서울=연합뉴스) 이성한 기자 = 미국 정부가 동맹국 기업의 최고경영자(CEO)와 비즈니스 리더들을 막후에서 위협하는 방식으로 동맹국을 백악관의...</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>사실 이 문제는 과거 수년 전부터 시장과 정책 당국 간에 누적되어 온 해묵은 과제가 특정 계기를 맞아 수면 위로 폭발한 것입니다.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>언론 헤드라인이 말해주지 않는 진짜 흑막(돈과 권력의 흐름)은 따로 있습니다. 표면적인 명분 뒤에는 이해관계자들의 치열한 득실 계산과 법·제도의 맹점을 파고든 치밀한 수싸움이 숨겨져 있습니다.</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>이 사건은 일회성 해프닝으로 끝나지 않습니다. 앞으로 한국 경제와 관련 산업의 판도를 바꿀 중요한 분수령이 될 것이며, 우리는 이해관계자들의 다음 행보를 면밀히 주시해야 합니다.</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014082500009</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>트렌드·유행 딥다이브</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>요즘 왜 이게 유행할까?</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>🔥 [트렌드·유행 딥다이브] "요즘 왜 이게 유행할까?": 블루 아카이브 품절 대란의 비밀</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>블루 아카이브</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>요즘 SNS와 거리에서 난리 난 '블루 아카이브', 사람들은 도대체 왜 여기에 줄을 서고 열광하는 걸까요?</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>지금 번화가와 온라인 쇼핑몰에서 가장 뜨거운 화두는 단연 **[GS25, '블루 아카이브'와 3차 협업…전국 팝업스토어도 운영]** 입니다. GS25, '블루 아카이브'와 3차 협업…전국 팝업스토어도 운영 매일경제 마켓</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>이 유행의 시초를 거슬러 올라가면 인플루언서와 숏폼(틱톡/릴스) 바이럴이 결정적 계기였습니다: 수영복 입은 문주님, 블루 아카이브에 '람과천청' 업데이트 월요신문 알림음과 배경 음악을 구분하는 블루아카이브 경마 사운드 안내 Calgary Roughnecks...</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>사람들이 지갑을 여는 진짜 심리는 무엇일까요? 단순한 맛이나 디자인을 넘어, '나도 경험해 봤다'는 즉각적인 소속감과 디토(Ditto) 소비 심리가 강력한 기폭제가 되었습니다.</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>이 유행은 단순한 반짝 인기에 그칠까요, 아니면 새로운 일상의 표준이 될까요? 빠르게 바뀌는 트렌드 주기 속에서 관련 업계는 벌써 다음 먹거리 선점에 나섰습니다.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>매일경제 마켓</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5oRlFmSDNxbVRUaEctLWp3SHVvbEtGeFRFajBNUndReGo0QzZNdFBacG1la0ZGR3BScW5qb091eW4xclJOQi1vYk9DVjM4NVd6cnc?oc=5</t>
         </is>
       </c>
     </row>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -15,6 +15,7 @@
     <sheet name="추천성과_검증누적" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="특수공시_누적" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="스토리딥다이브_누적" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="심층리포트_누적" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3625,32 +3626,32 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>김지용 "중수청, 외압 흔들림 없이 법·원칙 따라 공정 수사"</t>
+          <t>한미 국방장관 이달말 첫 대면 가능성...전작권 논의 주목</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>김지용 "중수청, 외압 흔들림 없이 법·원칙 따라 공정 수사"  MBC 뉴스김지용 중수청장 후보자 "약자 대상 범죄 보완수사 빈틈없이"  조선일보김민석 “각자 역할 집중해야”…‘김지용 비판’ 추미애에 [지금뉴스]  KBS 뉴스김지용 "김학의 불법출금 무리한 기소 인정…책임 없지 않아" ...</t>
+          <t>한미 국방장관 이달말 첫 대면 가능성...전작권 논의 주목 YTN 한미 전작권 이견에… SCM, 12월로 이례적 연기 조선일보브런슨 "시간도 하나의 조건"…한미 전작권 전환 협상 난항 예상 뉴스1주한미군사령관 "조건 충족시 전작권 전환 지지‥한반도 다층감지할 것" MBC 뉴스한미, SCM 일정 조율도 ‘삐그덕’…양국 국방장관 이달말 첫 대면 가능성 KBS 뉴스.</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFB5UDcySVc2Q3hrX1ZxUi1oOXVFTkJCSF9DUHZvVmVYY3BKeC0xdmN4RXVXcGxsRE45enFpYXNLcERDbVRBMWNWUHgydURaRkpTaV9KbHVqTGIwVEFTYkVXUHBzdVFMb1N3Zk80OUVzM1NRRGlNWVh30gF3QVVfeXFMUHgtOG9BQlprR3ZSc0JFeWthUFNsZ29BM0xyR2FmVm9iNkQxWm01REpPUmlPQzdHbUxobnpmVHp1ZE1ldHdRNHpZZ2h4YkFjWGREMzFWemcwUGFBY1JheDhOcHNlTzhsQ2VRUTIyWWRLbVMzZHZkU3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFByaGg5R3BoUm5yNXVJOENVOXc5cnVCdlpxdldkdFd4WFRVcDBPbmhHTlBPWnJTOUg0Q3FhYVAxV3dTSUVuNTd6N2s0VmxWWlo4NUhja1FtYVFHazRzYmRmZVVNaWtfVm5hZDdRYl9GOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3662,32 +3663,32 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>[사설]“대출 더 줄여야” “집값 급락 가능성”… LH 사장의 오지랖</t>
+          <t>UST, '청정 원전 해체' 길 열었다…신규 제염제 개발</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>[사설]“대출 더 줄여야” “집값 급락 가능성”… LH 사장의 오지랖  동아일보이성훈 LH 사장, 고양창릉 첫마을 입주 준비 점검…공공임대 품질 강화 주문  전기신문유승민 “LH사장이 집값 예측할 때인가…주택공급이나 열심히 해야”  경기일보[기자수첩]대출 없이 집 산 LH 사장의 대출 ...</t>
+          <t>원자력발전소를 해체할 때 방사성 오염물질은 제거하면서 독성 약품 사용량은 줄이고, 제염 후 남은 폐액까지 하나...</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE43QTc0VC1rSWlsSzZteVRkOXNDYU5YbmlxVjJoeVV6bFZXNmw2V1NfSklHY2JHVHVLU0pja196Ml91MXhrN3ZxTHQ5SE5ZQUZuTkRHUHVrOGUxbEhuV2phcWF3MllveFEwVzlEaEMyUDFvMHVzMlHSAWZBVV95cUxQZTUtX0dhUVdyNmw0T1JCTzQzc1NtakNnWDJ4MXZ3Vk1SaVBvRmFFakE1MjA5a3NMT0FvTWplYjFBZWF4am5zUnhnQVFHSFNpTVUweHpQMkcxZzFCZnl4Wms1MVpiVkE?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014112100063</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3700,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3709,12 +3710,12 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>국힘, 與 '신천지 의혹' 확인에 "특검·당원명부 압수수색 해야"</t>
+          <t>[속보] '1억 공천헌금' 무소속 강선우 의원 1심 징역 2년 6개월 선고</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 박수윤 조다운 기자 = 국민의힘은 14일 더불어민주당이 신천지 교인의 집단 당원 가입 정황을 자체 조사로 공식 확인하자 당원 ...</t>
+          <t>[속보] '1억 공천헌금' 무소속 강선우 의원 1심 징역 2년 6개월 선고의 핵심 내용과 시장 반응을 분석한 보도입니다.</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3724,7 +3725,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014089200001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014116600004</t>
         </is>
       </c>
     </row>
@@ -3736,32 +3737,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>교육위서 교부금 개편 도마…여야 '김민석·한동훈 자녀' 겨냥도</t>
+          <t>"국평 포기합니다"…서울 청약 넣으려다 마음 바꾼 이유</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 류미나 이율립 기자 = 국회 교육위원회가 14일 서울·인천·경기 등 수도권 교육청을 대상으로 실시한 국정감사에서는 정부의 지방...</t>
+          <t>"국평 포기합니다"…서울 청약 넣으려다. 바꾼 이유 “분양가 무서워 소형으로”…수도권 청약시장 면적별 양극화 심화 매일경제강원 아파트 9월 분양가 제곱미터에 636만 원 KBS 뉴스"국민평형 너무 비싸요"…서울 청약 80% 소형으로 쏠렸다.</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014088200001</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzR1c3Z3JwcXhPMTlOaHJtQzNmREJhdEpVOGtsZ0ZrTVI0RUVuRVV0aTVuREk4SS01d19keFBlWjhGV0VZb3lKeU84dHlQc1FiQ0RHa2lsOG9RUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3773,32 +3774,32 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>어린 딸 두고 입대한 6·25전쟁 두 호국영웅 유해 신원확인</t>
+          <t>카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 김효정 기자 = 국방부 유해발굴감식단(이하 국유단)은 각기 어린 딸을 두고 입대했다 6·25전쟁에서 전사한 고(故) 진성대 이...</t>
+          <t>카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가 연합인포맥스 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동…소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척 동아일보카카오 인적분할 앞두고 창사 첫 '그룹 공동 IR' 개최, 계열사 CEO 총출동 비즈니스포스트카카오, AI 시대 ‘신뢰·책임’ 검증 사례 나눈다.</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014085600504</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9FREp6R1lfYkJtTEhVUGZqRTdNbXBZbmNUYVpQWDN4c2M0OTZ0TV9OZzJmVW9CZFNITFdtWjNzY1RkTUpmLTYzMWgycEVFbjF6OWRpeGZFdWRjZkN0djBEeXlJVmJnZ1RSbkc4bEl5NDc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3810,22 +3811,22 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>복지위 '리밸런싱' 충돌…"회의록 공개해야"·"시장영향 우려"</t>
+          <t>모건스탠리 "한은, 10월 동결 후 11월 인상…물가 상승 압력"</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 권희원 기자 = 여야는 14일 국회 보건복지위원회 국민연금공단 국정감사에서 국민연금의 리밸런싱(자산 비중 재조정) 유예 결정 ...</t>
+          <t>모건스탠리는 한국은행이 오는 22일 금융통화위원회에서 기준금리를 연 3.0%로 동결한 후, 11월에 금리를 인...</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3835,7 +3836,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014090800001</t>
+          <t>https://www.yna.co.kr/view/AKR20261014111600008</t>
         </is>
       </c>
     </row>
@@ -3847,32 +3848,32 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>국정원 '美, 국정원장 방문거부' 보도 정정신청…이례적 법적대응</t>
+          <t>[속보] 중국 “단둥~신의주 연결 신압록강대교 15일 개통”</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 하채림 기자 = 국가정보원이 미국 국방부 산하 기관이 이종석 국정원장의 방문을 거부했다는 언론보도에 대해 이례적으로 법적 대응...</t>
+          <t>중국 “단둥~신의주 연결 신압록강대교 15일 개통” 한겨레中 신화통신 "북중 신압록강대교, 15일 공식 개통" MBC 뉴스“신압록강대교 내일 정식 개통…북·중, 개통식 합의” KBS 뉴스북·중 잇는 대교 왜 지금 열리나…북미 대화 앞두고 교류 확대? 마켓인완공부터 개통까지 12년···신압록강대교에 반영된 북·중관계 경향신문.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014084800504</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNSFZBSFp3Q2xBbzYtb29jUHllSzRBdlp0NWtKZVRkcXE0eWd4NUNvMDNqYjBicno3Mk53ZU9YalpGXzhnMW1vS0VuVy1ocEtFOHAxc29OYm93LWljYkN3SzdySlNFYlFRN1lOYk5wZmR4elZDSVJfX2U4bmEwT3hOTW13?oc=5</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3885,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3894,12 +3895,12 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>김창국 aT 사장대행 "브라질산 계란 수입, 수입선 다변화 측면"</t>
+          <t>한미반도체, 반도체대전서 HBM4용 TC 본더 등 선봬</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>(서울=연합뉴스) 한주홍 기자 = 김창국 한국농수산식품유통공사(aT) 사장 직무대행은 14일 브라질산 신선란 수입과 관련해 "수입선 다변화 측면...</t>
+          <t>한미반도체는 14일부터 16일까지 서울 강남구 코엑스에서 열리는 '제28회 반도체대전' 에...</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3909,2264 +3910,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014091000030</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>정치</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>특검, '선거용품 입찰비리' 중앙선관위 등 5곳 압수수색</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 최원정 기자 = 이태한 선거관리위원회 특별검사팀이 중앙선관위의 선거 용품 입찰 비리 의혹과 관련해 강제수사에 착수했다.</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014090600004</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>정치</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>김지용 "정치 편중되지 않게 일했다…부적격이라 생각지 않아"</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 황재하 기자 = 김지용 초대 중대범죄수사청장(중수청장) 후보자가 과거 검찰권 남용 사례들에 반대했었다고 재차 밝히면서 정치적 ...</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014089000004</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>정치</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>문체위, 이임생·이동국 국감증인 의결…암살자(들) 채택은 불발</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 박경준 기자 = 국회 문화체육관광위원회는 14일 전체회의를 열어 이용수 대한축구협회 회장 직무대행, 이임생 전 대한축구협회 기...</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014084500001</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>정치</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>LIG D&amp;A, 미국 방산 스타트업과 유도로켓 추진체계 '맞손'</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 홍규빈 기자 = LIG 디펜스&amp;amp;에어로스페이스(LIG D&amp;amp;A)가 미국 방산 스타트업 '파이어호크'와 손잡고 미국 ...</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014087800003</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>정치</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>육군 1군단, 19∼23일 파주·고양·양주서 호국훈련</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>(고양=연합뉴스) 노승혁 기자 = 육군 1군단은 군사대비태세 유지와 합동 작전 수행 능력 향상을 위해 오는 19∼23일 파주·고양·양주 등 경기...</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014087900060</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>정치</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>친청계 "허위면 책임져야"…與 '신천지 확인'에 갈등 재점화 조짐</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김정진 안정훈 기자 = 더불어민주당이 공식적으로 신천지 교인의 집단 당원 가입 사실을 확인하면서 당내 계파 갈등이 재점화하고 ...</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014078300001</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>'카이스트 러너' 유지원, 마라톤 레이스 중 사망 ...500m 남기고 '심정지' 비보</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>'카이스트 러너' 유지원, 마라톤 레이스 중 사망 ...500m 남기고 '심정지' 비보  스포츠조선황영조 ‘죽음에 이르는 러닝’ 경고···“욕심 부리지 말고, 필요하면 포기할 줄 알아야”  경향신문'서울 달리기' 마라톤대회 참가했던 20대 여성 사망  연합뉴스'서울달리기' 숨진 20대女...</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>스포츠조선</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQSTFXR09uYVhhTEJlb3BRQVg0RndvYkhVNThjcFB6VzNpdDhBa1o5dDFfbnFGXy1WYkFKTG1GOEtKUjBvS01Pc1VzTGtLbFBiYWR4U1dib01JdnZ1cnBfdlFxcGtObjdqSzZTRnE5Mml0WWZlMVJWLVJoVkl0Y3h1eXlJRDU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>생후 2개월 딸 때려 숨지게 한 친부 구속 갈림길‥"죄송하다"</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>생후 2개월 딸 때려 숨지게 한 친부 구속 갈림길‥"죄송하다"  MBC 뉴스“잠투정한다고” 생후 2개월 딸 숨지게 한 40대 친부 구속 갈림길  경기일보2개월 영아 멍든 채 숨져..."안 자고 울어 때렸다" [뉴스퀘어 2PM]  YTN오산 2개월 여아 살해 사건 수사 중인 경찰, 고의 ...</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>MBC 뉴스</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBnRzZabG1wTjhuTjNENmh4OGllVHB3bzJDMmdjWEhualNhYUFJNG9vN2ZyTGx5UjVHTWZBZ0E0bklWZnNBakhmVmVzbVJpaENwSl9sR25IRXpoSXQwLXp2a2RESmxEQ1RJUTRPeWtIaElvY1hadGNF0gF3QVVfeXFMUE5PNHVOWnU4N3NzNEdpR3pLMnlDWTk1NGRQWmdZeFEtU0JvMFdERTZwYnZXQ1Z5dEhQWVdaeTVrcXlXVFo4N2JfaG5sdEdNTGo4NWg5X1pwcUttN3p4OHhFZ1ptNnhHVEk0anJ5WW5JbEhTY0VJcUE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>"학대 정황 없어 안전" 판단했지만…비극 못 막은 경찰</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>(제주=연합뉴스) 백나용 기자 = 제주에서 부녀가 차 안에서 숨진 채 발견된 사건과 관련해 경찰이 아동학대 의심과 실종 신고에 따른 조사·면담과...</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014088500056</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>이진호 원자력환경공단 이사장 취임…"국민 신뢰받는 기관으로"</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>(경주=연합뉴스) 손대성 기자 = 이진호(61) 한국원자력환경공단 신임 이사장이 14일 경북 경주의 본사에서 취임식을 하고 업무에 들어갔다.</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014094000053</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>김지용 중수청장 후보 "정치검사 1호는 윤석열…한동훈도 포함"</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이승연 기자 = 김지용 중대범죄수사청장(중수청장) 후보자가 검찰의 개혁 필요성에 동의한다는 입장을 재차 밝히며 그 배경에 윤석...</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014093300004</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>'채용대가 뇌물수수' 강서구의회 前의장·운영위원장 징역 5년</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김채린 기자 = 공무원 채용 및 계약 연장 대가로 금품을 수수한 혐의로 재판에 넘겨진 구의회 전직 의장과 운영위원장이 1심에서...</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014087100004</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>평택 아파트 지하실 화재…2살 여아 등 11명 중경상(종합)</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>(평택=연합뉴스) 김지원 기자 = 경기 평택시의 한 아파트 지하에서 불이 나 2살 여아를 포함한 11명이 중경상을 입었다.</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014089151061</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>[게시판] 강남소방서, 서울시의원 '소방관의 하루' 체험 행사</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>▲ 강남소방서는 강신욱 서울시의원과 지난 9일 '소방관의 하루' 행사를 했다고 14일 밝혔다. 강 시의원이 화재 출동·주택 감지기 설치·산불 훈...</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014093200004</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>성동구, 가을 중랑천서 '걷고 듣는' 정원 프로그램 운영</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 정준영 기자 = 서울 성동구(구청장 유보화)는 가을을 맞아 '중랑천 정원투어'와 '중랑천 사운드캠프' 프로그램을 운영한다고 1...</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014092700004</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>[담양소식] 어린이 놀이공간 조성 국비 확보</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>(담양=연합뉴스) 전남광주통합특별시 담양군은 행정안전부의 '2026년 지역맞춤형 저출산 대응 공모사업'에 선정돼 특별교부세 5억원을 확보했다고 ...</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014093100054</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>'마약 투약 후 시내버스 운전' 40대 기사에 징역 2년 6개월</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>(안산=연합뉴스) 최해민 기자 = 필로폰을 투약한 채 수많은 시민이 타는 시내버스를 운전한 중국 국적의 40대 버스 기사에게 실형이 선고됐다.</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014075300061</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>전북도, 농기계 임대사업 예산 작년보다 16% 증가</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>(전주=연합뉴스) 임채두 기자 = 전북특별자치도는 올해 농기계 임대사업에 지난해보다 11억원(16%) 늘어난 78억원을 투입, 농기계 임대 기반...</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014090400055</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>곡성군, 하와이 교류 연계 고향사랑기부 사업 발굴</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>(전남광주=연합뉴스) 박철홍 기자 = 전남광주통합특별시 곡성군은 미국 하와이 카운티와의 자매결연을 활용해 청소년 교육 분야 고향사랑기부 사업과 ...</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014089600054</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>사회/사건사고</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>우상호 "원주 옛 종축장 부지, 시민 휴식 공간으로 우선 개방"</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>(춘천=연합뉴스) 이재현 기자 = 30년 가까이 개발계획만 반복된 강원 원주시 반곡동 옛 종축장 부지를 우선 시민 휴식 공간으로 개방하고, 향후...</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014088700062</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>"고객 마음을 훔쳐라"…온·오프 넘나드는 증권가 MTS '전면전'</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>"고객 마음을 훔쳐라"…온·오프 넘나드는 증권가 MTS '전면전'  연합인포맥스iM증권, MTS 새 단장…내 투자정보 한눈에 본다  뉴시스[게시판] 키움증권, MTS에 신규 국내주식 주문 화면 도입  연합뉴스키움증권, 국내주식 신규 주문 화면 오픈…차트·잔고·ETF 한눈에  전자신문iM...</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>연합인포맥스</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9oWi1hTHRMcW85NnlGU1pWSmZ2a1RiMS00VzhXTGxkbGVudTljV3Ywbzl0V3VxYV9adExGYVF1d0lZUVpXNEliYjVoVVA5b1p4ZnVaWDRNVkIxVlR0U2RLT0FNTnN2VWlTam1vc1VBemw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>삼전닉스 폭락에도 "지금이 저점"…'W자 반등' 전망한 이유 [분석+]</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>삼전닉스 폭락에도 "지금이 저점"…'W자 반등' 전망한 이유 [분석+]  한국경제“이젠 반도체 미련 버려야?”...내년 증시 주도주 바뀌나  매일경제삼성證 "메모리 가격 상승 둔화해도 이익 성장 가능…'삼전닉스' 매수 유지"  연합인포맥스반도체주 반등 언제쯤…“소부장이 투자 대안”  마...</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>한국경제</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9vTllzX2VGdExfcjB2aUM4dG8zNVY3TmFLZVQxV3JxSzNqZ3lGX0sxMnRIUjRUNzZBaW9mdEtxM2RQNDVYYTI0eVB6dTNaQURQVEZwZE1LaTJYQQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>부활한 '재계 저승사자' 1호 사건…대상·오뚜기·CJ제일제당(종합)</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>(세종=연합뉴스) 송정은 기자 = 새로 출범한 공정거래위원회 중점조사기획단이 1호 사건으로 식품업체 담합 사건을 조사하고 있다.</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014091451002</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>디지털엑스, 내달 미래에셋증권 본사 센터원으로 이전</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 유동현 기자 = 미래에셋그룹 가상자산 거래소 디지털엑스가 다음 달 미래에셋증권[006800] 본사로 사무실을 이전한다고 14일...</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014092600002</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>박홍근 "정책기획 역량이 조직 성패 좌우…체질 개선해야"</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>(세종=연합뉴스) 이대희 기자 = 박홍근 기획예산처 장관은 14일 "정책기획 역량이 조직의 성패를 좌우한다"며 강도 높은 조직체질 개선을 간부들...</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014092100002</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>[1보] 공정위 중점조사기획단 1호 대상·오뚜기·CJ제일제당 현장조사</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>(</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014091400002</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>국고채 금리 일제히 상승…3년물 장중 연 3.883%</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 14일 국고채 금리가 일제히 상승하고 있다.</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014091100008</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>삼성전자, 기후부 장관에 고효율·저탄소 주거 솔루션 제시</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 조성흠 기자 = 삼성전자는 14일 김성환 기후에너지환경부 장관에게 히트펌프 방식의 냉난방 솔루션과 인공지능(AI) 기반 에너지...</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014085100003</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>포천시-차의과학대학, 지역사회 건강증진 업무협약</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>(포천=연합뉴스) 노승혁 기자 = 경기 포천시보건소는 차의과학대학교 스포츠의학연구원과 '지역사회 건강증진 및 포CHA건강프로젝트 운영을 위한 업...</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014086500060</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>카카오뱅크 "18일 새벽 금융거래 일시 중단…전산시스템 점검"</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이도흔 기자 = 카카오뱅크[323410]는 오는 18일 새벽 전산시스템 정기 점검으로 금융거래를 일시 중단한다고 14일 밝혔다...</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014086400002</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>하나은행, 6억달러 규모 달러화 선순위채 발행</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 채새롬 기자 = 하나은행은 총 6억 달러 규모의 미 달러화 선순위 채권을 발행했다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014084900002</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>반도체산단 입지 용인 처인지역 '사통팔달' 도로망 구축 잰걸음</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>(용인=연합뉴스) 김광호 기자 = 원삼면과 남사·이동읍 일대에 초대형 반도체 산업단지가 조성 중인 경기 용인시 처인구의 주요 도로망 구축 사업이...</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014075200061</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 금융권 비상인데…새마을금고, 해킹 당하고도 60시간 몰랐다</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>400여명 이름 등 개인정보 유출 외부서 공격 IP 공유받아 인지 금융권 해킹 경계령 내렸지만 계속되는 감독 사각지대 논란새마을금고가 해킹 공격을 당하고도 약 60시간 가까이 이를..</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12175452</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>임신 위한 ‘적절한 성관계 횟수’는?…“‘이 시기’ 놓치지 않아야” [라이프+]</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>임신 위한 ‘적절한 성관계 횟수’는?…“‘이 시기’ 놓치지 않아야” [라이프+]  나우뉴스</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>나우뉴스</t>
-        </is>
-      </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5iTEVvT21uTXFZT251dWVLUFg5Q0VGWnlKaEhhWmpjMUNhTi1ObzdyQ05DcjJNLUpHTXNCbHc5ekxrRFRma2p0S2FSRFBYUUtjS191MVdvNEZ1RG00ZVBxTV9jTmljbW1HQzUtRmdrRWM?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>인니 11년 만에 최악의 산불…연무로 항공 진화 1주일째 난항</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>인니 11년 만에 최악의 산불…연무로 항공 진화 1주일째 난항  연합뉴스인니 보르네오섬, 오랜 산불에 서식지 잃은 오랑우탄 46마리 구조  뉴시스인니 대규모 산불 연무에 말레이 조호르州 학교 1198곳 최소 16일까지 휴교  아시아투데이[포토] 인니 깨끗한 공기는 언제쯤  뉴스1집단 대...</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9acHV4TGVfM016VEJxMVlXeVNOVWNkMFM3aXBEamE4emhrOGlyeTB3NnRlSG13RUt4dlAza1FVT3NNYi1SMHh1cTh4UmtWY3ZmRGZ2LVY3MVlGdTDSAWBBVV95cUxQNHpFNHBZSUwtU2pZQjh4YXFGR1pDRnpMU3REcUdVOUp4dnlXU09oZ2I0bmRocTRLNk5ReHlMYWRmcWtRLU1DekxTRTVqdWc1X3FTdmJxMGR2U2tfUUNWZnE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>MLB 휴스턴 감독, 계약 기간 중 시애틀 구단 감독 면접</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장현구 기자 = 미국프로야구 메이저리그(MLB) 휴스턴 애스트로스의 조 에스파다 감독이 계약 기간 중 구단의 승낙을 받아 같은...</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014094100007</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>중국 9월 수출 36.3% 급증…수입은 31.0% 늘어</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>(상하이=연합뉴스) 차병섭 특파원 = 세계적인 인공지능(AI) 투자 붐 속에 지난달 중국의 수출이 30% 넘게 급증한 것으로 집계됐다.</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014092900089</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>미 대학서 '동료 음료에 독' 中유학생 도피하다 공항서 체포</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김승욱 기자 = 미국 대학교에서 동료 대학원생의 음료에 독극물을 타 중상을 입힌 뒤 중국으로 도피하려던 중국인 유학생이 경찰에...</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014091800009</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>오라클, 데이터센터용 가스관 승인 신속처리 촉구</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 설원태 기자 = 오라클은 미국 뉴멕시코주에서 추진중인 대규모데이터센터 구축 프로젝트에 필요한 천연가스관 건설을 신속하게 승인해...</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014083000009</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>中 9월 생산자물가 5% 올라 4년여만 최고…소비자물가는 0.9%↑</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 권숙희 기자 = 국제유가와 원자재 비용 상승 속 중국의 지난달 생산자 물가가 가파르게 올라 4년여만에 최고 수준을 기록했다.</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014088400009</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>반크 '아프리카인이 삶의 주체'인 후원 광고 찾는다</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 박성진 기자 = 사이버 외교사절단 반크(단장 박기태)가 아프리카 사람들을 외부의 도움을 기다리는 '수혜자'로만 반복해 보여주는...</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014087500898</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>외국인 인력 부족에 '정원 돌려막기' 나선 日…급식·요양 지원</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>(도쿄=연합뉴스) 조성미 특파원 = 일본 정부가 체류 허가를 내준 외국인 인력 쿼터의 관리를 강화하면서 일부 업종의 인력 확보에 차질이 빚어지자...</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014086300073</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>[영상] 해킹에 80도까지 치솟은 냉장고…"다 녹았다" 프랑스 '발칵'</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 냉장고 신선식품 칸이 텅텅 비었고 냉동고에서도 상품을 찾아볼 수 없습니다. '기술적인 문제로 냉장고 안의 신선식품을 제공할 수...</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014084300704</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>줘룽타이 대만 총리 "中 패권이 전 세계 반감 불러"</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>(타이베이=연합뉴스) 김철문 통신원 = 라이칭더 대만 총통의 지난 10일 건국기념일 연설 이후 중국이 군사적, 외교적 압박을 강화하는 가운데 줘...</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014079900009</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>인니 11년 만에 최악의 산불…연무로 항공 진화 1주일째 난항</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>(자카르타=연합뉴스) 손현규 특파원 = 11년 만에 최악의 산불로 몸살을 앓는 인도네시아에서 연무로 인해 항공 진화 작업이 1주일 넘게 차질을 ...</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014083800104</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>[영상] 사우디, 후티 연료·군사시설 전격 공습…"공항 피격 보복"</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 사우디 주도 연합군이 후티 반군 측이 장악한 예멘 수도 사나 등지의 주요 석유 시설과 군사 지원 시설을 전격 공습했습니다.</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014080700704</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>캐나다 전 부총리 "트럼프, 동맹 압박하려 CEO들 협박"</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 이성한 기자 = 미국 정부가 동맹국 기업의 최고경영자(CEO)와 비즈니스 리더들을 막후에서 위협하는 방식으로 동맹국을 백악관의...</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014082500009</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>코드 이식·AI 실험 전담… MS 엑스박스, R&amp;D 조직 신설</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>코드 이식·AI 실험 전담… MS 엑스박스, R&amp;D 조직 신설  IT조선엑스박스, 신기술 실험조직 ‘엑스박스 랩스’ 출범  지디넷코리아게임 넘어 디즈니처럼… MS, 엑스박스 엔터 사업부 ‘XP’ 신설  IT조선Xbox, 영화, TV, 라이브 이벤트 및 소비재를 전담하는 새로운 부서 'X...</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>IT조선</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE43aDVmbHg3OUM2aTA5clJXZXJIbDFjNGQyclpiLTJ6Ql9HaDJYTHktZkgtQkNhbHVjWi1ENlJ6bkl1QUZ6WEZEZFVBZmw5a3NtREVlMFc4UHNUd0FpTnppaWk4U1JHUDdray14S1FpM3rSAXRBVV95cUxORmZUbmMtYVlXUTNYSWxVUFhyLXlwazE2T1R6X0NjQUZYbm5NQVRXenBtcFR6eFZMa05Xd3AyMVN3VFExOTZYNVJOLVdrSkliN1ZHMFV0TjNVbEJ2SWkzRlBteDdrTnpaaEgybDctbk1wUkMwYg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>[금주의인물] 프란시스 할전, ‘노벨 물리학상’ 단독 수상  주간한국Google 뉴스에서 헤드라인 및 의견 더보기</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>주간한국</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBfeGtUZl96V1ZLamFndzNRODRtVTdpRlQyV1g0VE5ZS3BBdlYwWkhGZk92VmxSeDJvLW1mWE9PTWl4VFgzM3p3UC1oTHZOWmZuX1N5M1pfNUQ2ME50dU1VWDNOY0lEeGNkcnJhSVNGUTfSAXRBVV95cUxNMFFsQS1KVzBucVd4Y2JGRTRCdWpOU2c5dkRXY2dRdkJ1Y1phV2FjSzg0Z2dfWUZUTS1NaW1wc3ZySUFhQkY5UU9EOW5KMXVEcVkxNU1yWktpRlBuN1RUWXpGTG4zZWRIOTNMa3ROaENtY05GeQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>삼성 반도체 부스 찾은 하정우 부위원장 "AI반도체 로드맵 확인"(종합)</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 김민지 강태우 기자 = 하정우 국가AI전략위원회 부위원장은 14일 서울 코엑스에서 열린 '제28회 반도체대전'(SEDEX 20...</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014042351003</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>[옥천소식] 15일 공설시장서 '우리동네 문화장날' 행사</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>(옥천=연합뉴스) 충북 옥천군은 이달 15일 옥천공설시장에서 '우리동네 문화장날' 행사를 연다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014091700064</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>아트광주 22일 개막…12개국 국내외 거장 작품 출품</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>(전남광주=연합뉴스) 장아름 기자 = 호남권 최대 미술시장인 제17회 광주국제아트페어 '아트광주'가 오는 22일부터 25일까지 전남광주 김대중컨...</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014089800054</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>[전남광주소식] 롯데백화점 11월8일까지 김장김치 예약</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>(전남광주=연합뉴스) 롯데백화점 광주점은 지하 1층 올가매장에서 11월8일까지 김장 김치 사전 예약행사를 한다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014088000054</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>말로 지시하면 AI가 광통신망 알아서 설정…'로컬LLM' 기술 확보</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>(대전=연합뉴스) 김준호 기자 = 한국전자통신연구원(ETRI)은 사용자가 자연어로 원하는 네트워크 동작을 지시하면 대규모언어모델(LLM)이 이를...</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014087300063</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>강릉커피거리 350m 노천카페로…21일 커피축제 개막</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>(강릉=연합뉴스) 유형재 기자 = '제18회 강릉커피축제'가 21∼25일 강릉커피거리와 강릉시 일원에서 열린다.</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014086200062</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>괴산군, 굴착기 등 불용 임대농기계 19대 공개 매각</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>(괴산=연합뉴스) 박재천 기자 = 충북 괴산군은 영농 자재비 상승 등으로 어려움을 겪는 농가들의 경영 부담을 덜어주고 농기계 활용을 극대화하기 ...</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014083200064</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>문체위, 이임생·이동국 국감증인 의결…암살자(들) 채택은 불발</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>문체위, 이임생·이동국 국감증인 의결…암살자(들) 채택은 불발  연합뉴스국민의힘 청년당원, 박정희대통령기념관에서 영화 '암살자(들)' 규탄  뉴시스[시론담론] 사실과 진실 사이  제민일보[기고]표현의 자유 뒤에 숨겨진 역사적 책임  경상일보'역사 왜곡' 암살자(들) 왜 보냐고 한 딸이 ...</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFB6ZjR1UU9sRTJ0djlRUTFyby0yeHNKWHNPNGVadEV1dTFiZTQ2VURiLTRKSUZnMnE1NjF0MDMtNFFjQzhIWTRqQ09CUUVFaTFoRENZbm94LXhBM0HSAWBBVV95cUxQdDZMM2dvcE5CeXd2Nkc2NThUWnZLTTQwNFJzamwtWWtiWUVFbThsOVZqc29uZ3Z4M25VZ25Fc29ZQVc3V04xMmRaUHZaY2VLMXZtRnppQVBUT3BtLUtqbEE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>박하선, 6년 만에 SBS 라디오 '씨네타운' 하차…"연기에 집중"</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>박하선, 6년 만에 SBS 라디오 '씨네타운' 하차…"연기에 집중"  연합뉴스[단독] 박하선, '씨네타운' DJ 6년만에 떠난다…본업 집중  뉴스1박하선, ‘박하선의 씨네타운’ 청취자들에게 작별 인사  스포츠경향박하선, 6년만에 아쉬운 이별 '씨네타운' 떠난다.."연기 집중" [공식] ...</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5LTDRGSEZFSnJlTk9qUnU0ZWVVZXlvczF2WU56TEp5RzR2NlVielBndUE5cjFQeWNjMGF6RGlnT0d0Vkg4clZPVVpiZk0zZ1l3VDA1SG9vb00yZWvSAWBBVV95cUxQNzdVUEdmWTAzRTVDM19CeUFYUWhwS2FfcHhVUVpQdDlEMjF0ZThUYVFTRUpJZEsxX1BMeDZvSTRhMzB5SzNNVUdXdDFxSS11TlpwazhJMzAzV09BTkE4YWU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>콘진원, 뉴욕 코믹콘서 Ｋ-게임 알려…340만달러 수출 상담</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>콘진원, 뉴욕 코믹콘서 Ｋ-게임 알려…340만달러 수출 상담  지디넷코리아[르포] 뉴욕 달군 한국 웹툰…韓작가 사인회에 3시간 대기줄  연합뉴스콘진원, '뉴욕 코믹콘' 韓 공동관 성료…상담액 45억 기록  뉴스핌네이버웹툰, 뉴욕 코믹콘 5만명…'포그랜드' 부스  뉴스1"울버린으로 변신했...</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>지디넷코리아</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBOQ1U1TGNZQnA2RDlXWm1lUEcwendSV2FKVm5ZTUlXaVZDakhGX0Z3aVB6LUlwUmhlUzRsN2EzMXhGSHJ5aXppNzI3Q1lnTTVBTmxEbXJR?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>초소형 말 '윌리'·가수 추혁진, 이천시 홍보대사 위촉</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>(이천=연합뉴스) 김광호 기자 = 경기 이천시는 초소형 말 '윌리'와 가수 추혁진을 시 홍보대사로 위촉했다고 14일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014089900061</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>박하선, 6년 만에 SBS 라디오 '씨네타운' 하차…"연기에 집중"</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>(서울=연합뉴스) 장진리 기자 = 배우 박하선이 다음 달 1일 방송을 끝으로 6년간 진행한 SBS 라디오 파워FM '박하선의 씨네타운'에서 하차...</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014086700005</t>
+          <t>https://www.yna.co.kr/view/AKR20261014115200003</t>
         </is>
       </c>
     </row>
@@ -6181,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6202,6 +3946,7 @@
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="65" customWidth="1" min="18" max="18"/>
+    <col width="53" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6295,6 +4040,11 @@
           <t>핵심뉴스</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>recent_closes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6385,6 +4135,7 @@
           <t>"차세대 D램 연내 출시" 창신메모리 선전포고...반도체 개미 곡소리 - 머니투데이 (머니투데이)</t>
         </is>
       </c>
+      <c r="S2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6475,6 +4226,7 @@
           <t>"차세대 D램 연내 출시" 창신메모리 선전포고...반도체 개미 곡소리 - 머니투데이 (머니투데이)</t>
         </is>
       </c>
+      <c r="S3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6565,6 +4317,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6655,6 +4408,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6745,6 +4499,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6835,6 +4590,7 @@
           <t>카카오, 카톡에 AI 비서 탑재…정신아 "연결에 개인 이해하는 지능 더할 것"(종합) (연합인포맥스)</t>
         </is>
       </c>
+      <c r="S7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6925,6 +4681,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7015,6 +4772,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7105,6 +4863,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7195,6 +4954,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7285,6 +5045,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7375,6 +5136,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7465,6 +5227,7 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7489,17 +5252,17 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>238,000원</t>
+          <t>237,000원</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+31,750.0원 (+15.38%)</t>
+          <t>+30,500.0원 (+14.77%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>236,000원</t>
+          <t>234,500원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -7509,12 +5272,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>230,000원</t>
+          <t>228,500원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+9.0%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -7524,7 +5287,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>RSI 38.3로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 37.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -7538,21 +5301,26 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>38.3</v>
+        <v>37.6</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>삼전닉스 폭락에도 "지금이 저점"…'W자 반등' 전망한 이유 [분석+] (한국경제)</t>
+          <t>한미반도체, 반도체대전서 HBM4용 TC 본더 등 선봬 (주요언론)</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 237000.0]</t>
         </is>
       </c>
     </row>
@@ -7579,32 +5347,32 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1,470,000원</t>
+          <t>1,449,000원</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+367,000.0원 (+33.27%)</t>
+          <t>+346,000.0원 (+31.37%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1,455,500원</t>
+          <t>1,434,500원</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1,705,500원</t>
+          <t>1,704,500원</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>1,418,500원</t>
+          <t>1,398,500원</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+17.2%</t>
+          <t>+18.8%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -7614,7 +5382,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>RSI 33.7로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 31.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -7628,21 +5396,26 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>33.7</v>
+        <v>31.9</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>[1812000.0, 1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1449000.0]</t>
         </is>
       </c>
     </row>
@@ -7669,17 +5442,17 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>320,000원</t>
+          <t>318,000원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-171,500.0원 (-34.89%)</t>
+          <t>-173,750.0원 (-35.35%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>313,500원</t>
+          <t>311,500원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -7689,12 +5462,12 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>304,000원</t>
+          <t>302,000원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+22.0%</t>
+          <t>+22.8%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -7718,21 +5491,26 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>26.6</v>
+        <v>24.5</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 317750.0]</t>
         </is>
       </c>
     </row>
@@ -7759,17 +5537,17 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>110,000원</t>
+          <t>109,000원</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-39,300.0원 (-26.34%)</t>
+          <t>-40,000.0원 (-26.81%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>107,500원</t>
+          <t>107,000원</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -7779,12 +5557,12 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>104,500원</t>
+          <t>103,500원</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+17.5%</t>
+          <t>+18.3%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -7808,21 +5586,26 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>33.5</v>
+        <v>31.6</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 109200.0]</t>
         </is>
       </c>
     </row>
@@ -7854,7 +5637,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-19,850.0원 (-9.85%)</t>
+          <t>-20,100.0원 (-9.98%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -7874,7 +5657,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+16.0%</t>
+          <t>+16.2%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -7898,21 +5681,26 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>32.7</v>
+        <v>32.3</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>콘진원, 뉴욕 코믹콘서 Ｋ-게임 알려…340만달러 수출 상담 (지디넷코리아)</t>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 181400.0]</t>
         </is>
       </c>
     </row>
@@ -8002,7 +5790,12 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>카카오뱅크 "18일 새벽 금융거래 일시 중단…전산시스템 점검" (주요언론)</t>
+          <t>카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가 (연합인포맥스)</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>[34500.0, 34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 32000.0]</t>
         </is>
       </c>
     </row>
@@ -8029,32 +5822,32 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>182,500원</t>
+          <t>181,500원</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-6,919.049999999988원 (-3.65%)</t>
+          <t>-8,219.049999999988원 (-4.33%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>179,000원</t>
+          <t>181,500원</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>192,000원</t>
+          <t>190,500원</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>173,500원</t>
+          <t>174,000원</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -8078,21 +5871,26 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>51.3</v>
+        <v>48.7</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 181400.0]</t>
         </is>
       </c>
     </row>
@@ -8185,6 +5983,11 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>[1081000.0, 1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 845000.0]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -8209,12 +6012,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>424,000원</t>
+          <t>425,500원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+23,750.0원 (+5.94%)</t>
+          <t>+25,500.0원 (+6.38%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -8224,17 +6027,17 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>424,000원</t>
+          <t>425,500원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>415,500원</t>
+          <t>417,000원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+13.8%</t>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -8244,7 +6047,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 71.4, 20일선 이격도 +13.8%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 71.8, 20일선 이격도 +14.3%로 단기 과열권, 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -8258,21 +6061,26 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+13.8%</t>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 425500.0]</t>
         </is>
       </c>
     </row>
@@ -8299,32 +6107,32 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>310,000원</t>
+          <t>309,500원</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>-51,500.0원 (-14.25%)</t>
+          <t>-52,000.0원 (-14.38%)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>304,000원</t>
+          <t>309,500원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>334,000원</t>
+          <t>325,000원</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>294,500원</t>
+          <t>297,000원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -8348,21 +6156,26 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>[334000.0, 326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 309500.0]</t>
         </is>
       </c>
     </row>
@@ -8399,7 +6212,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>$223.95 (약 300,289원)</t>
+          <t>$228.52 (약 306,417원)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -8409,12 +6222,12 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>$217.09</t>
+          <t>$219.38</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -8455,6 +6268,11 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>[213.9, 219.34, 222.27, 227.38, 228.87, 225.51, 224.58, 225.07, 228.86, 227.21, 228.38, 230.86, 233.95, 238.9, 239.24, 237.47, 230.48, 229.28, 226.32, 228.52]</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -8489,7 +6307,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>$334.44 (약 448,450원)</t>
+          <t>$341.27 (약 457,602원)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -8499,12 +6317,12 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>$324.21</t>
+          <t>$327.62</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -8545,6 +6363,11 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>[332.41, 337.0, 336.13, 338.98, 339.75, 337.02, 335.92, 341.07, 338.4, 329.4, 333.02, 330.32, 333.69, 332.89, 333.63, 336.67, 340.42, 336.64, 340.97, 341.27]</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -8579,7 +6402,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>$367.73 (약 493,075원)</t>
+          <t>$375.23 (약 503,138원)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -8589,12 +6412,12 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>$356.47</t>
+          <t>$360.22</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -8635,6 +6458,11 @@
           <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>[358.08, 366.2, 364.27, 375.3, 378.9, 380.12, 377.94, 372.11, 357.45, 352.84, 354.81, 354.11, 370.59, 378.73, 380.68, 377.81, 375.0, 382.7, 378.03, 375.23]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -8723,6 +6551,961 @@
       <c r="R28" s="3" t="inlineStr">
         <is>
           <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>[490.3, 497.75, 493.78, 501.61, 498.0, 500.59, 497.93, 516.17, 509.22, 508.96, 512.9, 512.8, 517.53, 525.18, 529.3, 529.76, 522.61, 535.07, 541.15, 543.45]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>028670.KS</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>7,160원</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>+1,870.0원 (+35.35%)</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>6,000원</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>7,160원</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>7,020원</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>+19.3%</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>RSI 72.1, 20일선 이격도 +19.3%로 단기 과열권, 분할 차익 실현 권고</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>+19.3%</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>94.4%</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>[6030.0, 6040.0, 5680.0, 5800.0, 5880.0, 5750.0, 5790.0, 5790.0, 5600.0, 5700.0, 5700.0, 5770.0, 5880.0, 6240.0, 6000.0, 6210.0, 6030.0, 6450.0, 6550.0, 7160.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>128940.KS</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>415,000원</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>-86,000.0원 (-17.17%)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>411,000원</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>484,000원</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>400,500원</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>+17.8%</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>RSI 34.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>-15.9%</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>32.8%</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 415000.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>HMM</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>011200.KS</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>23,400원</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>+2,400.0원 (+11.43%)</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>21,200원</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>23,400원</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>22,900원</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>+10.3%</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>RSI 68.4, 20일선 이격도 +10.3%로 단기 과열권, 분할 차익 실현 권고</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>+10.3%</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>78.0%</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>[20850.0, 21250.0, 20650.0, 20350.0, 20750.0, 20800.0, 21100.0, 21200.0, 20800.0, 21250.0, 21000.0, 20850.0, 21150.0, 21500.0, 21450.0, 21400.0, 20800.0, 21800.0, 22050.0, 23400.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>일진전기</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>103590.KS</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>77,000원</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>-7,300.0원 (-8.66%)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>77,000원</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>80,800원</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>73,900원</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>관망 (HOLD)</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>중립 구간 유지 중</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 77000.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>현대글로비스</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>086280.KS</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>185,500원</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>-33,900.0원 (-15.44%)</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>183,500원</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>196,500원</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>179,000원</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>RSI 38.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>[208500.0, 207000.0, 204500.0, 200500.0, 206000.0, 203500.0, 203000.0, 203000.0, 196900.0, 199100.0, 197500.0, 196800.0, 198400.0, 201500.0, 201000.0, 188000.0, 182900.0, 181900.0, 180600.0, 185600.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>삼성화재</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>000810.KS</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>581,000원</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>+91,500.0원 (+18.69%)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>575,000원</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>629,000원</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>560,500원</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>+9.4%</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>RSI 33.5로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>-9.5%</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>47.9%</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 581000.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>세아베스틸지주</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>001430.KS</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>43,600원</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>-24,000.0원 (-35.50%)</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>43,600원</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>45,800원</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>41,900원</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>관망 (HOLD)</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>중립 구간 유지 중</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>-2.1%</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>27.7%</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>[41450.0, 40950.0, 43250.0, 43250.0, 45450.0, 45050.0, 43800.0, 45600.0, 44300.0, 44600.0, 45300.0, 44950.0, 47000.0, 46650.0, 47250.0, 44150.0, 46800.0, 44500.0, 43150.0, 43600.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>한화손해보험</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>000370.KS</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>6,440원</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>-170.0원 (-2.57%)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>6,380원</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>7,510원</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>6,210원</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>+17.8%</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>RSI 30.7로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>-16.0%</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>24.2%</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>[8420.0, 8500.0, 8320.0, 8080.0, 8290.0, 8070.0, 8070.0, 7790.0, 7610.0, 7890.0, 7880.0, 7300.0, 7280.0, 7330.0, 7230.0, 7340.0, 7200.0, 7230.0, 7010.0, 6440.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>145020.KS</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>223,500원</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>-29,500.0원 (-11.66%)</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>221,500원</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>237,000원</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>215,500원</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>RSI 19.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>+11.7%</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>41.1%</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>[236000.0, 231000.0, 232000.0, 235500.0, 231000.0, 231500.0, 214000.0, 206000.0, 190400.0, 187000.0, 186100.0, 183300.0, 179700.0, 180600.0, 180100.0, 181500.0, 183600.0, 182800.0, 180000.0, 169900.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>306200.KS</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>142,000원</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>-6,500.0원 (-4.38%)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>142,000원</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>149,000원</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>136,500원</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>관망 (HOLD)</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>중립 구간 유지 중</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>-3.5%</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>39.0%</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>[150600.0, 151400.0, 146900.0, 145300.0, 147400.0, 149600.0, 145200.0, 142700.0, 138200.0, 147500.0, 146200.0, 153200.0, 148300.0, 154600.0, 155100.0, 148500.0, 145200.0, 143500.0, 141300.0, 142000.0]</t>
         </is>
       </c>
     </row>
@@ -8954,12 +7737,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6,137.60</t>
+          <t>6,106.83</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+102.25 (+1.69%)</t>
+          <t>+71.48 (+1.18%)</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7764,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>839.61</t>
+          <t>838.62</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>+2.58 (+0.31%)</t>
+          <t>-10.57 (-1.24%)</t>
         </is>
       </c>
     </row>
@@ -9200,27 +7983,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,951,000원</t>
+          <t>112,702,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>112,386,000원</t>
+          <t>112,138,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,987,000원</t>
+          <t>121,718,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,593,000원</t>
+          <t>110,586,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -9257,27 +8040,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3,393,000원</t>
+          <t>3,384,000원</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3,366,000원</t>
+          <t>3,357,000원</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3,596,500원</t>
+          <t>3,587,000원</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3,274,000원</t>
+          <t>3,265,500원</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -9292,7 +8075,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>RSI 47.6로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 46.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -9314,32 +8097,32 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>145,600원</t>
+          <t>145,000원</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>144,400원</t>
+          <t>143,800원</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>155,900원</t>
+          <t>155,800원</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>140,500원</t>
+          <t>139,900원</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>+7.9%</t>
+          <t>+8.3%</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -9349,7 +8132,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>RSI 48.2로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 47.3로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -9462,7 +8245,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -9491,7 +8274,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>한 단계 진화한 실적, 한 단계 진화할 주가 레벨 수급 영향으로 단기 주가의 변동폭은 과거 대비 커졌으나 우호적인 벌크·탱커 시황 감안 시 중기 우상향 흐름 지속될 것으로 판단. 환율 방향성이원화 환산 실적에 부담이나 펀더멘털에 미치는 영향은 제한적</t>
+          <t>한 단계 진화한 실적, 한 단계 진화할 주가 레벨 수급 영향으로 단기 주가의 변동폭은 과거 대비 커졌으나 우호적인 벌크·탱커 시황 감안 시 중기 우상향 흐름 지속될 것으로 판단. 환율 방향성이원화 환산 실적에 부담이나 펀더멘털에 미치는 영향은 제한적.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -9532,7 +8315,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -9561,7 +8344,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>선급금 4Q26 반영, 북경한미 정비 작업과 앱토즈 인수로 전체적인 실적은 부진 3Q26 실적은 연결기준 매출액 3,794억원(YoY+4.7%), 영업이익 381억원(YoY-30.8%, OPM 10.0%)으로 예상된다. 컨센서스와 크게 어긋나 보이지만, Genentech향 HM17321 L/O 선급금이 미국 HSR 행정절차가 10월 초 완료됨에 따라 4Q26에 인식되는데 컨센서스가 미리 3Q에 이를 반영했기 때문이다. 2Q에 Lilly향 L/O에 따른 선급금이 반영되었기 때문에 QoQ로 비교하는 것도 큰 의미가 없다. 선급금이 없던</t>
+          <t>선급금 4Q26 반영, 북경한미 정비 작업과 앱토즈 인수로 전체적인 실적은 부진 3Q26 실적은 연결기준 매출액 3,794억원(YoY+4.7%), 영업이익 381억원(YoY-30.8%, OPM 10.0%)으로 예상된다. 컨센서스와 크게 어긋나 보이지만, Genentech향 HM17321 L/O 선급금이 미국 HSR 행정절차가 10월 초 완료됨에 따라 4Q26에 인식되는데 컨센서스가 미리 3Q에 이를 반영했기 때문이다. 2Q에 Lilly향 L/O에 따른 선급금이 반영되었기 때문에 QoQ로 비교하는 것도 큰 의미가 없다.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -9602,7 +8385,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -9631,7 +8414,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다 큰 이익 회복에 주목</t>
+          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -9701,7 +8484,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단</t>
+          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -9771,7 +8554,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>자동차 밸류체인이지만 해운사이기도 함 단기 실적 가시성은 다소 낮아졌으나 이익 방향성은 여전히 긍정적. 비계열 고객 호조로 이익 개선이 뚜렷한 사업부를 가진 점은 차별화 포인트</t>
+          <t>자동차 밸류체인이지만 해운사이기도 함. 단기 실적 가시성은 다소 낮아졌으나 이익 방향성은 여전히 긍정적. 비계열 고객 호조로 이익 개선이 뚜렷한 사업부를 가진 점은 차별화 포인트.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -9812,7 +8595,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -9841,7 +8624,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다. 장기보험손익은 3,560억원으로 YoY/QoQ 모두 감소할 것으로 예상하며, 사업비 부담 확대가 주요 원인이다. 자동차보험손익은 전분기대비 감소하겠으나 YoY </t>
+          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -9886,17 +8669,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>세아베스틸지주</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
+          <t>3분기는 다소 부진하겠지만 4분기부터 회복 기대</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -9906,42 +8689,42 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다. 기존 유통사 재고 바이백으로 미국 매출은 마이너스가 예상된다. ASP가 높은 미국향 톡신 매출 공백으로 매출총이익률도 전년 동기 대비 6%p 하락이 </t>
+          <t>3Q26 주력 자회사들 판매 감소와 스프레드 축소 2026년 3분기 세아베스틸지주의 매출액과 영업이익은 각각 1.0조원(YoY +10.3%, QoQ -10.6%)과 236억원(YoY -12.4%, QoQ -60.6%)으로 영업이익은 시장컨센서스인 398억원을 크게 하회할 것으로 예상된다. 계절적 비수기와 9월 추석 연휴 영향으로 세아베스틸의 특수강 판매는 41.2만톤(YoY +5.0%, QoQ -9.8%)에 그치며 고정비 부담이 확대될 전망이다. 원가 상승분 가격 전가를 위한 노력으로 8월초까지 적극적인 가격 인상을 시도한 결과, 특수강 ASP가 1.6만원/톤 상승이 예상되나 스크랩가격이 이를 상회하는 2.1만원/톤 상승하여 스프레드도 소폭 축소될 전망이다.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
+          <t>2026-10-14_하나증권_세아베스틸지주_3분기는 다소 부진하겠지만 4분기부터 회복 기대.pdf</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>486십억원</t>
+          <t>4,116.0십억원</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>174십억원</t>
+          <t>140.6십억원</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>657십억원</t>
+          <t>4,496.9십억원</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>272십억원</t>
+          <t>223.3십억원</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 매출액은 1,009억원(-4</t>
+          <t>3Q26 영업이익 236억원(YoY -</t>
         </is>
       </c>
     </row>
@@ -9952,7 +8735,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -9961,12 +8744,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>세아베스틸지주</t>
+          <t>한화손해보험</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>3분기는 다소 부진하겠지만 4분기부터 회복 기대</t>
+          <t>3Q26 Pre - 보험손익 개선세에 주목</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -9981,37 +8764,37 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3Q26 주력 자회사들 판매 감소와 스프레드 축소 2026년 3분기 세아베스틸지주의 매출액과 영업이익은 각각 1.0조원(YoY +10.3%, QoQ -10.6%)과 236억원(YoY -12.4%, QoQ -60.6%)으로 영업이익은 시장컨센서스인 398억원을 크게 하회할 것으로 예상된다. 계절적 비수기와 9월 추석 연휴 영향으로 세아베스틸의 특수강 판매는 41.2만톤(YoY +5.0%, QoQ -9.8%)에 그치며 고정비 부담이 확대될 전망이다. 원가 상승분 가격 전가를 위한 노력으로 8월초까지 적극적인 가격 인상을 시도한 결과, </t>
+          <t>2026년 3분기 실적은 컨센서스 소폭 하회 전망 3분기 별도 당기순이익은 903억원으로 컨센서스(939억원)를 소폭 하회할 것으로 전망한다. 증시 부진 및 금리 상승에 따른 투자손익 악화가 예상되나, 보험손익은 전반적으로 개선될 전망이다. [보험손익] 보험손익은 1,377억원(YoY +44.5%, QoQ +35.2%)으로 추정한다.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_세아베스틸지주_3분기는 다소 부진하겠지만 4분기부터 회복 기대.pdf</t>
+          <t>2026-10-14_하나증권_한화손해보험_3Q26 Pre - 보험손익 개선세에 주목.pdf</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>4,116.0십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>140.6십억원</t>
+          <t>465십억원</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>4,496.9십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>223.3십억원</t>
+          <t>595십억원</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>3Q26 영업이익 236억원(YoY -</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -10022,21 +8805,21 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>한화손해보험</t>
+          <t>휴젤</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Pre - 보험손익 개선세에 주목</t>
+          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -10046,42 +8829,42 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 실적은 컨센서스 소폭 하회 전망 3분기 별도 당기순이익은 903억원으로 컨센서스(939억원)를 소폭 하회할 것으로 전망한다. 증시 부진 및 금리 상승에 따른 투자손익 악화가 예상되나, 보험손익은 전반적으로 개선될 전망이다. [보험손익] 보험손익은 1,377억원(YoY +44.5%, QoQ +35.2%)으로 추정한다. 장기·자동차·일반보험손익 모두 예상대비 양호한 수준을 기록할 전망이다. 장기보험손익은 1,411억원으로 YoY/QoQ 모두 큰 폭 증가할 것으로 예상한다. 관리급여 효과에 따른 보험금 예실차 개선이 주</t>
+          <t>3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_한화손해보험_3Q26 Pre - 보험손익 개선세에 주목.pdf</t>
+          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>486십억원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>465십억원</t>
+          <t>174십억원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>657십억원</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>595십억원</t>
+          <t>272십억원</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>3Q26 매출액은 1,009억원(-4</t>
         </is>
       </c>
     </row>
@@ -10121,7 +8904,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>3Q26 내수와 수출 모두 수익성 악화 2026년 3분기 세아제강의 매출액과 영업이익은 각각 4,318억원(YoY +30.2%, QoQ -12.8%)과 195억원(YoY 흑.전, QoQ -44.2%)으로 영업이익은 시장컨센서스인 254억원을 하회할 것으로 예상된다. 3분기 내수 강관 시장은 계절적 비수기와 추석 연휴 영향으로 다소 부진할 것으로 예상되는 가운데 수출의 경우 캐나다 LNG와 같은 프로젝트 덕분에 소폭 증가한 것으로 추정되어 결과적으로 세아제강의 3분기 전체 강관 판매는 22.8만톤(YoY +21.4%, QoQ -6.8</t>
+          <t>3Q26 내수와 수출 모두 수익성 악화 2026년 3분기 세아제강의 매출액과 영업이익은 각각 4,318억원(YoY +30.2%, QoQ -12.8%)과 195억원(YoY 흑.전, QoQ -44.2%)으로 영업이익은 시장컨센서스인 254억원을 하회할 것으로 예상된다. 3분기 내수 강관 시장은 계절적 비수기와 추석 연휴 영향으로 다소 부진할 것으로 예상되는 가운데 수출의 경우 캐나다. LNG와 같은 프로젝트 덕분에 소폭 증가한 것으로 추정되어 결과적으로 세아제강의 3분기 전체 강관 판매는 22.8만톤(YoY +21.4%, QoQ -6.8%)을 기록할 전망이다.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -10166,7 +8949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10288,12 +9071,12 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (보유 중)</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -10350,12 +9133,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (보유 중)</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -10412,12 +9195,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (보유 중)</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -10474,12 +9257,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (보유 중)</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+3.4%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -10536,17 +9319,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (보유 중)</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>849,000원</t>
+          <t>859,000원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -10598,7 +9381,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (보유 중)</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -10640,12 +9423,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>238,000원</t>
+          <t>238,500원</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>235,500원</t>
+          <t>236,000원</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -10655,22 +9438,22 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>229,500원</t>
+          <t>230,000원</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (당일 포지션 구축)</t>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>238,500원</t>
+          <t>236,750원</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -10702,40 +9485,350 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1,475,000원</t>
+          <t>1,456,000원</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1,460,000원</t>
+          <t>1,441,500원</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1,706,000원</t>
+          <t>1,705,000원</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,423,500원</t>
+          <t>1,405,000원</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>⏳ 진행 중 (당일 포지션 구축)</t>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>1,470,000원</t>
+          <t>1,447,000원</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>128940.KS</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>417,500원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>413,500원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>484,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>403,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>415,500원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>현대글로비스</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>086280.KS</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>185,500원</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>184,000원</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>197,000원</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>179,000원</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>185,600원</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>삼성화재</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>000810.KS</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>581,000원</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>575,000원</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>629,000원</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>560,500원</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>582,000원</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>한화손해보험</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>000370.KS</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>6,440원</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>6,380원</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>7,510원</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>6,210원</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>6,440원</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>145020.KS</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>223,500원</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>221,500원</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>237,000원</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>215,500원</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>223,500원</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
@@ -10756,7 +9849,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
@@ -11138,27 +10231,23 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>🏛️ 대주주/임원 장내매수 (책임경영)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>더핑크퐁컴퍼니</t>
-        </is>
-      </c>
+          <t>내부자 매수</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니, 50억원 규모 자사주 취득 신탁계약 해지 결정</t>
+          <t>풍산, 최대주주등 지분율 38.02% 유지, 임원 장내매수로 108주 증가</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>내부 사정을 가장 잘 아는 경영진의 직접 매수로 기업가치 저평가 방증</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -11168,12 +10257,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:43:38 GMT</t>
+          <t>Tue, 13 Oct 2026 08:03:15 GMT</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1MVmRGS1NqcEJobXNpM01fNTlJbV9MeFZUeXBTVktGWV9XOWFlMHFET09BeW1rQ1RJdzVCR0I1OXM1UkpxM3Nnazk4RnBPbC1EaGFxM0FpVVpqYzZPRnlGb0plTEwyYmZDSXJXNW8yYmh5M0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBCY2RfTnBJdUJVUW5lcFdtUGtuYXhMNmRwNkVmREpRVTdyRUQ3Y2ZfaWFTMUhNVkpSZEdJUGdzMnZ4RWZQSlpwSG9FS2FlV05kaktCSm16clk5Tjg1a0t2MHNmMkw0WHBrdm9fR2lkVXlCODA?oc=5</t>
         </is>
       </c>
     </row>
@@ -11394,4 +10483,234 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="53" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>수집일자</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>트랙구분</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>배지</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>리포트제목</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>핵심키워드</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>핵심요약</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>1_이슈개요_및_현황</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2_발단_및_누적타임라인</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>3_이면의구조_및_이해관계</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>4_시장파장_및_향후전망</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>핵심용어사전</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>언론사/출처</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>원문링크</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>경제·사회 심층 분석</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>심층 분석</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>🌐 [경제·사회 심층 리포트] 모두의 AI의 숨겨진 배경과 구조적 쟁점</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>모두의 AI</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '모두의 AI' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가 연합인포맥스 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동…소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척 동아일보카카오 인적분할 앞두고 창사 첫 '그룹 공동 IR' 개최, 계열사 CEO 총출동 비즈니스포스트카카오, AI 시대 ‘신뢰·책임’ 검증 사례 나눈다.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; KT컨소시엄, ‘모두의 AI Connect Summit 2026’ 개최 바끄로뉴스. '국민이 체감' 모두의 AI, 이용자 사로잡을 전략은 비즈워치.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 통신 3사, 3Q 영업익 1.4조 전망…일회성 비용 털고 AI 성장 가속 매일일보. SKT·KT·카카오, ‘모두의 AI’ 누가 먼저 기선잡나… 베타 서비스 10월 출격, 각축전 ‘점화’ CEO스코어데일리.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>앞으로 시장과 투자자 관점에서 눈여겨보아야 할 핵심 체크포인트입니다.&lt;br&gt;• &lt;b&gt;시장 파장:&lt;/b&gt; 단기적인 주가 출렁임을 넘어, 관련 산업의 밸류체인과 지형도를 재편하는 기폭제가 될 수 있습니다.&lt;br&gt;• &lt;b&gt;관전 포인트:&lt;/b&gt; 향후 발표될 세부 가이드라인과 주요 일정에 따라 관련 기업들의 실적 희비가 크게 엇갈릴 전망이므로 면밀한 추적이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>📌 **구조적 수혜(Structural Beneficiary)**: 단기적 유행이 아닌, 국가 정책이나 글로벌 지정학적 공급망 재편에 따라 수년간 장기적인 성장을 누리게 되는 산업 생태계 현상입니다.</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9FREp6R1lfYkJtTEhVUGZqRTdNbXBZbmNUYVpQWDN4c2M0OTZ0TV9OZzJmVW9CZFNITFdtWjNzY1RkTUpmLTYzMWgycEVFbjF6OWRpeGZFdWRjZkN0djBEeXlJVmJnZ1RSbkc4bEl5NDc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>트렌드 &amp; 소비 인사이트</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>트렌드 포커스</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>🔥 [트렌드 &amp; 소비 인사이트] 블루 아카이브 열풍의 배경과 소비 심리 분석</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>블루 아카이브</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>요즘 왜 난리일까? '블루 아카이브' 품절 대란과 오픈런 이면에 숨은 소비 심리와 바이럴 구조를 짚어봅니다.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>지금 거리와 SNS에서 소비자들이 가장 열광하고 있는 화제의 중심은 단연 **[GS25, '블루 아카이브'와 3차 협업…전국 팝업스토어도 운영]** 입니다.&lt;br&gt;• &lt;b&gt;트렌드 현황:&lt;/b&gt; GS25, '블루 아카이브'와 3차 협업…전국 팝업스토어도 운영 매일경제 마켓.&lt;br&gt;• &lt;b&gt;열풍의 온도:&lt;/b&gt; 매장 문이 열리기 전부터 줄을 서는 '오픈런'과 온라인 품절 사태가 잇따르며, 단순한 유행을 넘어 하나의 강력한 문화적 현상으로 자리 잡았습니다.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 수영복 입은 문주님, 블루 아카이브에 '람과천청' 업데이트 월요신문. 알림음과 배경 음악을 구분하는 블루아카이브 경마 사운드 안내 Calgary Roughnecks.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>소비자들이 기꺼이 시간과 비용을 들여 줄을 서는 심리적 이유를 쉽게 풀어보았습니다.&lt;br&gt;• &lt;b&gt;소비 심리:&lt;/b&gt; 넥슨 '블루 아카이브' 모집 BM 개편한다, 4분기 글로벌 적용 게임뷰. 생성형 AI와의 공존 ③ 넥슨게임즈 김용하 본부장 게임메카.&lt;br&gt;• &lt;b&gt;심리적 기제:&lt;/b&gt; 단순히 제품의 기능 때문이 아니라, '희소한 트렌드를 남들보다 빠르게 경험하고 인증했다'는 심리적 만족감과 소속감(디토 소비 및 포모 심리)이 지갑을 열게 만드는 핵심 동기입니다.</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>이 열풍이 유통업계에 미친 영향과 향후 지속 가능성에 대한 전망입니다.&lt;br&gt;• &lt;b&gt;유통가 파장:&lt;/b&gt; 편의점, 백화점, 패션·식음료 브랜드들이 앞다퉈 컬래버레이션 팝업스토어를 유치하며 고객 유입에 사활을 걸고 있습니다.&lt;br&gt;• &lt;b&gt;지속 가능성:&lt;/b&gt; 반짝 유행(Fad)에 그치지 않고 장기적인 메가 트렌드로 안착하려면, 일회성 화제성을 넘어 본질적인 품질 만족도와 지속적인 팬덤 관리가 뒷받침되어야 합니다.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>📌 **팝업스토어(Pop-up Store)**: 짧은 기간 동안 임시로 운영되는 매장으로, 단순 물건 판매를 넘어 소비자에게 특별한 브랜드 체험과 인증샷을 유도하는 현대 유통의 핵심 집객 전략입니다.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>매일경제 마켓</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5oRlFmSDNxbVRUaEctLWp3SHVvbEtGeFRFajBNUndReGo0QzZNdFBacG1la0ZGR3BScW5qb091eW4xclJOQi1vYk9DVjM4NVd6cnc?oc=5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -3636,22 +3636,22 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>한미 국방장관 이달말 첫 대면 가능성...전작권 논의 주목</t>
+          <t>윤석열 선거법 2심, 오는 27일 선고‥국민의힘 '선거비용 397억 원 반환' 달렸다</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>한미 국방장관 이달말 첫 대면 가능성...전작권 논의 주목 YTN 한미 전작권 이견에… SCM, 12월로 이례적 연기 조선일보브런슨 "시간도 하나의 조건"…한미 전작권 전환 협상 난항 예상 뉴스1주한미군사령관 "조건 충족시 전작권 전환 지지‥한반도 다층감지할 것" MBC 뉴스한미, SCM 일정 조율도 ‘삐그덕’…양국 국방장관 이달말 첫 대면 가능성 KBS 뉴스.</t>
+          <t>윤석열 선거법 2심, 오는 27일 선고‥국민의힘 '선거비용 397억 원 반환' 달렸다. MBC 뉴스'국힘 397억 반환' 걸린 尹 재판서 특검 '당선무효형 유지' 요청 MBC 뉴스‘국힘 397억 반환’ 걸린 2심서…윤 "이럴 거면 선거 왜 해" JTBC‘국힘 397억’ 걸린 尹 선거법 2심 27일 선고 동아일보특검, 尹 '여론조사 무상수수' 무죄 판결에 상고…"납득 어려워".</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFByaGg5R3BoUm5yNXVJOENVOXc5cnVCdlpxdldkdFd4WFRVcDBPbmhHTlBPWnJTOUg0Q3FhYVAxV3dTSUVuNTd6N2s0VmxWWlo4NUhja1FtYVFHazRzYmRmZVVNaWtfVm5hZDdRYl9GOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBqVlppeEExSms5RGVjN2ZqY2Y1bXN6ZlV4MTJlcnc3VERVT1BNRDRBZG94Q2xFaGxSZ3JEelJZVk1NNFMzOUt4WW1jOXd2Z0xydXlFajhLM05qZU8xc3RGVlM2NXdteHd1b3FPMjZPdm9UWHFmcjBJ0gF3QVVfeXFMT2FLNS01aG8xbG5qdVpQVl82RmpXVktST0k1VHZ6T2lzdk1lNXJGa1RrV21jZGkxRVUtMzVhdjRFdEF3QUJtRjI0RktXTjhmc2s1YzNLZHpHcDJUZy1Jb2lrYm43ZFpfazFmZUF6OFNtMUJwdEE4M28?oc=5</t>
         </is>
       </c>
     </row>
@@ -3673,22 +3673,22 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>UST, '청정 원전 해체' 길 열었다…신규 제염제 개발</t>
+          <t>대입 논술시험서 AI안경 쓴 수험생들 적발…시립대 "응시 3년 금지"</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>원자력발전소를 해체할 때 방사성 오염물질은 제거하면서 독성 약품 사용량은 줄이고, 제염 후 남은 폐액까지 하나...</t>
+          <t>대입 논술시험서 AI안경 쓴 수험생들 적발…시립대 "응시 3년 금지" 논술 시험장에 등장한 스마트안경…연세대·시립대서 줄줄이 적발 KBS 뉴스뿔테 안경 아니었어?···연세대 논술 시험장서 ‘스마트 안경’ 적발 주간경향정근식, '스마트 안경' 부정행위 우려에 "교육부 지침 따라 대응" MBC 뉴스수험생들 “이번 수능때 AI 안경 쓸것”… 대학선 방지책 비상 문화일보.</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014112100063</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBkb21vYW14V21SZVNZOVlHaGIyRkJ4TlA5RU9IYkRrekVpOVBSbjlqLWdSZ25mcnVpOUhvS1R5WGpjSGdicm4xSDhCR2xERjduVktqR3RveWJKY03SAWBBVV95cUxObXlQc0RwOFRTSnJaSk9MUTM1S3JsaFlsSUVsc1ZGeWc1SUVjNGFWLUNiWExVc2pTSkpmc1Eyek80WHN3cE9tOHdBZXJIMm5aNno5TGR2bFZ0cml1aEM0WE8?oc=5</t>
         </is>
       </c>
     </row>
@@ -3705,27 +3705,27 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>[속보] '1억 공천헌금' 무소속 강선우 의원 1심 징역 2년 6개월 선고</t>
+          <t>"뛰다가 죽음 이를 수도"…황영조가 러너들에 던진 경고</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>[속보] '1억 공천헌금' 무소속 강선우 의원 1심 징역 2년 6개월 선고의 핵심 내용과 시장 반응을 분석한 보도입니다.</t>
+          <t>이를 수도"…황영조가 러너들에 던진 경고 황영조 ’러닝 경고’…“기록·SNS 욕심 보다. 몸 상태 체크“ TV"포기할 줄 아는 사람이 잘 뛰는 사람"...잇따른 마라톤 사고에 황영조 '일침' YTN'서울달리기' 숨진 20대女는 '카이스트 대학원생' 유지원씨 파이낸셜뉴스“그냥 달리고 싶어”…결승선 앞 멈춰진 20대 러너의 꿈 KBS 뉴스.</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014116600004</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBnZE9PNDVINmZpajNMVEppN3IyZV9KUE1kZE1xcnd1RHlOV2NIWWJiSGFUUW5Ed2F1QkNFNllwY24xY0JUT29VZ3Z6eTJIcGFqZ2hsWk5ocHdfdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3737,32 +3737,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>"국평 포기합니다"…서울 청약 넣으려다 마음 바꾼 이유</t>
+          <t>‘한동훈 고발장’ 경찰·중수청 접수…‘자녀 허위스펙·부실 수사’ 의혹</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>"국평 포기합니다"…서울 청약 넣으려다. 바꾼 이유 “분양가 무서워 소형으로”…수도권 청약시장 면적별 양극화 심화 매일경제강원 아파트 9월 분양가 제곱미터에 636만 원 KBS 뉴스"국민평형 너무 비싸요"…서울 청약 80% 소형으로 쏠렸다.</t>
+          <t>‘한동훈 고발장’ 경찰·중수청 접수…‘자녀 허위스펙·부실 수사’ 의혹 한겨레시민단체, '딸 허위 스펙 수사무마' 의혹 한동훈 고발 MBC 뉴스 신지호 “한동훈 딸 의혹…민주당, 쓰레기 재활용하나?” KBS 뉴스한동훈, 법무부 장관 재직시 딸 `허위스펙` 수사무마 의혹으로 고발당해 국제신문한동훈이 자초한 3개의 '사법 리스크' OhmyNews.</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzR1c3Z3JwcXhPMTlOaHJtQzNmREJhdEpVOGtsZ0ZrTVI0RUVuRVV0aTVuREk4SS01d19keFBlWjhGV0VZb3lKeU84dHlQc1FiQ0RHa2lsOG9RUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE15T3V6NzcweXpta2U4ckpqX05XU21wRlgxQ0ltZ1dlejY5ZGgzbzFvaFF5OTBSZlQwcGRBUW1YWXRQdWV0VWU5Wk44azVOVUFtSzljaXJ0WDVpOWhzWTk4MVZzNEFWQnJucl9ldElENVV0QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3774,32 +3774,32 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가</t>
+          <t>국가원로회의 부산지부, 15일 임시총회…지역 발전방안 논의</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가 연합인포맥스 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동…소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척 동아일보카카오 인적분할 앞두고 창사 첫 '그룹 공동 IR' 개최, 계열사 CEO 총출동 비즈니스포스트카카오, AI 시대 ‘신뢰·책임’ 검증 사례 나눈다.</t>
+          <t>각계 원로 인사 모임인 국가원로회의 부산지부는 15일 오전 10시 30분 부산 부산진구 초원농원 양정점에서 임...</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9FREp6R1lfYkJtTEhVUGZqRTdNbXBZbmNUYVpQWDN4c2M0OTZ0TV9OZzJmVW9CZFNITFdtWjNzY1RkTUpmLTYzMWgycEVFbjF6OWRpeGZFdWRjZkN0djBEeXlJVmJnZ1RSbkc4bEl5NDc?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014122000051</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>모건스탠리 "한은, 10월 동결 후 11월 인상…물가 상승 압력"</t>
+          <t>제분업체 6곳, 사료 원료값 8년간 담합…과징금 최대 2100억원</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>모건스탠리는 한국은행이 오는 22일 금융통화위원회에서 기준금리를 연 3.0%로 동결한 후, 11월에 금리를 인...</t>
+          <t>관련매출액 1조4000억원 조사 시작되자 담합 중단 공정위, 임직원 고발 의견대한제분과 CJ제일제당 등 제분업체 6곳이 8년 넘게 사료 원료로 쓰이는 밀가루 부산물의 판매가격을 담..</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014111600008</t>
+          <t>https://www.mk.co.kr/news/economy/12175580</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>[속보] 중국 “단둥~신의주 연결 신압록강대교 15일 개통”</t>
+          <t>PS6, PS2와 PS3 게임 지원 전망 나왔다</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>중국 “단둥~신의주 연결 신압록강대교 15일 개통” 한겨레中 신화통신 "북중 신압록강대교, 15일 공식 개통" MBC 뉴스“신압록강대교 내일 정식 개통…북·중, 개통식 합의” KBS 뉴스북·중 잇는 대교 왜 지금 열리나…북미 대화 앞두고 교류 확대? 마켓인완공부터 개통까지 12년···신압록강대교에 반영된 북·중관계 경향신문.</t>
+          <t>PS6, PS2와 PS3 게임 지원 전망 나왔다. 게임와이“어차피 사라질 운명” 사이버커넥트2 대표 디스크 폐지 찬성 게임메카새로운 보도에 따르면 소니는 플레이스테이션 6를 세 가지 구성으로 출시할 계획입니다.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>게임와이</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNSFZBSFp3Q2xBbzYtb29jUHllSzRBdlp0NWtKZVRkcXE0eWd4NUNvMDNqYjBicno3Mk53ZU9YalpGXzhnMW1vS0VuVy1ocEtFOHAxc29OYm93LWljYkN3SzdySlNFYlFRN1lOYk5wZmR4elZDSVJfX2U4bmEwT3hOTW13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBWN3pmQjJpeUtWZkg5dVBVTUNSYW9zUVV3OXdySkM5NnIzSk5oX0MxMUpsUm55UzdQX2lNaHFpdExPc1VGMHh5UV9SZk1YLUFJOXZ1SFVOOTVNSHpvdDZwTVBPZjg2NUHSAWpBVV95cUxPeGZzYXkzczlJbGRyWG9fSzl5YnhMWFdaT0EzNm5IU19tSGlvTGswSWJZREp3akxKWkxWTzNHR3pDVVBMUXNDenV2UjQ4ZmY1d2NnQkdvdV80UDA2SjcwdDg3TEVpOGtWYXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3890,17 +3890,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>한미반도체, 반도체대전서 HBM4용 TC 본더 등 선봬</t>
+          <t>GC녹십자, LG CNS와 스마트공장 구축…AI 자동화 추진</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>한미반도체는 14일부터 16일까지 서울 강남구 코엑스에서 열리는 '제28회 반도체대전' 에...</t>
+          <t>GC녹십자가 LG CNS와 인공지능 기반 자동화·자율 운영 스마트 공장 구축을 추진한다.</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014115200003</t>
+          <t>https://www.yna.co.kr/view/AKR20261014121800017</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3938,7 +3938,7 @@
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
     <col width="65" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="65" customWidth="1" min="14" max="14"/>
@@ -5252,17 +5252,17 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>237,000원</t>
+          <t>236,000원</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+30,500.0원 (+14.77%)</t>
+          <t>+29,500.0원 (+14.29%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>234,500원</t>
+          <t>233,500원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5272,22 +5272,22 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>228,500원</t>
+          <t>227,500원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+9.5%</t>
+          <t>+10.0%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>RSI 37.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 37.0로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.66x)</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5301,26 +5301,26 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>37.6</v>
+        <v>37</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>한미반도체, 반도체대전서 HBM4용 TC 본더 등 선봬 (주요언론)</t>
+          <t>[하나증권] 삼성화재: 3Q26 Pre - 단기 실적보다 중요한 것은 (하나증권)</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 237000.0]</t>
+          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 236000.0]</t>
         </is>
       </c>
     </row>
@@ -5347,42 +5347,42 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1,449,000원</t>
+          <t>1,439,000원</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+346,000.0원 (+31.37%)</t>
+          <t>+336,000.0원 (+30.46%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1,434,500원</t>
+          <t>1,410,000원</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1,704,500원</t>
+          <t>1,868,000원</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>1,398,500원</t>
+          <t>1,367,000원</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+18.8%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>RSI 31.9로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -5396,16 +5396,16 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>[1812000.0, 1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1449000.0]</t>
+          <t>[1812000.0, 1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1439000.0]</t>
         </is>
       </c>
     </row>
@@ -5442,42 +5442,42 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>318,000원</t>
+          <t>316,000원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-173,750.0원 (-35.35%)</t>
+          <t>-175,500.0원 (-35.71%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>311,500원</t>
+          <t>299,000원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>382,500원</t>
+          <t>313,000원</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>302,000원</t>
+          <t>306,500원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+22.8%</t>
+          <t>+4.5%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>주가가 20일선(349,425원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5491,16 +5491,16 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>24.5</v>
+        <v>22.9</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 317750.0]</t>
+          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 316000.0]</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-40,000.0원 (-26.81%)</t>
+          <t>-40,100.0원 (-26.88%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -5562,17 +5562,17 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+18.3%</t>
+          <t>+18.4%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 109200.0]</t>
+          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 109100.0]</t>
         </is>
       </c>
     </row>
@@ -5632,42 +5632,42 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>181,500원</t>
+          <t>181,000원</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-20,100.0원 (-9.98%)</t>
+          <t>-20,600.0원 (-10.22%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>178,000원</t>
+          <t>169,000원</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>206,500원</t>
+          <t>179,000원</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>172,500원</t>
+          <t>175,500원</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>주가가 20일선(194,060원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5681,16 +5681,16 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>32.3</v>
+        <v>31.5</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 181400.0]</t>
+          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 180900.0]</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-16,100.0원 (-33.47%)</t>
+          <t>-16,150.0원 (-33.58%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5752,17 +5752,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>+10.5%</t>
+          <t>+10.7%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -5776,26 +5776,26 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>35.4</v>
+        <v>34.9</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가 (연합인포맥스)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>[34500.0, 34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 32000.0]</t>
+          <t>[34500.0, 34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 31950.0]</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>181,500원</t>
+          <t>181,000원</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-8,219.049999999988원 (-4.33%)</t>
+          <t>-8,819.049999999988원 (-4.65%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>181,500원</t>
+          <t>177,000원</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>190,500원</t>
+          <t>190,000원</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>174,000원</t>
+          <t>172,000원</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 181400.0]</t>
+          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 180800.0]</t>
         </is>
       </c>
     </row>
@@ -5917,42 +5917,42 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>845,000원</t>
+          <t>839,000원</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-678,000.0원 (-44.52%)</t>
+          <t>-684,000.0원 (-44.91%)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>828,000원</t>
+          <t>797,000원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>1,137,000원</t>
+          <t>830,500원</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>803,000원</t>
+          <t>814,000원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>+37.3%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-13) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>주가가 20일선(1,012,050원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -5966,16 +5966,16 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>[1081000.0, 1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 845000.0]</t>
+          <t>[1081000.0, 1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 839000.0]</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>425,500원</t>
+          <t>426,500원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+25,500.0원 (+6.38%)</t>
+          <t>+26,500.0원 (+6.62%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -6027,17 +6027,17 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>425,500원</t>
+          <t>426,500원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>417,000원</t>
+          <t>418,000원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+14.5%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 71.8, 20일선 이격도 +14.3%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 72.0, 20일선 이격도 +14.5%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -6061,16 +6061,16 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+14.5%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 425500.0]</t>
+          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 426500.0]</t>
         </is>
       </c>
     </row>
@@ -6117,22 +6117,22 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>309,500원</t>
+          <t>303,500원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>325,000원</t>
+          <t>334,000원</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>297,000원</t>
+          <t>294,000원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+10.1%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>$228.52 (약 306,417원)</t>
+          <t>$228.52 (약 305,755원)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -6212,22 +6212,22 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>$228.52 (약 306,417원)</t>
+          <t>$223.95 (약 299,640원)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>$239.95 (약 321,738원)</t>
+          <t>$239.95 (약 321,042원)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>$219.38</t>
+          <t>$217.09</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>$341.27 (약 457,602원)</t>
+          <t>$341.27 (약 456,612원)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6307,22 +6307,22 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>$341.27 (약 457,602원)</t>
+          <t>$334.44 (약 447,480원)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>$358.33 (약 480,482원)</t>
+          <t>$358.33 (약 479,443원)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>$327.62</t>
+          <t>$324.21</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>$375.23 (약 503,138원)</t>
+          <t>$375.23 (약 502,050원)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -6402,22 +6402,22 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>$375.23 (약 503,138원)</t>
+          <t>$367.73 (약 492,009원)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>$393.99 (약 528,295원)</t>
+          <t>$393.99 (약 527,152원)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>$360.22</t>
+          <t>$356.47</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>$543.45 (약 728,701원)</t>
+          <t>$543.45 (약 727,125원)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>$514.20 (약 689,480원)</t>
+          <t>$514.20 (약 687,989원)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>$543.45 (약 728,701원)</t>
+          <t>$543.45 (약 727,125원)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>RSI 70.7, 20일선 이격도 +5.7%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 70.7, 20일선 이격도 +5.7%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>028670.KS</t>
+          <t>128940.KS</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -6582,42 +6582,42 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>7,160원</t>
+          <t>408,000원</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>+1,870.0원 (+35.35%)</t>
+          <t>-93,000.0원 (-18.56%)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>6,000원</t>
+          <t>404,000원</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>7,160원</t>
+          <t>483,500원</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>7,020원</t>
+          <t>393,500원</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>+19.3%</t>
+          <t>+19.7%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>RSI 72.1, 20일선 이격도 +19.3%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>RSI 33.6로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.63x)</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -6631,16 +6631,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>33.6</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>+19.3%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>[6030.0, 6040.0, 5680.0, 5800.0, 5880.0, 5750.0, 5790.0, 5790.0, 5600.0, 5700.0, 5700.0, 5770.0, 5880.0, 6240.0, 6000.0, 6210.0, 6030.0, 6450.0, 6550.0, 7160.0]</t>
+          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 408000.0]</t>
         </is>
       </c>
     </row>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>128940.KS</t>
+          <t>030200.KS</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -6677,42 +6677,42 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>415,000원</t>
+          <t>49,800원</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>-86,000.0원 (-17.17%)</t>
+          <t>-14,400.0원 (-22.43%)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>411,000원</t>
+          <t>49,300원</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>484,000원</t>
+          <t>52,800원</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>400,500원</t>
+          <t>48,100원</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>+17.8%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>RSI 34.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 32.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.53x)</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -6726,16 +6726,16 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>34.6</v>
+        <v>32.1</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 415000.0]</t>
+          <t>[52700.0, 53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 49800.0]</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>011200.KS</t>
+          <t>032640.KS</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -6772,42 +6772,42 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>23,400원</t>
+          <t>14,700원</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>+2,400.0원 (+11.43%)</t>
+          <t>-2,770.0원 (-15.86%)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>21,200원</t>
+          <t>14,400원</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>23,400원</t>
+          <t>15,400원</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>14,000원</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>RSI 68.4, 20일선 이격도 +10.3%로 단기 과열권, 분할 차익 실현 권고</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -6821,16 +6821,16 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>[20850.0, 21250.0, 20650.0, 20350.0, 20750.0, 20800.0, 21100.0, 21200.0, 20800.0, 21250.0, 21000.0, 20850.0, 21150.0, 21500.0, 21450.0, 21400.0, 20800.0, 21800.0, 22050.0, 23400.0]</t>
+          <t>[14890.0, 15040.0, 14850.0, 14650.0, 14680.0, 14050.0, 14490.0, 14570.0, 14640.0, 14770.0, 14800.0, 14530.0, 14540.0, 14550.0, 14560.0, 14500.0, 14400.0, 14550.0, 14780.0, 14700.0]</t>
         </is>
       </c>
     </row>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>103590.KS</t>
+          <t>017670.KS</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -6867,42 +6867,42 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>77,000원</t>
+          <t>82,200원</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>-7,300.0원 (-8.66%)</t>
+          <t>-13,300.0원 (-13.93%)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>77,000원</t>
+          <t>81,400원</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>80,800원</t>
+          <t>87,100원</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>73,900원</t>
+          <t>79,300원</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>RSI 38.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.79x)</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -6916,16 +6916,16 @@
         </is>
       </c>
       <c r="O32" s="3" t="n">
-        <v>50.7</v>
+        <v>38.1</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 77000.0]</t>
+          <t>[90900.0, 90100.0, 88000.0, 88100.0, 87600.0, 89200.0, 87000.0, 87300.0, 87100.0, 88200.0, 86200.0, 85600.0, 86300.0, 88400.0, 88400.0, 87400.0, 84100.0, 79700.0, 80000.0, 82200.0]</t>
         </is>
       </c>
     </row>
@@ -6947,12 +6947,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>일진전기</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>086280.KS</t>
+          <t>103590.KS</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -6962,42 +6962,42 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>185,500원</t>
+          <t>76,000원</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>-33,900.0원 (-15.44%)</t>
+          <t>-8,300.0원 (-9.85%)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>183,500원</t>
+          <t>74,500원</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>196,500원</t>
+          <t>88,000원</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>179,000원</t>
+          <t>72,200원</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+18.2%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>RSI 38.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -7011,16 +7011,16 @@
         </is>
       </c>
       <c r="O33" s="3" t="n">
-        <v>38.6</v>
+        <v>49.4</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>[208500.0, 207000.0, 204500.0, 200500.0, 206000.0, 203500.0, 203000.0, 203000.0, 196900.0, 199100.0, 197500.0, 196800.0, 198400.0, 201500.0, 201000.0, 188000.0, 182900.0, 181900.0, 180600.0, 185600.0]</t>
+          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 76000.0]</t>
         </is>
       </c>
     </row>
@@ -7042,12 +7042,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>000810.KS</t>
+          <t>010140.KS</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7057,42 +7057,42 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>581,000원</t>
+          <t>19,200원</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>+91,500.0원 (+18.69%)</t>
+          <t>-8,750.0원 (-31.36%)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>575,000원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>629,000원</t>
+          <t>22,100원</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>560,500원</t>
+          <t>18,200원</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>+9.4%</t>
+          <t>+17.8%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>RSI 33.5로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -7106,16 +7106,16 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>33.5</v>
+        <v>42.7</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 581000.0]</t>
+          <t>[21400.0, 22100.0, 20700.0, 20200.0, 21500.0, 20800.0, 20600.0, 20600.0, 20250.0, 20100.0, 19330.0, 19700.0, 19720.0, 19960.0, 19700.0, 19540.0, 18860.0, 18010.0, 18360.0, 19150.0]</t>
         </is>
       </c>
     </row>
@@ -7137,12 +7137,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>세아베스틸지주</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>001430.KS</t>
+          <t>000810.KS</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -7152,42 +7152,42 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>43,600원</t>
+          <t>584,000원</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>-24,000.0원 (-35.50%)</t>
+          <t>+94,500.0원 (+19.31%)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>43,600원</t>
+          <t>578,000원</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>45,800원</t>
+          <t>629,500원</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>41,900원</t>
+          <t>563,500원</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>RSI 34.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.85x)</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -7201,16 +7201,16 @@
         </is>
       </c>
       <c r="O35" s="3" t="n">
-        <v>49.2</v>
+        <v>34.1</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>[41450.0, 40950.0, 43250.0, 43250.0, 45450.0, 45050.0, 43800.0, 45600.0, 44300.0, 44600.0, 45300.0, 44950.0, 47000.0, 46650.0, 47250.0, 44150.0, 46800.0, 44500.0, 43150.0, 43600.0]</t>
+          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 584000.0]</t>
         </is>
       </c>
     </row>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>한화손해보험</t>
+          <t>휴젤</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>000370.KS</t>
+          <t>145020.KS</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -7247,42 +7247,42 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>6,440원</t>
+          <t>223,500원</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>-170.0원 (-2.57%)</t>
+          <t>-29,500.0원 (-11.66%)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>6,380원</t>
+          <t>200,000원</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>7,510원</t>
+          <t>223,500원</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>6,210원</t>
+          <t>219,000원</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>+17.8%</t>
+          <t>+11.7%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
+          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>RSI 30.7로 단기 과매도 구간 진입, 기술적 반등 노림</t>
+          <t>RSI 19.6, 20일선 이격도 +11.7%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -7296,16 +7296,16 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>30.7</v>
+        <v>19.6</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>+11.7%</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
@@ -7315,197 +7315,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>[8420.0, 8500.0, 8320.0, 8080.0, 8290.0, 8070.0, 8070.0, 7790.0, 7610.0, 7890.0, 7880.0, 7300.0, 7280.0, 7330.0, 7230.0, 7340.0, 7200.0, 7230.0, 7010.0, 6440.0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>휴젤</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>145020.KS</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>증권사 공식리서치</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>223,500원</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>-29,500.0원 (-11.66%)</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>221,500원</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>237,000원</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>215,500원</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>+7.1%</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>🟢 오늘 단기 매수 (저점 반등)</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>RSI 19.6로 단기 과매도 구간 진입, 기술적 반등 노림</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>보유 / 중립 (HOLD)</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>장기 추세 유지</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>+11.7%</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>41.1%</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>최근 특이 뉴스 없음</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
           <t>[236000.0, 231000.0, 232000.0, 235500.0, 231000.0, 231500.0, 214000.0, 206000.0, 190400.0, 187000.0, 186100.0, 183300.0, 179700.0, 180600.0, 180100.0, 181500.0, 183600.0, 182800.0, 180000.0, 169900.0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>세아제강</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>306200.KS</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>증권사 공식리서치</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>142,000원</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>-6,500.0원 (-4.38%)</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>142,000원</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>149,000원</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>136,500원</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>+5.0%</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>관망 (HOLD)</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>중립 구간 유지 중</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>보유 / 중립 (HOLD)</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>장기 추세 유지</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>-3.5%</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>39.0%</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>최근 특이 뉴스 없음</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>[150600.0, 151400.0, 146900.0, 145300.0, 147400.0, 149600.0, 145200.0, 142700.0, 138200.0, 147500.0, 146200.0, 153200.0, 148300.0, 154600.0, 155100.0, 148500.0, 145200.0, 143500.0, 141300.0, 142000.0]</t>
         </is>
       </c>
     </row>
@@ -7520,14 +7330,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7737,12 +7547,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6,106.83</t>
+          <t>6,068.91</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+71.48 (+1.18%)</t>
+          <t>▲ +33.56 (+0.56%)</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7574,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>838.62</t>
+          <t>831.05</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-10.57 (-1.24%)</t>
+          <t>▼ -18.14 (-2.14%)</t>
         </is>
       </c>
     </row>
@@ -7781,22 +7591,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>환율</t>
+          <t>증시 지수</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>미국 달러 (USD)</t>
+          <t>나스닥 (NASDAQ)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1,340.88</t>
+          <t>27,204.38</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>매매기준율</t>
+          <t>▼ -41.52 (-0.15%)</t>
         </is>
       </c>
     </row>
@@ -7808,22 +7618,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>환율</t>
+          <t>증시 지수</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>일본 100엔 (JPY)</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>847.01</t>
+          <t>7,805.45</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>100엔 기준</t>
+          <t>▼ -1.79 (-0.02%)</t>
         </is>
       </c>
     </row>
@@ -7840,17 +7650,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>유로 (EUR)</t>
+          <t>미국 달러 (USD)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1,500.84</t>
+          <t>1,337.98</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>매매기준율</t>
+          <t>▼ -2.15원 (-0.16%)</t>
         </is>
       </c>
     </row>
@@ -7867,17 +7677,71 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>일본 100엔 (JPY)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>842.80</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>▼ -1.30원 (-0.15%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>유로 (EUR)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>1,498.50</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>▼ -1.40원 (-0.09%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>중국 위안 (CNY)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>199.98</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>매매기준율</t>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>199.96</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>▼ -0.25원 (-0.13%)</t>
         </is>
       </c>
     </row>
@@ -7983,27 +7847,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,702,000원</t>
+          <t>112,763,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>112,138,000원</t>
+          <t>112,199,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,718,000원</t>
+          <t>121,784,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,586,000원</t>
+          <t>110,584,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -8040,27 +7904,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3,384,000원</t>
+          <t>3,381,000원</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3,357,000원</t>
+          <t>3,354,000원</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3,587,000원</t>
+          <t>3,584,000원</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3,265,500원</t>
+          <t>3,262,500원</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -8075,7 +7939,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>RSI 46.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 46.5로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -8097,17 +7961,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>145,000원</t>
+          <t>144,700원</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>143,800원</t>
+          <t>143,500원</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -8117,12 +7981,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>139,900원</t>
+          <t>139,600원</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>+8.3%</t>
+          <t>+8.6%</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -8132,7 +7996,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>RSI 47.3로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 46.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -8153,15 +8017,15 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="65" customWidth="1" min="14" max="14"/>
   </cols>
@@ -8245,21 +8109,21 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>빛을 보기 시작한 포트폴리오 변화</t>
+          <t>컨센서스에 부합</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -8269,42 +8133,42 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>한 단계 진화한 실적, 한 단계 진화할 주가 레벨 수급 영향으로 단기 주가의 변동폭은 과거 대비 커졌으나 우호적인 벌크·탱커 시황 감안 시 중기 우상향 흐름 지속될 것으로 판단. 환율 방향성이원화 환산 실적에 부담이나 펀더멘털에 미치는 영향은 제한적.</t>
+          <t>3Q26 Preview: 컨센서스에 부합하는 실적 전망 SK하이닉스의 26년 3분기 매출액은 99.2조원(YoY +306%, QoQ +25%), 영업이익은 77.9조원(YoY +584%, QoQ +29%)으로 추정한다. 매출액과 영업이익 모두 최근 낮아진 컨센서스에 부합할 전망이다. 환율 가정은 기존대비 5% 하향 조정했고, DRAM 가격은 기존 19%에서 21%로 상향, NAND 가격은 기존 24%에서 17%로 하향했다.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_팬오션_빛을 보기 시작한 포트폴리오 변화.pdf</t>
+          <t>2026-10-14_하나증권_SK하이닉스_컨센서스에 부합.pdf</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>7,426.1십억원</t>
+          <t>335,642.4십억원</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>726.2십억원</t>
+          <t>258,778.7십억원</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>7,662.9십억원</t>
+          <t>500,127.3십억원</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>742.3십억원</t>
+          <t>405,117.1십억원</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>3Q26 영업이익 2,027억원(+61</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8179,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -8389,17 +8253,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>우려도 있지만 너무 잠잠한 주가</t>
+          <t>3Q 프리뷰 - 2027년도 내다본 매수 추천</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -8409,42 +8273,42 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>거버넌스 우려로 덮어놓기엔 아까운 실적 글로벌 컨테이너선사들은 가이던스 상향과 함께 주가도 상승했으나 동사 반응은 제한적. 거버넌스 불확실성에도 예상보다.</t>
+          <t>추천 사유는 1) 2027~2028년 장기 실적 전망이 여전히 낙관적이고, 2) 2026년 KT 실적 및 배당 관련 우려가 대부분 주가에 기반영된 상태이며, 3) 2027년 국내에서도 5G 요금제 개편 이슈가 불거질 것임을 감안하면 밸류에이션 매력도가 높고, 4) 연말 이후 국내 시중 금리가 하락 전환한다고 가정 시 배당 매력도 다시 부각될 수 있을 것이며, 5) 스페이스X 통신산업 진출 가능성으로 미국 통신사 주가 하락이 나타난 데 따른 연쇄 반응으로 KT/SKT 주가 하락이 나타났기 때문이다. 주파수 획득, 대주주 적격성 심사 등 국내 규제 상황과 최근 통신업 사업성을 감안 시 스페이스X가 직접 국내에 진출해 국내 통신 3사와 경쟁할 가능성은 희박하다.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_HMM_우려도 있지만 너무 잠잠한 주가.pdf</t>
+          <t>2026-10-14_하나증권_KT_3Q 프리뷰 - 2027년도 내다본 매수 추천.pdf</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>14,179.9십억원</t>
+          <t>27,767.0십억원</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2,497.7십억원</t>
+          <t>2,050.0십억원</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>14,293.1십억원</t>
+          <t>29,466.9십억원</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1,812.7십억원</t>
+          <t>2,088.5십억원</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>3Q26 매출 4조 802억원(+51%, 이하 YoY) 및 영업이익 1조 42억원(+</t>
+          <t>연결 영업이익 5,520억원으로 컨센서스와 비슷할 전망</t>
         </is>
       </c>
     </row>
@@ -8455,21 +8319,21 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>가장 저평가된 전력기기</t>
+          <t>3Q 프리뷰 - 특별한 대안 없다면 길게 보세요</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -8479,42 +8343,42 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단.</t>
+          <t>매수 투자의견/TP 20,000원 유지, 매도하기보단 배당 감안한 중/장기 매수 추천 LGU+에 대한 투자의견 매수, 12개월 목표주가 20,000원을 유지한다. 추천 사유는 1) 2분기에 이어 3분기에도 우수한 실적을 기록할 것으로 전망됨에 따라 2026년 연간 높은 연결 영업이익 성장 가능성이 높아졌고, 2) 양호한 실적 전망을 바탕으로 2027년도엔 다시 주주환원 증대 기대감이 높아질 전망이며, 3) 조만간 정책 금리 상승이 마무리되고 시중 금리가 하락 전환하면서 연말 이후 4.8%에 달하는 기대배당수익률이 매력적으로 인식될 수 있을 것이기 때문이다. 당장 특별한 재료가 부각될 수 있는 상황은 아니지만 국내 주식 시장이 강한 상승 탄력을 나타나고 있지 않은 점을 감안하면 차라리 매도하기 보단 2027년 초까지 LGU+ 보유 또는 배당을 염두에 둔 신규 매수 진입을 추천한다.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
+          <t>2026-10-14_하나증권_LG유플러스_3Q 프리뷰 - 특별한 대안 없다면 길게 보세요.pdf</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2,350.8십억원</t>
+          <t>15,429.4십억원</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>252.8십억원</t>
+          <t>1,144.2십억원</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2,595.2십억원</t>
+          <t>16,347.1십억원</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>271.7십억원</t>
+          <t>1,185.5십억원</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>연결 영업이익 3,221억원 전망, 4Q 인센티브 반영 고려해도 올해 실적 좋을 것</t>
         </is>
       </c>
     </row>
@@ -8525,21 +8389,21 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>환율은 야속하지만 너무 좋은 해운 업황</t>
+          <t>3Q 프리뷰 - DPS 증가 기대감 커지는 계기될 것</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -8549,42 +8413,42 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>자동차 밸류체인이지만 해운사이기도 함. 단기 실적 가시성은 다소 낮아졌으나 이익 방향성은 여전히 긍정적. 비계열 고객 호조로 이익 개선이 뚜렷한 사업부를 가진 점은 차별화 포인트.</t>
+          <t>더불어 국내 통신서비스 업종 12개월/10월 Top Pick으로 제시한다. 추천 사유는 1) 3분기 실적도 양호할 전망이라 2026년 연간 연결 영업이익이 2조원에 육박할 전망이고, 2) 2026년 우수한 실적을 바탕으로 DPS가 2024년 수준으로 회귀할 전망이며, 3) 엔트로픽 상장 가치가 당초 기대를 뛰어넘을 것으로 보여 밸류에이션상 저평가 논란이 생겨날 것이고, 4) 금리 인상 기조가 마무리되고 SKT 비과세 배당이 시작되는 2026년 말/2027년 초부터는 수급 개선이 예상되기 때문이다.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_현대글로비스_환율은 야속하지만 너무 좋은 해운 업황.pdf</t>
+          <t>2026-10-14_하나증권_SK텔레콤_3Q 프리뷰 - DPS 증가 기대감 커지는 계기될 것.pdf</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>33,217.4십억원</t>
+          <t>17,658.0십억원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2,077.2십억원</t>
+          <t>1,950.1십억원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>34,964.5십억원</t>
+          <t>18,217.8십억원</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>2,408.5십억원</t>
+          <t>2,013.5십억원</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>2026년 연간 연결 영업이익이 2조원에 육박할 전망이고, 2) 2026년 우수한 실적을 바탕으</t>
         </is>
       </c>
     </row>
@@ -8599,17 +8463,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>일진전기</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
+          <t>가장 저평가된 전력기기</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -8619,37 +8483,37 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
+          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
+          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,350.8십억원</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>3,496십억원</t>
+          <t>252.8십억원</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,595.2십억원</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>4,566십억원</t>
+          <t>271.7십억원</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -8665,21 +8529,21 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>DS투자증권</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>세아베스틸지주</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>3분기는 다소 부진하겠지만 4분기부터 회복 기대</t>
+          <t>3Q26 Preview: 증익의 시작점</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -8689,42 +8553,42 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 주력 자회사들 판매 감소와 스프레드 축소 2026년 3분기 세아베스틸지주의 매출액과 영업이익은 각각 1.0조원(YoY +10.3%, QoQ -10.6%)과 236억원(YoY -12.4%, QoQ -60.6%)으로 영업이익은 시장컨센서스인 398억원을 크게 하회할 것으로 예상된다. 계절적 비수기와 9월 추석 연휴 영향으로 세아베스틸의 특수강 판매는 41.2만톤(YoY +5.0%, QoQ -9.8%)에 그치며 고정비 부담이 확대될 전망이다. 원가 상승분 가격 전가를 위한 노력으로 8월초까지 적극적인 가격 인상을 시도한 결과, 특수강 ASP가 1.6만원/톤 상승이 예상되나 스크랩가격이 이를 상회하는 2.1만원/톤 상승하여 스프레드도 소폭 축소될 전망이다.</t>
+          <t>3Q26 Preview: 영업이익 3,791억원으로 컨센서스 소폭 상회 전망 26년 3분기 실적은 매출액 3.2조원(이하 YoY +22.8%), 영업이익 3,791억원(+59.2%, OPM 11.7%)으로 시장 컨센서스를 10% 상회할 전망이다. 조업일수는 하계 휴가와 추석 연휴 등으로 전분기 대비 9일 감소하나 글로벌 오퍼레이션과 2도크 재가동에 따른 매출 확대가 이를 상쇄하며 탑라인은 전분기 대비 소폭 성장할 것으로 예상된다. 수익성 또한 확대될 예정이다.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_세아베스틸지주_3분기는 다소 부진하겠지만 4분기부터 회복 기대.pdf</t>
+          <t>2026-10-14_DS투자증권_삼성중공업_3Q26 Preview 증익의 시작점.pdf</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>4,116.0십억원</t>
+          <t>10,650십억원</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>140.6십억원</t>
+          <t>862십억원</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4,496.9십억원</t>
+          <t>12,916십억원</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>223.3십억원</t>
+          <t>1,416십억원</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 영업이익 236억원(YoY -</t>
+          <t>3Q26 Preview: 영업이익 3,791억원으로 컨센서스 소폭 상회 전망</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8608,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>한화손해보험</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Pre - 보험손익 개선세에 주목</t>
+          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -8764,12 +8628,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 실적은 컨센서스 소폭 하회 전망 3분기 별도 당기순이익은 903억원으로 컨센서스(939억원)를 소폭 하회할 것으로 전망한다. 증시 부진 및 금리 상승에 따른 투자손익 악화가 예상되나, 보험손익은 전반적으로 개선될 전망이다. [보험손익] 보험손익은 1,377억원(YoY +44.5%, QoQ +35.2%)으로 추정한다.</t>
+          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_한화손해보험_3Q26 Pre - 보험손익 개선세에 주목.pdf</t>
+          <t>2026-10-14_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -8779,7 +8643,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>465십억원</t>
+          <t>3,496십억원</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -8789,7 +8653,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>595십억원</t>
+          <t>4,566십억원</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -8809,17 +8673,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>유안타증권</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
+          <t>바닥 통과, 성장 엔진 점화</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -8829,42 +8693,42 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다.</t>
+          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY 3Q26 연결 영업수익은 7.1조원(-1.1% YoY), 영업이익은 5,350억원(-0.6% YoY)으로 시장 컨센서스(7.0조원, 5,442억원)에 부합할 전망이다. 부동산 관련 일회성 비용 제거시 영업이익은 +2.8% YoY 증가한 것으로 추정된다. 별도 영업이익은 3,400억원으로 전년과 유사한 수준이 예상된다.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
+          <t>2026-10-14_유안타증권_KT_바닥 통과, 성장 엔진 점화.pdf</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>486십억원</t>
+          <t>27,426십억원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>174십억원</t>
+          <t>2,076십억원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>657십억원</t>
+          <t>27,905십억원</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>272십억원</t>
+          <t>2,256십억원</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>3Q26 매출액은 1,009억원(-4</t>
+          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY</t>
         </is>
       </c>
     </row>
@@ -8875,21 +8739,21 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>휴젤</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>어려운 영업환경!</t>
+          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -8899,42 +8763,42 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>3Q26 내수와 수출 모두 수익성 악화 2026년 3분기 세아제강의 매출액과 영업이익은 각각 4,318억원(YoY +30.2%, QoQ -12.8%)과 195억원(YoY 흑.전, QoQ -44.2%)으로 영업이익은 시장컨센서스인 254억원을 하회할 것으로 예상된다. 3분기 내수 강관 시장은 계절적 비수기와 추석 연휴 영향으로 다소 부진할 것으로 예상되는 가운데 수출의 경우 캐나다. LNG와 같은 프로젝트 덕분에 소폭 증가한 것으로 추정되어 결과적으로 세아제강의 3분기 전체 강관 판매는 22.8만톤(YoY +21.4%, QoQ -6.8%)을 기록할 전망이다.</t>
+          <t>3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_세아제강_어려운 영업환경!.pdf</t>
+          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1,822.7십억원</t>
+          <t>486십억원</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>103.1십억원</t>
+          <t>174십억원</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>1,852.8십억원</t>
+          <t>657십억원</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>124.3십억원</t>
+          <t>272십억원</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 세아제강의 매출액과 영업이익은 각각 4,318억원(YoY +30</t>
+          <t>3Q26 매출액은 1,009억원(-4</t>
         </is>
       </c>
     </row>
@@ -8949,20 +8813,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -9076,7 +8940,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -9138,7 +9002,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -9200,7 +9064,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -9262,7 +9126,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -9324,7 +9188,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -9386,7 +9250,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -9423,12 +9287,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>238,500원</t>
+          <t>236,500원</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>236,000원</t>
+          <t>234,000원</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -9438,7 +9302,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>230,000원</t>
+          <t>228,000원</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -9448,12 +9312,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>236,750원</t>
+          <t>235,750원</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -9475,32 +9339,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>000660.KS</t>
+          <t>128940.KS</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1,456,000원</t>
+          <t>409,000원</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1,441,500원</t>
+          <t>405,000원</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1,705,000원</t>
+          <t>483,500원</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,405,000원</t>
+          <t>394,500원</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -9510,12 +9374,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>1,447,000원</t>
+          <t>408,000원</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -9537,32 +9401,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>128940.KS</t>
+          <t>030200.KS</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>417,500원</t>
+          <t>49,800원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>413,500원</t>
+          <t>49,300원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>484,000원</t>
+          <t>52,700원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>403,000원</t>
+          <t>48,000원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -9572,12 +9436,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>415,500원</t>
+          <t>49,800원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -9599,32 +9463,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>086280.KS</t>
+          <t>017670.KS</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>185,500원</t>
+          <t>82,200원</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>184,000원</t>
+          <t>81,400원</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>197,000원</t>
+          <t>87,100원</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>179,000원</t>
+          <t>79,300원</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -9634,12 +9498,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>185,600원</t>
+          <t>82,200원</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -9671,22 +9535,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>581,000원</t>
+          <t>584,000원</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>575,000원</t>
+          <t>578,000원</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>629,000원</t>
+          <t>629,500원</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>560,500원</t>
+          <t>563,500원</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -9696,139 +9560,15 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>582,000원</t>
+          <t>584,000원</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>1일차</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>한화손해보험</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>000370.KS</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>6,440원</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>6,380원</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>7,510원</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>6,210원</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>+0.9%</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>6,440원</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>1일차</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>휴젤</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>145020.KS</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>223,500원</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>221,500원</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>237,000원</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>215,500원</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>+0.9%</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>223,500원</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
@@ -10242,7 +9982,7 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>풍산, 최대주주등 지분율 38.02% 유지, 임원 장내매수로 108주 증가</t>
+          <t>사이먼 쿠케스 박사 측, 페데브코 보통주 14만 7070주 장내 매수…지분율 34.2%로 확대</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -10257,12 +9997,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 08:03:15 GMT</t>
+          <t>Tue, 13 Oct 2026 12:14:51 GMT</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBCY2RfTnBJdUJVUW5lcFdtUGtuYXhMNmRwNkVmREpRVTdyRUQ3Y2ZfaWFTMUhNVkpSZEdJUGdzMnZ4RWZQSlpwSG9FS2FlV05kaktCSm16clk5Tjg1a0t2MHNmMkw0WHBrdm9fR2lkVXlCODA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE8wVldLdklzOFE4cnp4RmlPLVJ2LVdveDVQTUV2UjhyTjh1NVhIMG5maUxkelFnUkhEV1ZxdGY2empxS252cDk5QW9ua2EtZ3lRUl94bVA5UEg4b09SZXdMcUk5UnlrbHRpZGU4V1VNYTdzNjQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10594,32 +10334,32 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>🌐 [경제·사회 심층 리포트] 모두의 AI의 숨겨진 배경과 구조적 쟁점</t>
+          <t>🌐 [경제·사회 심층 리포트] GC녹십자의 숨겨진 배경과 구조적 쟁점</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>모두의 AI</t>
+          <t>GC녹십자</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '모두의 AI' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
+          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: 'GC녹십자' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 카카오 '모두의 AI' MAU 500만 목표…과업 완료율로 성과 평가 연합인포맥스 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동…소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척 동아일보카카오 인적분할 앞두고 창사 첫 '그룹 공동 IR' 개최, 계열사 CEO 총출동 비즈니스포스트카카오, AI 시대 ‘신뢰·책임’ 검증 사례 나눈다.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
+          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[GC녹십자, LG CNS와 스마트공장 구축…AI 자동화 추진]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; GC녹십자가 LG CNS와 인공지능 기반 자동화·자율 운영 스마트 공장 구축을 추진한다.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; KT컨소시엄, ‘모두의 AI Connect Summit 2026’ 개최 바끄로뉴스. '국민이 체감' 모두의 AI, 이용자 사로잡을 전략은 비즈워치.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
+          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; GC녹십자, 헌터라제 알레르기 유발 항체 정밀 검출 기술 개발 뉴스저널리즘. 어려울 때 GC녹십자 2분기 살린 건, 끈끈한 '피의 힘' 히트뉴스.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 통신 3사, 3Q 영업익 1.4조 전망…일회성 비용 털고 AI 성장 가속 매일일보. SKT·KT·카카오, ‘모두의 AI’ 누가 먼저 기선잡나… 베타 서비스 10월 출격, 각축전 ‘점화’ CEO스코어데일리.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
+          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; GC녹십자, 헌터라제 특이 IgE 항체 정밀 분석법 개발…국제학술지 게재 나눔경제뉴스. GC녹십자웰빙, 비만·체형관리까지…'에스테틱' 판 키운다.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -10634,12 +10374,12 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9FREp6R1lfYkJtTEhVUGZqRTdNbXBZbmNUYVpQWDN4c2M0OTZ0TV9OZzJmVW9CZFNITFdtWjNzY1RkTUpmLTYzMWgycEVFbjF6OWRpeGZFdWRjZkN0djBEeXlJVmJnZ1RSbkc4bEl5NDc?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014121800017</t>
         </is>
       </c>
     </row>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3631,27 +3631,27 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>윤석열 선거법 2심, 오는 27일 선고‥국민의힘 '선거비용 397억 원 반환' 달렸다</t>
+          <t>“신임 비서실장은 임광현”…떠나는 강훈식 마지막 브리핑 [지금뉴스]</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>윤석열 선거법 2심, 오는 27일 선고‥국민의힘 '선거비용 397억 원 반환' 달렸다. MBC 뉴스'국힘 397억 반환' 걸린 尹 재판서 특검 '당선무효형 유지' 요청 MBC 뉴스‘국힘 397억 반환’ 걸린 2심서…윤 "이럴 거면 선거 왜 해" JTBC‘국힘 397억’ 걸린 尹 선거법 2심 27일 선고 동아일보특검, 尹 '여론조사 무상수수' 무죄 판결에 상고…"납득 어려워".</t>
+          <t>“신임 비서실장은 임광현”떠나는 강훈식 마지막 브리핑 KBS 뉴스 신임 대통령 비서실장에 임광현 국세청장 JTBC이 대통령, ‘강훈식 후임’ 새 비서실장에 임광현 국세청장 임명 한겨레안철수 "임광현 비서실장, 보은 인사 결정판처남 대장동 변호사" 뉴스1李 '먹사니즘' 세제 공약 설계한 임광현黨영입인재서 靑비서실장까지 아시아경제.</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBqVlppeEExSms5RGVjN2ZqY2Y1bXN6ZlV4MTJlcnc3VERVT1BNRDRBZG94Q2xFaGxSZ3JEelJZVk1NNFMzOUt4WW1jOXd2Z0xydXlFajhLM05qZU8xc3RGVlM2NXdteHd1b3FPMjZPdm9UWHFmcjBJ0gF3QVVfeXFMT2FLNS01aG8xbG5qdVpQVl82RmpXVktST0k1VHZ6T2lzdk1lNXJGa1RrV21jZGkxRVUtMzVhdjRFdEF3QUJtRjI0RktXTjhmc2s1YzNLZHpHcDJUZy1Jb2lrYm43ZFpfazFmZUF6OFNtMUJwdEE4M28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBOT2xfekhrRnVZc3FfaENuU0xNRUJEczB5Z2RWVjRCLUtheS1VZ2UyUk9GT3J4aHNuclBVS0o5T3FPMFRRYWhwMTYxQWNiUDVQYkd4Ni1XbTdfem8?oc=5</t>
         </is>
       </c>
     </row>
@@ -3668,27 +3668,27 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>대입 논술시험서 AI안경 쓴 수험생들 적발…시립대 "응시 3년 금지"</t>
+          <t>인천 흉기난동범 "관심 끌려 범행…힘없어 보이는 사람 골랐다"</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>대입 논술시험서 AI안경 쓴 수험생들 적발…시립대 "응시 3년 금지" 논술 시험장에 등장한 스마트안경…연세대·시립대서 줄줄이 적발 KBS 뉴스뿔테 안경 아니었어?···연세대 논술 시험장서 ‘스마트 안경’ 적발 주간경향정근식, '스마트 안경' 부정행위 우려에 "교육부 지침 따라 대응" MBC 뉴스수험생들 “이번 수능때 AI 안경 쓸것”… 대학선 방지책 비상 문화일보.</t>
+          <t>인천 대형 상업시설에서 흉기를 휘둘러 8명을 다치게 한 50대 남성이 자신의 불만을 사회적으로 알리고 싶어 범.</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBkb21vYW14V21SZVNZOVlHaGIyRkJ4TlA5RU9IYkRrekVpOVBSbjlqLWdSZ25mcnVpOUhvS1R5WGpjSGdicm4xSDhCR2xERjduVktqR3RveWJKY03SAWBBVV95cUxObXlQc0RwOFRTSnJaSk9MUTM1S3JsaFlsSUVsc1ZGeWc1SUVjNGFWLUNiWExVc2pTSkpmc1Eyek80WHN3cE9tOHdBZXJIMm5aNno5TGR2bFZ0cml1aEM0WE8?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014134000065</t>
         </is>
       </c>
     </row>
@@ -3710,22 +3710,22 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>"뛰다가 죽음 이를 수도"…황영조가 러너들에 던진 경고</t>
+          <t>'1심 무죄' 前경호처장 2심 징역 1년…尹비화폰 증거인멸 유죄(종합)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>이를 수도"…황영조가 러너들에 던진 경고 황영조 ’러닝 경고’…“기록·SNS 욕심 보다. 몸 상태 체크“ TV"포기할 줄 아는 사람이 잘 뛰는 사람"...잇따른 마라톤 사고에 황영조 '일침' YTN'서울달리기' 숨진 20대女는 '카이스트 대학원생' 유지원씨 파이낸셜뉴스“그냥 달리고 싶어”…결승선 앞 멈춰진 20대 러너의 꿈 KBS 뉴스.</t>
+          <t>12·3 비상계엄 사태 이후 윤석열 전 대통령 등의 비화폰 정보를 삭제한 혐의로 기소된 박종준 전 대통령 경호.</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBnZE9PNDVINmZpajNMVEppN3IyZV9KUE1kZE1xcnd1RHlOV2NIWWJiSGFUUW5Ed2F1QkNFNllwY24xY0JUT29VZ3Z6eTJIcGFqZ2hsWk5ocHdfdw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014123851004</t>
         </is>
       </c>
     </row>
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>‘한동훈 고발장’ 경찰·중수청 접수…‘자녀 허위스펙·부실 수사’ 의혹</t>
+          <t>제주 평화로에서 다중 추돌 교통사고…12대 추정</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>‘한동훈 고발장’ 경찰·중수청 접수…‘자녀 허위스펙·부실 수사’ 의혹 한겨레시민단체, '딸 허위 스펙 수사무마' 의혹 한동훈 고발 MBC 뉴스 신지호 “한동훈 딸 의혹…민주당, 쓰레기 재활용하나?” KBS 뉴스한동훈, 법무부 장관 재직시 딸 `허위스펙` 수사무마 의혹으로 고발당해 국제신문한동훈이 자초한 3개의 '사법 리스크' OhmyNews.</t>
+          <t>14일 오후 3시께 제주시 애월읍 평화로에서 차량 12대 가 잇따라 추돌했다.</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE15T3V6NzcweXpta2U4ckpqX05XU21wRlgxQ0ltZ1dlejY5ZGgzbzFvaFF5OTBSZlQwcGRBUW1YWXRQdWV0VWU5Wk44azVOVUFtSzljaXJ0WDVpOWhzWTk4MVZzNEFWQnJucl9ldElENVV0QQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014135000056</t>
         </is>
       </c>
     </row>
@@ -3774,32 +3774,32 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>국가원로회의 부산지부, 15일 임시총회…지역 발전방안 논의</t>
+          <t>카카오, ‘모두의 AI’ 연내 공개 예정…월 이용자 500만 명 목표</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>각계 원로 인사 모임인 국가원로회의 부산지부는 15일 오전 10시 30분 부산 부산진구 초원농원 양정점에서 임...</t>
+          <t>카카오, ‘모두의 AI’ 연내 공개 예정월 이용자 500만 명 목표 KBS 뉴스카카오그룹, 인적분할 앞두고 주요 계열사 CEO 함께 모여 ‘첫 공동 IR’ 개최 카카오연말 출시 ‘모두의 AI’“카톡 익숙함. 활용할 것” 마켓 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척.</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014122000051</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE43NnU3MlhmZWZkcEdnRU1abkNDcHdIdG85YU9NZVBqVF90N3BXTHFCVlJIbDZQbkg3RGR5NWltZ29IaXNWNkdIWm1aYzBmLU4wbnVfd1hhVnlwdVk?oc=5</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>제분업체 6곳, 사료 원료값 8년간 담합…과징금 최대 2100억원</t>
+          <t>대구 신세계 프리미엄 아울렛 건립 속도…인허가기간 절반 이하로</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>관련매출액 1조4000억원 조사 시작되자 담합 중단 공정위, 임직원 고발 의견대한제분과 CJ제일제당 등 제분업체 6곳이 8년 넘게 사료 원료로 쓰이는 밀가루 부산물의 판매가격을 담..</t>
+          <t>대구시가 신세계사이먼의 '대구 프리미엄 아울렛' 건립을 위한 인허가 기간을 통상의 절반 이하로 줄이는 등 사업.</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175580</t>
+          <t>https://www.yna.co.kr/view/AKR20261014129100053</t>
         </is>
       </c>
     </row>
@@ -3848,32 +3848,32 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>PS6, PS2와 PS3 게임 지원 전망 나왔다</t>
+          <t>토스뱅크, 디지털 취약계층에 노트북 기부</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>PS6, PS2와 PS3 게임 지원 전망 나왔다. 게임와이“어차피 사라질 운명” 사이버커넥트2 대표 디스크 폐지 찬성 게임메카새로운 보도에 따르면 소니는 플레이스테이션 6를 세 가지 구성으로 출시할 계획입니다.</t>
+          <t>토스뱅크가 고령층 문해학습자와 장애인 등 디지털 교육이 필요한 학습자를 지원하기 위해 업무용으로 사용하던 노트북 46대를 기부한다고 14일 밝혔다.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>게임와이</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBWN3pmQjJpeUtWZkg5dVBVTUNSYW9zUVV3OXdySkM5NnIzSk5oX0MxMUpsUm55UzdQX2lNaHFpdExPc1VGMHh5UV9SZk1YLUFJOXZ1SFVOOTVNSHpvdDZwTVBPZjg2NUHSAWpBVV95cUxPeGZzYXkzczlJbGRyWG9fSzl5YnhMWFdaT0EzNm5IU19tSGlvTGswSWJZREp3akxKWkxWTzNHR3pDVVBMUXNDenV2UjQ4ZmY1d2NnQkdvdV80UDA2SjcwdDg3TEVpOGtWYXlR?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12175659</t>
         </is>
       </c>
     </row>
@@ -3885,22 +3885,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>GC녹십자, LG CNS와 스마트공장 구축…AI 자동화 추진</t>
+          <t>올해만 10대 선진국 10년물 국채금리 0.81%p 급등</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>GC녹십자가 LG CNS와 인공지능 기반 자동화·자율 운영 스마트 공장 구축을 추진한다.</t>
+          <t>국제 신용평가사 피치는 국채 금리 상승으로 프랑스, 미국, 영국 등 주요 선진국이 채무 부담을 안정적으로 유지.</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3910,7 +3910,81 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014121800017</t>
+          <t>https://www.yna.co.kr/view/AKR20261014133700009</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>“칼로리에 깜짝” 악뮤 수현도 놀란 ‘최근 유행 디저트’ 정체</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>“칼로리에 깜짝” 악뮤 수현도 놀란 ‘최근 유행 디저트’ 정체 헬스조선‘30㎏ 감량 이수현’ 콘서트 끝나고 ‘한정선’ 먹자트레이너 “10㎞ 뛰어야” '-30kg' 악뮤 이수현, 콘서트 직후 디저트 흡입트레이너에 "말 걸지 마라" 미주30kg 감량한 이수현, ‘이 음식’ 먹자트레이너 “10km 달려야” 서울신문"3시간 줄 선다고?" 갸우뚱이수현, '한정선' 솔직 후기 -.</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>헬스조선</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBldDBTc0RkSFJEOVQ5Y2o5bmJIY3gwaGQxZzZvVzZpRHdsX0RCZ3l3NS1oTm5iR0VERmYybWx4NGhSaGRMSFhXdnpPN1l0Y2JpalJ4WGZ0N3V5RHVKX2NUeF92NzVwOV9tenl5WDVyTXpjd281cHVuZmlGUkwzekU?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>“낙찰가 2400억, 역대 최고가 기대”…반 고흐 '꽃 핀 밤나무' 60년 만에 공개</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>“낙찰가 2400억, 역대 최고가 기대”반 고흐 '꽃 핀 밤나무' 60년 만에 공개 전자신문낙찰 예상가만 2400억60여 년 만에 공개 반고흐의 ‘꽃 핀 밤나무’ KBS 뉴스고흐 말년작 60년만에 공개내달 경매 2400억원 예상 동아일보홍콩서 60여년 만에 반고흐 '꽃 핀 밤나무' 공개수백명 몰려 60년만에 세상 나온 반고흐 명작'경매가 2400억' 신기록 전망 뉴스1.</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>전자신문</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE80XzRkdG90QUU3QUtFbVJUcEJmNVhja2ZjYnRoY09GRUI3WjJfZzZFY1NkbVlwXzJTYWVUUVpfcG5oTVFENHVXbTFJQTRaZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5252,17 +5326,17 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>236,000원</t>
+          <t>232,500원</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+29,500.0원 (+14.29%)</t>
+          <t>+26,000.0원 (+12.59%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>233,500원</t>
+          <t>230,000원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5272,12 +5346,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>227,500원</t>
+          <t>224,500원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+10.0%</t>
+          <t>+11.6%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -5287,7 +5361,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>RSI 37.0로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.66x)</t>
+          <t>RSI 34.7로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.82x)</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5301,16 +5375,16 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -5320,7 +5394,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 236000.0]</t>
+          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 232500.0]</t>
         </is>
       </c>
     </row>
@@ -5347,17 +5421,17 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1,439,000원</t>
+          <t>1,419,000원</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+336,000.0원 (+30.46%)</t>
+          <t>+316,000.0원 (+28.65%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1,410,000원</t>
+          <t>1,390,500원</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -5367,12 +5441,12 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>1,367,000원</t>
+          <t>1,348,000원</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+34.3%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -5396,16 +5470,16 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>31.2</v>
+        <v>30.5</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -5415,7 +5489,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>[1812000.0, 1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1439000.0]</t>
+          <t>[1812000.0, 1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1419000.0]</t>
         </is>
       </c>
     </row>
@@ -5442,32 +5516,32 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>316,000원</t>
+          <t>314,000원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-175,500.0원 (-35.71%)</t>
+          <t>-177,500.0원 (-36.11%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>299,000원</t>
+          <t>298,500원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>313,000원</t>
+          <t>311,000원</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>306,500원</t>
+          <t>304,500원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -5477,7 +5551,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(349,425원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(349,325원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5491,16 +5565,16 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
@@ -5510,7 +5584,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 316000.0]</t>
+          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 314000.0]</t>
         </is>
       </c>
     </row>
@@ -5537,42 +5611,42 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>109,000원</t>
+          <t>108,500원</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-40,100.0원 (-26.88%)</t>
+          <t>-40,800.0원 (-27.35%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>107,000원</t>
+          <t>101,500원</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>126,500원</t>
+          <t>107,500원</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>103,500원</t>
+          <t>105,000원</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+18.4%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>주가가 20일선(115,820원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5586,16 +5660,16 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>31.3</v>
+        <v>29.3</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -5605,7 +5679,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 109100.0]</t>
+          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 108400.0]</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5706,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>181,000원</t>
+          <t>180,000원</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-20,600.0원 (-10.22%)</t>
+          <t>-21,700.0원 (-10.77%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -5647,17 +5721,17 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>179,000원</t>
+          <t>178,000원</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>175,500원</t>
+          <t>174,500원</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -5667,7 +5741,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(194,060원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(194,005원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5681,16 +5755,16 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>31.5</v>
+        <v>29.8</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -5700,7 +5774,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 180900.0]</t>
+          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 179800.0]</t>
         </is>
       </c>
     </row>
@@ -5727,17 +5801,17 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>32,000원</t>
+          <t>31,700원</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-16,150.0원 (-33.58%)</t>
+          <t>-16,400.0원 (-34.10%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>31,300원</t>
+          <t>31,100원</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5747,12 +5821,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>30,100원</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>+10.7%</t>
+          <t>+11.5%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -5776,26 +5850,26 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>34.9</v>
+        <v>32.4</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>카카오, ‘모두의 AI’ 연내 공개 예정…월 이용자 500만 명 목표 (KBS 뉴스)</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>[34500.0, 34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 31950.0]</t>
+          <t>[34500.0, 34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 31700.0]</t>
         </is>
       </c>
     </row>
@@ -5822,27 +5896,27 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>181,000원</t>
+          <t>180,000원</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-8,819.049999999988원 (-4.65%)</t>
+          <t>-9,719.049999999988원 (-5.13%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>177,000원</t>
+          <t>176,500원</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>190,000원</t>
+          <t>189,000원</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>172,000원</t>
+          <t>171,000원</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -5871,16 +5945,16 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -5890,7 +5964,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 180800.0]</t>
+          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 179900.0]</t>
         </is>
       </c>
     </row>
@@ -6012,32 +6086,32 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>426,500원</t>
+          <t>420,500원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+26,500.0원 (+6.62%)</t>
+          <t>+20,500.0원 (+5.12%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>372,500원</t>
+          <t>372,000원</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>426,500원</t>
+          <t>420,500원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>418,000원</t>
+          <t>412,000원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+14.5%</t>
+          <t>+13.0%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -6047,7 +6121,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 72.0, 20일선 이격도 +14.5%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
+          <t>RSI 70.6, 20일선 이격도 +13.0%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -6061,16 +6135,16 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>72</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+14.5%</t>
+          <t>+13.0%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
@@ -6080,7 +6154,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 426500.0]</t>
+          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 420500.0]</t>
         </is>
       </c>
     </row>
@@ -6107,17 +6181,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>309,500원</t>
+          <t>307,500원</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>-52,000.0원 (-14.38%)</t>
+          <t>-54,000.0원 (-14.94%)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>303,500원</t>
+          <t>301,500원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -6127,12 +6201,12 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>294,000원</t>
+          <t>292,000원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+10.1%</t>
+          <t>+10.8%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -6156,16 +6230,16 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>45.7</v>
+        <v>44.2</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
@@ -6175,7 +6249,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>[334000.0, 326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 309500.0]</t>
+          <t>[334000.0, 326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 307500.0]</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6276,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>$228.52 (약 305,755원)</t>
+          <t>$228.52 (약 305,782원)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -6212,12 +6286,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>$223.95 (약 299,640원)</t>
+          <t>$223.95 (약 299,666원)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>$239.95 (약 321,042원)</t>
+          <t>$239.95 (약 321,071원)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -6297,7 +6371,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>$341.27 (약 456,612원)</t>
+          <t>$341.27 (약 456,653원)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6307,12 +6381,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>$334.44 (약 447,480원)</t>
+          <t>$334.44 (약 447,520원)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>$358.33 (약 479,443원)</t>
+          <t>$358.33 (약 479,486원)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -6392,7 +6466,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>$375.23 (약 502,050원)</t>
+          <t>$375.23 (약 502,095원)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -6402,12 +6476,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>$367.73 (약 492,009원)</t>
+          <t>$367.73 (약 492,053원)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>$393.99 (약 527,152원)</t>
+          <t>$393.99 (약 527,200원)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6487,7 +6561,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>$543.45 (약 727,125원)</t>
+          <t>$543.45 (약 727,190원)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -6497,12 +6571,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>$514.20 (약 687,989원)</t>
+          <t>$514.20 (약 688,051원)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>$543.45 (약 727,125원)</t>
+          <t>$543.45 (약 727,190원)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -6582,17 +6656,17 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>408,000원</t>
+          <t>403,500원</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>-93,000.0원 (-18.56%)</t>
+          <t>-97,500.0원 (-19.46%)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>404,000원</t>
+          <t>399,500원</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -6602,12 +6676,12 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>393,500원</t>
+          <t>389,500원</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+21.0%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -6617,7 +6691,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>RSI 33.6로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.63x)</t>
+          <t>RSI 33.0로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.99x)</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -6631,16 +6705,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>33.6</v>
+        <v>33</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
@@ -6650,7 +6724,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 408000.0]</t>
+          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 403500.0]</t>
         </is>
       </c>
     </row>
@@ -6677,27 +6751,27 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>49,800원</t>
+          <t>50,200원</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>-14,400.0원 (-22.43%)</t>
+          <t>-14,000.0원 (-21.81%)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>49,300원</t>
+          <t>49,700원</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>52,800원</t>
+          <t>53,200원</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>48,100원</t>
+          <t>48,400원</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -6712,7 +6786,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>RSI 32.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.53x)</t>
+          <t>RSI 35.8로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.81x)</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -6726,16 +6800,16 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>32.1</v>
+        <v>35.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -6745,7 +6819,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>[52700.0, 53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 49800.0]</t>
+          <t>[52700.0, 53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 50200.0]</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6831,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>032640.KS</t>
+          <t>017670.KS</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -6772,27 +6846,27 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>14,700원</t>
+          <t>81,900원</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>-2,770.0원 (-15.86%)</t>
+          <t>-13,600.0원 (-14.24%)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>14,400원</t>
+          <t>81,100원</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>15,400원</t>
+          <t>86,800원</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>14,000원</t>
+          <t>79,000원</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -6802,12 +6876,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>RSI 37.3로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.96x)</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -6821,16 +6895,16 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>50.7</v>
+        <v>37.3</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
@@ -6840,7 +6914,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>[14890.0, 15040.0, 14850.0, 14650.0, 14680.0, 14050.0, 14490.0, 14570.0, 14640.0, 14770.0, 14800.0, 14530.0, 14540.0, 14550.0, 14560.0, 14500.0, 14400.0, 14550.0, 14780.0, 14700.0]</t>
+          <t>[90900.0, 90100.0, 88000.0, 88100.0, 87600.0, 89200.0, 87000.0, 87300.0, 87100.0, 88200.0, 86200.0, 85600.0, 86300.0, 88400.0, 88400.0, 87400.0, 84100.0, 79700.0, 80000.0, 81900.0]</t>
         </is>
       </c>
     </row>
@@ -6852,12 +6926,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>017670.KS</t>
+          <t>032640.KS</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -6867,27 +6941,27 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>82,200원</t>
+          <t>14,800원</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>-13,300.0원 (-13.93%)</t>
+          <t>-2,700.0원 (-15.46%)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>81,400원</t>
+          <t>14,500원</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>87,100원</t>
+          <t>15,500원</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>79,300원</t>
+          <t>14,000원</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -6897,12 +6971,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>RSI 38.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.79x)</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -6916,16 +6990,16 @@
         </is>
       </c>
       <c r="O32" s="3" t="n">
-        <v>38.1</v>
+        <v>52.5</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -6935,7 +7009,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>[90900.0, 90100.0, 88000.0, 88100.0, 87600.0, 89200.0, 87000.0, 87300.0, 87100.0, 88200.0, 86200.0, 85600.0, 86300.0, 88400.0, 88400.0, 87400.0, 84100.0, 79700.0, 80000.0, 82200.0]</t>
+          <t>[14890.0, 15040.0, 14850.0, 14650.0, 14680.0, 14050.0, 14490.0, 14570.0, 14640.0, 14770.0, 14800.0, 14530.0, 14540.0, 14550.0, 14560.0, 14500.0, 14400.0, 14550.0, 14780.0, 14770.0]</t>
         </is>
       </c>
     </row>
@@ -6962,17 +7036,17 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>76,000원</t>
+          <t>75,000원</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>-8,300.0원 (-9.85%)</t>
+          <t>-9,300.0원 (-11.03%)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>74,500원</t>
+          <t>73,500원</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -6982,12 +7056,12 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>72,200원</t>
+          <t>71,200원</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>+18.2%</t>
+          <t>+19.7%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -7011,16 +7085,16 @@
         </is>
       </c>
       <c r="O33" s="3" t="n">
-        <v>49.4</v>
+        <v>48</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -7030,7 +7104,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 76000.0]</t>
+          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 75000.0]</t>
         </is>
       </c>
     </row>
@@ -7057,12 +7131,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>19,200원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>-8,750.0원 (-31.36%)</t>
+          <t>-8,960.0원 (-32.11%)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -7072,27 +7146,27 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>22,100원</t>
+          <t>20,100원</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>18,200원</t>
+          <t>18,300원</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>+17.8%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>RSI 40.9로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.46x)</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -7106,16 +7180,16 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>42.7</v>
+        <v>40.9</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -7125,7 +7199,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>[21400.0, 22100.0, 20700.0, 20200.0, 21500.0, 20800.0, 20600.0, 20600.0, 20250.0, 20100.0, 19330.0, 19700.0, 19720.0, 19960.0, 19700.0, 19540.0, 18860.0, 18010.0, 18360.0, 19150.0]</t>
+          <t>[21400.0, 22100.0, 20700.0, 20200.0, 21500.0, 20800.0, 20600.0, 20600.0, 20250.0, 20100.0, 19330.0, 19700.0, 19720.0, 19960.0, 19700.0, 19540.0, 18860.0, 18010.0, 18360.0, 18940.0]</t>
         </is>
       </c>
     </row>
@@ -7152,42 +7226,42 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>584,000원</t>
+          <t>582,000원</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>+94,500.0원 (+19.31%)</t>
+          <t>+92,500.0원 (+18.90%)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>578,000원</t>
+          <t>553,000원</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>629,500원</t>
+          <t>576,000원</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>563,500원</t>
+          <t>564,500원</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>+8.9%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>RSI 34.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.85x)</t>
+          <t>주가가 20일선(642,100원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -7201,16 +7275,16 @@
         </is>
       </c>
       <c r="O35" s="3" t="n">
-        <v>34.1</v>
+        <v>33.7</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
@@ -7220,7 +7294,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 584000.0]</t>
+          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 582000.0]</t>
         </is>
       </c>
     </row>
@@ -7547,12 +7621,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6,068.91</t>
+          <t>5,997.24</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>▲ +33.56 (+0.56%)</t>
+          <t>▼ -38.11 (-0.63%)</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7648,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>831.05</t>
+          <t>820.32</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>▼ -18.14 (-2.14%)</t>
+          <t>▼ -28.87 (-3.40%)</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7729,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1,337.98</t>
+          <t>1,338.10</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>▼ -2.15원 (-0.16%)</t>
+          <t>▼ -2.03원 (-0.15%)</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7756,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>842.80</t>
+          <t>843.10</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>▼ -1.30원 (-0.15%)</t>
+          <t>▼ -1.00원 (-0.12%)</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7783,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1,498.50</t>
+          <t>1,498.90</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>▼ -1.40원 (-0.09%)</t>
+          <t>▼ -1.00원 (-0.07%)</t>
         </is>
       </c>
     </row>
@@ -7736,12 +7810,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>199.96</t>
+          <t>200.02</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>▼ -0.25원 (-0.13%)</t>
+          <t>▼ -0.19원 (-0.10%)</t>
         </is>
       </c>
     </row>
@@ -7847,27 +7921,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,763,000원</t>
+          <t>112,687,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>112,199,000원</t>
+          <t>112,124,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,784,000원</t>
+          <t>121,702,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,584,000원</t>
+          <t>110,580,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7939,7 +8013,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>RSI 46.5로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 46.4로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -7961,17 +8035,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>144,700원</t>
+          <t>144,800원</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>143,500원</t>
+          <t>143,600원</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -7981,12 +8055,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>139,600원</t>
+          <t>139,700원</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>+8.6%</t>
+          <t>+8.5%</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -7996,7 +8070,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>RSI 46.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 47.0로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8253,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -8328,12 +8402,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>3Q 프리뷰 - 특별한 대안 없다면 길게 보세요</t>
+          <t>3Q 프리뷰 - DPS 증가 기대감 커지는 계기될 것</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -8348,37 +8422,37 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>매수 투자의견/TP 20,000원 유지, 매도하기보단 배당 감안한 중/장기 매수 추천 LGU+에 대한 투자의견 매수, 12개월 목표주가 20,000원을 유지한다. 추천 사유는 1) 2분기에 이어 3분기에도 우수한 실적을 기록할 것으로 전망됨에 따라 2026년 연간 높은 연결 영업이익 성장 가능성이 높아졌고, 2) 양호한 실적 전망을 바탕으로 2027년도엔 다시 주주환원 증대 기대감이 높아질 전망이며, 3) 조만간 정책 금리 상승이 마무리되고 시중 금리가 하락 전환하면서 연말 이후 4.8%에 달하는 기대배당수익률이 매력적으로 인식될 수 있을 것이기 때문이다. 당장 특별한 재료가 부각될 수 있는 상황은 아니지만 국내 주식 시장이 강한 상승 탄력을 나타나고 있지 않은 점을 감안하면 차라리 매도하기 보단 2027년 초까지 LGU+ 보유 또는 배당을 염두에 둔 신규 매수 진입을 추천한다.</t>
+          <t>더불어 국내 통신서비스 업종 12개월/10월 Top Pick으로 제시한다. 추천 사유는 1) 3분기 실적도 양호할 전망이라 2026년 연간 연결 영업이익이 2조원에 육박할 전망이고, 2) 2026년 우수한 실적을 바탕으로 DPS가 2024년 수준으로 회귀할 전망이며, 3) 엔트로픽 상장 가치가 당초 기대를 뛰어넘을 것으로 보여 밸류에이션상 저평가 논란이 생겨날 것이고, 4) 금리 인상 기조가 마무리되고 SKT 비과세 배당이 시작되는 2026년 말/2027년 초부터는 수급 개선이 예상되기 때문이다.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_LG유플러스_3Q 프리뷰 - 특별한 대안 없다면 길게 보세요.pdf</t>
+          <t>2026-10-14_하나증권_SK텔레콤_3Q 프리뷰 - DPS 증가 기대감 커지는 계기될 것.pdf</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>15,429.4십억원</t>
+          <t>17,658.0십억원</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>1,144.2십억원</t>
+          <t>1,950.1십억원</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>16,347.1십억원</t>
+          <t>18,217.8십억원</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1,185.5십억원</t>
+          <t>2,013.5십억원</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>연결 영업이익 3,221억원 전망, 4Q 인센티브 반영 고려해도 올해 실적 좋을 것</t>
+          <t>2026년 연간 연결 영업이익이 2조원에 육박할 전망이고, 2) 2026년 우수한 실적을 바탕으</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8463,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -8398,12 +8472,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>3Q 프리뷰 - DPS 증가 기대감 커지는 계기될 것</t>
+          <t>3Q 프리뷰 - 특별한 대안 없다면 길게 보세요</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -8418,37 +8492,37 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>더불어 국내 통신서비스 업종 12개월/10월 Top Pick으로 제시한다. 추천 사유는 1) 3분기 실적도 양호할 전망이라 2026년 연간 연결 영업이익이 2조원에 육박할 전망이고, 2) 2026년 우수한 실적을 바탕으로 DPS가 2024년 수준으로 회귀할 전망이며, 3) 엔트로픽 상장 가치가 당초 기대를 뛰어넘을 것으로 보여 밸류에이션상 저평가 논란이 생겨날 것이고, 4) 금리 인상 기조가 마무리되고 SKT 비과세 배당이 시작되는 2026년 말/2027년 초부터는 수급 개선이 예상되기 때문이다.</t>
+          <t>매수 투자의견/TP 20,000원 유지, 매도하기보단 배당 감안한 중/장기 매수 추천 LGU+에 대한 투자의견 매수, 12개월 목표주가 20,000원을 유지한다. 추천 사유는 1) 2분기에 이어 3분기에도 우수한 실적을 기록할 것으로 전망됨에 따라 2026년 연간 높은 연결 영업이익 성장 가능성이 높아졌고, 2) 양호한 실적 전망을 바탕으로 2027년도엔 다시 주주환원 증대 기대감이 높아질 전망이며, 3) 조만간 정책 금리 상승이 마무리되고 시중 금리가 하락 전환하면서 연말 이후 4.8%에 달하는 기대배당수익률이 매력적으로 인식될 수 있을 것이기 때문이다. 당장 특별한 재료가 부각될 수 있는 상황은 아니지만 국내 주식 시장이 강한 상승 탄력을 나타나고 있지 않은 점을 감안하면 차라리 매도하기 보단 2027년 초까지 LGU+ 보유 또는 배당을 염두에 둔 신규 매수 진입을 추천한다.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_SK텔레콤_3Q 프리뷰 - DPS 증가 기대감 커지는 계기될 것.pdf</t>
+          <t>2026-10-14_하나증권_LG유플러스_3Q 프리뷰 - 특별한 대안 없다면 길게 보세요.pdf</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>17,658.0십억원</t>
+          <t>15,429.4십억원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>1,950.1십억원</t>
+          <t>1,144.2십억원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>18,217.8십억원</t>
+          <t>16,347.1십억원</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>2,013.5십억원</t>
+          <t>1,185.5십억원</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026년 연간 연결 영업이익이 2조원에 육박할 전망이고, 2) 2026년 우수한 실적을 바탕으</t>
+          <t>연결 영업이익 3,221억원 전망, 4Q 인센티브 반영 고려해도 올해 실적 좋을 것</t>
         </is>
       </c>
     </row>
@@ -8813,16 +8887,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -8940,7 +9014,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -9002,7 +9076,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -9064,7 +9138,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -9126,7 +9200,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -9250,7 +9324,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -9287,22 +9361,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>236,500원</t>
+          <t>231,500원</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>234,000원</t>
+          <t>229,000원</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>257,000원</t>
+          <t>256,500원</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>228,000원</t>
+          <t>223,500원</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -9312,12 +9386,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>235,750원</t>
+          <t>232,750원</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -9339,32 +9413,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>엔비디아 (NVIDIA)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>128940.KS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>409,000원</t>
+          <t>$228.52 (약 305,908원)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>405,000원</t>
+          <t>$228.52 (약 305,908원)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>483,500원</t>
+          <t>$246.80 (약 330,380원)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>394,500원</t>
+          <t>$219.38</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -9374,12 +9448,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>408,000원</t>
+          <t>$228.52</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -9401,32 +9475,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>애플 (Apple)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>030200.KS</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>49,800원</t>
+          <t>$341.27 (약 456,841원)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>49,300원</t>
+          <t>$341.27 (약 456,841원)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>52,700원</t>
+          <t>$368.57 (약 493,388원)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>48,000원</t>
+          <t>$327.62</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -9436,12 +9510,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>49,800원</t>
+          <t>$341.27</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -9463,32 +9537,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>017670.KS</t>
+          <t>128940.KS</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>82,200원</t>
+          <t>400,000원</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>81,400원</t>
+          <t>396,000원</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>87,100원</t>
+          <t>483,000원</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>79,300원</t>
+          <t>386,000원</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -9498,12 +9572,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>82,200원</t>
+          <t>403,000원</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -9525,50 +9599,236 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>030200.KS</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>50,000원</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>49,500원</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>48,200원</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>50,200원</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>017670.KS</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>81,600원</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>80,800원</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>86,500원</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>78,700원</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>81,900원</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>010140.KS</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>18,700원</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>20,000원</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>18,200원</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>18,920원</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>삼성화재</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>000810.KS</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>584,000원</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>578,000원</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>583,000원</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>577,000원</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>629,500원</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>563,500원</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>562,500원</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>⏳ 목표가 추적 중 (신규 진입)</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>+1.0%</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>584,000원</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>582,000원</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
@@ -10334,32 +10594,32 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>🌐 [경제·사회 심층 리포트] GC녹십자의 숨겨진 배경과 구조적 쟁점</t>
+          <t>🌐 [경제·사회 심층 리포트] 카카오의 숨겨진 배경과 구조적 쟁점</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>GC녹십자</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: 'GC녹십자' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
+          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '카카오' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[GC녹십자, LG CNS와 스마트공장 구축…AI 자동화 추진]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; GC녹십자가 LG CNS와 인공지능 기반 자동화·자율 운영 스마트 공장 구축을 추진한다.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
+          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[카카오, ‘모두의 AI’ 연내 공개 예정…월 이용자 500만 명 목표]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 카카오, ‘모두의 AI’ 연내 공개 예정월 이용자 500만 명 목표 KBS 뉴스카카오그룹, 인적분할 앞두고 주요 계열사 CEO 함께 모여 ‘첫 공동 IR’ 개최 카카오연말 출시 ‘모두의 AI’“카톡 익숙함. 활용할 것” 마켓 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; GC녹십자, 헌터라제 알레르기 유발 항체 정밀 검출 기술 개발 뉴스저널리즘. 어려울 때 GC녹십자 2분기 살린 건, 끈끈한 '피의 힘' 히트뉴스.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
+          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; 피지컬 AI 시동 건 카카오모빌리티…상생재단서 '카카오' 뗀 이유는? 알림음과 배경 음악을 구분하는 카카오 라인 블록 체인 사운드 안내 Calgary Roughnecks.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; GC녹십자, 헌터라제 특이 IgE 항체 정밀 분석법 개발…국제학술지 게재 나눔경제뉴스. GC녹십자웰빙, 비만·체형관리까지…'에스테틱' 판 키운다.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
+          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 카카오 AI, 올해 사회경제적 가치 약 5500억 창출 전망 서울경제. 카카오 AI 사회경제적 가치 연 5506억원…2030년 최대 1.8조원 전망 지디넷코리아.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -10374,12 +10634,12 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014121800017</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE43NnU3MlhmZWZkcEdnRU1abkNDcHdIdG85YU9NZVBqVF90N3BXTHFCVlJIbDZQbkg3RGR5NWltZ29IaXNWNkdIWm1aYzBmLU4wbnVfd1hhVnlwdVk?oc=5</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10681,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 수영복 입은 문주님, 블루 아카이브에 '람과천청' 업데이트 월요신문. 알림음과 배경 음악을 구분하는 블루아카이브 경마 사운드 안내 Calgary Roughnecks.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
+          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 알림음과 배경 음악을 구분하는 블루아카이브 경마 사운드 안내 Calgary Roughnecks. 수영복 입은 문주님, 블루 아카이브에 '람과천청' 업데이트 월요신문.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3636,22 +3636,22 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>“신임 비서실장은 임광현”…떠나는 강훈식 마지막 브리핑 [지금뉴스]</t>
+          <t>與, 임광현 靑비서실장 발탁에 "국정성과에 속도 낼 적임자"</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>“신임 비서실장은 임광현”떠나는 강훈식 마지막 브리핑 KBS 뉴스 신임 대통령 비서실장에 임광현 국세청장 JTBC이 대통령, ‘강훈식 후임’ 새 비서실장에 임광현 국세청장 임명 한겨레안철수 "임광현 비서실장, 보은 인사 결정판처남 대장동 변호사" 뉴스1李 '먹사니즘' 세제 공약 설계한 임광현黨영입인재서 靑비서실장까지 아시아경제.</t>
+          <t>더불어민주당은 14일 임광현 국세청장이 이재명 정부 청와대 2기 비서실장으로 발탁에 대해 "국민이 피부로 느끼.</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBOT2xfekhrRnVZc3FfaENuU0xNRUJEczB5Z2RWVjRCLUtheS1VZ2UyUk9GT3J4aHNuclBVS0o5T3FPMFRRYWhwMTYxQWNiUDVQYkd4Ni1XbTdfem8?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014144800001</t>
         </is>
       </c>
     </row>
@@ -3663,22 +3663,22 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>인천 흉기난동범 "관심 끌려 범행…힘없어 보이는 사람 골랐다"</t>
+          <t>정부, 후티 반군의 사우디 민간시설 공격 규탄…"중단 촉구"</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>인천 대형 상업시설에서 흉기를 휘둘러 8명을 다치게 한 50대 남성이 자신의 불만을 사회적으로 알리고 싶어 범.</t>
+          <t>정부는 최근 후티 반군이 사우디아라비아 수도 리야드에 위치한 국제공항 등 민간 시설을 공격해 다수의 민간인 사.</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014134000065</t>
+          <t>https://www.yna.co.kr/view/AKR20261014148100504</t>
         </is>
       </c>
     </row>
@@ -3700,22 +3700,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>'1심 무죄' 前경호처장 2심 징역 1년…尹비화폰 증거인멸 유죄(종합)</t>
+          <t>해군2함대-중부해경청, 서해 안보협력 강화를 위한 MOU 체결</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>12·3 비상계엄 사태 이후 윤석열 전 대통령 등의 비화폰 정보를 삭제한 혐의로 기소된 박종준 전 대통령 경호.</t>
+          <t>해군 제2함대사령부는 14일 중부지방해양경찰청과 서해 안보협력 강화를 위한 양해각서 를 체결했다.</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014123851004</t>
+          <t>https://www.yna.co.kr/view/AKR20261014148400061</t>
         </is>
       </c>
     </row>
@@ -3737,22 +3737,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>제주 평화로에서 다중 추돌 교통사고…12대 추정</t>
+          <t>李대통령, 임광현에 "훈식이 형 만큼, 그 이상 해내실 것 기대"</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>14일 오후 3시께 제주시 애월읍 평화로에서 차량 12대 가 잇따라 추돌했다.</t>
+          <t>이재명 대통령은 14일 신임 대통령 비서실장으로 임광현 국세청장을 발탁한 뒤 엑스 에 "임 실장.</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014135000056</t>
+          <t>https://www.yna.co.kr/view/AKR20261014146400001</t>
         </is>
       </c>
     </row>
@@ -3774,32 +3774,32 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>카카오, ‘모두의 AI’ 연내 공개 예정…월 이용자 500만 명 목표</t>
+          <t>李대통령, '경제형 비서실장' 전격 발탁…실용주의로 2년차 돌파</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>카카오, ‘모두의 AI’ 연내 공개 예정월 이용자 500만 명 목표 KBS 뉴스카카오그룹, 인적분할 앞두고 주요 계열사 CEO 함께 모여 ‘첫 공동 IR’ 개최 카카오연말 출시 ‘모두의 AI’“카톡 익숙함. 활용할 것” 마켓 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척.</t>
+          <t>이재명 대통령이 2년 차에 접어든 국정을 보좌할 비서실장으로 14일 경제 관료 출신인 임광현 국세청장을 전격.</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE43NnU3MlhmZWZkcEdnRU1abkNDcHdIdG85YU9NZVBqVF90N3BXTHFCVlJIbDZQbkg3RGR5NWltZ29IaXNWNkdIWm1aYzBmLU4wbnVfd1hhVnlwdVk?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014138500001</t>
         </is>
       </c>
     </row>
@@ -3811,32 +3811,32 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>대구 신세계 프리미엄 아울렛 건립 속도…인허가기간 절반 이하로</t>
+          <t>'尹 비화폰 삭제' 박종준 전 경호처장 2심 징역형‥1심 무죄 뒤집혀</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>대구시가 신세계사이먼의 '대구 프리미엄 아울렛' 건립을 위한 인허가 기간을 통상의 절반 이하로 줄이는 등 사업.</t>
+          <t>'尹 비화폰 삭제' 박종준 전 경호처장 2심 징역형‥1심 무죄 뒤집혀.</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014129100053</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4yS19JendCbGpWdW11Mll3YnExWWJ4clJpa0lHbXJrUmVPZ2xveC0xN2xCWlJPLVd3anh2dXRla3BRWHFYUmVOLVlVLWhjSjR4ZTFXY0FnXzF4SWIwU1BwOGpFTjBuY3FCMk1OTkVTNmtRcWlueXZv0gF3QVVfeXFMTXZqdlJQeHl1N0hQNFBUZnExVGxSMnY0V1VzYkRpelRUVVR1NXczZlpKcU11QkgzV0NGaUxVMGxVNVpybjJYNjhNYWROVHJLYTVfa0s4ZEZkQkFjRWpGMUtNbm9kbXZIbzFGcjRVU1dCbDBaeU1DMzg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3848,22 +3848,22 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>토스뱅크, 디지털 취약계층에 노트북 기부</t>
+          <t>대전중리초 체육관 전면보수 특별교부금 확보…교육 인프라 개선</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>토스뱅크가 고령층 문해학습자와 장애인 등 디지털 교육이 필요한 학습자를 지원하기 위해 업무용으로 사용하던 노트북 46대를 기부한다고 14일 밝혔다.</t>
+          <t>더불어민주당 박정현 국회의원 은 대전중리초등학교 체육관 전면 보수 사업을 위한 2026년 교육부.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175659</t>
+          <t>https://www.yna.co.kr/view/AKR20261014154100063</t>
         </is>
       </c>
     </row>
@@ -3885,22 +3885,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>올해만 10대 선진국 10년물 국채금리 0.81%p 급등</t>
+          <t>창원서 제조 AI·스마트공장 통합 'The Next AI×SMATOF' 개막</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>국제 신용평가사 피치는 국채 금리 상승으로 프랑스, 미국, 영국 등 주요 선진국이 채무 부담을 안정적으로 유지.</t>
+          <t>경남도는 14일부터 16일까지 창원컨벤션센터 에서 제조 인공지능 전시회인 'The Next A.</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014133700009</t>
+          <t>https://www.yna.co.kr/view/AKR20261014151200052</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3932,22 +3932,22 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>“칼로리에 깜짝” 악뮤 수현도 놀란 ‘최근 유행 디저트’ 정체</t>
+          <t>직원 노동분쟁에 '교비' 쓴 한신대 총장, 횡령 혐의 송치</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>“칼로리에 깜짝” 악뮤 수현도 놀란 ‘최근 유행 디저트’ 정체 헬스조선‘30㎏ 감량 이수현’ 콘서트 끝나고 ‘한정선’ 먹자트레이너 “10㎞ 뛰어야” '-30kg' 악뮤 이수현, 콘서트 직후 디저트 흡입트레이너에 "말 걸지 마라" 미주30kg 감량한 이수현, ‘이 음식’ 먹자트레이너 “10km 달려야” 서울신문"3시간 줄 선다고?" 갸우뚱이수현, '한정선' 솔직 후기 -.</t>
+          <t>한신대학교 강성영 총장이 직원들의 부당해고 등 노동 분쟁에 대응하기 위한 노무사 비용을 교비회계에서 지출한 혐.</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>헬스조선</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBldDBTc0RkSFJEOVQ5Y2o5bmJIY3gwaGQxZzZvVzZpRHdsX0RCZ3l3NS1oTm5iR0VERmYybWx4NGhSaGRMSFhXdnpPN1l0Y2JpalJ4WGZ0N3V5RHVKX2NUeF92NzVwOV9tenl5WDVyTXpjd281cHVuZmlGUkwzekU?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014153100061</t>
         </is>
       </c>
     </row>
@@ -3959,32 +3959,1253 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>전남교육음악제·초등교원미술작품전 16일 개최</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>전남광주통합특별시교육청은 가을을 맞아 교육 가족이 함께하는 문화예술행사를 개최한다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014152400054</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>[동포의 창] 지구촌동포연대 "사할린 한인에게 음력 달력 선물"</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>지구촌동포연대 는 러시아 사할린에 거주하는 한인들을 위해 '세상에 하나뿐인 달력 2027'을 제작한다고.</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014153500371</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>"횟수보다 방법"…26년 차 치과의사가 전하는 '백년양치질'</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>"더 열심히 닦을수록 잇몸은 망가집니다. 핵심은 횟수가 아니라 방법입니다.".</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014152100055</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>제주 평화로에서 차량 12대 추돌 사고…16명 중경상(종합)</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>제주 평화로에서 다중 추돌 교통사고가 발생해 16명이 중경상을 입었다.</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014135051056</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>산림청, 국토부와 소나무재선충 피해목 신속 제거 협의</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>산림청은 14일 정부세종청사에서 국토교통부와 공동으로 생활권 주변 소나무재선충병 피해목의 신속한 제거를 위한.</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014149600063</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>김성주 "리밸런싱 유예 안했다면 매일 8천억 매도…증시 충격"</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>김성주 국민연금공단 이사장이 올해 초 국내주식 비율 초과에 따른 자산 비중 재조정 작업 을 유예하지.</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014151100530</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>지식재산처, 기술경찰 수사범위 확대한다…제도 개선 추진</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>지식재산처는 기술경찰의 수사 범위를 영업비밀 침해를 넘어 국가핵심기술·국가첨단전략기술 유출 범죄까지 확대하는.</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014151800063</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>국공노 "2차 행정기관 이전 대상 공무원 주거·정주대책 필요"</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>정부가 추진하는 2차 중앙행정기관 이전과 관련해 국가공무원노조 가 이전 공무원에 대한 실질적인 주거·정.</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014148900063</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>태백 문곡소도동에 '얼굴 없는 천사'…쌀 280㎏ 기부</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>강원 태백시 문곡소도동에 익명의 주민이 어려운 이웃을 위해 쌀 280㎏을 기부해 훈훈함을 전하고 있다.</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014150000062</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>시흥 오이도 해상서 10대 2명 물에 빠져…해경 구조</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>14일 오후 3시 5분께 경기 시흥시 오이도 빨간등대 인근 해상에서 10대 2명이 물에 빠졌다는 신고가 해경에.</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014150200065</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>교육부, 12월부터 두달간 유아 레벨테스트 금지 집중점검</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>교육부는 유아를 대상으로 한 '레벨테스트' 금지 제도가 현장에 안착하도록 점검을 강화하겠다고 14일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014149800530</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>사회/사건사고</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>경기도 버스 노사 교섭 최종 결렬…지노위 조정신청 접수</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>경기도 버스 노사의 임금 및 단체협약 교섭이 최종 결렬되면서 노조가 지방노동위원회에 노동쟁의 조정을 신청하고.</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014149500061</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>삼성전자 '반도체대전' 참가‥HBM4E 등 AI 반도체 기술 선보인다</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>삼성전자 '반도체대전' 참가‥HBM4E 등 AI 반도체 기술 선보인다.</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>MBC 뉴스</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9QLWl1VjBqYUpRc3BydE96Y1c1N2JQNUJ4TTdmazF6NmRlb01JaHpYa3NSX2llQkRyUFU3S1JYOUxVbkp3N3VMOUlITWFoUEk2YlpkTDdmUzE3MUJwbG9LclBOQzNYNzkzZnJLcDdveDZKMkFG0gF0QVVfeXFMUG52cWpIVDZJZFNKelIwTmczTFJmVUtRTjVBYlI0ZEJtNkJYWWVYaWVRR1plUFR0M3pQUVZUdmF6RDJRNm5qWjlHNUFzNlZ0d2N6TV8tNm1RUldCMVh3b3l4eWhkdlBUOGMtSVZwMm5YUTlGUzg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>‘이자만 2700만원’ 이 대통령 아파트 거래…증여세 대상 아닌 이유는?</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>‘이자만 2700만원’ 이 대통령 아파트 거래증여세 대상 아닌 이유는?</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>한겨레</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFA1Nmc0MHpKSV9zMzg1WFBKR3dVRW45aW5lcXVFb3M1V3cydTZ4eXN5Y0ppOWcwc1VGUks1YWdoWEw5TUsxYnp2WWxhQlBrbllRcjgzSURycEpQNkJwWFZhdnNKWTYtQXl2LUpjUS1hQ1lOdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>코스피, 반등 실패…6거래일 연속 내리며 '6천피' 턱걸이(종합)</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>코스피가 14일 전날 급락을 딛고 상승 출발했지만, 장 후반 들어 하락 전환하며 6거래일 연속 하락세를 이어갔.</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014138351008</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>[동정] 농식품부 장관, 수확기 맞아 사과 재배 농가 방문</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>▲ 송미령 농림축산식품부 장관은 14일 가을 수확기를 맞아 경남 함양군의 사과 재배 농가를 방문하고, 올해부터 운영 중인 '사과 안정생산 추진단.</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014059400030</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>거시경제/비즈니스</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>LS증권, 수요예측서 4천640억 몰려…모집예정액 7배 수준</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>LS증권 의 무보증사채 수요예측에서 모집예정액의 7배 가까운 자금이 몰렸다.</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261013159900008</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>佛 마트 냉장고들 해킹당했다... 온도 50도 폭주 ‘먹거리 테러’</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>佛 마트 냉장고들 해킹당했다 온도 50도 폭주 ‘먹거리 테러’. 아울러 에펠탑 옆 '슈퍼마켓 냉동고'가 텅 비었다'냉장고 해킹' 덮친 佛파리 가보니.</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNX3hlMG9oaUR4eWpCTGRxV3d5LWpsVU4wa082NWk0MXZLZWx4aWY3UHo5SUVvc1Jkb0pNdWZtTVMyMkQtbnZUN21Sc05KdjlaMndnS0s4aWZvRmszSTNic3BkbF9HY0Zlb3dwQkF4bVl3bFVOYXJ4M0JLSThaWXpOVV9vaG92M1FlR25KZDFMN3d0eWpZQXRJcElaVXdUdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>이란 매체 "미군 드론, 어선 공격해 3명 부상"</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>김상훈 특파원 = 이란 남부 호르모즈간주 시리크 인근 해상에서 미군의 무인기 공격으로 3명이 부상했다고 반관영.</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014153200079</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>서울 세계청년대회 성공 기원 음악회…조수미도 무대에</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>민경락 특파원 = 내년 서울에서 열리는 세계청년대회 의 성공 개최를 기원하는 음악회가 이탈리아 로마에서 열렸다고 주교.</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014149900109</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>중간선거 앞두고 거칠어진 트럼프의 입…종교·인종 차별까지</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>달 치러지는 미국 중간선거에서 공화당이 고전할 것이란 전망이 짙어지면서 도널드 트럼프 대통령의 언사가 점.</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014147100009</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>[쇼츠] 차단봉에 머리 '쿵' 쓰러졌는데…오히려 혼난 남성</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>12일 인도 타밀나두주 쿠달로르 지역의 한 도로 요금소에서 한 남성이 차단봉에 맞아 쓰러지는 사고가 발생했습니다.</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014148200704</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>세계/국제</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>"미국에 할말 하겠다"는 일본. ICC 제재 진의 파악 공들여</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>일본 정부가 미국의 국제형사재판소 제재 발표와 관련해 ICC에 대한 지지를 강조하면서도 도널드 트럼프.</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014145800009</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>엔비디아 RTX 스파크 16일 출격…24GB로 돌리는 740억 파라미터 에이전트 모델 공개</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>엔비디아 RTX 스파크 16일 출격24GB로 돌리는 740억 파라미터 에이전트 모델 공개. 아울러 DLSS 5, 다음은 '연운'이다 적용 예고 및 성능 개선 진행.</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>ER 이코노믹리뷰</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5jZnVIcU1McmlHa3Itbm4wYVJPSHlFR2llaFRwUHdBd181c3ZQWjA3czhndkpfQnh1S19rQXpINk1HSTg4ZzhEVHNRTDBlSVJ3M2RoS0Z5MXIzSFpqVFZNT3VfWkNpY1RKY2E4MQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>‘메트로 2039’ 예약판매 시작, 스토리 확장 DLC·에디션 구성 공개</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>‘메트로 2039’ 예약판매 시작, 스토리 확장 DLC·에디션 구성 공개.</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>인벤</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE50Ym5RWDNGNjltd0NLMmJTbG5fUldPNW13SHprT1YzYllzSDNnR05DUS0zMVp5dWE0WElMUTlfZWlCdGdpcmRNbktpTTVqMEptUjVkVWo0YTQyRUU0T2c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>무게 줄이고 가격 낮췄다…렉트릭, 가성비 도심형 전기자전거 출시</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>무게 줄이고 가격 낮췄다렉트릭, 가성비 도심형 전기자전거 출시.</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>디지털투데이</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5TNk9veHRBWmtQZVdPS2NPUEQwVFVKeTRLLWFnc2pYX3hTNHVpbWFqdzJmTmVrdkYtaW05d0VjenRmNTdHLTNJakJyR3QyZHdtRmlnazItR0tLR0lXREFhYVJweXVyU1ZpNlZqeXd3OGM2Ums?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>한전, 고졸 입사직원 2명 차장 특별승진…"능력·성과 중심"</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>한국전력은 고졸 전형 입사 직원을 포함해 탁월한 업무성과를 거둔 직원 12명을 특별승진 대상자로 선정했다고 1.</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014146200003</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>엘리시안강촌, '숲속빵시장' 우천 예보에 25일로 연기</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>강원 춘천 엘리시안강촌에서 열릴 예정이던 '제5회 숲속빵시장'이 우천 예보로 일주일 연기됐다.</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014152300062</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>미국·영국 등 13개국 서울 집결…양자기술 협력 논의</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>과학기술정보통신부는 14~16일 서울에서 '제9차 양자기술다자대화'와 '양자기술 산업화 비즈니스 나이트'를 개.</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014147900017</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>'경기 스타트업 서밋' 개막…혁신 스타트업-벤처 투자사 매칭</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>경기도가 주최하고 경기도경제과학진흥원이 주관하는 '2026 경기 스타트업 서밋'이 14일 수원컨벤션센터에서 개.</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014147000061</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>연예/대중문화</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>“낙찰가 2400억, 역대 최고가 기대”…반 고흐 '꽃 핀 밤나무' 60년 만에 공개</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>“낙찰가 2400억, 역대 최고가 기대”반 고흐 '꽃 핀 밤나무' 60년 만에 공개 전자신문낙찰 예상가만 2400억60여 년 만에 공개 반고흐의 ‘꽃 핀 밤나무’ KBS 뉴스고흐 말년작 60년만에 공개내달 경매 2400억원 예상 동아일보홍콩서 60여년 만에 반고흐 '꽃 핀 밤나무' 공개수백명 몰려 60년만에 세상 나온 반고흐 명작'경매가 2400억' 신기록 전망 뉴스1.</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>전자신문</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE80XzRkdG90QUU3QUtFbVJUcEJmNVhja2ZjYnRoY09GRUI3WjJfZzZFY1NkbVlwXzJTYWVUUVpfcG5oTVFENHVXbTFJQTRaZw?oc=5</t>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>김종국, 대만서 ’런닝맨’ 파워 실감..길거리 사진 요청까지 “부러워”(상남자의 여행법)</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>김종국, 대만서 ’런닝맨’ 파워 실감길거리 사진 요청까지 “부러워”. 아울러 먹뱉 위기22! 들쥐 비주얼에 단체 멘붕 초대형 닭X알 걸린 추성훈ㅋㅋㅋㅋ | #상남자의여행법 EP.02.</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNTmlJNUxKQTNNV2FMZEZJdU90VmxGYXNVLWdpVTk3VHNrTHdNN0wySjhBWklYU0FfYVN3Q1RCLTdYclFKSHRfWVZndjhFeHJRUERwWlJ4b3d5bmtYdmYyR1NROXV1eURESkVyTkl4OHQtaFcwUVNQMGljYjVFSFFobTFhc2ZqZzlvTHNvSGU0QQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>[경주소식] KBS 대하드라마 '문무' 성공기원 행사</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>경북 경주시는 14일 감포읍 문무대왕 해양역사관 앞 광장에서 KBS 대하드라마 '문무'의 성공 기원 행사를 열었다.</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014153300053</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>[방송소식] 웨이브, '더 커뮤니티2' 비하인드 토크 16일 공개</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>▲ '더 커뮤니티2' 비하인드 토크, 최후 9인 출연 = 웨이브는 오리지널 예능 '더 커뮤니티2: 보이지 않는.</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014144600005</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>[가요소식] BTS '훌리건' 뮤직비디오 1억뷰</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>▲ BTS '훌리건' 뮤직비디오 1억뷰 = 그룹 방탄소년단 의 '훌리건' 뮤직비디오가.</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261014146900005</t>
         </is>
       </c>
     </row>
@@ -3999,7 +5220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5326,42 +6547,42 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>232,500원</t>
+          <t>232,000원</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+26,000.0원 (+12.59%)</t>
+          <t>+25,500원 (+12.35%)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>230,000원</t>
+          <t>220,500원</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>257,000원</t>
+          <t>229,500원</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>224,500원</t>
+          <t>225,000원</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
+          <t>🔴 단기 비중 축소 (악재 주의)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>RSI 34.7로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.82x)</t>
+          <t>악재 보도 및 5일 연속 약세(-4% 이상)로 단기 추가 하락 위험</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -5375,26 +6596,26 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>34.7</v>
+        <v>34.4</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>[하나증권] 삼성화재: 3Q26 Pre - 단기 실적보다 중요한 것은 (하나증권)</t>
+          <t>삼성전자 '반도체대전' 참가‥HBM4E 등 AI 반도체 기술 선보인다 (MBC 뉴스)</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 232500.0]</t>
+          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 232000.0]</t>
         </is>
       </c>
     </row>
@@ -5426,7 +6647,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+316,000.0원 (+28.65%)</t>
+          <t>+316,000원 (+28.65%)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -5484,7 +6705,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>(마감시황) 코스피, 6,000선 턱걸이…삼전 보합·SK하이닉스 1.66%↓ (뉴스투데이)</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -5516,27 +6737,27 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>314,000원</t>
+          <t>313,500원</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>-177,500.0원 (-36.11%)</t>
+          <t>-178,000원 (-36.22%)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>298,500원</t>
+          <t>298,000원</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>311,000원</t>
+          <t>310,500원</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>304,500원</t>
+          <t>304,000원</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -5551,7 +6772,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(349,325원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(349,300원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -5565,16 +6786,16 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
@@ -5584,7 +6805,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 314000.0]</t>
+          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 313500.0]</t>
         </is>
       </c>
     </row>
@@ -5616,7 +6837,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>-40,800.0원 (-27.35%)</t>
+          <t>-40,600원 (-27.21%)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -5631,12 +6852,12 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>105,000원</t>
+          <t>105,500원</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+5.8%</t>
+          <t>+6.0%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -5646,7 +6867,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(115,820원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(115,830원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -5660,16 +6881,16 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -5679,7 +6900,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 108400.0]</t>
+          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 108600.0]</t>
         </is>
       </c>
     </row>
@@ -5706,12 +6927,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>180,000원</t>
+          <t>179,500원</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>-21,700.0원 (-10.77%)</t>
+          <t>-22,100원 (-10.97%)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -5721,17 +6942,17 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>178,000원</t>
+          <t>177,500원</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>174,500원</t>
+          <t>174,000원</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -5741,7 +6962,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(194,005원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(193,985원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -5755,16 +6976,16 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>29.8</v>
+        <v>29.1</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -5774,7 +6995,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 179800.0]</t>
+          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 179400.0]</t>
         </is>
       </c>
     </row>
@@ -5806,7 +7027,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-16,400.0원 (-34.10%)</t>
+          <t>-16,400원 (-34.10%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -5864,7 +7085,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>카카오, ‘모두의 AI’ 연내 공개 예정…월 이용자 500만 명 목표 (KBS 뉴스)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -5901,12 +7122,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>-9,719.049999999988원 (-5.13%)</t>
+          <t>-9,819원 (-5.18%)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>176,500원</t>
+          <t>176,000원</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5945,16 +7166,16 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -5964,7 +7185,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 179900.0]</t>
+          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 179800.0]</t>
         </is>
       </c>
     </row>
@@ -5991,12 +7212,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>839,000원</t>
+          <t>842,000원</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-684,000.0원 (-44.91%)</t>
+          <t>-681,000원 (-44.71%)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -6006,17 +7227,17 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>830,500원</t>
+          <t>833,500원</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>814,000원</t>
+          <t>816,500원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -6026,7 +7247,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(1,012,050원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(1,012,200원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -6040,16 +7261,16 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>29.6</v>
+        <v>30.1</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -6059,7 +7280,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>[1081000.0, 1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 839000.0]</t>
+          <t>[1081000.0, 1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 842000.0]</t>
         </is>
       </c>
     </row>
@@ -6086,12 +7307,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>420,500원</t>
+          <t>422,000원</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>+20,500.0원 (+5.12%)</t>
+          <t>+22,000원 (+5.50%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -6101,17 +7322,17 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>420,500원</t>
+          <t>422,000원</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>412,000원</t>
+          <t>413,500원</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>+13.0%</t>
+          <t>+13.4%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -6121,7 +7342,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>RSI 70.6, 20일선 이격도 +13.0%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
+          <t>RSI 71.0, 20일선 이격도 +13.4%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -6135,16 +7356,16 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>+13.0%</t>
+          <t>+13.4%</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
@@ -6154,7 +7375,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 420500.0]</t>
+          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 422000.0]</t>
         </is>
       </c>
     </row>
@@ -6181,17 +7402,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>307,500원</t>
+          <t>309,000원</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>-54,000.0원 (-14.94%)</t>
+          <t>-52,500원 (-14.52%)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>301,500원</t>
+          <t>303,000원</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -6201,12 +7422,12 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>292,000원</t>
+          <t>293,500원</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>+10.8%</t>
+          <t>+10.3%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -6230,16 +7451,16 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>44.2</v>
+        <v>45.3</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
@@ -6249,7 +7470,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>[334000.0, 326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 307500.0]</t>
+          <t>[334000.0, 326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 309000.0]</t>
         </is>
       </c>
     </row>
@@ -6276,22 +7497,22 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>$228.52 (약 305,782원)</t>
+          <t>$228.52 (약 305,131원)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>+39.21000000000001$ (+20.71%)</t>
+          <t>+39.21$ (+20.71%)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>$223.95 (약 299,666원)</t>
+          <t>$223.95 (약 299,028원)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>$239.95 (약 321,071원)</t>
+          <t>$239.95 (약 320,387원)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -6339,7 +7560,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>엔비디아 RTX 스파크 16일 출격…24GB로 돌리는 740억 파라미터 에이전트 모델 공개 (ER 이코노믹리뷰)</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -6371,7 +7592,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>$341.27 (약 456,653원)</t>
+          <t>$341.27 (약 455,680원)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6381,12 +7602,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>$334.44 (약 447,520원)</t>
+          <t>$334.44 (약 446,567원)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>$358.33 (약 479,486원)</t>
+          <t>$358.33 (약 478,464원)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -6466,22 +7687,22 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>$375.23 (약 502,095원)</t>
+          <t>$375.23 (약 501,025원)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>+22.810000000000002$ (+6.47%)</t>
+          <t>+22.81$ (+6.47%)</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>$367.73 (약 492,053원)</t>
+          <t>$367.73 (약 491,005원)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>$393.99 (약 527,200원)</t>
+          <t>$393.99 (약 526,077원)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -6561,22 +7782,22 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>$543.45 (약 727,190원)</t>
+          <t>$543.45 (약 725,641원)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>+159.08000000000004$ (+41.39%)</t>
+          <t>+159.08$ (+41.39%)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>$514.20 (약 688,051원)</t>
+          <t>$514.20 (약 686,585원)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>$543.45 (약 727,190원)</t>
+          <t>$543.45 (약 725,641원)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -6656,17 +7877,17 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>403,500원</t>
+          <t>404,500원</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>-97,500.0원 (-19.46%)</t>
+          <t>-96,500원 (-19.26%)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>399,500원</t>
+          <t>400,500원</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -6676,12 +7897,12 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>389,500원</t>
+          <t>390,500원</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>+21.0%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -6691,7 +7912,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>RSI 33.0로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.99x)</t>
+          <t>RSI 33.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 2.11x)</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -6705,16 +7926,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
@@ -6724,7 +7945,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 403500.0]</t>
+          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 404500.0]</t>
         </is>
       </c>
     </row>
@@ -6751,27 +7972,27 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>50,200원</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>-14,000.0원 (-21.81%)</t>
+          <t>-14,300원 (-22.27%)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>49,700원</t>
+          <t>49,400원</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>53,200원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>48,400원</t>
+          <t>48,200원</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -6786,7 +8007,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>RSI 35.8로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.81x)</t>
+          <t>RSI 33.1로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.99x)</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -6800,16 +8021,16 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>35.8</v>
+        <v>33.1</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -6819,7 +8040,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>[52700.0, 53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 50200.0]</t>
+          <t>[52700.0, 53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 49900.0]</t>
         </is>
       </c>
     </row>
@@ -6851,7 +8072,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>-13,600.0원 (-14.24%)</t>
+          <t>-13,600원 (-14.24%)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -6881,7 +8102,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>RSI 37.3로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 0.96x)</t>
+          <t>RSI 37.3로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.17x)</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -6941,22 +8162,22 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>14,800원</t>
+          <t>14,700원</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>-2,700.0원 (-15.46%)</t>
+          <t>-2,770원 (-15.86%)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>14,500원</t>
+          <t>14,400원</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>15,500원</t>
+          <t>15,400원</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -6990,16 +8211,16 @@
         </is>
       </c>
       <c r="O32" s="3" t="n">
-        <v>52.5</v>
+        <v>50.7</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -7009,7 +8230,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>[14890.0, 15040.0, 14850.0, 14650.0, 14680.0, 14050.0, 14490.0, 14570.0, 14640.0, 14770.0, 14800.0, 14530.0, 14540.0, 14550.0, 14560.0, 14500.0, 14400.0, 14550.0, 14780.0, 14770.0]</t>
+          <t>[14890.0, 15040.0, 14850.0, 14650.0, 14680.0, 14050.0, 14490.0, 14570.0, 14640.0, 14770.0, 14800.0, 14530.0, 14540.0, 14550.0, 14560.0, 14500.0, 14400.0, 14550.0, 14780.0, 14700.0]</t>
         </is>
       </c>
     </row>
@@ -7021,12 +8242,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>103590.KS</t>
+          <t>000810.KS</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7036,42 +8257,42 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>75,000원</t>
+          <t>582,000원</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>-9,300.0원 (-11.03%)</t>
+          <t>+92,500원 (+18.90%)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>73,500원</t>
+          <t>553,000원</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>88,000원</t>
+          <t>576,000원</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>71,200원</t>
+          <t>564,500원</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>주가가 20일선(642,100원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -7085,16 +8306,16 @@
         </is>
       </c>
       <c r="O33" s="3" t="n">
-        <v>48</v>
+        <v>33.7</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -7104,7 +8325,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 75000.0]</t>
+          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 582000.0]</t>
         </is>
       </c>
     </row>
@@ -7116,12 +8337,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>휴젤</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>010140.KS</t>
+          <t>145020.KS</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7131,42 +8352,42 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>223,500원</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>-8,960.0원 (-32.11%)</t>
+          <t>-29,500원 (-11.66%)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>18,800원</t>
+          <t>200,000원</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>20,100원</t>
+          <t>223,500원</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>18,300원</t>
+          <t>219,000원</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+11.7%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
+          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>RSI 40.9로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.46x)</t>
+          <t>RSI 19.6, 20일선 이격도 +11.7%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -7180,16 +8401,16 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>40.9</v>
+        <v>19.6</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>+11.7%</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -7199,7 +8420,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>[21400.0, 22100.0, 20700.0, 20200.0, 21500.0, 20800.0, 20600.0, 20600.0, 20250.0, 20100.0, 19330.0, 19700.0, 19720.0, 19960.0, 19700.0, 19540.0, 18860.0, 18010.0, 18360.0, 18940.0]</t>
+          <t>[236000.0, 231000.0, 232000.0, 235500.0, 231000.0, 231500.0, 214000.0, 206000.0, 190400.0, 187000.0, 186100.0, 183300.0, 179700.0, 180600.0, 180100.0, 181500.0, 183600.0, 182800.0, 180000.0, 169900.0]</t>
         </is>
       </c>
     </row>
@@ -7211,12 +8432,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>일진전기</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>000810.KS</t>
+          <t>103590.KS</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -7226,42 +8447,42 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>582,000원</t>
+          <t>74,900원</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>+92,500.0원 (+18.90%)</t>
+          <t>-9,400원 (-11.15%)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>553,000원</t>
+          <t>73,400원</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>576,000원</t>
+          <t>88,000원</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>564,500원</t>
+          <t>71,200원</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+19.9%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(642,100원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -7275,16 +8496,16 @@
         </is>
       </c>
       <c r="O35" s="3" t="n">
-        <v>33.7</v>
+        <v>47.8</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
@@ -7294,7 +8515,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 582000.0]</t>
+          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 74900.0]</t>
         </is>
       </c>
     </row>
@@ -7306,12 +8527,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>145020.KS</t>
+          <t>298040.KS</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -7321,42 +8542,42 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>223,500원</t>
+          <t>2,135,000원</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>-29,500.0원 (-11.66%)</t>
+          <t>-907,000원 (-29.82%)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>200,000원</t>
+          <t>2,028,000원</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>223,500원</t>
+          <t>2,113,500원</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>219,000원</t>
+          <t>2,071,000원</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>RSI 19.6, 20일선 이격도 +11.7%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
+          <t>주가가 20일선(2,701,200원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -7370,16 +8591,16 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>19.6</v>
+        <v>26.2</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
@@ -7389,7 +8610,102 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>[236000.0, 231000.0, 232000.0, 235500.0, 231000.0, 231500.0, 214000.0, 206000.0, 190400.0, 187000.0, 186100.0, 183300.0, 179700.0, 180600.0, 180100.0, 181500.0, 183600.0, 182800.0, 180000.0, 169900.0]</t>
+          <t>[2854000.0, 2803000.0, 2689000.0, 2806000.0, 2861000.0, 2915000.0, 2917000.0, 2901000.0, 2896000.0, 2780000.0, 2804000.0, 2773000.0, 2822000.0, 2785000.0, 2807000.0, 2588000.0, 2494000.0, 2242000.0, 2152000.0, 2135000.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>010140.KS</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>증권사 공식리서치</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>19,000원</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>-8,950원 (-32.08%)</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>20,100원</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>18,300원</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>🟢 오늘 단기 매수 (저점 과매도 반등)</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>RSI 41.0로 단기 과매도 구간 도달 및 지지선 부근 기술적 반등 기대 (거래량비율 1.7x)</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>보유 / 중립 (HOLD)</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>장기 추세 유지</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>-5.3%</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>9.6%</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>최근 특이 뉴스 없음</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>[21400.0, 22100.0, 20700.0, 20200.0, 21500.0, 20800.0, 20600.0, 20600.0, 20250.0, 20100.0, 19330.0, 19700.0, 19720.0, 19960.0, 19700.0, 19540.0, 18860.0, 18010.0, 18360.0, 18950.0]</t>
         </is>
       </c>
     </row>
@@ -7621,12 +8937,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5,997.24</t>
+          <t>6,008.81</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>▼ -38.11 (-0.63%)</t>
+          <t>▼ -26.54 (-0.44%)</t>
         </is>
       </c>
     </row>
@@ -7648,12 +8964,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>820.32</t>
+          <t>823.88</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>▼ -28.87 (-3.40%)</t>
+          <t>▼ -13.15 (-1.57%)</t>
         </is>
       </c>
     </row>
@@ -7729,12 +9045,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1,338.10</t>
+          <t>1,335.25</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>▼ -2.03원 (-0.15%)</t>
+          <t>▼ -4.88원 (-0.36%)</t>
         </is>
       </c>
     </row>
@@ -7756,12 +9072,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>843.10</t>
+          <t>841.40</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>▼ -1.00원 (-0.12%)</t>
+          <t>▼ -2.70원 (-0.32%)</t>
         </is>
       </c>
     </row>
@@ -7783,12 +9099,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1,498.90</t>
+          <t>1,495.50</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>▼ -1.00원 (-0.07%)</t>
+          <t>▼ -4.40원 (-0.29%)</t>
         </is>
       </c>
     </row>
@@ -7810,12 +9126,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>200.02</t>
+          <t>199.60</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>▼ -0.19원 (-0.10%)</t>
+          <t>▼ -0.62원 (-0.31%)</t>
         </is>
       </c>
     </row>
@@ -7921,27 +9237,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>112,687,000원</t>
+          <t>112,550,000원</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>112,124,000원</t>
+          <t>111,987,000원</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>121,702,000원</t>
+          <t>121,554,000원</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>110,580,000원</t>
+          <t>110,574,000원</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7978,27 +9294,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3,381,000원</t>
+          <t>3,380,000원</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3,354,000원</t>
+          <t>3,353,000원</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3,584,000원</t>
+          <t>3,583,000원</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>3,262,500원</t>
+          <t>3,261,500원</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -8013,7 +9329,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>RSI 46.4로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 46.5로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -8312,7 +9628,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>3Q26 실적은 연결기준 매출액 3,794억원(YoY+4</t>
+          <t>3Q26 실적은 연결기준 매출액 3,794억원(YoY+4)</t>
         </is>
       </c>
     </row>
@@ -8537,17 +9853,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>가장 저평가된 전력기기</t>
+          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -8557,37 +9873,37 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단.</t>
+          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
+          <t>2026-10-14_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2,350.8십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>252.8십억원</t>
+          <t>3,496십억원</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2,595.2십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>271.7십억원</t>
+          <t>4,566십억원</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -8607,17 +9923,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DS투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>휴젤</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 증익의 시작점</t>
+          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -8632,37 +9948,37 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 영업이익 3,791억원으로 컨센서스 소폭 상회 전망 26년 3분기 실적은 매출액 3.2조원(이하 YoY +22.8%), 영업이익 3,791억원(+59.2%, OPM 11.7%)으로 시장 컨센서스를 10% 상회할 전망이다. 조업일수는 하계 휴가와 추석 연휴 등으로 전분기 대비 9일 감소하나 글로벌 오퍼레이션과 2도크 재가동에 따른 매출 확대가 이를 상쇄하며 탑라인은 전분기 대비 소폭 성장할 것으로 예상된다. 수익성 또한 확대될 예정이다.</t>
+          <t>3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_DS투자증권_삼성중공업_3Q26 Preview 증익의 시작점.pdf</t>
+          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>10,650십억원</t>
+          <t>486십억원</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>862십억원</t>
+          <t>174십억원</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>12,916십억원</t>
+          <t>657십억원</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1,416십억원</t>
+          <t>272십억원</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 영업이익 3,791억원으로 컨센서스 소폭 상회 전망</t>
+          <t>3Q26 매출액은 1,009억원(-4)</t>
         </is>
       </c>
     </row>
@@ -8673,21 +9989,21 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>일진전기</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
+          <t>가장 저평가된 전력기기</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -8697,37 +10013,37 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
+          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
+          <t>2026-10-14_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,350.8십억원</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>3,496십억원</t>
+          <t>252.8십억원</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,595.2십억원</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>4,566십억원</t>
+          <t>271.7십억원</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -8743,21 +10059,21 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>유안타증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>바닥 통과, 성장 엔진 점화</t>
+          <t>중장기 카탈리스트는 여전히 유효</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -8767,42 +10083,42 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY 3Q26 연결 영업수익은 7.1조원(-1.1% YoY), 영업이익은 5,350억원(-0.6% YoY)으로 시장 컨센서스(7.0조원, 5,442억원)에 부합할 전망이다. 부동산 관련 일회성 비용 제거시 영업이익은 +2.8% YoY 증가한 것으로 추정된다. 별도 영업이익은 3,400억원으로 전년과 유사한 수준이 예상된다.</t>
+          <t>3Q26 Preview: 매출 인식 지연으로 컨센서스 하회 전망 동사의 3Q26 매출액은 1조 7,438억원(+7.4% YoY, 컨센서스 8.7% 하회), 영업이익은 2,816억원(+16.2% YoY, 컨센서스 10.6% 하회)을 전망한다. 컨센서스 하회는 2분기에 이어 중공업 부문의 일부 출하 물량에 대한 매출 인식이 지연된 데 기인한다. 중동향 물량은 지정학적 리스크로 선적 확보에 차질이 발생하고 있으며, 미국향 물량은 고객사 변전설비 부지의 준비 지연으로 제품 인도가 이연되고 있는 것으로 파악된다.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_유안타증권_KT_바닥 통과, 성장 엔진 점화.pdf</t>
+          <t>2026-10-14_미래에셋증권_효성중공업_중장기 카탈리스트는 여전히 유효.pdf</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>27,426십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2,076십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>27,905십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2,256십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -8813,21 +10129,21 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>DS투자증권</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
+          <t>3Q26 Preview: 증익의 시작점</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -8842,37 +10158,37 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다.</t>
+          <t>3Q26 Preview: 영업이익 3,791억원으로 컨센서스 소폭 상회 전망 26년 3분기 실적은 매출액 3.2조원(이하 YoY +22.8%), 영업이익 3,791억원(+59.2%, OPM 11.7%)으로 시장 컨센서스를 10% 상회할 전망이다. 조업일수는 하계 휴가와 추석 연휴 등으로 전분기 대비 9일 감소하나 글로벌 오퍼레이션과 2도크 재가동에 따른 매출 확대가 이를 상쇄하며 탑라인은 전분기 대비 소폭 성장할 것으로 예상된다. 수익성 또한 확대될 예정이다.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
+          <t>2026-10-14_DS투자증권_삼성중공업_3Q26 Preview 증익의 시작점.pdf</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>486십억원</t>
+          <t>10,650십억원</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>174십억원</t>
+          <t>862십억원</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>657십억원</t>
+          <t>12,916십억원</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>272십억원</t>
+          <t>1,416십억원</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>3Q26 매출액은 1,009억원(-4</t>
+          <t>3Q26 Preview: 영업이익 3,791억원으로 컨센서스 소폭 상회 전망</t>
         </is>
       </c>
     </row>
@@ -8887,16 +10203,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -9076,7 +10392,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -9138,7 +10454,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+1.9%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -9200,7 +10516,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -9262,7 +10578,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -9324,7 +10640,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -9351,32 +10667,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>005930.KS</t>
+          <t>128940.KS</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>231,500원</t>
+          <t>404,500원</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>229,000원</t>
+          <t>400,500원</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>256,500원</t>
+          <t>483,500원</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>223,500원</t>
+          <t>390,500원</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -9386,12 +10702,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>232,750원</t>
+          <t>404,500원</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -9413,32 +10729,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>엔비디아 (NVIDIA)</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>030200.KS</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>$228.52 (약 305,908원)</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>$228.52 (약 305,908원)</t>
+          <t>49,400원</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>$246.80 (약 330,380원)</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>$219.38</t>
+          <t>48,200원</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -9448,12 +10764,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>$228.52</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -9475,32 +10791,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>애플 (Apple)</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>017670.KS</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>$341.27 (약 456,841원)</t>
+          <t>81,900원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>$341.27 (약 456,841원)</t>
+          <t>81,100원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>$368.57 (약 493,388원)</t>
+          <t>86,800원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>$327.62</t>
+          <t>79,000원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -9510,12 +10826,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>$341.27</t>
+          <t>81,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -9537,32 +10853,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>128940.KS</t>
+          <t>010140.KS</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>400,000원</t>
+          <t>19,000원</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>396,000원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>483,000원</t>
+          <t>20,100원</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>386,000원</t>
+          <t>18,300원</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -9572,263 +10888,15 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>403,000원</t>
+          <t>18,950원</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>1일차</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>030200.KS</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>50,000원</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>49,500원</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>48,200원</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>+1.4%</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>50,200원</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>1일차</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>SK텔레콤</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>017670.KS</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>81,600원</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>80,800원</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>86,500원</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>78,700원</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>+1.4%</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>81,900원</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>1일차</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>삼성중공업</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>010140.KS</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>18,700원</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>20,000원</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>18,200원</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>+1.2%</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>18,920원</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>1일차</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>삼성화재</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>000810.KS</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>583,000원</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>577,000원</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>629,500원</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>562,500원</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>+0.9%</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>582,000원</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
@@ -9854,7 +10922,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="53" customWidth="1" min="9" max="9"/>
   </cols>
@@ -9969,10 +11037,14 @@
           <t>자사주 취득</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>엘컴텍</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>“역시 주주환원은 뒷전입니까”…코스피 자사주 매입, 삼전닉스 뺐더니 줄었다</t>
+          <t>엘컴텍, 20억원 규모 자사주 취득 결정</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -9982,17 +11054,17 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>매일경제 마켓</t>
+          <t>데이터투자</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Sun, 11 Oct 2026 11:51:10 GMT</t>
+          <t>Tue, 13 Oct 2026 07:22:52 GMT</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE0zXzFYa0xGekFCVWtnODd6QVRIRmp1MnFLcXhBWWVadVdXQWZaY3lGcGg3WUl1dzY4M1R1cTBWV1h1a0JBbXdGV3Y0aC1KV25lRmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE13UXpQT2FyUjBQSkpSdFNtQVpJOHFGMExaeDFtajBra1h5dHl5S2dMbUV5TUdmMzFYZkF6b1RmSTd0TVk1NUZCOGN1Y1pWS3d1Rk50WmRUS19XZkJISzdJX3k1YXpPU2V3X3FhNkloOWs1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10012,10 +11084,14 @@
           <t>자사주 취득</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>더핑크퐁컴퍼니</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>데스트라 멀티 대체 투자 펀드, 자사주 매입 프로그램 도입·월 배당금 주당 0.115달러로 인상</t>
+          <t>더핑크퐁컴퍼니, 50억원 규모 자사주 취득 신탁계약 해지 결정</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -10030,12 +11106,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 19:52:27 GMT</t>
+          <t>Tue, 13 Oct 2026 05:43:38 GMT</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1lemt2YTFaYUFFeVI4cVJZbjFYOHpWLVJmNTUxN3huQlRtYUVHYXplTUpvQktSZFdKenhkMl9PYXlNci1RbHNtTUdQdXgxelpjaEJVbWNjVmFndWFiaV9KZFAxd2ozbVZXVUd4MHFPNlZYT0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1MVmRGS1NqcEJobXNpM01fNTlJbV9MeFZUeXBTVktGWV9XOWFlMHFET09BeW1rQ1RJdzVCR0I1OXM1UkpxM3Nnazk4RnBPbC1EaGFxM0FpVVpqYzZPRnlGb0plTEwyYmZDSXJXNW8yYmh5M0k?oc=5</t>
         </is>
       </c>
     </row>
@@ -10055,10 +11131,14 @@
           <t>자사주 취득</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>메디앙스</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AZZ, 연간 실적 가이던스 상향…2000만 달러 규모 자사주 매입</t>
+          <t>메디앙스, 10억원 규모 자사주 취득 결정</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -10073,12 +11153,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 20:20:27 GMT</t>
+          <t>Mon, 12 Oct 2026 05:39:56 GMT</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9QR3MyNXVOWndYaXJsdTF5Z2NaQnlGUVRFanBlUjhmN1U0TDNCMXNUZ2RrNTRselZhSGtXTW9YMUJGVWtvSTdDdFhCVVN6ZTVCcTZ0WnlkeUNsRTZlMGZBXzJnSnkxZ1Z3NjI5MlF0N0N3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1TRmxBdndpdk9HTXZRTzdxNF8wSWpxQklLcDBRQks1TmxUSm4xRU9zVzRCSkxLZ3RUYy1JbS1vZXhhSnRxMXRJZnNGVHJLdkwyZzNTZTlLUWlCb0xkQUpnSWtnVURLcExLaGtWOTFMcnV6cGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10090,42 +11170,42 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>🏛️ 대주주/임원 장내매수 (책임경영)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
+          <t>내부자 매수</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>트러스트</t>
+          <t>회장</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>선라이즈 리얼티 트러스트, 2000만 달러 자사주 매입 프로그램 승인</t>
+          <t>원종석 신영증권 회장, 5거래일간 자사주 30억 장내 매수</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>내부 사정을 가장 잘 아는 경영진의 직접 매수로 기업가치 저평가 방증</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>더팩트</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 12:13:59 GMT</t>
+          <t>Thu, 11 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1fQmV2cFR2OFA5M1B6UXE3NF83TmRrd2lGSE1QelFpZWFMUDhZT1lHWHJYUnFBcmtKNUJmRWlwRTU3ME1ydno4cmpDMnpWMTF0Q09HQ0dmOVVubFFIYXNWZ1FhWlRZaEp3dk4xcHd2TmdFQ00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tYTBhV0h3WkQzbG5SbklZMW16enV2UWxnZHlkYzFjYmhYaVNQclkyYWxQM1VDTjdWYVhuMHNXRklUMGsyT2F0ck5EZkhSWGlUX2I2MmxjUENKUdIBVEFVX3lxTE1RcVhPeC1tU2FoTThuWHFyMnJFa2VSRm91eUs3dFQ5YmU2Y25BVzF2cHFycEN5UmYxTDdxWGZBM2p4ZVFFX1NwblFIMWU5cGEtcGxqZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10137,42 +11217,42 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>📈 대규모 단일판매·공급계약</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
+          <t>대규모 수주</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>아웃렛</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>올리스 바겐 아웃렛, 5억 달러 규모 신규 자사주 매입 승인</t>
+          <t>[속보] 스피어, 285억원 규모 특수합금 공급계약…지난해 매출액 대비 29.84%</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>매출액 직결 확정 계약으로 향후 분기 실적 퀀텀점프 기대</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>CBC뉴스</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 11:09:56 GMT</t>
+          <t>Wed, 14 Oct 2026 05:49:26 GMT</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5nZklvLUJYTTRmYUtlSnZGdWgzaE9aeExETGVnWDF1dXpLTGVMWWpSSEdodW1WMkprQW5oeEMxV0xtM0pIcndVZDVhVk5UWnIwcFNyMlI2X0hjb2M3UHBXME5sRGFCN0pYdDJWTEstSmpqVE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBVR0NZZ25tdjlPRnB3TFQ4UXpFNVZaTWJPaVBfWWZhRUVVWnpiRk5fWDFJM2staGx2NEhsZ1pHWVRINjBDZng3bFBZMGtQeUdWWi0xN2xROWU3ejNMNHJObmpuSjQ2TTJy?oc=5</t>
         </is>
       </c>
     </row>
@@ -10184,42 +11264,42 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>📈 대규모 단일판매·공급계약</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
+          <t>대규모 수주</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>엘컴텍</t>
+          <t>우진아이엔에스</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>엘컴텍, 20억원 규모 자사주 취득 결정</t>
+          <t>우진아이엔에스, 144억원 규모 공급계약 체결… 매출의 8.74%</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>매출액 직결 확정 계약으로 향후 분기 실적 퀀텀점프 기대</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>CEO경제신문</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 07:22:52 GMT</t>
+          <t>Wed, 14 Oct 2026 01:10:42 GMT</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE13UXpQT2FyUjBQSkpSdFNtQVpJOHFGMExaeDFtajBra1h5dHl5S2dMbUV5TUdmMzFYZkF6b1RmSTd0TVk1NUZCOGN1Y1pWS3d1Rk50WmRUS19XZkJISzdJX3k1YXpPU2V3X3FhNkloOWs1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9OMkc3SVNncl9rSWxrMjZmMFE5ZGJTaGxrem9zb2t3ZzlGYWFhcFo0dHNNMVlWa0tuVE1zeG9MOTlKRThmVS1rR3Fqb3pVNUJjQUs3MElsVFNqaHozeExqNllLbERJbHdKT0RnUA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10231,38 +11311,42 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>🏛️ 대주주/임원 장내매수 (책임경영)</t>
+          <t>📈 대규모 단일판매·공급계약</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>내부자 매수</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>대규모 수주</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>LS머트리얼즈</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>사이먼 쿠케스 박사 측, 페데브코 보통주 14만 7070주 장내 매수…지분율 34.2%로 확대</t>
+          <t>[공시 Pick] LS머트리얼즈, 美 연료전지용 UC 공급계약에 주가 강세…증시 급락 속 ‘역주행’</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>내부 사정을 가장 잘 아는 경영진의 직접 매수로 기업가치 저평가 방증</t>
+          <t>매출액 직결 확정 계약으로 향후 분기 실적 퀀텀점프 기대</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>뉴스투데이</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 12:14:51 GMT</t>
+          <t>Tue, 13 Oct 2026 01:48:00 GMT</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE8wVldLdklzOFE4cnp4RmlPLVJ2LVdveDVQTUV2UjhyTjh1NVhIMG5maUxkelFnUkhEV1ZxdGY2empxS252cDk5QW9ua2EtZ3lRUl94bVA5UEg4b09SZXdMcUk5UnlrbHRpZGU4V1VNYTdzNjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQTWoxNDVLVWtBTXVoS3MtWmFpd1UwMG9FYkVLM0EtcWhTbThJZFVkOWdVekxQMEpNR2ZMTklDQTZHdWpZU3BJSkJpTUQ2TnNVcW8weHFGM1pEVnBqNlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10498,14 +11582,14 @@
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="53" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -10594,32 +11678,32 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>🌐 [경제·사회 심층 리포트] 카카오의 숨겨진 배경과 구조적 쟁점</t>
+          <t>🌐 [경제·사회 심층 리포트] 반도체대전의 숨겨진 배경과 구조적 쟁점</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>반도체대전</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '카카오' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
+          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '반도체대전' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[카카오, ‘모두의 AI’ 연내 공개 예정…월 이용자 500만 명 목표]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 카카오, ‘모두의 AI’ 연내 공개 예정월 이용자 500만 명 목표 KBS 뉴스카카오그룹, 인적분할 앞두고 주요 계열사 CEO 함께 모여 ‘첫 공동 IR’ 개최 카카오연말 출시 ‘모두의 AI’“카톡 익숙함. 활용할 것” 마켓 카카오, 웹툰·음원·카카오T에 스테이블코인 결제 연동소설 원작 AI 애니 제작도 전자신문카톡에 “메시지 정리, 답장 보내줘” 말하면 AI비서가 척척.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
+          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[삼성전자 '반도체대전' 참가‥HBM4E 등 AI 반도체 기술 선보인다]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 삼성전자 '반도체대전' 참가‥HBM4E 등 AI 반도체 기술 선보인다.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; 피지컬 AI 시동 건 카카오모빌리티…상생재단서 '카카오' 뗀 이유는? 알림음과 배경 음악을 구분하는 카카오 라인 블록 체인 사운드 안내 Calgary Roughnecks.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
+          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; 신성이엔지, 반도체대전서 클린룸 기술 공개...해외시장 공략 확대 헬로티. KTC, ‘제28회 반도체대전’ 참가… 시스템반도체·미래차 전장부품 신뢰성 검증 인프라 공개 기계신문.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 카카오 AI, 올해 사회경제적 가치 약 5500억 창출 전망 서울경제. 카카오 AI 사회경제적 가치 연 5506억원…2030년 최대 1.8조원 전망 지디넷코리아.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
+          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 반도체대전, 기술 전시 넘어 채용까지…삼성·SK하이닉스 등 300개사 집결 매일일보. ② 반도체 쏠림이 위험하다고?…“올해 코스피 이익 증가분 90%가 반도체" - 조선비즈 Chosunbiz.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -10629,17 +11713,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>📌 **구조적 수혜(Structural Beneficiary)**: 단기적 유행이 아닌, 국가 정책이나 글로벌 지정학적 공급망 재편에 따라 수년간 장기적인 성장을 누리게 되는 산업 생태계 현상입니다.</t>
+          <t>📌 **HBM(고대역폭 메모리)**: D램을 수직으로 높게 쌓아 데이터 처리 속도를 획기적으로 끌어올린 인공지능(AI) 그래픽처리장치(GPU) 필수 탑재 메모리입니다.</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE43NnU3MlhmZWZkcEdnRU1abkNDcHdIdG85YU9NZVBqVF90N3BXTHFCVlJIbDZQbkg3RGR5NWltZ29IaXNWNkdIWm1aYzBmLU4wbnVfd1hhVnlwdVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9QLWl1VjBqYUpRc3BydE96Y1c1N2JQNUJ4TTdmazF6NmRlb01JaHpYa3NSX2llQkRyUFU3S1JYOUxVbkp3N3VMOUlITWFoUEk2YlpkTDdmUzE3MUJwbG9LclBOQzNYNzkzZnJLcDdveDZKMkFG0gF0QVVfeXFMUG52cWpIVDZJZFNKelIwTmczTFJmVUtRTjVBYlI0ZEJtNkJYWWVYaWVRR1plUFR0M3pQUVZUdmF6RDJRNm5qWjlHNUFzNlZ0d2N6TV8tNm1RUldCMVh3b3l4eWhkdlBUOGMtSVZwMm5YUTlGUzg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10661,32 +11745,32 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>🔥 [트렌드 &amp; 소비 인사이트] 블루 아카이브 열풍의 배경과 소비 심리 분석</t>
+          <t>🔥 [트렌드 &amp; 소비 인사이트] 시오라 열풍의 배경과 소비 심리 분석</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>블루 아카이브</t>
+          <t>시오라</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>요즘 왜 난리일까? '블루 아카이브' 품절 대란과 오픈런 이면에 숨은 소비 심리와 바이럴 구조를 짚어봅니다.</t>
+          <t>요즘 왜 난리일까? '시오라' 품절 대란과 오픈런 이면에 숨은 소비 심리와 바이럴 구조를 짚어봅니다.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>지금 거리와 SNS에서 소비자들이 가장 열광하고 있는 화제의 중심은 단연 **[GS25, '블루 아카이브'와 3차 협업…전국 팝업스토어도 운영]** 입니다.&lt;br&gt;• &lt;b&gt;트렌드 현황:&lt;/b&gt; GS25, '블루 아카이브'와 3차 협업…전국 팝업스토어도 운영 매일경제 마켓.&lt;br&gt;• &lt;b&gt;열풍의 온도:&lt;/b&gt; 매장 문이 열리기 전부터 줄을 서는 '오픈런'과 온라인 품절 사태가 잇따르며, 단순한 유행을 넘어 하나의 강력한 문화적 현상으로 자리 잡았습니다.</t>
+          <t>지금 거리와 SNS에서 소비자들이 가장 열광하고 있는 화제의 중심은 단연 **[시오라, 성수동 팝업스토어 오픈…슬로우에이징 스킨케어 선보여]** 입니다.&lt;br&gt;• &lt;b&gt;트렌드 현황:&lt;/b&gt; 시오라, 성수동 팝업스토어 오픈…슬로우에이징 스킨케어 선보여 중앙일보.&lt;br&gt;• &lt;b&gt;열풍의 온도:&lt;/b&gt; 매장 문이 열리기 전부터 줄을 서는 '오픈런'과 온라인 품절 사태가 잇따르며, 단순한 유행을 넘어 하나의 강력한 문화적 현상으로 자리 잡았습니다.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 알림음과 배경 음악을 구분하는 블루아카이브 경마 사운드 안내 Calgary Roughnecks. 수영복 입은 문주님, 블루 아카이브에 '람과천청' 업데이트 월요신문.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
+          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 호남오페라단 '달하 비취시오라, 정읍사' - 지역사 예술적 부각, 감동 무대 전북일보 인터넷신문. ‘달하, 비취시오라’와 창작오페라를 위한 제언 서울문화투데이.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>소비자들이 기꺼이 시간과 비용을 들여 줄을 서는 심리적 이유를 쉽게 풀어보았습니다.&lt;br&gt;• &lt;b&gt;소비 심리:&lt;/b&gt; 넥슨 '블루 아카이브' 모집 BM 개편한다, 4분기 글로벌 적용 게임뷰. 생성형 AI와의 공존 ③ 넥슨게임즈 김용하 본부장 게임메카.&lt;br&gt;• &lt;b&gt;심리적 기제:&lt;/b&gt; 단순히 제품의 기능 때문이 아니라, '희소한 트렌드를 남들보다 빠르게 경험하고 인증했다'는 심리적 만족감과 소속감(디토 소비 및 포모 심리)이 지갑을 열게 만드는 핵심 동기입니다.</t>
+          <t>소비자들이 기꺼이 시간과 비용을 들여 줄을 서는 심리적 이유를 쉽게 풀어보았습니다.&lt;br&gt;• &lt;b&gt;소비 심리:&lt;/b&gt; 시오라, 성수동 팝업 통해 오프라인 시장 공략 세계비즈.&lt;br&gt;• &lt;b&gt;심리적 기제:&lt;/b&gt; 단순히 제품의 기능 때문이 아니라, '희소한 트렌드를 남들보다 빠르게 경험하고 인증했다'는 심리적 만족감과 소속감(디토 소비 및 포모 심리)이 지갑을 열게 만드는 핵심 동기입니다.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -10701,12 +11785,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>매일경제 마켓</t>
+          <t>중앙일보</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5oRlFmSDNxbVRUaEctLWp3SHVvbEtGeFRFajBNUndReGo0QzZNdFBacG1la0ZGR3BScW5qb091eW4xclJOQi1vYk9DVjM4NVd6cnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE4wV1Y5MTVqUTFlVHpha3BmY201YjVydFgydlFybzU3VTh0MmxneTJ6TGwwT1dWVURpRjFaaVFZWjNSYVU1ZEx3UDRmSTM3VWhJTVN0WWd3?oc=5</t>
         </is>
       </c>
     </row>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G285"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -5222,27 +5222,27 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>국힘 “임광현 비서실장 임명, 대장동 패밀리 보은 인사 결정판”</t>
+          <t>공수처 "조희대 업무추진비 수사 예정", 중수청장 후보자 "수사 가능"</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>국힘 “임광현 비서실장 임명, 대장동 패밀리 보은 인사 결정판”.</t>
+          <t>공수처 "조희대 업무추진비 수사 예정", 중수청장 후보자 "수사 가능". 아울러 행안위, 오늘 김지용 청문보고서 채택‥與 '적격' 의견.</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>뉴스타파</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9aY09BMFZUQ3B4YThtaWtpWl9wU2NvQmpBT05xUkcwX1pjS2lHX0JaYW9iaHJHaGpwOEtlTzV2S29mb2p1RUJKb3VpZ3V6eUFwVE9XdUN5UzVIMmZiWWR2d0Y4TUMwa25WYmROZ3kyeDIzYmtMUFRn0gFmQVVfeXFMTndadXlheEZvRGM2V0lHWmc3ei1EV1JoTkZ6Q1FmMzM0T3I2aFJSVFNnejliZDZON3hsZGd2cU9GbUVVaGNMcVBWd2wwbG5RSnpYLVNjZ1FCcm95THgxX3kzWWFOYWx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE52a0pKejBqUm52SEoyVi1SVW1vQ09MY0hsZGJ6NHNlUG1WaUxTc0pMQkNXalJVMGkzaWVBWmJNOWtQNUYyV1hjTzJB?oc=5</t>
         </is>
       </c>
     </row>
@@ -5259,27 +5259,27 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>김지용 “정진웅 독직폭행 사건, 업무상 과실치상 기소 의견은 정당”</t>
+          <t>李, 임광현 비서실장에 임명장…강훈식엔 공로패</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>김지용 “정진웅 독직폭행 사건, 업무상 과실치상 기소 의견은 정당”.</t>
+          <t>李, 임광현 비서실장에 임명장강훈식엔 공로패. 아울러 김민석, ‘강훈식 서울시장 후보설’에 “역량 검증된 전국적 인물···가능성 열려 있어”.</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9keXlOT0NOYmZDczYyZzZIVnRwVW1rU2Y4N29iaVd3WmVLLXpaUUdpQjZsZ1ZkeC1NcFFGcDFkT0MtZnc5Y0VXajBsdkFTT0hOTEhLam01NHFHUGRRdWN4bXFleXRKcVJLVjRSdEVhRWJzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9qb2xyWHlLZGsxb0dZX3BWQXVNeWMwbl81Zk9mZFZwRElVR2tWaGVaVWFkUnczc0RCTnhsT0swcWdHNXVqOUZ6TVVOLUFjYlNnblBsY05SXy14Mlk3Q0loT2liNUdoSkFPV1dvOTY5aVUyS0dJUDFJ0gFmQVVfeXFMTnVNeExQOWw3MDE3cTc4OW40N2kwQmNpZjBqaHJlc2UxVVZEZE9MeGEtYjFBTWFYcmxEaWM0VDNjbWxwbEpNajVDVlJyQ3RjTVVZRV9QRktPV0dpSU54MjZjaFI1MVd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -5296,27 +5296,27 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>‘김지용 명예훼손 혐의’ 임은정 고발 사건, 서울중수청 반부패부 배당</t>
+          <t>김민석, 신천지 논란에 "당헌당규 지키며 처리 중"</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>‘김지용 명예훼손 혐의’ 임은정 고발 사건, 서울중수청 반부패부 배당.</t>
+          <t>김민석, 신천지 논란에 "당헌당규 지키며 처리 중".</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9SMUR3WDlVLW9mdnd1NlphOWU2d2FHcmxlelhxdmlEZGd5LTBlay1SZmNfTmc5aTNtNWtZR3BwZi1kRkVHTUZ6LUlxQzljRG5aXzF1WjJIZW9DUdIBX0FVX3lxTE5Ob21LRVhEaGJWbUV1QXQ5VXNnc1k0bmc0ZWxxSUE4Tk81TVUwaFNkakZ4YWVMem16R2lvQmFIcENTblNacTFjNjBLSFlIOFRVUUlsaHUxVlZSaUsxbTMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE04bDMxN2NiSmF1SENCZWprZDFxNmZmUmU3aWZ3aUNqTVdSMEczMGJtWE1vVDc3T0Q2WGZ4ZlM5YXFLYXNTZU1MU3VZLVRVSmxLdXRCdnZBektGOFJmbXV6T0Zhd2NjWVFUVUpNaGNOaGJLUXk0ODBFSdIBeEFVX3lxTFBIY0RfeGNXWUNUMGdyUFdTZnNtN3JEUGtUTWswR3NMX1JZVy0wZkpUb0d0dl8ybHBsWUkyS2JCLTlwRE5wbzZjc0U3bmF4V0lQSk1EaGFhUlB1MkFzWWlEcXZDOV9RWVNMWTlvcnJmX1B1bHl6cGEtUA?oc=5</t>
         </is>
       </c>
     </row>
@@ -5333,27 +5333,27 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>국힘, '신천지 민주당 집단 가입 정황'에 "압수수색·특검 필요"</t>
+          <t>알래스카 가스관공사 전 임원 “한국 750억달러 넘게 낼 수도” [인터뷰]</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>국힘, '신천지 민주당 집단 가입 정황'에 "압수수색·특검 필요".</t>
+          <t>알래스카 가스관공사 전 임원 “한국 750억달러 넘게 낼 수도”. 아울러 트럼프 "한국, 알래스카에 500억 달러 투자‥무역·투자합의 일부".</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE53T2xTSlVLTHJOUFByb1FjZFl4bS1KdVNOdUpJREg0SmM1QmhJZ3R2OVIydTNSbnFYNmtnaXFsX3IwXzczaV95ZTdCVFVwX0NKcUlZZ3JaMWo3anRmbmhaLVlaUE9KUDlKb0QxMjhQOThWYXNnZ0RHT9IBeEFVX3lxTE5UdXRNcGxnNldydGZDdEJCZTJyYTJYTXltMF80SnlJdjlaRl9aLU5lMDY2cW1XaUNuM1NmX2I2LUo1NUNYY3ZmQmtuUlZQTFJRY0FWaFU5M0JHZV9CR1F6TW9xTXlZazhyRWRLMDVma1pNXzY5YUN5Xw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZU8waXlhQlJxTmI4dUc5VzZLakpSWUZ6bEdodHk0MnF0VzRLZEJqYy1nUnVIR256cUdlV2luNGdmZmpoMThKbW5kRnJmMnI1S3RNREtlY0hHTVo3MkJLMno0RzAtMTk3cnJKYVVsaEp6ajRMeFZkN0gwM08yVkFKS3Zn?oc=5</t>
         </is>
       </c>
     </row>
@@ -5370,27 +5370,27 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>트럼프 “한국의 알래스카 500억 달러 투자, 나와의 무역·투자 합의”</t>
+          <t>"의원직 박탈될 수도?" 한동훈 고발 예고 #shorts #오마이tv</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>트럼프 “한국의 알래스카 500억 달러 투자, 나와의 무역·투자 합의”.</t>
+          <t>"의원직 박탈될 수도?" 한동훈 고발 예고 #shorts #오마이tv.</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5ZazBWaUstTGcwX0lOZjJVdEhzdUMxR2xVdFQ0eWk1eGczMFczQjNmeXJzaGstMVpSc2pvN0VRSERBNzBKOFY5UzJwS1I3ZmIzVDVXMHlKaTBXM0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE5WbUV5bUZjOE42S0JUY2pzMldHZ2haSGVLRjc0LUdlZUhfU3VhTE5NVm1TdzVXQkhiVm1IRVJzc0Q0VXVETHpJT0p3V2tVSk12aEdWQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5407,27 +5407,27 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>'이종섭 호주대사 도피' 윤석열 2심 재판 이달 19일부터 시작</t>
+          <t>오세훈 "용산공원 개발은 특별법 위반…주택공급 규제 풀어야"</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>'이종섭 호주대사 도피' 윤석열 2심 재판 이달 19일부터 시작.</t>
+          <t>)= 오세훈 서울시장은 용산공원 부지 일부에 주택을 공급하려는 현 정부 구상에 대해 재차 반대 입장을 밝혔다.</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE0xcE0wQ0VmTTl0V1BTbEpTbmtTV09uX1FpcTc1Q2dhcndWOWM4MzJLTHJ5QjhGaXlqWE5TV05wVXVyWFlQZkk4bjdrYkFCWkpQM3BMUFVxajVJakYzRWE4NDBHeW45cUtBNUQ0OVBVUUk1cENXdmRV0gF3QVVfeXFMT0hvTHlHcVBUVjA0QWVheENRNkZuTjVxVm5hVDkzanlGTVdKQTlTQi01eUw3SVBIbmlEamU4RjI0all4Y2hjS3dvdldONEZ2cTZxZXdTR1E5VDR4VV9mWjl2SmlIZG1jX2sxVUdfUlNzeGo1V2laZm8?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015095200004</t>
         </is>
       </c>
     </row>
@@ -5449,22 +5449,22 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>[칼럼] 대통령기록관은 대통령기록을 관리할 자격이 있나</t>
+          <t>법제처장 "DMZ 평화적 이용 가능…유엔사와도 의견 접근 있어"</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>대통령기록관은 대통령기록을 관리할 자격이 있나.</t>
+          <t>)= 조원철 법제처장은 15일 평화적 목적의 비무장지대 출입 권한을 유엔사가 아닌 한국 정부가 행사.</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>뉴스타파</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE9mYmUtMUpOT2lIYkI3TzQ3dkxITkRSV244d1BXclNEeFo3TnRWV3R6XzN6enc5R1FEMDM4dlM0cHYzWDd0ODdnbWRR?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015093800001</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5486,12 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>北 미사일 발사날 "미 해군 무인정찰기 동해 상공 비행"</t>
+          <t>소진공 "홈플러스 입점업체 긴급자금 금리 인하 적극 협의"</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>북한이 잠수함발사 전략순항미사일 시험발사를 한 지난 14일 미국 해군의 무인정찰기가 동해를 중심으로 한반도 상.</t>
+          <t>)= 인태연 소상공인시장진흥공단 이사장은 15일 홈플러스 입점 업체에 지원한 긴급 자금에 대해 추가 금리 인하를.</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015033900504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015094500030</t>
         </is>
       </c>
     </row>
@@ -5518,17 +5518,17 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>[부고] 이기철(전 재외동포청장)씨 부친상</t>
+          <t>국힘 최고위서 '용인갑 조직위원장 경선 논란'에 고성 충돌</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>▲ 이충열 씨 별세, 이기만 ·이기철 ·이기준 씨 부친상, 김.</t>
+          <t>)= 국민의힘 지도부가 15일 연 최고위원회의에서 양향자 최고위원이 결선까지 갔다가 패배한 '경기.</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015033300504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015088700001</t>
         </is>
       </c>
     </row>
@@ -5555,17 +5555,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>[게시판] 방사청, 제안서평가 제도 개선 공청회 개최</t>
+          <t>"성남 라인"·"정치 공세"…기노위 '기관장 자소서 제출' 공방</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>▲ 방위사업청은 15일 정부과천청사에서 제안서평가 제도 개선을 위한 '방위력개선사업 협상에 의한 계약체결기준' 개정 공청회를 개최한다고 밝혔다.</t>
+          <t>)= 국회 기후에너지환경노동위의 15일 국정감사는 남광우 한국환경산업기술원장을 비롯한 기관장들의 인사 자료 제출.</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015032000504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015087000001</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>기보, 전세보증금 10억 이사장 관사 운영…보증금 상한 없어</t>
+          <t>김상훈 "지방정부 조달 자율화 계약형태 수의계약이 96.5%"</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>담보력이 부족한 기술기업을 지원하기 위해 설립된 기술보증기금이 전세보증금 10억원짜리 해변 초고층 주상복합 아.</t>
+          <t>)= 경기도와 전북도에서 '지방정부 조달 자율화'를 시범 운영한 결과, 소액 등 수의 계약이 96.5%에 달하는.</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015024400051</t>
+          <t>https://www.yna.co.kr/view/AKR20261015092900063</t>
         </is>
       </c>
     </row>
@@ -5629,17 +5629,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업, 첫 미해군 함정 MRO 수행…군수지원함 정비</t>
+          <t>여야, '불법사찰 의혹' 공방…'김현미·김건희' 증인 요구 맞불</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>HJ중공업 이 미국 해군 함정 MRO 사업을 성공적으로 끝냈다.</t>
+          <t>)= 여야는 15일 국회 국토교통위원회의 한국부동산원과 주택도시보증공사 등을 대상으로 한 국정감사에서 야당.</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015029500051</t>
+          <t>https://www.yna.co.kr/view/AKR20261015090400001</t>
         </is>
       </c>
     </row>
@@ -5671,12 +5671,12 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>김민석, '강훈식 서울시장 후보'질문에 "가능성·미래 열려있다"</t>
+          <t>진보당, 전남광주 농어촌기본소득 "지역별 차등지급 반대"</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>더불어민주당 김민석 대표는 15일 당무 관련, "당헌·당규를 지키면서 할 것은 다.</t>
+          <t>)= 진보당 전남광주통합특별시당이 농어촌기본소득 지급 대상을 모든 농어촌으로 확대하고 지역별 차등지급을 철폐할.</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015021500001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015085300054</t>
         </is>
       </c>
     </row>
@@ -5708,12 +5708,12 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>경제인협회 류진 "한미 전략투자 실행 단계…이제 기업의 시간"</t>
+          <t>법제처장 "대법원장 제청권은 제안 의미…재제청, 헌법상 책무"(종합)</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>한국과 미국 경제계가 양국 정부의 대미 전략투자 프로젝트를 성공적으로 이행하기 위해 신속한 인허가와 비자 문제.</t>
+          <t>)= 조원철 법제처장은 15일 이른바 대법관 후보자 재제청 문제를 둘러싼 청와대와 조희대 대법원장 간 갈등과.</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014188100003</t>
+          <t>https://www.yna.co.kr/view/AKR20261015077351001</t>
         </is>
       </c>
     </row>
@@ -5740,17 +5740,17 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>1억원 들었는데…"HUG '부동산 금융' 용역, 기존 저작물 짜깁기"</t>
+          <t>특검 "30개 시군구 선관위 투표자수 허위입력"…7곳 압수수색(종합)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>주택도시보증공사 가 2023년 수의계약을 통해 1억원을 들여 진행한 연구용역이 기존 저작물을 개정한 수.</t>
+          <t>)= 이태한 선거관리위원회 특별검사팀이 지난 6·3지방선거에서 선거관리위원회들이 시간대별 투표자 수를 허위로 입력한.</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014170200001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015080451004</t>
         </is>
       </c>
     </row>
@@ -5782,12 +5782,12 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>"여기가 동사무소냐 꺼져" 폭언 육군 장교…정직 2개월 정당</t>
+          <t>법제처 국감도 조희대 공방…"직무유기"·"재제청 근거없어"</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>부하 병사들의 휴가와 외박 승인을 수백차례 늦게 처리하고 폭언을 한 데다.</t>
+          <t>)= 여야는 15일 국회 법제사법위원회의 법제처에 대한 국정감사에서도 조희대 대법원장의 대법관 후보자 재제청 거부를.</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014119100051</t>
+          <t>https://www.yna.co.kr/view/AKR20261015088900001</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>"국중박 전시 나온 친일파 유묵, 주인은 유홍준 관장"</t>
+          <t>"이사장 해외출장 보내려"…교육시설안전원, 허위초청문서 작성</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>국립중앙박물관이 애국지사의 글씨로 소개했다가 친일파 박중양 의 유묵으로 확인돼 철거한 유물이.</t>
+          <t>)= 한국교육시설안전원이 이사장의 국외 출장 근거 마련을 위해 직무 관련 여행사에 허위 초청문서를 작성할 것을 요구.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015010600001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015040200001</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>[속보] 北 "어제 동해서 2종 잠수함발사 전략순항미사일 시험발사"</t>
+          <t>英해리왕자, 상이군경체전 축하 메시지…"도약 위한 발판 되길"</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>北 어제 동해서 2종 잠수함발사 전략순항미사일 시험발사과 관련하여 주요 정책 및 시장 이해관계자들의 입장과 향후 파급 효과를 전했습니다.</t>
+          <t>)= 찰스 3세 영국 국왕의 차남 해리 왕자가 15일 수원에서 진행 중인 제60회 전국상이군경체육대회 참가자들에게.</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015008400504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015084900504</t>
         </is>
       </c>
     </row>
@@ -5888,17 +5888,17 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>윤준병 "농협, 최근 3년간 영농지원비 195억원 홍보비로 전용"</t>
+          <t>李대통령 지지율 44%…민주, 33%로 현정부 출범 후 최저치[NBS](종합)</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>농협중앙회가 농민 조합원의 영농 지원을 위한 예산을 줄여 최근 3년간 195억원에 달하는 홍보비를 추가 편성해.</t>
+          <t>)= 이재명 대통령의 국정운영을 긍정적으로 평가한 비율이 44%로 집계됐다는 여론조사 결과가 15일 나왔다.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014171300001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015078251001</t>
         </is>
       </c>
     </row>
@@ -5930,12 +5930,12 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>외교부 공무원이 폭행·절도…野김대식 "공직기강 세워야"</t>
+          <t>레이저 대공무기 천광, 드론 요격 시연 성공…1회 발사 2천원</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>올해 들어 적지 않은 외교부 공무원이 폭행과 절도 등으로 수사기관으로부터 기소·기소유예 등의 처분을 받은 것으.</t>
+          <t>)= 한화시스템 은 지난 14일 육군본부 주관으로 열린 '아미 타이거 플러스.</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014155000001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015088300003</t>
         </is>
       </c>
     </row>
@@ -5962,17 +5962,17 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>"기보, 수천억 팩토링금융 성과측정 없이 '깜깜이' 지원"</t>
+          <t>美 "전작권 전환조건 변화"…韓 "골대 옮기면 영원히 불가능"</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>기술보증기금 이 수천억 원의 예산을 투입하는 팩토링금융 사업의 성과를 제대로 측정하지 않고 있다고 국회.</t>
+          <t>)= 정빛나 국방부 대변인은 15일 제이비어 브런슨 주한미군사령관이 언급한 전시작전통제권 전환 조건 변화와.</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014174600001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015081200504</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -6004,22 +6004,22 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>경찰 '시민영웅' CCTV공개 '의자로 막고 온몸 던졌다'</t>
+          <t>과방위, 구글 사장·LG U+ CEO 국감 증인으로 채택</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>경찰 '시민영웅' CCTV공개 '의자로 막고 온몸 던졌다'. 아울러 흉기난동범 "뉴스거리 만들려"경찰, ‘살인미수’ 영장 신청.</t>
+          <t>)= 구글코리아 사장, LG유플러스 최고경영자 등이 국회 과학기술정보방송통신위원회 국정감사 증인으로 추가.</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9KMXlxemFOWlpQVThESGVCX0x5eTg4OEFWanJTQXVOUk5xN3ZRY2hPRURjZnBmQWZMT0F5Nm92RG96V2J5UlRyNWtzRWIxZzRBY19Obm44YTVpckxOZGRTZzZRRTVza3F2V2pxSVZyVnZmRjFMUEE40gF3QVVfeXFMTUZkdl81QkxPemZGMmFHcFY2VWs0NjA0ZUljS0piZ0RvM1Z0d3JGRTR6UURVMFpjU2ZaRGhrRG01UHlFMWhlNEowVHJNWDdPZ2RyU2tfV3ZKRWl5V2Rjb3AtRkxwZVQ1VmFXZ2liYVl6V0NzYlp1T2c?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015083000001</t>
         </is>
       </c>
     </row>
@@ -6031,32 +6031,32 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>임광현 처남은 ‘대장동·대북송금’ 변호인</t>
+          <t>특검, 경남선관위 압수수색…시간대별 투표자수 허위입력 관련</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>임광현 처남은 ‘대장동·대북송금’ 변호인. 아울러 김민석, '강훈식 서울시장 후보'질문에 "가능성·미래 열려있다".</t>
+          <t>)= 선거관리위원회 특별검사팀이 경상남도선거관리위원회에 대한 압수수색에 나섰다.</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNb085SDFxNmlnM1d1NW4tQmJfYWFUSkx2UEVodGJiMU5DU1oycVF0cGtMeEx1dk1QWXItZUFmUFVhenRWSy1wVmtxU1AtOVZPLTFVaEZDTTJ0cWMya2RxdHVUOWJhUWxWQ3dFRFhhNmVxY0hrYnNHc2l6bjdyMnFZQ2RzcldzdzlrVi1YcndUdUo?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015082000052</t>
         </is>
       </c>
     </row>
@@ -6068,32 +6068,32 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>민주, 김지용 ‘적격’ 의견...15일 청문보고서 채택한다</t>
+          <t>'DMZ 평화공존 방안 모색'…경기도, 28일 국제 포럼</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>민주, 김지용 ‘적격’ 의견15일 청문보고서 채택한다. 아울러 “친윤” “반윤” “여당도 반대”여-여·여-야 충돌한 청문회.</t>
+          <t>)= 경기도는 28일 소노캄 고양에서 '비무장지대 오픈 페스티벌' 학술 행사로 국제 포럼을 연다고 15일.</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5EeGwyaURmdWNEMFlXV0l4Nm1PYnlPSzBQc0ZkZkwyOHNsb0VINXk3NURnUHFKSG5SQmNHdUVSSE9YN3doNjlnVU5CZkk2Ui0tdVBtc3dwVC1hSTJGOFk3TG5nd1NuWE5CSW95b1NDMUU1U19V?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015083500060</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6110,17 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>주한미군사령관 "전작권 전환조건 변화‥계획 바꿔 새 기준 생겨"</t>
+          <t>선관위 특검, '투표자수 허위 입력' 중앙선관위 등 7곳 압수수색</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>주한미군사령관 "전작권 전환조건 변화‥계획 바꿔 새 기준 생겨".</t>
+          <t>선관위 특검, '투표자수 허위 입력' 중앙선관위 등 7곳 압수수색. 아울러 특검, 경남선관위 압수수색지방선거 투표자 수 오류 수사.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB6X3lvNEsxZmpVNDRzSXlpODBSTF81WVA1Z1RNaExQU0lRLXRhVUVmSXllVjU5aUZZMFU3N1BudTVQcWZ5ck1VSFA1aEdDVFZERVExRVFqWFhqU21DYkJiYnNJazBEaE55MnNHT1YzQWFXTkdV0gF0QVVfeXFMTlFwTUxUb2pDSndlVlpkclpOSjVkNkl5UUtvN2VDWVptZGExX19ua1VNTm9DTlZ6SDFtalJtQVNQcWxzX2JFbXFOX3lkdXF4NzE4RUQ1VG1rOS1scnRENFh1YW81dHNtSkVBVmhicFR2d1g3OGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE10ZGptcWVZNmQ3UEYyU0w2cjdWdngzQjJIdXQyS2RJTFJKNlVMWEFCOFhCNE1tYzNVOVhHZlpPc2F1NVM2MXpyRXJZRjVCYzc0eU9wNWdhYnFsM2o3UlI5TWRBRHUxeU9aTjBfNjRWLWdKZ25OSC1Z0gF3QVVfeXFMTVRkLWV6WTlBOFZMWHlNc2NVeGhybEhKbDdDdWw2OUZRREFtZzRhNVZ5aGh0SUUxR002VHE1cDlPYmxTN0V5b05wekw0QkpoWjl4NzNVUENCdUJyUkZPWkxSaU1FRnQ3ZjhKdEo2U2pGbXFVZzZtVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>국민 46.8% "대통령 SNS 그만"…李 지지율 34.9% [KSOI]</t>
+          <t>김민석, ‘강훈식 서울시장 후보설’에 “역량 검증된 전국적 인물···가능성 열려 있어”</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>국민 46.8% "대통령 SNS 그만"李 지지율 34.9%.</t>
+          <t>김민석, ‘강훈식 서울시장 후보설’에 “역량 검증된 전국적 인물···가능성 열려 있어”. 아울러 대장동 변호인 가족을 국세청장 이어 비서실장에.</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE56ZFBoVk5CR1JLZWVjTDgwM0oySk4xZnFDS3VualZPY3o4Qy1kWmlKQng0OHNHeWEtcmxNamkwYUJ4NU90VHM0aHMxQVJMUl9BMUoyR1JiWUd1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9HcHBhZW85UEhNZnJsdmNPSHp0LWlLeEhoM05aVzhaY3ZEeEF3Rl9TTEdpWnNYLVpLMUJJTXdSMzh5aFVTZW5SZjM0RExUTEx3T3hkQ0ZKbndCUdIBX0FVX3lxTFBPWTF5VjN5YzRfbWNWMkdSOGxFbDVvaWdSRW00RTJDRjdVdVlHZ0d4dWNreW5ydGx3YzloTGQ0VTh2c0IwTXlEbnJ5WUZHNU9LRk9YZnY5MDBodFVMTDNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -6184,27 +6184,27 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>추미애 “소방이 골치 아픈 재정 빨대” 발언에···소방관들 “사과해라” 촉구</t>
+          <t>인천 흉기난동범, 감방 피한 이유…22년 전 사건 봤더니</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>추미애 “소방이 골치 아픈 재정 빨대” 발언에···소방관들 “사과해라” 촉구.</t>
+          <t>인천 흉기난동범, 감방 피한 이유22년 전 사건 봤더니. 아울러 범행 전 휴학계 제출·현금 600만 원 소지한 인천 흉기 난동범···경찰 “도피 의혹” 조사.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBiVWRyUWtQaXNPNHdPOWJfTk9uRXFOT1RuV1JhU2hEaHN1UjBwai1XRUhqVjZSeHY1M0hwVy1NRlB4Y3U3d0pmX1pWYnNlTlFORWl1ZGtCdEp2QdIBX0FVX3lxTFBhYVdpMTdNYjA5RlQ4Vk1HRWYyNmJiUmd1NmJreXAwX3ViM0tsajJFY1hMaXV5SzBueFB6b0E2NEQ0MjJkcUxISGVxSDRrVVl4VTVGd1lLM05UY09PWFM0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5fYnBJdi0zbWlUU08temJSbUlhSnBZdURCeG5samIxdnFJQ3JrU25DNWRXcV9EVXEzYThLTWIyRmlMWkNKM0dRTG9zR2tYUnVJU0FvYzM1d1NrUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6221,27 +6221,27 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>[김창균 칼럼] 경보音 급박해지는 ‘이화영 시한폭탄’</t>
+          <t>[천지일보 여론조사] 이재명 대통령 지지율 37.4%… 부정 평가 60.3%</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>경보音 급박해지는 ‘이화영 시한폭탄’.</t>
+          <t>이재명 대통령 지지율 37.4% 부정 평가 60.3%.</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>천지일보</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNbzhkRXZmd3pkY3B6M01YN3lLVVhHOHYzMldNX0FOT2Nmbmh3UmxiVzhiVWRpOUhjVWs1WVZ1dUh4ZV9ZM3NrcGRXWmpZUmpoN1RuTWVqTHpSSWNvd1hoVEcxZzctNmE4NXZmdks4VVJlZnBDeW9vTVhUSi1jY1ZHUVdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE85WGRUeE5RZ1Jub21venA0akstVjkwSlN6MFpZVU50elJIQVU0UENvNjJ4bmg5VnNwT1JPWEttMVQwTmtPR21rNVdBYWxDdkRSYk5CUzJyVl9jYV9vUVIwZkMwTXJRTmlpQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>'김지용 명예훼손' 임은정 광주청장 사건 서울중수청에 배당</t>
+          <t>주한美사령관, 전작권 전환 관련 “계획 변경돼 새 기준 생겨”</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>'김지용 명예훼손' 임은정 광주청장 사건 서울중수청에 배당.</t>
+          <t>주한美사령관, 전작권 전환 관련 “계획 변경돼 새 기준 생겨”.</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1meDBUX0VhYmw1QzNHb0RDTmFHUm9tR1RHZkh5bWlEVDJtWG5SbFNJV2Z3UXR1RkhITmxfRWlpNFBkbUFIRG1NNTBJQjlDR2EtQzBCTU9jYWoyUTRwQ1Y3VGQ5dEdVcFp6WkRzaHIyejB5Q0lGS0Rv0gF3QVVfeXFMTnhYVmFKR0NYbE5wTmNWbzh2anBYM1dsSlRRNEdaWC11dVQ3NUQ1R21BV1dvM2s0NHlGbnZpRE1obFpuQjFORzhQOVJHQTZFaHFKTDNzZWUtS2ctWERKMzJHeENmUldXSGViZDFMaE1ucnh4bTVHZVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBmRlF5MkJPeXNkUkNxMkhRWFdoakZodV91OEZERDJ2b1RoT3FFRnNJbUM0cW0tc2E3ZFgxV3M3RW1STDBVcDRPRU5YYS1qNE5jdlN4Wmdud0VkQmlXUTVnMm5vdTFOQ01XTmo2SS15OHUtTG_SAWZBVV95cUxOeTNkbEtjT0FtNG9kd2p4YVRaTzhEQWgwTTRCcEZYRFpyVEl3SnFmaG1lUmxKejBWTXVmUXY2MXpBaHhLMFU2WlFhc2t0WjE2d3IzZUg1XzBGZkJOQnF4SEdXaUo0VUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6295,17 +6295,17 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>중부고속도로 점촌함창나들목서 승용차-화물차 추돌로 1명 사망</t>
+          <t>장모 살해·아내 납치 20대 남성, 내주 신상공개 경찰 심의</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>중부고속도로 점촌함창나들목서 승용차-화물차 추돌로 1명 사망. 아울러 중부내륙고속도로서 승용차가 화물차 추돌30대 운전자 숨져.</t>
+          <t>장모 살해·아내 납치 20대 남성, 내주 신상공개 경찰 심의.</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9uZ0VHMEtsdHIyeW5ZdHRrbHZobjQ1aC12c1IzYnplQ3E3TzdmT3g4dmZ0SVJOQ2FYWmlrWFA5a3ZlNHFxVWR4X3dpOHB3VVZ2OWo4OUhwWlFFUjhydzZBdFJjalVzakJ2aXEtQi1UYzlYSGl1NXVz0gF3QVVfeXFMT3lLLUc4al94aFJSTFkzZkxkYXpyWkhSSVVQTzNHQzVsYWVGWTkyMXJnUnp6aW9mZ1lTamZyY1hHY2FPV2VNbEFzRW52cjIwTWZtWl9Tc1hxQ2NfZVZUOWZvYl9jYUIzdF96dlFmMkZsdXJXTWJPc1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9CQ0RRbHZIdUxRdnN1c2FSYU03cXRCRkdsbXR4MUxPSFBuS2dLRXdxbFNoNjAxM0ZYTHA0STMweWcyT0tTWTE5WXlJSlc5V3pfUkxQaW40NXBYTW5YeGUwdFBtUHFjT0trc1F4N3ZITVVhUTU2emtn0gF3QVVfeXFMTkdpU3JFZHYySUt1blVCN0RnQVVnSm5hVXM4SnJoVzhQMXJ3WXJVRUdFMkx3cUxIQmRHdDNiUzJVbkZEUVlndkZPSDZpdDIyR2dMd2JvSllvcG5MWDd2YWtRVUQyN3Nzc042a0RxMnkxTkVfR3doTXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6337,22 +6337,22 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>"잠 안 자고 보채서"‥생후 2개월 딸 살해 혐의 40대 아버지 구속</t>
+          <t>“생사 갈리는 초응급 순간에 압수수색”…의협, 경찰 소아응급센터 압수수색 규탄 [현장영상]</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>"잠 안 자고 보채서"‥생후 2개월 딸 살해 혐의 40대 아버지 구속.</t>
+          <t>“생사 갈리는 초응급 순간에 압수수색”의협, 경찰 소아응급센터 압수수색 규탄.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5iWkQ5c2FrTGFCb2lSbXcyRWx1S2ZKOHhTSS0ycmR4UmxtSTBSM25sRDVlNmxEMkZoUTBjT3RPb3I1YzFFcEprVnA3QUduVXdrNS1yaW0tSGk2RnBNRVVyck5GYS13TVhSXzdHNl8wdVRtMC12RHgw0gF3QVVfeXFMUDlmazFvQy1qVm82X05UODMycEhqS0sxdkljVlFmWDRac2x3N3lVX21oMF9SQVFLYXA0Yllwd21SdG01RTlibEthdV90UEJXS3FVMk12QkdzSHRIN1pDa3YtNHRObjczVmNkNmczUmU3cHo5QXhZTkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFB5NHV3RnhoVVo3alpXTG43dk1kZnJSYlJRaVIzaXNiMVFiVmNZX1p0RjI5X1VNNjA2ZXFzcXNsWU4zQVE0R0xGcXR1STZOLUVrUmV3VTJEbTVOc0U?oc=5</t>
         </is>
       </c>
     </row>
@@ -6374,22 +6374,22 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>’1억 원 공천 헌금’ 강선우, 1심 징역 2년 6개월…법정구속</t>
+          <t>농지 전수조사, 불안 넘어 농지제도 개선 출발점으로 - 오피니언 | 뉴스</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>’1억 원 공천 헌금’ 강선우, 1심 징역 2년 6개월법정구속.</t>
+          <t>농지 전수조사, 불안 넘어 농지제도 개선 출발점으로 - 오피니언 | 뉴스.</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>정책브리핑</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5mN3hjRWd2SzhfYjBDSk9vX2pGZzhMekd0MTF2R3dQMnU5cWs4dHFMSDBjcXVyYVNtblBfbTduU2FXTVZPaTRtUkdDZVJnM0NvOHlDal9La0VIb19yWDN6RnRxZWNlekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5XN0w3alRBSHFIUDZLSWtjWGVhemE1UC1iaXpYcHhkWWhKNkZpdWhQTkRpRWdQbkI1MmRBeUE4OG9ORFlEVlVwNF9na0tzc1lyeXdOWHRXRzJmdExrMVNENk4xS0FHWFdxNEdGdjRHZ1lzWlRo?oc=5</t>
         </is>
       </c>
     </row>
@@ -6406,27 +6406,27 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>'송파 장모 살해' 유족 울음바다…"고인 딸도 결혼생활 중 상습 폭행당해"</t>
+          <t>누리호 탄 초소형군집위성, 발사 14시간 만에 첫 사진 전송</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>'송파 장모 살해' 유족 울음바다"고인 딸도 결혼생활 중 상습 폭행당해". 아울러 장모 살해범, 이미 ‘수차례 전과’상습범의 계획범죄 정황.</t>
+          <t>누리호 탄 초소형군집위성, 발사 14시간 만에 첫 사진 전송.</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1hUkhrQkxRQTZKTTRveTM1ZXF2eS1rSm5PSXp1ZU5oV3AzMS1jUW8xNlAxRTNIdDdsSnJuZE1DcmZJVE9ZcmxCOGl0RjgtbEpBMWphMDhPNC03V0tNZWYtejd5VUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9jVVFCVUJIUzVxR0o0NXJfOV84VEgtczR4bmRQSEpmU0xONWtTMUZCTEFCNUJwbEYzd1hXZmdYMUltYjhFcUZobHdjekxCZS0wbnFuU044VnozNkxvMjA3ZDZSQ20yWmRFbU03WEN0UGpHWmtD0gF0QVVfeXFMTjFCVVlTMzVKT1lpYTFLMkMtMm5hSE9IcUI3Y25nOWFZdGdXUTNMLUtjejdkMHlDYWk2RExWZ3c2azRVMzhTRjU0NmNKalFmSi1KS0VqbXg5bmk3ZGpjZ0pvTWhoV2ttQ3hRdkhxYzdtQVJ3SWo?oc=5</t>
         </is>
       </c>
     </row>
@@ -6443,27 +6443,27 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>경찰, 나주 부부 강도살인 혐의 피의자 53세 박용수 신상 공개</t>
+          <t>전주서 아내 살해 70대 체포…과거에도 가정폭력</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>경찰, 나주 부부 강도살인 혐의 피의자 53세 박용수 신상 공개.</t>
+          <t>전주서 아내 살해 70대 체포과거에도 가정폭력.</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPMlFGcnlCQUNZckpacHZkSTRlY1JlV051bnlTRkJSXy16NHp1d19RbklDY21vUXE3ZjR2X29vTGg5ZWtySEZHaGlqeUxOMS14U2ZRa2ZRdTR0XzB0TVJPV2l0b2pkR3phbEhwN0Z5N0RCbW9RRzZNUXFQQnNCdkh0Ym9NTnQ4cndwMHhOSGNFdVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5vWFhJcHNLZmZnZFpIQkZDYVF6VWs5TGM3M2s1Z0NPM2c3MlBRN3QySkJucGdzRTVfTFA0eUg1RmwwYjVHRklGY3BnaV9wX3NnbHhrc2JsQjlQbE0?oc=5</t>
         </is>
       </c>
     </row>
@@ -6480,27 +6480,27 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>현대ENG, 베트남 기후변화 대응 지원…3년 사업 마무리</t>
+          <t>[단독] 애국지사 유묵이라던 친일파 글씨… 유홍준 관장의 개인 소장품이었다</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>현대엔지니어링은 베트남 타인호아성에서 3년간 추진한 기후변화 대응 지원사업을 마무리하고 교육·환경 인프라를 현.</t>
+          <t>애국지사 유묵이라던 친일파 글씨 유홍준 관장의 개인 소장품이었다.</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015033500003</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQeDh5QXV2S0p3aGgxdnE5RjQzMDdfQ25rMHdsNGRjNEVoa3NiNnhuQllhT09QR1VoYjktdV82enpfTmltaDNPZV91ZmVhVWhjLTFBQ0JWWVY0XzU3b0NwOWd6RGRTOE80VVAzTmRWQlNwZHRlNzUtRkZoS3RfLVRleHNGMUlJVEJFa25BbEFkbFlRUE9G?oc=5</t>
         </is>
       </c>
     </row>
@@ -6517,27 +6517,27 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>서산시의원 내년 의정비 4천603만2천원…올해보다 2.1%↑</t>
+          <t>"딸 위험" 엄마 경고 무시한 경찰… 아빠·4세 아이 결국 숨진채 발견</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>충남 서산시는 내년 시의원 의정비가 올해보다 2.1% 인상된다고 15일 밝혔다.</t>
+          <t>"딸 위험" 엄마 경고 무시한 경찰 아빠·4세 아이 결국 숨진채 발견. 아울러 제주 4세 여아 사망경찰 대응 적절했나.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015034700063</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQT3NKSkNwN0NSTmMxT1NLUEp5T1AxX2FqWVExdk9lTXp2LWxidUdWNWNEeGtlQ2JacllWYldROUY5QnBpbU9hY1U1X1ZSTWN0UkRxZnhfUXd0b0JtOHJRWkpvTF9FT0VCN1JHUEJNWmJFeEh0TjFtcFpQZjV6dDg3dmVaenltQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6554,27 +6554,27 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>충남 지역 측량업체 327곳 일제 점검…등록 기준 위반 단속</t>
+          <t>국회, 오늘 서울시·서울경찰청 대상 국감 진행</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>충남도는 측량업체의 불법·부실 운영을 막기 위해 올해 말까지 도내 측량업체 327곳을 일제 점검한다고 15일.</t>
+          <t>국회, 오늘 서울시·서울경찰청 대상 국감 진행. 아울러 파기될 뻔한 한강버스 수사의뢰서, '브로커와 뇌물 의혹' 담겼다.</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015034000063</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9pUkx0ekhycVJ0RnFjMzU3Z2F6OWdjbzZBaVRVWklXX2FvS25TbjlJM2NRMEdpbEt6UDlKM1RtM1EwZ2R0UEdMOExLUTJlbGpyYlpmLXYzanNPdDQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6591,27 +6591,27 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>아침엔 쌀쌀, 낮엔 20도 이상…일교차 15도 안팎</t>
+          <t>나주 부부 살해범은 52세 박용수…빼앗은 1100만원 도박 탕진</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>15일 아침에는 찬 공기와 복사냉각의 영향으로 대부분 지역이 쌀쌀했으나 낮에는 기온이 20도 안팎까지 오르겠다.</t>
+          <t>나주 부부 살해범은 52세 박용수빼앗은 1100만원 도박 탕진.</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015027800530</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE93Q1ItcmxJRTFXeV9wNk5ibDc2ZmV2X0JCUmxKOV9BNS1VMjQ4UDU3aTUxZGIza19TYzVLRXJHN2o4NDItWm93WEd4bGVzNnY0LWdJS1NnaHZ5M0xYYjMxcS1FWVlsUGpRdm13NWNIbUxXMndZcUHSAWZBVV95cUxPcFMzWC1kMGQ1UWxkSUtQS1FoakFoMFR3c09mRzlLdGlzNWRzOVZZZnRnWmJScnVBYUx1c3RjZTU3aTFzZks4SUNCOTc1bm9pUlQyTXVrNTJzTGcteFFWWVRvT2RqNlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6633,22 +6633,22 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>한화 건설부문, 음성신고·AI 분석으로 안전신문고 개선</t>
+          <t>‘딸 경찰 수사 무마 의혹’ 한동훈, 국수본·중수청 양쪽에 고발됐다</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>한화 건설부문은 건설 현장 근로자의 안전 신고 편의성을 높이기 위해 기존 '안전신문고'에 음성인식과 인공지능(.</t>
+          <t>‘딸 경찰 수사 무마 의혹’ 한동훈, 국수본·중수청 양쪽에 고발됐다.</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015030800003</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9WRVY5ajZFeHZ0OFMxRlp4RjdpMzJZS21oT3p5MTVick1hX1ZmVURTNXN1b0h0SGdlR1h0RG1USmF6WWh6TDNzMHpIMTc5MDQ0VkVTeWE1U0x0UdIBX0FVX3lxTE9vb3A3SUhkZks1OWVUX2hVdTNQNmxBS1JVaFl1UmVwbWJBZFU4OUxRQmJhcnBmRmVlSXRWYmF6bzlxaWtsdm5lbi0tZ1FMeE9HQVNid1hDNjY0a1hnVHVJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6665,17 +6665,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>울산시, 무장애 관광 교통수단 확충…KTX 역에 안내센터 조성</t>
+          <t>전남광주 5개 자치구, 조정교부금 교부율 27％로 상향 재건의</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>울산시는 장애인과 고령자 등 관광 취약계층의 여행 편의를 높이기 위해 연말까지 무장애 관광 교통수단과 안내시설.</t>
+          <t>)= 전남광주 5개 자치구가 민형배 전남광주통합특별시장에게 시·군과 동일한 수준의 재원 조정교부금 교부율을 재차.</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014181200057</t>
+          <t>https://www.yna.co.kr/view/AKR20261015098800054</t>
         </is>
       </c>
     </row>
@@ -6707,12 +6707,12 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>울산 야음동서 흐린 수돗물 잇단 민원…시, 원인 조사</t>
+          <t>고흥 밭에서 불…1시간여만에 인명피해 없이 진화</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>울산 남구 야음동 일대에서 흐린 수돗물이 나온다는 민원이 잇따르자 울산시가 긴급조치하고 원인 조사에 나섰다.</t>
+          <t>)= 15일 오전 10시 36분께 전남광주 고흥군 덕흥리 한 밭에서 불이 났다.</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014181100057</t>
+          <t>https://www.yna.co.kr/view/AKR20261015096900054</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>부산서 모텔·단독주택 화재로 2명 숨져</t>
+          <t>경남 장애학생 1천800명 '한자리에'…교육감기 체육대회 개최</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>지난밤 부산의 모텔과 단독주택에서 잇달아 화재가 발생해 2명이 숨졌다.</t>
+          <t>)= 경남도교육청은 15일 창원시와 함안군 일대에서 '제11회 경남도교육감기 장애학생체육대회'를 개최했다.</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015031900051</t>
+          <t>https://www.yna.co.kr/view/AKR20261015095900052</t>
         </is>
       </c>
     </row>
@@ -6776,17 +6776,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>해인사, 800년 만에 팔만대장경 다시 새긴다…29일 판각 고불식</t>
+          <t>인천 서해에 풍랑주의보…백령도·대청도에 강풍주의보 유지</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>법보종찰 해인사는 오는 29일 오후 2시 경남 합천군 해인사 법계탑 마당에서 국보이자 세계기록유산인 팔만대장경.</t>
+          <t>) 기상청은 15일 오후 3시를 기해 서해 중부 바깥 먼바다, 서해 중부 안쪽 먼바다에 풍랑주의보를 발효한다고 밝혔다.</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014104100052</t>
+          <t>https://www.yna.co.kr/view/AKR20261015096000527</t>
         </is>
       </c>
     </row>
@@ -6818,12 +6818,12 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>올 상반기 중대재해사업장 37곳…경영책임자 1명 징역 3년 확정</t>
+          <t>중소기업 청년 "임금격차 줄이는 것 넘어 청약·주거지원 필요"</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>중대재해처벌법 위반으로 올해 상반기 경영책임자의 형이 확정된 사업장 37곳이 공개됐다.</t>
+          <t>)= 경제사회노동위원회 내 청년일자리희망위원회는 충남 천안 풍세일반산업단지에 있는 중소기업 ㈜아라에서 청년들의 일자.</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014135100530</t>
+          <t>https://www.yna.co.kr/view/AKR20261015086100530</t>
         </is>
       </c>
     </row>
@@ -6850,17 +6850,17 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>울산시, 납 배출사업장 9곳 특별점검…무단배출 등 확인</t>
+          <t>경남교육청, 학부모 대상 학폭 예방 토크 콘서트…해결책 모색</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>최근 울산지역 산업 현장에서 납 노출에 따른 노동자 건강과 환경오염 우려가 제기되자 지자체가 납 배출사업장 특.</t>
+          <t>)= 경남도교육청은 15일 김해 남명아트홀에서 도내 학부모와 예비 학부모를 대상으로 '2026년 학교폭력.</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014181000057</t>
+          <t>https://www.yna.co.kr/view/AKR20261015094900052</t>
         </is>
       </c>
     </row>
@@ -6887,17 +6887,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>[내일날씨] 일교차 큰 날씨 이어져…새벽 수도권·강원 빗방울</t>
+          <t>제2경인고속도로 문학IC 인근서 화물차 2대 추돌…1명 부상</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>일교차 큰 날씨 이어져…새벽 수도권·강원 빗방울과 관련하여 주요 정책 및 시장 이해관계자들의 입장과 향후 파급 효과를 전했습니다.</t>
+          <t>)= 15일 오전 11시 37분께 인천시 미추홀구 제2경인고속도로 안양 방면 문학IC 인근에서 70대 남성 A씨가.</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015008700004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015094000065</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>관악구, 소상공인의 날 맞아 '소상공인·전통시장 한마당'</t>
+          <t>'무기징역 받고 가석방' 10년간 151명…재범 관리는 '깜깜'</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>서울 관악구 는 제11회 소상공인의 날 을 앞두고 오는 28∼30일 구청 광장에서.</t>
+          <t>)= 최근 10년간 무기징역을 선고받은 수형자 150여명이 가석방을 받은 것으로 집계됐다.</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015031300004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015067700004</t>
         </is>
       </c>
     </row>
@@ -6966,12 +6966,12 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>자전거로 횡단보도 건너던 60대 시외버스에 치여 숨져</t>
+          <t>추미애 '소방 재정 빨대' 발언에 양대 노총 소방노조 반발</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>자전거를 타고 횡단보도를 건너던 60대가 신호를 위반한 시외버스에 치여 숨졌다.</t>
+          <t>)= 추미애 경기도지사의 이른바 '소방 재정 빨대' 발언을 두고 양대 노총 소속 소방공무원 노동조합이 일제히 반발하.</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015030900065</t>
+          <t>https://www.yna.co.kr/view/AKR20261015092400061</t>
         </is>
       </c>
     </row>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>굽네 운영사 지앤푸드, 연세대 의대 신축에 1억원 기부</t>
+          <t>진성준 국방위원장 "광주 군공항 이전·전력 배치 차질 없어야"</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>치킨 프랜차이즈 브랜드 굽네를 운영하는 지앤푸드는 연세대학교 의과대학 신축과 증설을 위해 1억원을 기부했다고.</t>
+          <t>)= 더불어민주당 진성준 국회 국방위원회 위원장은 15일 "광주 군공항 이전과 전력의 임시 배치 과정에서 국가.</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015029700030</t>
+          <t>https://www.yna.co.kr/view/AKR20261015090200054</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -7040,22 +7040,22 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>CPI 상회·채권 부실, 미 증시↓</t>
+          <t>충북참여연대 "청주 가정용 하수도 요금 비싸…20％ 인하해야"</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>CPI 상회·채권 부실, 미 증시↓. 아울러 美 물가 충격에 3대 지수 하락나스닥 1.9%↓.</t>
+          <t>)= 충북참여자치시민연대는 15일 "인구 50만명 이상 대도시 가운데 청주시 동 지역의 가정용 하수도 요금이 가장.</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>KB Think</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ieFlTZm1yRUJva3E2LWZ0bGswYW9Sdk9lS1ctU3Q5VEdKWm4zdDMyaVdHME5FOFl2Qnh5U25DWFFTMi1kVHZRcjk2U0cxY3o0cWJMRGRyRi1zeW8zc0pQQVNwRkhsWWV1NlZpUQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015091400064</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -7077,22 +7077,22 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>[현승윤 칼럼] 서울 집값 87주 상승이 우리 사회에 던진 함의</t>
+          <t>제주항공 참사 핵심 증거 로컬라이저 둔덕 재수색 착수</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>서울 집값 87주 상승이 우리 사회에 던진 함의. 아울러 거래 식었는데 집값은 끓었다"이게 아닌데" 10·15 대책 1년 성적표 - 머니투데이.</t>
+          <t>)= 12·29 제주항공 여객기 참사 희생자 유해를 찾기 위한 무안국제공항 방위각 시설 둔덕 추가 수색.</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE8ydFNrLVZuZkZRM09ER2tzNDVEWElzLVlSOXVFSmRHUEU4Rmh4bjM1elJlUDdFT1VTWkN0WEhETDgtaUtNUE5BRmZDZWMtMGRJSFRSTTJRQVVJdw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015085100054</t>
         </is>
       </c>
     </row>
@@ -7104,32 +7104,32 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>인도서 21조 투자하는 현대차그룹…국내 부품사 기회도 커질 듯</t>
+          <t>말다툼하다 14세 딸 둔기로 때려 살해한 친부 징역 22년 확정</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>인도서 21조 투자하는 현대차그룹국내 부품사 기회도 커질 듯. 아울러 정의선의 승부수 “인도에 155억달러 투자”.</t>
+          <t>)= 말다툼 끝에 10대 친딸을 둔기로 때려 숨지게 한 40대 친부에게 징역 22년형이 확정됐다.</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>한국무역협회-KITA.NET</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQSkphc2tGODM1ZlVlVjY2QTYwd0RHOTBiQllrOEhYR0tyVnFRRUVXYS1nWE1yejNCaW5kY2tZWXZjRHRZalRCVnd0d3kybl83SkpuQWhvQWJzeFNEQ3F6Uks1UmFwMmtySTdqLWxudVZSOGJCNXROSUc0Q3Y3MGVoU3ZMWk1ZMEwySWNZYUlKNTJLUmw3M3U2N0kxa1V6SU5ONjJqM3pjdjBPc2JxMmVjNi1vNXh5SkQ5aVpLTVlUclNZUmVTOGJtMURyc0JYeVdtekpOYUhB?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014118400004</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -7151,22 +7151,22 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>6천 뚫린 코스피에 사모펀드 셈법 갈렸다…'현금 확보'vs'반도체 줍자'</t>
+          <t>2027학년도 대입 수시모집에 1인당 4.96회 지원…작년보다↑</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>6천 뚫린 코스피에 사모펀드 셈법 갈렸다'현금 확보'vs'반도체 줍자'. 아울러 코스피 ‘죽음의 십자가’ 오나美 금리·유가 변수가 갈림길.</t>
+          <t>)= 전국 4년제 대학 협의체인 한국대학교육협의회 는 2027학년도 대입 수시모집에서 1인당 평균 4.96회.</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE15NVRxdTdqdURiMFAxVy1FZnNaeW9uZTBreWpzSEk1WHZmaFdRalVxalFRRFhLVUdKYVJSdjZSaHp2NG9OOUdNS1UyYkZ5cC1oSHZ5cUlXbG8wM0xjZ1F6aEFzSnFnanhWM0h5TjdMRm4?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015052100530</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -7188,22 +7188,22 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>셀타스퀘어 "약물감시 '중증도'까지 반영…시뮬레이션서 위양성률 65% 감소"</t>
+          <t>ESS는 공작물? 건축물?…정부, 분류 기준 마련</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>셀타스퀘어 "약물감시 '중증도'까지 반영시뮬레이션서 위양성률 65% 감소". 아울러 4천조 굴리는 월가 큰손 진단AI 신약 혁명, 한국 바이오에 판 깔렸다 By EBN.</t>
+          <t>)= 에너지저장장치 를 건축법상 '공작물'로 볼지, '건축물'로 볼지 구분하는 기준이 마련됐다.</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>약업신문</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9oSGtmZi1XdUdtREZCZGVoeURDNXBOVDFtNnh4T0c1VGdhbE9qbXhkd09taGdUQXJfQnZMUXhoV1Z3dzROM2wzd0NpVWJqOXJob2NNUDZEeFBlVEpodVpGQ3NEYVNjV2k4eDFyM1drTE9xVmM1b2c?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015046400530</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -7225,22 +7225,22 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>국산 비만약 '에페' 첫 달 13만원 전망…마운자로 반값</t>
+          <t>어린이집-유치원 입소·입학 신청, 더 쉽고 편해진다</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>국산 비만약 '에페' 첫 달 13만원 전망마운자로 반값. 아울러 한미약품, 3분기 실적 눈높이 낮췄지만“신약·비만약에 주목”.</t>
+          <t>)= 교육부는 11월 2일부터 시작하는 2027학년도 신학기 어린이집·유치원 입소·입학 신청을 앞두고 관련 서비스를.</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBIYmtqdEJRQmRJZTV3emxKZGpjdEZsLXFyeEtkTW5XRnFOVU5rZlduVFRLVXQzclRuTmJraHpKaWZ0X3FyaXItdnNVS3VpaUZwZERwb2xnMk81NTDSAWBBVV95cUxQLWRFdmZLX0x6X2EwMnN3U09KYU5KVDBxZzJJUGhRT3dSX2FDeUFvb3ZZODdLN1FWbzl6RzRFeDE1YWFLOTdyQ2xvOF9fbG1SWi0yZDV2QkFBdzNuTXpnSUQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015055000530</t>
         </is>
       </c>
     </row>
@@ -7252,32 +7252,32 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>국채선물, 미국 CPI발 요동 속 혼조…10년물 5틱↑</t>
+          <t>서울교육청 '서논술형 평가 AI' 세종·충남·경북서도 쓴다</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>국채선물, 미국 CPI발 요동 속 혼조10년물 5틱↑. 아울러 26년 11~12월 국채발행 추가 축소 여부 및 규모는 정해지지 않았습니다.</t>
+          <t>)= 서울시교육청은 세종·충남·경북교육청과 인공지능 서·논술형 평가지원시스템인 '채움AI' 공동 운영을 위한.</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBEZ0lxRXZRUjBXTDNfQVN0UWc0TmFDTVZ0YVRXenhTcTRLWTVQNHhyelItRmVBc3lKQlE0cjFOX2JOUS15Zk55aWk0T241b29DQ3o0aXdVQjVYVHJWNFFqUS1ibktVWUlfLXdzT0VlTGk?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015059300530</t>
         </is>
       </c>
     </row>
@@ -7294,27 +7294,27 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>영업점에서 만든 증권계좌는 수수료 10배?…금감원, '개선' 조치</t>
+          <t>코스피 5% 급락 출발…이틀 만에 매도 사이드카 발동</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>영업점에서 만든 증권계좌는 수수료 10배?금감원, '개선' 조치.</t>
+          <t>코스피 5% 급락 출발이틀 만에 매도 사이드카 발동.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBsNFVCcXdzQkU2N2trS2lGbmZtemI4dmdVc2dmNFk1YlRBdEJUWUU2VExUWVZnd3NkOWZtbkRDZzdQdHRSR2VOMnRXNkI2bFBUaWoyRzRsbmluTlNibGJjS2F3aWFYUGxZSUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE14QVhoUnU2Ul9lbHdYVFItV0NBMUdoZmpQZTc1eVQybUFNT3F5S24zbmFfZm84ODRuWk9Ta3pYcDNkd193dDVqVmhnRXBndTgyRzQ5Y29TaHctakxDaUVSaHNjbDIwTjg?oc=5</t>
         </is>
       </c>
     </row>
@@ -7336,22 +7336,22 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>‘차세대 D램’ 예고한 CXMT, 삼전·닉스와 기술격차 줄일까</t>
+          <t>中 CXMT 반도체 신기술, 왜 삼전닉스 주가 흔들었나</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>‘차세대 D램’ 예고한 CXMT, 삼전·닉스와 기술격차 줄일까.</t>
+          <t>中 CXMT 반도체 신기술, 왜 삼전닉스 주가 흔들었나.</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9pYnRtUDYwZzdZTklQMEUzamw2d0xlcW1URGFHaFJKSmZNbXRQQ09uaGVBQ2hxZm1HRGs0ZnAwRTNYSEFRMEplc3pLVE96ZGIzRVhnVlpGWHAwUnNQeWFzQ1MtU2VpMmFUOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQRjYxSEpUU1RQMVJzOWtfdnlPQzBoTnp1NWFkby1uOW1IcmljbFpNeUdaU3VmUV81NHFuRkdOanZHeXg3WE9IWXpuODJZOWNnTVRLUlZLRE1PV1djT2lqRkJLUTAtVHdkUzkwWDZvM25WOW9OandfbnlQTTBfbzVXTmVaZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7368,27 +7368,27 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>넷플릭스, 직원 1천명 감원…2022년 이후 최대 규모</t>
+          <t>미국 8개 주, 오픈AI에 동시 소송..."청소년 자해·폭력 부추겨"</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>넷플릭스, 직원 1천명 감원2022년 이후 최대 규모.</t>
+          <t>미국 8개 주, 오픈AI에 동시 소송"청소년 자해·폭력 부추겨".</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE85Y0JyeDl0MmFoN2VPR1RXWEhMeHVSY1VENXp4WHJQZjJjTVNTX253MkhfLW5KR3Izel8weGVuRVZpT0JSZXhIX1ZPMHNKQjZ2YWtOV2hZaTM3X2NmcW55R3dnSmhMSG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE93cXUwdnlqRXhWRWNZeUNPTHdSZEJNb01LR0hwNVA3TXpwRThjNUVBLVFKcmJ6bzN5YWgwTlBnaEFIX3c5aXpyTGxWVGZFb3I2NkVwTTdYNTBSeWhBSUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7405,27 +7405,27 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>[단독] 새마을금고, 해킹 이틀 지나도록 몰랐다‥이미 차단한 IP에 정보 유출</t>
+          <t>“스캔 폭격하고 안전장치 뚫는 AI 해킹툴”... 티오리, ‘아르텍스’ 분석 백서 발간</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>새마을금고, 해킹 이틀 지나도록 몰랐다‥이미 차단한 IP에 정보 유출. 아울러 산은캐피탈도 해킹 피해“848명 이름·주민번호·생년월일 유출”.</t>
+          <t>“스캔 폭격하고 안전장치 뚫는 AI 해킹툴” 티오리, ‘아르텍스’ 분석 백서 발간. 아울러 "금융사 침해사고 발생 총 16곳약 10만건 유출".</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>보안뉴스</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5rRHhITTlHR1c5MXZyTXBxOGVxSkxBUXNqbjBSVWNrY19nT1FWTEJEaUFVLTYwS1Q3VHhlZG0wM0M4V2ltM2t1elNnekNaY3hWcVlaeWJBYnBaMy1tMERlOF84NXFrMU9MQUViRm5NR0tMQ0Z40gF0QVVfeXFMT2ZqVXNISzU1NGY3c0NHZjBJTU9VQkdTQUFudGkzNUtzZ2h4TlN0eXBaMm9lQzZzd3QtMVBnZFR5UjhVWVZaQ2wwSGdZSlBWVlRLWFlXWE4wdW1kWnNXdXVJSmdGeGlody1aWlhoMF96UjlBOXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1sM3V1eUZiTXVaWm9sazNFMzBvTjJpLUpOYnJCaHZWNXpKQUNLVThCQXZJZUxnT0dnVWFkREVmODREaV9EZGRfRWJoOXdzU0k2NVFhVHh4eW84c3FqbWl6eGkxYTZ1azF1bG1V?oc=5</t>
         </is>
       </c>
     </row>
@@ -7447,22 +7447,22 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>[시니어 외면한 포용금융②] 사라지는 은행 점포, 소외되는 고령층</t>
+          <t>배달 라이더 201명 개인정보 노출 정황…대행업체 관리 부실</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>사라지는 은행 점포, 소외되는 고령층. 아울러 해외은행들은 주말 문 여는 곳 많은데"한국도 야간·주말 개장 검토해야".</t>
+          <t>배달 라이더 201명 개인정보 노출 정황대행업체 관리 부실.</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>이투데이</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5DckNSazhQbjdnMklKRmFWOVlzNzVnbVdkb0lvaWwtVFUzbXJaT2lvU19sVURhR2dZZnJHWjl2T2oxV1BJX0F2dWxGckFCQ29scjlYNGJsUS1SUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1vSlQ4bGRNZHdXS0NNQVZXOEpvNkpGcXA0WG11RTdCNm5BcmVPMUtLYVZUNlRRTzRKSm9tbW1WbnpVSndTdUw2bkhYLW01aWQ4U2JoRnJEenZPYlNTN0JPSXB3eUUwQWs?oc=5</t>
         </is>
       </c>
     </row>
@@ -7479,27 +7479,27 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>'AI 해킹'에 털린 금융권…16개사 뚫리고 개인정보 10만 건 유출</t>
+          <t>"빚내서 SK하닉 샀는데"…두 달 만에 '600억' 결국 멘붕</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>'AI 해킹'에 털린 금융권16개사 뚫리고 개인정보 10만 건 유출.</t>
+          <t>"빚내서 SK하닉 샀는데"두 달 만에 '600억' 결국 멘붕. 아울러 "비명조차 안 나온다"다시 찾아온 급락장에 개미들 '망연자실'.</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>KBC광주방송</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE8xWVlidzdDbDBudzJZODBGU0FhMC1mTFc4Y19HTXZ6VUF6aFFwZFdhOGZUajBxTm5ENVpyWDU3cWh3WUphMjhmcEVfN1U0SmdRTVk5N2dKT2M0Y0FTRlZiWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9WUjFtM2lFNUJyTTlvZWtZMGZfV2F5Q1ZrRnBmbjVzVno2azhiYUgzVXo1WVhQTDdQNFVnYnBYMzBfMmtLWG1HRXJTRkJxdkpIZk5CeG5yVmdadw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7516,27 +7516,27 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>[속보] 코스피, 장중 4%대 급락…매도 사이드카 발동</t>
+          <t>이헌욱 부동산원장 “외국인 주택 소유 현황 등 신규 통계 만들 것” - 조선비즈</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>코스피, 장중 4%대 급락…매도 사이드카 발동과 관련하여 주요 정책 및 시장 이해관계자들의 입장과 향후 파급 효과를 전했습니다.</t>
+          <t>이헌욱 부동산원장 “외국인 주택 소유 현황 등 신규 통계 만들 것” - 조선비즈. 아울러 국토부 "주간 아파트값 통계, 전문가는 조정·국민은 공표 원해".</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015035900008</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOUlB6Z29IWUtaSDlmaDVPbS1OSklpM1RLYXROSC1xT3J1Z1pKU2tBMExkZXdLZmZ6ZENzd1ZUWXVPRzE3THl4bFM4dExjT25hNWpiVzdEdGlWRXNHUl9iY19xSlhsN1JiVGJrbU9jTUVhZG8wX1NkcWI0R2J0ZFMxakVrRXUzaVVTU0RVMzIwSnZPeVpuVVIyctIBrAFBVV95cUxNTmRhRURFbDhpaFFBTHFxdkllcGlxQkVTTGFPS2c0cXNVLUx4TlFqcE5uMTg1NHlVZ19pLU5TUWlZS0dzQ1Fac0JMcnFuRTROM0YzMlpUX3Y1X2tFeUtiNXRFODlKcE9ibHdEdjNka09nbkFsOTZWRFBHbTZ3MmFQQ1czczV1WkM3LUtoYzZhb0JxeGlNbHktcFRxTEk0dXp1dkM2czczZXBZT3Y4?oc=5</t>
         </is>
       </c>
     </row>
@@ -7553,27 +7553,27 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>건설연구원, 전국 730만동 건물 행정자료 연계 '데이터넷' 구축</t>
+          <t>국산 비만약 에페 가격 책정 완료…양강 구도 깰까</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>한국건설기술연구원 은 전국 730만 동 건물의 상권, 업종인허가 등 행정정보를 연계한 체계인 '데이터넷.</t>
+          <t>국산 비만약 에페 가격 책정 완료양강 구도 깰까.</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015031000003</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1YTU12QUExOFUtNV9hVzRPNmlmR2t5aGxYQ2ROdF9mVFlNRHF5dkk5ZTliMzhIMl9mcFduQzNsQUs2d0ZmZ3U0VDRJazdTRzRLLTc5a1RsNXV4NkdhTTZLaXlyRFhnckVhR25faFFqdmY?oc=5</t>
         </is>
       </c>
     </row>
@@ -7590,27 +7590,27 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>'반도체 투톱' 급락에 코스피, 장 초반 5% 내려 5,600대</t>
+          <t>위험회피 분위기 속 커브 플래트닝…국고 10년 4.2%선 하회(종합)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>인공지능 투자 수익성 논란이 다시 부각된 가운데 코스피가 15일 장 초반 반도체 대형주 중심으로 급락.</t>
+          <t>위험회피 분위기 속 커브 플래트닝국고 10년 4.2%선 하회. 아울러 '26년 11~12월 국채발행 추가 축소 여부 및 규모는 정해지지 않았습니다.</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015034500008</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsNkItM3N0ejNnMkdISzd3MjlVUHFxSklWRmJHUU5PRDVsaWVLTUJ5UG94VWJybzJ2ZlZLWnFWYXRHdjkzUGxHalEtdkxESXllLVo1U3hpLUJkNEpDa0MyZ2RRUXdwRnRwR0VXVl9UWTY?oc=5</t>
         </is>
       </c>
     </row>
@@ -7632,22 +7632,22 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>[속보] 코스피, 5.6% 급락한 5,673개장…코스닥도 4.8% 내려</t>
+          <t>현대차, 인도 푸네 신공장 준공…연 17만대 생산체제 구축</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>코스피, 5.6% 급락한 5,673개장…코스닥도 4.8% 내려과 관련하여 주요 정책 및 시장 이해관계자들의 입장과 향후 파급 효과를 전했습니다.</t>
+          <t>현대차, 인도 푸네 신공장 준공연 17만대 생산체제 구축.</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>전기신문</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015032400008</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1fNzluUml6dWtNTXRxRzZSMEJ5dFU3YWs3YmkxY2VZZHpfNkZPTW1FcUllWndwckxsc2VOa29qaFYyb0dfSFkxcC1EQ3F3SXZDY09abjFMeExTckU1LXlKZGlwTHplbXlTSUh4TtIBcEFVX3lxTFBLVXI2R1JLUVVESHl1N1p0ZW9WZS1VSXBCWkE5ZVVaM08tZVJ2QnB1LU5fMkNNOHIzLTR4UUxwNGF6QTVhZlRNT2FfcC1aVU9kOERESEhsT0Vodl9xZ0F2VHZ2UldxbTFoU3ZMbkhNME0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7664,27 +7664,27 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>대신증권 "백화점 3사, 성장 둔화에도 이익 개선 전망"</t>
+          <t>"가전 넘어 주택으로"…삼성·LG '모듈러'에 꽂힌 이유</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>대신증권 은 15일 백화점 3사의 3분기 매출 성장세가 상반기보다.</t>
+          <t>"가전 넘어 주택으로"삼성·LG '모듈러'에 꽂힌 이유.</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015029900008</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5uM0Q5YU5TQ2Y3S2ZEZTUybGIza0JsSnNzY1R6OVRqRlVtaWdfMGZmclE4b0xLSklxODlyQnRUMjFLT0cycHNYTEh3QUFOellSSnVuMXp3ZE5wZGF6U2JnSXN5Y1JuYmRqNXROaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7706,22 +7706,22 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>삼양사, 日 식품소재 전시회 참가해 스페셜티 식품소재 소개</t>
+          <t>위메이드, 중국 자본 매각 일정 두 달 연기</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>삼양사 는 14∼16일 일본 도쿄에서 열리는 식품소재 전시회 '하이 재팬 2026'에 참가해 당류.</t>
+          <t>위메이드, 중국 자본 매각 일정 두 달 연기.</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015029600030</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOenJsMDB0a2tlLWJxVm9YaEpSUzlGWUZObEp6VmFPUHYxUXZqallkekthTk1TcHdYbXJCcDJYb29RS2hNY2dzeUxDdWNpOUVObWJrXzhmcndxanVTZ29Ed1VENXFINGxNTktpbWlXcE43bDZkZERxd05YaWxyNjVCcnVJWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7738,27 +7738,27 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>삼성웰스토리, 경북 중소기업 상품 활용 급식 메뉴 선봬</t>
+          <t>한국 콕 찍어 경고한 IMF..."AI 흔들리면 가장 민감"[와이파일]</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>삼성웰스토리는 경북경제진흥원과 협력해 경북 중소기업의 판로 확대를 지원하기 위해 전국 구내식당에서 지역 기업의.</t>
+          <t>한국 콕 찍어 경고한 IMF"AI 흔들리면 가장 민감". 아울러 한국 경제성장률, 3.3% 성장 전망.</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015027200030</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9zSV9UUjhKYnU4SmZpTmdPcUhLb2JvMkQ1ZmtxNnNXT05lNmJyTDduaktENllJVE9EM2VfdzJiQ0xDOWY1SllRNV82bFdPU0VzZ3RoMDNqVVIxcXJNWUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7780,22 +7780,22 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>무보·BNK경남은행, 동남권 수출기업에 78억원 우대금융 지원</t>
+          <t>K-제약 해외 규제 대응, 제약바이오협-코트라가 함께 돕는다</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>한국무역보험공사는 지난 14일 경남 창원 BNK경남은행 본점에서 BNK경남은행과 부산·울산·경남 지역 수출 중.</t>
+          <t>K-제약 해외 규제 대응, 제약바이오협-코트라가 함께 돕는다. 아울러 제바협·코트라, '해외 규제대응·글로벌 진출' 협약.</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>의협신문</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015024600003</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE91aTR0T1dDQjNqSnh5TmY4Mkg4MWIwOS1BbXUybjdwWnEwNTFfaVJIZFUxenBKQXVoNUlLVms5UWltdURSNmNPZG5WZmQ1QVc5c2s3QS1aUTVGU2x5MS1pSm84ZWV6QkNUd1BaY2YxOEw5Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7817,22 +7817,22 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>DS증권, CJ프레시웨이 목표가↓…"3분기 실적 기대치 하회전망"</t>
+          <t>SK그룹, 웨스팅하우스 지분투자 검토…대형 원전으로 확장</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>DS투자증권은 CJ프레시웨이 에 대한 목표주가를 5만원에서 4만원으로 하향 조정했다고 15일 밝혔.</t>
+          <t>SK그룹, 웨스팅하우스 지분투자 검토대형 원전으로 확장.</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015025800008</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5UMUlmRFR4ZjB4VXlubFlPTklsdkRfYWhtTW1WX3dZNnh3ZDFwX3oweHNneTRHV1VIVzBYeDgzMzZra2NhZG82YTdYNjJ6ei14a1B2b2ZtMTZKQlRON0d0NGZEWWMxSHM?oc=5</t>
         </is>
       </c>
     </row>
@@ -7849,27 +7849,27 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>신한증권 "현대건설, 원전 수주 불확실성"…목표주가 하향</t>
+          <t>코어위브發 회사채 쇼크… 'AI 버블 붕괴'인가 '차입 모델의 경고'인가</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>신한투자증권은 15일 현대건설 에 대해 "미국 금리 상승, 미 중간선거에 따른 원전 수주 불확실성.</t>
+          <t>코어위브發 회사채 쇼크 'AI 버블 붕괴'인가 '차입 모델의 경고'인가. 아울러 코스피 급락한 원인? 화제의 ‘가트너 보고서’ 살펴보니.</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015025400008</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGcmNtdWVyejJnTWhEUFNQSjFPUUVTOHZqVjZ1blhBaGctb1VJZEhGYUh4eHIxQWQ4V2NuY1JSOUIyZTZCV2NBam1EQmYyUzFkbEVWaktJVVkwQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7886,17 +7886,17 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>SK증권 "KT, 4분기 실적 반등 가능성…지금이 매수 적기"</t>
+          <t>日 메가뱅크 '환골탈태'…은행 사무직 수천명, AI개발직 전환</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>SK증권은 15일 KT 에 대해 4분기 실적 반등이 예상되는 가운데 주주환원, 인공지능데이터센터(.</t>
+          <t>)= 일본 3대 메가뱅크 중 하나인 미즈호 파이낸셜그룹이 영업직과 사무직 사원 수천 명을 인공지능.</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015025300008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015097500009</t>
         </is>
       </c>
     </row>
@@ -7923,17 +7923,17 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>“금융사 10곳 중 9곳이 서울, 왜 흩어놓나”…이언주, 금융기관 이전에 반기</t>
+          <t>현대차그룹 장재훈 "AI·스타트업 등 인도 신사업에 4조 투자"</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>금융 분야 이전에 반대입장 밝혀 “정보·자본·전문인력은 물론 기업과 투자자 긴밀 연결돼야”정부의 공공기관 지방 이전에 대해 여당내에서도 반대 목소리가 나왔다.</t>
+          <t>)= 장재훈 현대차그룹 부회장은 14일 그룹 차원에서 향후 7년간 인도 시장에 약 21조원을 투자.</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176375</t>
+          <t>https://www.yna.co.kr/view/AKR20261015003200003</t>
         </is>
       </c>
     </row>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>“집주인에 카톡 한줄 깜빡해 사달 났다”…전세보증보험도 ‘무쓸모’ 된다는데</t>
+          <t>코트라 "대일본 수출 2030년까지 350억달러로 확대"</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>2개월전 계약종료 통지안했으면 HUG 반환보험 거절 당할수있어 거절사유 54%가 ‘종료 미통지’전세보증금 반환보증보험에 가입했더라도 집주인에게 계약 종료 의사를 제대로 알리지 않으.</t>
+          <t>)= 대한무역투자진흥공사 가 수출품목 다변화, 판로 확대 등을 통해 2030년 대 일본 수출액 350억달.</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175691</t>
+          <t>https://www.yna.co.kr/view/AKR20261015087900003</t>
         </is>
       </c>
     </row>
@@ -7997,17 +7997,17 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>“부모·자식 다 내 책임, 쓰러질 수도 없네요”…60대 연체율 4년새 두배로</t>
+          <t>[속보] 코스닥 이어 코스피도 거래재개…서킷브레이커 해제</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>한은 2분기 가계부채 분석 연체율 0.7%서 1.5%로 급등 부실차주 20%가 60대 이상 소득 적어 금리인상 충격 커가구 제작회사를 운영하는 60대 초반 A씨는 거래처 부도로 매.</t>
+          <t>코스닥 이어 코스피도 거래재개…서킷브레이커 해제 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176319</t>
+          <t>https://www.yna.co.kr/view/AKR20261015095300008</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>건보료 아끼는 연금 포트폴리오 … 은퇴자가 알아야 할 3가지</t>
+          <t>코스피·코스닥 1단계 서킷브레이커 발동…8% 넘게 폭락(종합)</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>현실로 다가오는 건보료 폭탄61세 퇴직자 김 씨는 매달 통장을 보면 한숨만 나온다. 가뜩이나 소득이 줄어들어 불안한데, 매달 적지 않은 건강보험료가 통장에서 빠져나가고 있다.</t>
+          <t>)= 15일 국내 증시가 급락하는 가운데 코스피와 코스닥 지수가 8% 이상 폭락하며 연이은 서킷브레이커가 발동됐다.</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175663</t>
+          <t>https://www.yna.co.kr/view/AKR20261015093551008</t>
         </is>
       </c>
     </row>
@@ -8076,12 +8076,12 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>계란 공급에서 드러난 K관료들의 ‘포퓰리즘 담력’ [논설실 Pick]</t>
+          <t>[속보] 코스닥, 거래재개…20분간 매매중단 후 서킷브레이커 해제</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>국민 호주머니 펑펑 쓰는 정부 물가 관리 선의로 포장됐지만 가격 신호 망가뜨려“정부에 사하라 사막 관리를 맡기면, 5년 안에 모래가 부족해질 것이다.” 자유시장주의 경제학의 거목인.</t>
+          <t>코스닥, 거래재개…20분간 매매중단 후 서킷브레이커 해제 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176192</t>
+          <t>https://www.yna.co.kr/view/AKR20261015094300008</t>
         </is>
       </c>
     </row>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>[단독] “모르면 연 256만원씩 버리는 꼴”…온라인 주담대 갈아타기, 1800명만 했다</t>
+          <t>국토부 "주간 아파트값 통계, 전문가는 조정·국민은 공표 원해"</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>연256만원 이자절감 효과에도 가계대출 관리강화에 실적 ‘뚝’온라인 대출 갈아타기 서비스를 통해 주택담보대출을 옮긴 차주가 올해 들어 85% 넘게 급감했다.</t>
+          <t>)= 주간 아파트 가격 통계 개편을 놓고 전문가들은 통계의 한계를 이유로 조정이 필요하다는 의견.</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176052</t>
+          <t>https://www.yna.co.kr/view/AKR20261015091600003</t>
         </is>
       </c>
     </row>
@@ -8150,12 +8150,12 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>[단독] “국산차 왜 타냐?” 비웃던 테슬라 오너…2배 수리비에 말 없어졌다</t>
+          <t>[속보] 코스닥 이어 코스피도 1단계 서킷브레이커 발동</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>500만원 이상 고액 수리 비중 16.1% 8개월 고액 수리건수, 작년 전체 추월테슬라 전기차의 보험 수리비가 현대자동차·기아 전기차의 두 배 수준인 것으로 나타났다.</t>
+          <t>코스닥 이어 코스피도 1단계 서킷브레이커 발동 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176050</t>
+          <t>https://www.yna.co.kr/view/AKR20261015093900008</t>
         </is>
       </c>
     </row>
@@ -8182,17 +8182,17 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>이형일 부총리, G7·G20 재무장관회의 참석차 출국</t>
+          <t>코스닥 8%대 폭락에 서킷브레이커 발동…20분간 거래 중단</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>올해 두 번째 G7장관회의 초청 IMF 등 국제금융기구 수장 회동 글로벌 3대 신용평가사 총괄 면담이형일 부총리 겸 재정경제부 장관이 국제통화기금 ·세계은행 연차총회.</t>
+          <t>)= 15일 국내 증시가 급락하는 가운데 코스닥 지수가 8% 이상 폭락하며 서킷브레이커가 발동됐다.</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175586</t>
+          <t>https://www.yna.co.kr/view/AKR20261015093500008</t>
         </is>
       </c>
     </row>
@@ -8219,17 +8219,17 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>[단독] 삼성·SK, 美웨스팅하우스 지분확보 전격 참여</t>
+          <t>[속보] 코스닥 폭락에 서킷브레이커 발동…20분간 거래 중단</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>삼성·SK·현대차·두산그룹 등으로 구성된 '팀 코리아'가 미국 원전 설계기업 웨스팅하우스에 대해 최대 4조원 규모의 지분 투자를 검토하고 나섰다.</t>
+          <t>코스닥 폭락에 서킷브레이커 발동…20분간 거래 중단 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176030</t>
+          <t>https://www.yna.co.kr/view/AKR20261015093000008</t>
         </is>
       </c>
     </row>
@@ -8256,17 +8256,17 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>[단독] SK·삼성 ‘원전 동맹’…웨스팅하우스 4조지분 확보해 美진출</t>
+          <t>여당도 가상자산 과세 유예법안 첫 발의한다…"2029년부터 시행"</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>SK·삼성·현대·두산 등으로 구성된 ‘팀 코리아’가 미국 원전 설계기업 웨스팅하우스에 대해 최대 4조원 규모의 지분 투자를 검토하고 나섰다. 한국전력·한국수력원자력 등 정부 주도의.</t>
+          <t>)= 가상자산 과세를 2년 늦추는 법안이 여당에서도 처음으로 발의될 예정이다.</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/business/12176026</t>
+          <t>https://www.yna.co.kr/view/AKR20261015091500002</t>
         </is>
       </c>
     </row>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>[단독] 한전과 '팀코리아' 띄운 韓기업들 …"美원전이 새 먹거리"</t>
+          <t>한투증권, JCR 일본 신용평가서 신용등급 'A'로 상향</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>SK그룹과 삼성물산, 현대건설, 두산에너빌리티 등 국내 주요 대기업이 미국 원전 시장 진출을 위해 최대 4조원 규모의 투자 컨소시엄 구성을 추진한다.</t>
+          <t>)= 한국투자증권은 일본 신용평가사 JCR 이 당사의 외화 장기.</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176015</t>
+          <t>https://www.yna.co.kr/view/AKR20261015092100008</t>
         </is>
       </c>
     </row>
@@ -8335,12 +8335,12 @@
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>월가 멘토들 "AI는 이미 필수 도구… 새모델 나올 때마다 무조건 익혀야"</t>
+          <t>75개 농림축수산단체 "CPTPP 가입 반대 기본입장 변함없다"</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>미국 월가에서 활동하는 한인 금융인들이 금융권 진출을 준비하는 대학생들에게 인공지능 활용 능력과 인적 네트워크 구축의 중요성을 강조했다.</t>
+          <t>)= 농업·축산·수산·임업 분야 75개 단체는 15일 포괄적·점진적 환태평양경제동반자협정 가입에 대해.</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015089900030</t>
         </is>
       </c>
     </row>
@@ -8367,17 +8367,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>이자 갚기도 버거운 60대… 연체율 4년새 두배로 뛰어</t>
+          <t>소비자원 "편의점 김밥 나트륨 함량, 하루 기준치 최대 70%"</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>가구 제작회사를 운영하는 60대 초반 A씨는 거래처 부도로 매출이 급감하면서 최근 은행 대출과 카드 사용에 의존하게 됐다. 이 과정에서 빚이 2억원가량 불어났고 배우자의 월 200.</t>
+          <t>)= 편의점에서 판매하는 김밥 한 줄에 하루 나트륨 섭취 기준치의 최대 70%가 들어 있는 것으로 나타났다.</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175950</t>
+          <t>https://www.yna.co.kr/view/AKR20261014126200030</t>
         </is>
       </c>
     </row>
@@ -8404,17 +8404,17 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>IMF "올 韓부채비율 전망 54%→46%"</t>
+          <t>중기부, '모두의 창업' 1라운드 1만명…창업자금 200만원 지원</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>한국의 올해 경제성장률을 3.3%로 내다본 국제통화기금 이 올해 국내총생산 대비 일반정부부채 비율 전망치를 46.1%로 대폭 낮췄다.</t>
+          <t>)= 중소벤처기업부는 9만3천여명이 몰린 2차 '모두의 창업' 프로젝트에서 1라운드 진출자 1만명(일반·기술 8천명.</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175949</t>
+          <t>https://www.yna.co.kr/view/AKR20261014182900030</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>"K뷰티테크 육성하자" 250억 벤처펀드 조성</t>
+          <t>“잊고 있던 페이 잔액 255억원 돌려받으세요”…빅테크 3사, 정기 알림·환급 안내</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>재정경제부가 14일 경제관계장관회의 겸 서비스산업발전 태스크포스 에서 인공지능 을 접목한 K뷰티 산업을 육성하는 방안을 발표했다. 정부는 뷰티테크 스타트업과 대·중견기업.</t>
+          <t>빅테크 3개사 매년 1회 이상 이용자에게 잠든 잔액 통지네이버파이낸셜 등 빅테크 3개사가 오랜 기간 사용되지 않고 잠들어 있는 선불 잔액을 매년 주기적으로 알려주는 서비스를 실시한.</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12175948</t>
+          <t>https://www.mk.co.kr/news/economy/12176532</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -8483,22 +8483,22 @@
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>[포착] 폭탄도 미사일도 아니었다…우크라 ‘뱀파이어’, 러 무인기에 몸통박치기</t>
+          <t>오세훈 “전월세난 적극 대응…올해 주택 1만5천호 착공”</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>폭탄도 미사일도 아니었다우크라 ‘뱀파이어’, 러 무인기에 몸통박치기. 아울러 '소리는 들리는데 안 보인다'시속 600㎞ 러 제트드론에 키이우 자원봉사 방공대 고전.</t>
+          <t>오세훈 서울시장은 15일 서울의 주택 공급과 관련해 “올해 1만5000호가 실제 착공에 들어갔고, 모아주택‘도 지난 8월 첫 준공의 결실을 보았다”며 “그동안 꾸준히 다져온 공급.</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>나우뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBPcGZkemJqZTVjVnNSZHZTZElqQ2R5S3RYa0JzelNsQ2g0dWdXeWtFMV9lVEZOam9fS2VSaHY1RHJmbm1Gemc4emlBOTRFQUtDLXhTYW50TUV2OGR0eHNnbC1zeXpQSGQxNE43VGZZZDU?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176554</t>
         </is>
       </c>
     </row>
@@ -8510,32 +8510,32 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>후티 반군 "사우디 리야드 국제공항 탄도미사일로 공격…명중"</t>
+          <t>[단독]LH 토지 계약해제, 4년 만에 6.9배…11조 규모 토지는 미재공급</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>후티 반군 "사우디 리야드 국제공항 탄도미사일로 공격명중". 아울러 중동이 지핀 전쟁 불씨, ‘아프리카의 뿔’까지 옮겨붙었다.</t>
+          <t>계약해제 2021년 146필지 5년 뒤 1002필지 2026년 8월까지 계약해제 2689필지 달해 당초 계약금액 따지면 16조8000억원 규모 미재공급 토지 402만㎡해제 토지면.</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE51cVdoMDhhdDZEcUNhYUlQNFgtUEQ4ZS1xX1JEbGp4bW9ISUpnSlA2RzRyTlFndXZpTGxTdDN2bGV5My1pYXAxbW1qeDZyTWEyRWtFczNJS0FELUHSAWBBVV95cUxOb2FxcmI0bmdXNTd5TGE5Sy12bHllQmpNSjBvOTJzR2FHN0NvcXNQOTAySklMdkp0SGhwNkhHM09BZThpY3ZKOXVTMDhMblhMb3Y1LTdETTdaZzA0aDd2RlE?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176535</t>
         </is>
       </c>
     </row>
@@ -8547,32 +8547,32 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>이라크 총리 사우디 방문...왕세자와 중동전 현안 논의</t>
+          <t>NH농협은행, 美 천연가스 파이프라인 금융 참여…6천만 달러 대출 실행</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>이라크 총리 사우디 방문왕세자와 중동전 현안 논의.</t>
+          <t>미드스트림 인프라 시장 진출 본격화NH농협은행은 미국 텍사스주 퍼미안 분지에서 아과 둘세와 케이티 지역을 연결하는 천연가스 파이프라인 건설 사업에 참여해 총 6000만 달러(원화.</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFA0TVFvbW9YcUZyMGdKa2xhckZJNVRsNElFcFNHVmxCU1dKcC1rM2xNUkRpNG9pTEhhMkMwRFpYWVpUa3hUVW1QZFYxWnEwY3Nfd2c1QnNvaURjS2pBN0E?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176525</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -8594,22 +8594,22 @@
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>젤렌스키 “트럼프가 다른 편 선택하면 고통…솔직히 배신감 느껴”</t>
+          <t>2026년 3분기 중고차 판매량 TOP5는?</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>젤렌스키 “트럼프가 다른 편 선택하면 고통솔직히 배신감 느껴”. 아울러 美 정보공유 끊었나우크라 "공습 조기경보 이틀째 못받아".</t>
+          <t>KB차차차 상위 5개차종 모두 현기차 20대는 아반떼, 3040은 카니발KB캐피탈이 운영하는 중고차 거래 플랫폼 ‘KB차차차’에서 올해 3분기 가장 많이 판매된 중고차는 현대차.</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE13SnhKVnc4WldKUDA3ZWZOdWc0MWRRU1ZCaFdLOF9SN1ZpdHpuaXNzclFkRjlWN3hzaDh1SE93VVEtRU5OZHRnTlVKSGNCdWRaRmVmNmpJWWFYd9IBX0FVX3lxTFBFdDg3azhqTmdzOUFLakV3UGVsN3pnbi14X0VWeGItVmp5VkJYTGNST3JuRjdoR0NhcFpNaVUtV2c0SGZXQlYtOGlhdzJiV0dmZkhnMVBvMHd2QzZ0TF9R?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176523</t>
         </is>
       </c>
     </row>
@@ -8621,32 +8621,32 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>12년 만에 신압록강대교 개통…북중 전면적 협력으로 가나</t>
+          <t>“반도체에 큰절 한번씩 해야겠네”…올해 적자 43조 ‘8년 만에 최소’</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>12년 만에 신압록강대교 개통북중 전면적 협력으로 가나.</t>
+          <t>반도체발 법인세 예납으로 세수가 큰 폭으로 늘어나면서 올해 8월까지 나라살림 적자 규모가 8년 만에 가장 작은 것으로 나타났다. 총수입에서 총지출을 뺀 통합재정수지도 8년 만에.</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>노컷뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5Vam5uZ2QxaU5ZOHd0Qlc5UkNqcXZXcGhOdzAxYVVPcm1COVFOR3FEdXU0aFNiZHdqNTdFSllaM2ROUjlKNU5LTE5zN0NKLThDOHc?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176503</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -8668,22 +8668,22 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>호르무즈서 피격된 UAE 화물선 2척 침몰</t>
+          <t>현대차·LX인터 등 11곳 ‘2026년 아이 키우기 좋은 기업’ 수상</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>호르무즈서 피격된 UAE 화물선 2척 침몰. 아울러 이란 호르무즈해협 선박 공격 '최고조'11일 하루만 6척 피격.</t>
+          <t>한미연, ‘2026 아이 키우기 좋은 기업’ 발표 제도만 ‘갖춘 곳’ 아닌 ‘제대로 쓰는 곳’ 선정 “임직원 출산·양육 지원 넘어 지역상생까지” 4개부처 장관상27일 서울 은행회.</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFAydWRaVzJfTzRnZURRS01uTHAyR0lXS3pnamNTWVRPSWtqTDZsR2RjQU1BbEFybUk5REVqS0FYRlVUcmpXTFZ2X0dsMzZmRG5OeTg0UmJQRktVUFBTUGQ0eDdRbWttRUE?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176468</t>
         </is>
       </c>
     </row>
@@ -8695,32 +8695,32 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>레오 14세 교황, 폐암 수술 후 회복세… 교황청 “검사 수치 정상 범위” - 조선비즈</t>
+          <t>“곰팡이 벽지, 집주인? 세입자? 누가 도배하냐”…임대차분쟁 접수 급증</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>레오 14세 교황, 폐암 수술 후 회복세 교황청 “검사 수치 정상 범위” - 조선비즈.</t>
+          <t>올 8월까지 1217건 4년새 2.3배로 조정 성립된 사례는 6건중 1건 그쳐전세보증금 반환과 집 수리 문제 등을 둘러싼 임대인과 임차인 간 분쟁이 크게 늘고 있다.</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOaHpfTHMwUWczTmRfa1RKZmJVVXU0ZVA2Z2dPdU5iU25nSEVSZUg0MG1oazhLREo2cnV6bzFMQ2xKRzBwRG0zdzB5dmtzV0NFZmxNZlA3NktnTUFkMHNxcHRYdWF0UU1xYV9wVVVlcWYxWktIVFlKOXIyd1VOdTFxdy1ZSHJtTm1qMDV3Z3N3MTlqaUhqNUVFNXhaVm9fZ9IBsgFBVV95cUxQajI3bzBYbnhoOE9vNWdKbkVnZTkyaFFrb2lETmdld29waXl4c1J4UHRjYXJiQTBQM1plZVoxaG5JdHpDaFhSdVlGakJKWE55RTJWbklXU0N6NG43TlV2Vm9jSDd5b0Z2eXlzV3BzNWNnLUM5S0d5NnBuYjlnWks5dS1vb2w1WkNJT2JSdTRTeEFWQWpKcFd3Q0g3UE1veHQ5TU1OSWxZRVpLbmtZUEliVzNR?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176465</t>
         </is>
       </c>
     </row>
@@ -8732,32 +8732,32 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>러, 사할린서 일본인 기자 ‘간첩혐의’ 체포… 中 대표단은 쿠릴열도 방문… 日상대 협공</t>
+          <t>“아들아, 네 노후는 내가 도와줄게”…10건 중 7건 ‘부모가 대신’ 신청한 청년 첫 연금</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>러, 사할린서 일본인 기자 ‘간첩혐의’ 체포 中 대표단은 쿠릴열도 방문 日상대 협공.</t>
+          <t>강남권·학군지 등에 신청 몰려 농어촌과 비교하면 편차 두드러져내년 시행되는 ‘청년 생애 첫 연금보험료 지원’ 사업의 사전 신청 10건 중 7건은 청년 본인이 아닌 부모가 대신 신청.</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1xTnlGcUp5NlJKRi1uYWpnM05mS3ZXZ2tJV0RMa3pJWk1RcmVORFV0YzlKemhBNlBJVG5hUEYtMUtmVnlvZVdVQWpJcVRNalhTdHNuOG1FNC1wb0dodFNQVGo4aGJUQkdYVkMzbWdMNF92ZnfSAWZBVV95cUxPLThtMHJYSllBUFB3RzVuak5MM0VtaENlNXBJQWJFN3B2YWNMRDJiVDlDSWZMa1hTRXhJbDBPYjZ0dzRnUmY2RjI1aXpRbXUxSENMVlFrUTBjNzZkY0FHZDR1NGR2ZFE?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176464</t>
         </is>
       </c>
     </row>
@@ -8769,32 +8769,32 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>트럼프, 스타링크·군정보로 우크라에 '에너지 휴전' 강요하나</t>
+          <t>김재식·장종필의 법을 알면 부동산이 보인다</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>트럼프, 스타링크·군정보로 우크라에 '에너지 휴전' 강요하나.</t>
+          <t>계약금을 포기하거나 두 배로 돌려주면 부동산 계약을 언제든 되돌릴 수 있을까. 계약 해제의 기준이 되는 ‘이행의 착수’와 최근 대법원 판례를 통해 계약금과 중도금을 둘러싼 법적.</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>계약금 두 배 주면 끝일까? 부동산 계약을 되돌릴 수 있는 마지막 순간</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9IbWRDZks3T05Mc1loVE1kUWN1T0UxbUc0YjF1TmNXNEY5eGV6amZNWlMxMDBGMlpZTm45X21YR0JtNW5LdmdwRk5SLUhhN2Y1WDVwNUU3VDZoVkXSAWBBVV95cUxNOFBlRGpRYk9scFc3QnBHUnhaWlRzZ3ZXdk1xTlNQZ0U2QWNIaXZ1U3NLcmtvdldVTzlCdEljMW1nT3J1dEZNenpBNzJhd0hMVHRBLU1zRXlWN2pjbDdVUUg?oc=5</t>
+          <t>https://www.mk.co.kr/news/sports/12176461</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>민주 잠룡 아내·트럼프 장남 약혼녀…美 '정치계 스타'의 추락</t>
+          <t>“평생 월 200만원 꽂힌다는데”…100명 중 2명만 가입하는 주택연금 왜?</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>민주 잠룡 아내·트럼프 장남 약혼녀美 '정치계 스타'의 추락.</t>
+          <t>“실질적인 인센티브 확대해 문턱 낮춰야”“월 200만원씩 나오는 주택연금에 들면 여유 있게 여행도 다니고 숨통이 좀 트일 것 같은데, 자식들에게 집 한 채라도 물려줘야 하나 싶어.</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5hRXZqaTlDU2EyVWJnN3ZyM1IyZmljR1RwakZwdU5TNlUxd3RZM0ZxNXFCQzk0RjlKakl6T0gwQU1hTTFUMWxkelhwT0RtbjhhZnVzVk40QmRYZw?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176433</t>
         </is>
       </c>
     </row>
@@ -8848,27 +8848,27 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>평양서 북러 수교 78주년 연회…"피로 맺어진 동맹 영구불멸"</t>
+          <t>호르무즈 해협서 컨테이너선 침몰…이란 공격 확대에 원유 수송 차질</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>평양서 북러 수교 78주년 연회"피로 맺어진 동맹 영구불멸".</t>
+          <t>호르무즈 해협서 컨테이너선 침몰이란 공격 확대에 원유 수송 차질. 아울러 호르무즈서 피격된 UAE 화물선 2척 침몰"이란 공격 강화".</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>뉴스핌</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1TaGFDaXY5VlNXYXRLNjQxcEZsVmZpdTRXdF9UbzlKbmp4T2pIN2dqcmRoYVdZNFozbDVQNFFfenppbndibVg5QTN5M1plb1F4OG9acUdrTFNKZUnSAWBBVV95cUxNSUdUOXYwbzhlekc2cmZWUmU0QUtMWFJ0SWdxMC02Q05PbDd4ZDhEN21ZWjlGLTNUbUlya1JoQWs1c3h2UXF3eUFWbG1Fb0ZpMWJjWUN4M2h4UmhrQXZ6TkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE95MEh5LUtzVjNXSGt2LUs5eWwtVnV6Y2VZY3VhTFk2d0Q0U1BzdnQtT1cyN0RnSnp5ZnlKNjJRWUNHNFFPQ2J0U1M2RWU1QVVGSTZlRUJHaHZNVWl5?oc=5</t>
         </is>
       </c>
     </row>
@@ -8885,27 +8885,27 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>우크라, 러 최대 IT기업 얀덱스 집중 타격…이메일·택시·아파트 출입까지 먹통</t>
+          <t>[속보]북·중 ‘신압록강대교’ 완공 12년 만에 공식 개통</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>우크라, 러 최대 IT기업 얀덱스 집중 타격이메일·택시·아파트 출입까지 먹통. 아울러 러 공습 피해 주민에게 CPR 시도하는 구급대원들.</t>
+          <t>북·중 ‘신압록강대교’ 완공 12년 만에 공식 개통.</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>뉴스핌</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1sRWMzUHhxSW5vWUJXSVhPQlRtMVB5SFBvZzJ0N2IyMmI2ZHc3azdTdkdYaWhodWNSTFFkVmlteUFaY1ZfQmF5elNoZkVTb1NXaHZzWlYzYW5qSTNX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lTzlzbjVWd19xZjRuVm5aZlJ3b2tJTzZRUjVJSVpqc2pteHpmS1NfalhrWERWUVFSTVl1SHpTTU1yZl9pX3NvYnRpbm1US1BZb2p2TmQtTjE4d9IBX0FVX3lxTFBpbDFrNmoydS1NQzNlTlBSMlk1VVktd0pveko1TGRzZmUwcnFLS1dkM2daNEU0OFJXZHNTaEFaSEQ0NmRTeV9lY2pNT2VjQ29Qd0l4R3JPbmtrVlk2VmlN?oc=5</t>
         </is>
       </c>
     </row>
@@ -8922,27 +8922,27 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>"北, 러시아 드론공장서 기술 습득…대량생산 설비 구축 가능성"</t>
+          <t>젤렌스키 “트럼프 다른 편 선택 고통스럽다…배신감 느껴”</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>"北, 러시아 드론공장서 기술 습득대량생산 설비 구축 가능성".</t>
+          <t>젤렌스키 “트럼프 다른 편 선택 고통스럽다배신감 느껴”. 아울러 러시아 “미국과 ‘경유 딜’ 며칠 내 체결될 것세계시장 10% 규모”.</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1VUXpweHg2QklUYmRkaHh0U0FyeGFxcmRnZ0JVWndxNFA4YnNuSzNYZ0I5WnZzUzB5QWtUNUpSZXVKNHE5a3hELW5hWkJuNlRabVU0SzdHM2RFcllrOFdqZXY4N3hDU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4tNGtPT2ZtcjhWQnp4MU1KcGIwck5fZzY0eDRRX00tNk03UTh0bEc2dWFneG9kUFZhQlJQZGVZZXhUZ0JHTnRHcGVrTFIycVY3QWFIYTFOaDA1dHZXS2VINUJhcDFQbE13eFR2WW53?oc=5</t>
         </is>
       </c>
     </row>
@@ -8964,22 +8964,22 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>상장 앞둔 앤트로픽, 3분기 매출 45%↑…2분기 연속 흑자 달성</t>
+          <t>프로축구선수협 "1월 사우디 아시안컵 우려··선수 안전 보장돼야"</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>권영전 특파원 = 기업공개 를 추진 중인 앤트로픽의 3분기 매출이 직전 분기 대비 45% 성장하고, 영업이익도.</t>
+          <t>프로축구선수협 "1월 사우디 아시안컵 우려··선수 안전 보장돼야".</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015032300091</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBxMjRNdFk3aTNSc1Rzbnp5c291UFNGWDNZWk45TlFXRG1ST0JvUE82YU1nazcwWGJtc3FRRjhMSlhsVURoWkhqcnF3bDJmWVRhVzYzUUVEYlhjTTNwZEJDNU56cEFwWTV0dGh2YWF0UXE3RVdpcUHSAXZBVV95cUxQRXAxbXBXWXRxRlZPaUNUcHhweGNiQVR1UWZ5U0lCS0FiaDN4MEFxaWtMMllCeHdyeDIwVmxQRnR4cHBhWjZCOEVrQzJIQTF2RGtzbUdGY1hxdGFFMnRvcm5MU19UNXVEOXlqMmtGYm9VckxjWi1B?oc=5</t>
         </is>
       </c>
     </row>
@@ -9001,22 +9001,22 @@
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>엔비디아, 유럽 AI에 2조7천억원 투자</t>
+          <t>스페이스X(SPCX.O), 우크라군 스타링크 통신 제한...우크라 "정치적 상황과 관련" 주장</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>젠슨 황 엔비디아 최고경영자 가 앞으로 유럽지역 국가들의 인공지능 산업 육성에 총 20억달러(약.</t>
+          <t>스페이스X, 우크라군 스타링크 통신 제한우크라 "정치적 상황과 관련" 주장.</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>알파경제</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015025700009</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1rMDdpbkY5empESDhoSUVTUzRJUU9tZ2VwQmo4dmdsZDlQR19rT2lhTnFWOGdPcGNvb0pWTHgwRUZyUDA0UFRRajR6MlFqZGJIWlJGMTZiT2NxTWhYMUI4OHNWWTY1Ry1uSzZOVDBB?oc=5</t>
         </is>
       </c>
     </row>
@@ -9038,22 +9038,22 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>"하쿠나 마타타"…케냐 공연단 '카얌바 아프리카' 첫 방한 열광</t>
+          <t>교황 충분히 완치 기대…수년간 폐암치료 혁명 있었다</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>하쿠나 마타타…케냐 공연단 카얌바 아프리카 첫 방한 열광과 관련하여 주요 정책 및 시장 이해관계자들의 입장과 향후 파급 효과를 전했습니다.</t>
+          <t>교황 충분히 완치 기대수년간 폐암치료 혁명 있었다. 아울러 ‘폐암 진단’ 교황, 폐수술 하루 만에 식사·미사 재개···“여러분 기도는 교회의 큰 선물” 첫 메시지.</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015022500371</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9ucUxoMmwxT0ZKZFhNc1J0NlJLS01wYXlFc0ZzMFhDX2ppb3NaUEMyczkzclZqYVczamNXRXZnUXRPckpxRjcyenI1b3JqRm4zcExEQjA4MzdDQVHSAWBBVV95cUxPOXVEZHlSVjI5TExtZlpsdEtjaUZUdjNOdWs2MzFQYnNFWlZUWkJJN3NFNG5UMGRUMXJ3Y0dMb1dYOEMtaVhHSEZEdy1hRjRuQ09xY0xoX2tPdFZWTE5zNGE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9070,27 +9070,27 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>코이카, 베트남 의사면허시험 기틀 마련…호찌민의대 사업 완료</t>
+          <t>노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭"</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>한국국제협력단 이 연세의료원과 함께 추진한 베트남 보건의료 역량 강화 사업이 5년 만에 결실.</t>
+          <t>노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭".</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015023100371</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9ZcTM4YlJJUTFoUXZ5ZGZydnpQUnVFSGtHeHhOQWo0VUU3Wm9oc2VQMlFvM2c4SnVwVFRfNHh5NThkWERpQ3NZLWZRaXZvMG9aRE5PLUNxWXVJUjVaUDE4c3FfREhTczA?oc=5</t>
         </is>
       </c>
     </row>
@@ -9107,27 +9107,27 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>예멘 반군 후티, F-15 이어 유로타이푼도 격추 주장</t>
+          <t>북·러, 평양서 수교 78주년 연회…"피로 맺어진 동맹"</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>예멘 반군 후티는 사우디아라비아 공군의 유로파이터 타이푼 전투기 1대를 격추했다고 15일 주장했다.</t>
+          <t>북·러, 평양서 수교 78주년 연회"피로 맺어진 동맹".</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015030200009</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE52R25VQ05LdEo0MnpyelpFeFpKaHRqaUhwMWNadlFNX0d3TkhIWVQ4V3pCbmFlT0JtblNUaVBZU3dsdi1HYWdIMGY2cjlTTXY3NjFqaUVUdndVN2lXV0ZlbnM0b2lhODQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9144,27 +9144,27 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>"'日투자' 美뉴욕 반도체공장, 통신·자동차용 생산"</t>
+          <t>금발·짙은 화장·도톰한 입술···트럼프 오른팔 여성들, 꼭 닮은 ‘마가 페이스’와 충성 공식 [이윤정 기자의 소소월드]</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>조성미 특파원 = 도널드 트럼프 미국 대통령이 14일 일본의 새 대미 투자 대상으로 발표한 뉴욕 반도체 공장에서는.</t>
+          <t>금발·짙은 화장·도톰한 입술···트럼프 오른팔 여성들, 꼭 닮은 ‘마가 페이스’와 충성 공식. 아울러 남편을 "대통령"으로 부르기도 백악관 새 대변인, 망신살 신고식.</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015028500073</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1hbTVZN2xGX25aQkdlTnNwZEVQRVZzbDdjeHYxOGZmNDBxVU4yUFU0NmlRanFHbVY3N0VNY1JHbTNUS0ZWd2ZtVktjTnE4WFo2MlRBQS1xdnU0UdIBX0FVX3lxTE9ZdTl0OEZYbmtzQ2k4ZkhWVGNJeS11NjBLZjE2MVhaUkE2M1hBTVNVblRNcG4zUnpJY0lNbUFmQlFmTkw2b2hDLWNvbWhtcGh5VmdzLTJ3VGpUWnNxX0NZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9181,27 +9181,27 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>트럼프, 스타링크·군정보로 우크라에 '에너지 휴전' 강요하나</t>
+          <t>유럽, 트럼프 압박받는 젤렌스키 지지…'美 대체 불가' 지적도</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>도널드 트럼프 미국 행정부가 러시아와의 '에너지 휴전'을 강요하기 위해 우크라이나에 스타링크 서비스를 제한하고.</t>
+          <t>유럽, 트럼프 압박받는 젤렌스키 지지'美 대체 불가' 지적도.</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015029100009</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5ZZ2hlb3ZSajNaXzJGQzhpcWRGSkdlRTM2U1RlamZzU0JSZ0JvOVBtWXhYUkNQb0NBaEh2dzVyemdXbjZBRWxlbng5eFFFME5ZZDZobmpMby1XX0HSAWBBVV95cUxQYk1nUUhFSW9ockQ3YWlsUGxTUmVoTkRaNG9pdWhhNFdsc2lXd1VlQndvWldFRDBXNzQtdnBIaTFpVWxldnBKRGtVRVI3Qi1WeEx0RFRXdlMyXzZFVzVqcGg?oc=5</t>
         </is>
       </c>
     </row>
@@ -9218,27 +9218,27 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>호르무즈서 피격된 UAE 화물선 2척 침몰…"이란 공격 강화"</t>
+          <t>“北, 러 드론 공장에 1.2만명 파견…대량생산 노하우 갖고 평양으로”</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>호르무즈 해협에서 공격받았던 아랍에미리트 선사 소유 화물선 2척이 최근 24시간 사이 잇따라 침몰했다.</t>
+          <t>“北, 러 드론 공장에 1.2만명 파견대량생산 노하우 갖고 평양으로”.</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015026600009</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4yczZSa0J2UkVfVnRQaWRCd19Db2dZRzdXZ1U0TzZ6Zkl1bE9HYlRPSnVhTS12a0ZEQUttY1hpOW5lMWhMb0FLNGJvZGtmS19WbmJMSjRRVnEzREFZSld4c3dKUU5GU09EMVVKMVM1SjltVXVZZW130gFmQVVfeXFMTjdIVDRtbDJHSEdpcF8yUjZtRjVsYkdIRTB1SDhQOHNFYXMwal8xNEdMbGxpdVFiOFJ6R3hDZXpoWGttNjNDblpGQ2tITS1yZU9xYXl2eVJCcXBMak5sd3FkTi1MQXhB?oc=5</t>
         </is>
       </c>
     </row>
@@ -9255,27 +9255,27 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>트럼프, 애리조나 유세 도중 "정보 유출자는 총살해야"(종합)</t>
+          <t>미군 "지난 6일 오만만서 美함정 감시하던 이란 연계 선박 격침"</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>박성민 이유미 특파원 = 도널드 트럼프 미국 대통령은 14일 자신과 공화당에 대한 지지세가 강한 지역을 찾아 11.</t>
+          <t>미군 "지난 6일 오만만서 美함정 감시하던 이란 연계 선박 격침".</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015014351071</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE12OUdGaERjaUtZcVg5blA0RF9ZUUZSM0F2UUZGaEUtM2l3ZTIyOExNX2U5TXdpdFdLbExxQThqRzNnZmlzWTZhbEJlYkdGSm9SdGx2NmozbEQ3Q3RUVnhvTVhaMUhqMURtSlpIWF9CcEF3bkYx0gF0QVVfeXFMT3VPR0xfbGlzSmJqMWJTTGNLd1hGM1BjUU1RaVVRZE9YODhCUlZ6VVoxaVljM0QyQnpUNWZfOGlkaHNNbTRYNlgzWmRXN1lDQjNTZHA5TDZzZG9ZTF82XzQtX29YLTg0Q1JIUG8xOTVnLXExVjE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9292,27 +9292,27 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>방산 테크 안두릴 몸값 천정부지…"기업가치 122조원"</t>
+          <t>러시아, 우크라이나 공격 중 발전소 타격...젤렌스키 “에너지 휴전 위반”</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>미국의 인공지능 방산기업 안두릴이 임직원의 주식을 투자자에게 공개 매각하는 '텐더 오퍼'에 들어가면서.</t>
+          <t>러시아, 우크라이나 공격 중 발전소 타격젤렌스키 “에너지 휴전 위반”. 아울러 "러 경유 사고 우크라엔 정보 제한"美, 對우크라 정책 이상기류.</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>VOA 한국어 홈페이지</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015020600009</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5Fd2dpZ2NmbmZ6TlQ3OFpwVlpLU2pDSkY0LTE5d2kyX29sQ2g4TFdQLTdnSjlMNGM0UWdVUGlDUUtkWEc5VmVuMjc4d1ZpUnQ1N1FwcG0yYTJRcmcwOGF5TkNkYWFiT1lGMUd1LWpnWFcxd9IBdEFVX3lxTE1xMDdUU3BSblZnM3haek1GUnN6UkpEbXJCT3lzMHFuYzduZHRYOTlzT3E0eW1mQk8yRFpOVHYzYWh5U29RemNCUVZPUXU0MXQ3QkhJaWpvYlF6R20za0FLWEhDN2VDOU5XQXFzWGd0NlhRMmdI?oc=5</t>
         </is>
       </c>
     </row>
@@ -9329,27 +9329,27 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>'트럼프 밀착' 베네수 국회의장 8년 만에 美 제재서 벗어나</t>
+          <t>美 '총살형 생중계' 역풍 맞을라…트럼프 "무산될수도" 일보후퇴</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>송광호 특파원 = 베네수엘라 자원 문제와 관련해 미국의 주요 소통 창구 중 한명으로 알려진 호르헤 로드리게스 국회의장이.</t>
+          <t>美 '총살형 생중계' 역풍 맞을라트럼프 "무산될수도" 일보후퇴.</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015021000087</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1GcnBkc1RpT25jMjhScnR5b0pCU0VNemJ6SlBTNG04QzlvMzd1Q3VaVXVUVzk4MGVoRGtXYlpfc1BpUlFkM2RrZ0h0RHAzaHVkM0hOQkNmU09Fb3fSAWBBVV95cUxOM2FwVmJDWnhOY2RWd01OS0pnQ3pZVWRlU2dOX1dtSmJJdlVNTDQxVHBGcGp3U2EzbWF1NktFaExSajk1UC0xTF9NRXVpWGlHYjFMcEN2THlNT3hKSDFPeGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>[K-ODA 현장]⑩ '원조 넘어 상생'…신흥 시장 영토 넓히는 한국 기업(끝)</t>
+          <t>MLB 가을야구 '스몰마켓' 반란…새 노사협약 앞두고 비상한 관심(종합)</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>대한민국 공적개발원조 패러다임이 진화하고 있다. 과거 인프라 건설 중심의 일.</t>
+          <t>)= 미국프로야구 메이저리그 양대 리그 챔피언십시리즈가 한창인 와중에 미국 언론이 '스몰 마켓' 팀의 선전.</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261011037500371</t>
+          <t>https://www.yna.co.kr/view/AKR20261015080151007</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>[K-ODA 현장]⑨ '스캠국' 오명 씻는 캄보디아…치안 인프라 이식 본격화</t>
+          <t>中지방정부 "반도체는 국가안보 전략적 산업…CXMT 전폭 지지"</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>최근 몇 년간 동남아시아 일대는 스캠 범죄의 온상이라는 오명에 시달려왔다.</t>
+          <t>) 차병섭 특파원 = 반도체 산업 주도권을 둘러싼 경쟁 격화 속에, 중국 공업정보화부장 출신인 리러청 안후이성 신임 당서.</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261011001400371</t>
+          <t>https://www.yna.co.kr/view/AKR20261015093400089</t>
         </is>
       </c>
     </row>
@@ -9445,12 +9445,12 @@
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>[K-ODA 현장]⑧ 킬링필드 상처 보듬고 생명 살린다…캄보디아 '회복의 길'</t>
+          <t>'홈런 3방' 밀워키, 다저스에 3연승…WS 진출까지 단 1승</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>캄보디아 프놈펜 시내 중심가의 뚜얼슬렝 대학살 박물관 은 과거 크메르루주 정권.</t>
+          <t>)= 밀워키 브루어스가 월드시리즈 3연패를 노리는 로스앤젤레스 다저스를 벼랑 끝에 몰아넣었다.</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261011000400371</t>
+          <t>https://www.yna.co.kr/view/AKR20261015092500007</t>
         </is>
       </c>
     </row>
@@ -9472,32 +9472,32 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>하루 만에 결함 1411개... 마이크로소프트, 역대 최대 규모 10월 정기 패치 배포</t>
+          <t>'多死사회' 일본 도쿄 도심에 소규모 화장장 늘어난다</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>하루 만에 결함 1411개 마이크로소프트, 역대 최대 규모 10월 정기 패치 배포.</t>
+          <t>) 조성미 특파원 = 심각한 저출산 고령화로 '다사 사회'에 진입한 일본에서 도심에 소규모 화장장을 세워 화장시설 부족.</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>보안뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE91TEZhV1I2cUltZDl4YTJwS0FZSURSN3VuM1VjbUR3a2h3Y3U3dl9fVU1Da1ZTYnNZSnotZ1VsMkNFY0dMWFJqaWVVRjVMOHZkZkpoSElUOUxxVHk0NndlUnFJWEJERkUtNGFn?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015092000073</t>
         </is>
       </c>
     </row>
@@ -9509,32 +9509,32 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>소니는 2028년 1월까지 디스크 생산을 영구적으로 중단할 것이라고 확인했습니다.</t>
+          <t>대만 야당, 전 국민에게 83만원 'AI 보너스' 지급 추진</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>소니는 2028년 1월까지 디스크 생산을 영구적으로 중단할 것이라고 확인했습니다. 아울러 PS6, PS2와 PS3 게임 지원 전망 나왔다.</t>
+          <t>) 김철문 통신원 = 내달 지방선거를 앞두고 유권자의 표심을 공략하기 위해 대만 야당이 전 국민에게 1인당 2만 대만달러(약.</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>GameGPU</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNQWoxanRqQ3JCMnZHUVd6UzRhb3Jqd0pKTHZNekpHNDFyTjMzaFFJRXJHY05WTXBGd0cwX19DRFZ6cU1pZE43SFhKRUdQX0Y5VWx2QzktREJYRXd2dUMtS0RWNFVLZ2Nkc3pBLUR5WFNRN2VITU1TWFVCVDdFNjV2R1I3dGFlY1QyZ3dZanVzSkJhSzNJb05VcjF0Zm0tQkdHdWIwSHNsUUY3d0hERDBJOFFWTWZxa3NtWHc?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015088600009</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>UA Empirical Labs FATSO Tape Simulator 네이티브 플러그인 출시</t>
+          <t>러 '쿠릴열도서 폭격훈련' 통보에 日 항의…갈등 고조</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>UA Empirical Labs FATSO Tape Simulator 네이티브 플러그인 출시.</t>
+          <t>)= 러시아와 일본 간 갈등이 고조되는 가운데 러시아가 양국 간 영토분쟁 지역인 쿠릴 4개 섬 에서.</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>월간 믹싱</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiP0FVX3lxTE5NQTY1QjB6YXdQVjV3ZnJ0bXNaWWMzWUhfUXE4cnpkOGdhSzJRVFdpX3luaG9vUlBwQWptYVVIZw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015089600009</t>
         </is>
       </c>
     </row>
@@ -9583,32 +9583,32 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>IRQ inc., 새 브랜드 Adeder 첫 플러그인 'Adeder Limiter'·'Adeder Enhancer' 출시</t>
+          <t>북중 신압록강대교, 완공 12년만에 공식 개통…"무역 교류 촉진"(종합)</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>IRQ inc., 새 브랜드 Adeder 첫 플러그인 'Adeder Limiter'·'Adeder Enhancer' 출시.</t>
+          <t>) 정성조 김현정 특파원 = 중국 랴오닝성 단둥과 북한 평안북도 신의주를 잇는 신압록강대교가 15일 완공된 지 12년 만에.</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>월간 믹싱</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiP0FVX3lxTE51WF9ZemtqWE12VE1pdHpEaWg3N2lVQlRVM3hJZUlhbGd1ckZESVpoVHJTeURLc2ZaOVFLYklCdw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015076652083</t>
         </is>
       </c>
     </row>
@@ -9620,32 +9620,32 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>무료 피치 에디터 'Bubblegum' 공개…음표 단위로 음정·포먼트 편집, 폴리포닉도 가능</t>
+          <t>[영상] 태국서 길이 1.5m 자이언트 잉어 폐사 직전 상태로 발견</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>무료 피치 에디터 'Bubblegum' 공개음표 단위로 음정·포먼트 편집, 폴리포닉도 가능.</t>
+          <t>) 태국 중북부 프라친부리주 의 한 마을에서 길이 1.5m의 초대형 잉어가 잡혔습니다.</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>월간 믹싱</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiP0FVX3lxTE5JbUNhaGVNQmFSTlZyNnBESHBQZXpmdUU2YUVZYTBxeFZqZVdNaHRIUDJ6YTliVjNwSGJQQ2oyTQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015088500704</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Safari Audio 플러그인 16종 담은 'Everything Bundle V2' 출시…신제품 포함</t>
+          <t>"청천벽력" 교황 폐암진단에 개혁과제·순방일정 차질 우려</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>Safari Audio 플러그인 16종 담은 'Everything Bundle V2' 출시신제품 포함.</t>
+          <t>)= 레오 14세 교황의 폐암 진단 소식이 갑작스레 전해지면서 교황의 건강 문제가 향후 직무 수행에 영향을 주는.</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>월간 믹싱</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiP0FVX3lxTE5KdTNfekVzUllUdU9QZXBQTVlVZzgzRzlGbGJXVEZESTBtWmtodDNua1pLdHFQZDh2VWpRdGVfWQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015085200009</t>
         </is>
       </c>
     </row>
@@ -9694,32 +9694,32 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Psytrance Plugins, 초보자용 온라인 DAW 'JLoopz' 출시..전자음악 특화</t>
+          <t>러, '북한군 참전' 영화 예고…북한 병사역에 한국 출신 배우</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Psytrance Plugins, 초보자용 온라인 DAW 'JLoopz' 출시전자음악 특화.</t>
+          <t>)= 러시아가 우크라이나전에 파병된 북한군 활약상을 다룬 영화 제작 계획을 발표했다.</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>월간 믹싱</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiP0FVX3lxTE8xTkVRcGNYVnpkVkNYdnRpTUtoa2Q1aVljNUFOMDZWVGZhMjlYWXRudFBRZDU2SGJzeUJPRl9BZw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015087100009</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -9741,22 +9741,22 @@
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>애플, 12인치 맥북 3세대 전부 지원 종료…920g 초경량 맥북 공식 수리 길 닫혔다</t>
+          <t>[영상] 태국왕비, 이번엔 여객기 직접 몰고 일본행…전용차 운전 '파격'</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>애플, 12인치 맥북 3세대 전부 지원 종료920g 초경량 맥북 공식 수리 길 닫혔다.</t>
+          <t>) 스웨덴산 그리펜 전투기 첫 단독 비행에 나선 태국 수티다. 왕비가 전투기를 360도 회전시키는 '롤 기동'을 선보입니다.</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>위키트리</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE82WTVFVk80Um4wZjlnSm5CdEpNNjNGeFZEa01Mb1JqSVlRYkgyV1h2TnNEelVhRUhQR1BHWXA3aFlFN1AyLVM5MEJ3ZTJSTlV0NGtfRVNn?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015085400704</t>
         </is>
       </c>
     </row>
@@ -9768,32 +9768,32 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>"스팀보다 1.8배 빠르다" 에픽, 새 런처 프리뷰 공개</t>
+          <t>日연립여당, '조속한 개헌' 의견 일치…평화헌법 조항엔 견해차</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>"스팀보다 1.8배 빠르다" 에픽, 새 런처 프리뷰 공개.</t>
+          <t>) 조성미 특파원 = 헌법 개정을 추진 중인 일본 연립 여당이 개정 헌법 조문안 작성을 서두른다는 방침에는 일치했으나 핵심 쟁점인.</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>인벤</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBaOUtaNmRmbDhQWUVuSzJ5Tll4Q1BnNnExa3RyaTlRLXhYTzFqYkJ6b1BFTU0wS3BLVU05Z3drcmhWTmkxaXhnRE1YQ0V4bkJkWVNkcUdCNl9UUjJTNnc?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015086200073</t>
         </is>
       </c>
     </row>
@@ -9805,32 +9805,32 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>유튜브 뮤직, AI 생성 음악에 라벨 표시… 수익화는 그대로</t>
+          <t>애플, 중국서 첫 AI 기능 12월 출시…새 시리는 제외</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>유튜브 뮤직, AI 생성 음악에 라벨 표시 수익화는 그대로.</t>
+          <t>)= 애플이 오랜 기간 규제 끝에 중국 본토에서 인공지능 플랫폼을 출시할 준비를 하고 있다고 블룸버그 통신이.</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Martin Cid Magazine</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxPTmZGMGZDamZBRWh2UFlSZVRnNlRaVmFRQ1pkVDRINzBGZXd1dk4zT1REVTQ1ZzhFdzVlb09OYzl5RTNtb3JkMjVlQmRQT2lscXFydmdUX2k4YUxXT1pMQXZ0eFQ1NHdWQkZHd1ZPUUdTem9sa1pNV25YanJ4aWZ0b3FiU3liczF2eTRFRXRQdEs5YVMtdnBqYlYySGQyTU5DVDBlS245RHBiSnZZRjNvTVdQR2VCTVo1QWItM1B0TlNHNVdNc0tnSUxyOEtpRUU0bzZDaEhKalZaNEVsMWQ5ZDFHR3R3cl9XSWM0emZFRG5xMXlXSk55Ykx3ajFLeWpUeGRuYkRyTE5SajRhRTVESV93SWRtUUJISUZfMHJsajV5b0ZpdlZGZnQwbE5ucW8?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015074900009</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -9852,22 +9852,22 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Red Dead Redemption 2 RenoDX DLSS 5 v8.5 업데이트 덕분에 실사에 더 가까워졌습니다.</t>
+          <t>우크라 생명줄 된 스타링크…일부 제한만으로도 전쟁수행 '비상'</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Red Dead Redemption 2 RenoDX DLSS 5 v8.5 업데이트 덕분에 실사에 더 가까워졌습니다.</t>
+          <t>)= 미국의 위성 인터넷 서비스 스타링크의 군사용 버전인 '스타실드'에 갑작스럽게 속도 제한이 걸리면서 우크라이나군.</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>GameGPU</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNQTRnV0d1SXBTM2R4cmNtbFJDMjc1Y00yZlUtWENPMUlLYkZ3N1ZYbk9JOXV1dl9sRUJLS3RLdGlienhRSUMyUHpKMjFIN3QtNEtMWHJKMEFidTZJeWlKczkxeUdrdjBjMWUyOU9NVHBlVmtEUXlrNGhmSy1SQUdZNGR2R21aRGRFNTQ4ZXBfUWdaVUU3TUp4UjByWkQyNWtEVVZ2TndRcVNiRXZoTGtLVVMxRQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015084700009</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -9889,22 +9889,22 @@
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>에픽 게임즈는 이지 안티 치트 리눅스 v2와 포트나이트 출시를 발표했습니다.</t>
+          <t>AI가 생물무기 문턱 낮추나…"가능성 있지만 현실적 장벽"</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>에픽 게임즈는 이지 안티 치트 리눅스 v2와 포트나이트 출시를 발표했습니다.</t>
+          <t>)= 인공지능 이 급속하게 발달하면서 AI가 생물무기 개발에 악용될 수 있다는 우려도 커지고 있다.</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>GameGPU</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQNnUyZTE3eXNpbkFfeVptZTd6YUo0ZFZNQzRtOF9HUGRuMndNTDNwYnotaS1HM0FTSDhvRUV5U3I4SGlGM1NkZ096aHFjXzV3dE5FdjFfUmNaVnp4VmNhbjF6Y2xHZER0VHJ6bndHRDNieHcwY1JOWW81bGZKR2xZTGE3aGp3bGZIUUhfQmx0Tl9jU29qSG5TMzNjblNXQmk0RHBrZWhkbHNHaXZGZ1JOODM2VWFHYXM?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015082500009</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>대한전선, 미국서 대규모 초고압 전력망 프로젝트 턴키 수주</t>
+          <t>MLB 가을야구 '스몰마켓' 반란…새 노사협약 앞두고 비상한 관심</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>대한전선은 미국 법인인 T.E.USA가 현지에서 초고압 전력망 프로젝트를 턴키 방식으로 수주했다고 15일 밝혔.</t>
+          <t>)= 미국프로야구 메이저리그 양대 리그 챔피언십시리즈가 한창인 와중에 미국 언론이 '스몰 마켓' 팀의 선전.</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015033100003</t>
+          <t>https://www.yna.co.kr/view/AKR20261015080100007</t>
         </is>
       </c>
     </row>
@@ -9953,22 +9953,22 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (8개사)]</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>CJ온스타일, K-라이프스타일 소개하는 '글로벌몰' 오픈</t>
+          <t>유럽, 트럼프 압박받는 젤렌스키 지지…'美 대체 불가' 지적도</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>CJ온스타일은 K-라이프스타일 제품을 판매하는 글로벌몰을 열고 미국, 홍콩, 싱가포르에서 서비스를 시작했다고.</t>
+          <t>)= 유럽 각국이 러시아와 전쟁 중인 우크라이나에 대한 지원을 강화하겠다고 나섰다.</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015030700030</t>
+          <t>https://www.yna.co.kr/view/AKR20261015075900009</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>현대차 하이브리드, 미국 매체 10대 엔진·동력시스템 선정</t>
+          <t>오픈AI "애플이 주장하는 탈취 영업기밀 사용 않겠다"</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>현대차는 팰리세이드 하이브리드에 탑재된 2.5 터보 하이브리드 파워트레인이 미국 자동차 전문매체인 워즈오토가.</t>
+          <t>)= 오픈AI가 애플에서 옮겨온 직원들로부터 탈취했다는 의심을 받는 영업기밀을 소송이 마무리될 때까지 제품 개발에.</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015030100003</t>
+          <t>https://www.yna.co.kr/view/AKR20261015074300009</t>
         </is>
       </c>
     </row>
@@ -10037,22 +10037,22 @@
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>'절임배추·청결고추 고장' 괴산서 내달 5∼8일 김장축제</t>
+          <t>GTA 6 차기작?…록스타게임즈가 밝힌 변화</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>달 5∼8일 괴산유기농엑스포광장 및 종합운동장 일원에서 2026김장축제를 개최한다고 15일.</t>
+          <t>GTA 6 차기작?록스타게임즈가 밝힌 변화. 아울러 GTA6, 'NPC 대사를 위한 작가 팀'이 별도 존재한다.</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>디지털투데이</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015028300064</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE45NUt4NGdWTW96S0k3MXAwVmxyclh2TDU0Z2dyVVFCOHE3QzNNendZT2dGcEpVUTdGUHBSSnAyTzBOY21VYXEyZURlV2daQTJJRWhhdVpPSTlDMi13bUJfTnJyZ3VQMENLeGF3ZmNnOVJNbjQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10069,27 +10069,27 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>더현대 서울, 외국인 고객 짐 배송 서비스 도입</t>
+          <t>젤다의 전설 시간의 오카리나 리메이크는 생각보다 훨씬 많이 달라졌다 | IGN 프리뷰</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>현대백화점은 여행 물류 스타트업 굿럭컴퍼니와 제휴해 더현대 서울을 찾는 외국인 고객을 대상으로 짐 배송 서비스.</t>
+          <t>젤다의 전설 시간의 오카리나 리메이크는 생각보다 훨씬 많이 달라졌다 | IGN 프리뷰.</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>IGN Korea</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015030600030</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQY1JGbG0tcW1rVjY1ZW5TTUFaZ2doaHBaQzFHOG1FQlgzSVl6c3pvY3NTLVlSekNFd2F2ZF8tRXJhRHZiVFpWVUVKRU5FNVd6UUdZSzZ4MV8waWdEaXA5VnV4TFpjSVVHaXpOUElKUDRiUWpsLTVQNVVDVllpY3ZSUnB4dmNma3FqU2R3c1F4Mk45dHNBS0JNaF9MQTdhUzVLV1lCdzZaQ3RHYmpKVXViMnZfQlRyLXNZdFZzUXBYZzVmLTRLTF9aaVlnT2tWVWhVOHZRNUVIU3FmdUI4R1VOcEVDdVNET2NFY3I5Y2paaFhTbEk?oc=5</t>
         </is>
       </c>
     </row>
@@ -10106,27 +10106,27 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>내포신도시 밤하늘에 드론이 춤춘다…17일 드론페스타</t>
+          <t>콜 오브 듀티: 모던 워페어4, 로드맵 공개</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>충남도는 오는 17일 오전 10시부터 도청 일원에서 '2026 충청남도 드론 페스타'를 연다고 15일 밝혔다.</t>
+          <t>콜 오브 듀티: 모던 워페어4, 로드맵 공개.</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>인벤</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015030500063</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBIVXNOTVVYUUFuRjBmTjlqMVRnQl96Y0RmS0FzOXBtZmg5SFVMME5TSjVEeE1Ec0VTY0ZXSXp4Yy1NVl83NE1IcS1LeDJudzh6a3FYc3VFV2dKNl9rMFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10138,32 +10138,32 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>6년 연애한 하정우·차정원, 12월 3일 결혼한다</t>
+          <t>“AI가 취향 분석해 게임 추천”… 구글플레이, 소셜·검색 기능 강화</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>6년 연애한 하정우·차정원, 12월 3일 결혼한다.</t>
+          <t>“AI가 취향 분석해 게임 추천” 구글플레이, 소셜·검색 기능 강화. 아울러 구글, AI '바이브 코딩' 앱 비공개 실행 기능 도입"개발자 등록 필요 없어".</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>주간경향</t>
+          <t>IT조선</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9zRlFRbmd4eVJlMDVvOTZvTmcwRDM0UEd4elBPajJTNXd5T2lFWEFEUUdVd05EeVJGSDZiNE95VmI0NDNad1Z4WkxKSlRKSXlobVJKekU2eHp0V0kzRHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE0wUzFuRGc4TGVWVkJ4SVlGN3FYaFh3R29JdnhyQWpNaDQ4S0RnNm9YOUo4RHlBazUwa2ZqUFF3a3pPYWpKcjA3cUFVY09CelBJdnctVEpoLUkteXZtajdydWU5NmJwZEpDaHpfRHVwUmvSAXRBVV95cUxNQWtXU1gwdWNfanpzUk15djQ3RE5kcVBMSm9YSHkyS3NwOFlxcDlHeDRIX2tqNlFZN0dWZ3E1OVdQWnByTjRsN3VtX3dIZ051QXdFQ3B4eks2aTRSM3FrXzFJd1R2UlEyWWpGcDZ2ZEJOemttdQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -10185,22 +10185,22 @@
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>솔비·이규한, 열애설도 없었는데…내년 결혼</t>
+          <t>'몬길 : 스타 다이브' 캐릭터 이렇게 바뀐다</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>솔비·이규한, 열애설도 없었는데내년 결혼.</t>
+          <t>'몬길 : 스타 다이브' 캐릭터 이렇게 바뀐다. 아울러 "언제든 가볍게, 매력있는 캐릭터와 함께" 환골탈태한 '몬길'의 반주년.</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>더게임스</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBiazJzcWtqLXRHMFN5NWd5VzIycHJwcldSelZXU1NKb1JMeHduR01SSlk5QXJDR0ROckFTRnkzTU5uMURnQllWSHRlNUduUTJ6TnNDZTBNT0pEQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9KSDJ0bVBVck04dWlqQVZFemhpUHlJN1lwMXQxTGkxN21UN1RBV2hpMExOYlFqbnE1S09YV1dUR0lPalAyZXVjZndKbmx1cTUzR2thVDg5cWc4R3FaSnZtZmNPdWJINkNGWkI0MA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10212,32 +10212,32 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>이수만이 다시 꺼낸 K팝 DNA…A20라이트, 데뷔 직후 ‘멜론 1위’</t>
+          <t>코나미디지털엔터테인먼트, ‘캐슬바니아: 벨몬트의 저주’ 출시</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>이수만이 다시 꺼낸 K팝 DNAA20라이트, 데뷔 직후 ‘멜론 1위’.</t>
+          <t>코나미디지털엔터테인먼트, ‘캐슬바니아: 벨몬트의 저주’ 출시.</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>아이러브PC방</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5JRUQ3ZnhwRE5PWHViekxuRXZMQWt2X05Qb0ZncTJkQnZrM2pJR2ZDTFI0RGttNnBZU1Y4VXpmNXVqNmNIbE05LWRubS1fR1hJeUhZZGRWT29ZVzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFA3WTJMVThOazc1RDl6WmVCb3RJX1lvMXpTaWlrZnVzalhmTnp6XzZObXU0aHFsZjlBZlZfZThUY3RjX3BDbDVMZ1VUcVoySF83RXk0Wm5WSWZBbXZzOVdVY3ZIcEh5WTJHSnlvbDQ2MA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10249,32 +10249,32 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>황정음, 조윤희 '이혼 기사' 보고 충격…"밥줄 끊길 수도 있는 무시무시한 일"</t>
+          <t>콕스, 컴팩트한 디자인의 RGB 미러 라이팅 스피커 ‘CST30’ 출시</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>황정음, 조윤희 '이혼 기사' 보고 충격"밥줄 끊길 수도 있는 무시무시한 일".</t>
+          <t>콕스, 컴팩트한 디자인의 RGB 미러 라이팅 스피커 ‘CST30’ 출시.</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>아이러브PC방</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOU2g1blBwNFFxR1N0N0lNNWQ1VFRWbmRaX2prT1lCb3lMcXJMWkcxNFYzVXZuRGxSR2RkYnlDdWFnclljMVM5TUMzWnVoTGV5aTZwdWUzNjg1Tnp1Z2dDMmFCX25TSEdVVG96cW9rUk5zWVdVRUJ3aXhSMlhNWklweTFEWHA3bEw3cWlyRTFpYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE45MXVwei1LODAyTnd4bzZza2F2dURqRXZvTWlyVXU5MEo0cERNR1IwUFI5NzVCRW1RanNvbmVjZDlHQTliOWpDSTI3YXZSdE4zUGFTU1RpZkptazNMNl9CVkt4VUctdmNGZjFfNmlLdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10286,32 +10286,32 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>[오늘의 운세] 2026년 10월 15일 별자리 운세</t>
+          <t>USB Type-A·C 연결 지원 게이밍 마우스... '콕스 CM1100'</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 15일 별자리 운세.</t>
+          <t>USB Type-A·C 연결 지원 게이밍 마우스 '콕스 CM1100'.</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>디지털포스트</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1DdlZmQzVNUlB1aDhSTFhCc09iLXJxV0syWnQ0OS1qNzZ2YzNaZm5jUnV1azgzdjJXaXkwelIyQVdlTl9QLXpsM0hxX1pXYlNwMDV6NlBiUGhQeFZPNUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE41R0FmNXRNMVpaMkRGTWVFaGt1c01iSDJFY1pidWJJN18xN0hDbnVPRzNIc1Yyd1h0TU1MLVJ1UkF2N3pVRENiTkdaZEpZa2tSX3J6bmpLdGdSQ0VmN2ZGNkpLQVFDRno2WW0w?oc=5</t>
         </is>
       </c>
     </row>
@@ -10323,32 +10323,32 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>[리뷰] 아버지가 알려준 살아남는 법, 아버지를 품고 살아가는 법,</t>
+          <t>애플, 12인치 맥북 전 모델 공식 수리 끝냈다…2017년형도 '단종 서비스' 전환</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>아버지가 알려준 살아남는 법, 아버지를 품고 살아가는 법,. 아울러 “할리우드 사로잡은 벨벳 아우라” 태민, ‘웨일폴’ 프리미어서 뽐낸 파격 존재감.</t>
+          <t>애플, 12인치 맥북 전 모델 공식 수리 끝냈다2017년형도 '단종 서비스' 전환.</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>씨네21</t>
+          <t>디지털투데이</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9uU25RQkZkZHJQS3dSUXhHOG5ZdWt4UklEMjU5UXZLR0hMR1BfSjdGVWVCZUkwUFVPaFFleFFiNDhqYjRFSGxCUVBOT19pTFVBaU5kZWdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9yajl2YkRibFRIVExQX0NxU3NtQ3lVMnU0UXRuT1FEYXJwVnZDajRES2Z0bzNKMWgzUk80VTdCUlZLNW5heGFEME9oWVZwVGVXeUhvOHI0Z3lUeUpYaFB3bzdXeUM2RDZmQWhpWThxeFRsOE0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -10370,22 +10370,22 @@
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>홈캠 255회 접속…원격으로 보면 스토킹 아니다?</t>
+          <t>‘온라인삼국지2’, 천금서버에 장비 성장 지역 ‘천금촌’ 추가</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>홈캠 255회 접속원격으로 보면 스토킹 아니다?</t>
+          <t>‘온라인삼국지2’, 천금서버에 장비 성장 지역 ‘천금촌’ 추가. 아울러 2026년 9월 4주차 주간게임동향.</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>경향게임스</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAyTzU3VGF0R0ptYmtYd05ubnhCM1otVm9VSDI0cDZBWUM1NWNyTFFDTjVCMjktY2NkUTVyem9tNlBwa2FoMERSbTVfelZFMHhhbDduWExSekVaUUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBjUVBTU3lkS1IyQWpvZFJZS244UE1XTUtOVHc4MXdqQ3F1a3JUWm9GajJUZ0VoWjBaSEhaa3dTbVBzcFdkNXd5RVBGakw5S2pSV1hkTThmWC1aVW9xY09LdG9na1p6NFQwdy0yZg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10397,32 +10397,32 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>"술 따르라는 PD 뺨 때려 방송 정지?"…박준금, 직접 밝힌 당시 상황 ('라스') - 조선비즈</t>
+          <t>커세어, 첫 프리미엄 USB 마이크 ‘복사라’ 출시… 엘가토 기술 결합</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>"술 따르라는 PD 뺨 때려 방송 정지?"박준금, 직접 밝힌 당시 상황  - 조선비즈.</t>
+          <t>커세어, 첫 프리미엄 USB 마이크 ‘복사라’ 출시 엘가토 기술 결합.</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>뉴스탭</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQaDlRSXJiZUdHbGhTSzR3UmFwYUJBcFB1RzVPcUljRkxMSTNNOUJXdDVyU0ZMYXVJb1FSVk5SNkpnM0xRX24xTklTcC00VmszV0NydXFWLWxyMTRzbktuN0owT0JIaWVTVjh1NEF2Tmc1LUxRaHU1Nl85bjlBUEVLb2JjcFJxcFZkOTFBb09ubVRaTHfSAacBQVVfeXFMUGhuU3hiMXFiaHJtd2tseEJ6a3lLZzdYcktmWjRsQlRxYmFoZEFyaU4xaUVubkNxWWxoYVgzX0NYdFU0YVhDeW9GbHlnOF9KTUJQU0pkdDlQT0w0WUlkSXp4dHJDRkFrRzlxYzV4TWJjU1F6dEt2TW5kSG0tblFZRGpnelRLMHFrYmxpS2ZmaWgtZldaWDBVOWpPczNWbktnRG1BNWNYelU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE40cGhsYmpXdGppa2k5RjRwLUNzcnRKaUU4c2xucE5JNFZHWXc0Z3NxbFpjeFJIUXNoUmNKQkdTcUtJWndxZ09PVFV4X2xDVlZoOEpCT1YxQU54X1B4X1JKRjRvaVptdjZWb2hXNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,32 +10434,32 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>김수현 측 "김세의 주장 재배포는 위법행위"</t>
+          <t>(단독)해외투자 전문 KIND, 6000억 쏟았는데…회수액은 800억</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>김수현 측 "김세의 주장 재배포는 위법행위". 아울러 "김새론 안고 자고 싶다" 카톡 보낸 인물은 연예인 A 씨조작 진술 확보.</t>
+          <t>해외투자 전문 KIND, 6000억 쏟았는데회수액은 800억.</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>뉴스토마토</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1hZmhCRWE2dFdJYzdiUVlyRG5hUUp0Yk1XTkg4dWFLdV9GOExpdFZfRFVFSHA5aDRzVjhuYi14OTNTVXNTVEdVOWxMRzc0SmFvamF0ci13UUViY3BPdjRieGcxYUktSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9qV04xdEw0RDZVcXE2bF9hSDBJQ3FJMXpMZTdHb1ExM3lKZnVqUU8zUEs5SFZLbTgta0ZjOTlhbnM3Mmc2Um94T3lZVUh5czhHb0RIUEo0N3pzLWF6Qk1JMQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10471,32 +10471,32 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>박정희기념관 달려간 국힘, "패륜적 각색" 맹비난</t>
+          <t>게임 간 경계 허무는 AI...이용자 관심도 높아</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>박정희기념관 달려간 국힘, "패륜적 각색" 맹비난. 아울러 문체위서 '영화 암살자' 증인 채택 불발‥국힘 반발하며 퇴장.</t>
+          <t>게임 간 경계 허무는 AI이용자 관심도 높아. 아울러 복원·패치·이식까지, AI 이용한 '게임 역분석' 주목.</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>OhmyNews</t>
+          <t>이코리아</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBvWjR6SFBKcGFiMUpZMVQxLWxtS0M1MUVXX1NNdGN3R2o5TmVYZURjX0l4a1NzYldCUEN3OWVZd3JWZEJLSkwyRWlFRkY0VENibjhFeFpWb3cyT3JDLUVLOEl5V0trWGdPZDkxcHU0eWVQOTg3WnZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBLYnNHbzBzMzNnd0ZCYU4zbHVMTnlCLVRZbVRMNVNhRE1kTjZCWWRqNE1ZR3ZLb3B1ck5teE1wd0JfUFhVRHQyQXpRanRGd0ttVUJZa2p6b0h0azlkTTN6T0xHTUxMSm1pY3hLWldscw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10508,32 +10508,32 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>[현장톡] 류혜영 "'킬링타임'으로 액션 맛 알아…끝까지 액션하는 작품 해보고파"</t>
+          <t>우치코시 코타로, CRASH KEYS 공식 공개</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>류혜영 "'킬링타임'으로 액션 맛 알아끝까지 액션하는 작품 해보고파".</t>
+          <t>우치코시 코타로, CRASH KEYS 공식 공개.</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>뉴스핌</t>
+          <t>인벤</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBTbVJacHRpdlNvcVFaeG9mSHBzODQtUXVNMUhJU1dtRzFDcm9IZlMzN1AyQmgzNUVwWTlqYUlaMk1BM1BXQjBoWER3MzUyenJPUDNOLTZOUzctRjNU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5URGtRcEx2YUZ1WHFhekRTN2JXVS1RVzZ5QUljRGZqakJBcnFPZmRuNUY5Yk1GYi03M2xsTTNBMUtoV01IUHdqQmZtb21SX0lrMHl4Ujd3czhGazBzM0E?oc=5</t>
         </is>
       </c>
     </row>
@@ -10545,32 +10545,32 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>이지혜, '성심당 빵 싹쓸이' 논란에 입 열었다</t>
+          <t>브릭 바이 브릭, 15일 스팀 출시 예정</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>이지혜, '성심당 빵 싹쓸이' 논란에 입 열었다.</t>
+          <t>브릭 바이 브릭, 15일 스팀 출시 예정.</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>인벤</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQQ2xUbU43T1gxbVVBMWtKaW1HbWM3aFBibXhDMUxZa3ZGMnpBTnJSekhGZmdFbkVNVUxOQkdSMExGYUpQQlczc0xSSkJfVDNJTnNUUmltNzcxSHZXc2NMX0RKcTRFamVmLUpWSmpIbmVmLUs2Y2pGd0NVX08tQnVHaU9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9hZVdmSXZYTUljR1hoX2huRE9RWmxDbzNPb3NIUWJEVHJBQnJoZjZzMHhONzhHOXE3YWs2RVRDOW5ET0s3TUxoOHFhXzhidERPOVByeUtsd0VHQzhINmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -10592,22 +10592,22 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>가수 솔비·배우 이규한, 내년 4월 결혼…양가 상견례 마쳐</t>
+          <t>‘Max’ 붙이더니 전력도 냉각도 키웠다…MSI 사이보그 15 Max C2WF-C7</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>가수 겸 화가 솔비 와 배우 이규한 이 내년 4월 결혼한다.</t>
+          <t>‘Max’ 붙이더니 전력도 냉각도 키웠다MSI 사이보그 15 Max C2WF-C7.</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>뉴스탭</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015034100005</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE94LWcwd1RJb2FuNGJ4azA4SUtXTmR2V1lMODA1UncySDZiS00zQU5ZUURBVUZCX0lXcnA4azJ3SGwwOGd6c3p1bXFnaUFROXd0aTFnaEc1b2xqTlZ0VDVDakwwaWg1UXRNa2pWZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10619,22 +10619,22 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>커넥트플레이스, 서울역점서 K-드라마 전시…외국인 관광객 공략</t>
+          <t>제주공항 국제선 여객 작년 연간 실적 넘는 303만명…역대 최대</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>한화커넥트가 운영하는 커넥트플레이스 서울역점은 한국관광공사, 스튜디오드래곤과 함께 오는 31일까지 K-드라마.</t>
+          <t>)= 올해 제주공항 국제선 이용객이 303만명을 넘어서며 역대 최대 실적을 경신했다.</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015028800030</t>
+          <t>https://www.yna.co.kr/view/AKR20261015098400056</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>12년만에 첫 앨범 낸 니카 "음악으로 사랑받으리란 믿음 있었죠"</t>
+          <t>포스코 개발 고망간강, LNG선 화물창 실증…한화오션과 맞손</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>"아무리 힘들어도 음악을 포기 안 할 자신이 생겼어요. 음악으로 사랑받을 수 있다는 흔들리지 않는 믿음이 있었.</t>
+          <t>)= 포스코가 독자 기술로 개발한 '고망간강'을 액화천연가스 연료탱크에 이어 대형 LNG 운반선의 핵심.</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014150300005</t>
+          <t>https://www.yna.co.kr/view/AKR20261015071100003</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -10703,12 +10703,12 @@
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>이수만이 다시 꺼낸 K팝 DNA…A20라이트, 데뷔 직후 '멜론 1위'</t>
+          <t>[르포] 로봇 손 6대에서 204대로…현대차 푸네 공장 가보니</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>이수만 A2O엔터테인먼트 키 프로듀서 가 선보인 신인 걸그룹 A2O 라이트(A2O LI.</t>
+          <t>)= "기존 제너럴모터스 공장일 때는 이곳에 로봇이 6대에 불과했습니다.</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014160000005</t>
+          <t>https://www.yna.co.kr/view/AKR20261015005400003</t>
         </is>
       </c>
     </row>
@@ -10730,22 +10730,22 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>넷플릭스, 성장 둔화에 1천명 감원…2022년 이후 최대 규모</t>
+          <t>"서해·동해 이용료 수십배 차이"…대한상의, 지역규제 개선건의</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>임수정 특파원 = 세계 최대 동영상 스트리밍 업체 넷플릭스가 성장세 둔화와 이용자들의 서비스 이용 감소에 대응하기 위해 전체.</t>
+          <t>)= "같은 바다인데 서해인지 동해인지에 따라 이용료 차이가 수십 배 나는 것은 불합리합니다".</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014190500072</t>
+          <t>https://www.yna.co.kr/view/AKR20261015031400003</t>
         </is>
       </c>
     </row>
@@ -10767,22 +10767,22 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>빅나티, '별도 따다 주겠다'던 어린 시절 짝사랑과 결혼</t>
+          <t>AI 챗봇 청소년 유해성 점검…성적 묘사·범죄 조장 등 확인</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>가수 빅나티 가 노래를 통해 여러 차례 애정을 드러내 온 어린 시절 짝사랑과 결혼했다.</t>
+          <t>)= 일부 인공지능 캐릭터 챗봇이 청소년에게 유해한 응답을 하는 것으로 나타났다.</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014188900005</t>
+          <t>https://www.yna.co.kr/view/AKR20261015045600530</t>
         </is>
       </c>
     </row>
@@ -10804,22 +10804,22 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>JTBC "10월 중 매각 공고"…주관사로 한영회계법인 확정</t>
+          <t>KIST, 건물 외벽따라 자유롭게 형태 바꾸는 3차원 태양광 개발</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>기업회생 절차를 밟고 있는 종합편성채널 JTBC가 매각 주관사로 한영회계법인을 확정하고 본격적인 매각 작업에.</t>
+          <t>)= 건물 외벽 모양에 따라 자유롭게 형태를 바꾸는 3차원 태양광 시스템이 개발됐다.</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014180400005</t>
+          <t>https://www.yna.co.kr/view/AKR20261015083800017</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>"가을밤 영화 야외 관람" ACC 빅도어시네마 29일 개막</t>
+          <t>오픈AI, 아태·일본 세일즈 총괄에 안드레아스 하틀 선임</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>국립아시아문화전당재단은 오는 29∼31일 국립아시아문화전당 예술극장1 야외무대에서 '2026 ACC 빅도어.</t>
+          <t>)= 오픈AI가 아시아태평양·일본 지역의 초대 세일즈 부사장으로 안드레아스 하틀을 선임했다고 15일 밝혔다.</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014165200054</t>
+          <t>https://www.yna.co.kr/view/AKR20261015086000017</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>티빙, 11월 23일 애플TV 브랜드관 서비스 종료</t>
+          <t>잠자는 '충전형 선불금' 255억 주인 찾는다…환급·통지 강화</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>온라인동영상서비스 티빙이 오는 11월 23일 애플TV 브랜드관 서비스를 종료한다.</t>
+          <t>)= 앞으로 잠들어 있는 페이·머니형 선불금을 정기적으로 안내받고, 더 쉽게 돌려받을 수 있게 된다.</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014163800017</t>
+          <t>https://www.yna.co.kr/view/AKR20261015085800002</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>티빙, 정보보호 책임자에 국태호 CISO 선임</t>
+          <t>HD현대 정기선 취임 1년…사업통합 시너지·마스가 공략</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>온라인동영상서비스 티빙이 정보보호 역량 강화를 위해 국태호 최고정보보호책임자 를 선임했다고.</t>
+          <t>)= 정기선 HD현대 회장이 오는 17일 취임 1주년을 맞는다.</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014161300017</t>
+          <t>https://www.yna.co.kr/view/AKR20261015084600003</t>
         </is>
       </c>
     </row>
@@ -10952,22 +10952,22 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>연예/대중문화</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>부산국제영화제서 故 안성기 특별전…"항상 친절했던 배우"</t>
+          <t>bhc "'콰삭모짜킹', 출시 3주 만에 20만개 판매"</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>올해 1월 세상을 떠난 국민 배우 안성기를 추모하는 특별 프로그램이 제31회 부산국제영화제에서 진행됐다.</t>
+          <t>)= 다이닝브랜즈그룹의 치킨 브랜드 bhc는 신제품 '콰삭모짜킹'이 출시 3주 만에 누적 판매량 20만개를 돌파했다.</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014156300051</t>
+          <t>https://www.yna.co.kr/view/AKR20261015087200030</t>
         </is>
       </c>
     </row>
@@ -10989,32 +10989,1179 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
+          <t>IT/과학/신상품</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>가을까지 이어진 가뭄…대구, 8년만에 금호강 물 끌어온다</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>)= 가을까지 이어진 극심한 가뭄으로 청도 운문댐이 바닥을 드러내면서. 달 초부터 대구 일부 지역에는 8년 만에.</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015074700053</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
           <t>연예/대중문화</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>’하정우·차정원’ 이어 ’솔비·이규한’도…깜짝 결혼 발표</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>’하정우·차정원’ 이어 ’솔비·이규한’도깜짝 결혼 발표.</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>연합뉴스TV</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1EV1dQTlB2ZWdfTGJlc25OcU9ZeTBCT0VfRHFFNXREaGE2S0tsNlJMc0pEbVp3RXpGY2lvY0Jvc2RKcnNBcXQ2YzBTc3VVTkNYcVVIMnR1X19pVTdfU0sxUUpScDk0T0k?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>‘가능한 사랑’, 메인 포스터 공개…전도연·설경구·조인성·조여정의 감춰진 감정</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>‘가능한 사랑’, 메인 포스터 공개전도연·설경구·조인성·조여정의 감춰진 감정. 아울러 어쩌면 사랑까진 필요 없을지도.</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>스포츠동아</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE42ZVY2RXM1Vm5VZ19Udzg5dDN0d3VzZHFhX0ktdVJvUGVqZURWZWQ1M1pfeVNyeWQ0akY0dS1oTUZxSjVDU0RjTEozMG5VMG1mRVBMaDF4eEVpamdhQmVXZmNGd21temdPRkFoZXZR?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
         <is>
           <t>신규 이슈</t>
         </is>
       </c>
-      <c r="D285" s="3" t="inlineStr">
-        <is>
-          <t>임시완 "화려해 보이는 재벌 3세, 공허함 드러내려 했죠"</t>
-        </is>
-      </c>
-      <c r="E285" s="3" t="inlineStr">
-        <is>
-          <t>"재벌 역할이라 이제껏 출연한 작품 중에서 가장 쾌적한 환경에서 촬영했어요.</t>
-        </is>
-      </c>
-      <c r="F285" s="3" t="inlineStr">
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>최수종, '♥하희라' 똑 닮은 딸에 "말없이 가방 들어주는 남자 만나라"('유퀴즈')</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>최수종, '♥하희라' 똑 닮은 딸에 "말없이 가방 들어주는 남자 만나라". 아울러 "최수종이 때리고 이벤트?"하희라, 루머에 입 열었다 - 머니투데이.</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPRnpYX2JWU09IcGZBY0piWVdDc3hEZ2FDRDU5bEgyd0lfUy1LeTlwaEdCV3lUb09PTTdQazhjV25fajRSMU5ZU3BIWTduTWJ3MGZ3RUkxZVhIeE1sN244aWpOUGVnMWMzb3V6cVBPeVpaNUZQT0xZLXJsajExb25uQjVEQkwwTFctNXVKVTd4Zw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>서인영, 본토 갸루 완벽 소화에 일본인도 ‘동공 지진’</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>서인영, 본토 갸루 완벽 소화에 일본인도 ‘동공 지진’.</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>스포츠경향</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5WWXRhZ19LcFpETGZWOGtZLTVJQkEwTDIwbkJhaVFkQzMzYWc1eXQ5U2p6ZEdneWd5Vk9OSmFBMXlvMTBRV3ItRE5MX2NYU29nYUhEdDIxSVhqQU5ScXfSAWNBVV95cUxNSi1ZeWVhbWRPQ1dVZVZGakZaLXRJMndmN1NqNmVSN3JKWmtXRWdQeVpWMHVhY2NNc3RaLWN2M2tQcUZPNmFfMVk5U003NmV3Z09ycWtpbHBjMUh5cHF4eVdQbTA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>'병원장 사모님' 이정현, 3주년에 지갑 크게 열었다.."랍스터 100마리" 복지 클래스 ('편스토랑')</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>'병원장 사모님' 이정현, 3주년에 지갑 크게 열었다"랍스터 100마리" 복지 클래스.</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQc0JQQTFMRS1nT0hjb3lsTG9Ha3UweXB5dndBYzNnSFNiMjRlSW81dHFENWVmaXJfUzZ6cXBkT2FraGtfamxwOHFzUFdEQ2ZfTy1YZFpNUmdSanYtcDRvaVVGalJBZ2dWS2NOWjI0Z3JFN1p2ei1vQXJmSUhTeDFXM2NwOEVUTEZYa1lEWFFORQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>임진모, 뇌종양 투병 끝 먼저 간 아들 향한 그리움…아들 양말 신고 ‘유퀴즈’ 출연</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>임진모, 뇌종양 투병 끝 먼저 간 아들 향한 그리움아들 양말 신고 ‘유퀴즈’ 출연.</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>스포츠경향</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1TTnJ0cXJybnFkTlVBTkVsbkFleFBSYjFmYUloLWhtWmdoa1BvOHVfXy1qVEdqYzFfVTNfSGh4VERJYXZaWmpSYjNlWDl5SlJ5OUw1SG1Ldlc5T19RbmfSAWNBVV95cUxQLTNrcHViUFZZUzRnN2RkdnNFdjZyT2JROHdFZzRrX2ZmVGdZRktOaEZKV2VmMVNpcGVEWnZhcmdzenY0UmxQcmxpbGJkZVNqWEZhU0RuZXA2REkxMXJMWkRLd1E?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>조윤희, 이동건과 이혼 심경…“나도 이렇게 용감한 줄 몰랐다”</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>조윤희, 이동건과 이혼 심경“나도 이렇게 용감한 줄 몰랐다”.</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE03TDA2RGkwS095ZUtUUGt5OENNS0wxMUlodmY5eWlDQXc0bW9DNEtubE5pcC1jWFVBMFRLem1lUXVDWldnX05JUUc0S2pwd3VGTnctNFN5cVg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>서정희, 故서세원과 이혼 원치 않았다.."30kg대 난민 상태 돼"</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>서정희, 故서세원과 이혼 원치 않았다"30kg대 난민 상태 돼".</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNLXN1dXpHM0JCSHdnNVZteWdWVGdmRjRFU2o2Z0lkalEtbXhWcTA0SjdZS19UTFdFR2VQSmlOalhvU1hKci1zUHVZSzhEU0NKNzdNUktzbk15V0R6VXQ5TjJSZTVodld5aktBczZiRWkwcktRU29vUDJNTVV2dDJFN21ualc1am40bWp0ZFhzcw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>연결 이슈 (후속)</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>"빵값만 결제했는데"…이지혜, '성심당 싹쓸이' 주장 반박</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>"빵값만 결제했는데"이지혜, '성심당 싹쓸이' 주장 반박.</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5hYkxWS1g5bm5aN1IxS0FRZGJPWk5HWmZRQnB2ZVBiUlFoQ0hMOEVYSllyOW5QbHF3eGhpekdiYXhDMmtvN1pmRnBTU3ZveEZyc0NROWR5Nm9zQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>BIFF 11년 만에 관객 20만 넘었다…폐막식 때 경쟁부문 수상작 발표</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>BIFF 11년 만에 관객 20만 넘었다폐막식 때 경쟁부문 수상작 발표. 아울러 제31회 부국제 결산 기자회견하는 정한석 집행위원장.</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>국제신문</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORFdsajRJQkZCdURlUjE3azQwNDhKWjBUdXAyM2RTYVZqb09lVWpxZTVwLVlBeHBJcmdxMG02VVdvdVpiMkc0bzF4dHhoTXd3X3g0OXdVRFphbVpKZWsyYmY5LVFJQjhZMTM3ZF9aU2ItZmw2Nll1T0FPM1F1TmttNEx3c0FLdk5IMFZF?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>악뮤 이찬혁·이수현 합숙소 공개..운동방·노래방에 초특급 올드카 보유(전참시) - 조선비즈</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>악뮤 이찬혁·이수현 합숙소 공개운동방·노래방에 초특급 올드카 보유 - 조선비즈. 아울러 악뮤, 콘서트 시야제한석에 시각장애인 초대관객 후기 화제.</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPVmhuVWFjbkJrbTFwQlN1YWlacUVuamFpQmh1SEhIQk9uZ1NKSnpQWjF6Z2JWbFNJdG9aWVhBSU9pVVItcUhEOUp3bk5FSTNYUUZQQWFNMDhabFJ1dXZVWVNhZzY3SGRCTlVubzMwUmtIZzNhazdGNkFPNzU3bkNRMmdEX1NHbXA0VndldTg5UjZpR0nSAacBQVVfeXFMUGNxb0ZKRWpNU01SX3ZpbDVxLW9CZERZZUp4V0dtckRHRUxKTmx6eS1tRFpwWkRXeEx6UmpNRG9SWkEzckxMOXBoTjdweEo3SWtlOE1LZHNzX3daR2JRM3d0XzlfQTFyQk9YYkxiLUM3RWgwRG9OUVJCUUtibGljSzdvakZsaVRpejZzTkNWYUc1MVB2RTVIay0weEFoX3RGbFNVOElvajQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>방미통위원장 “공영방송 본질 중요 시점…공론장 형성해야”</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>방미통위원장 “공영방송 본질 중요 시점공론장 형성해야”.</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>KBS 뉴스</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1rTHd6QXF6SngyaU5TNHY5bVpDZm9VUHp3blRxZ1A4SWFMTWJGMXE2eWU5R2liSnk5RDJoWTNtTUVlakpVa1hPbmdRNnlTbk9SRk5LMXkyVFBqazg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>독립영화, 극장 밖에서 관객 만난다</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>독립영화, 극장 밖에서 관객 만난다.</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>지디넷코리아</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE91ODdOUXBZbTRTWmxZZWZPbDlGa2xwN0hiTnBQRXVuWk8xQzhfZlBVVzZMX3JjbmFwaHFpMENHQ3R2eVRsWWN2ck1VbXpoVmNNTXdwNUZn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>문체위, 이임생 등 국감 증인 채택...암살자(들) 증인은 불발</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>문체위, 이임생 등 국감 증인 채택암살자 증인은 불발. 아울러 ‘암살자’ 감독 증인 채택 불발에 항의.</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>YTN</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1oWmZPSGEzMHhMOFFwZHZtb3NZRFZKZGdzcTM5VV96U3hHWkw0ZkwwWlNtOTZnTy1zakNJUXlLcWpFcjNXcUU0X0FwRDhoMW1IaG5zMTdmTnRuQzViMEE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>‘김수현 명예훼손’ 김세의, 풀려날까…보석 청구 내일 심문</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>‘김수현 명예훼손’ 김세의, 풀려날까보석 청구 내일 심문.</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>문화일보</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBHaTdhTDBmY1hfYW43WDRsWDJld2FKd1FTbjg3Y0RhWVFUd3l5Q2tnbHNXMVJWX09kdTB2ZzBWdjF2Q2Z3QUs5dVRZRlliV1It?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>장항준 "'거~장항준' 제안했는데…제목 보고 놀리는 줄"</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>)= " 제 이름이 들어가서 책임감을 딱히 느끼진 않았어요. 혼자 하면 부담스러울 것 같은데 송은이,.</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr">
         <is>
           <t>주요언론</t>
         </is>
       </c>
-      <c r="G285" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014141700005</t>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015094100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>KF, '퓨전엠씨'와 비보잉으로 베트남·인도네시아 청년 만난다</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>)= 한국국제교류재단 은 인도네시아 자카르타와 베트남 하노이·호찌민 등 3개 도시에서 한국 대표.</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015086900371</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>[가요소식] 그룹 유어즈, 21일 미니 1집 '비' 발매</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>)= ▲ 유어즈, 21일 미니 1집 '비' = 그룹 유어즈가 오는 21일 미니 1집 '비' 를 발매한다고 피나클.</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015086400005</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>부산국제영화제 관객 20만명 넘었다…"11년 만에 처음"</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>)= 부산국제영화제를 찾은 관객 수가 11년 만에 20만명을 넘은 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015086800051</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>"장우혁이 폭행" 주장 전 소속사 직원 2심도 명예훼손 무죄</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>출신 가수 장우혁이 폭언과 폭행을 했다고 주장한 전 소속사 직원이 항소심에서도 명예훼손 혐의.</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015081700004</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>[대전소식] 대전부르스 창작가요제 18일 열려</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>) ▲ 대전부르스 창작가요제 18일 개최 = 대전시는 18일 오후 7시 대전 엑스포과학공원 주 무대에서 대전 빵축제와 연계해 '제.</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015081300063</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>곡성군, 전국요리경연대회 23일 개최…지역 특산물 활용</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>)= 전남광주 곡성군은 오는 23일 섬진강기차마을 중앙광장에서 '2026년 제4회 곡성 전국 요리경연대회'를 개최한.</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015080900054</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>저항하고 고발하는 이들의 영화…23∼25일 서울국제휘슬러영화제</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>)= 불의와 비리에 맞서 저항하고 인간 내면의 부조리를 고발하는 이들을 담은 영화들이 오는 23∼25일 서울 아트하.</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015074000005</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>세븐틴 승관이 소개하는 고향 제주…마을 여행 영상 공개</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>)= 제주 출신 아이돌그룹 세븐틴의 승관 이 고향 제주의 작은 마을을 여행하며 지역의 매력을 소개하는.</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015065200056</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>넷플릭스 "자막·더빙도 제2의 제작"…K-콘텐츠 세계화의 힘</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>'피지컬: 100' 멕시코판 첫 주 250만 시청이탈리아판도 흥행.</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015031200017</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>원주국제걷기대회 24∼25일 개최…'가을 정취 만끽하며 걸어요'</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>)= 강원 원주시는 오는 24∼25일 원주시 일원에서 제32회 원주국제걷기대회를 개최한다고 15일 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015054400062</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>[가요소식] 터치드, 데뷔 6년 만에 첫 정규앨범 '극야'</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>)= ▲ 터치드, 데뷔 6년 만에 첫 정규앨범 '극야' = 밴드 터치드가 15일 낮 12시 첫 번째 정규앨범 '극야.</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015057900005</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>'서울의 봄' 김성수 감독, AI로 단편 '웜 트레인' 제작</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>)= 영화 '서울의 봄' 의 김성수 감독이 인공지능 을 활용해 단편 '웜 트레인'을 제작한다고 15일.</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015051500005</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>[방송소식] 윤두준·배윤경, '무한상사-하와수 네버다이' 출연</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>)= ▲ 윤두준·배윤경, '무한상사' 출연 = 웨이브는 그룹 하이라이트 멤버 겸 배우 윤두준과 배우 배윤경이 12월.</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015046800005</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>신규 이슈</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>[테크스냅] IPTV방송협회, 23일 '휘슬러 포럼'…독립영화 유통 논의</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>)= 방송·미디어 업계가 독립영화 유통 활성화와 관객 접점 확대를 위한 논의의 장을 마련한다.</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015043400017</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>연예/대중문화</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>[가요소식] 2PM 장우영, 내달 14∼15일 솔로 콘서트</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>)= ▲ 2PM 장우영, 내달 14∼15일 솔로 콘서트 = 그룹 2PM의 장우영이.</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>주요언론</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261015041100005</t>
         </is>
       </c>
     </row>
@@ -11029,7 +12176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14541,42 +15688,42 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>232,000원</t>
+          <t>209,000원</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>+21,000원 (+9.95%)</t>
+          <t>-2,000원 (-0.95%)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>220,500원</t>
+          <t>205,000원</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>229,500원</t>
+          <t>285,500원</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>225,000원</t>
+          <t>198,500원</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+39.4%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (악재 주의)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>악재 보도 및 5일 연속 약세(-4% 이상)로 단기 추가 하락 위험</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -14590,26 +15737,26 @@
         </is>
       </c>
       <c r="O38" s="3" t="n">
-        <v>34.4</v>
+        <v>27.5</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>6천 뚫린 코스피에 사모펀드 셈법 갈렸다…'현금 확보'vs'반도체 줍자' (연합인포맥스)</t>
+          <t>中 CXMT 반도체 신기술, 왜 삼전닉스 주가 흔들었나 (조선일보)</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>[259500.0, 249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 232000.0]</t>
+          <t>[249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 232000.0, 209000.0]</t>
         </is>
       </c>
     </row>
@@ -14636,42 +15783,42 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>1,419,000원</t>
+          <t>1,260,000원</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>+283,000원 (+24.91%)</t>
+          <t>+124,000원 (+10.92%)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1,390,500원</t>
+          <t>1,197,000원</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>1,868,000원</t>
+          <t>1,247,500원</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>1,348,000원</t>
+          <t>1,222,000원</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>+34.3%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (악재 주의)</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>악재 보도 및 5일 연속 약세(-4% 이상)로 단기 추가 하락 위험</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -14685,26 +15832,26 @@
         </is>
       </c>
       <c r="O39" s="3" t="n">
-        <v>30.5</v>
+        <v>25</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>[개장시황] SK하이닉스 7%대 급락 이유…이틀 만에 또 사이드카 (자본시장뉴스)</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>[1812000.0, 1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1419000.0]</t>
+          <t>[1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1419000.0, 1260000.0]</t>
         </is>
       </c>
     </row>
@@ -14731,27 +15878,27 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>313,500원</t>
+          <t>294,000원</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>-194,500원 (-38.29%)</t>
+          <t>-214,000원 (-42.13%)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>298,000원</t>
+          <t>279,500원</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>310,500원</t>
+          <t>291,000원</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>304,000원</t>
+          <t>285,000원</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -14766,40 +15913,40 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(349,300원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(344,875원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O40" s="3" t="n">
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>인도서 21조 투자하는 현대차그룹…국내 부품사 기회도 커질 듯 (한국무역협회-KITA.NET)</t>
+          <t>현대차, 인도 푸네 신공장 준공…연 17만대 생산체제 구축 (전기신문)</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>[382500.0, 371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 313500.0]</t>
+          <t>[371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 313500.0, 294000.0]</t>
         </is>
       </c>
     </row>
@@ -14826,32 +15973,32 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>108,500원</t>
+          <t>105,000원</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>-42,900원 (-28.32%)</t>
+          <t>-46,300원 (-30.56%)</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>101,500원</t>
+          <t>99,900원</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>107,500원</t>
+          <t>104,000원</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>105,500원</t>
+          <t>102,000원</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>+6.0%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -14861,40 +16008,40 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(115,830원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(114,760원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O41" s="3" t="n">
-        <v>29.9</v>
+        <v>25.9</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>[단독] “국산차 왜 타냐?” 비웃던 테슬라 오너…2배 수리비에 말 없어졌다 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>[126600.0, 124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 108600.0]</t>
+          <t>[124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 108600.0, 105200.0]</t>
         </is>
       </c>
     </row>
@@ -14921,32 +16068,32 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>179,500원</t>
+          <t>172,500원</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>-31,600원 (-14.98%)</t>
+          <t>-38,300원 (-18.15%)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>169,000원</t>
+          <t>164,000원</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>177,500원</t>
+          <t>171,000원</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>174,000원</t>
+          <t>167,500원</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -14956,40 +16103,40 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(193,985원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(192,295원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O42" s="3" t="n">
-        <v>29.1</v>
+        <v>24.9</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>“잊고 있던 페이 잔액 255억원 돌려받으세요”…빅테크 3사, 정기 알림·환급 안내 (주요언론)</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>[206500.0, 204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 179400.0]</t>
+          <t>[204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 179400.0, 172700.0]</t>
         </is>
       </c>
     </row>
@@ -15016,75 +16163,75 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>31,700원</t>
+          <t>30,600원</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>-17,900원 (-36.09%)</t>
+          <t>-18,975원 (-38.26%)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>31,100원</t>
+          <t>29,100원</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>34,600원</t>
+          <t>30,300원</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>30,100원</t>
+          <t>29,700원</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>+11.5%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>주가가 20일선(33,168원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O43" s="3" t="n">
-        <v>32.4</v>
+        <v>27.5</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>[한화투자증권] 카카오게임즈: 기업가치 정상화를 위한 모든 변화 시작 (한화투자증권)</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>[34500.0, 34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 31700.0]</t>
+          <t>[34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 31700.0, 30625.0]</t>
         </is>
       </c>
     </row>
@@ -15111,27 +16258,27 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>180,000원</t>
+          <t>180,500원</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>-12,580원 (-6.54%)</t>
+          <t>-11,980원 (-6.23%)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>176,000원</t>
+          <t>177,000원</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>189,000원</t>
+          <t>189,500원</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>171,000원</t>
+          <t>171,500원</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -15160,16 +16307,16 @@
         </is>
       </c>
       <c r="O44" s="3" t="n">
-        <v>45.2</v>
+        <v>46.7</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
@@ -15179,7 +16326,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>[178200.0, 178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 179800.0]</t>
+          <t>[178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 179800.0, 180400.0]</t>
         </is>
       </c>
     </row>
@@ -15206,32 +16353,32 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>842,000원</t>
+          <t>817,000원</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>-667,000원 (-44.20%)</t>
+          <t>-692,000원 (-45.86%)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>797,000원</t>
+          <t>776,000원</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>833,500원</t>
+          <t>809,000원</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>816,500원</t>
+          <t>792,500원</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -15241,30 +16388,30 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(1,012,200원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(999,000원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O45" s="3" t="n">
-        <v>30.1</v>
+        <v>28.3</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -15274,7 +16421,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>[1081000.0, 1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 842000.0]</t>
+          <t>[1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 842000.0, 817000.0]</t>
         </is>
       </c>
     </row>
@@ -15301,32 +16448,32 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>422,000원</t>
+          <t>401,500원</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>+14,000원 (+3.43%)</t>
+          <t>-6,500원 (-1.59%)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>372,000원</t>
+          <t>374,500원</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>422,000원</t>
+          <t>401,500원</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>413,500원</t>
+          <t>393,500원</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>+13.4%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -15336,7 +16483,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>RSI 71.0, 20일선 이격도 +13.4%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
+          <t>RSI 60.1, 20일선 이격도 +7.3%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -15350,16 +16497,16 @@
         </is>
       </c>
       <c r="O46" s="3" t="n">
-        <v>71</v>
+        <v>60.1</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>+13.4%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -15369,7 +16516,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>[360000.0, 351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 422000.0]</t>
+          <t>[351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 422000.0, 401500.0]</t>
         </is>
       </c>
     </row>
@@ -15396,42 +16543,42 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>309,000원</t>
+          <t>292,500원</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>-59,000원 (-16.03%)</t>
+          <t>-75,500원 (-20.52%)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>303,000원</t>
+          <t>278,000원</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>334,000원</t>
+          <t>289,500원</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>293,500원</t>
+          <t>283,500원</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>주가가 20일선(312,775원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -15445,26 +16592,26 @@
         </is>
       </c>
       <c r="O47" s="3" t="n">
-        <v>45.3</v>
+        <v>36.8</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>최근 특이 뉴스 없음</t>
+          <t>포스코 개발 고망간강, LNG선 화물창 실증…한화오션과 맞손 (주요언론)</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>[334000.0, 326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 309000.0]</t>
+          <t>[326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 309000.0, 292500.0]</t>
         </is>
       </c>
     </row>
@@ -15491,7 +16638,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>$221.30 (약 297,112원)</t>
+          <t>$221.30 (약 298,219원)</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -15501,17 +16648,17 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>$217.98 (약 292,656원)</t>
+          <t>$217.98 (약 293,746원)</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>$254.50 (약 341,679원)</t>
+          <t>$254.50 (약 342,952원)</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>$206.33</t>
+          <t>$206.61</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -15540,11 +16687,11 @@
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>52</v>
+        <v>43.9</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -15554,12 +16701,12 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>엔비디아, 유럽 AI에 2조7천억원 투자 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>[213.9, 219.34, 222.27, 227.38, 228.87, 225.51, 224.58, 225.07, 228.86, 227.21, 228.38, 230.86, 233.95, 238.9, 239.24, 237.47, 230.48, 229.28, 226.32, 228.52]</t>
+          <t>[219.34, 222.27, 227.38, 228.87, 225.51, 224.58, 225.07, 228.86, 227.21, 228.38, 230.86, 233.95, 238.9, 239.24, 237.47, 230.48, 229.28, 226.32, 228.52, 221.3]</t>
         </is>
       </c>
     </row>
@@ -15586,7 +16733,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>$342.96 (약 460,451원)</t>
+          <t>$342.96 (약 462,166원)</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -15596,12 +16743,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>$336.10 (약 451,242원)</t>
+          <t>$336.10 (약 452,922원)</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>$360.11 (약 483,473원)</t>
+          <t>$360.11 (약 485,274원)</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -15635,11 +16782,11 @@
         </is>
       </c>
       <c r="O49" s="3" t="n">
-        <v>60.5</v>
+        <v>62.1</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -15649,12 +16796,12 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>애플, 12인치 맥북 3세대 전부 지원 종료…920g 초경량 맥북 공식 수리 길 닫혔다 (위키트리)</t>
+          <t>애플, 중국서 첫 AI 기능 12월 출시…새 시리는 제외 (주요언론)</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>[332.41, 337.0, 336.13, 338.98, 339.75, 337.02, 335.92, 341.07, 338.4, 329.4, 333.02, 330.32, 333.69, 332.89, 333.63, 336.67, 340.42, 336.64, 340.97, 341.27]</t>
+          <t>[337.0, 336.13, 338.98, 339.75, 337.02, 335.92, 341.07, 338.4, 329.4, 333.02, 330.32, 333.69, 332.89, 333.63, 336.67, 340.42, 336.64, 340.97, 341.27, 342.96]</t>
         </is>
       </c>
     </row>
@@ -15681,7 +16828,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>$367.16 (약 492,941원)</t>
+          <t>$367.16 (약 494,777원)</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -15691,12 +16838,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>$359.82 (약 483,082원)</t>
+          <t>$359.82 (약 484,881원)</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>$385.52 (약 517,588원)</t>
+          <t>$385.52 (약 519,516원)</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -15730,11 +16877,11 @@
         </is>
       </c>
       <c r="O50" s="3" t="n">
-        <v>54.5</v>
+        <v>49.3</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -15744,12 +16891,12 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>[단독] “국산차 왜 타냐?” 비웃던 테슬라 오너…2배 수리비에 말 없어졌다 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>[358.08, 366.2, 364.27, 375.3, 378.9, 380.12, 377.94, 372.11, 357.45, 352.84, 354.81, 354.11, 370.59, 378.73, 380.68, 377.81, 375.0, 382.7, 378.03, 375.23]</t>
+          <t>[366.2, 364.27, 375.3, 378.9, 380.12, 377.94, 372.11, 357.45, 352.84, 354.81, 354.11, 370.59, 378.73, 380.68, 377.81, 375.0, 382.7, 378.03, 375.23, 367.16]</t>
         </is>
       </c>
     </row>
@@ -15776,7 +16923,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>$533.69 (약 716,521원)</t>
+          <t>$533.69 (약 719,189원)</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -15786,32 +16933,32 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>$514.20 (약 690,354원)</t>
+          <t>$516.40 (약 695,890원)</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>$533.69 (약 716,521원)</t>
+          <t>$560.37 (약 755,149원)</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>$523.02</t>
+          <t>$507.01</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+8.5%</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>RSI 70.7, 20일선 이격도 +3.8%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -15825,11 +16972,11 @@
         </is>
       </c>
       <c r="O51" s="3" t="n">
-        <v>70.7</v>
+        <v>62.4</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+3.4%</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -15839,12 +16986,12 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>하루 만에 결함 1411개... 마이크로소프트, 역대 최대 규모 10월 정기 패치 배포 (보안뉴스)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>[490.3, 497.75, 493.78, 501.61, 498.0, 500.59, 497.93, 516.17, 509.22, 508.96, 512.9, 512.8, 517.53, 525.18, 529.3, 529.76, 522.61, 535.07, 541.15, 543.45]</t>
+          <t>[497.75, 493.78, 501.61, 498.0, 500.59, 497.93, 516.17, 509.22, 508.96, 512.9, 512.8, 517.53, 525.18, 529.3, 529.76, 522.61, 535.07, 541.15, 543.45, 533.69]</t>
         </is>
       </c>
     </row>
@@ -15871,17 +17018,17 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>404,500원</t>
+          <t>370,500원</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>-107,500원 (-21.00%)</t>
+          <t>-141,500원 (-27.64%)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>396,500원</t>
+          <t>363,000원</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -15891,45 +17038,45 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>384,500원</t>
+          <t>352,000원</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>+34.7%</t>
+          <t>+47.1%</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-14) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O52" s="3" t="n">
-        <v>33.1</v>
+        <v>28.8</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
@@ -15939,7 +17086,7 @@
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>[464000.0, 474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 404500.0]</t>
+          <t>[474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 404500.0, 370500.0]</t>
         </is>
       </c>
     </row>
@@ -15951,12 +17098,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>103590.KS</t>
+          <t>000810.KS</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -15966,42 +17113,42 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>74,900원</t>
+          <t>576,000원</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>-11,900원 (-13.71%)</t>
+          <t>+90,000원 (+18.52%)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>73,400원</t>
+          <t>547,000원</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>88,000원</t>
+          <t>570,000원</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>71,200원</t>
+          <t>558,500원</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>+19.9%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>주가가 20일선(636,600원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -16015,16 +17162,16 @@
         </is>
       </c>
       <c r="O53" s="3" t="n">
-        <v>47.8</v>
+        <v>32.5</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
@@ -16034,7 +17181,7 @@
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>[71000.0, 69700.0, 68400.0, 70400.0, 70200.0, 76600.0, 73000.0, 76500.0, 81700.0, 82100.0, 80900.0, 82500.0, 82900.0, 86200.0, 87900.0, 88000.0, 81400.0, 73800.0, 73400.0, 74900.0]</t>
+          <t>[675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 582000.0, 576000.0]</t>
         </is>
       </c>
     </row>
@@ -16046,12 +17193,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>000810.KS</t>
+          <t>030200.KS</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -16061,42 +17208,42 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>582,000원</t>
+          <t>50,400원</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>+96,000원 (+19.75%)</t>
+          <t>-14,000원 (-21.74%)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>553,000원</t>
+          <t>49,400원</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>576,000원</t>
+          <t>53,400원</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>564,500원</t>
+          <t>47,900원</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
+          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(642,100원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>최근 1일 전(2026-10-14) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -16110,16 +17257,16 @@
         </is>
       </c>
       <c r="O54" s="3" t="n">
-        <v>33.7</v>
+        <v>37.8</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
@@ -16129,7 +17276,7 @@
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>[686000.0, 675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 582000.0]</t>
+          <t>[53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 49900.0, 50400.0]</t>
         </is>
       </c>
     </row>
@@ -16141,12 +17288,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>145020.KS</t>
+          <t>017670.KS</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -16156,42 +17303,42 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>223,500원</t>
+          <t>78,300원</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>-40,000원 (-15.18%)</t>
+          <t>-19,800원 (-20.18%)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>197,000원</t>
+          <t>74,400원</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>223,500원</t>
+          <t>77,500원</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>219,000원</t>
+          <t>76,000원</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>🔴 오늘 단기 매도 (과열 차익실현)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>RSI 23.1, 20일선 이격도 +13.5%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
+          <t>주가가 20일선(85,945원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -16205,16 +17352,16 @@
         </is>
       </c>
       <c r="O55" s="3" t="n">
-        <v>23.1</v>
+        <v>31.9</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
@@ -16224,7 +17371,7 @@
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>[231000.0, 232000.0, 235500.0, 231000.0, 231500.0, 214000.0, 206000.0, 190400.0, 187000.0, 186100.0, 183300.0, 179700.0, 180600.0, 180100.0, 181500.0, 183600.0, 182800.0, 180000.0, 169900.0, 172500.0]</t>
+          <t>[90100.0, 88000.0, 88100.0, 87600.0, 89200.0, 87000.0, 87300.0, 87100.0, 88200.0, 86200.0, 85600.0, 86300.0, 88400.0, 88400.0, 87400.0, 84100.0, 79700.0, 80000.0, 81900.0, 78300.0]</t>
         </is>
       </c>
     </row>
@@ -16236,12 +17383,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>030200.KS</t>
+          <t>034020.KS</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -16251,65 +17398,65 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>49,900원</t>
+          <t>62,900원</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>-14,500원 (-22.52%)</t>
+          <t>-41,300원 (-39.64%)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>48,900원</t>
+          <t>61,600원</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>53,400원</t>
+          <t>87,000원</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>47,400원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>+9.2%</t>
+          <t>+41.1%</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-14) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O56" s="3" t="n">
-        <v>33.1</v>
+        <v>24.4</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
@@ -16319,7 +17466,7 @@
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>[52700.0, 53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 49900.0]</t>
+          <t>[87000.0, 86200.0, 83800.0, 85400.0, 84900.0, 85300.0, 86500.0, 81700.0, 82000.0, 79700.0, 81600.0, 82100.0, 81100.0, 81500.0, 80500.0, 78000.0, 71500.0, 70200.0, 69400.0, 62900.0]</t>
         </is>
       </c>
     </row>
@@ -16331,12 +17478,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>010140.KS</t>
+          <t>055550.KS</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -16346,42 +17493,42 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>19,000원</t>
+          <t>93,700원</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>-9,150원 (-32.56%)</t>
+          <t>-6,100원 (-6.11%)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>18,600원</t>
+          <t>91,800원</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>22,100원</t>
+          <t>114,500원</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>18,000원</t>
+          <t>89,000원</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>+19.0%</t>
+          <t>+24.8%</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-14) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -16395,16 +17542,16 @@
         </is>
       </c>
       <c r="O57" s="3" t="n">
-        <v>41</v>
+        <v>28.3</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
@@ -16414,7 +17561,7 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>[21400.0, 22100.0, 20700.0, 20200.0, 21500.0, 20800.0, 20600.0, 20600.0, 20250.0, 20100.0, 19330.0, 19700.0, 19720.0, 19960.0, 19700.0, 19540.0, 18860.0, 18010.0, 18360.0, 18950.0]</t>
+          <t>[114600.0, 112200.0, 112100.0, 113300.0, 110100.0, 113100.0, 113200.0, 109300.0, 111300.0, 110500.0, 106100.0, 103800.0, 104800.0, 103600.0, 103300.0, 99500.0, 100500.0, 99700.0, 95000.0, 93700.0]</t>
         </is>
       </c>
     </row>
@@ -16426,12 +17573,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>017670.KS</t>
+          <t>352820.KS</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -16441,42 +17588,42 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>81,900원</t>
+          <t>162,500원</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>-16,200원 (-16.51%)</t>
+          <t>-92,800원 (-36.32%)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>80,300원</t>
+          <t>159,500원</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>90,900원</t>
+          <t>175,500원</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>77,800원</t>
+          <t>154,500원</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>+10.2%</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-14) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -16490,16 +17637,16 @@
         </is>
       </c>
       <c r="O58" s="3" t="n">
-        <v>37.3</v>
+        <v>46.6</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
@@ -16509,7 +17656,7 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>[90900.0, 90100.0, 88000.0, 88100.0, 87600.0, 89200.0, 87000.0, 87300.0, 87100.0, 88200.0, 86200.0, 85600.0, 86300.0, 88400.0, 88400.0, 87400.0, 84100.0, 79700.0, 80000.0, 81900.0]</t>
+          <t>[175700.0, 173100.0, 169900.0, 165600.0, 165900.0, 162500.0, 156300.0, 156800.0, 161900.0, 158700.0, 156600.0, 156200.0, 155300.0, 157000.0, 167000.0, 163900.0, 156500.0, 163400.0, 163800.0, 162700.0]</t>
         </is>
       </c>
     </row>
@@ -16521,12 +17668,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>042660.KS</t>
+          <t>271560.KS</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -16536,65 +17683,65 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>67,400원</t>
+          <t>106,000원</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>-58,400원 (-46.42%)</t>
+          <t>-32,200원 (-23.33%)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>63,700원</t>
+          <t>103,500원</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>66,700원</t>
+          <t>116,000원</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>65,400원</t>
+          <t>100,500원</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+11.9%</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(78,225원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O59" s="3" t="n">
-        <v>23.6</v>
+        <v>32.6</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
@@ -16604,102 +17751,7 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>[85600.0, 85900.0, 82400.0, 81300.0, 83600.0, 82900.0, 81800.0, 81600.0, 79600.0, 80000.0, 78600.0, 78800.0, 78500.0, 78800.0, 77200.0, 74100.0, 72000.0, 67300.0, 67100.0, 67400.0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>신한지주</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>055550.KS</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>증권사 공식리서치</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>95,000원</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>-4,800원 (-4.81%)</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>93,100원</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>114,500원</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>90,200원</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>+23.1%</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>관망 (HOLD)</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>중립 구간 유지 중</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>보유 / 중립 (HOLD)</t>
-        </is>
-      </c>
-      <c r="N60" s="3" t="inlineStr">
-        <is>
-          <t>장기 추세 유지</t>
-        </is>
-      </c>
-      <c r="O60" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="P60" s="3" t="inlineStr">
-        <is>
-          <t>-11.6%</t>
-        </is>
-      </c>
-      <c r="Q60" s="3" t="inlineStr">
-        <is>
-          <t>81.5%</t>
-        </is>
-      </c>
-      <c r="R60" s="3" t="inlineStr">
-        <is>
-          <t>최근 특이 뉴스 없음</t>
-        </is>
-      </c>
-      <c r="S60" s="3" t="inlineStr">
-        <is>
-          <t>[112900.0, 114600.0, 112200.0, 112100.0, 113300.0, 110100.0, 113100.0, 113200.0, 109300.0, 111300.0, 110500.0, 106100.0, 103800.0, 104800.0, 103600.0, 103300.0, 99500.0, 100500.0, 99700.0, 95000.0]</t>
+          <t>[115300.0, 116000.0, 111400.0, 113500.0, 111500.0, 111200.0, 110900.0, 110100.0, 111500.0, 111500.0, 106900.0, 106100.0, 105300.0, 106500.0, 106100.0, 104200.0, 105600.0, 106500.0, 105600.0, 105800.0]</t>
         </is>
       </c>
     </row>
@@ -16721,7 +17773,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17147,12 +18199,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5,684.67</t>
+          <t>5,569.79</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>▼ -324.14 (-5.39%)</t>
+          <t>▼ -439.02 (-7.31%)</t>
         </is>
       </c>
     </row>
@@ -17174,12 +18226,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>778.72</t>
+          <t>762.96</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>▼ -45.16 (-5.48%)</t>
+          <t>▼ -60.92 (-7.39%)</t>
         </is>
       </c>
     </row>
@@ -17255,12 +18307,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>1,342.58</t>
+          <t>1,347.58</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>▲ +1.72원 (+0.13%)</t>
+          <t>▲ +6.72원 (+0.50%)</t>
         </is>
       </c>
     </row>
@@ -17282,12 +18334,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>847.10</t>
+          <t>852.00</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>▲ +2.30원 (+0.27%)</t>
+          <t>▲ +7.20원 (+0.85%)</t>
         </is>
       </c>
     </row>
@@ -17309,12 +18361,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>1,500.20</t>
+          <t>1,512.10</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>▲ +5.20원 (+0.35%)</t>
+          <t>▲ +17.10원 (+1.14%)</t>
         </is>
       </c>
     </row>
@@ -17336,12 +18388,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>200.21</t>
+          <t>201.54</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>▼ -0.21원 (-0.10%)</t>
+          <t>▲ +1.12원 (+0.56%)</t>
         </is>
       </c>
     </row>
@@ -17618,27 +18670,27 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>110,560,000원</t>
+          <t>110,478,000원</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>108,902,000원</t>
+          <t>108,821,000원</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>119,415,000원</t>
+          <t>119,410,000원</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>105,032,000원</t>
+          <t>104,954,000원</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -17675,32 +18727,32 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3,281,000원</t>
+          <t>3,229,000원</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3,255,000원</t>
+          <t>3,203,000원</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>3,497,000원</t>
+          <t>3,494,500원</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>3,166,000원</t>
+          <t>3,116,000원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+9.1%</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -17710,7 +18762,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>RSI 39.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 36.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -17732,17 +18784,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>141,100원</t>
+          <t>141,000원</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>140,000원</t>
+          <t>139,900원</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -17752,12 +18804,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>136,200원</t>
+          <t>136,100원</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+10.4%</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -17767,7 +18819,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>RSI 41.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 41.6로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -17788,7 +18840,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="47" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -18580,7 +19632,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -18650,21 +19702,21 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>가장 저평가된 전력기기</t>
+          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -18674,37 +19726,37 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>변압기 29년 수주 논의 및 전선 상반기 수주 급증 5월 시가총액 약 6.9조원 도달 이후 7월말 2.2조원까지 약 68% 하락. 전선업체들의 수주잔고총계 연간 증가율은 24년 25.4%, 25년 21.2%에서 26년 상반기에만 23.2% 증가. 변압기에 이은 전선 부문의 호황이 확대되는 것을 감안할 때 펀더멘털 문제가 아닌 수급 측면의 주가 하락으로 판단.</t>
+          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_신한투자증권_일진전기_가장 저평가된 전력기기.pdf</t>
+          <t>2026-10-15_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2,350.8십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>252.8십억원</t>
+          <t>3,496십억원</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2,595.2십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>271.7십억원</t>
+          <t>4,566십억원</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -18720,21 +19772,21 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>유안타증권</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
+          <t>바닥 통과, 성장 엔진 점화</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -18749,37 +19801,37 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
+          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY 3Q26 연결 영업수익은 7.1조원(-1.1% YoY), 영업이익은 5,350억원(-0.6% YoY)으로 시장 컨센서스(7.0조원, 5,442억원)에 부합할 전망이다. 부동산 관련 일회성 비용 제거시 영업이익은 +2.8% YoY 증가한 것으로 추정된다. 별도 영업이익은 3,400억원으로 전년과 유사한 수준이 예상된다.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
+          <t>2026-10-15_유안타증권_KT_바닥 통과, 성장 엔진 점화.pdf</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27,426십억원</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>3,496십억원</t>
+          <t>2,076십억원</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27,905십억원</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>4,566십억원</t>
+          <t>2,256십억원</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY</t>
         </is>
       </c>
     </row>
@@ -18794,17 +19846,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 단기 실적 눈높이 조정</t>
+          <t>3Q26 잠정 실적 - ESS 판매 호조와 일회성 이익</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -18814,42 +19866,42 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>3분기 실적은 미국 판매체계 전환 영향으로 부진 휴젤의 3Q26 매출액은 1,009억원(-4.7% YoY), 영업이익 211억원(-55.5% YoY)으로 추정했다. 3Q26 영업이익은 미국 판매체계 전환 영향으로 전년 동기 대비 55.5% 감소할 것으로 보인다. 3분기는 미국 유통사 모델에서 CSO 모델로 전환하는 과정에서 일회성 매출 차감과 비용 증가가 동반되는 구간이었기 때문이다.</t>
+          <t>WHAT’S THE STORY? View, 2027년 영업이익 228% 성장 전망: 12MF EPS 및 BPS 상향을 감안하여 P/E 및 P/B 평균 밸류에이션상 목표주가를 9% 상향(46→50만원). 보상금 수령 효과를 제외하더라도 ESS 생산 병목 현상(모듈/팩 생산 차질)이 소멸되기 시작한 점과 보상금 제외하더라도 유럽 공장 가동률 상승에 힘입어 자동차 적자 축소도 지속되고 있는 점이 긍정적.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_미래에셋증권_휴젤_3Q26 Preview 단기 실적 눈높이 조정.pdf</t>
+          <t>2026-10-15_삼성증권_LG에너지솔루션_3Q26 잠정 실적 - ESS 판매 호조와 일회성 이익.pdf</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>486십억원</t>
+          <t>43,977십억원</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>174십억원</t>
+          <t>4,125십억원</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>657십억원</t>
+          <t>52,314십억원</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>272십억원</t>
+          <t>6,402십억원</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>3Q26 매출액은 1,009억원(-4)</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -18860,7 +19912,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -18869,12 +19921,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>바닥 통과, 성장 엔진 점화</t>
+          <t>이익 회복 위에 쌓이는 AIDC 가치</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -18889,37 +19941,37 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY 3Q26 연결 영업수익은 7.1조원(-1.1% YoY), 영업이익은 5,350억원(-0.6% YoY)으로 시장 컨센서스(7.0조원, 5,442억원)에 부합할 전망이다. 부동산 관련 일회성 비용 제거시 영업이익은 +2.8% YoY 증가한 것으로 추정된다. 별도 영업이익은 3,400억원으로 전년과 유사한 수준이 예상된다.</t>
+          <t>3Q26 Preview: 컨센서스 부합, 이익 회복 지속 3Q26 연결 영업수익은 4.5조원(+12.5% YoY), 영업이익은 5,340억원(+1,002.1% YoY)으로 시장 컨센서스(4.5조원, 5,240억원)에 부합할 전망이다. 3개 분기 연속 이어진 플래그십 단말기 출시와 3G 중심의 장기 미사용회선 정리 효과로 무선 ARPU가 상승한 것으로 파악된다. 마케팅비와 감가상각비도 안정화되며 비용 부담 완화 기조가 유지되고 있어, 영업이익 회복 추세는 이어질 전망이다.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_유안타증권_KT_바닥 통과, 성장 엔진 점화.pdf</t>
+          <t>2026-10-15_유안타증권_SK텔레콤_이익 회복 위에 쌓이는 AIDC 가치.pdf</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>27,426십억원</t>
+          <t>17,718십억원</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2,076십억원</t>
+          <t>2,017십억원</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>27,905십억원</t>
+          <t>18,101십억원</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2,256십억원</t>
+          <t>2,075십억원</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -18930,21 +19982,21 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>선방할 실적, FDC 본계약 기대</t>
+          <t>전력 수요 증가에 최적화된 사업 포트폴리오</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -18959,37 +20011,37 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 컨센서스 부합하는 실적 기록 예상 3Q26 연결 매출액 3 조 1,724 억원(+20.4% YoY, -1.8% QoQ), 영업이익 3,405억원(+43.0% YoY, +5.0% QoQ)을 기록하며 시장 예상치(3,446억원)에 부합하는 실적 기록할 것으로 예상한다. 조업일수 감소에도 불구하고 이번 분기에도 2도크 및 글로벌 오퍼레이션 효과로 인해 탑라인 유지, 그리고 환헷지 100% 정책 및 분기별 충당금 설정으로 통해 컨센서스 부합하는 이익 시현한 것으로 추정한다. 동사는 올해 상선 수주 80.5 억불로, 수주목표(57 억불)의 141%를 달성한 상황이며, 해양 수주는 44 억불로, 연내 미국 델핀 FLNG 2 호기(25 억불) 및 캐나다.</t>
+          <t>WHAT’S THE STORY? 원전 확대 정책의 최대 수혜주: 국내 유일의 원전 설비 통합 제작사로 원자로, 증기발생기 등 주기기에 해당하는 1차 계통부터, 증기터빈 및 발전기와 같은 2차 계통까지 원전 주요 설비 전반에 대한 제조 능력을 보유. 2020년대 들어 에너지 안보와 AI의 확산, 그리고 환경 규제 강화 등으로 전력 부족에 대한 우려가 가중되면서 무탄소 기저 발전원으로서 원전에 대한 관심이 고조.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_SK증권_삼성중공업_선방할 실적, FDC 본계약 기대.pdf</t>
+          <t>2026-10-15_삼성증권_두산에너빌리티_전력 수요 증가에 최적화된 사업 포트폴리오.pdf</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>3.2십억원</t>
+          <t>21,159십억원</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>4.0십억원</t>
+          <t>1,883십억원</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3,182십억원</t>
+          <t>24,494십억원</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>345십억원</t>
+          <t>2,350십억원</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>3Q26 연결 매출액 3 조 1,724억원(+20)</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -19000,21 +20052,21 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>유안타증권</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>이익 회복 위에 쌓이는 AIDC 가치</t>
+          <t>롯데손해보험 인수, 기대와 우려가 동반</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -19029,32 +20081,32 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 컨센서스 부합, 이익 회복 지속 3Q26 연결 영업수익은 4.5조원(+12.5% YoY), 영업이익은 5,340억원(+1,002.1% YoY)으로 시장 컨센서스(4.5조원, 5,240억원)에 부합할 전망이다. 3개 분기 연속 이어진 플래그십 단말기 출시와 3G 중심의 장기 미사용회선 정리 효과로 무선 ARPU가 상승한 것으로 파악된다. 마케팅비와 감가상각비도 안정화되며 비용 부담 완화 기조가 유지되고 있어, 영업이익 회복 추세는 이어질 전망이다.</t>
+          <t>사실과 설명: 롯데손해보험 인수계약 체결 - 신한지주는 롯데손해보험의 최대주주 보유 지분 77.04%를 6,933억원(주당 2,900원)에 매수하는 주식매매계약을 체결. 역산하면 회사가치(100%)를 9,000억원으로 산정한 결과로, 단순 산출 시 2025년 EPS 대비 17.5배, 1H26 말 자본 대비 0.91배에 해당하는 가격 - 신한지주는 롯데손해보험에 투입될 자금으로 (1)현재 가치로 잔여지분을 전량 인수할 경우의 총 9,000억원과 (2)인수 후 증자 예상 규모 3,000억원을 언급. 이때 3,000억원은 기존 계열사인 신한EZ손해보험에 향후 5년간 투입했어야 할 증자 규모의 예상치로, 롯데손보 인수에 따른 추가 자본 소요가 아니라고 설명 - 롯데손보의 2Q26 말 기본자본(T1)비율은 -6.4%를 기록.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_유안타증권_SK텔레콤_이익 회복 위에 쌓이는 AIDC 가치.pdf</t>
+          <t>2026-10-15_한화투자증권_신한지주_롯데손해보험 인수, 기대와 우려가 동반.pdf</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>17,718십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2,017십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>18,101십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2,075십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -19070,21 +20122,21 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>해양&amp;함정 수주 이젠 보여줘야 할 때</t>
+          <t>낮은 눈높이, 26.4Q에 거는 기대</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -19094,42 +20146,42 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>매수</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 시장예상치 하회하는 실적 기록 예상 3Q26 연결 매출액 3 조 4,995 억원(+15.8% YoY, -35.7% QoQ), 영업이익 5,050 억원(+74.3% YoY, -31.4% QoQ)으로, 시장예상치(5,633 억원)를 하회하는 실적 기록할 것으로 추정한다. 추석 연휴 및 하계 휴가로 이전 분기 대비 조업일수 9 일 감소했으며, 환율 하락 영향 반영됐기 때문이다. 이번 분기 선종별 믹스는 LNG 60%, 컨테이너선 및 VLCC 각각 15~20%, VLGC/VLAC 10%이며, 수주연도별 비중은 '22 년 7%, '23 년 13%, '24 년 40%, '25 년 40%로 추정된다.</t>
+          <t>[투자포인트] ■ 26.3Q 매출액 45.3조원 (-2.7% YoY) , 영업이익 2.4조원 ( -2.8% YoY, +5.4% OPM) 전망. 1) 26.3Q 글로벌 도매 판매 91.8만대 (-11.5% YoY)를 기록. 2) 26.3Q 원/달러 평균 환율은 1,420원으로 직전 분기 대비 80원 하락했으나, 원/달러 기말 환율이 동시에 1,352원으로 직전 분기 대비 197원 하락하며 부정적 환율효과 일정부분 상쇄할 것.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_SK증권_한화오션_해양&amp;함정 수주 이젠 보여줘야 할 때.pdf</t>
+          <t>2026-10-15_iM증권_현대차_낮은 눈높이, 26.4Q에 거는 기대.pdf</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>16,586십억원</t>
+          <t>188,434십억원</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>-19.7십억원</t>
+          <t>12,744십억원</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>16,292십억원</t>
+          <t>194,151십억원</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>563십억원</t>
+          <t>14,461십억원</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>3Q26 연결 매출액 3 조 4,995 억원(+15)</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -19140,21 +20192,21 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>교보증권</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>롯데손해보험 인수 Comment</t>
+          <t>3Q26 Preview: 실적도, 성장 동력도 풍부</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -19164,17 +20216,17 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>롯데손해보험 인수 결정 신한지주는 전일 롯데손해보험의 지분 77.04%를 6,933 억원에 취득할 계획을 공시하였다. 100%로 단순 환산 시 9,000 억원 수준이며, 상반기 순자산 9,935억 기준으로 P/B 약 0.9배이다. 100% 인수가정한 9,000 억원과 EZ손해보험에 필요했던 증자 규모인 3,000 억원, 총 1.2 조원을 투입할 계획이다.</t>
+          <t>3Q26 시장 기대치 부합 전망 하이브 3Q26 매출액 1조 4,630억원(YoY +101.2%), 영업이익 1,655억원(YoY 흑전, OPM 11.3%)으로 영업이익 기준 시장 기대치(FnGuide 기준 1,636억) 부합 전망 [음반/음원] 매출액 2,679억원(YoY +41.1%, QoQ -18.0%) 전망. 3분기 앨범 판매량은 총 915만장 수준(써클차트 기준)으로 추정되며, 엔하이픈(229만장), &amp;TEAM(139만장), 코르티스(181만장) 등이 기여. 전분기 아티스트 앨범 발매가 집중된 데 따른 기저 부담으로 매출액은 QoQ 감소할 전망 [공연] 매출액 7,244억원(YoY +195.7%, QoQ +11.8%) 전망.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_SK증권_신한지주_롯데손해보험 인수 Comment.pdf</t>
+          <t>2026-10-15_교보증권_하이브_3Q26 Preview 실적도, 성장 동력도 풍부.pdf</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -19184,7 +20236,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>68.2십억원</t>
+          <t>-42.2십억원</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -19194,12 +20246,12 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>-64.7십억원</t>
+          <t>4.0십억원</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>3Q26 매출액 1조 4,630억원(YoY +101)</t>
         </is>
       </c>
     </row>
@@ -19210,21 +20262,21 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>유안타증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>L/O 계약금 인식 지연</t>
+          <t>실적은 시장 기대 부합 했으나…</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -19239,37 +20291,37 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>3Q26Pre: HM17321 계약금 인식 지연 연결 기준 매출액 3,740억원(+3.2% YoY, 이하 YoY 생략), 영업이익 445억원(-19.2%, OPM 11.9%)로 컨센서스를 하회할 전망. 이는 HM17321(UCN2 analogue) L/O이 미국 반독점법 관련 행정절차로 인해 지연된 영향으로 계약금(1.9억달러)는 4분기 인식될 것으로 예상. 로수젯과 스피리바, 오보덴스(프롤리아 시밀러) 등 도입 품목의 성장이 지속되고 있으며, 비만 치료제로 허가된 efpeglenatide도 10월말 첫 공급을 시작할 예정.</t>
+          <t>7~9월 Re: 시장 기대 부합 7~9월 누계 매출액 및 영업이익은 각각 9,203억원(YoY 10.8%), 1,519억원(YoY 6.7%)을 기록했다. 시장 기대에 부합하는 수치이다. 3Q 국가별 매출 성장률은 각각 국내 YoY 4.9%/ 중국 YoY 13.8%/ 베트남 8.3%/ 러시아 21.9%를 시현했다.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_유안타증권_한미약품_LO 계약금 인식 지연.pdf</t>
+          <t>2026-10-15_하나증권_오리온_실적은 시장 기대 부합 했으나….pdf</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1,910십억원</t>
+          <t>3,719.3십억원</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>496십억원</t>
+          <t>629.0십억원</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1,577십억원</t>
+          <t>3,830.7십억원</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>233십억원</t>
+          <t>677.1십억원</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>연결 기준 매출액 3,740억원(+3)</t>
+          <t>연결 매출액 및 영업이익을 각각 9,751억원(YoY 5)</t>
         </is>
       </c>
     </row>
@@ -19284,16 +20336,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -20026,12 +21078,12 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>⏳ 목표가 추적 중</t>
+          <t>🛑 손절 기준 터치</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -20041,7 +21093,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>1일 경과</t>
+          <t>2일차</t>
         </is>
       </c>
     </row>
@@ -20088,12 +21140,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>⏳ 목표가 추적 중</t>
+          <t>🛑 손절 기준 터치</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -20103,7 +21155,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>1일 경과</t>
+          <t>2일차</t>
         </is>
       </c>
     </row>
@@ -20150,12 +21202,12 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>⏳ 목표가 추적 중</t>
+          <t>🛑 손절 기준 터치</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -20165,7 +21217,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>1일 경과</t>
+          <t>2일차</t>
         </is>
       </c>
     </row>
@@ -20217,7 +21269,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -20227,7 +21279,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>1일 경과</t>
+          <t>2일 경과</t>
         </is>
       </c>
     </row>
@@ -20279,7 +21331,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -20289,7 +21341,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>1일 경과</t>
+          <t>2일 경과</t>
         </is>
       </c>
     </row>
@@ -20341,7 +21393,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -20351,7 +21403,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1일 경과</t>
+          <t>2일 경과</t>
         </is>
       </c>
     </row>
@@ -20398,17 +21450,17 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+          <t>🛑 손절 기준 터치</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>404,500원</t>
+          <t>393,500원</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -20460,22 +21512,22 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>49,900원</t>
+          <t>50,800원</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1일차</t>
+          <t>1일 경과</t>
         </is>
       </c>
     </row>
@@ -20522,17 +21574,17 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>⏳ 목표가 추적 중 (신규 진입)</t>
+          <t>🛑 손절 기준 터치</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>81,900원</t>
+          <t>79,600원</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -20584,20 +21636,82 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
+          <t>🛑 손절 기준 터치</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>-2.7%</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>18,570원</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>1일차</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>엔비디아 (NVIDIA)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>$221.30 (약 297,112원)</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>$217.98 (약 292,656원)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>$254.50 (약 341,679원)</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>$206.33</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>⏳ 목표가 추적 중 (신규 진입)</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>+0.8%</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>18,950원</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>+1.5%</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>$221.30</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
@@ -20623,7 +21737,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="53" customWidth="1" min="9" max="9"/>
   </cols>
@@ -21069,12 +22183,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>SK가스</t>
+          <t>에스원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>[공시분석]SK가스, 3년간 900억 자사주 매입·소각…'기업가치 제고' 주주환원 승부수</t>
+          <t>에스원, 4500억원 규모 자사주 취득 결정에 강세</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -21084,17 +22198,17 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>알파경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Wed, 14 Oct 2026 23:59:44 GMT</t>
+          <t>Thu, 15 Oct 2026 00:14:55 GMT</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB3Sm5OQVhMODZ0YnlMUC04Tmw4bmt0em1oUEE3YTBjcFBPOWFkZVh3UHloUC1YSGxnVjJQcHgzQ3lSVW11NEVmQmd2X1NQTk4ydzNwTjNRaFRKbGN6UWRDR2ZBRkk4d2wtbk5HU3FB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9LdkxXYlFGMTFTSlZhbk1vVDY3akpjQzZIU1hoRk9TNzRTVEV1ZTRPcWxVWjlNdkF6ZV9fZFl6QjVtSUgyY1NwWUVlM19OMDc2Ym02S1owdzFCdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -21116,12 +22230,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>스틱인베스트먼트</t>
+          <t>SK가스</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>[공시 Pick] 스틱인베스트먼트, 41억원 자사주 취득에 강세…장중 4%↑</t>
+          <t>[공시분석]SK가스, 3년간 900억 자사주 매입·소각…'기업가치 제고' 주주환원 승부수</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -21131,17 +22245,17 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>뉴스투데이</t>
+          <t>알파경제</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:20:00 GMT</t>
+          <t>Wed, 14 Oct 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE41b0xlNUs4c2FxVTNMaENRVHJFM1prZDE0dWw0dy1CY1VYOVN3LVV4REtOUDJhTTFhU2lCS1RMcDlQeU8tVG8xSXVSbURwRW9oOHNaelhKdktwRjhmSWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB3Sm5OQVhMODZ0YnlMUC04Tmw4bmt0em1oUEE3YTBjcFBPOWFkZVh3UHloUC1YSGxnVjJQcHgzQ3lSVW11NEVmQmd2X1NQTk4ydzNwTjNRaFRKbGN6UWRDR2ZBRkk4d2wtbk5HU3FB?oc=5</t>
         </is>
       </c>
     </row>
@@ -21163,12 +22277,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>엘컴텍</t>
+          <t>스틱인베스트먼트</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>엘컴텍, 20억원 규모 자사주 취득 결정</t>
+          <t>[공시 Pick] 스틱인베스트먼트, 41억원 자사주 취득에 강세…장중 4%↑</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -21178,17 +22292,17 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>뉴스투데이</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 07:22:52 GMT</t>
+          <t>Tue, 13 Oct 2026 05:20:00 GMT</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE13UXpQT2FyUjBQSkpSdFNtQVpJOHFGMExaeDFtajBra1h5dHl5S2dMbUV5TUdmMzFYZkF6b1RmSTd0TVk1NUZCOGN1Y1pWS3d1Rk50WmRUS19XZkJISzdJX3k1YXpPU2V3X3FhNkloOWs1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE41b0xlNUs4c2FxVTNMaENRVHJFM1prZDE0dWw0dy1CY1VYOVN3LVV4REtOUDJhTTFhU2lCS1RMcDlQeU8tVG8xSXVSbURwRW9oOHNaelhKdktwRjhmSWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -21210,12 +22324,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>엘컴텍</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니, 50억원 규모 자사주 취득 신탁계약 해지 결정</t>
+          <t>엘컴텍, 20억원 규모 자사주 취득 결정</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -21230,12 +22344,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:43:38 GMT</t>
+          <t>Tue, 13 Oct 2026 07:22:52 GMT</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1MVmRGS1NqcEJobXNpM01fNTlJbV9MeFZUeXBTVktGWV9XOWFlMHFET09BeW1rQ1RJdzVCR0I1OXM1UkpxM3Nnazk4RnBPbC1EaGFxM0FpVVpqYzZPRnlGb0plTEwyYmZDSXJXNW8yYmh5M0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE13UXpQT2FyUjBQSkpSdFNtQVpJOHFGMExaeDFtajBra1h5dHl5S2dMbUV5TUdmMzFYZkF6b1RmSTd0TVk1NUZCOGN1Y1pWS3d1Rk50WmRUS19XZkJISzdJX3k1YXpPU2V3X3FhNkloOWs1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -21257,12 +22371,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>메디앙스</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>메디앙스, 10억원 규모 자사주 취득 결정</t>
+          <t>더핑크퐁컴퍼니, 50억원 규모 자사주 취득 신탁계약 해지 결정</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -21277,12 +22391,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 05:39:56 GMT</t>
+          <t>Tue, 13 Oct 2026 05:43:38 GMT</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1TRmxBdndpdk9HTXZRTzdxNF8wSWpxQklLcDBRQks1TmxUSm4xRU9zVzRCSkxLZ3RUYy1JbS1vZXhhSnRxMXRJZnNGVHJLdkwyZzNTZTlLUWlCb0xkQUpnSWtnVURLcExLaGtWOTFMcnV6cGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1MVmRGS1NqcEJobXNpM01fNTlJbV9MeFZUeXBTVktGWV9XOWFlMHFET09BeW1rQ1RJdzVCR0I1OXM1UkpxM3Nnazk4RnBPbC1EaGFxM0FpVVpqYzZPRnlGb0plTEwyYmZDSXJXNW8yYmh5M0k?oc=5</t>
         </is>
       </c>
     </row>
@@ -21304,12 +22418,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>애니플러스</t>
+          <t>메디앙스</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>애니플러스, 20억원 규모 자사주 취득 공시</t>
+          <t>메디앙스, 10억원 규모 자사주 취득 결정</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -21319,17 +22433,17 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>전자신문</t>
+          <t>데이터투자</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Tue, 29 Sep 2026 07:00:00 GMT</t>
+          <t>Mon, 12 Oct 2026 05:39:56 GMT</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5pUEJfS3dXeldZeDBXUVVBQkVzOWJYcFdPbTd0UzNTNnAzZkMwTV9pY1VXUjQ5MjJmaGRnakpFN1NXOThDekFjY1BSUi0tdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1TRmxBdndpdk9HTXZRTzdxNF8wSWpxQklLcDBRQks1TmxUSm4xRU9zVzRCSkxLZ3RUYy1JbS1vZXhhSnRxMXRJZnNGVHJLdkwyZzNTZTlLUWlCb0xkQUpnSWtnVURLcExLaGtWOTFMcnV6cGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -21398,12 +22512,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>[공시 Pick] LS머트리얼즈, 美 연료전지용 UC 공급계약에 주가 강세…증시 급락 속 ‘역주행’</t>
+          <t>[공시] 파두, 227억원 기업용 SSD 컨트롤러 공급계약 체결</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -21413,17 +22527,17 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>뉴스투데이</t>
+          <t>글로벌이코노믹</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 01:48:00 GMT</t>
+          <t>Thu, 15 Oct 2026 01:32:10 GMT</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQTWoxNDVLVWtBTXVoS3MtWmFpd1UwMG9FYkVLM0EtcWhTbThJZFVkOWdVekxQMEpNR2ZMTklDQTZHdWpZU3BJSkJpTUQ2TnNVcW8weHFGM1pEVnBqNlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVHRxZDBxdjIxTkw2a1FtdmtGclJEMHJvc0dSeGtMT2NDRlhMM1FwVWc2eUtLdnE4V0t0R3JxM2JFRmxXc0ppRVJxSDZzYndNTlZpTjJMMjBMWUd5M0lJN0M4c3ZGZnNDZXEzMmhjalZyeE9KYjBZQkVXcWFYLVA4SEcteDQ0QThr?oc=5</t>
         </is>
       </c>
     </row>
@@ -21659,7 +22773,7 @@
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
@@ -21889,32 +23003,32 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>🌐 [경제·사회 심층 리포트] 트럼프 밀착의 숨겨진 배경과 구조적 쟁점</t>
+          <t>🌐 [경제·사회 심층 리포트] 트럼프 ICC 제재는 불법 간섭의 숨겨진 배경과 구조적 쟁점</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>트럼프 밀착</t>
+          <t>트럼프 ICC 제재는 불법 간섭</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '트럼프 밀착' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
+          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '트럼프 ICC 제재는 불법 간섭' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **['트럼프 밀착' 베네수 국회의장 8년 만에 美 제재서 벗어나]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 송광호 특파원 = 베네수엘라 자원 문제와 관련해 미국의 주요 소통 창구 중 한명으로 알려진 호르헤 로드리게스 국회의장이.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
+          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭"]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭".&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; 눈에 띄는 애니메이션을 해설하는 포커스 온 유 모드 연출 페이지 Histoire pour tous. 아르헨티나, 이란 혁명수비대 테러 조직 지정…트럼프 밀착 행보 KBS 뉴스.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
+          <t>이 사안은 과거 수년간 시장과 정책 당국 간에 누적되어 온 구조적 과제가 수면 위로 표출된 결과입니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; 글로벌 공급망 재편과 정책 기조의 전환이 이어지며 시장의 압력이 누적되어 왔습니다.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 최근의 제도적 변화와 주요 이해관계자들의 입장 차이가 정면으로 맞닥뜨리면서 본격적인 쟁점으로 급부상했습니다.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 베이조스·트럼프 밀착…블루오리진 계약 급증 한국경제. 콜롬비아 ‘극우’ 후보 당선에···“트럼프 밀착, 민주주의 파괴 가속화할 것” 경향신문.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
+          <t>언론 헤드라인 이면에는 각 주체들의 치열한 손익 계산이 숨겨져 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 정책 당국은 거시적 안정과 공공성을 명분으로 내세우고 있으나, 산업계는 규제 비용과 수익성 방어에 비상이 걸렸습니다.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 결국 누가 비용을 부담하고 누가 장기적인 주도권을 쥐느냐를 둘러싼 치열한 헤게모니 싸움으로 해석할 수 있습니다.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -21929,12 +23043,12 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015021000087</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9ZcTM4YlJJUTFoUXZ5ZGZydnpQUnVFSGtHeHhOQWo0VUU3Wm9oc2VQMlFvM2c4SnVwVFRfNHh5NThkWERpQ3NZLWZRaXZvMG9aRE5PLUNxWXVJUjVaUDE4c3FfREhTczA?oc=5</t>
         </is>
       </c>
     </row>
@@ -21956,32 +23070,32 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>🔥 [트렌드 &amp; 소비 인사이트] 지그재그 열풍의 배경과 소비 심리 분석</t>
+          <t>🔥 [트렌드 &amp; 소비 인사이트] “오픈 열풍의 배경과 소비 심리 분석</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>지그재그</t>
+          <t>“오픈</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>요즘 왜 난리일까? '지그재그' 품절 대란과 오픈런 이면에 숨은 소비 심리와 바이럴 구조를 짚어봅니다.</t>
+          <t>요즘 왜 난리일까? '“오픈' 품절 대란과 오픈런 이면에 숨은 소비 심리와 바이럴 구조를 짚어봅니다.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>지금 거리와 SNS에서 소비자들이 가장 열광하고 있는 화제의 중심은 단연 **[지그재그, 16일부터 성수동서 팝업스토어…쇼핑몰 50곳 참여]** 입니다.&lt;br&gt;• &lt;b&gt;트렌드 현황:&lt;/b&gt; 지그재그, 16일부터 성수동서 팝업스토어…쇼핑몰 50곳 참여 연합뉴스.&lt;br&gt;• &lt;b&gt;열풍의 온도:&lt;/b&gt; 매장 문이 열리기 전부터 줄을 서는 '오픈런'과 온라인 품절 사태가 잇따르며, 단순한 유행을 넘어 하나의 강력한 문화적 현상으로 자리 잡았습니다.</t>
+          <t>지금 거리와 SNS에서 소비자들이 가장 열광하고 있는 화제의 중심은 단연 **[“오픈 1시간 만에 품절”…젠틀몬스터×프라다, 한국서도 완판]** 입니다.&lt;br&gt;• &lt;b&gt;트렌드 현황:&lt;/b&gt; “오픈 1시간 만에 품절”…젠틀몬스터×프라다, 한국서도 완판 스타패션.&lt;br&gt;• &lt;b&gt;열풍의 온도:&lt;/b&gt; 매장 문이 열리기 전부터 줄을 서는 '오픈런'과 온라인 품절 사태가 잇따르며, 단순한 유행을 넘어 하나의 강력한 문화적 현상으로 자리 잡았습니다.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 무신사 vs 지그재그 '디스전' 벌이더니…둘 다. 무신사·지그재그, 대놓고 붙었다…패션 플랫폼 디스전의 탄생 한국섬유신문.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
+          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 분당서울대병원, 23년 발자취 담은 역사홍보관 ‘스페이스 이음’ 오픈 후생신보. 30년 SK텔레콤오픈 역사 속으로...기업 후원 생태계 흔들리나 더팩트.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>소비자들이 기꺼이 시간과 비용을 들여 줄을 서는 심리적 이유를 쉽게 풀어보았습니다.&lt;br&gt;• &lt;b&gt;소비 심리:&lt;/b&gt; 2030 '가을 산행' 인기 전망…지그재그, '등산' 검색량 폭증 뉴스저널리즘. 지그재그, 슈즈 카테고리 상반기 거래액 15% 성장…직진배송 영향도 Daum.&lt;br&gt;• &lt;b&gt;심리적 기제:&lt;/b&gt; 단순히 제품의 기능 때문이 아니라, '희소한 트렌드를 남들보다 빠르게 경험하고 인증했다'는 심리적 만족감과 소속감(디토 소비 및 포모 심리)이 지갑을 열게 만드는 핵심 동기입니다.</t>
+          <t>소비자들이 기꺼이 시간과 비용을 들여 줄을 서는 심리적 이유를 쉽게 풀어보았습니다.&lt;br&gt;• &lt;b&gt;소비 심리:&lt;/b&gt; AI 안전협약 속 ‘오픈모델 규제’ 부상… 책임 기준 새 쟁점 이코노미톡뉴스. “서버는 해킹·회의실은 도청 위협” 오픈AI 사건 파장, 기업 내부 통제 시험대 The Economy Korea.&lt;br&gt;• &lt;b&gt;심리적 기제:&lt;/b&gt; 단순히 제품의 기능 때문이 아니라, '희소한 트렌드를 남들보다 빠르게 경험하고 인증했다'는 심리적 만족감과 소속감(디토 소비 및 포모 심리)이 지갑을 열게 만드는 핵심 동기입니다.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -21991,17 +23105,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>📌 **팝업스토어(Pop-up Store)**: 짧은 기간 동안 임시로 운영되는 매장으로, 단순 물건 판매를 넘어 소비자에게 특별한 브랜드 체험과 인증샷을 유도하는 현대 유통의 핵심 집객 전략입니다.</t>
+          <t>📌 **희소성 마케팅(Scarcity Marketing)**: 수량이나 판매 기간을 극도로 제한하여 '지금 구매하지 않으면 품절된다'는 조급함(FOMO)을 자극하고 소장 가치를 극대화하는 소비 심리 기법입니다.</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>스타패션</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1QUzdRcTJLWFNJVzZhUHZiS3BGZEZkZEljNWVZUE80bGVrZ2RlcmhBTWNsclVFTzNrNDNwSDhuMmpuQkhRTmN2LXBtVTFoMzcwTkJMMzdOM2VNWjjSAWBBVV95cUxQTjJ1OEQyVlpjZkpIS3VOb3JjbGpOSFp4S2JXaE9JSGxOZGVkS3hsNmNCSlZfUjc1dV9YZzlCWG1jZmJubUh1NFpzeEFreS1OdVNVRU1XLVZSWDlmaUp5akM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1QVnBDX2JJZVBuYTgzek10UThCUTVMWXFCSGVSNVNSOWFja3lLMVVYRWVBYmlzMVlNZ1VSTDBkMXY3RXpDdG52YjlnYmtvM3BUcHR0WlY0WUV4YXJrYXow?oc=5</t>
         </is>
       </c>
     </row>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -5227,22 +5227,22 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>공수처 "조희대 업무추진비 수사 예정", 중수청장 후보자 "수사 가능"</t>
+          <t>[속보] 국회 행안위, 김지용 중수청장 후보자 청문보고서 채택</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>공수처 "조희대 업무추진비 수사 예정", 중수청장 후보자 "수사 가능". 아울러 행안위, 오늘 김지용 청문보고서 채택‥與 '적격' 의견.</t>
+          <t>국회 행안위, 김지용 중수청장 후보자 청문보고서 채택.</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>뉴스타파</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE52a0pKejBqUm52SEoyVi1SVW1vQ09MY0hsZGJ6NHNlUG1WaUxTc0pMQkNXalJVMGkzaWVBWmJNOWtQNUYyV1hjTzJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFB6TFpTSkJPRU52d3hWWEFBcERxdlppUVZ5NlR1QkFlY203S1lvNDhyU3JRV3RWRWt1MS1USWNPUlpvZ3pWVlV0RnJrbXdLTVN5cHp1VjZ5dGlod21HaXZJclJybGRFMUhva0E?oc=5</t>
         </is>
       </c>
     </row>
@@ -5259,27 +5259,27 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>李, 임광현 비서실장에 임명장…강훈식엔 공로패</t>
+          <t>이 대통령 손 들어 준 법제처장‥"대법원장 재제청, 헌법상 책무"</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>李, 임광현 비서실장에 임명장강훈식엔 공로패. 아울러 김민석, ‘강훈식 서울시장 후보설’에 “역량 검증된 전국적 인물···가능성 열려 있어”.</t>
+          <t>이 대통령 손 들어 준 법제처장‥"대법원장 재제청, 헌법상 책무".</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9qb2xyWHlLZGsxb0dZX3BWQXVNeWMwbl81Zk9mZFZwRElVR2tWaGVaVWFkUnczc0RCTnhsT0swcWdHNXVqOUZ6TVVOLUFjYlNnblBsY05SXy14Mlk3Q0loT2liNUdoSkFPV1dvOTY5aVUyS0dJUDFJ0gFmQVVfeXFMTnVNeExQOWw3MDE3cTc4OW40N2kwQmNpZjBqaHJlc2UxVVZEZE9MeGEtYjFBTWFYcmxEaWM0VDNjbWxwbEpNajVDVlJyQ3RjTVVZRV9QRktPV0dpSU54MjZjaFI1MVd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9UdWtaU2FFS0pWMDA0SFdEdy1pcEE2YndTSUNGS1dtZlNDZThKcGN4S2oxMmI4TVprZHZkWVhJX2d2WFdHdzlWZVNtdG55YlRlYzkwSjVfdHU3Mk5Yb0ZIWHBrTk5uV0xaUGVuMnVEVHNnaVNuWG9hN9IBeEFVX3lxTFBwQTVOUklSd3RGUnBsSGgxMnFMdERMSllVWDBGcGEyYV9XZ3RWTDhRdXdPbmZYVVpuYmlydHl2djQ4dlRjekRTaDJ4TEZtN2hyRl9nWmpybUFYc3FQb3RFVTNXb0t6OUdkcnlDNGgxR2Q4SDRZSDJ5SA?oc=5</t>
         </is>
       </c>
     </row>
@@ -5296,27 +5296,27 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>김민석, 신천지 논란에 "당헌당규 지키며 처리 중"</t>
+          <t>[속보] 특검, 대법원에 김건희 추가 구속영장 발부 요청</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>김민석, 신천지 논란에 "당헌당규 지키며 처리 중".</t>
+          <t>특검, 대법원에 김건희 추가 구속영장 발부 요청. 아울러 범행 전 휴학계 제출·현금 600만 원 소지한 인천 흉기 난동범···경찰 “도피 의혹” 조사.</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE04bDMxN2NiSmF1SENCZWprZDFxNmZmUmU3aWZ3aUNqTVdSMEczMGJtWE1vVDc3T0Q2WGZ4ZlM5YXFLYXNTZU1MU3VZLVRVSmxLdXRCdnZBektGOFJmbXV6T0Zhd2NjWVFUVUpNaGNOaGJLUXk0ODBFSdIBeEFVX3lxTFBIY0RfeGNXWUNUMGdyUFdTZnNtN3JEUGtUTWswR3NMX1JZVy0wZkpUb0d0dl8ybHBsWUkyS2JCLTlwRE5wbzZjc0U3bmF4V0lQSk1EaGFhUlB1MkFzWWlEcXZDOV9RWVNMWTlvcnJmX1B1bHl6cGEtUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE5GZm9PYzdLQnMtcVFxbzl5ZElIUG10eWtmajRaRWhnNUFhQmZCVTVBX24weEl6X0hxVUhzbU0yc3lJZG4yT3JxT2x4Ung2Yng5Y3lkag?oc=5</t>
         </is>
       </c>
     </row>
@@ -5333,27 +5333,27 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>알래스카 가스관공사 전 임원 “한국 750억달러 넘게 낼 수도” [인터뷰]</t>
+          <t>野, 외교·통일·국방 세종행에 "유사시 서울 포기 메시지 될 수도"</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>알래스카 가스관공사 전 임원 “한국 750억달러 넘게 낼 수도”. 아울러 트럼프 "한국, 알래스카에 500억 달러 투자‥무역·투자합의 일부".</t>
+          <t>野, 외교·통일·국방 세종행에 "유사시 서울 포기 메시지 될 수도". 아울러 주호영 “국방·외교부 세종 이전은 국가 안위 흔드는 자해적 결정”.</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZU8waXlhQlJxTmI4dUc5VzZLakpSWUZ6bEdodHk0MnF0VzRLZEJqYy1nUnVIR256cUdlV2luNGdmZmpoMThKbW5kRnJmMnI1S3RNREtlY0hHTVo3MkJLMno0RzAtMTk3cnJKYVVsaEp6ajRMeFZkN0gwM08yVkFKS3Zn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQWgzeDZDRU1meVJxTTVfXzRIWDl6WHdNYmxNVGlhdEtvSW4yc1F3V0ZPR1k3MDM2LUVraWQtRWxaNHZPOFg0R1JFTkl2Tm5TaGpuckczMmozQmsxbF9qTjJTQk1NS2Rxek04NjZXM0p5YVVqUWUxOE9fallDaXFDeXNyYktyUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5370,27 +5370,27 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>"의원직 박탈될 수도?" 한동훈 고발 예고 #shorts #오마이tv</t>
+          <t>해리스 "트럼프의 한미훈련 중단·징벌적 관세, 동맹 강화에 역행"</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>"의원직 박탈될 수도?" 한동훈 고발 예고 #shorts #오마이tv.</t>
+          <t>해리스 "트럼프의 한미훈련 중단·징벌적 관세, 동맹 강화에 역행". 아울러 아산기념강좌 참석한 정몽준 아산재단 이사장.</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE5WbUV5bUZjOE42S0JUY2pzMldHZ2haSGVLRjc0LUdlZUhfU3VhTE5NVm1TdzVXQkhiVm1IRVJzc0Q0VXVETHpJT0p3V2tVSk12aEdWQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOUWR5dU9nZnV6eHRMMmVGdDJndEZ5Q1pud0xiM2hwU2JOSkxiU1BwaEg4ZVdxUVVwLWNNQng2ek1SOXR2ZXVWQXREZEZpY29KQnQweC1fd3hzNG9LQlpEN2VrX3E3NUhWa2k1QTVwN3VvenFYWVExeUUyNE40eEZ4bWM1VlJrNHdpWVVNTVZJTlhUZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5407,17 +5407,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>오세훈 "용산공원 개발은 특별법 위반…주택공급 규제 풀어야"</t>
+          <t>[영상] 로봇·드론·무인체계 총출동…눈앞 다가온 韓육군의 '미래전투'</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>)= 오세훈 서울시장은 용산공원 부지 일부에 주택을 공급하려는 현 정부 구상에 대해 재차 반대 입장을 밝혔다.</t>
+          <t>) 14일 경기도 양평훈련장에서 육군의 '아미 타이거 플러스' 미래전 통합 전투 수행훈련이 진행됐습니다.</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015095200004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015137000704</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>법제처장 "DMZ 평화적 이용 가능…유엔사와도 의견 접근 있어"</t>
+          <t>韓총리 "창업열풍, 성장으로 이어져야…지역 창업생태계 만들것"</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>)= 조원철 법제처장은 15일 평화적 목적의 비무장지대 출입 권한을 유엔사가 아닌 한국 정부가 행사.</t>
+          <t>)= 한성숙 국무총리는 15일 "중요한 것은 창업 열풍이 지역으로 이어져 지역에서 기업의 성장으로 이어지고, 이것이.</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015093800001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015132600001</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5486,12 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>소진공 "홈플러스 입점업체 긴급자금 금리 인하 적극 협의"</t>
+          <t>북한 영변 핵시설 내부 3D로 구현한다…정부, 가상모델 구축</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>)= 인태연 소상공인시장진흥공단 이사장은 15일 홈플러스 입점 업체에 지원한 긴급 자금에 대해 추가 금리 인하를.</t>
+          <t>)= 정부가 영변 핵시설 내 우라늄 농축시설 내부 공간을 3차원 가상공간으로 구현하는 연구에 착수한다.</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015094500030</t>
+          <t>https://www.yna.co.kr/view/AKR20261015128600017</t>
         </is>
       </c>
     </row>
@@ -5518,17 +5518,17 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>국힘 최고위서 '용인갑 조직위원장 경선 논란'에 고성 충돌</t>
+          <t>국방부, 軍수사 지휘·감독 '서면으로' 규칙개정…투명성 강화</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>)= 국민의힘 지도부가 15일 연 최고위원회의에서 양향자 최고위원이 결선까지 갔다가 패배한 '경기.</t>
+          <t>)= 국방부가 군 수사기관에 대한 지휘·감독의 투명성을 높이기 위한 규정 개정을 추진한다.</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015088700001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015115100504</t>
         </is>
       </c>
     </row>
@@ -5560,12 +5560,12 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>"성남 라인"·"정치 공세"…기노위 '기관장 자소서 제출' 공방</t>
+          <t>데이터처장, 국토부·국세청 통계 오류에 "신뢰얻는 노력 지속"</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>)= 국회 기후에너지환경노동위의 15일 국정감사는 남광우 한국환경산업기술원장을 비롯한 기관장들의 인사 자료 제출.</t>
+          <t>)= 안형준 국가데이터처장은 15일 국토교통부·국세청 통계 오류에 관한 지적에 "오류를 공개해서 바로 잡고 신뢰를.</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015087000001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015133300002</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>김상훈 "지방정부 조달 자율화 계약형태 수의계약이 96.5%"</t>
+          <t>2025년까지 옮긴다더니 2031년으로…포항 해병대 사격장 갈등</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>)= 경기도와 전북도에서 '지방정부 조달 자율화'를 시범 운영한 결과, 소액 등 수의 계약이 96.5%에 달하는.</t>
+          <t>)= 경북 포항시 오천읍 주민들이 해병대 1사단의 사격장 이전 지연과 부대 내 배수시설 확충 미이행에 반발해 이틀째.</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015092900063</t>
+          <t>https://www.yna.co.kr/view/AKR20261015126100053</t>
         </is>
       </c>
     </row>
@@ -5629,17 +5629,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>여야, '불법사찰 의혹' 공방…'김현미·김건희' 증인 요구 맞불</t>
+          <t>국힘, 이진숙 국정감사 제척안 헌재 가처분·권한쟁의 청구</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>)= 여야는 15일 국회 국토교통위원회의 한국부동산원과 주택도시보증공사 등을 대상으로 한 국정감사에서 야당.</t>
+          <t>)= 국민의힘은 국회 과학기술정보방송통신위원회가 이진숙 의원을 방송미디어통신위원회 국정감사에서 제척하는 안을 여권.</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015090400001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015127000001</t>
         </is>
       </c>
     </row>
@@ -5671,12 +5671,12 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>진보당, 전남광주 농어촌기본소득 "지역별 차등지급 반대"</t>
+          <t>캠코 선박금융 2조8천억원 중 90% 수도권 해운사에 지원</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>)= 진보당 전남광주통합특별시당이 농어촌기본소득 지급 대상을 모든 농어촌으로 확대하고 지역별 차등지급을 철폐할.</t>
+          <t>)= 공적 자산관리 전문기관인 한국자산관리공사 가 시행하는 선박금융 지원이 수도권 소재 해운사에 90% 편중돼.</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015085300054</t>
+          <t>https://www.yna.co.kr/view/AKR20261015120500051</t>
         </is>
       </c>
     </row>
@@ -5703,17 +5703,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>법제처장 "대법원장 제청권은 제안 의미…재제청, 헌법상 책무"(종합)</t>
+          <t>국힘 충북도당 "민주당 선거앱 공짜 이용 의혹 진실 밝혀라"</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>)= 조원철 법제처장은 15일 이른바 대법관 후보자 재제청 문제를 둘러싼 청와대와 조희대 대법원장 간 갈등과.</t>
+          <t>)= 국민의힘 충북도당은 15일 "이강일 국회의원과 더불어민주당 충북도당은 유료 선거앱 공짜 이용 관련 의혹에 대해.</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015077351001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015125900064</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>특검 "30개 시군구 선관위 투표자수 허위입력"…7곳 압수수색(종합)</t>
+          <t>구속 만기 앞둔 김건희…특검, 대법에 추가 구속영장 발부 요청</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>)= 이태한 선거관리위원회 특별검사팀이 지난 6·3지방선거에서 선거관리위원회들이 시간대별 투표자 수를 허위로 입력한.</t>
+          <t>)= 민중기 특별검사팀이 구속 만기를 앞둔 김건희 여사에 대한 추가 구속영장을 발부해달라고 15일 대법원에 요청했다.</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015080451004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015125500004</t>
         </is>
       </c>
     </row>
@@ -5782,12 +5782,12 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>법제처 국감도 조희대 공방…"직무유기"·"재제청 근거없어"</t>
+          <t>北, 日핵잠 도입 논의에 "핵무장화 노린 것, 열도에 재앙" 주장</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>)= 여야는 15일 국회 법제사법위원회의 법제처에 대한 국정감사에서도 조희대 대법원장의 대법관 후보자 재제청 거부를.</t>
+          <t>도입 가능성이 논의되는 일본을 향해 "핵무장화를 노린 것"이라며 "기필코 열도에.</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015088900001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015120300504</t>
         </is>
       </c>
     </row>
@@ -5814,17 +5814,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>"이사장 해외출장 보내려"…교육시설안전원, 허위초청문서 작성</t>
+          <t>'퇴임' 강훈식 "李대통령, 탁월·좋은 분…모시는 내내 감탄"</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>)= 한국교육시설안전원이 이사장의 국외 출장 근거 마련을 위해 직무 관련 여행사에 허위 초청문서를 작성할 것을 요구.</t>
+          <t>)= 강훈식 전 대통령 비서실장은 15일 퇴임하면서 "책임을 지는 것이 옳다는 생각에는 변함이 없다"고 밝혔다.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015040200001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015119500001</t>
         </is>
       </c>
     </row>
@@ -5851,17 +5851,17 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>英해리왕자, 상이군경체전 축하 메시지…"도약 위한 발판 되길"</t>
+          <t>경찰, '당원 가입 관여 의혹' 함안군수실·국힘 도당사 압수수색(종합)</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>)= 찰스 3세 영국 국왕의 차남 해리 왕자가 15일 수원에서 진행 중인 제60회 전국상이군경체육대회 참가자들에게.</t>
+          <t>)= 공무원 신분으로 국민의힘 당원 가입에 관여했다는 의혹을 받는 차석호 경남 함안군수에 대해 경찰이 강제수.</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015084900504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015070451052</t>
         </is>
       </c>
     </row>
@@ -5888,17 +5888,17 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>李대통령 지지율 44%…민주, 33%로 현정부 출범 후 최저치[NBS](종합)</t>
+          <t>李대통령 "부마항쟁과 5·18, 내란극복 큰 의미…헌법에 새겨야"</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>)= 이재명 대통령의 국정운영을 긍정적으로 평가한 비율이 44%로 집계됐다는 여론조사 결과가 15일 나왔다.</t>
+          <t>)= 이재명 대통령은 15일 "5·18는 점에 대해서는.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015078251001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015118700001</t>
         </is>
       </c>
     </row>
@@ -5930,12 +5930,12 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>레이저 대공무기 천광, 드론 요격 시연 성공…1회 발사 2천원</t>
+          <t>韓총리 "돌봄은 함께 풀 과제…지역별 인프라 격차 큰 문제"</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>)= 한화시스템 은 지난 14일 육군본부 주관으로 열린 '아미 타이거 플러스.</t>
+          <t>)= 한성숙 국무총리는 15일 "우리는 오랫동안 돌봄을 개인의 희생이나 한 가족의 유대관계에 의존해 왔다.</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015088300003</t>
+          <t>https://www.yna.co.kr/view/AKR20261015117500001</t>
         </is>
       </c>
     </row>
@@ -5962,17 +5962,17 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>美 "전작권 전환조건 변화"…韓 "골대 옮기면 영원히 불가능"</t>
+          <t>李대통령 "출범 500일…주요 지표 우수에도 민생회복 속도 더뎌"</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>)= 정빛나 국방부 대변인은 15일 제이비어 브런슨 주한미군사령관이 언급한 전시작전통제권 전환 조건 변화와.</t>
+          <t>)= 이재명 대통령은 15일 "내일은 우리 국민주권정부가 출범 500일을 맞이하는 날"이라며 "어떤 외풍이나.</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015081200504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015115400001</t>
         </is>
       </c>
     </row>
@@ -5999,17 +5999,17 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>과방위, 구글 사장·LG U+ CEO 국감 증인으로 채택</t>
+          <t>美 항모 입항 부산 해군기지 드론 촬영 중국 유학생 2심도 실형</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>)= 구글코리아 사장, LG유플러스 최고경영자 등이 국회 과학기술정보방송통신위원회 국정감사 증인으로 추가.</t>
+          <t>등이 입항한 부산 해군기지를 드론으로 불법 촬영한 혐의로 기소된 중국인 유학생이 항소심에서.</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015083000001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015113300051</t>
         </is>
       </c>
     </row>
@@ -6036,17 +6036,17 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>특검, 경남선관위 압수수색…시간대별 투표자수 허위입력 관련</t>
+          <t>네팔서 관광비자로 종교 활동하다 체포된 한국인 24명 전원 석방</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>)= 선거관리위원회 특별검사팀이 경상남도선거관리위원회에 대한 압수수색에 나섰다.</t>
+          <t>)= 네팔에서 관광비자로 입국했다가 종교 프로그램에 참여해 체포됐던 한국인 24명이 전원 석방됐다.</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015082000052</t>
+          <t>https://www.yna.co.kr/view/AKR20261015115600504</t>
         </is>
       </c>
     </row>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>'DMZ 평화공존 방안 모색'…경기도, 28일 국제 포럼</t>
+          <t>특검, '선거물품 독점 특혜' 부산선관위 등 10곳 추가 압수수색</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>)= 경기도는 28일 소노캄 고양에서 '비무장지대 오픈 페스티벌' 학술 행사로 국제 포럼을 연다고 15일.</t>
+          <t>)= 이태한 선거관리위원회 특별검사팀이 선관위의 선거 물품 보관계약 독점 특혜 정황을 포착하고 강제수사에 나섰다.</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015083500060</t>
+          <t>https://www.yna.co.kr/view/AKR20261015115200004</t>
         </is>
       </c>
     </row>
@@ -6110,27 +6110,27 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>선관위 특검, '투표자수 허위 입력' 중앙선관위 등 7곳 압수수색</t>
+          <t>[영상] 의자 들고 맨몸으로 흉기난동범 맞선 ‘의인 5명’…필사의 2분</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>선관위 특검, '투표자수 허위 입력' 중앙선관위 등 7곳 압수수색. 아울러 특검, 경남선관위 압수수색지방선거 투표자 수 오류 수사.</t>
+          <t>의자 들고 맨몸으로 흉기난동범 맞선 ‘의인 5명’필사의 2분. 아울러 범행 전 휴학계 제출·현금 600만 원 소지한 인천 흉기 난동범···경찰 “도피 의혹” 조사.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE10ZGptcWVZNmQ3UEYyU0w2cjdWdngzQjJIdXQyS2RJTFJKNlVMWEFCOFhCNE1tYzNVOVhHZlpPc2F1NVM2MXpyRXJZRjVCYzc0eU9wNWdhYnFsM2o3UlI5TWRBRHUxeU9aTjBfNjRWLWdKZ25OSC1Z0gF3QVVfeXFMTVRkLWV6WTlBOFZMWHlNc2NVeGhybEhKbDdDdWw2OUZRREFtZzRhNVZ5aGh0SUUxR002VHE1cDlPYmxTN0V5b05wekw0QkpoWjl4NzNVUENCdUJyUkZPWkxSaU1FRnQ3ZjhKdEo2U2pGbXFVZzZtVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE53QWdRZGFSYnRLbWNtUVU4cUtQQkdsY0JJTzQ4UWlGYVBXbzJiYXRDVUxvNXAwd04wZFJ0VTAtYUc2T1pxQnM2T0E4Y05LMnVfa3RjcGk4NmszTzJxVGZHcHpzODRDRV9jeFZ0WVlJNFJ6Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6147,27 +6147,27 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>김민석, ‘강훈식 서울시장 후보설’에 “역량 검증된 전국적 인물···가능성 열려 있어”</t>
+          <t>강선우 “김병기에 원하는 면접 질문 카톡 말고 텔레로 보내라”</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>김민석, ‘강훈식 서울시장 후보설’에 “역량 검증된 전국적 인물···가능성 열려 있어”. 아울러 대장동 변호인 가족을 국세청장 이어 비서실장에.</t>
+          <t>강선우 “김병기에 원하는 면접 질문 카톡 말고 텔레로 보내라”.</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9HcHBhZW85UEhNZnJsdmNPSHp0LWlLeEhoM05aVzhaY3ZEeEF3Rl9TTEdpWnNYLVpLMUJJTXdSMzh5aFVTZW5SZjM0RExUTEx3T3hkQ0ZKbndCUdIBX0FVX3lxTFBPWTF5VjN5YzRfbWNWMkdSOGxFbDVvaWdSRW00RTJDRjdVdVlHZ0d4dWNreW5ydGx3YzloTGQ0VTh2c0IwTXlEbnJ5WUZHNU9LRk9YZnY5MDBodFVMTDNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1KeXNwYVJ2bkt4VFA2RHNESjdnM3dRLWJTR2ZFcHhKcHFQRk1FSEl4TDdlOW11dUVMOWFQZjhVWkZ0VVBjTkVaYVYzaWFWekJ0M1ViVDM0VlVFX3J4SnNzRjVCaUJrZmNmcDJuOUJBV2U5V0tMMlHSAWZBVV95cUxNZzNBd01sSFBxQ1lWZHlyQWdGQmlqWXROZWcycTMwSFZlNmpDUUpFdEhjNWUyclBocTF6NFpXUmRvVEVzdkFacW5ZYmNpSDhoQnFnSnlnOGpWZk1vX2ZfUFRYSHRJU3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6184,27 +6184,27 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>인천 흉기난동범, 감방 피한 이유…22년 전 사건 봤더니</t>
+          <t>이 대통령 지지율 44% 보합‥민주-국힘 지지율 격차 줄어 [NBS]</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>인천 흉기난동범, 감방 피한 이유22년 전 사건 봤더니. 아울러 범행 전 휴학계 제출·현금 600만 원 소지한 인천 흉기 난동범···경찰 “도피 의혹” 조사.</t>
+          <t>이 대통령 지지율 44% 보합‥민주-국힘 지지율 격차 줄어.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5fYnBJdi0zbWlUU08temJSbUlhSnBZdURCeG5samIxdnFJQ3JrU25DNWRXcV9EVXEzYThLTWIyRmlMWkNKM0dRTG9zR2tYUnVJU0FvYzM1d1NrUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1IN0k3azRBQ2RJN1l6cTRndUNaRERUWW0zaHFkOFdLZl9MT2owQ1RTQkg1T3pmNzZzbVFqcWpTVkljSkpmTTFkaWNSRDhuQWlnZVZfbWhRNlZSZ3B6S3N0ZUxQblluMmZfeHQtMWNZR3EtejEzZHpCNdIBeEFVX3lxTE9pd3J6U2YxTF82RFNNMzJ4NVlTU1Z3OWpsdGNFQl9qY09TTW93RDRJdnRSSzU2NFJCSTZZTzNHZ3JkdlZYMUJMSzBSQkJKdUdPd3VIdjFxT0NjWVFaTkx0bTFVRHBMcVZPTkdJdldHT0hkNVRkVVRoYQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6221,27 +6221,27 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>[천지일보 여론조사] 이재명 대통령 지지율 37.4%… 부정 평가 60.3%</t>
+          <t>토요일까지 포근, 일요일엔 ‘요란한 가을비’…내주부터 ‘쌀쌀’</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>이재명 대통령 지지율 37.4% 부정 평가 60.3%.</t>
+          <t>토요일까지 포근, 일요일엔 ‘요란한 가을비’내주부터 ‘쌀쌀’. 아울러 주말 전국 거센 가을비다음주 최고기온 4도 더 ‘뚝’ 더 쌀쌀해진다.</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>천지일보</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE85WGRUeE5RZ1Jub21venA0akstVjkwSlN6MFpZVU50elJIQVU0UENvNjJ4bmg5VnNwT1JPWEttMVQwTmtPR21rNVdBYWxDdkRSYk5CUzJyVl9jYV9vUVIwZkMwTXJRTmlpQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5QUGp6UHhpM2xnSW1DTlZGTzFGN2szZUN4c3IxNkd4V2xvb3BtZmdaYmo1QlZXUTJpei1GQ0VSY1k0ekVDWlQ5d29FeFczVm1XUnpXNjhoYjMyYnU1em0zNGgwM2RSY2hrVHVWRw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>주한美사령관, 전작권 전환 관련 “계획 변경돼 새 기준 생겨”</t>
+          <t>[속보] 특검, 중앙선관위 등 각급 선관위 7곳 동시다발 압수수색</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>주한美사령관, 전작권 전환 관련 “계획 변경돼 새 기준 생겨”.</t>
+          <t>특검, 중앙선관위 등 각급 선관위 7곳 동시다발 압수수색.</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBmRlF5MkJPeXNkUkNxMkhRWFdoakZodV91OEZERDJ2b1RoT3FFRnNJbUM0cW0tc2E3ZFgxV3M3RW1STDBVcDRPRU5YYS1qNE5jdlN4Wmdud0VkQmlXUTVnMm5vdTFOQ01XTmo2SS15OHUtTG_SAWZBVV95cUxOeTNkbEtjT0FtNG9kd2p4YVRaTzhEQWgwTTRCcEZYRFpyVEl3SnFmaG1lUmxKejBWTXVmUXY2MXpBaHhLMFU2WlFhc2t0WjE2d3IzZUg1XzBGZkJOQnF4SEdXaUo0VUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5vMXlDcWZUOXp3QVdtUmF1Qm1yWVl2TTFucUxqMUhtWTFRRmdTRW9rRVVPMTdXa3pBMmtJX2d1bmw5RU40X1Z1VHNGWTJYUERfV0NnOXR6R3lEUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6295,27 +6295,27 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>장모 살해·아내 납치 20대 남성, 내주 신상공개 경찰 심의</t>
+          <t>브라질산 계란 한판 수입가 4만4000원…올해만 16억 썼다, 왜?</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>장모 살해·아내 납치 20대 남성, 내주 신상공개 경찰 심의.</t>
+          <t>브라질산 계란 한판 수입가 4만4000원올해만 16억 썼다, 왜? 아울러 이 대통령, '브라질 계란 고가 수입' 주장에 "허위사실 시정 바라".</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9CQ0RRbHZIdUxRdnN1c2FSYU03cXRCRkdsbXR4MUxPSFBuS2dLRXdxbFNoNjAxM0ZYTHA0STMweWcyT0tTWTE5WXlJSlc5V3pfUkxQaW40NXBYTW5YeGUwdFBtUHFjT0trc1F4N3ZITVVhUTU2emtn0gF3QVVfeXFMTkdpU3JFZHYySUt1blVCN0RnQVVnSm5hVXM4SnJoVzhQMXJ3WXJVRUdFMkx3cUxIQmRHdDNiUzJVbkZEUVlndkZPSDZpdDIyR2dMd2JvSllvcG5MWDd2YWtRVUQyN3Nzc042a0RxMnkxTkVfR3doTXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1NQU5PN1hvTWF5SzNESnVOeG94Z2dvd2R5RjhEclUtd05ueVpiV1NlYkF6RXBnTUJpd3lrTXZueEFkUnBCQVBtbjhEVjlTRWFLQVdZR1RHSDlRbkNjcWZjdmV3YkszR3VBc0lfZURXUml3N210cHfSAWZBVV95cUxQVERObWpHa25ZdDRCYTN0eHY3SmRYUnNXTDdOcndlNWY4MmhIN3FNSDRjeDZKRDlXSzQwZnZzTW9yamRtX0hrNHhFVDFZdGNRcWdrR0tLeWlIekRTcHFGOVV2c1E2Smc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6332,27 +6332,27 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>“생사 갈리는 초응급 순간에 압수수색”…의협, 경찰 소아응급센터 압수수색 규탄 [현장영상]</t>
+          <t>국힘 최고위 공개 충돌…양향자 "경선 전면 재선거" 정희용 "당 시스템 무력화"</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>“생사 갈리는 초응급 순간에 압수수색”의협, 경찰 소아응급센터 압수수색 규탄.</t>
+          <t>국힘 최고위 공개 충돌양향자 "경선 전면 재선거" 정희용 "당 시스템 무력화". 아울러 국민의힘, '용인갑 조직위원장 경선 논란'에 지도부간 내부 충돌 계파 갈등 양상으로.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFB5NHV3RnhoVVo3alpXTG43dk1kZnJSYlJRaVIzaXNiMVFiVmNZX1p0RjI5X1VNNjA2ZXFzcXNsWU4zQVE0R0xGcXR1STZOLUVrUmV3VTJEbTVOc0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVGlLbHpDQkxxcVcydTdBOHYzQ080X1pkazN3RGpQekRtazdpR0tMY0w1VmVIMjlVbWt5UjJYQ1hLazFBOFo3Y3JQM2ltWUcyUzIyZmxWV1JZSVZ2TzFEcmptS1N3SjRTaEc2ZHRPMlp1Tldjamk0cHMwd1pwc0R2b1NnWnFGQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6369,27 +6369,27 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>농지 전수조사, 불안 넘어 농지제도 개선 출발점으로 - 오피니언 | 뉴스</t>
+          <t>‘접근·연락 금지’ 스토킹 남편, 아내 살해…경찰은 연락두절에도 안 찾아가</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>농지 전수조사, 불안 넘어 농지제도 개선 출발점으로 - 오피니언 | 뉴스.</t>
+          <t>‘접근·연락 금지’ 스토킹 남편, 아내 살해경찰은 연락두절에도 안 찾아가. 아울러 8번 경찰에 신고했지만 결국 남편에게 살해됐다.</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>정책브리핑</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5XN0w3alRBSHFIUDZLSWtjWGVhemE1UC1iaXpYcHhkWWhKNkZpdWhQTkRpRWdQbkI1MmRBeUE4OG9ORFlEVlVwNF9na0tzc1lyeXdOWHRXRzJmdExrMVNENk4xS0FHWFdxNEdGdjRHZ1lzWlRo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBHVUVPXy1zbEhpZHA5dUJSbV9sdE9XQVFnOGRnUzU1Y3FwRUtvcjI5cThLTDVUM2VUNGxDNVcxZ0V4VXR4LVNnbXBKcTMzcnhCNFd0bFphTVY0THlCR3NQcg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6406,27 +6406,27 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>누리호 탄 초소형군집위성, 발사 14시간 만에 첫 사진 전송</t>
+          <t>[단독] 가정폭력도 전자발찌 채운다…경찰, 법 개정 추진</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>누리호 탄 초소형군집위성, 발사 14시간 만에 첫 사진 전송.</t>
+          <t>가정폭력도 전자발찌 채운다경찰, 법 개정 추진. 아울러 보호관찰 처분 연간 10만건 쏟아지는데관찰관 2천명도 안돼.</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9jVVFCVUJIUzVxR0o0NXJfOV84VEgtczR4bmRQSEpmU0xONWtTMUZCTEFCNUJwbEYzd1hXZmdYMUltYjhFcUZobHdjekxCZS0wbnFuU044VnozNkxvMjA3ZDZSQ20yWmRFbU03WEN0UGpHWmtD0gF0QVVfeXFMTjFCVVlTMzVKT1lpYTFLMkMtMm5hSE9IcUI3Y25nOWFZdGdXUTNMLUtjejdkMHlDYWk2RExWZ3c2azRVMzhTRjU0NmNKalFmSi1KS0VqbXg5bmk3ZGpjZ0pvTWhoV2ttQ3hRdkhxYzdtQVJ3SWo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1LQ2FKSHRLZGl6Nm9sZlBMMWVsZVh4Z1hIRVJaLWFDanZyX184bGpqLU5Oa0dGQVZkLVBqRTUzMkdUWGw5c2ZONkh3TFc1ZW1HQkcxZ2UzZjU5bmhhSWoweDBhY1BKcGs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6443,17 +6443,17 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>전주서 아내 살해 70대 체포…과거에도 가정폭력</t>
+          <t>이 대통령 “강력범죄에 전쟁 선포 각오로 특단 대책 조속히” [지금뉴스]</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>전주서 아내 살해 70대 체포과거에도 가정폭력.</t>
+          <t>이 대통령 “강력범죄에 전쟁 선포 각오로 특단 대책 조속히”.</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5vWFhJcHNLZmZnZFpIQkZDYVF6VWs5TGM3M2s1Z0NPM2c3MlBRN3QySkJucGdzRTVfTFA0eUg1RmwwYjVHRklGY3BnaV9wX3NnbHhrc2JsQjlQbE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA0MlNRb0FPb2VKa3BrRkZyRVc0bldsVU8yZ2FaWnRqc3FXOEFsbE42czF0S0cyN0dVZUJfdHBlRDltRTdiZjhVeXdoXzdNbmU1LVZXcDJhbUlod1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -6480,27 +6480,27 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>[단독] 애국지사 유묵이라던 친일파 글씨… 유홍준 관장의 개인 소장품이었다</t>
+          <t>'창원 택시기사 살인' 재심 개시 결정…아크말씨 형집행정지</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>애국지사 유묵이라던 친일파 글씨 유홍준 관장의 개인 소장품이었다.</t>
+          <t>)= 17년 전 경남 창원에서 택시기사를 살해한 혐의로 무기징역을 선고받은 우즈베키스탄 국적의 보조로브 아크말(37.</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQeDh5QXV2S0p3aGgxdnE5RjQzMDdfQ25rMHdsNGRjNEVoa3NiNnhuQllhT09QR1VoYjktdV82enpfTmltaDNPZV91ZmVhVWhjLTFBQ0JWWVY0XzU3b0NwOWd6RGRTOE80VVAzTmRWQlNwZHRlNzUtRkZoS3RfLVRleHNGMUlJVEJFa25BbEFkbFlRUE9G?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015138500052</t>
         </is>
       </c>
     </row>
@@ -6517,27 +6517,27 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>"딸 위험" 엄마 경고 무시한 경찰… 아빠·4세 아이 결국 숨진채 발견</t>
+          <t>[게시판] 행안부, '사회연대경제 생태계 리더십 국제교류회' 개최</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>"딸 위험" 엄마 경고 무시한 경찰 아빠·4세 아이 결국 숨진채 발견. 아울러 제주 4세 여아 사망경찰 대응 적절했나.</t>
+          <t>행정안전부는 15일 서울 한국고등교육재단에서 SK 사회적가치연구원과 함께 '사회연대경제 생태계 리더십 국제교류회' 세션을 개최했다고 밝혔다.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQT3NKSkNwN0NSTmMxT1NLUEp5T1AxX2FqWVExdk9lTXp2LWxidUdWNWNEeGtlQ2JacllWYldROUY5QnBpbU9hY1U1X1ZSTWN0UkRxZnhfUXd0b0JtOHJRWkpvTF9FT0VCN1JHUEJNWmJFeEh0TjFtcFpQZjV6dDg3dmVaenltQQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015063300530</t>
         </is>
       </c>
     </row>
@@ -6554,27 +6554,27 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>국회, 오늘 서울시·서울경찰청 대상 국감 진행</t>
+          <t>'DMZ 폭발' 李대통령 고발사건 서울중수청 반부패수사국 배당</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>국회, 오늘 서울시·서울경찰청 대상 국감 진행. 아울러 파기될 뻔한 한강버스 수사의뢰서, '브로커와 뇌물 의혹' 담겼다.</t>
+          <t>)= 서부전선 비무장지대 지뢰 폭발 사고와 관련해 일반이적 등 혐의로 고발된 이재명 대통령 사건이 서울지방.</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9pUkx0ekhycVJ0RnFjMzU3Z2F6OWdjbzZBaVRVWklXX2FvS25TbjlJM2NRMEdpbEt6UDlKM1RtM1EwZ2R0UEdMOExLUTJlbGpyYlpmLXYzanNPdDQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015137100004</t>
         </is>
       </c>
     </row>
@@ -6596,22 +6596,22 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>나주 부부 살해범은 52세 박용수…빼앗은 1100만원 도박 탕진</t>
+          <t>울산 야음동 수돗물 공급 차질에 긴급 수도관 공사</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>나주 부부 살해범은 52세 박용수빼앗은 1100만원 도박 탕진.</t>
+          <t>)= 울산시는 남구 야음동 일대 수돗물 공급 차질과 흐린 물 발생 문제를 해소하기 위해 긴급 수도관 공사를 마쳤다고.</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE93Q1ItcmxJRTFXeV9wNk5ibDc2ZmV2X0JCUmxKOV9BNS1VMjQ4UDU3aTUxZGIza19TYzVLRXJHN2o4NDItWm93WEd4bGVzNnY0LWdJS1NnaHZ5M0xYYjMxcS1FWVlsUGpRdm13NWNIbUxXMndZcUHSAWZBVV95cUxPcFMzWC1kMGQ1UWxkSUtQS1FoakFoMFR3c09mRzlLdGlzNWRzOVZZZnRnWmJScnVBYUx1c3RjZTU3aTFzZks4SUNCOTc1bm9pUlQyTXVrNTJzTGcteFFWWVRvT2RqNlE?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015138400057</t>
         </is>
       </c>
     </row>
@@ -6628,27 +6628,27 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>‘딸 경찰 수사 무마 의혹’ 한동훈, 국수본·중수청 양쪽에 고발됐다</t>
+          <t>"공원등 고장나면 QR코드로 신고" 익산시, 도심공원에 표찰 설치</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>‘딸 경찰 수사 무마 의혹’ 한동훈, 국수본·중수청 양쪽에 고발됐다.</t>
+          <t>)= 전북 익산시는 영등시민공원과 어양공원, 모현공원 등 3개 공원에 '공원등 큐알 코드' 표찰 333개를.</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9WRVY5ajZFeHZ0OFMxRlp4RjdpMzJZS21oT3p5MTVick1hX1ZmVURTNXN1b0h0SGdlR1h0RG1USmF6WWh6TDNzMHpIMTc5MDQ0VkVTeWE1U0x0UdIBX0FVX3lxTE9vb3A3SUhkZks1OWVUX2hVdTNQNmxBS1JVaFl1UmVwbWJBZFU4OUxRQmJhcnBmRmVlSXRWYmF6bzlxaWtsdm5lbi0tZ1FMeE9HQVNid1hDNjY0a1hnVHVJ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015134700055</t>
         </is>
       </c>
     </row>
@@ -6665,17 +6665,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>전남광주 5개 자치구, 조정교부금 교부율 27％로 상향 재건의</t>
+          <t>서울교육청 "여명학교 건립 예정대로 추진…2028년 착공"</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>)= 전남광주 5개 자치구가 민형배 전남광주통합특별시장에게 시·군과 동일한 수준의 재원 조정교부금 교부율을 재차.</t>
+          <t>)= 주민 반발 등으로 북한이탈주민 청소년 대안교육기관인 여명학교의 교사 건립이 지연될 수 있다는 우려에.</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015098800054</t>
+          <t>https://www.yna.co.kr/view/AKR20261015135700530</t>
         </is>
       </c>
     </row>
@@ -6702,17 +6702,17 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>고흥 밭에서 불…1시간여만에 인명피해 없이 진화</t>
+          <t>하동 양보면 야산서 불…1시간 32분 만에 주불 진화</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>)= 15일 오전 10시 36분께 전남광주 고흥군 덕흥리 한 밭에서 불이 났다.</t>
+          <t>)= 15일 오후 1시 50분께 경남 하동군 양보면 한 야산에서 불이 났다.</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015096900054</t>
+          <t>https://www.yna.co.kr/view/AKR20261015137800052</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>경남 장애학생 1천800명 '한자리에'…교육감기 체육대회 개최</t>
+          <t>경남도, 재선충병 '선제 방제'로…광역방제전략 수립 최종보고회</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>)= 경남도교육청은 15일 창원시와 함안군 일대에서 '제11회 경남도교육감기 장애학생체육대회'를 개최했다.</t>
+          <t>)= 경남도는 15일 진주시 월아산 숲속의 진주 달음홀에서 '소나무재선충병 광역방제전략 수립.</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015095900052</t>
+          <t>https://www.yna.co.kr/view/AKR20261015133200052</t>
         </is>
       </c>
     </row>
@@ -6776,17 +6776,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>인천 서해에 풍랑주의보…백령도·대청도에 강풍주의보 유지</t>
+          <t>서울공소청 불송치심사부에 검사 9명 배치…'사건암장' 통제</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>) 기상청은 15일 오후 3시를 기해 서해 중부 바깥 먼바다, 서해 중부 안쪽 먼바다에 풍랑주의보를 발효한다고 밝혔다.</t>
+          <t>)= 서울중앙지방공소청은 직제 개편에 따라 불송치 사건 및 수사 중지 사건 등을 전담 심사하는 불송치심사 1·2부를.</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015096000527</t>
+          <t>https://www.yna.co.kr/view/AKR20261015126200004</t>
         </is>
       </c>
     </row>
@@ -6813,17 +6813,17 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>중소기업 청년 "임금격차 줄이는 것 넘어 청약·주거지원 필요"</t>
+          <t>폐철도 터널을 스마트팜으로…보령시-건설기술연구원 협약</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>)= 경제사회노동위원회 내 청년일자리희망위원회는 충남 천안 풍세일반산업단지에 있는 중소기업 ㈜아라에서 청년들의 일자.</t>
+          <t>)= 폐철도 터널을 지능형 농장 으로 활용하기 위한 실증사업이 충남 보령에서 진행된다.</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015086100530</t>
+          <t>https://www.yna.co.kr/view/AKR20261015133900063</t>
         </is>
       </c>
     </row>
@@ -6850,17 +6850,17 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>경남교육청, 학부모 대상 학폭 예방 토크 콘서트…해결책 모색</t>
+          <t>이철우, 주한 이탈리아 대사와 관광·음식 교류 확대 논의</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>)= 경남도교육청은 15일 김해 남명아트홀에서 도내 학부모와 예비 학부모를 대상으로 '2026년 학교폭력.</t>
+          <t>)= 이철우 경북도지사는 15일 도청을 방문한 에밀리아 가토 주한 이탈리아 대사와 문화, 관광, 음식 분야 교류.</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015094900052</t>
+          <t>https://www.yna.co.kr/view/AKR20261015135000053</t>
         </is>
       </c>
     </row>
@@ -6887,17 +6887,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>제2경인고속도로 문학IC 인근서 화물차 2대 추돌…1명 부상</t>
+          <t>경남 공무원노조 "지자체 보조사업 공무원에 떠넘기지 말라"</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>)= 15일 오전 11시 37분께 인천시 미추홀구 제2경인고속도로 안양 방면 문학IC 인근에서 70대 남성 A씨가.</t>
+          <t>)= 전국공무원노조 경남지부는 15회견을 열고 "다수 시·군에서 체육·문화행사 등.</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015094000065</t>
+          <t>https://www.yna.co.kr/view/AKR20261015129400052</t>
         </is>
       </c>
     </row>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>'무기징역 받고 가석방' 10년간 151명…재범 관리는 '깜깜'</t>
+          <t>화천군, 강풍 속 산불·문화재 화재 복합재난 대응 30일 훈련</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>)= 최근 10년간 무기징역을 선고받은 수형자 150여명이 가석방을 받은 것으로 집계됐다.</t>
+          <t>)= 강원 화천군이 강풍 속 산불과 문화재 화재 등 복합재난에 대비한 실전 대응훈련을 실시한다.</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015067700004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015135200062</t>
         </is>
       </c>
     </row>
@@ -6961,17 +6961,17 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>추미애 '소방 재정 빨대' 발언에 양대 노총 소방노조 반발</t>
+          <t>한강버스 리베이트 공방…"최상층에 오시장" vs "과장된 의혹"(종합)</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>)= 추미애 경기도지사의 이른바 '소방 재정 빨대' 발언을 두고 양대 노총 소속 소방공무원 노동조합이 일제히 반발하.</t>
+          <t>)= 15일 국회 행정안전위원회가 서울시를 대상으로 한 국정감사에서 한강버스 리베이트 의혹으로 공방이 벌어졌.</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015092400061</t>
+          <t>https://www.yna.co.kr/view/AKR20261015090351004</t>
         </is>
       </c>
     </row>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>진성준 국방위원장 "광주 군공항 이전·전력 배치 차질 없어야"</t>
+          <t>강원 직업계고, 1학과 1심화동아리로 전공 역량 키운다</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>)= 더불어민주당 진성준 국회 국방위원회 위원장은 15일 "광주 군공항 이전과 전력의 임시 배치 과정에서 국가.</t>
+          <t>)= 강원특별자치도교육청은 직업계고 학생들의 전공 실무역량과 취업 경쟁력을 높이고, 적성과 소질에 맞는 진로를 주도.</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015090200054</t>
+          <t>https://www.yna.co.kr/view/AKR20261015128200062</t>
         </is>
       </c>
     </row>
@@ -7040,12 +7040,12 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>충북참여연대 "청주 가정용 하수도 요금 비싸…20％ 인하해야"</t>
+          <t>진짜인 줄 알았는데 가짜…사업자 사칭 사이트 71건 적발</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>)= 충북참여자치시민연대는 15일 "인구 50만명 이상 대도시 가운데 청주시 동 지역의 가정용 하수도 요금이 가장.</t>
+          <t>)= 방송미디어통신심의위원회는 다른 사업자의 정보를 도용해 공식 사이트인 것처럼 위장한 사칭 사이트에 대해 올해.</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015091400064</t>
+          <t>https://www.yna.co.kr/view/AKR20261015126400017</t>
         </is>
       </c>
     </row>
@@ -7077,12 +7077,12 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>제주항공 참사 핵심 증거 로컬라이저 둔덕 재수색 착수</t>
+          <t>[철원소식] 김일남 문화관광해설사, 도 경진대회서 대상</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>)= 12·29 제주항공 여객기 참사 희생자 유해를 찾기 위한 무안국제공항 방위각 시설 둔덕 추가 수색.</t>
+          <t>) ▲ 김일남 문화관광해설사, 도 경진대회서 대상 = 강원 철원군은 최근 원주시 오크밸리에서 열린 '2026 강원특별자치도 문화관.</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015085100054</t>
+          <t>https://www.yna.co.kr/view/AKR20261015127500062</t>
         </is>
       </c>
     </row>
@@ -7109,17 +7109,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>말다툼하다 14세 딸 둔기로 때려 살해한 친부 징역 22년 확정</t>
+          <t>8개월 아들 리모컨으로 때려 숨지게 한 30대 친모에 징역 12년</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>)= 말다툼 끝에 10대 친딸을 둔기로 때려 숨지게 한 40대 친부에게 징역 22년형이 확정됐다.</t>
+          <t>)= 생후 8개월 된 아들의 머리를 TV 리모컨으로 때려 숨지게 한 30대 친모에게 중형이 선고됐다.</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014118400004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015132500061</t>
         </is>
       </c>
     </row>
@@ -7141,32 +7141,32 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>2027학년도 대입 수시모집에 1인당 4.96회 지원…작년보다↑</t>
+          <t>코스피 8% 넘게 떨어져 서킷 브레이커…‘7월 폭락장’ 이후 처음</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>)= 전국 4년제 대학 협의체인 한국대학교육협의회 는 2027학년도 대입 수시모집에서 1인당 평균 4.96회.</t>
+          <t>코스피 8% 넘게 떨어져 서킷 브레이커‘7월 폭락장’ 이후 처음. 아울러 공포의 '검은 목요일'‥코스피·코스닥 7%대 급락 마감.</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015052100530</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5mZlRCTlllLTZnVDZHWF9HMHc5T2M2S05la1B6d1ZXbkpSamF3V3F2bjJzU3RnZlZPcVREMmFlRm0yTnJJUWFuQTR5bEhzX1pOVEdJZ1VpdEJXSmh0bFowcmNCallUY2s?oc=5</t>
         </is>
       </c>
     </row>
@@ -7178,32 +7178,32 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>ESS는 공작물? 건축물?…정부, 분류 기준 마련</t>
+          <t>"삼성전자, CXMT와 기술격차 최대 7년…시장 우려 과도"</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>)= 에너지저장장치 를 건축법상 '공작물'로 볼지, '건축물'로 볼지 구분하는 기준이 마련됐다.</t>
+          <t>"삼성전자, CXMT와 기술격차 최대 7년시장 우려 과도".</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015046400530</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1admhLWjR3QzJUNjFXSldvTXh4Q3NBdlhDWGVldFVjRXBvM1JxWl9YRk5uOF9DZ2VCVXlvTFlud2ViYVFPNlpFLXl2dW9RMjJkWlhPZTFXMGZUZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7215,32 +7215,32 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>어린이집-유치원 입소·입학 신청, 더 쉽고 편해진다</t>
+          <t>지뢰밭 뚫는 로봇·자폭드론 기습‥육군 "2040년까지 전군 유무인복합부대로 전환"</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>)= 교육부는 11월 2일부터 시작하는 2027학년도 신학기 어린이집·유치원 입소·입학 신청을 앞두고 관련 서비스를.</t>
+          <t>지뢰밭 뚫는 로봇·자폭드론 기습‥육군 "2040년까지 전군 유무인복합부대로 전환". 아울러 레이저 대공무기 천광, 드론 요격 시연 성공1회 발사 2천원.</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015055000530</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBMMkNldEZtOFJuYmU4Skl3bGZUWnpVOENCa2xmUzVnbER2bnd4OTE5TnptM2xadjYxZlhoWVBTcVpnOHdFZDN6RGtEdzdiT3hTS1ZFQ3hCNE5sWXNBNXNBQTBaXzlFN2VlTjIzZUdMcWtFZGMxWjFCMtIBeEFVX3lxTE9TdjFpZzVZWUlqakZBOTJiaWd4NHY5eWVkdm52cmt5cjRIa3dWMFZGSlQ3T0VQWVBxUGRmaU9FZkJpalZ1NEdhV0szMk9lRTItMDQtcERHLU11RktUeU04TVZHeVBKX3pzNEJ6dnowanFlclBQRFF0Rg?oc=5</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -7262,22 +7262,22 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>서울교육청 '서논술형 평가 AI' 세종·충남·경북서도 쓴다</t>
+          <t>OK저축은행 개인정보 유출 고객 규모 183명→250명</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>)= 서울시교육청은 세종·충남·경북교육청과 인공지능 서·논술형 평가지원시스템인 '채움AI' 공동 운영을 위한.</t>
+          <t>OK저축은행 개인정보 유출 고객 규모 183명→250명.</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015059300530</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBUUkZBTHI5VllFTjFtYVBZMklaQU9oZkVULVlTRFhnQ3I2NE5iSVhhYTQyZlhkUHI1Sl9wbnRRaHlZemdpeGp2Q3hNeW9Hdm5qckw3YzUwUXVNcWVjQmNJV01Pdm5UQTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7294,27 +7294,27 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>코스피 5% 급락 출발…이틀 만에 매도 사이드카 발동</t>
+          <t>정부 요청받은 SK·삼성·현대차, 美 웨스팅하우스 지분투자 검토…최대 4조 규모</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>코스피 5% 급락 출발이틀 만에 매도 사이드카 발동.</t>
+          <t>정부 요청받은 SK·삼성·현대차, 美 웨스팅하우스 지분투자 검토최대 4조 규모.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>인베스트조선</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE14QVhoUnU2Ul9lbHdYVFItV0NBMUdoZmpQZTc1eVQybUFNT3F5S24zbmFfZm84ODRuWk9Ta3pYcDNkd193dDVqVmhnRXBndTgyRzQ5Y29TaHctakxDaUVSaHNjbDIwTjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQY3M4MkFsQ1JpMW43Wm9IZ3hqRmFQVUp3M3NDUFlPSzlYSWtJbHIxNGk2V1BZQ1JWaEhWYXZQc182U2NhUHotZHBOZFd4ZXJoVWFIQkczcHlkcXRSUFNFYU1DMDJEbjB5czdJbEw4WkFhaVc2VTRFUEh1ak1lZjRjaXlMRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7331,27 +7331,27 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>中 CXMT 반도체 신기술, 왜 삼전닉스 주가 흔들었나</t>
+          <t>AI 클라우드업체 코어위브 회사채 가격 급락…'부실영역' 진입</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>中 CXMT 반도체 신기술, 왜 삼전닉스 주가 흔들었나.</t>
+          <t>AI 클라우드업체 코어위브 회사채 가격 급락'부실영역' 진입. 아울러 "전세계 돈 끌어온다"더니증시 덮친 '15%' 공포의 정체.</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQRjYxSEpUU1RQMVJzOWtfdnlPQzBoTnp1NWFkby1uOW1IcmljbFpNeUdaU3VmUV81NHFuRkdOanZHeXg3WE9IWXpuODJZOWNnTVRLUlZLRE1PV1djT2lqRkJLUTAtVHdkUzkwWDZvM25WOW9OandfbnlQTTBfbzVXTmVaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1Ud2RXUWZrWFNsejM3Q2J2cUdieXdiSmZVMnk0S2dCU3NrOGRLOEQtQmZ6MWlTcGlSeGU1Y2VEVl90aThINzUwOXRwUEF0d0U2RjlzUGFFU1Rna3VOM3dyRFlLalJPN0Q4R3FRZ3lvU1o?oc=5</t>
         </is>
       </c>
     </row>
@@ -7373,22 +7373,22 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>미국 8개 주, 오픈AI에 동시 소송..."청소년 자해·폭력 부추겨"</t>
+          <t>믿었던 ‘삼전닉스’에 발목...주요 반도체 ETF 줄줄이 수익률 바닥</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>미국 8개 주, 오픈AI에 동시 소송"청소년 자해·폭력 부추겨".</t>
+          <t>믿었던 ‘삼전닉스’에 발목주요 반도체 ETF 줄줄이 수익률 바닥.</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE93cXUwdnlqRXhWRWNZeUNPTHdSZEJNb01LR0hwNVA3TXpwRThjNUVBLVFKcmJ6bzN5YWgwTlBnaEFIX3c5aXpyTGxWVGZFb3I2NkVwTTdYNTBSeWhBSUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNRUFoOGM4RW40SVlwck9DR2dPU1VIWHE0VHE3SGFWc2FFZkQ4Z2N0ZlJ5OXBkb3N5QXhhcnVvMzJfdEJjUlVYS25VdUE2MERYQ1VoY1drc0xDWENaQVBFanllVDlhVVEtN05pYnMyTzVVUkRwMEE5VEFqTVVnM3dhXw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7405,27 +7405,27 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>“스캔 폭격하고 안전장치 뚫는 AI 해킹툴”... 티오리, ‘아르텍스’ 분석 백서 발간</t>
+          <t>‘배민 라이더’ 201명 개인정보 노출 정황…로그인 없이 열람 가능</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>“스캔 폭격하고 안전장치 뚫는 AI 해킹툴” 티오리, ‘아르텍스’ 분석 백서 발간. 아울러 "금융사 침해사고 발생 총 16곳약 10만건 유출".</t>
+          <t>‘배민 라이더’ 201명 개인정보 노출 정황로그인 없이 열람 가능.</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>보안뉴스</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1sM3V1eUZiTXVaWm9sazNFMzBvTjJpLUpOYnJCaHZWNXpKQUNLVThCQXZJZUxnT0dnVWFkREVmODREaV9EZGRfRWJoOXdzU0k2NVFhVHh4eW84c3FqbWl6eGkxYTZ1azF1bG1V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBBR3JBSlpPZFEyQXpzZWczLVFNMkttZmRPVlhaR3ZtRmdlaGtmN003Wmc4dXNSMlFSdjRNSzFBOHFrd0U5aFE0aGF2Ry1CYTNDVHFYQWVUbks4YlU?oc=5</t>
         </is>
       </c>
     </row>
@@ -7442,27 +7442,27 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>배달 라이더 201명 개인정보 노출 정황…대행업체 관리 부실</t>
+          <t>[정신아의 약속 1년②] 카카오 주가 반토막에 인적분할 승부수</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>배달 라이더 201명 개인정보 노출 정황대행업체 관리 부실.</t>
+          <t>카카오 주가 반토막에 인적분할 승부수.</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1vSlQ4bGRNZHdXS0NNQVZXOEpvNkpGcXA0WG11RTdCNm5BcmVPMUtLYVZUNlRRTzRKSm9tbW1WbnpVSndTdUw2bkhYLW01aWQ4U2JoRnJEenZPYlNTN0JPSXB3eUUwQWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5pbWNtWko5a2hiY000YzJ2RndTSlJKa0cxOE5RTVNJWnJTc0d0UFlVWHJFVHVDOXliNUk5Z0RUN1RVTUJzbEdjcHY0d1FCenZXdENMa1A1QnhnM0N4OHRYVWotNU1ZYWtMLVVwaHNUblg?oc=5</t>
         </is>
       </c>
     </row>
@@ -7479,27 +7479,27 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>"빚내서 SK하닉 샀는데"…두 달 만에 '600억' 결국 멘붕</t>
+          <t>트럼프 “한국 알래스카 500억달러 투자는 나와 맺은 합의” 또 못박기</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>"빚내서 SK하닉 샀는데"두 달 만에 '600억' 결국 멘붕. 아울러 "비명조차 안 나온다"다시 찾아온 급락장에 개미들 '망연자실'.</t>
+          <t>트럼프 “한국 알래스카 500억달러 투자는 나와 맺은 합의” 또 못박기.</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9WUjFtM2lFNUJyTTlvZWtZMGZfV2F5Q1ZrRnBmbjVzVno2azhiYUgzVXo1WVhQTDdQNFVnYnBYMzBfMmtLWG1HRXJTRkJxdkpIZk5CeG5yVmdadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1OYmFhOGZZWDc2UW5JSzBBOHhuNzQ1VWxGY1pmY0ZoNGdIaTZENDU4TWpxMVBVMWNYQ1FteE9NRzVDWGU0SDB2OUx1NEdoS1FuTXdNb1h6TzFRY2k5Z29fSmR6QWFBNnNtOFVPcy1naw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7516,27 +7516,27 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>이헌욱 부동산원장 “외국인 주택 소유 현황 등 신규 통계 만들 것” - 조선비즈</t>
+          <t>비트코인, 미국 물가상승 직격탄…8만 1500달러까지 하락</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>이헌욱 부동산원장 “외국인 주택 소유 현황 등 신규 통계 만들 것” - 조선비즈. 아울러 국토부 "주간 아파트값 통계, 전문가는 조정·국민은 공표 원해".</t>
+          <t>비트코인, 미국 물가상승 직격탄8만 1500달러까지 하락. 아울러 코스피 급락 부른 美 CPI 충격"사실상 올해 최악 성적표".</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>지디넷코리아</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOUlB6Z29IWUtaSDlmaDVPbS1OSklpM1RLYXROSC1xT3J1Z1pKU2tBMExkZXdLZmZ6ZENzd1ZUWXVPRzE3THl4bFM4dExjT25hNWpiVzdEdGlWRXNHUl9iY19xSlhsN1JiVGJrbU9jTUVhZG8wX1NkcWI0R2J0ZFMxakVrRXUzaVVTU0RVMzIwSnZPeVpuVVIyctIBrAFBVV95cUxNTmRhRURFbDhpaFFBTHFxdkllcGlxQkVTTGFPS2c0cXNVLUx4TlFqcE5uMTg1NHlVZ19pLU5TUWlZS0dzQ1Fac0JMcnFuRTROM0YzMlpUX3Y1X2tFeUtiNXRFODlKcE9ibHdEdjNka09nbkFsOTZWRFBHbTZ3MmFQQ1czczV1WkM3LUtoYzZhb0JxeGlNbHktcFRxTEk0dXp1dkM2czczZXBZT3Y4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9Wdkp3aG5zbU9pUXVXaU8xc1M0a2RPbFBlNG1Gci1idDlBWFZFRllzMko3Q3M0YVZ2V0RObWV5bFRIdksxUEZ0TmNBMEZfdW5lWmxQREpn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7553,27 +7553,27 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>국산 비만약 에페 가격 책정 완료…양강 구도 깰까</t>
+          <t>“주간 아파트값 통계, 전문가는 조정·국민은 공표 원해…추가 의견수렴 예정”</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>국산 비만약 에페 가격 책정 완료양강 구도 깰까.</t>
+          <t>“주간 아파트값 통계, 전문가는 조정·국민은 공표 원해추가 의견수렴 예정”. 아울러 다시 불붙은 ‘주간 집값 통계’ 실효성 논란 부동산원장 “유의미, 검증 강화” - 조선비즈.</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1YTU12QUExOFUtNV9hVzRPNmlmR2t5aGxYQ2ROdF9mVFlNRHF5dkk5ZTliMzhIMl9mcFduQzNsQUs2d0ZmZ3U0VDRJazdTRzRLLTc5a1RsNXV4NkdhTTZLaXlyRFhnckVhR25faFFqdmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAweW1pcXVEcmxTZFotbVYwLUJpaDNNN1J2OHlTa2pCenExNDI2aWVZZDJSVGtGc09sQ2Zza3BtenFpYnRSYXo2QnpMWFp2NkxidDJ0WVRyMzlWZkU?oc=5</t>
         </is>
       </c>
     </row>
@@ -7590,27 +7590,27 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>위험회피 분위기 속 커브 플래트닝…국고 10년 4.2%선 하회(종합)</t>
+          <t>AI 챗봇과 수다 떨다 성적·폭력 대화까지…정부, 유해 응답 차단 추진</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>위험회피 분위기 속 커브 플래트닝국고 10년 4.2%선 하회. 아울러 '26년 11~12월 국채발행 추가 축소 여부 및 규모는 정해지지 않았습니다.</t>
+          <t>AI 챗봇과 수다 떨다 성적·폭력 대화까지정부, 유해 응답 차단 추진.</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsNkItM3N0ejNnMkdISzd3MjlVUHFxSklWRmJHUU5PRDVsaWVLTUJ5UG94VWJybzJ2ZlZLWnFWYXRHdjkzUGxHalEtdkxESXllLVo1U3hpLUJkNEpDa0MyZ2RRUXdwRnRwR0VXVl9UWTY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9yQW5TNHlDWXh1OUJFdFl3YU9VWl9BYm5tMU1JY3JSdkFNRDY4TGRteW1hTjRkQW1hRWFEbk50U0RORzNOTEtTSGtuTndkcHdwSFVGVEpzYjMxUdIBX0FVX3lxTE0zZVlrbk1DTDBOb2JtSDJnNDdYTWljNWlCd1NjbG1uaVhjXzFua1k0QzdJVWw1bklheUxZbFV2aEJ5ZWtIeDFOalNBS05XdjZtWjRDckV6dENpRUhobldr?oc=5</t>
         </is>
       </c>
     </row>
@@ -7627,27 +7627,27 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>현대차, 인도 푸네 신공장 준공…연 17만대 생산체제 구축</t>
+          <t>서울 아파트값 88주째↑…분당·영통·동탄, 반도체 머니로 ’들썩’</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>현대차, 인도 푸네 신공장 준공연 17만대 생산체제 구축.</t>
+          <t>서울 아파트값 88주째↑분당·영통·동탄, 반도체 머니로 ’들썩’. 아울러 '88주' 최장 상승 서울 아파트값용산 '상승 전환'에 오름폭도 꿈틀 - 머니투데이.</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>전기신문</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1fNzluUml6dWtNTXRxRzZSMEJ5dFU3YWs3YmkxY2VZZHpfNkZPTW1FcUllWndwckxsc2VOa29qaFYyb0dfSFkxcC1EQ3F3SXZDY09abjFMeExTckU1LXlKZGlwTHplbXlTSUh4TtIBcEFVX3lxTFBLVXI2R1JLUVVESHl1N1p0ZW9WZS1VSXBCWkE5ZVVaM08tZVJ2QnB1LU5fMkNNOHIzLTR4UUxwNGF6QTVhZlRNT2FfcC1aVU9kOERESEhsT0Vodl9xZ0F2VHZ2UldxbTFoU3ZMbkhNME0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBTUjZiemJlZlhLeHdnZndBUzVGckN6SllpTFM2bE9UNVZVRUN6SDdiLWdWOEwyVHY4WEM1Zi0tLUVYWGh4WXp5d3IxOEtyUjA5MDhub0lIVGxQUEdINGtDZkpaNzVvZHM?oc=5</t>
         </is>
       </c>
     </row>
@@ -7664,27 +7664,27 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>"가전 넘어 주택으로"…삼성·LG '모듈러'에 꽂힌 이유</t>
+          <t>아파트 가격 최장 상승에…10월 입주 전망 지수 반등</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>"가전 넘어 주택으로"삼성·LG '모듈러'에 꽂힌 이유.</t>
+          <t>아파트 가격 최장 상승에10월 입주 전망 지수 반등. 아울러 서울·경기 아파트값 상승세 지속에 수도권 입주전망 개선.</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5uM0Q5YU5TQ2Y3S2ZEZTUybGIza0JsSnNzY1R6OVRqRlVtaWdfMGZmclE4b0xLSklxODlyQnRUMjFLT0cycHNYTEh3QUFOellSSnVuMXp3ZE5wZGF6U2JnSXN5Y1JuYmRqNXROaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5SMDcwSF9HRDY1TnFjd1d1ZEFGQ0Q0V2s0MDBGeFdDQjlueURaTzJvRWRpdGw1dUFpUmM0YVc2eDhpTWpyeWRXVDRwYngwenVmSVZsN3Frc2lXQVVVWmx6aG0ySk0xV1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -7701,17 +7701,17 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>위메이드, 중국 자본 매각 일정 두 달 연기</t>
+          <t>GM 시절 로봇 6대가 204대로… 현대차가 바꿔놓은 인도 푸네 공장</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>위메이드, 중국 자본 매각 일정 두 달 연기.</t>
+          <t>GM 시절 로봇 6대가 204대로 현대차가 바꿔놓은 인도 푸네 공장. 아울러 정의선 '21兆 승부수'인도 車수출 전진기지로.</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOenJsMDB0a2tlLWJxVm9YaEpSUzlGWUZObEp6VmFPUHYxUXZqallkekthTk1TcHdYbXJCcDJYb29RS2hNY2dzeUxDdWNpOUVObWJrXzhmcndxanVTZ29Ed1VENXFINGxNTktpbWlXcE43bDZkZERxd05YaWxyNjVCcnVJWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPTDlENkJxSnk0UjhyWDlTYkxqR2M4WVk3bXlhVUw5RE9pd1RIM0hPYWtQYlFacG5QOFdwLS1hN3VxZVhFNHlvWkl4b1NXTG41UThJQkE3VTR6VEtUVlFaRVVJNHlBU0NLNE05ZjVUMWRvSjBZRW5jcWtFYkV0VmRubllHQ2oyN2s5WVhyM2pqdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7738,27 +7738,27 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>한국 콕 찍어 경고한 IMF..."AI 흔들리면 가장 민감"[와이파일]</t>
+          <t>'서울디자인위크'에서 내 취향에 딱 맞는 디자인 레시피 찾아볼까?</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>한국 콕 찍어 경고한 IMF"AI 흔들리면 가장 민감". 아울러 한국 경제성장률, 3.3% 성장 전망.</t>
+          <t>'서울디자인위크'에서 내 취향에 딱 맞는 디자인 레시피 찾아볼까? 아울러 마우로 포르치니 삼성전자 디바이스경험부문 최고디자인책임자 사장.</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9zSV9UUjhKYnU4SmZpTmdPcUhLb2JvMkQ1ZmtxNnNXT05lNmJyTDduaktENllJVE9EM2VfdzJiQ0xDOWY1SllRNV82bFdPU0VzZ3RoMDNqVVIxcXJNWUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZNWlZVmU2VTlGX1pUdW85cXQ3ZndNTDJlRnlYTVRJQVhkZzdaWGU5N282UUhjamNSSUdjMGgxYXpoT3dNOHIwV1JOTE5PSWJKUGs4Z2pWdFA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7780,22 +7780,22 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>K-제약 해외 규제 대응, 제약바이오협-코트라가 함께 돕는다</t>
+          <t>[심층] 결국 ‘건보 급여화’ 문 두드린 위고비…에페, 출시 전부터 ‘덜덜’</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>K-제약 해외 규제 대응, 제약바이오협-코트라가 함께 돕는다. 아울러 제바협·코트라, '해외 규제대응·글로벌 진출' 협약.</t>
+          <t>결국 ‘건보 급여화’ 문 두드린 위고비에페, 출시 전부터 ‘덜덜’. 아울러 K비만약 ‘에페’ 월12만9800원 마운자로 반값인데주가도 반값될라.</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>의협신문</t>
+          <t>농민신문</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE91aTR0T1dDQjNqSnh5TmY4Mkg4MWIwOS1BbXUybjdwWnEwNTFfaVJIZFUxenBKQXVoNUlLVms5UWltdURSNmNPZG5WZmQ1QVc5c2s3QS1aUTVGU2x5MS1pSm84ZWV6QkNUd1BaY2YxOEw5Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1jQWJUWU5QQ3p1WUhKZFRxY3U1V1U0VHJIQ2g1aGFCSk56ZFEwZjhsTEZLbUNYS1hwY1RLcDdLZU12bkJxaWpFN1Q4OXNGR2JuUGFEVF9abk1rUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7817,22 +7817,22 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>SK그룹, 웨스팅하우스 지분투자 검토…대형 원전으로 확장</t>
+          <t>내달 5일까지 전국에서 '지역 활성화 투자 펀드 로드쇼'</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>SK그룹, 웨스팅하우스 지분투자 검토대형 원전으로 확장.</t>
+          <t>)= 기획예산처는 15일 전북을 시작으로. 달 5일까지 13개 광역·관내 기초 지방정부를 대상으로 '지역 활성화.</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5UMUlmRFR4ZjB4VXlubFlPTklsdkRfYWhtTW1WX3dZNnh3ZDFwX3oweHNneTRHV1VIVzBYeDgzMzZra2NhZG82YTdYNjJ6ei14a1B2b2ZtMTZKQlRON0d0NGZEWWMxSHM?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015109500002</t>
         </is>
       </c>
     </row>
@@ -7849,27 +7849,27 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>코어위브發 회사채 쇼크… 'AI 버블 붕괴'인가 '차입 모델의 경고'인가</t>
+          <t>송미령 장관, 군수협의회 참석…농지조사·기본소득 협력 당부</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>코어위브發 회사채 쇼크 'AI 버블 붕괴'인가 '차입 모델의 경고'인가. 아울러 코스피 급락한 원인? 화제의 ‘가트너 보고서’ 살펴보니.</t>
+          <t>)= 송미령 농림축산식품부 장관은 15일 전북 무주군에서 열린 제16차 전국농어촌지역군수협의회 총회에 참석해 정부의.</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGcmNtdWVyejJnTWhEUFNQSjFPUUVTOHZqVjZ1blhBaGctb1VJZEhGYUh4eHIxQWQ4V2NuY1JSOUIyZTZCV2NBam1EQmYyUzFkbEVWaktJVVkwQQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015084300030</t>
         </is>
       </c>
     </row>
@@ -7886,17 +7886,17 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>日 메가뱅크 '환골탈태'…은행 사무직 수천명, AI개발직 전환</t>
+          <t>광주은행, 어르신 치매·실종예방 캠페인…4년간 20억 지원</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>)= 일본 3대 메가뱅크 중 하나인 미즈호 파이낸셜그룹이 영업직과 사무직 사원 수천 명을 인공지능.</t>
+          <t>)= 광주은행은 15일 적십자 무료급식소 에서 광주사회복지공동모금회, 대한적십자사 전남광주통합특별.</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015097500009</t>
+          <t>https://www.yna.co.kr/view/AKR20261015137600054</t>
         </is>
       </c>
     </row>
@@ -7923,17 +7923,17 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>현대차그룹 장재훈 "AI·스타트업 등 인도 신사업에 4조 투자"</t>
+          <t>농림축수산단체 "CPTPP 반대 변함없다"…5대 요구안 제시(종합)</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>)= 장재훈 현대차그룹 부회장은 14일 그룹 차원에서 향후 7년간 인도 시장에 약 21조원을 투자.</t>
+          <t>)= 농업·축산·수산·임업 분야 75개 단체는 15일 포괄적·점진적 환태평양경제동반자협정 가입에 대해.</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015003200003</t>
+          <t>https://www.yna.co.kr/view/AKR20261015089951030</t>
         </is>
       </c>
     </row>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>코트라 "대일본 수출 2030년까지 350억달러로 확대"</t>
+          <t>[특징주] 멜콘, 코스닥 입성 첫날 42% 강세 마감…상승폭은 줄어(종합)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>)= 대한무역투자진흥공사 가 수출품목 다변화, 판로 확대 등을 통해 2030년 대 일본 수출액 350억달.</t>
+          <t>)= 반도체 공정용 환경제어 장비 기업 멜콘이 코스닥 시장 상장 첫날인 15일 40%대 강세 마감했다.</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015087900003</t>
+          <t>https://www.yna.co.kr/view/AKR20261015043951008</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>[속보] 코스닥 이어 코스피도 거래재개…서킷브레이커 해제</t>
+          <t>[바이오스냅] 한미사이언스, '건강한 헌혈문화' 확산에 앞장</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>코스닥 이어 코스피도 거래재개…서킷브레이커 해제 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
+          <t>)= 한미사이언스 가 대한적십자사와 함께 건강한 헌혈문화 확산에 나선다.</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015095300008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015128500017</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>코스피·코스닥 1단계 서킷브레이커 발동…8% 넘게 폭락(종합)</t>
+          <t>'검은 목요일' 패닉…코스피·코스닥, 7%대 급락 마감</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>)= 15일 국내 증시가 급락하는 가운데 코스피와 코스닥 지수가 8% 이상 폭락하며 연이은 서킷브레이커가 발동됐다.</t>
+          <t>)= 인공지능 투자 수익성 논란이 다시 부각된 가운데 코스피가 15일 7% 넘게 급락했다.</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015093551008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015134100008</t>
         </is>
       </c>
     </row>
@@ -8076,12 +8076,12 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>[속보] 코스닥, 거래재개…20분간 매매중단 후 서킷브레이커 해제</t>
+          <t>노동부 "DN오토모티브 납 조작 검진기관 개입 의혹도 수사 요청"</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>코스닥, 거래재개…20분간 매매중단 후 서킷브레이커 해제 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
+          <t>)= 자동차 부품업체 DN오토모티브의 노동자 혈중 납 농도 조작 의혹과 관련해 고용노동부가 특수건강진단기관이 개입.</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015094300008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015129500530</t>
         </is>
       </c>
     </row>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>국토부 "주간 아파트값 통계, 전문가는 조정·국민은 공표 원해"</t>
+          <t>코스피 급락에 긴급 점검회의…이억원 "리스크 관리에 만전"</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>)= 주간 아파트 가격 통계 개편을 놓고 전문가들은 통계의 한계를 이유로 조정이 필요하다는 의견.</t>
+          <t>)= 코스피가 급락해 장중 5,500선을 밑돈 가운데 금융당국이 긴급 점검회의를 하고 리스크 관리와 투자자 보호를.</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015091600003</t>
+          <t>https://www.yna.co.kr/view/AKR20261015130500002</t>
         </is>
       </c>
     </row>
@@ -8145,17 +8145,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>[속보] 코스닥 이어 코스피도 1단계 서킷브레이커 발동</t>
+          <t>[속보] 공포의 '검은 목요일'…코스피·코스닥 7%대 급락 마감</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>코스닥 이어 코스피도 1단계 서킷브레이커 발동 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
+          <t>공포의 검은 목요일…코스피·코스닥 7%대 급락 마감 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015093900008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015131900008</t>
         </is>
       </c>
     </row>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>코스닥 8%대 폭락에 서킷브레이커 발동…20분간 거래 중단</t>
+          <t>[외환] 원/달러 환율 6.3원 오른 1,344.6원(15:30 기준가)</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>)= 15일 국내 증시가 급락하는 가운데 코스닥 지수가 8% 이상 폭락하며 서킷브레이커가 발동됐다.</t>
+          <t>원/달러 환율 6.3원 오른 1,344.6원 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015093500008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015130900002</t>
         </is>
       </c>
     </row>
@@ -8219,17 +8219,17 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>[속보] 코스닥 폭락에 서킷브레이커 발동…20분간 거래 중단</t>
+          <t>LH, AI 대전환 선포식…" 주거 혁신 앞당길 것"</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>코스닥 폭락에 서킷브레이커 발동…20분간 거래 중단 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
+          <t>)= 한국토지주택공사 는 인공지능 을 기반으로 경영을 혁신하고자 15일 'AI 대전환 선포식'을 열었다고.</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015093000008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015093200003</t>
         </is>
       </c>
     </row>
@@ -8256,17 +8256,17 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>여당도 가상자산 과세 유예법안 첫 발의한다…"2029년부터 시행"</t>
+          <t>주담대 변동금리 또 오른다…9월 코픽스 0.25%p↑</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>)= 가상자산 과세를 2년 늦추는 법안이 여당에서도 처음으로 발의될 예정이다.</t>
+          <t>)= 기준금리와 시장금리 상승 영향으로 은행권 주택담보대출 변동금리의 기준인 코픽스.</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015091500002</t>
+          <t>https://www.yna.co.kr/view/AKR20261015126700002</t>
         </is>
       </c>
     </row>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>한투증권, JCR 일본 신용평가서 신용등급 'A'로 상향</t>
+          <t>[게시판] 소비자원, '한국 ESG 혁신정책 대상' 최우수상</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>)= 한국투자증권은 일본 신용평가사 JCR 이 당사의 외화 장기.</t>
+          <t>한국소비자원은 15일 사단법인 한국정책학회 주관 '제5회 한국 ESG 혁신정책 대상'에서 사회 부문 최우수상을 받았다고 밝혔다.</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015092100008</t>
+          <t>https://www.yna.co.kr/view/AKR20261015127700030</t>
         </is>
       </c>
     </row>
@@ -8330,17 +8330,17 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>75개 농림축수산단체 "CPTPP 가입 반대 기본입장 변함없다"</t>
+          <t>관세청장 "세관 '수사심사과' 신설 추진…공소청과 많은 협력"</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>)= 농업·축산·수산·임업 분야 75개 단체는 15일 포괄적·점진적 환태평양경제동반자협정 가입에 대해.</t>
+          <t>)= 이종욱 관세청장은 검찰청 폐지 후 특별사법경찰관 수사 시스템을 보완하도록 "수사 심사과.</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015089900030</t>
+          <t>https://www.yna.co.kr/view/AKR20261015112900002</t>
         </is>
       </c>
     </row>
@@ -8367,17 +8367,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>소비자원 "편의점 김밥 나트륨 함량, 하루 기준치 최대 70%"</t>
+          <t>캠코 선박금융 90% 수도권에 집중…“해양수도 육성과 엇박자”</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>)= 편의점에서 판매하는 김밥 한 줄에 하루 나트륨 섭취 기준치의 최대 70%가 들어 있는 것으로 나타났다.</t>
+          <t>올해 선박금융 총 2조8000억원 달해 부울경 지원 규모는 2854억원 그쳐한국자산관리공사 가 시행하는 선박금융 지원이 수도권 소재 해운사에 90% 편중돼 개선해야 한다는.</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014126200030</t>
+          <t>https://www.mk.co.kr/news/politics/12176819</t>
         </is>
       </c>
     </row>
@@ -8409,12 +8409,12 @@
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>중기부, '모두의 창업' 1라운드 1만명…창업자금 200만원 지원</t>
+          <t>코스피 급락에…이억원 “투자자 보호에 적극 대응하라” 주문</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>)= 중소벤처기업부는 9만3천여명이 몰린 2차 '모두의 창업' 프로젝트에서 1라운드 진출자 1만명(일반·기술 8천명.</t>
+          <t>7%대 ‘뚝’5500선 마감하며 하락세 금융당국, 대내외 경제 여건 영향 분석 투자자에 “기업 본질적 가치 판단 필요”코스피가 15일 급락하며 하루에만 7%대 빠지며 5500선에.</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014182900030</t>
+          <t>https://www.mk.co.kr/news/economy/12176796</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>“잊고 있던 페이 잔액 255억원 돌려받으세요”…빅테크 3사, 정기 알림·환급 안내</t>
+          <t>[단독] 펄펄 끓는 바다, 양식장 1747만마리 폐사…‘고수온경보’ 역대최다</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>빅테크 3개사 매년 1회 이상 이용자에게 잠든 잔액 통지네이버파이낸셜 등 빅테크 3개사가 오랜 기간 사용되지 않고 잠들어 있는 선불 잔액을 매년 주기적으로 알려주는 서비스를 실시한.</t>
+          <t>정부 양식장 이전지원 해상 1곳 그쳐 피해 반복에 육상양식 대안 부상올 여름 고수온 경보가 내려진 해역이 역대 최다인 27곳으로 늘면서 양식어류 1747만마리가 폐사한 것으로 나타.</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176532</t>
+          <t>https://www.mk.co.kr/news/economy/12176779</t>
         </is>
       </c>
     </row>
@@ -8483,12 +8483,12 @@
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>오세훈 “전월세난 적극 대응…올해 주택 1만5천호 착공”</t>
+          <t>“주식은 빠지는데 주담대 이자는”…코픽스, 3년 10개월만에 최대폭 상승</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>오세훈 서울시장은 15일 서울의 주택 공급과 관련해 “올해 1만5000호가 실제 착공에 들어갔고, 모아주택‘도 지난 8월 첫 준공의 결실을 보았다”며 “그동안 꾸준히 다져온 공급.</t>
+          <t>8월 신규취급액 코픽스 연 3.45% 지난달 숨고르기 후 0.25%P 급등 5대銀 변동형 금리 상단은 6.46%은행권 주택담보대출 변동금리의 기준이 되는 코픽스(COFIX·자금조달.</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176554</t>
+          <t>https://www.mk.co.kr/news/economy/12176776</t>
         </is>
       </c>
     </row>
@@ -8515,17 +8515,17 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>[단독]LH 토지 계약해제, 4년 만에 6.9배…11조 규모 토지는 미재공급</t>
+          <t>최형욱 행복청 차장 “사람 옮기는 건 기관, 눌러앉게 하는 건 정주환경”</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>계약해제 2021년 146필지 5년 뒤 1002필지 2026년 8월까지 계약해제 2689필지 달해 당초 계약금액 따지면 16조8000억원 규모 미재공급 토지 402만㎡해제 토지면.</t>
+          <t>행복도시 현장 누빈 첫 내부 승진 차장 첫마을 입주 때 상수관·이삿짐까지 챙겨 44개 기관 이전 앞두고 “청사만으론 부족” 병원·대학 갖추고 국가 장기계획 세워야최근 행정중심복합도.</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176535</t>
+          <t>https://www.mk.co.kr/news/economy/12176769</t>
         </is>
       </c>
     </row>
@@ -8552,17 +8552,17 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>NH농협은행, 美 천연가스 파이프라인 금융 참여…6천만 달러 대출 실행</t>
+          <t>“내가 손절만 하면 다시 오르네”…하루 만에 반등한 금값 이유는?</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>미드스트림 인프라 시장 진출 본격화NH농협은행은 미국 텍사스주 퍼미안 분지에서 아과 둘세와 케이티 지역을 연결하는 천연가스 파이프라인 건설 사업에 참여해 총 6000만 달러(원화.</t>
+          <t>4084달러까지 하락한 국제금값, 15일 4158달러 美 CPI 3.7% ↑고금리 장기화 우려에 금값 출렁 국내 금 투자 수익률도 국제 금값·원달러 환율 영향미국의 물가 상승률.</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176525</t>
+          <t>https://www.mk.co.kr/news/economy/12176754</t>
         </is>
       </c>
     </row>
@@ -8589,17 +8589,17 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 중고차 판매량 TOP5는?</t>
+          <t>[Visual] ‘AI 해킹’ 금융권이 뚫렸다</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>KB차차차 상위 5개차종 모두 현기차 20대는 아반떼, 3040은 카니발KB캐피탈이 운영하는 중고차 거래 플랫폼 ‘KB차차차’에서 올해 3분기 가장 많이 판매된 중고차는 현대차.</t>
+          <t>연초부터 금융권 해킹 시도 포착 신한은행 시작으로 피해 확산 금융사 16곳·정보 10만건 유출 中 AI 해킹 도구 사용 정황 당국, 동일범·AI 활용 여부 조사국내 금융권을 겨냥한.</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176523</t>
+          <t>https://www.mk.co.kr/news/economy/12176706</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>“반도체에 큰절 한번씩 해야겠네”…올해 적자 43조 ‘8년 만에 최소’</t>
+          <t>[속보] 다시 오르는 용산 집값…상봉·신내동 소형아파트까지 ‘들썩’</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>반도체발 법인세 예납으로 세수가 큰 폭으로 늘어나면서 올해 8월까지 나라살림 적자 규모가 8년 만에 가장 작은 것으로 나타났다. 총수입에서 총지출을 뺀 통합재정수지도 8년 만에.</t>
+          <t>서울 아파트값 88주 연속 상승 중랑·성북 등 강북권 상승세 주도 강남3구 하락 지속용산은 반등 경기 0.26% 상승, 세종 상승 전환강남3구의 아파트값 하락세에도 서울 집값.</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176503</t>
+          <t>https://www.mk.co.kr/news/economy/12176569</t>
         </is>
       </c>
     </row>
@@ -8658,32 +8658,32 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>현대차·LX인터 등 11곳 ‘2026년 아이 키우기 좋은 기업’ 수상</t>
+          <t>AFC, 중동 정세 불안에‥"1월 사우디 아시안컵, 1년 연기 검토"</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>한미연, ‘2026 아이 키우기 좋은 기업’ 발표 제도만 ‘갖춘 곳’ 아닌 ‘제대로 쓰는 곳’ 선정 “임직원 출산·양육 지원 넘어 지역상생까지” 4개부처 장관상27일 서울 은행회.</t>
+          <t>AFC, 중동 정세 불안에‥"1월 사우디 아시안컵, 1년 연기 검토".</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176468</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE82M05tbUctTmVxaGdlY1VWdDdtNTRyS1Y2eFU4bFVNRTg4ZmljVHgxVWhCWTlOWGRkLXZ6QTlJR0xMNldpWTBNaE93ZWN2NkUyc1FZbmZXLVJVYzNQNGd6TkpybTItQklHVnR2QWlMakhQU3hBcEHSAXZBVV95cUxOSzJsR2NHTnBNM1MxLWdRTjRySnFmZm1WUWgzZzBMdXprb29YS3JCYzdObUppZUl5U0VXaUxfQ2VSUXJJaDNLd0VWaUVVS3J6akdsbGRQM2huTXNZSUhNRDF2RTNYWFJTYThTaHpaNnBmOWFiUkln?oc=5</t>
         </is>
       </c>
     </row>
@@ -8695,32 +8695,32 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>“곰팡이 벽지, 집주인? 세입자? 누가 도배하냐”…임대차분쟁 접수 급증</t>
+          <t>트럼프 새 대변인, 美변호사시험 불합격…경력 논란 확산</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>올 8월까지 1217건 4년새 2.3배로 조정 성립된 사례는 6건중 1건 그쳐전세보증금 반환과 집 수리 문제 등을 둘러싼 임대인과 임차인 간 분쟁이 크게 늘고 있다.</t>
+          <t>트럼프 새 대변인, 美변호사시험 불합격경력 논란 확산.</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176465</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9hTW9HYWFBTWpib1Fnd1hMY0l4VjhhanNmcWVDc1luWnlCNEFQelItWG5JX2E2dHE3ai1UVVFuVnVocW1PWDNJSFA3Y25wN0R3VW1kSnVsSkUtNk91allsTmJZOFJOWVk?oc=5</t>
         </is>
       </c>
     </row>
@@ -8732,32 +8732,32 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>“아들아, 네 노후는 내가 도와줄게”…10건 중 7건 ‘부모가 대신’ 신청한 청년 첫 연금</t>
+          <t>노벨평화상 필라이, 트럼프 ICC 제재 비판</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>강남권·학군지 등에 신청 몰려 농어촌과 비교하면 편차 두드러져내년 시행되는 ‘청년 생애 첫 연금보험료 지원’ 사업의 사전 신청 10건 중 7건은 청년 본인이 아닌 부모가 대신 신청.</t>
+          <t>노벨평화상 필라이, 트럼프 ICC 제재 비판.</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176464</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB1eURfdmF4ZTVVbE8wVzVKVkItdHhSWERSWkhpN2ppYWJDUVNreVJVLTAxREJTVlB5bmRWdHQ4ZThYckxhbWpPbW4ySDZvbnNEZlcwdjYybDZuVTdKUDk1MHFfa1haLURUVHRaRDhyRFdBOUl30gF0QVVfeXFMT0lwcEtUT3ptY3FZLXdIZVd6MWdiMUlVanZxbmgzTUI4NHZfSlFreElCWG85VUhzNE9tQmdRMTNza05za0pnTXdPbXlqNUJwTXhleHJQZ1VLTDVSTnRmYmJmd3o1RE9TYjBJLVdDaEVTZTRTMU0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8769,32 +8769,32 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>김재식·장종필의 법을 알면 부동산이 보인다</t>
+          <t>미국, 이란 공격에 ‘비핵무기 중 최강’ MOAB 투하 검토 - CNN</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>계약금을 포기하거나 두 배로 돌려주면 부동산 계약을 언제든 되돌릴 수 있을까. 계약 해제의 기준이 되는 ‘이행의 착수’와 최근 대법원 판례를 통해 계약금과 중도금을 둘러싼 법적.</t>
+          <t>미국, 이란 공격에 ‘비핵무기 중 최강’ MOAB 투하 검토 - CNN. 아울러 총선 앞 네타냐후, 전쟁 불씨 만지작트럼프는 멈칫.</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>계약금 두 배 주면 끝일까? 부동산 계약을 되돌릴 수 있는 마지막 순간</t>
+          <t>경향신문</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/sports/12176461</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE8wYnV4dFRLNVlTUC1EdEE3QlBBUHNaWVF1SGJKUnZqSFg3bDNaWDN3dGZsQ1dnLWFZREhDSVVmVEJwQnZxa1JVN1RXbHBqbHhTUkROeDZLZUN1UdIBX0FVX3lxTE1xVEZFM3luMGg1QnhEN1JhdjRXRnlRVTZRaFhiUE5hVm1QZk5VaVFBVGRKemFUVGFIWFhMS0FaMkx1LXpONU5BdGVFS0xtY2ZtTDlaMzllLUxIdk4zZmhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>“평생 월 200만원 꽂힌다는데”…100명 중 2명만 가입하는 주택연금 왜?</t>
+          <t>[포착] “5000년 만에 처음 만졌다”…‘세계서 가장 오래된 난파선’ 튀르키예서 발견</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>“실질적인 인센티브 확대해 문턱 낮춰야”“월 200만원씩 나오는 주택연금에 들면 여유 있게 여행도 다니고 숨통이 좀 트일 것 같은데, 자식들에게 집 한 채라도 물려줘야 하나 싶어.</t>
+          <t>“5000년 만에 처음 만졌다”‘세계서 가장 오래된 난파선’ 튀르키예서 발견.</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>나우뉴스</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/economy/12176433</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFAxTEY1bTQ2Q2Y2QmRpY2JfUGo5M1c2Y01pV2lfYUF6ZmZxYzRlbXBYYzNuMzk4UTZQTC1rb0JzTFBQUVl3SXZhd0VQazgxVGo0OHNyaTFfRkdSd1JkOWw5YWp3LXBDVjhVdHV3OVNjMVk?oc=5</t>
         </is>
       </c>
     </row>
@@ -8853,22 +8853,22 @@
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>호르무즈 해협서 컨테이너선 침몰…이란 공격 확대에 원유 수송 차질</t>
+          <t>“북한, 러시아서 드론 대량생산 기술 습득…한국·일본에 새 위협”</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>호르무즈 해협서 컨테이너선 침몰이란 공격 확대에 원유 수송 차질. 아울러 호르무즈서 피격된 UAE 화물선 2척 침몰"이란 공격 강화".</t>
+          <t>“북한, 러시아서 드론 대량생산 기술 습득한국·일본에 새 위협”. 아울러 “北, 러 드론 공장에 1.2만명 파견대량생산 노하우 갖고 평양으로”.</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>뉴스핌</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE95MEh5LUtzVjNXSGt2LUs5eWwtVnV6Y2VZY3VhTFk2d0Q0U1BzdnQtT1cyN0RnSnp5ZnlKNjJRWUNHNFFPQ2J0U1M2RWU1QVVGSTZlRUJHaHZNVWl5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOczVHZ1RfWklZTWcwOWI4d2xnS1lLOFRuUE5iVm1tcVkzaXRZb05Oa3lnOEE5LVE1ZzJvcXpKd1ZDUFQyYUM2eUJUQnFPOW85R3pGXzYzOWRIdVdVa2loVEZwcUJDTkV4dFVQVzdna213eGc1MUE1X0tFTmVkakxZV1FR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8885,27 +8885,27 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>[속보]북·중 ‘신압록강대교’ 완공 12년 만에 공식 개통</t>
+          <t>중간선거앞 '사익추구' 불똥튈라…트럼프, 그리스 대사 경질</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>북·중 ‘신압록강대교’ 완공 12년 만에 공식 개통.</t>
+          <t>중간선거앞 '사익추구' 불똥튈라트럼프, 그리스 대사 경질.</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lTzlzbjVWd19xZjRuVm5aZlJ3b2tJTzZRUjVJSVpqc2pteHpmS1NfalhrWERWUVFSTVl1SHpTTU1yZl9pX3NvYnRpbm1US1BZb2p2TmQtTjE4d9IBX0FVX3lxTFBpbDFrNmoydS1NQzNlTlBSMlk1VVktd0pveko1TGRzZmUwcnFLS1dkM2daNEU0OFJXZHNTaEFaSEQ0NmRTeV9lY2pNT2VjQ29Qd0l4R3JPbmtrVlk2VmlN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFB6M3AtNHdfanMxZXZVb2RCN2l6U2ZCcEhkMjBqeklYb3VoRGsxcnpCeXg3SWYyUUlfbTRJS1llMW9ZT0Q4ZmxhY2x4UXVITjhHYXFnVS1yYlZ3cWfSAWBBVV95cUxQNjlNV2NaT0pWWTMwMUF3OXNhZUR5OE1WV2lkVVRHR25WOW0wYTlNV0VrSGlSMU9CWFdpT0V3MmVuSTF1djZSXzNEVFlQQ3lRcENubmtBMkdIdWpEM3J6N3o?oc=5</t>
         </is>
       </c>
     </row>
@@ -8922,27 +8922,27 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (8개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>젤렌스키 “트럼프 다른 편 선택 고통스럽다…배신감 느껴”</t>
+          <t>[사진] 영국 총리관저 앞에서 만난 버넘과 젤렌스키</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>젤렌스키 “트럼프 다른 편 선택 고통스럽다배신감 느껴”. 아울러 러시아 “미국과 ‘경유 딜’ 며칠 내 체결될 것세계시장 10% 규모”.</t>
+          <t>영국 총리관저 앞에서 만난 버넘과 젤렌스키. 아울러 "미 압박 막아주겠다"트럼프 빈자리 채우고 나선 유럽 각국.</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>뉴스핌</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4tNGtPT2ZtcjhWQnp4MU1KcGIwck5fZzY0eDRRX00tNk03UTh0bEc2dWFneG9kUFZhQlJQZGVZZXhUZ0JHTnRHcGVrTFIycVY3QWFIYTFOaDA1dHZXS2VINUJhcDFQbE13eFR2WW53?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBkUHFoU1lLTlFhSHlpZ09VMU9vZ2JTVXhzRW1teHJiQ2NQemJsUGt5QXprS2MxUFNWN1pVZTVBbzAxbXVZOE9RejROdzRSektQcVBrM2VqX24zcDFv?oc=5</t>
         </is>
       </c>
     </row>
@@ -8959,27 +8959,27 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>프로축구선수협 "1월 사우디 아시안컵 우려··선수 안전 보장돼야"</t>
+          <t>미군 "이란 연계 선박 격침…미 해군 함정 표적 삼았다"</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>프로축구선수협 "1월 사우디 아시안컵 우려··선수 안전 보장돼야".</t>
+          <t>미군 "이란 연계 선박 격침미 해군 함정 표적 삼았다".</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBxMjRNdFk3aTNSc1Rzbnp5c291UFNGWDNZWk45TlFXRG1ST0JvUE82YU1nazcwWGJtc3FRRjhMSlhsVURoWkhqcnF3bDJmWVRhVzYzUUVEYlhjTTNwZEJDNU56cEFwWTV0dGh2YWF0UXE3RVdpcUHSAXZBVV95cUxQRXAxbXBXWXRxRlZPaUNUcHhweGNiQVR1UWZ5U0lCS0FiaDN4MEFxaWtMMllCeHdyeDIwVmxQRnR4cHBhWjZCOEVrQzJIQTF2RGtzbUdGY1hxdGFFMnRvcm5MU19UNXVEOXlqMmtGYm9VckxjWi1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1qMVh5Tmh6WWRaRk4xMjFxZ3BLVXFIc0V4ZGpaYVFjdHg2cllFNTc4OVBnbXBJSGhrbHVvc3ZIUFA4SDZ4UUdBRUhydXh0bEdGRlVkbHg1U1A1Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8996,27 +8996,27 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>스페이스X(SPCX.O), 우크라군 스타링크 통신 제한...우크라 "정치적 상황과 관련" 주장</t>
+          <t>美 건국 최초 '총살형 생중계' 논란…어떤 방식으로 집행되나</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>스페이스X, 우크라군 스타링크 통신 제한우크라 "정치적 상황과 관련" 주장.</t>
+          <t>美 건국 최초 '총살형 생중계' 논란어떤 방식으로 집행되나.</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>알파경제</t>
+          <t>광주타임즈</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1rMDdpbkY5empESDhoSUVTUzRJUU9tZ2VwQmo4dmdsZDlQR19rT2lhTnFWOGdPcGNvb0pWTHgwRUZyUDA0UFRRajR6MlFqZGJIWlJGMTZiT2NxTWhYMUI4OHNWWTY1Ry1uSzZOVDBB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9aTUcwZmdWMzVzSUdVRXVseDBHRVJPakR6eGlIZDNYRVlUc0pQek5nLUpZN0VISFpxN25xR2JWRzVVOHVtenRXZ3RvZ3pFMUJTUmQzWExlVkp5NXJYM09OSHRnMEdHYlR2Nmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9033,27 +9033,27 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>교황 충분히 완치 기대…수년간 폐암치료 혁명 있었다</t>
+          <t>그린란드 정부, 트럼프 ‘대규모 석유·가스 탐사 임박’ 주장 반박 - 조선비즈</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>교황 충분히 완치 기대수년간 폐암치료 혁명 있었다. 아울러 ‘폐암 진단’ 교황, 폐수술 하루 만에 식사·미사 재개···“여러분 기도는 교회의 큰 선물” 첫 메시지.</t>
+          <t>그린란드 정부, 트럼프 ‘대규모 석유·가스 탐사 임박’ 주장 반박 - 조선비즈.</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9ucUxoMmwxT0ZKZFhNc1J0NlJLS01wYXlFc0ZzMFhDX2ppb3NaUEMyczkzclZqYVczamNXRXZnUXRPckpxRjcyenI1b3JqRm4zcExEQjA4MzdDQVHSAWBBVV95cUxPOXVEZHlSVjI5TExtZlpsdEtjaUZUdjNOdWs2MzFQYnNFWlZUWkJJN3NFNG5UMGRUMXJ3Y0dMb1dYOEMtaVhHSEZEdy1hRjRuQ09xY0xoX2tPdFZWTE5zNGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPZXIwSlFQWi02cEl1UkU3cGNUSkQxdjV1aTVlQ0VRYVI1dVR0MVBuNEk3WmdUX0R0ZHpSa2ppVzdHcnNkbnJLS3AyMnBZbEhRWWZZVGdabVJDc0hYdko3Q1EwbmJTOUhTZmd2OEZ0ejlIbUtIZDhFMUFjOF9SS3FJTUEtNjRKRmF1YWxMVU1iVU95ZUZuNjQzbWZWZ2hwQdIBsgFBVV95cUxOR0FMWjlCb0pEcjJVYllMZlY3ejZ0RjRzM3RjOEFDNkwtOWZWUnQzRmZ1TXk2UkRpMEtyS3JpQ1ZDREF1RXU0dEI5eC1hYTV5YWFyTGZwSHBKN3NXVEYtUHNhMUJuelk5NkZPRXhnV2gwNldTRFFaUnZFX0dkV1JuQ0FoX3dGaGFHcnR2MlRyNVF1TGdQRmJQaVdUSDVoNWllSE4xdHhxVS1BbVU1VE9mOGZB?oc=5</t>
         </is>
       </c>
     </row>
@@ -9070,27 +9070,27 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (8개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭"</t>
+          <t>노르트스트림 폭파 4년만에 재판…전직 우크라 장교 법정에</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭".</t>
+          <t>노르트스트림 폭파 4년만에 재판전직 우크라 장교 법정에.</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9ZcTM4YlJJUTFoUXZ5ZGZydnpQUnVFSGtHeHhOQWo0VUU3Wm9oc2VQMlFvM2c4SnVwVFRfNHh5NThkWERpQ3NZLWZRaXZvMG9aRE5PLUNxWXVJUjVaUDE4c3FfREhTczA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1DY0NGMTlFY2JJTGYyNHBtUjh5ZW51SjR2ZFZEOEhUYnV0Ym15anptZTN4RklEUEFudS1rVlVjQ2tyOE82UEkyWVhvbEJrNF90MXkycjRBd1Z6d00?oc=5</t>
         </is>
       </c>
     </row>
@@ -9107,27 +9107,27 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>북·러, 평양서 수교 78주년 연회…"피로 맺어진 동맹"</t>
+          <t>젤렌스키 "러 정유시설 공격 재개"…트럼프 압박 정면돌파 시사</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>북·러, 평양서 수교 78주년 연회"피로 맺어진 동맹".</t>
+          <t>)= 볼로디미르 젤렌스키 우크라이나 대통령이 미국 트럼프 행정부의 압박에도 러시아의 정유시설에 대한 공격을 재개한다.</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE52R25VQ05LdEo0MnpyelpFeFpKaHRqaUhwMWNadlFNX0d3TkhIWVQ4V3pCbmFlT0JtblNUaVBZU3dsdi1HYWdIMGY2cjlTTXY3NjFqaUVUdndVN2lXV0ZlbnM0b2lhODQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015138100009</t>
         </is>
       </c>
     </row>
@@ -9144,27 +9144,27 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (8개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>금발·짙은 화장·도톰한 입술···트럼프 오른팔 여성들, 꼭 닮은 ‘마가 페이스’와 충성 공식 [이윤정 기자의 소소월드]</t>
+          <t>인니 대규모 산불로 연무 확산…이웃국들 대기질 악화로 골머리</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>금발·짙은 화장·도톰한 입술···트럼프 오른팔 여성들, 꼭 닮은 ‘마가 페이스’와 충성 공식. 아울러 남편을 "대통령"으로 부르기도 백악관 새 대변인, 망신살 신고식.</t>
+          <t>) 손현규 특파원 = 인도네시아에서 11년 만에 발생한 최악의 산불로 연무가 계속 확산하면서 대기질이 악화한 이웃국들이 골머리.</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1hbTVZN2xGX25aQkdlTnNwZEVQRVZzbDdjeHYxOGZmNDBxVU4yUFU0NmlRanFHbVY3N0VNY1JHbTNUS0ZWd2ZtVktjTnE4WFo2MlRBQS1xdnU0UdIBX0FVX3lxTE9ZdTl0OEZYbmtzQ2k4ZkhWVGNJeS11NjBLZjE2MVhaUkE2M1hBTVNVblRNcG4zUnpJY0lNbUFmQlFmTkw2b2hDLWNvbWhtcGh5VmdzLTJ3VGpUWnNxX0NZ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015136700104</t>
         </is>
       </c>
     </row>
@@ -9181,27 +9181,27 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (8개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>유럽, 트럼프 압박받는 젤렌스키 지지…'美 대체 불가' 지적도</t>
+          <t>[쇼츠] 새벽하늘 푸른색 괴생명체?…팰컨9이 만든 '우주 해파리'</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>유럽, 트럼프 압박받는 젤렌스키 지지'美 대체 불가' 지적도.</t>
+          <t>) 아직 동이 트지 않은 새벽 시간, 미국 동부 연안 상공에서 정체불명의 거대한 불빛 덩어리가 목격돼 시민들을 놀라게 했습니다.</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5ZZ2hlb3ZSajNaXzJGQzhpcWRGSkdlRTM2U1RlamZzU0JSZ0JvOVBtWXhYUkNQb0NBaEh2dzVyemdXbjZBRWxlbng5eFFFME5ZZDZobmpMby1XX0HSAWBBVV95cUxQYk1nUUhFSW9ockQ3YWlsUGxTUmVoTkRaNG9pdWhhNFdsc2lXd1VlQndvWldFRDBXNzQtdnBIaTFpVWxldnBKRGtVRVI3Qi1WeEx0RFRXdlMyXzZFVzVqcGg?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015130100704</t>
         </is>
       </c>
     </row>
@@ -9218,27 +9218,27 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>“北, 러 드론 공장에 1.2만명 파견…대량생산 노하우 갖고 평양으로”</t>
+          <t>[쇼츠] 그리펜 전투기 360도 돌리더니…태국 왕비, 여객기 몰고 일본행</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>“北, 러 드론 공장에 1.2만명 파견대량생산 노하우 갖고 평양으로”.</t>
+          <t>) 14일 방콕비즈뉴스 등 태국 매체에 따르면 수티다. 왕비가 이날 전용기를 직접 조종해 태국에서 약 7시간의 비행 끝에.</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4yczZSa0J2UkVfVnRQaWRCd19Db2dZRzdXZ1U0TzZ6Zkl1bE9HYlRPSnVhTS12a0ZEQUttY1hpOW5lMWhMb0FLNGJvZGtmS19WbmJMSjRRVnEzREFZSld4c3dKUU5GU09EMVVKMVM1SjltVXVZZW130gFmQVVfeXFMTjdIVDRtbDJHSEdpcF8yUjZtRjVsYkdIRTB1SDhQOHNFYXMwal8xNEdMbGxpdVFiOFJ6R3hDZXpoWGttNjNDblpGQ2tITS1yZU9xYXl2eVJCcXBMak5sd3FkTi1MQXhB?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015135500704</t>
         </is>
       </c>
     </row>
@@ -9255,27 +9255,27 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>미군 "지난 6일 오만만서 美함정 감시하던 이란 연계 선박 격침"</t>
+          <t>'트럼프 구상' 가자 다국적군기지, 이스라엘 불허에 첫삽도 못떠</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>미군 "지난 6일 오만만서 美함정 감시하던 이란 연계 선박 격침".</t>
+          <t>)= 도널드 트럼프 미국 대통령 주도로 만들어진 가자 평화위원회가 이스라엘의 불허로 가자지구 내 임무지원 기지 건립.</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE12OUdGaERjaUtZcVg5blA0RF9ZUUZSM0F2UUZGaEUtM2l3ZTIyOExNX2U5TXdpdFdLbExxQThqRzNnZmlzWTZhbEJlYkdGSm9SdGx2NmozbEQ3Q3RUVnhvTVhaMUhqMURtSlpIWF9CcEF3bkYx0gF0QVVfeXFMT3VPR0xfbGlzSmJqMWJTTGNLd1hGM1BjUU1RaVVRZE9YODhCUlZ6VVoxaVljM0QyQnpUNWZfOGlkaHNNbTRYNlgzWmRXN1lDQjNTZHA5TDZzZG9ZTF82XzQtX29YLTg0Q1JIUG8xOTVnLXExVjE?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015136500009</t>
         </is>
       </c>
     </row>
@@ -9292,27 +9292,27 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>러시아, 우크라이나 공격 중 발전소 타격...젤렌스키 “에너지 휴전 위반”</t>
+          <t>대만 "中, 타이베이시장 후보 부친 기업 제재로 지방선거 개입"</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>러시아, 우크라이나 공격 중 발전소 타격젤렌스키 “에너지 휴전 위반”. 아울러 "러 경유 사고 우크라엔 정보 제한"美, 對우크라 정책 이상기류.</t>
+          <t>) 김철문 통신원 = 중국이 집권 여당 타이베이시장 후보의 부친 회사에 대한 제재를 가해 지방선거 개입에 나섰다고 대만 당국이.</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>VOA 한국어 홈페이지</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5Fd2dpZ2NmbmZ6TlQ3OFpwVlpLU2pDSkY0LTE5d2kyX29sQ2g4TFdQLTdnSjlMNGM0UWdVUGlDUUtkWEc5VmVuMjc4d1ZpUnQ1N1FwcG0yYTJRcmcwOGF5TkNkYWFiT1lGMUd1LWpnWFcxd9IBdEFVX3lxTE1xMDdUU3BSblZnM3haek1GUnN6UkpEbXJCT3lzMHFuYzduZHRYOTlzT3E0eW1mQk8yRFpOVHYzYWh5U29RemNCUVZPUXU0MXQ3QkhJaWpvYlF6R20za0FLWEhDN2VDOU5XQXFzWGd0NlhRMmdI?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015124000009</t>
         </is>
       </c>
     </row>
@@ -9329,27 +9329,27 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (8개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>美 '총살형 생중계' 역풍 맞을라…트럼프 "무산될수도" 일보후퇴</t>
+          <t>[영상] 컨테이너 2천500개 물에 둥둥…호르무즈 해협서 화물선 침몰</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>美 '총살형 생중계' 역풍 맞을라트럼프 "무산될수도" 일보후퇴.</t>
+          <t>컨테이너 2천500개 물에 둥둥…호르무즈 해협서 화물선 침몰 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1GcnBkc1RpT25jMjhScnR5b0pCU0VNemJ6SlBTNG04QzlvMzd1Q3VaVXVUVzk4MGVoRGtXYlpfc1BpUlFkM2RrZ0h0RHAzaHVkM0hOQkNmU09Fb3fSAWBBVV95cUxOM2FwVmJDWnhOY2RWd01OS0pnQ3pZVWRlU2dOX1dtSmJJdlVNTDQxVHBGcGp3U2EzbWF1NktFaExSajk1UC0xTF9NRXVpWGlHYjFMcEN2THlNT3hKSDFPeGc?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015132100704</t>
         </is>
       </c>
     </row>
@@ -9366,17 +9366,17 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>MLB 가을야구 '스몰마켓' 반란…새 노사협약 앞두고 비상한 관심(종합)</t>
+          <t>佛 극우 르펜 "대통령 되면 EU와 힘겨루기"…정면충돌 예고</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>)= 미국프로야구 메이저리그 양대 리그 챔피언십시리즈가 한창인 와중에 미국 언론이 '스몰 마켓' 팀의 선전.</t>
+          <t>)= 프랑스의 유력 대선 후보인 극우 국민연합 의 마린 르펜 의원이 내년 대선에서 승리하면 프랑스가 유럽연합(.</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015080151007</t>
+          <t>https://www.yna.co.kr/view/AKR20261015131100009</t>
         </is>
       </c>
     </row>
@@ -9403,17 +9403,17 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>中지방정부 "반도체는 국가안보 전략적 산업…CXMT 전폭 지지"</t>
+          <t>[게시판] 주오사카총영사관, '코리아타운의 미래' 세미나 개최</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>) 차병섭 특파원 = 반도체 산업 주도권을 둘러싼 경쟁 격화 속에, 중국 공업정보화부장 출신인 리러청 안후이성 신임 당서.</t>
+          <t>주오사카총영사관은 지난 14일 오사카 뉴오타니 호텔에서 '다문화 공생 플랫폼, 오사카 코리아타운의 도전과 미래'라는 주제로 재일동포, 오사카.</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015093400089</t>
+          <t>https://www.yna.co.kr/view/AKR20261015127800073</t>
         </is>
       </c>
     </row>
@@ -9445,12 +9445,12 @@
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>'홈런 3방' 밀워키, 다저스에 3연승…WS 진출까지 단 1승</t>
+          <t>4천400억원 투입된 北中신압록강대교…왕복 4차로·3㎞ 사장교</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>)= 밀워키 브루어스가 월드시리즈 3연패를 노리는 로스앤젤레스 다저스를 벼랑 끝에 몰아넣었다.</t>
+          <t>)= 압록강을 가로질러 북한과 중국을 연결하는 신압록강대교는 폭 33ｍ, 총연장 3천26ｍ의 왕복 4차로로 건설됐다.</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015092500007</t>
+          <t>https://www.yna.co.kr/view/AKR20261015124500009</t>
         </is>
       </c>
     </row>
@@ -9482,12 +9482,12 @@
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>'多死사회' 일본 도쿄 도심에 소규모 화장장 늘어난다</t>
+          <t>손주 자랑하려 사진 올렸는데…신상 털린 日 운동회</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>) 조성미 특파원 = 심각한 저출산 고령화로 '다사 사회'에 진입한 일본에서 도심에 소규모 화장장을 세워 화장시설 부족.</t>
+          <t>)= 가을 운동회 시즌을 맞은 일본에서 자녀나 손주 사진을 사회관계망서비스 에 올렸다가 타인의 신상 정보까지.</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015092000073</t>
+          <t>https://www.yna.co.kr/view/AKR20261015126600009</t>
         </is>
       </c>
     </row>
@@ -9519,12 +9519,12 @@
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>대만 야당, 전 국민에게 83만원 'AI 보너스' 지급 추진</t>
+          <t>'소니 산하 애니 OTT' 크런치롤 "번역에 AI 안쓴다…창작 영역"</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>) 김철문 통신원 = 내달 지방선거를 앞두고 유권자의 표심을 공략하기 위해 대만 야당이 전 국민에게 1인당 2만 대만달러(약.</t>
+          <t>) 이도연 특파원 = 소니 그룹 산하의 애니메이션 전문 온라인 동영상서비스 가 일본 애니메이션의 해외 서비스용 자막·더빙.</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015088600009</t>
+          <t>https://www.yna.co.kr/view/AKR20261015124100073</t>
         </is>
       </c>
     </row>
@@ -9551,17 +9551,17 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>러 '쿠릴열도서 폭격훈련' 통보에 日 항의…갈등 고조</t>
+          <t>트럼프 지지율 폭스뉴스 조사 36%…1·2기 통틀어 최저</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>)= 러시아와 일본 간 갈등이 고조되는 가운데 러시아가 양국 간 영토분쟁 지역인 쿠릴 4개 섬 에서.</t>
+          <t>)= 우파·친 공화당 성향 미국 뉴스채널 폭스뉴스에서 도널드 트럼프 미국 대통령의 국정 수행 지지율이 트럼프.</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015089600009</t>
+          <t>https://www.yna.co.kr/view/AKR20261015121200009</t>
         </is>
       </c>
     </row>
@@ -9588,17 +9588,17 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>북중 신압록강대교, 완공 12년만에 공식 개통…"무역 교류 촉진"(종합)</t>
+          <t>TSMC, 3분기 순이익 68.7% 늘어…6분기 연속 신기록</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>) 정성조 김현정 특파원 = 중국 랴오닝성 단둥과 북한 평안북도 신의주를 잇는 신압록강대교가 15일 완공된 지 12년 만에.</t>
+          <t>) 차병섭 특파원 = 세계 최대 파운드리 업체인 대만 TSMC가 인공지능 붐에 힘입어 올해 3분기에.</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015076652083</t>
+          <t>https://www.yna.co.kr/view/AKR20261015124300089</t>
         </is>
       </c>
     </row>
@@ -9630,12 +9630,12 @@
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>[영상] 태국서 길이 1.5m 자이언트 잉어 폐사 직전 상태로 발견</t>
+          <t>[게시판] 서강대 유로메나연구소, '수에즈 운하' 국제학술대회</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>) 태국 중북부 프라친부리주 의 한 마을에서 길이 1.5m의 초대형 잉어가 잡혔습니다.</t>
+          <t>서강대학교 유로메나연구소 와 사학과는 16∼17일 학내 정하상관에서 '수에즈 위기 70주년, 역사 유산과 세계질서 재편'을 주제로.</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015088500704</t>
+          <t>https://www.yna.co.kr/view/AKR20261015122000009</t>
         </is>
       </c>
     </row>
@@ -9662,17 +9662,17 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>"청천벽력" 교황 폐암진단에 개혁과제·순방일정 차질 우려</t>
+          <t>[르포] 12년만에 이어진 北中신압록강대교…긴장속 中주민 수천명 운집</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>)= 레오 14세 교황의 폐암 진단 소식이 갑작스레 전해지면서 교황의 건강 문제가 향후 직무 수행에 영향을 주는.</t>
+          <t>) 정성조 특파원 = "개방하고 무역하면 모두에게 좋아요. 조선 뿐만 아니라 조선반도 , 동아시아 전체를 연결하는.</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015085200009</t>
+          <t>https://www.yna.co.kr/view/AKR20261015115700083</t>
         </is>
       </c>
     </row>
@@ -9699,17 +9699,17 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (6개사)]</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>러, '북한군 참전' 영화 예고…북한 병사역에 한국 출신 배우</t>
+          <t>트럼프 새 대변인, 美변호사시험 불합격 확인…경력 논란 확산</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>)= 러시아가 우크라이나전에 파병된 북한군 활약상을 다룬 영화 제작 계획을 발표했다.</t>
+          <t>)= 변호사 경력을 내세우고 활동했던 케이티 재커라이어 백악관 대변인이 미국 변호사시험에 합격하지 못한 것으로 확인.</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015087100009</t>
+          <t>https://www.yna.co.kr/view/AKR20261015117600009</t>
         </is>
       </c>
     </row>
@@ -9736,17 +9736,17 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>[영상] 태국왕비, 이번엔 여객기 직접 몰고 일본행…전용차 운전 '파격'</t>
+          <t>"미군, 이란 추가공격에 '모든 폭탄의 어머니' 투하 검토"</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>) 스웨덴산 그리펜 전투기 첫 단독 비행에 나선 태국 수티다. 왕비가 전투기를 360도 회전시키는 '롤 기동'을 선보입니다.</t>
+          <t>)= 중간선거 전후 도널드 트럼프 미 대통령이 이란 공격 재개를 명령할 때를 대비해 미군이 이란의 에너지 인프라.</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015085400704</t>
+          <t>https://www.yna.co.kr/view/AKR20261015116600009</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -9778,22 +9778,22 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>日연립여당, '조속한 개헌' 의견 일치…평화헌법 조항엔 견해차</t>
+          <t>GTA6, 'NPC 대사를 위한 작가 팀'이 별도 존재한다</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>) 조성미 특파원 = 헌법 개정을 추진 중인 일본 연립 여당이 개정 헌법 조문안 작성을 서두른다는 방침에는 일치했으나 핵심 쟁점인.</t>
+          <t>GTA6, 'NPC 대사를 위한 작가 팀'이 별도 존재한다. 아울러 GTA 6 최신 정보 총정리: 현실적인 강도·수배 시스템 완벽 분석.</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>인벤</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015086200073</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yTUpmS0daaV9EVTVVM25TM25xT2sxUW9aWWlFNUQyMXR4UTI3NE9yVnFDdDh5dW9MY3pwQUl5amVzazV3TXdvcGRIMW85ZzVtakxxd3JiWmZlSU5LdDBuNGZyOWNLeUFqamV3S1k2NA?oc=5</t>
         </is>
       </c>
     </row>
@@ -9805,32 +9805,32 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>애플, 중국서 첫 AI 기능 12월 출시…새 시리는 제외</t>
+          <t>조지아 새벽하늘에 신비한 빛줄기…“우주 해파리 현상”</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>)= 애플이 오랜 기간 규제 끝에 중국 본토에서 인공지능 플랫폼을 출시할 준비를 하고 있다고 블룸버그 통신이.</t>
+          <t>조지아 새벽하늘에 신비한 빛줄기“우주 해파리 현상”.</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>애틀랜타 중앙일보</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015074900009</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5vX1dFOWFNNkg2Yk95dFFMZVhZdnRPSUZhdHBBSER4bkVNVW9jWlZnU2cxRlVOdVNQSHZyQmpTaEdnOG5jdXBEc3N3eEc0U28?oc=5</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -9852,22 +9852,22 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>우크라 생명줄 된 스타링크…일부 제한만으로도 전쟁수행 '비상'</t>
+          <t>[정보] 린델 나인 코어 시세 반등? 거래소 시세 살펴보기</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>)= 미국의 위성 인터넷 서비스 스타링크의 군사용 버전인 '스타실드'에 갑작스럽게 속도 제한이 걸리면서 우크라이나군.</t>
+          <t>린델 나인 코어 시세 반등? 거래소 시세 살펴보기.</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>인벤</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015084700009</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE8xeFVqNGtidm5vWDh1TnpORkxoeUVyUVVURXI2M2M1Z0p2OHJUb0ltZGVVOUVpSTJXd2VmLWxYcUZlY1lCRU1RV2l2OTktelltU1RGWkNjazBIY05sd0E?oc=5</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -9889,22 +9889,22 @@
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>AI가 생물무기 문턱 낮추나…"가능성 있지만 현실적 장벽"</t>
+          <t>갤럭시S23·갤Z폴드5도 원UI 9 업데이트 받는다</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>)= 인공지능 이 급속하게 발달하면서 AI가 생물무기 개발에 악용될 수 있다는 우려도 커지고 있다.</t>
+          <t>갤럭시S23·갤Z폴드5도 원UI 9 업데이트 받는다.</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>지디넷코리아</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015082500009</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBtSVVidk5hR284U29DeDRuZFZzVFJoaVFrWE1RRko4bWx2bWktbFVGam5kRTFLUWJDQUt6RG1IVk03ZlI5NnJBbFhoV2RibFgtb1VkZllB?oc=5</t>
         </is>
       </c>
     </row>
@@ -9916,32 +9916,32 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>MLB 가을야구 '스몰마켓' 반란…새 노사협약 앞두고 비상한 관심</t>
+          <t>코나미, '캐슬바니아: 벨몬트의 저주' 정식 출시</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>)= 미국프로야구 메이저리그 양대 리그 챔피언십시리즈가 한창인 와중에 미국 언론이 '스몰 마켓' 팀의 선전.</t>
+          <t>코나미, '캐슬바니아: 벨몬트의 저주' 정식 출시.</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>전자신문</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015080100007</t>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE1PY2M3anFfTTBzeGVzT283eFgxRE0wdnRaYzBzMjFEUnJqQ2Q4TDJZQUVNUFd2dzRHWnpTYzJOQlNTREZqUWFGOHJyRV9mUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9953,32 +9953,32 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (8개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>유럽, 트럼프 압박받는 젤렌스키 지지…'美 대체 불가' 지적도</t>
+          <t>다시 만나는 인페리아와 셀레스티아의 모험 ‘테일즈 오브 이터니아 리마스터’</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>)= 유럽 각국이 러시아와 전쟁 중인 우크라이나에 대한 지원을 강화하겠다고 나섰다.</t>
+          <t>다시 만나는 인페리아와 셀레스티아의 모험 ‘테일즈 오브 이터니아 리마스터’. 아울러 리마스터부터 신작까지 콘솔·PC 게임 5종 15일 대격돌.</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>디지털포스트</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015075900009</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBQbUlKekZEYWYxT1RUcmZmRE4ycUYwNlRESzdiOXJZVlRsVVZYVGRSQWVjT0dpWVlkRzB0UGhCSEM2NjZVZE1TdTlkaUhLMWpnMmFISjJMQkxqeEYtNmZ4Wnl3dXVqTWxtY3J3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9990,32 +9990,32 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>세계/국제</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>오픈AI "애플이 주장하는 탈취 영업기밀 사용 않겠다"</t>
+          <t>SIE, 30주년 맞은 '그란 투리스모' 한정판 컨트롤러 공개</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>)= 오픈AI가 애플에서 옮겨온 직원들로부터 탈취했다는 의심을 받는 영업기밀을 소송이 마무리될 때까지 제품 개발에.</t>
+          <t>SIE, 30주년 맞은 '그란 투리스모' 한정판 컨트롤러 공개.</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>게임뷰</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015074300009</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE8zVEg3cEl1QTNhanZybURWRTdfVFp0SUZDbVUxbjdwbmJvS2xPM042czRwalVXWXc1QU81LW13WWFHdDlfM1dCbkwzaklNbFgtZkdTQmVGRWdxemNQbXkwY25XM3JabnpmREE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10032,27 +10032,27 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>GTA 6 차기작?…록스타게임즈가 밝힌 변화</t>
+          <t>엑스박스, AI 게임 디컴파일 확산에 실험 조직 ‘엑스박스 랩스’ 신설</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>GTA 6 차기작?록스타게임즈가 밝힌 변화. 아울러 GTA6, 'NPC 대사를 위한 작가 팀'이 별도 존재한다.</t>
+          <t>엑스박스, AI 게임 디컴파일 확산에 실험 조직 ‘엑스박스 랩스’ 신설.</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>AI 매터스</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE45NUt4NGdWTW96S0k3MXAwVmxyclh2TDU0Z2dyVVFCOHE3QzNNendZT2dGcEpVUTdGUHBSSnAyTzBOY21VYXEyZURlV2daQTJJRWhhdVpPSTlDMi13bUJfTnJyZ3VQMENLeGF3ZmNnOVJNbjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE03VUVQVGI3eEhXc2pBYmhUcFprZUNtMm00Uld4NmJnamUtQno5cThDeGtiV0EtNkI4MW85MVk3dENOLWVZRVhNZndjck1XLU9FaGNwcg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10074,22 +10074,22 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>젤다의 전설 시간의 오카리나 리메이크는 생각보다 훨씬 많이 달라졌다 | IGN 프리뷰</t>
+          <t>마비노기 영웅전 시즌4 대단원 에피소드16 "운명의 권좌 열렸다"</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>젤다의 전설 시간의 오카리나 리메이크는 생각보다 훨씬 많이 달라졌다 | IGN 프리뷰.</t>
+          <t>마비노기 영웅전 시즌4 대단원 에피소드16 "운명의 권좌 열렸다".</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>IGN Korea</t>
+          <t>ER 이코노믹리뷰</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQY1JGbG0tcW1rVjY1ZW5TTUFaZ2doaHBaQzFHOG1FQlgzSVl6c3pvY3NTLVlSekNFd2F2ZF8tRXJhRHZiVFpWVUVKRU5FNVd6UUdZSzZ4MV8waWdEaXA5VnV4TFpjSVVHaXpOUElKUDRiUWpsLTVQNVVDVllpY3ZSUnB4dmNma3FqU2R3c1F4Mk45dHNBS0JNaF9MQTdhUzVLV1lCdzZaQ3RHYmpKVXViMnZfQlRyLXNZdFZzUXBYZzVmLTRLTF9aaVlnT2tWVWhVOHZRNUVIU3FmdUI4R1VOcEVDdVNET2NFY3I5Y2paaFhTbEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1lZUZlVEQzU0RGSkpiNW1yZEVmeklRVEVETUZIdUZGRERjdW9vbnQxQi1VYVdJS09RelBMTlNjbGxGQzhiQ29QOUtrRVBpdS1sd0g4NmZPM1h2UlR4cVR1SkFVX3lWbS1yZjVEQg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10106,27 +10106,27 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>콜 오브 듀티: 모던 워페어4, 로드맵 공개</t>
+          <t>아디다스 오리지널스와 에디슨 진, 클롯 슈퍼스타 컬렉션 공개</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>콜 오브 듀티: 모던 워페어4, 로드맵 공개.</t>
+          <t>아디다스 오리지널스와 에디슨 진, 클롯 슈퍼스타 컬렉션 공개.</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>인벤</t>
+          <t>Hypebeast.KR</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBIVXNOTVVYUUFuRjBmTjlqMVRnQl96Y0RmS0FzOXBtZmg5SFVMME5TSjVEeE1Ec0VTY0ZXSXp4Yy1NVl83NE1IcS1LeDJudzh6a3FYc3VFV2dKNl9rMFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNGlTaDBZWjZfWnV0QjBEdWhGb3Z3V3RlaFRlN3VlT2p2blhsdU13TjhQTTJjNThvVXh4ZWtWaktfR21aNWdjbWJITWc2el8tSjNOeHpXdGNLZktGYnhSZnRFWmhaUzFpY1o0Q01UM0gxVmRKRjFBWmJkajhMNWlzeG9HempxMVRheTQyMy1tLWRVaGxiOXRnc3VwMHdTNWpQQXh4d1hSNGxUZ1h2bHoxU0tCUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10148,22 +10148,22 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>“AI가 취향 분석해 게임 추천”… 구글플레이, 소셜·검색 기능 강화</t>
+          <t>DLSS 5 테스트 S.T.A.L.K.E.R. 2: Heart of Chornobyl그래픽, FPS 및 이미지 품질</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>“AI가 취향 분석해 게임 추천” 구글플레이, 소셜·검색 기능 강화. 아울러 구글, AI '바이브 코딩' 앱 비공개 실행 기능 도입"개발자 등록 필요 없어".</t>
+          <t>DLSS 5 테스트 S.T.A.L.K.E.R. 2: Heart of Chornobyl그래픽, FPS 및 이미지 품질.</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>IT조선</t>
+          <t>GameGPU</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE0wUzFuRGc4TGVWVkJ4SVlGN3FYaFh3R29JdnhyQWpNaDQ4S0RnNm9YOUo4RHlBazUwa2ZqUFF3a3pPYWpKcjA3cUFVY09CelBJdnctVEpoLUkteXZtajdydWU5NmJwZEpDaHpfRHVwUmvSAXRBVV95cUxNQWtXU1gwdWNfanpzUk15djQ3RE5kcVBMSm9YSHkyS3NwOFlxcDlHeDRIX2tqNlFZN0dWZ3E1OVdQWnByTjRsN3VtX3dIZ051QXdFQ3B4eks2aTRSM3FrXzFJd1R2UlEyWWpGcDZ2ZEJOemttdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNZWFlWl8yVmlybDkxNFc3TW1PUjVvSmlHNlVIdTFQSVk4R1F5QjlnU05CMWNQVVc2WG5fQkhwMGJOUkdQa0h6Z3dTMVd5TkFVRVAyUWdWcm5VSmNhYnY1ajBoNzJiN1Bwb2RuQlo3OW5oQ3N1UWUzanVFelgxQmE5VXprU3JnTXdrUHZpcnZmRXlMVUl6Y2p6V1ZJeENXYmVqMlM5TktNaWd0RVB6WXZfalpiTWJSd1p0cTJhWTA5SkpfMDhMRUZ6Q0Rnc1hUZGI0VnRONDZRSjI?oc=5</t>
         </is>
       </c>
     </row>
@@ -10185,22 +10185,22 @@
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>'몬길 : 스타 다이브' 캐릭터 이렇게 바뀐다</t>
+          <t>'디아블로2' 팬게임 'D2서바이버' 인터넷 강타 … '뱀서'와 '디아블로2' 조합 성공적</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>'몬길 : 스타 다이브' 캐릭터 이렇게 바뀐다. 아울러 "언제든 가볍게, 매력있는 캐릭터와 함께" 환골탈태한 '몬길'의 반주년.</t>
+          <t>'디아블로2' 팬게임 'D2서바이버' 인터넷 강타  '뱀서'와 '디아블로2' 조합 성공적.</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>더게임스</t>
+          <t>경향게임스</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9KSDJ0bVBVck04dWlqQVZFemhpUHlJN1lwMXQxTGkxN21UN1RBV2hpMExOYlFqbnE1S09YV1dUR0lPalAyZXVjZndKbmx1cTUzR2thVDg5cWc4R3FaSnZtZmNPdWJINkNGWkI0MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBWUnFGbkk0b1dxSDZ3MVB0QUV4dnFuZ3Npd09USzA5NEEzX0JjbzJ0a2xQWnVRTVd0SzJyWkt5UDBzLUROOTY5RjBMRzhKbFAtelBGcE9zYkw1cy16TF9LMDhIRENfMVRNSE40bw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10222,22 +10222,22 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>코나미디지털엔터테인먼트, ‘캐슬바니아: 벨몬트의 저주’ 출시</t>
+          <t>건담 블리츠 오더 첫 공개, 테스트 참가자 모집</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>코나미디지털엔터테인먼트, ‘캐슬바니아: 벨몬트의 저주’ 출시.</t>
+          <t>건담 블리츠 오더 첫 공개, 테스트 참가자 모집.</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>아이러브PC방</t>
+          <t>인벤</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFA3WTJMVThOazc1RDl6WmVCb3RJX1lvMXpTaWlrZnVzalhmTnp6XzZObXU0aHFsZjlBZlZfZThUY3RjX3BDbDVMZ1VUcVoySF83RXk0Wm5WSWZBbXZzOVdVY3ZIcEh5WTJHSnlvbDQ2MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1hdFhLWnJXbVJ4UHJaaDZUYlpXTHZxa1pCZllfSGVkekxDTVlpUHEtZ1ZxcUk5NHdyaWhCZUFnZmNZWmNfQ3Q2cTZERVpsckpRWWd4UE5nS3A2dFV1X3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -10254,27 +10254,27 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>콕스, 컴팩트한 디자인의 RGB 미러 라이팅 스피커 ‘CST30’ 출시</t>
+          <t>드로리안, 에어스피더 전기 플라잉 카 레이싱 시리즈에 참가하는 최초의 미국 팀이 되다</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>콕스, 컴팩트한 디자인의 RGB 미러 라이팅 스피커 ‘CST30’ 출시.</t>
+          <t>드로리안, 에어스피더 전기 플라잉 카 레이싱 시리즈에 참가하는 최초의 미국 팀이 되다.</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>아이러브PC방</t>
+          <t>Hypebeast.KR</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE45MXVwei1LODAyTnd4bzZza2F2dURqRXZvTWlyVXU5MEo0cERNR1IwUFI5NzVCRW1RanNvbmVjZDlHQTliOWpDSTI3YXZSdE4zUGFTU1RpZkptazNMNl9CVkt4VUctdmNGZjFfNmlLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNMUVlU3NSNTFzU0JITFVYaFdrVU5tOVZ5Tng5cDYteTFPSE1BMnVFVXlucjY5WlNYT3RFSzhsR2Q3bDZaSjdkeUpINUdKUllTc1RudlpYUkRhdUJZbkNURWw5RXEzRXJIQTZlSExEZ0lNbm5TX0xack8yRGs3UUROOHExUE54NVpxS0RhQ0pB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10291,27 +10291,27 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>USB Type-A·C 연결 지원 게이밍 마우스... '콕스 CM1100'</t>
+          <t>최휘영 "문화가 AI 기술 주도해야…기업·창작자·연구자 협력"</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>USB Type-A·C 연결 지원 게이밍 마우스 '콕스 CM1100'.</t>
+          <t>)= 최휘영 문화체육관광부 장관은 15일 "문화가 인공지능 기술개발을 주도해야 한다"고 강조했다.</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>디지털포스트</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE41R0FmNXRNMVpaMkRGTWVFaGt1c01iSDJFY1pidWJJN18xN0hDbnVPRzNIc1Yyd1h0TU1MLVJ1UkF2N3pVRENiTkdaZEpZa2tSX3J6bmpLdGdSQ0VmN2ZGNkpLQVFDRno2WW0w?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015120100005</t>
         </is>
       </c>
     </row>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>애플, 12인치 맥북 전 모델 공식 수리 끝냈다…2017년형도 '단종 서비스' 전환</t>
+          <t>"세계인이 즐기는 K푸드 축제로"…순창장류축제 개막</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>애플, 12인치 맥북 전 모델 공식 수리 끝냈다2017년형도 '단종 서비스' 전환.</t>
+          <t>)= 전북 순창군의 대표 축제인 제21회 순창장류축제가 15일 순창읍 전통고추장민속마을과 순창발효테마파크 일원에서.</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9yajl2YkRibFRIVExQX0NxU3NtQ3lVMnU0UXRuT1FEYXJwVnZDajRES2Z0bzNKMWgzUk80VTdCUlZLNW5heGFEME9oWVZwVGVXeUhvOHI0Z3lUeUpYaFB3bzdXeUM2RDZmQWhpWThxeFRsOE0?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015130300055</t>
         </is>
       </c>
     </row>
@@ -10365,27 +10365,27 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>‘온라인삼국지2’, 천금서버에 장비 성장 지역 ‘천금촌’ 추가</t>
+          <t>이마트, 758억원 규모 자사주 소각 결정…"주주가치 제고"</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>‘온라인삼국지2’, 천금서버에 장비 성장 지역 ‘천금촌’ 추가. 아울러 2026년 9월 4주차 주간게임동향.</t>
+          <t>)= 이마트는 758억5천만원 규모의 자사주를 소각한다고 15일 공시했다.</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>경향게임스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBjUVBTU3lkS1IyQWpvZFJZS244UE1XTUtOVHc4MXdqQ3F1a3JUWm9GajJUZ0VoWjBaSEhaa3dTbVBzcFdkNXd5RVBGakw5S2pSV1hkTThmWC1aVW9xY09LdG9na1p6NFQwdy0yZg?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015138800030</t>
         </is>
       </c>
     </row>
@@ -10402,27 +10402,27 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>커세어, 첫 프리미엄 USB 마이크 ‘복사라’ 출시… 엘가토 기술 결합</t>
+          <t>어기구 "수자원공사 해외사업 손실 눈덩이…목표액 5.7%만 회수"</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>커세어, 첫 프리미엄 USB 마이크 ‘복사라’ 출시 엘가토 기술 결합.</t>
+          <t>)= 한국수자원공사가 해외사업에 수천억 원 투자하고도 당초 계획의 5.7%만 회수했다는 지적이 나왔다.</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>뉴스탭</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE40cGhsYmpXdGppa2k5RjRwLUNzcnRKaUU4c2xucE5JNFZHWXc0Z3NxbFpjeFJIUXNoUmNKQkdTcUtJWndxZ09PVFV4X2xDVlZoOEpCT1YxQU54X1B4X1JKRjRvaVptdjZWb2hXNA?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015138200063</t>
         </is>
       </c>
     </row>
@@ -10444,22 +10444,22 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>(단독)해외투자 전문 KIND, 6000억 쏟았는데…회수액은 800억</t>
+          <t>우주태양광 필름 쥔 이소영 장관…"중소기업, 성장엔진으로 육성"(종합2보)</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>해외투자 전문 KIND, 6000억 쏟았는데회수액은 800억.</t>
+          <t>)= "반도체에 이어 태양광 소재를 연구개발하고 있는데 인상적입니다.".</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>뉴스토마토</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9qV04xdEw0RDZVcXE2bF9hSDBJQ3FJMXpMZTdHb1ExM3lKZnVqUU8zUEs5SFZLbTgta0ZjOTlhbnM3Mmc2Um94T3lZVUh5czhHb0RIUEo0N3pzLWF6Qk1JMQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261014190352030</t>
         </is>
       </c>
     </row>
@@ -10476,27 +10476,27 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>게임 간 경계 허무는 AI...이용자 관심도 높아</t>
+          <t>한국전기공사협회, 한국전력과 상생협력 업무협약</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>게임 간 경계 허무는 AI이용자 관심도 높아. 아울러 복원·패치·이식까지, AI 이용한 '게임 역분석' 주목.</t>
+          <t>)= 한국전기공사협회는 한전 아트센터에서 한국전력과 상생협력 업무협약을 체결했다고 15일 밝혔다.</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>이코리아</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBLYnNHbzBzMzNnd0ZCYU4zbHVMTnlCLVRZbVRMNVNhRE1kTjZCWWRqNE1ZR3ZLb3B1ck5teE1wd0JfUFhVRHQyQXpRanRGd0ttVUJZa2p6b0h0azlkTTN6T0xHTUxMSm1pY3hLWldscw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015134900064</t>
         </is>
       </c>
     </row>
@@ -10513,27 +10513,27 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>우치코시 코타로, CRASH KEYS 공식 공개</t>
+          <t>양평 농가 한우, 올해 경기지역 최고급육 선정</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>우치코시 코타로, CRASH KEYS 공식 공개.</t>
+          <t>)= 올해 경기지역 최고급육으로 양평 농가 한우가 선정됐다.</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>인벤</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5URGtRcEx2YUZ1WHFhekRTN2JXVS1RVzZ5QUljRGZqakJBcnFPZmRuNUY5Yk1GYi03M2xsTTNBMUtoV01IUHdqQmZtb21SX0lrMHl4Ujd3czhGazBzM0E?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015136800060</t>
         </is>
       </c>
     </row>
@@ -10550,27 +10550,27 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>브릭 바이 브릭, 15일 스팀 출시 예정</t>
+          <t>충남 산하기관 평가서 신용보증재단 최고등급…일부 기관 하락</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>브릭 바이 브릭, 15일 스팀 출시 예정.</t>
+          <t>)= 충남도 산하 공공기관 경영평가에서 충남신용보증재단이 2년 연속 최고 등급을 받았지만, 한국 유교문화 진흥원은년.</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>인벤</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9hZVdmSXZYTUljR1hoX2huRE9RWmxDbzNPb3NIUWJEVHJBQnJoZjZzMHhONzhHOXE3YWs2RVRDOW5ET0s3TUxoOHFhXzhidERPOVByeUtsd0VHQzhINmc?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015134800063</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -10592,22 +10592,22 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>‘Max’ 붙이더니 전력도 냉각도 키웠다…MSI 사이보그 15 Max C2WF-C7</t>
+          <t>장영란, 中 진출 안 한 것 후회 “인기 엄청 나, 채연처럼 나갈걸"···김영철 증인(‘A급 장영란’)</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>‘Max’ 붙이더니 전력도 냉각도 키웠다MSI 사이보그 15 Max C2WF-C7.</t>
+          <t>장영란, 中 진출 안 한 것 후회 “인기 엄청 나, 채연처럼 나갈걸"···김영철 증인.</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>뉴스탭</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE94LWcwd1RJb2FuNGJ4azA4SUtXTmR2V1lMODA1UncySDZiS00zQU5ZUURBVUZCX0lXcnA4azJ3SGwwOGd6c3p1bXFnaUFROXd0aTFnaEc1b2xqTlZ0VDVDakwwaWg1UXRNa2pWZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPM3NPcXpzaUVteWRodXpQVEpoVkRaZG12VEsycHRrWHhaTEYzV19wWUJISDg1bkhuSGFHaVQ0WmZyZTlpVmpWWkRsLXVHYVNfMlJ5S0ZfRWlkd0RJZzNnYXRiMEhrRl90OUNKZ0FmVVRBdmtCQ1JaWWFRYzhZcW5sTllLa1paM092c3VWRHR5bw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10619,32 +10619,32 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>제주공항 국제선 여객 작년 연간 실적 넘는 303만명…역대 최대</t>
+          <t>하희라 “♥최수종, 술 마시고 나 때린다는 소문까지”…33년 잉꼬부부의 해명 (유퀴즈)</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>)= 올해 제주공항 국제선 이용객이 303만명을 넘어서며 역대 최대 실적을 경신했다.</t>
+          <t>하희라 “♥최수종, 술 마시고 나 때린다는 소문까지”33년 잉꼬부부의 해명.</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>스포츠경향</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015098400056</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1IakJHX1U3bnNKaGtyYl81eDN5Yl9uUTJZb2s2cjcwVmpuem9jRnRqZG1jZFo4dkhXM0hwSm5SWXpZQm53UVpyWFViaExhaF91VmU0MmNhencwQ1pBdUHSAWNBVV95cUxNM3ZXSEpYcU1ZUFlaN1VmMU9RUWlITk5wVVhuWDJfMl90dlBEZGtsZEdwWjJhTTlaN0czbkVSVHJZZ0pNeC1aVEdPMk5SWWJkcTd2YnBwdk96VDlXeVFLYlVfUlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10656,32 +10656,32 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>포스코 개발 고망간강, LNG선 화물창 실증…한화오션과 맞손</t>
+          <t>이수만 신인 걸그룹 아이찡 부모에 임금체불 의혹…모친 사과</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>)= 포스코가 독자 기술로 개발한 '고망간강'을 액화천연가스 연료탱크에 이어 대형 LNG 운반선의 핵심.</t>
+          <t>이수만 신인 걸그룹 아이찡 부모에 임금체불 의혹모친 사과. 아울러 이수만이 다시 꺼낸 K팝 DNAA20라이트, 데뷔 직후 '멜론 1위'.</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>경기일보</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015071100003</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE4yWUlSaTFLeWVvMUI0Q1o2bFJzVGRZWldocjVVQmxDdmM0RW5ITlVJYzBCTnNQdVV2WGdTQWtKellRZWo1NDBxdUx6UUhSSF91dDdJUmFTZjY3dTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -10703,22 +10703,22 @@
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>[르포] 로봇 손 6대에서 204대로…현대차 푸네 공장 가보니</t>
+          <t>‘개과천선’ 서인영 “일본인과 3년 연애…번역기 썼다”</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>)= "기존 제너럴모터스 공장일 때는 이곳에 로봇이 6대에 불과했습니다.</t>
+          <t>‘개과천선’ 서인영 “일본인과 3년 연애번역기 썼다”.</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015005400003</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE92cXFLcERXbmkxeG1xNWYyN05QTGNwWURDcld6NHd0dTRORVpGU0xxalAtbzFUc1B1bFhzck9lUjJQUU9YZUVkaTRxR19VVnp5RkFxSHNwZ2lnZDN0YndmczJpMlEtMzVmMDNrZktRNnRZSFEyNTFjN0F3LVdaZ9IBZkFVX3lxTE44M3RXZzBOYVlDT2h0aEpCR1RBQnBHVHY0eF9PWno2Qk44NGNzUXRsbnNxcjhDNHpkNGhHN1JDVXUzTjhKUFlDc0lDbnhnT3FHbDBBYlFwbE5NTDlndHNFSkdTUk9xUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10730,32 +10730,32 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>"서해·동해 이용료 수십배 차이"…대한상의, 지역규제 개선건의</t>
+          <t>부산국제영화제, 관객 20만 명 넘어...2015년 이후 처음</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>)= "같은 바다인데 서해인지 동해인지에 따라 이용료 차이가 수십 배 나는 것은 불합리합니다".</t>
+          <t>부산국제영화제, 관객 20만 명 넘어2015년 이후 처음.</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015031400003</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE42MXpmdWtqdzZnVV9YSjZfZTNQZWpFVWlSODRfRTJMWms2dm1OZGhBa0FHTUlSUjYwR19qRzF6MFlvQWFlTExHanBKcjUxcU1oQVFHZ1BKeV92MnVQQlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10767,32 +10767,32 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>AI 챗봇 청소년 유해성 점검…성적 묘사·범죄 조장 등 확인</t>
+          <t>김세의 "독방이 정신건강 해쳐"…검사 "보석을 무죄로 왜곡할것"</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>)= 일부 인공지능 캐릭터 챗봇이 청소년에게 유해한 응답을 하는 것으로 나타났다.</t>
+          <t>김세의 "독방이 정신건강 해쳐"검사 "보석을 무죄로 왜곡할것". 아울러 "김새론 안고 자고 싶다" 카톡 보낸 인물은 연예인 A 씨조작 진술 확보.</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015045600530</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBuSHp6cm1lR1hIUmRLZGxhU1hhaHIxSVRnb2h5dnBRdmhxUjEtb0ctWDJDVXQxXzhIUHhSSW9kMGFCdkNDZng2Wk5lN0ZRMDg1ZlRKRXNSWnRZYk3SAWBBVV95cUxOdkdSOVlKN1VqNHBtMi1hVjF6SU41SVY0WTNQTVczQ0FIR1hsWG80RzVYVUJVRndPNm90QjZha0lkYkQyR2pVY3RuVjJMWnlvZ19McWVwVmZIcWhxdTFKaTk?oc=5</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -10814,22 +10814,22 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>KIST, 건물 외벽따라 자유롭게 형태 바꾸는 3차원 태양광 개발</t>
+          <t>‘편스토랑’ 이정현, 남편 위한 몰래 카메라</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>)= 건물 외벽 모양에 따라 자유롭게 형태를 바꾸는 3차원 태양광 시스템이 개발됐다.</t>
+          <t>‘편스토랑’ 이정현, 남편 위한 몰래 카메라.</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>BNT뉴스</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015083800017</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9FUVV5YTlmaEY4ZjNyWjVQRXc5VWVMZTg4UmRaSWJQTjBGRTdJc0JzX29GaWFNQnpBMm5sLUltVEhzYW5HRFdHWElrSld2cGVXcEJOdWdZdWpFcmpzMHh4QlctbHU?oc=5</t>
         </is>
       </c>
     </row>
@@ -10841,32 +10841,32 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>오픈AI, 아태·일본 세일즈 총괄에 안드레아스 하틀 선임</t>
+          <t>“민희진, 전 어도어 직원 명예훼손 사건 불송치·불기소 처분 받아”</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>)= 오픈AI가 아시아태평양·일본 지역의 초대 세일즈 부사장으로 안드레아스 하틀을 선임했다고 15일 밝혔다.</t>
+          <t>“민희진, 전 어도어 직원 명예훼손 사건 불송치·불기소 처분 받아”.</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015086000017</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5XZ2owc2NfT3hDeUk3Unpia0pxRWxfT3EyZnYtSHRISU5FRU9kMXdkSXFIa3N6SHFhVWppV1lxT0Y2R28ycFRuMi05Q3NCLXM0RDhyTUtvQ1UyS3VNUmRHcnFBaUJXQUtQcGhIaDAwN2MzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -10888,22 +10888,22 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>잠자는 '충전형 선불금' 255억 주인 찾는다…환급·통지 강화</t>
+          <t>김유신 된 박성웅의 든든한 리더십…신라의 운명 짊어졌다(‘문무’)</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>)= 앞으로 잠들어 있는 페이·머니형 선불금을 정기적으로 안내받고, 더 쉽게 돌려받을 수 있게 된다.</t>
+          <t>김유신 된 박성웅의 든든한 리더십신라의 운명 짊어졌다. 아울러 KBS 대하드라마 ‘문무’다음 달 14일 첫 방송.</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015085800002</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOenh6OFFhTWFJWHpKUjFDbThveGJHMkR0UXpRWWpWWDV0NHdoYnVPMzdxRndZU01PR3ZDUVY3dzhJN3Mwemo4Y3l2bUxTYTBkUzh4WDBHVVh3YTNuTzNkUTZpVDljMkJFMjVKT3ZWVWFCaFI3VGt6MG0tNDhuei11VEVRQ1JIWVo3Yjlham5OYw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -10925,22 +10925,22 @@
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>HD현대 정기선 취임 1년…사업통합 시너지·마스가 공략</t>
+          <t>[남다은 평론가의 RECORDER] 카메라, 이룰 수 없는 눈,</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>)= 정기선 HD현대 회장이 오는 17일 취임 1주년을 맞는다.</t>
+          <t>카메라, 이룰 수 없는 눈,. 아울러 어쩌면 사랑까진 필요 없을지도.</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>씨네21</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015084600003</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9VUmJmYUJKcGlKMEpaWURJRVlqM2JKS2ZJQVdtbHhORnQ1bHRuNm9Fd3l2LThlUzJTQkZSaVk4Wm9NeVNyOFQ3dTVqUVg4aDFJVGhUV1VB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10952,32 +10952,32 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>bhc "'콰삭모짜킹', 출시 3주 만에 20만개 판매"</t>
+          <t>이지혜, ’성심당 빵 싹쓸이 의혹’ 반박…“스태프들 결제만 도왔다“</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>)= 다이닝브랜즈그룹의 치킨 브랜드 bhc는 신제품 '콰삭모짜킹'이 출시 3주 만에 누적 판매량 20만개를 돌파했다.</t>
+          <t>이지혜, ’성심당 빵 싹쓸이 의혹’ 반박“스태프들 결제만 도왔다“.</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015087200030</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBKRVloSXNsbU40S1lXNVhrQm5ZbmhucUtKRW9nT2swQTlBUXl5YWNuRVVoLUlPQ1FlN3RLZVV1V1ZKTW82WG40S1h2Z2FtWG1SM3dLYWlEUng3NUtFTEp2RUFSZ3NLY2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>IT/과학/신상품</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -10999,22 +10999,22 @@
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>가을까지 이어진 가뭄…대구, 8년만에 금호강 물 끌어온다</t>
+          <t>기안84, 영어 공부할 걸..톰 크루즈와 만남에 "울컥하는 기분" [순간포착]</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>)= 가을까지 이어진 극심한 가뭄으로 청도 운문댐이 바닥을 드러내면서. 달 초부터 대구 일부 지역에는 8년 만에.</t>
+          <t>기안84, 영어 공부할 걸톰 크루즈와 만남에 "울컥하는 기분".</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015074700053</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOLXh6TXRnTmMzcWd4c3RmU3dScWtwYjBUVS11WG1ZeTFaR29GLVIyclVYY2NGMkt1Ump2SUlleUNRdldTUER2QUJWeDNuTHAzNFFybGk3QTdsOF9IUU5qakQzLVdwbkJ3OGRhZTNMaS1LZVVrdHBYY0tSR2tIaGJsSDlfTjFOMEZYell0NVBsZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -11031,27 +11031,27 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>’하정우·차정원’ 이어 ’솔비·이규한’도…깜짝 결혼 발표</t>
+          <t>'닥터X' 글로벌 1위·'나를 충전해줘' 3위…K-드라마의 위엄</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>’하정우·차정원’ 이어 ’솔비·이규한’도깜짝 결혼 발표.</t>
+          <t>'닥터X' 글로벌 1위·'나를 충전해줘' 3위K-드라마의 위엄. 아울러 천재 의사 활약 그린 '닥터X', 넷플릭스 비영어쇼 1위 직행.</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1EV1dQTlB2ZWdfTGJlc25OcU9ZeTBCT0VfRHFFNXREaGE2S0tsNlJMc0pEbVp3RXpGY2lvY0Jvc2RKcnNBcXQ2YzBTc3VVTkNYcVVIMnR1X19pVTdfU0sxUUpScDk0T0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5GZkhpSnBocWR3QlpKOThvVlN3cVJscVZxTjRzVTdyczJMU1JxS01UTTJzTllnTmYwMVhMWjFHS2Jydk5LaE04X2ZvbUFDMTQ2aHRzRnRxYTdGZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -11068,27 +11068,27 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>‘가능한 사랑’, 메인 포스터 공개…전도연·설경구·조인성·조여정의 감춰진 감정</t>
+          <t>‘암살자(들)’ 허진호 감독 등 제작진, 국감 증인채택 또 불발</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>‘가능한 사랑’, 메인 포스터 공개전도연·설경구·조인성·조여정의 감춰진 감정. 아울러 어쩌면 사랑까진 필요 없을지도.</t>
+          <t>‘암살자’ 허진호 감독 등 제작진, 국감 증인채택 또 불발.</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>스포츠동아</t>
+          <t>채널A</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE42ZVY2RXM1Vm5VZ19Udzg5dDN0d3VzZHFhX0ktdVJvUGVqZURWZWQ1M1pfeVNyeWQ0akY0dS1oTUZxSjVDU0RjTEozMG5VMG1mRVBMaDF4eEVpamdhQmVXZmNGd21temdPRkFoZXZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5hMDhvSVduY2otNlhjRlZzRDhZLXdsN0t2RDBIS2haMDg0OFdjQndRVG9KbE5hSU9Qb2FfblQ5ZDFhWE9sQlg0OFpCZE5Mc1VLclRPV1U3cEdMV2l3aUHSAWNBVV95cUxOLUtuNzlPYV9TNWxmVmRnX1Zkb1BXRXkwMVpxV2QwZG5mc2I4Z1J6Snk2S0lHQ1RVLW5ITUF6eGFJSVlSenFuUUJTeDE0Q1pENXBuMXAxRnAzTDFST3ZNdDFoSEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -11110,22 +11110,22 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>최수종, '♥하희라' 똑 닮은 딸에 "말없이 가방 들어주는 남자 만나라"('유퀴즈')</t>
+          <t>고대 신화에서 길어 올린 사랑과 상실…노벨문학상 앤 카슨의 세계</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>최수종, '♥하희라' 똑 닮은 딸에 "말없이 가방 들어주는 남자 만나라". 아울러 "최수종이 때리고 이벤트?"하희라, 루머에 입 열었다 - 머니투데이.</t>
+          <t>고대 신화에서 길어 올린 사랑과 상실노벨문학상 앤 카슨의 세계.</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>경기일보</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPRnpYX2JWU09IcGZBY0piWVdDc3hEZ2FDRDU5bEgyd0lfUy1LeTlwaEdCV3lUb09PTTdQazhjV25fajRSMU5ZU3BIWTduTWJ3MGZ3RUkxZVhIeE1sN244aWpOUGVnMWMzb3V6cVBPeVpaNUZQT0xZLXJsajExb25uQjVEQkwwTFctNXVKVTd4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA0bVdYRFRucllKMHU3RUNvUHI3UUV2RlRvTE1YTXFYblExQ0Y0T1RrNlpRWF85ekM4ZTJuYjVyRjltY3hxeE9wN3dZX0stX0F2MjlPaDV3bkZTRjA?oc=5</t>
         </is>
       </c>
     </row>
@@ -11147,22 +11147,22 @@
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>서인영, 본토 갸루 완벽 소화에 일본인도 ‘동공 지진’</t>
+          <t>울주시네마, '문화가 있는 날' 운영…영화관람 2천원 할인</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>서인영, 본토 갸루 완벽 소화에 일본인도 ‘동공 지진’.</t>
+          <t>)= 울산 울주군시설관리공단은 영화관 울주시네마가 지역 주민들의 문화 향유 기회를 확대하고 영화 관람 접근성을 높이.</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>스포츠경향</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5WWXRhZ19LcFpETGZWOGtZLTVJQkEwTDIwbkJhaVFkQzMzYWc1eXQ5U2p6ZEdneWd5Vk9OSmFBMXlvMTBRV3ItRE5MX2NYU29nYUhEdDIxSVhqQU5ScXfSAWNBVV95cUxNSi1ZeWVhbWRPQ1dVZVZGakZaLXRJMndmN1NqNmVSN3JKWmtXRWdQeVpWMHVhY2NNc3RaLWN2M2tQcUZPNmFfMVk5U003NmV3Z09ycWtpbHBjMUh5cHF4eVdQbTA?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015121600057</t>
         </is>
       </c>
     </row>
@@ -11179,27 +11179,27 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>'병원장 사모님' 이정현, 3주년에 지갑 크게 열었다.."랍스터 100마리" 복지 클래스 ('편스토랑')</t>
+          <t>김영광·채수빈 "웃음 넘친 로코 케미, 10점 만점에 100점"</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>'병원장 사모님' 이정현, 3주년에 지갑 크게 열었다"랍스터 100마리" 복지 클래스.</t>
+          <t>)= 배우 김영광 과 채수빈 에게 넷플릭스 시리즈 '나를 충전해줘'는 배우로서의 에너지를 충전해 준 고마.</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQc0JQQTFMRS1nT0hjb3lsTG9Ha3UweXB5dndBYzNnSFNiMjRlSW81dHFENWVmaXJfUzZ6cXBkT2FraGtfamxwOHFzUFdEQ2ZfTy1YZFpNUmdSanYtcDRvaVVGalJBZ2dWS2NOWjI0Z3JFN1p2ei1vQXJmSUhTeDFXM2NwOEVUTEZYa1lEWFFORQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015095600005</t>
         </is>
       </c>
     </row>
@@ -11221,22 +11221,22 @@
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>임진모, 뇌종양 투병 끝 먼저 간 아들 향한 그리움…아들 양말 신고 ‘유퀴즈’ 출연</t>
+          <t>'2026 PBI 서울총회' 개막…"위기 속 공영방송, 사명 변함없어"</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>임진모, 뇌종양 투병 끝 먼저 간 아들 향한 그리움아들 양말 신고 ‘유퀴즈’ 출연.</t>
+          <t>)= KBS가 주최하는 '2026 세계공영방송 서울총회'가 15일 서울 여의도 페어몬트 앰배서더 호텔에서.</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>스포츠경향</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1TTnJ0cXJybnFkTlVBTkVsbkFleFBSYjFmYUloLWhtWmdoa1BvOHVfXy1qVEdqYzFfVTNfSGh4VERJYXZaWmpSYjNlWDl5SlJ5OUw1SG1Ldlc5T19RbmfSAWNBVV95cUxQLTNrcHViUFZZUzRnN2RkdnNFdjZyT2JROHdFZzRrX2ZmVGdZRktOaEZKV2VmMVNpcGVEWnZhcmdzenY0UmxQcmxpbGJkZVNqWEZhU0RuZXA2REkxMXJMWkRLd1E?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015118300005</t>
         </is>
       </c>
     </row>
@@ -11253,27 +11253,27 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>조윤희, 이동건과 이혼 심경…“나도 이렇게 용감한 줄 몰랐다”</t>
+          <t>아도이, 오늘 3년 만의 신보 '굿'…정규 3집 선공개</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>조윤희, 이동건과 이혼 심경“나도 이렇게 용감한 줄 몰랐다”.</t>
+          <t>)= 밴드 아도이가 15일 오후 6시 새 싱글 '굿' 을 발매한다고 소속사 엔젤하우스가 밝혔다.</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE03TDA2RGkwS095ZUtUUGt5OENNS0wxMUlodmY5eWlDQXc0bW9DNEtubE5pcC1jWFVBMFRLem1lUXVDWldnX05JUUc0S2pwd3VGTnctNFN5cVg?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015113100005</t>
         </is>
       </c>
     </row>
@@ -11295,22 +11295,22 @@
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>서정희, 故서세원과 이혼 원치 않았다.."30kg대 난민 상태 돼"</t>
+          <t>[동포의 창] "진정한 집 어디에"…스위스서 한인 2세 신해섭 감독 영화 상영</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>서정희, 故서세원과 이혼 원치 않았다"30kg대 난민 상태 돼".</t>
+          <t>)= 스위스의 한 영화관에서 한인 2세 신해섭 감독의 작품이 소개돼 동포사회와 현지 시민, 외교관 등으로부터.</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNLXN1dXpHM0JCSHdnNVZteWdWVGdmRjRFU2o2Z0lkalEtbXhWcTA0SjdZS19UTFdFR2VQSmlOalhvU1hKci1zUHVZSzhEU0NKNzdNUktzbk15V0R6VXQ5TjJSZTVodld5aktBczZiRWkwcktRU29vUDJNTVV2dDJFN21ualc1am40bWp0ZFhzcw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015111900371</t>
         </is>
       </c>
     </row>
@@ -11327,27 +11327,27 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>"빵값만 결제했는데"…이지혜, '성심당 싹쓸이' 주장 반박</t>
+          <t>2인조 형제 록밴드 레드씨, 신곡 '아이 워너 싱' 발표</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>"빵값만 결제했는데"이지혜, '성심당 싹쓸이' 주장 반박.</t>
+          <t>)= 2인조 형제 록 밴드 레드씨 가 신곡 '아이 워너 싱' 을 발표했다고 소속사.</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5hYkxWS1g5bm5aN1IxS0FRZGJPWk5HWmZRQnB2ZVBiUlFoQ0hMOEVYSllyOW5QbHF3eGhpekdiYXhDMmtvN1pmRnBTU3ZveEZyc0NROWR5Nm9zQQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015113000005</t>
         </is>
       </c>
     </row>
@@ -11364,804 +11364,27 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>BIFF 11년 만에 관객 20만 넘었다…폐막식 때 경쟁부문 수상작 발표</t>
+          <t>[영상] 이수만과 A2O LITE가 소환한 케이팝 순정</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>BIFF 11년 만에 관객 20만 넘었다폐막식 때 경쟁부문 수상작 발표. 아울러 제31회 부국제 결산 기자회견하는 정한석 집행위원장.</t>
+          <t>) 송영인 PD = 이수만 A2O엔터테인먼트 키 프로듀서의 신인 걸그룹 A2O 라이트 가 2021년 멜론차트 개편.</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>국제신문</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORFdsajRJQkZCdURlUjE3azQwNDhKWjBUdXAyM2RTYVZqb09lVWpxZTVwLVlBeHBJcmdxMG02VVdvdVpiMkc0bzF4dHhoTXd3X3g0OXdVRFphbVpKZWsyYmY5LVFJQjhZMTM3ZF9aU2ItZmw2Nll1T0FPM1F1TmttNEx3c0FLdk5IMFZF?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B296" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D296" s="3" t="inlineStr">
-        <is>
-          <t>악뮤 이찬혁·이수현 합숙소 공개..운동방·노래방에 초특급 올드카 보유(전참시) - 조선비즈</t>
-        </is>
-      </c>
-      <c r="E296" s="3" t="inlineStr">
-        <is>
-          <t>악뮤 이찬혁·이수현 합숙소 공개운동방·노래방에 초특급 올드카 보유 - 조선비즈. 아울러 악뮤, 콘서트 시야제한석에 시각장애인 초대관객 후기 화제.</t>
-        </is>
-      </c>
-      <c r="F296" s="3" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="G296" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPVmhuVWFjbkJrbTFwQlN1YWlacUVuamFpQmh1SEhIQk9uZ1NKSnpQWjF6Z2JWbFNJdG9aWVhBSU9pVVItcUhEOUp3bk5FSTNYUUZQQWFNMDhabFJ1dXZVWVNhZzY3SGRCTlVubzMwUmtIZzNhazdGNkFPNzU3bkNRMmdEX1NHbXA0VndldTg5UjZpR0nSAacBQVVfeXFMUGNxb0ZKRWpNU01SX3ZpbDVxLW9CZERZZUp4V0dtckRHRUxKTmx6eS1tRFpwWkRXeEx6UmpNRG9SWkEzckxMOXBoTjdweEo3SWtlOE1LZHNzX3daR2JRM3d0XzlfQTFyQk9YYkxiLUM3RWgwRG9OUVJCUUtibGljSzdvakZsaVRpejZzTkNWYUc1MVB2RTVIay0weEFoX3RGbFNVOElvajQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B297" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C297" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D297" s="3" t="inlineStr">
-        <is>
-          <t>방미통위원장 “공영방송 본질 중요 시점…공론장 형성해야”</t>
-        </is>
-      </c>
-      <c r="E297" s="3" t="inlineStr">
-        <is>
-          <t>방미통위원장 “공영방송 본질 중요 시점공론장 형성해야”.</t>
-        </is>
-      </c>
-      <c r="F297" s="3" t="inlineStr">
-        <is>
-          <t>KBS 뉴스</t>
-        </is>
-      </c>
-      <c r="G297" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1rTHd6QXF6SngyaU5TNHY5bVpDZm9VUHp3blRxZ1A4SWFMTWJGMXE2eWU5R2liSnk5RDJoWTNtTUVlakpVa1hPbmdRNnlTbk9SRk5LMXkyVFBqazg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B298" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D298" s="3" t="inlineStr">
-        <is>
-          <t>독립영화, 극장 밖에서 관객 만난다</t>
-        </is>
-      </c>
-      <c r="E298" s="3" t="inlineStr">
-        <is>
-          <t>독립영화, 극장 밖에서 관객 만난다.</t>
-        </is>
-      </c>
-      <c r="F298" s="3" t="inlineStr">
-        <is>
-          <t>지디넷코리아</t>
-        </is>
-      </c>
-      <c r="G298" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE91ODdOUXBZbTRTWmxZZWZPbDlGa2xwN0hiTnBQRXVuWk8xQzhfZlBVVzZMX3JjbmFwaHFpMENHQ3R2eVRsWWN2ck1VbXpoVmNNTXdwNUZn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D299" s="3" t="inlineStr">
-        <is>
-          <t>문체위, 이임생 등 국감 증인 채택...암살자(들) 증인은 불발</t>
-        </is>
-      </c>
-      <c r="E299" s="3" t="inlineStr">
-        <is>
-          <t>문체위, 이임생 등 국감 증인 채택암살자 증인은 불발. 아울러 ‘암살자’ 감독 증인 채택 불발에 항의.</t>
-        </is>
-      </c>
-      <c r="F299" s="3" t="inlineStr">
-        <is>
-          <t>YTN</t>
-        </is>
-      </c>
-      <c r="G299" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1oWmZPSGEzMHhMOFFwZHZtb3NZRFZKZGdzcTM5VV96U3hHWkw0ZkwwWlNtOTZnTy1zakNJUXlLcWpFcjNXcUU0X0FwRDhoMW1IaG5zMTdmTnRuQzViMEE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D300" s="3" t="inlineStr">
-        <is>
-          <t>‘김수현 명예훼손’ 김세의, 풀려날까…보석 청구 내일 심문</t>
-        </is>
-      </c>
-      <c r="E300" s="3" t="inlineStr">
-        <is>
-          <t>‘김수현 명예훼손’ 김세의, 풀려날까보석 청구 내일 심문.</t>
-        </is>
-      </c>
-      <c r="F300" s="3" t="inlineStr">
-        <is>
-          <t>문화일보</t>
-        </is>
-      </c>
-      <c r="G300" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBHaTdhTDBmY1hfYW43WDRsWDJld2FKd1FTbjg3Y0RhWVFUd3l5Q2tnbHNXMVJWX09kdTB2ZzBWdjF2Q2Z3QUs5dVRZRlliV1It?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D301" s="3" t="inlineStr">
-        <is>
-          <t>장항준 "'거~장항준' 제안했는데…제목 보고 놀리는 줄"</t>
-        </is>
-      </c>
-      <c r="E301" s="3" t="inlineStr">
-        <is>
-          <t>)= " 제 이름이 들어가서 책임감을 딱히 느끼진 않았어요. 혼자 하면 부담스러울 것 같은데 송은이,.</t>
-        </is>
-      </c>
-      <c r="F301" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G301" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015094100005</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D302" s="3" t="inlineStr">
-        <is>
-          <t>KF, '퓨전엠씨'와 비보잉으로 베트남·인도네시아 청년 만난다</t>
-        </is>
-      </c>
-      <c r="E302" s="3" t="inlineStr">
-        <is>
-          <t>)= 한국국제교류재단 은 인도네시아 자카르타와 베트남 하노이·호찌민 등 3개 도시에서 한국 대표.</t>
-        </is>
-      </c>
-      <c r="F302" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G302" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015086900371</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D303" s="3" t="inlineStr">
-        <is>
-          <t>[가요소식] 그룹 유어즈, 21일 미니 1집 '비' 발매</t>
-        </is>
-      </c>
-      <c r="E303" s="3" t="inlineStr">
-        <is>
-          <t>)= ▲ 유어즈, 21일 미니 1집 '비' = 그룹 유어즈가 오는 21일 미니 1집 '비' 를 발매한다고 피나클.</t>
-        </is>
-      </c>
-      <c r="F303" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G303" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015086400005</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
-        </is>
-      </c>
-      <c r="D304" s="3" t="inlineStr">
-        <is>
-          <t>부산국제영화제 관객 20만명 넘었다…"11년 만에 처음"</t>
-        </is>
-      </c>
-      <c r="E304" s="3" t="inlineStr">
-        <is>
-          <t>)= 부산국제영화제를 찾은 관객 수가 11년 만에 20만명을 넘은 것으로 나타났다.</t>
-        </is>
-      </c>
-      <c r="F304" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G304" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015086800051</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D305" s="3" t="inlineStr">
-        <is>
-          <t>"장우혁이 폭행" 주장 전 소속사 직원 2심도 명예훼손 무죄</t>
-        </is>
-      </c>
-      <c r="E305" s="3" t="inlineStr">
-        <is>
-          <t>출신 가수 장우혁이 폭언과 폭행을 했다고 주장한 전 소속사 직원이 항소심에서도 명예훼손 혐의.</t>
-        </is>
-      </c>
-      <c r="F305" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G305" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015081700004</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B306" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D306" s="3" t="inlineStr">
-        <is>
-          <t>[대전소식] 대전부르스 창작가요제 18일 열려</t>
-        </is>
-      </c>
-      <c r="E306" s="3" t="inlineStr">
-        <is>
-          <t>) ▲ 대전부르스 창작가요제 18일 개최 = 대전시는 18일 오후 7시 대전 엑스포과학공원 주 무대에서 대전 빵축제와 연계해 '제.</t>
-        </is>
-      </c>
-      <c r="F306" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G306" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015081300063</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D307" s="3" t="inlineStr">
-        <is>
-          <t>곡성군, 전국요리경연대회 23일 개최…지역 특산물 활용</t>
-        </is>
-      </c>
-      <c r="E307" s="3" t="inlineStr">
-        <is>
-          <t>)= 전남광주 곡성군은 오는 23일 섬진강기차마을 중앙광장에서 '2026년 제4회 곡성 전국 요리경연대회'를 개최한.</t>
-        </is>
-      </c>
-      <c r="F307" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G307" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015080900054</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D308" s="3" t="inlineStr">
-        <is>
-          <t>저항하고 고발하는 이들의 영화…23∼25일 서울국제휘슬러영화제</t>
-        </is>
-      </c>
-      <c r="E308" s="3" t="inlineStr">
-        <is>
-          <t>)= 불의와 비리에 맞서 저항하고 인간 내면의 부조리를 고발하는 이들을 담은 영화들이 오는 23∼25일 서울 아트하.</t>
-        </is>
-      </c>
-      <c r="F308" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G308" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015074000005</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B309" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D309" s="3" t="inlineStr">
-        <is>
-          <t>세븐틴 승관이 소개하는 고향 제주…마을 여행 영상 공개</t>
-        </is>
-      </c>
-      <c r="E309" s="3" t="inlineStr">
-        <is>
-          <t>)= 제주 출신 아이돌그룹 세븐틴의 승관 이 고향 제주의 작은 마을을 여행하며 지역의 매력을 소개하는.</t>
-        </is>
-      </c>
-      <c r="F309" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G309" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015065200056</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B310" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D310" s="3" t="inlineStr">
-        <is>
-          <t>넷플릭스 "자막·더빙도 제2의 제작"…K-콘텐츠 세계화의 힘</t>
-        </is>
-      </c>
-      <c r="E310" s="3" t="inlineStr">
-        <is>
-          <t>'피지컬: 100' 멕시코판 첫 주 250만 시청이탈리아판도 흥행.</t>
-        </is>
-      </c>
-      <c r="F310" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G310" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015031200017</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B311" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C311" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D311" s="3" t="inlineStr">
-        <is>
-          <t>원주국제걷기대회 24∼25일 개최…'가을 정취 만끽하며 걸어요'</t>
-        </is>
-      </c>
-      <c r="E311" s="3" t="inlineStr">
-        <is>
-          <t>)= 강원 원주시는 오는 24∼25일 원주시 일원에서 제32회 원주국제걷기대회를 개최한다고 15일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F311" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G311" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015054400062</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (7개사)]</t>
-        </is>
-      </c>
-      <c r="D312" s="3" t="inlineStr">
-        <is>
-          <t>[가요소식] 터치드, 데뷔 6년 만에 첫 정규앨범 '극야'</t>
-        </is>
-      </c>
-      <c r="E312" s="3" t="inlineStr">
-        <is>
-          <t>)= ▲ 터치드, 데뷔 6년 만에 첫 정규앨범 '극야' = 밴드 터치드가 15일 낮 12시 첫 번째 정규앨범 '극야.</t>
-        </is>
-      </c>
-      <c r="F312" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G312" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015057900005</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B313" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C313" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D313" s="3" t="inlineStr">
-        <is>
-          <t>'서울의 봄' 김성수 감독, AI로 단편 '웜 트레인' 제작</t>
-        </is>
-      </c>
-      <c r="E313" s="3" t="inlineStr">
-        <is>
-          <t>)= 영화 '서울의 봄' 의 김성수 감독이 인공지능 을 활용해 단편 '웜 트레인'을 제작한다고 15일.</t>
-        </is>
-      </c>
-      <c r="F313" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G313" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015051500005</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B314" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C314" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D314" s="3" t="inlineStr">
-        <is>
-          <t>[방송소식] 윤두준·배윤경, '무한상사-하와수 네버다이' 출연</t>
-        </is>
-      </c>
-      <c r="E314" s="3" t="inlineStr">
-        <is>
-          <t>)= ▲ 윤두준·배윤경, '무한상사' 출연 = 웨이브는 그룹 하이라이트 멤버 겸 배우 윤두준과 배우 배윤경이 12월.</t>
-        </is>
-      </c>
-      <c r="F314" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G314" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015046800005</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B315" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C315" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D315" s="3" t="inlineStr">
-        <is>
-          <t>[테크스냅] IPTV방송협회, 23일 '휘슬러 포럼'…독립영화 유통 논의</t>
-        </is>
-      </c>
-      <c r="E315" s="3" t="inlineStr">
-        <is>
-          <t>)= 방송·미디어 업계가 독립영화 유통 활성화와 관객 접점 확대를 위한 논의의 장을 마련한다.</t>
-        </is>
-      </c>
-      <c r="F315" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G315" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015043400017</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="inlineStr">
-        <is>
-          <t>[가요소식] 2PM 장우영, 내달 14∼15일 솔로 콘서트</t>
-        </is>
-      </c>
-      <c r="E316" s="3" t="inlineStr">
-        <is>
-          <t>)= ▲ 2PM 장우영, 내달 14∼15일 솔로 콘서트 = 그룹 2PM의 장우영이.</t>
-        </is>
-      </c>
-      <c r="F316" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G316" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015041100005</t>
+          <t>https://www.yna.co.kr/view/AKR20261015092300893</t>
         </is>
       </c>
     </row>
@@ -15688,17 +14911,17 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>209,000원</t>
+          <t>210,000원</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>-2,000원 (-0.95%)</t>
+          <t>-1,000원 (-0.47%)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>205,000원</t>
+          <t>206,000원</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -15708,12 +14931,12 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>198,500원</t>
+          <t>199,500원</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>+39.4%</t>
+          <t>+38.7%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -15737,26 +14960,26 @@
         </is>
       </c>
       <c r="O38" s="3" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>中 CXMT 반도체 신기술, 왜 삼전닉스 주가 흔들었나 (조선일보)</t>
+          <t>"삼성전자, CXMT와 기술격차 최대 7년…시장 우려 과도" (한국경제)</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>[249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 232000.0, 209000.0]</t>
+          <t>[249000.0, 248500.0, 253500.0, 252500.0, 261000.0, 274000.0, 276500.0, 285500.0, 270000.0, 272500.0, 268500.0, 276000.0, 276000.0, 272000.0, 268500.0, 262000.0, 250500.0, 232000.0, 232000.0, 210000.0]</t>
         </is>
       </c>
     </row>
@@ -15783,42 +15006,42 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>1,260,000원</t>
+          <t>1,262,000원</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>+124,000원 (+10.92%)</t>
+          <t>+126,000원 (+11.09%)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1,197,000원</t>
+          <t>1,237,000원</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>1,247,500원</t>
+          <t>1,868,000원</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>1,222,000원</t>
+          <t>1,199,000원</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+51.0%</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>🔴 단기 비중 축소 (악재 주의)</t>
+          <t>관망 (HOLD)</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>악재 보도 및 5일 연속 약세(-4% 이상)로 단기 추가 하락 위험</t>
+          <t>중립 구간 유지 중</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -15832,26 +15055,26 @@
         </is>
       </c>
       <c r="O39" s="3" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>[개장시황] SK하이닉스 7%대 급락 이유…이틀 만에 또 사이드카 (자본시장뉴스)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>[1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1419000.0, 1260000.0]</t>
+          <t>[1697000.0, 1690000.0, 1759000.0, 1745000.0, 1857000.0, 1868000.0, 1840000.0, 1862000.0, 1768000.0, 1765000.0, 1776000.0, 1833000.0, 1841000.0, 1773000.0, 1723000.0, 1681000.0, 1605000.0, 1443000.0, 1419000.0, 1262000.0]</t>
         </is>
       </c>
     </row>
@@ -15878,27 +15101,27 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>294,000원</t>
+          <t>295,500원</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>-214,000원 (-42.13%)</t>
+          <t>-212,500원 (-41.83%)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>279,500원</t>
+          <t>280,500원</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>291,000원</t>
+          <t>292,500원</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>285,000원</t>
+          <t>286,500원</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -15913,7 +15136,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(344,875원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(344,950원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -15927,26 +15150,26 @@
         </is>
       </c>
       <c r="O40" s="3" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>현대차, 인도 푸네 신공장 준공…연 17만대 생산체제 구축 (전기신문)</t>
+          <t>정부 요청받은 SK·삼성·현대차, 美 웨스팅하우스 지분투자 검토…최대 4조 규모 (인베스트조선)</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>[371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 313500.0, 294000.0]</t>
+          <t>[371500.0, 367000.0, 362000.0, 363000.0, 365000.0, 359000.0, 360500.0, 353500.0, 354500.0, 350000.0, 345000.0, 349000.0, 346500.0, 348000.0, 336000.0, 324500.0, 320000.0, 315000.0, 313500.0, 295500.0]</t>
         </is>
       </c>
     </row>
@@ -15973,27 +15196,27 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
+          <t>106,000원</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>-45,600원 (-30.10%)</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>100,500원</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
           <t>105,000원</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>-46,300원 (-30.56%)</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>99,900원</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>104,000원</t>
-        </is>
-      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>102,000원</t>
+          <t>102,500원</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -16008,7 +15231,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(114,760원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(114,795원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -16022,16 +15245,16 @@
         </is>
       </c>
       <c r="O41" s="3" t="n">
-        <v>25.9</v>
+        <v>26.7</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
@@ -16041,7 +15264,7 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>[124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 108600.0, 105200.0]</t>
+          <t>[124200.0, 121800.0, 120700.0, 120900.0, 121900.0, 120000.0, 118500.0, 115400.0, 117600.0, 116000.0, 112800.0, 113300.0, 112900.0, 112600.0, 109600.0, 106800.0, 108100.0, 108300.0, 108600.0, 105900.0]</t>
         </is>
       </c>
     </row>
@@ -16068,27 +15291,27 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>172,500원</t>
+          <t>173,500원</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>-38,300원 (-18.15%)</t>
+          <t>-37,400원 (-17.73%)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>164,000원</t>
+          <t>165,000원</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>171,000원</t>
+          <t>172,000원</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>167,500원</t>
+          <t>168,500원</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -16103,7 +15326,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(192,295원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(192,340원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -16117,26 +15340,26 @@
         </is>
       </c>
       <c r="O42" s="3" t="n">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>“잊고 있던 페이 잔액 255억원 돌려받으세요”…빅테크 3사, 정기 알림·환급 안내 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>[204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 179400.0, 172700.0]</t>
+          <t>[204000.0, 206000.0, 201500.0, 199000.0, 197700.0, 197900.0, 201000.0, 194700.0, 197700.0, 194800.0, 193700.0, 191200.0, 192200.0, 191100.0, 189000.0, 183800.0, 180500.0, 178000.0, 179400.0, 173600.0]</t>
         </is>
       </c>
     </row>
@@ -16163,27 +15386,27 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>30,600원</t>
+          <t>31,000원</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>-18,975원 (-38.26%)</t>
+          <t>-18,600원 (-37.50%)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>29,100원</t>
+          <t>29,400원</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>30,300원</t>
+          <t>30,700원</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>29,700원</t>
+          <t>30,100원</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -16198,7 +15421,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(33,168원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(33,187원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -16212,26 +15435,26 @@
         </is>
       </c>
       <c r="O43" s="3" t="n">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>[한화투자증권] 카카오게임즈: 기업가치 정상화를 위한 모든 변화 시작 (한화투자증권)</t>
+          <t>[정신아의 약속 1년②] 카카오 주가 반토막에 인적분할 승부수 (연합인포맥스)</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>[34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 31700.0, 30625.0]</t>
+          <t>[34650.0, 34500.0, 33500.0, 33500.0, 33550.0, 33200.0, 34150.0, 33450.0, 34150.0, 33700.0, 33550.0, 33550.0, 33450.0, 33500.0, 33050.0, 32300.0, 32000.0, 31300.0, 31700.0, 31000.0]</t>
         </is>
       </c>
     </row>
@@ -16258,27 +15481,27 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>180,500원</t>
+          <t>182,000원</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>-11,980원 (-6.23%)</t>
+          <t>-10,280원 (-5.34%)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>177,000원</t>
+          <t>178,500원</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>189,500원</t>
+          <t>191,000원</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>171,500원</t>
+          <t>173,000원</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -16307,16 +15530,16 @@
         </is>
       </c>
       <c r="O44" s="3" t="n">
-        <v>46.7</v>
+        <v>50.5</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
@@ -16326,7 +15549,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>[178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 179800.0, 180400.0]</t>
+          <t>[178800.0, 177500.0, 177200.0, 180300.0, 179400.0, 181400.0, 178500.0, 177400.0, 178300.0, 178900.0, 177700.0, 183600.0, 182600.0, 182400.0, 183500.0, 179600.0, 180400.0, 179700.0, 179800.0, 182100.0]</t>
         </is>
       </c>
     </row>
@@ -16353,27 +15576,27 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>817,000원</t>
+          <t>824,000원</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>-692,000원 (-45.86%)</t>
+          <t>-685,000원 (-45.39%)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>776,000원</t>
+          <t>783,000원</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>809,000원</t>
+          <t>816,000원</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>792,500원</t>
+          <t>799,500원</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -16388,7 +15611,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(999,000원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(999,350원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -16402,16 +15625,16 @@
         </is>
       </c>
       <c r="O45" s="3" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -16421,7 +15644,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>[1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 842000.0, 817000.0]</t>
+          <t>[1137000.0, 1063000.0, 1055000.0, 1097000.0, 1078000.0, 1067000.0, 1057000.0, 1021000.0, 1034000.0, 1012000.0, 1007000.0, 1034000.0, 1072000.0, 1023000.0, 972000.0, 891000.0, 862000.0, 839000.0, 842000.0, 824000.0]</t>
         </is>
       </c>
     </row>
@@ -16448,12 +15671,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>401,500원</t>
+          <t>402,500원</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>-6,500원 (-1.59%)</t>
+          <t>-5,500원 (-1.35%)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -16463,17 +15686,17 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>401,500원</t>
+          <t>402,500원</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>393,500원</t>
+          <t>394,500원</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -16483,7 +15706,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>RSI 60.1, 20일선 이격도 +7.3%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
+          <t>RSI 60.5, 20일선 이격도 +7.5%로 단기 과열권 진입. 욕심을 줄이고 분할 차익 실현 권고</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -16497,16 +15720,16 @@
         </is>
       </c>
       <c r="O46" s="3" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -16516,7 +15739,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>[351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 422000.0, 401500.0]</t>
+          <t>[351500.0, 365500.0, 367000.0, 365000.0, 364000.0, 352000.0, 350500.0, 351500.0, 364000.0, 352500.0, 357000.0, 360500.0, 371000.0, 390000.0, 391000.0, 401000.0, 398000.0, 410000.0, 422000.0, 402500.0]</t>
         </is>
       </c>
     </row>
@@ -16543,27 +15766,27 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>292,500원</t>
+          <t>292,000원</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>-75,500원 (-20.52%)</t>
+          <t>-76,000원 (-20.65%)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>278,000원</t>
+          <t>277,500원</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>289,500원</t>
+          <t>289,000원</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>283,500원</t>
+          <t>283,000원</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -16578,7 +15801,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(312,775원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(312,750원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -16592,26 +15815,26 @@
         </is>
       </c>
       <c r="O47" s="3" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>포스코 개발 고망간강, LNG선 화물창 실증…한화오션과 맞손 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>[326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 309000.0, 292500.0]</t>
+          <t>[326000.0, 332000.0, 326500.0, 326500.0, 323000.0, 317000.0, 317500.0, 311500.0, 316500.0, 304000.0, 306000.0, 306500.0, 311000.0, 318000.0, 307500.0, 306500.0, 299000.0, 299000.0, 309000.0, 292000.0]</t>
         </is>
       </c>
     </row>
@@ -16638,7 +15861,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>$221.30 (약 298,219원)</t>
+          <t>$221.30 (약 296,648원)</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -16648,12 +15871,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>$217.98 (약 293,746원)</t>
+          <t>$217.98 (약 292,198원)</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>$254.50 (약 342,952원)</t>
+          <t>$254.50 (약 341,145원)</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -16733,7 +15956,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>$342.96 (약 462,166원)</t>
+          <t>$342.96 (약 459,731원)</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -16743,12 +15966,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>$336.10 (약 452,922원)</t>
+          <t>$336.10 (약 450,536원)</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>$360.11 (약 485,274원)</t>
+          <t>$360.11 (약 482,717원)</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -16796,7 +16019,7 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>애플, 중국서 첫 AI 기능 12월 출시…새 시리는 제외 (주요언론)</t>
+          <t>최근 특이 뉴스 없음</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -16828,7 +16051,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>$367.16 (약 494,777원)</t>
+          <t>$367.16 (약 492,170원)</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -16838,12 +16061,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>$359.82 (약 484,881원)</t>
+          <t>$359.82 (약 482,327원)</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>$385.52 (약 519,516원)</t>
+          <t>$385.52 (약 516,779원)</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -16923,7 +16146,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>$533.69 (약 719,189원)</t>
+          <t>$533.69 (약 715,400원)</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -16933,12 +16156,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>$516.40 (약 695,890원)</t>
+          <t>$516.40 (약 692,223원)</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>$560.37 (약 755,149원)</t>
+          <t>$560.37 (약 751,170원)</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -17003,12 +16226,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>128940.KS</t>
+          <t>042660.KS</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -17018,42 +16241,42 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>370,500원</t>
+          <t>62,400원</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>-141,500원 (-27.64%)</t>
+          <t>-63,400원 (-50.40%)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>363,000원</t>
+          <t>59,300원</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>534,000원</t>
+          <t>61,800원</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>352,000원</t>
+          <t>60,500원</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>+47.1%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>주가가 20일선(77,065원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -17067,16 +16290,16 @@
         </is>
       </c>
       <c r="O52" s="3" t="n">
-        <v>28.8</v>
+        <v>19.1</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
@@ -17086,7 +16309,7 @@
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>[474000.0, 496500.0, 502000.0, 515000.0, 503000.0, 505000.0, 502000.0, 520000.0, 504000.0, 507000.0, 499000.0, 497500.0, 506000.0, 523000.0, 534000.0, 480500.0, 474500.0, 453000.0, 404500.0, 370500.0]</t>
+          <t>[85900.0, 82400.0, 81300.0, 83600.0, 82900.0, 81800.0, 81600.0, 79600.0, 80000.0, 78600.0, 78800.0, 78500.0, 78800.0, 77200.0, 74100.0, 72000.0, 67300.0, 67100.0, 67400.0, 62400.0]</t>
         </is>
       </c>
     </row>
@@ -17098,12 +16321,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>000810.KS</t>
+          <t>298040.KS</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -17113,27 +16336,27 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>576,000원</t>
+          <t>1,821,000원</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>+90,000원 (+18.52%)</t>
+          <t>-1,144,000원 (-38.58%)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>547,000원</t>
+          <t>1,730,000원</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>570,000원</t>
+          <t>1,803,000원</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>558,500원</t>
+          <t>1,766,500원</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -17148,30 +16371,30 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(636,600원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(2,649,550원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O53" s="3" t="n">
-        <v>32.5</v>
+        <v>20.5</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
@@ -17181,7 +16404,7 @@
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>[675000.0, 661000.0, 661000.0, 666000.0, 648000.0, 651000.0, 655000.0, 648000.0, 661000.0, 653000.0, 633000.0, 626000.0, 626000.0, 635000.0, 629000.0, 612000.0, 622000.0, 612000.0, 582000.0, 576000.0]</t>
+          <t>[2803000.0, 2689000.0, 2806000.0, 2861000.0, 2915000.0, 2917000.0, 2901000.0, 2896000.0, 2780000.0, 2804000.0, 2773000.0, 2822000.0, 2785000.0, 2807000.0, 2588000.0, 2494000.0, 2242000.0, 2152000.0, 2135000.0, 1821000.0]</t>
         </is>
       </c>
     </row>
@@ -17193,12 +16416,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>030200.KS</t>
+          <t>012330.KS</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -17208,65 +16431,65 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>50,400원</t>
+          <t>337,500원</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>-14,000원 (-21.74%)</t>
+          <t>-78,000원 (-18.77%)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>49,400원</t>
+          <t>320,500원</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>53,400원</t>
+          <t>334,000원</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>47,900원</t>
+          <t>327,500원</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>⏸️ 관망/보유 (쿨다운 1일차)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>최근 1일 전(2026-10-14) 단기 매수 추천 이력 존재 ➔ 중복 매수 방지 쿨다운 적용(기존 포지션 분할 보유/관망 권고)</t>
+          <t>주가가 20일선(371,725원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O54" s="3" t="n">
-        <v>37.8</v>
+        <v>27.4</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
@@ -17276,7 +16499,7 @@
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>[53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 49900.0, 50400.0]</t>
+          <t>[400000.0, 394500.0, 383000.0, 381000.0, 379000.0, 373000.0, 372500.0, 367500.0, 373000.0, 367000.0, 367000.0, 382000.0, 383500.0, 380000.0, 373500.0, 359000.0, 354500.0, 348500.0, 358500.0, 337500.0]</t>
         </is>
       </c>
     </row>
@@ -17288,12 +16511,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>017670.KS</t>
+          <t>064350.KS</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -17303,27 +16526,27 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>78,300원</t>
+          <t>91,800원</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>-19,800원 (-20.18%)</t>
+          <t>-118,200원 (-56.29%)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>74,400원</t>
+          <t>87,200원</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>77,500원</t>
+          <t>90,900원</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>76,000원</t>
+          <t>89,000원</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -17338,30 +16561,30 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>주가가 20일선(85,945원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
+          <t>주가가 20일선(112,140원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>보유 / 중립 (HOLD)</t>
+          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>장기 추세 유지</t>
+          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
         </is>
       </c>
       <c r="O55" s="3" t="n">
-        <v>31.9</v>
+        <v>19.6</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
@@ -17371,7 +16594,7 @@
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>[90100.0, 88000.0, 88100.0, 87600.0, 89200.0, 87000.0, 87300.0, 87100.0, 88200.0, 86200.0, 85600.0, 86300.0, 88400.0, 88400.0, 87400.0, 84100.0, 79700.0, 80000.0, 81900.0, 78300.0]</t>
+          <t>[124400.0, 121400.0, 119500.0, 122300.0, 122500.0, 118800.0, 117100.0, 115900.0, 115700.0, 112300.0, 111600.0, 112500.0, 116500.0, 112400.0, 107900.0, 105200.0, 100000.0, 97700.0, 97300.0, 91800.0]</t>
         </is>
       </c>
     </row>
@@ -17383,12 +16606,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>034020.KS</t>
+          <t>030200.KS</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -17398,32 +16621,32 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>62,900원</t>
+          <t>50,500원</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>-41,300원 (-39.64%)</t>
+          <t>-13,900원 (-21.58%)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>61,600원</t>
+          <t>49,500원</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>87,000원</t>
+          <t>53,400원</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>48,000원</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>+41.1%</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -17438,25 +16661,25 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 장기 비중 축소 / 손절 검토</t>
+          <t>보유 / 중립 (HOLD)</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>60일선 하향 이탈 및 52주 신저가 부근, 중장기 추세 하향 전환 우려</t>
+          <t>장기 추세 유지</t>
         </is>
       </c>
       <c r="O56" s="3" t="n">
-        <v>24.4</v>
+        <v>38.7</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
@@ -17466,7 +16689,7 @@
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>[87000.0, 86200.0, 83800.0, 85400.0, 84900.0, 85300.0, 86500.0, 81700.0, 82000.0, 79700.0, 81600.0, 82100.0, 81100.0, 81500.0, 80500.0, 78000.0, 71500.0, 70200.0, 69400.0, 62900.0]</t>
+          <t>[53200.0, 53000.0, 52800.0, 53400.0, 53000.0, 53100.0, 53100.0, 52700.0, 52900.0, 52900.0, 52300.0, 51800.0, 51900.0, 51500.0, 51300.0, 52100.0, 49900.0, 49750.0, 49900.0, 50500.0]</t>
         </is>
       </c>
     </row>
@@ -17478,12 +16701,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>한화손해보험</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>055550.KS</t>
+          <t>000370.KS</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -17493,32 +16716,32 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>93,700원</t>
+          <t>6,210원</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>-6,100원 (-6.11%)</t>
+          <t>-460원 (-6.90%)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>91,800원</t>
+          <t>6,090원</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>114,500원</t>
+          <t>8,500원</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>89,000원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>+24.8%</t>
+          <t>+39.7%</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
@@ -17546,12 +16769,12 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
@@ -17561,7 +16784,7 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>[114600.0, 112200.0, 112100.0, 113300.0, 110100.0, 113100.0, 113200.0, 109300.0, 111300.0, 110500.0, 106100.0, 103800.0, 104800.0, 103600.0, 103300.0, 99500.0, 100500.0, 99700.0, 95000.0, 93700.0]</t>
+          <t>[8500.0, 8320.0, 8080.0, 8290.0, 8070.0, 8070.0, 7790.0, 7610.0, 7890.0, 7880.0, 7300.0, 7280.0, 7330.0, 7230.0, 7340.0, 7200.0, 7230.0, 7010.0, 6360.0, 6210.0]</t>
         </is>
       </c>
     </row>
@@ -17573,12 +16796,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>352820.KS</t>
+          <t>066570.KS</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -17588,32 +16811,32 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>162,500원</t>
+          <t>168,500원</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>-92,800원 (-36.32%)</t>
+          <t>+46,400원 (+37.97%)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>159,500원</t>
+          <t>165,000원</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>175,500원</t>
+          <t>232,500원</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>154,500원</t>
+          <t>160,000원</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>+10.2%</t>
+          <t>+40.7%</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -17637,16 +16860,16 @@
         </is>
       </c>
       <c r="O58" s="3" t="n">
-        <v>46.6</v>
+        <v>33.6</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
@@ -17656,7 +16879,7 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>[175700.0, 173100.0, 169900.0, 165600.0, 165900.0, 162500.0, 156300.0, 156800.0, 161900.0, 158700.0, 156600.0, 156200.0, 155300.0, 157000.0, 167000.0, 163900.0, 156500.0, 163400.0, 163800.0, 162700.0]</t>
+          <t>[198200.0, 202000.0, 200000.0, 197900.0, 198400.0, 202500.0, 216500.0, 209000.0, 214500.0, 213500.0, 212500.0, 211500.0, 216000.0, 232500.0, 208000.0, 200500.0, 184700.0, 178000.0, 177400.0, 168600.0]</t>
         </is>
       </c>
     </row>
@@ -17668,12 +16891,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>271560.KS</t>
+          <t>001740.KS</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -17683,42 +16906,42 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>106,000원</t>
+          <t>5,540원</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>-32,200원 (-23.33%)</t>
+          <t>+120원 (+2.21%)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>103,500원</t>
+          <t>5,260원</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>116,000원</t>
+          <t>5,480원</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>100,500원</t>
+          <t>5,370원</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>+11.9%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>관망 (HOLD)</t>
+          <t>🔴 단기 비중 축소 (추세 이탈 경고)</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>중립 구간 유지 중</t>
+          <t>주가가 20일선(6,166원)을 하향 이탈하고 이동평균선 역배열 지속. 리스크 관리 차원 비중 축소 권고</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -17732,16 +16955,16 @@
         </is>
       </c>
       <c r="O59" s="3" t="n">
-        <v>32.6</v>
+        <v>27.4</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
@@ -17751,7 +16974,7 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>[115300.0, 116000.0, 111400.0, 113500.0, 111500.0, 111200.0, 110900.0, 110100.0, 111500.0, 111500.0, 106900.0, 106100.0, 105300.0, 106500.0, 106100.0, 104200.0, 105600.0, 106500.0, 105600.0, 105800.0]</t>
+          <t>[6240.0, 6300.0, 6290.0, 6310.0, 6260.0, 6090.0, 6170.0, 6070.0, 6120.0, 6200.0, 6210.0, 6450.0, 6550.0, 6550.0, 6370.0, 6100.0, 5900.0, 5850.0, 5760.0, 5540.0]</t>
         </is>
       </c>
     </row>
@@ -17773,7 +16996,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18199,12 +17422,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5,569.79</t>
+          <t>5,554.22</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>▼ -439.02 (-7.31%)</t>
+          <t>▼ -454.59 (-7.57%)</t>
         </is>
       </c>
     </row>
@@ -18226,12 +17449,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>762.96</t>
+          <t>760.82</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>▼ -60.92 (-7.39%)</t>
+          <t>▼ -63.06 (-7.65%)</t>
         </is>
       </c>
     </row>
@@ -18307,12 +17530,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>1,347.58</t>
+          <t>1,340.48</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>▲ +6.72원 (+0.50%)</t>
+          <t>▼ -0.38원 (-0.03%)</t>
         </is>
       </c>
     </row>
@@ -18334,12 +17557,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>852.00</t>
+          <t>846.90</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>▲ +7.20원 (+0.85%)</t>
+          <t>▲ +2.10원 (+0.25%)</t>
         </is>
       </c>
     </row>
@@ -18361,12 +17584,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>1,512.10</t>
+          <t>1,502.30</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>▲ +17.10원 (+1.14%)</t>
+          <t>▲ +7.30원 (+0.49%)</t>
         </is>
       </c>
     </row>
@@ -18388,12 +17611,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>201.54</t>
+          <t>200.43</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>▲ +1.12원 (+0.56%)</t>
+          <t>▲ +0.01원 (+0.00%)</t>
         </is>
       </c>
     </row>
@@ -18670,32 +17893,32 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>110,478,000원</t>
+          <t>109,677,000원</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>108,821,000원</t>
+          <t>108,032,000원</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>119,410,000원</t>
+          <t>119,368,000원</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>104,954,000원</t>
+          <t>104,193,000원</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>+10.5%</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -18727,32 +17950,32 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3,229,000원</t>
+          <t>3,201,000원</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-2.17%</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3,203,000원</t>
+          <t>3,175,500원</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>3,494,500원</t>
+          <t>3,493,000원</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>3,116,000원</t>
+          <t>3,089,000원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>+9.1%</t>
+          <t>+10.0%</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -18762,7 +17985,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>RSI 36.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 35.5로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -18784,32 +18007,32 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>141,000원</t>
+          <t>138,400원</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>139,900원</t>
+          <t>137,300원</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>154,400원</t>
+          <t>154,300원</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>136,100원</t>
+          <t>133,600원</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+12.4%</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -18819,7 +18042,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>RSI 41.6로 단기 과매도 구간 진입, 기술적 반등 기대</t>
+          <t>RSI 38.8로 단기 과매도 구간 진입, 기술적 반등 기대</t>
         </is>
       </c>
     </row>
@@ -18840,7 +18063,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="47" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -19632,21 +18855,21 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>더 안정적인 성장을 위한 정비 작업(3Q26 Pre)</t>
+          <t>3Q26 Preview: 진검승부</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -19656,42 +18879,42 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>선급금 4Q26 반영, 북경한미 정비 작업과 앱토즈 인수로 전체적인 실적은 부진 3Q26 실적은 연결기준 매출액 3,794억원(YoY+4.7%), 영업이익 381억원(YoY-30.8%, OPM 10.0%)으로 예상된다. 컨센서스와 크게 어긋나 보이지만, Genentech향 HM17321 L/O 선급금이 미국 HSR 행정절차가 10월 초 완료됨에 따라 4Q26에 인식되는데 컨센서스가 미리 3Q에 이를 반영했기 때문이다. 2Q에 Lilly향 L/O에 따른 선급금이 반영되었기 때문에 QoQ로 비교하는 것도 큰 의미가 없다.</t>
+          <t>실적에 비우호적으로 작용한 대내외 변수 한화오션의 2026년 3분기 영업실적은 매출액 3조 4,314억원(yoy +13.5%, qoq -37.0%), 영업이익 4,726억원(yoy +63.1%, qoq -35.8%)으로 시장 기대치를 하회할 것으로 전망한다. 거제도 폭우와 노사분규 발생으로 근로손실일수가 증가하였고, 8월 이후 원달러 환율이 급격히 하락한 것이 주요 요인이다. 특수선과 에너지플랜트 부문에서는 고정비 부담이 이어지겠으나, 전사 영업실적으로의 영향은 크지 않을 것으로 예상한다.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_하나증권_한미약품_더 안정적인 성장을 위한 정비 작업(3Q26 Pre).pdf</t>
+          <t>2026-10-15_IBK투자증권_한화오션_3Q26 Preview 진검승부.pdf</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1,895.0십억원</t>
+          <t>15,712십억원</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>494.6십억원</t>
+          <t>2,038십억원</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>1,844.1십억원</t>
+          <t>14,014십억원</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>284.7십억원</t>
+          <t>1,993십억원</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>3Q26 실적은 연결기준 매출액 3,794억원(YoY+4)</t>
+          <t>2026년 3분기 영업실적은 매출액 3조 4,314억원(yoy +13)</t>
         </is>
       </c>
     </row>
@@ -19702,21 +18925,21 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>유안타증권</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Pre - 단기 실적보다 중요한 것은</t>
+          <t>3Q26 Preview Update: 눈높이는 낮추지만</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -19731,37 +18954,37 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026년 3분기 실적은 컨센서스 하회 전망 3분기 연결 지배순이익은 4,863억원으로 컨센서스(5,825억원)를 하회할 것으로 전망한다. 장기보험손익이 사업비 부담 확대로 예상대비 부한 가운데, 증시 부진과 금리 상승에 따른 투자손익 악화도 실적에 부담으로 작용할 것으로 예상한다. [보험손익] 보험손익은 4,006억원(YoY +8.6%, QoQ -27.5%)으로 추정한다.</t>
+          <t>3Q26 Preview: 건설 비용 반영으로 추정치 하향 3Q26 매출액 1조 9,162억원(YoY +18.0%, QoQ +13.6%), 영업이익 2,631억원(YoY +19.7%, QoQ -0.5%), OPM 13.7%로 영업이익은 컨센서스를 하회할 전망이다. 지난 10월 7일 프리뷰에서 제시한 영업이익 3,126억원 대비 추정치를 하향한다. 주요 원인은 건설 부문의 예상치 못한 원가 반영이다.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_하나증권_삼성화재_3Q26 Pre - 단기 실적보다 중요한 것은.pdf</t>
+          <t>2026-10-15_유안타증권_효성중공업_3Q26 Preview Update 눈높이는 낮추지만.pdf</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7,221십억원</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>3,496십억원</t>
+          <t>1,068십억원</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9,748십억원</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>4,566십억원</t>
+          <t>1,774십억원</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>3Q26 매출액 1조 9,162억원(YoY +18)</t>
         </is>
       </c>
     </row>
@@ -19772,21 +18995,21 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>유안타증권</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>바닥 통과, 성장 엔진 점화</t>
+          <t>우수한 본업임에도 믹스 악화가 걸린다</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -19801,37 +19024,37 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY 3Q26 연결 영업수익은 7.1조원(-1.1% YoY), 영업이익은 5,350억원(-0.6% YoY)으로 시장 컨센서스(7.0조원, 5,442억원)에 부합할 전망이다. 부동산 관련 일회성 비용 제거시 영업이익은 +2.8% YoY 증가한 것으로 추정된다. 별도 영업이익은 3,400억원으로 전년과 유사한 수준이 예상된다.</t>
+          <t>[투자포인트] ■ 26.3Q 매출액 31.5조원 (+10.2% YoY) , 영업이익 2.3조원 ( +62.1% YoY, 7.5% OPM) 전망. 1) 26.3Q 글로벌 도매 판매 84.4만대 (+7.8% YoY)를 기록. 2) 26.3Q 원/달러 평균 환율은 1,420원으로 직전 분기 대비 80원 하락했으나, 원/달러 기말 환율이 동시에 1,352원으로 직전 분기 대비 197원 하락하며 부정적 환율효과 일정 부분 상쇄할 것.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_유안타증권_KT_바닥 통과, 성장 엔진 점화.pdf</t>
+          <t>2026-10-15_iM증권_기아_우수한 본업임에도 믹스 악화가 걸린다.pdf</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>27,426십억원</t>
+          <t>141,199십억원</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2,076십억원</t>
+          <t>11,904십억원</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>27,905십억원</t>
+          <t>148,651십억원</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2,256십억원</t>
+          <t>13,161십억원</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 일회성 제거시 영업이익 +3% YoY</t>
+          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
         </is>
       </c>
     </row>
@@ -19842,21 +19065,21 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>3Q26 잠정 실적 - ESS 판매 호조와 일회성 이익</t>
+          <t>26.4Q에는 더 좋아질 이익</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -19871,32 +19094,32 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>WHAT’S THE STORY? View, 2027년 영업이익 228% 성장 전망: 12MF EPS 및 BPS 상향을 감안하여 P/E 및 P/B 평균 밸류에이션상 목표주가를 9% 상향(46→50만원). 보상금 수령 효과를 제외하더라도 ESS 생산 병목 현상(모듈/팩 생산 차질)이 소멸되기 시작한 점과 보상금 제외하더라도 유럽 공장 가동률 상승에 힘입어 자동차 적자 축소도 지속되고 있는 점이 긍정적.</t>
+          <t>[투자포인트] ■ 26.3Q 매출액 15.1조원 (+0.8% YoY) , 영업이익 9,091억원 (+16.5% YoY) 전망. 1) 26.3Q 국내 완성차 생산 대수가 감소함에 따른 영향 존재하나, 주요 EV 생산 확대에 따른 전동화 부문 적자 폭 축소 될 것. 2) 26.3Q AS 사업부 영업이익률은 26% 이상 수준으로 나타날 것이고, 물류비 상승에 따른 영향 또한 제한적.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_삼성증권_LG에너지솔루션_3Q26 잠정 실적 - ESS 판매 호조와 일회성 이익.pdf</t>
+          <t>2026-10-15_iM증권_현대모비스_26.4Q에는 더 좋아질 이익.pdf</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>43,977십억원</t>
+          <t>70,482십억원</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>4,125십억원</t>
+          <t>3,845십억원</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>52,314십억원</t>
+          <t>73,040십억원</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>6,402십억원</t>
+          <t>3,984십억원</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -19912,21 +19135,21 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>유안타증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>이익 회복 위에 쌓이는 AIDC 가치</t>
+          <t>3Q26 Preview: 컨센서스 상회 전망</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -19941,37 +19164,37 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 컨센서스 부합, 이익 회복 지속 3Q26 연결 영업수익은 4.5조원(+12.5% YoY), 영업이익은 5,340억원(+1,002.1% YoY)으로 시장 컨센서스(4.5조원, 5,240억원)에 부합할 전망이다. 3개 분기 연속 이어진 플래그십 단말기 출시와 3G 중심의 장기 미사용회선 정리 효과로 무선 ARPU가 상승한 것으로 파악된다. 마케팅비와 감가상각비도 안정화되며 비용 부담 완화 기조가 유지되고 있어, 영업이익 회복 추세는 이어질 전망이다.</t>
+          <t>다만 폴란드 EC2 체결 직전 12MF EV/EBITDA 멀티플은 20배, 현재 멀티플은 6.1배, 페루 사업을 반영하지 않은 27년 실적 기준 EV/EBITDA 멀티플로도 8.0배 수준으로 22년 폴란드와의 기본계약 체결 전 밸류에이션인 15배보다도 낮은 수준. 4Q26 내 페루 신규 전차 사업 수주 시 27년 감익을 상쇄할 수 있을 것이라 전망하며 목표주가는 낮추지만 투자의견 매수 유지.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_유안타증권_SK텔레콤_이익 회복 위에 쌓이는 AIDC 가치.pdf</t>
+          <t>2026-10-15_대신증권_현대로템_3Q26 Preview 컨센서스 상회 전망.pdf</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>17,718십억원</t>
+          <t>7,371십억원</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2,017십억원</t>
+          <t>1,105십억원</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>18,101십억원</t>
+          <t>7,118십억원</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2,075십억원</t>
+          <t>804십억원</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>3Q26 연결 기준 매출액 2조 1,210억원(+30)</t>
         </is>
       </c>
     </row>
@@ -19982,21 +19205,21 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>전력 수요 증가에 최적화된 사업 포트폴리오</t>
+          <t>밑그림은 그려졌고, 이제 실행을 볼 차례</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -20011,37 +19234,37 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>WHAT’S THE STORY? 원전 확대 정책의 최대 수혜주: 국내 유일의 원전 설비 통합 제작사로 원자로, 증기발생기 등 주기기에 해당하는 1차 계통부터, 증기터빈 및 발전기와 같은 2차 계통까지 원전 주요 설비 전반에 대한 제조 능력을 보유. 2020년대 들어 에너지 안보와 AI의 확산, 그리고 환경 규제 강화 등으로 전력 부족에 대한 우려가 가중되면서 무탄소 기저 발전원으로서 원전에 대한 관심이 고조.</t>
+          <t>" 3Q Preview: 연결 매출액 7조 1,174억원(-0.1%yoy), 영업이익 5,120억원(-4.9%yoy)으로 시장 컨센서스를 소폭 하회할 전망. 7월까지 이어진 고객보상 프로그램에 따른 무선 수익성 저하와 판매비 증가가 복합적으로 작용한 영향 " 고객보상 프로그램에 따른 ARPU가 하락으로 무선 매출은 전년 동기 대비 2.4% 감소할 전망. 전년 번호이동시장 경쟁 심화로 증가한 판매비의 상각 부담도 지속되며 전년 동기 대비 3.2% 증가할 것으로 예상.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_삼성증권_두산에너빌리티_전력 수요 증가에 최적화된 사업 포트폴리오.pdf</t>
+          <t>2026-10-15_유진투자증권_KT_밑그림은 그려졌고, 이제 실행을 볼 차례.pdf</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>21,159십억원</t>
+          <t>27십억원</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>1,883십억원</t>
+          <t>2십억원</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>24,494십억원</t>
+          <t>,376십억원</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2,350십억원</t>
+          <t>,136십억원</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>2026/2027 실적 성장세 및 기업가치 재평가 전망</t>
+          <t>연결 매출액 7조 1,174억원(-0)</t>
         </is>
       </c>
     </row>
@@ -20052,21 +19275,21 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>한화투자증권</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>롯데손해보험 인수, 기대와 우려가 동반</t>
+          <t>4분기 턴어라운드 가능성이 확인될 3분기 실적</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -20076,37 +19299,37 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>매수</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>사실과 설명: 롯데손해보험 인수계약 체결 - 신한지주는 롯데손해보험의 최대주주 보유 지분 77.04%를 6,933억원(주당 2,900원)에 매수하는 주식매매계약을 체결. 역산하면 회사가치(100%)를 9,000억원으로 산정한 결과로, 단순 산출 시 2025년 EPS 대비 17.5배, 1H26 말 자본 대비 0.91배에 해당하는 가격 - 신한지주는 롯데손해보험에 투입될 자금으로 (1)현재 가치로 잔여지분을 전량 인수할 경우의 총 9,000억원과 (2)인수 후 증자 예상 규모 3,000억원을 언급. 이때 3,000억원은 기존 계열사인 신한EZ손해보험에 향후 5년간 투입했어야 할 증자 규모의 예상치로, 롯데손보 인수에 따른 추가 자본 소요가 아니라고 설명 - 롯데손보의 2Q26 말 기본자본(T1)비율은 -6.4%를 기록.</t>
+          <t>3Q26 Preview: 4 분기 턴어라운드 가능성 확인 KT 3Q26 실적은 영업수익 7.0 조원(-1.8% 이하 YoY), 영업이익 5,146 억원(-4.4%, OPM: 7.4%)으로 예상한다.7월까지 지속된 고객보답 프로그램 영향으로 무선 매출이 감소(-3.1%)하면서 영업이익 컨센서스(5,396 억원)를 소폭 하회할 것으로 예상한다. 다만 무선 매출은 2분기를 저점으로 QoQ 상승기조가 3분기와 4분기까지 이어질 전망이다. 이와 함께 클라우드, 에스테이트의 견조한 그룹사 매출, 인건비, 감가상각비 등 주요 비용 안정화를 통해4분기 영업이익은 3,536억원(+55.6%)으로 턴어라운드를 예상한다.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_한화투자증권_신한지주_롯데손해보험 인수, 기대와 우려가 동반.pdf</t>
+          <t>2026-10-15_SK증권_KT_4분기 턴어라운드 가능성이 확인될 3분기 실적.pdf</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27,326십억원</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9.6십억원</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28,003십억원</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>540십억원</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -20122,21 +19345,21 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>iM증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한화손해보험</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>낮은 눈높이, 26.4Q에 거는 기대</t>
+          <t>3Q26 Pre - 보험손익 개선세에 주목</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -20151,32 +19374,32 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>[투자포인트] ■ 26.3Q 매출액 45.3조원 (-2.7% YoY) , 영업이익 2.4조원 ( -2.8% YoY, +5.4% OPM) 전망. 1) 26.3Q 글로벌 도매 판매 91.8만대 (-11.5% YoY)를 기록. 2) 26.3Q 원/달러 평균 환율은 1,420원으로 직전 분기 대비 80원 하락했으나, 원/달러 기말 환율이 동시에 1,352원으로 직전 분기 대비 197원 하락하며 부정적 환율효과 일정부분 상쇄할 것.</t>
+          <t>2026년 3분기 실적은 컨센서스 소폭 하회 전망 3분기 별도 당기순이익은 903억원으로 컨센서스(939억원)를 소폭 하회할 것으로 전망한다. 증시 부진 및 금리 상승에 따른 투자손익 악화가 예상되나, 보험손익은 전반적으로 개선될 전망이다. [보험손익] 보험손익은 1,377억원(YoY +44.5%, QoQ +35.2%)으로 추정한다.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_iM증권_현대차_낮은 눈높이, 26.4Q에 거는 기대.pdf</t>
+          <t>2026-10-15_하나증권_한화손해보험_3Q26 Pre - 보험손익 개선세에 주목.pdf</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>188,434십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>12,744십억원</t>
+          <t>465십억원</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>194,151십억원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>14,461십억원</t>
+          <t>595십억원</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -20192,21 +19415,21 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>교보증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>3Q26 Preview: 실적도, 성장 동력도 풍부</t>
+          <t>흔들거리는 실적보다 신사업 성장에 초점</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -20221,37 +19444,37 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>3Q26 시장 기대치 부합 전망 하이브 3Q26 매출액 1조 4,630억원(YoY +101.2%), 영업이익 1,655억원(YoY 흑전, OPM 11.3%)으로 영업이익 기준 시장 기대치(FnGuide 기준 1,636억) 부합 전망 [음반/음원] 매출액 2,679억원(YoY +41.1%, QoQ -18.0%) 전망. 3분기 앨범 판매량은 총 915만장 수준(써클차트 기준)으로 추정되며, 엔하이픈(229만장), &amp;TEAM(139만장), 코르티스(181만장) 등이 기여. 전분기 아티스트 앨범 발매가 집중된 데 따른 기저 부담으로 매출액은 QoQ 감소할 전망 [공연] 매출액 7,244억원(YoY +195.7%, QoQ +11.8%) 전망.</t>
+          <t>WHAT’S THE STORY? 투자 의견 - 실적 변동성은 커졌으나 명확해지는 신사업: 3Q 실적은 기대치를 크게 하회했지만, 이를 회사의 펀더멘털 훼손으로 해석할 필요는 없다고 판단한다. 가전의 원재료비와 물류비, 환율, 전장의 매출 인식 시점 등 단기적인 요인들이 이익 변동성을 높였지만, 제품 경쟁력과 매출 성장, 신사업 확장이라는 보다.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_교보증권_하이브_3Q26 Preview 실적도, 성장 동력도 풍부.pdf</t>
+          <t>2026-10-15_삼성증권_LG전자_흔들거리는 실적보다 신사업 성장에 초점.pdf</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>96,361십억원</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>-42.2십억원</t>
+          <t>4,193십억원</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>97,190십억원</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>4.0십억원</t>
+          <t>4,569십억원</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>3Q26 매출액 1조 4,630억원(YoY +101)</t>
+          <t>3Q26 영업이익은 7,818억원으로 당사 추정치 하회</t>
         </is>
       </c>
     </row>
@@ -20262,7 +19485,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -20271,12 +19494,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>실적은 시장 기대 부합 했으나…</t>
+          <t>일회성 비용으로 단기 실적 부진 전망</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -20291,37 +19514,37 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>7~9월 Re: 시장 기대 부합 7~9월 누계 매출액 및 영업이익은 각각 9,203억원(YoY 10.8%), 1,519억원(YoY 6.7%)을 기록했다. 시장 기대에 부합하는 수치이다. 3Q 국가별 매출 성장률은 각각 국내 YoY 4.9%/ 중국 YoY 13.8%/ 베트남 8.3%/ 러시아 21.9%를 시현했다.</t>
+          <t>3분기 실적은 시장 기대치를 하회할 전망이다. 사업 부문 대부분 양호한 실적을 기록할 것으로 예상되는 가운데 일회성 비용으로 인해 실적은 단기 부진이 예상된다. SK인텔릭스 마진 하락 가능성은 아쉬운 지점이나 정보통신 실적 성장이 만회할 것으로 기대된다.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15_하나증권_오리온_실적은 시장 기대 부합 했으나….pdf</t>
+          <t>2026-10-15_하나증권_SK네트웍스_일회성 비용으로 단기 실적 부진 전망.pdf</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>3,719.3십억원</t>
+          <t>7,042.6십억원</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>629.0십억원</t>
+          <t>95.5십억원</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>3,830.7십억원</t>
+          <t>6,783.5십억원</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>677.1십억원</t>
+          <t>126.3십억원</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>연결 매출액 및 영업이익을 각각 9,751억원(YoY 5)</t>
+          <t>3Q26 영업이익 115억원(YoY -48)</t>
         </is>
       </c>
     </row>
@@ -21140,12 +20363,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>🛑 손절 기준 터치</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -21155,7 +20378,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2일차</t>
+          <t>2일 경과</t>
         </is>
       </c>
     </row>
@@ -21202,12 +20425,12 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>🛑 손절 기준 터치</t>
+          <t>⏳ 목표가 추적 중</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -21217,7 +20440,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2일차</t>
+          <t>2일 경과</t>
         </is>
       </c>
     </row>
@@ -21269,7 +20492,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -21331,7 +20554,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -21393,7 +20616,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -21517,12 +20740,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>50,800원</t>
+          <t>51,100원</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -21678,22 +20901,22 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>$221.30 (약 297,112원)</t>
+          <t>$221.30 (약 298,219원)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>$217.98 (약 292,656원)</t>
+          <t>$217.98 (약 293,746원)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>$254.50 (약 341,679원)</t>
+          <t>$254.50 (약 342,952원)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>$206.33</t>
+          <t>$206.61</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -21737,7 +20960,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="53" customWidth="1" min="9" max="9"/>
   </cols>
@@ -22173,42 +21396,42 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>💎 자사주 소각 (주주환원 극대화)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
+          <t>자사주 소각</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>에스원</t>
+          <t>우리엔터프라이즈</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>에스원, 4500억원 규모 자사주 취득 결정에 강세</t>
+          <t>[공시 Pick] 우리엔터프라이즈, 자사주 소각 결정에 4%대 강세</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>발행주식 총수 감소로 주당순이익(EPS) 및 주주가치 대폭 상승</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>뉴스투데이</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Thu, 15 Oct 2026 00:14:55 GMT</t>
+          <t>Thu, 08 Oct 2026 05:30:00 GMT</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9LdkxXYlFGMTFTSlZhbk1vVDY3akpjQzZIU1hoRk9TNzRTVEV1ZTRPcWxVWjlNdkF6ZV9fZFl6QjVtSUgyY1NwWUVlM19OMDc2Ym02S1owdzFCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE14M0w3V29ISXQ5ekU1bm5keHRscHJlUW9weFNCakZpcHhUeWd3Mk1JbERILWZndFVjaHA5dm5jdWVWYm1qbER5a1VvRElKMEJHdTQtRjRQVVlLSWRhVnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -22220,42 +21443,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>💎 자사주 소각 (주주환원 극대화)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
+          <t>자사주 소각</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>SK가스</t>
+          <t>영화금속</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>[공시분석]SK가스, 3년간 900억 자사주 매입·소각…'기업가치 제고' 주주환원 승부수</t>
+          <t>영화금속, 19만주 자사주 소각…주주가치 제고 목적</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>발행주식 총수 감소로 주당순이익(EPS) 및 주주가치 대폭 상승</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>알파경제</t>
+          <t>주주경제신문</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Wed, 14 Oct 2026 06:30:00 GMT</t>
+          <t>Mon, 28 Sep 2026 06:28:53 GMT</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB3Sm5OQVhMODZ0YnlMUC04Tmw4bmt0em1oUEE3YTBjcFBPOWFkZVh3UHloUC1YSGxnVjJQcHgzQ3lSVW11NEVmQmd2X1NQTk4ydzNwTjNRaFRKbGN6UWRDR2ZBRkk4d2wtbk5HU3FB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5FLTljYU1JeEhxdnc4THhLb1A1YzVwQVQ0ZF9ySjFkU2JIRS04bHpTdkFwT25oY2dJRDloQXN2VElrallJQjF4TTR1RHZsQ3JnZllnQlR1OG5JNlgzeXdSM0J0M1dNaDMy?oc=5</t>
         </is>
       </c>
     </row>
@@ -22267,42 +21490,42 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>💎 자사주 소각 (주주환원 극대화)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
+          <t>자사주 소각</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>스틱인베스트먼트</t>
+          <t>LG생활건강</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>[공시 Pick] 스틱인베스트먼트, 41억원 자사주 취득에 강세…장중 4%↑</t>
+          <t>[주주경영 보고서] LG생활건강, 분기배당자사주 소각 ‘착착’</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>발행주식 총수 감소로 주당순이익(EPS) 및 주주가치 대폭 상승</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>뉴스투데이</t>
+          <t>주주경제신문</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:20:00 GMT</t>
+          <t>Tue, 16 Dec 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE41b0xlNUs4c2FxVTNMaENRVHJFM1prZDE0dWw0dy1CY1VYOVN3LVV4REtOUDJhTTFhU2lCS1RMcDlQeU8tVG8xSXVSbURwRW9oOHNaelhKdktwRjhmSWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9jN1l3WVEyRmJObDdhazlMRm0wZ3hBM19nd0x6U0F2bkMtYnVzc05fYzh4eWVtaWpkNUpOV3lsZ0t6V1FKeGlGZzB0enEzYXJ0QlhxMDluSldSVGN1bnQ5QldXM1pYUHlf?oc=5</t>
         </is>
       </c>
     </row>
@@ -22324,12 +21547,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>엘컴텍</t>
+          <t>애니플러스</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>엘컴텍, 20억원 규모 자사주 취득 결정</t>
+          <t>애니플러스, 20억원 규모 자사주 취득 공시</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -22339,17 +21562,17 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>전자신문</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 07:22:52 GMT</t>
+          <t>Tue, 29 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE13UXpQT2FyUjBQSkpSdFNtQVpJOHFGMExaeDFtajBra1h5dHl5S2dMbUV5TUdmMzFYZkF6b1RmSTd0TVk1NUZCOGN1Y1pWS3d1Rk50WmRUS19XZkJISzdJX3k1YXpPU2V3X3FhNkloOWs1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5pUEJfS3dXeldZeDBXUVVBQkVzOWJYcFdPbTd0UzNTNnAzZkMwTV9pY1VXUjQ5MjJmaGRnakpFN1NXOThDekFjY1BSUi0tdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -22371,12 +21594,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>칩스앤미디어</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니, 50억원 규모 자사주 취득 신탁계약 해지 결정</t>
+          <t>[공시 Pick] 칩스앤미디어, 100억 자사주 취득 소식에 주가 강세</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -22386,17 +21609,17 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>데이터투자</t>
+          <t>뉴스투데이</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:43:38 GMT</t>
+          <t>Mon, 28 Sep 2026 06:44:00 GMT</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1MVmRGS1NqcEJobXNpM01fNTlJbV9MeFZUeXBTVktGWV9XOWFlMHFET09BeW1rQ1RJdzVCR0I1OXM1UkpxM3Nnazk4RnBPbC1EaGFxM0FpVVpqYzZPRnlGb0plTEwyYmZDSXJXNW8yYmh5M0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBIdC1XZFZ0S3Y1VXRhMklyLU9EVnUyT0FzaGRiZHluXzNSVWRNOS1saEZ6UnRVMkd0Njd5a3FUeHAzMl9BaHE0OC1yMkhHMTBncXVYQW1mQm5paVNLSGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -22408,27 +21631,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>💎 자사주 취득 (주가 부양)</t>
+          <t>📈 대규모 단일판매·공급계약</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>자사주 취득</t>
+          <t>대규모 수주</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>메디앙스</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>메디앙스, 10억원 규모 자사주 취득 결정</t>
+          <t>우리로, 227억원 규모 데이터센터용 광반도체 공급계약</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>기업 자금 투입으로 유통 물량 흡수 및 강력한 주가 바닥 지지 신호</t>
+          <t>매출액 직결 확정 계약으로 향후 분기 실적 퀀텀점프 기대</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -22438,12 +21661,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 05:39:56 GMT</t>
+          <t>Thu, 15 Oct 2026 06:39:29 GMT</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1TRmxBdndpdk9HTXZRTzdxNF8wSWpxQklLcDBRQks1TmxUSm4xRU9zVzRCSkxLZ3RUYy1JbS1vZXhhSnRxMXRJZnNGVHJLdkwyZzNTZTlLUWlCb0xkQUpnSWtnVURLcExLaGtWOTFMcnV6cGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5PU2I1Z3FJaERnZzc3MTlRWTlHS0V4WV9jbWFyUEpjSF81Njl2T0RyS0Y4YW9ZbXBGY1FmazNIeTdxQmp4c3Z0TWpmdzJCdWpBYkgxOFJRaThxVTlQVmxIaUVHR2RKQWh6em5LMzlTQlMtMUk?oc=5</t>
         </is>
       </c>
     </row>
@@ -22455,42 +21678,42 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>🏛️ 대주주/임원 장내매수 (책임경영)</t>
+          <t>📈 대규모 단일판매·공급계약</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>내부자 매수</t>
+          <t>대규모 수주</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>회장</t>
+          <t>태영건설</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>원종석 신영증권 회장, 5거래일간 자사주 30억 장내 매수</t>
+          <t>[2020년 6월]태영건설, 한국도로공사와 847억원 규모 공급계약</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>내부 사정을 가장 잘 아는 경영진의 직접 매수로 기업가치 저평가 방증</t>
+          <t>매출액 직결 확정 계약으로 향후 분기 실적 퀀텀점프 기대</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>더팩트</t>
+          <t>데이터투자</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Thu, 11 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 14 Oct 2026 12:08:23 GMT</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tYTBhV0h3WkQzbG5SbklZMW16enV2UWxnZHlkYzFjYmhYaVNQclkyYWxQM1VDTjdWYVhuMHNXRklUMGsyT2F0ck5EZkhSWGlUX2I2MmxjUENKUdIBVEFVX3lxTE1RcVhPeC1tU2FoTThuWHFyMnJFa2VSRm91eUs3dFQ5YmU2Y25BVzF2cHFycEN5UmYxTDdxWGZBM2p4ZVFFX1NwblFIMWU5cGEtcGxqZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5KbEVGd3dvWUVGMFc1a0lRQlAxLWV2UGlkX3ZTV3dnbWJUczZvZV96YV9haWhPTzZyTlJhRW5EdHpHdS00cU9kZVdpVG1WZTZ0enlmbG1GY3N4RHdVckF2Vm1hR1JuOG05MWh1b21hUUlfT1U?oc=5</t>
         </is>
       </c>
     </row>
@@ -22512,12 +21735,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>[공시] 파두, 227억원 기업용 SSD 컨트롤러 공급계약 체결</t>
+          <t>[공시 Pick] LS머트리얼즈, 美 연료전지용 UC 공급계약에 주가 강세…증시 급락 속 ‘역주행’</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -22527,17 +21750,17 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>글로벌이코노믹</t>
+          <t>뉴스투데이</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Thu, 15 Oct 2026 01:32:10 GMT</t>
+          <t>Tue, 13 Oct 2026 01:48:00 GMT</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVHRxZDBxdjIxTkw2a1FtdmtGclJEMHJvc0dSeGtMT2NDRlhMM1FwVWc2eUtLdnE4V0t0R3JxM2JFRmxXc0ppRVJxSDZzYndNTlZpTjJMMjBMWUd5M0lJN0M4c3ZGZnNDZXEzMmhjalZyeE9KYjBZQkVXcWFYLVA4SEcteDQ0QThr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQTWoxNDVLVWtBTXVoS3MtWmFpd1UwMG9FYkVLM0EtcWhTbThJZFVkOWdVekxQMEpNR2ZMTklDQTZHdWpZU3BJSkJpTUQ2TnNVcW8weHFGM1pEVnBqNlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -22773,7 +21996,7 @@
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
@@ -23003,32 +22226,32 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>🌐 [경제·사회 심층 리포트] 트럼프 ICC 제재는 불법 간섭의 숨겨진 배경과 구조적 쟁점</t>
+          <t>🌐 [경제·사회 심층 리포트] 노벨평화상의 숨겨진 배경과 구조적 쟁점</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>트럼프 ICC 제재는 불법 간섭</t>
+          <t>노벨평화상</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '트럼프 ICC 제재는 불법 간섭' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
+          <t>단순 뉴스 헤드라인을 넘어선 전후 맥락: '노벨평화상' 이슈가 촉발된 진짜 배경과 이해관계자들의 득실 계산을 분석합니다.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭"]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 노벨평화상 필라이 "트럼프 ICC 제재는 불법 간섭".&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
+          <t>오늘 주요 언론을 통해 집중 조명된 핵심 사안은 바로 **[노벨평화상 필라이, 트럼프 ICC 제재 비판]** 입니다.&lt;br&gt;• &lt;b&gt;핵심 현황:&lt;/b&gt; 노벨평화상 필라이, 트럼프 ICC 제재 비판.&lt;br&gt;• &lt;b&gt;왜 중요한가:&lt;/b&gt; 단순한 단발성 소식이 아니라 정부 정책, 규제 환경, 기업들의 실질적 손익과 직결되어 시장 전반에 큰 파장을 일으키고 있기 때문입니다.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>이 사안은 과거 수년간 시장과 정책 당국 간에 누적되어 온 구조적 과제가 수면 위로 표출된 결과입니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; 글로벌 공급망 재편과 정책 기조의 전환이 이어지며 시장의 압력이 누적되어 왔습니다.&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 최근의 제도적 변화와 주요 이해관계자들의 입장 차이가 정면으로 맞닥뜨리면서 본격적인 쟁점으로 급부상했습니다.</t>
+          <t>이 문제는 오늘 갑자기 발생한 사안이 아니라, 과거부터 축적되어 온 구조적 원인이 있습니다.&lt;br&gt;• &lt;b&gt;과거 배경:&lt;/b&gt; 미하일 고르바초프 노벨 평화상 수상 뉴스1. 트럼프, 노벨평화상에 집착하는 이유는 천국 가기 위해?&lt;br&gt;• &lt;b&gt;결정적 계기:&lt;/b&gt; 잠재되어 있던 제도적 갈등과 시장 환경의 변화가 맞물리면서, 이번 계기를 통해 본격적으로 수면 위로 표출되었습니다.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>언론 헤드라인 이면에는 각 주체들의 치열한 손익 계산이 숨겨져 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 정책 당국은 거시적 안정과 공공성을 명분으로 내세우고 있으나, 산업계는 규제 비용과 수익성 방어에 비상이 걸렸습니다.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 결국 누가 비용을 부담하고 누가 장기적인 주도권을 쥐느냐를 둘러싼 치열한 헤게모니 싸움으로 해석할 수 있습니다.</t>
+          <t>겉으로 보이는 명분 뒤에는 각 주체들의 아주 명확한 '실질적 손익 계산'이 숨어 있습니다.&lt;br&gt;• &lt;b&gt;이해관계 분석:&lt;/b&gt; 노벨평화상 파장 확산…美, ICC 제재 vs 수상자 "전례 없다" 반발 - 머니투데이 머니투데이. 나비 필레이 노벨평화상, 인권과 국제정의의 시대적 과제 조명 데일리연합.&lt;br&gt;• &lt;b&gt;핵심 구조:&lt;/b&gt; 규제 당국은 시장 통제력과 정책 주도권을 강화하려 하고, 관련 기업들은 비용 부담을 줄이고 수익성을 지키기 위해 치열한 수싸움을 벌이고 있는 구도입니다.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -23043,12 +22266,12 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9ZcTM4YlJJUTFoUXZ5ZGZydnpQUnVFSGtHeHhOQWo0VUU3Wm9oc2VQMlFvM2c4SnVwVFRfNHh5NThkWERpQ3NZLWZRaXZvMG9aRE5PLUNxWXVJUjVaUDE4c3FfREhTczA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB1eURfdmF4ZTVVbE8wVzVKVkItdHhSWERSWkhpN2ppYWJDUVNreVJVLTAxREJTVlB5bmRWdHQ4ZThYckxhbWpPbW4ySDZvbnNEZlcwdjYybDZuVTdKUDk1MHFfa1haLURUVHRaRDhyRFdBOUl30gF0QVVfeXFMT0lwcEtUT3ptY3FZLXdIZVd6MWdiMUlVanZxbmgzTUI4NHZfSlFreElCWG85VUhzNE9tQmdRMTNza05za0pnTXdPbXlqNUJwTXhleHJQZ1VLTDVSTnRmYmJmd3o1RE9TYjBJLVdDaEVTZTRTMU0?oc=5</t>
         </is>
       </c>
     </row>
@@ -23070,32 +22293,32 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>🔥 [트렌드 &amp; 소비 인사이트] “오픈 열풍의 배경과 소비 심리 분석</t>
+          <t>🔥 [트렌드 &amp; 소비 인사이트] 지그재그 열풍의 배경과 소비 심리 분석</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>“오픈</t>
+          <t>지그재그</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>요즘 왜 난리일까? '“오픈' 품절 대란과 오픈런 이면에 숨은 소비 심리와 바이럴 구조를 짚어봅니다.</t>
+          <t>요즘 왜 난리일까? '지그재그' 품절 대란과 오픈런 이면에 숨은 소비 심리와 바이럴 구조를 짚어봅니다.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>지금 거리와 SNS에서 소비자들이 가장 열광하고 있는 화제의 중심은 단연 **[“오픈 1시간 만에 품절”…젠틀몬스터×프라다, 한국서도 완판]** 입니다.&lt;br&gt;• &lt;b&gt;트렌드 현황:&lt;/b&gt; “오픈 1시간 만에 품절”…젠틀몬스터×프라다, 한국서도 완판 스타패션.&lt;br&gt;• &lt;b&gt;열풍의 온도:&lt;/b&gt; 매장 문이 열리기 전부터 줄을 서는 '오픈런'과 온라인 품절 사태가 잇따르며, 단순한 유행을 넘어 하나의 강력한 문화적 현상으로 자리 잡았습니다.</t>
+          <t>지금 거리와 SNS에서 소비자들이 가장 열광하고 있는 화제의 중심은 단연 **[지그재그, 16일부터 성수동서 팝업스토어…쇼핑몰 50곳 참여]** 입니다.&lt;br&gt;• &lt;b&gt;트렌드 현황:&lt;/b&gt; 지그재그, 16일부터 성수동서 팝업스토어…쇼핑몰 50곳 참여 연합뉴스.&lt;br&gt;• &lt;b&gt;열풍의 온도:&lt;/b&gt; 매장 문이 열리기 전부터 줄을 서는 '오픈런'과 온라인 품절 사태가 잇따르며, 단순한 유행을 넘어 하나의 강력한 문화적 현상으로 자리 잡았습니다.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 분당서울대병원, 23년 발자취 담은 역사홍보관 ‘스페이스 이음’ 오픈 후생신보. 30년 SK텔레콤오픈 역사 속으로...기업 후원 생태계 흔들리나 더팩트.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
+          <t>이 유행은 과연 어디서부터 시작되었을까요? 시작점을 추적해 보면 아주 흥미로운 바이럴 계기가 있습니다.&lt;br&gt;• &lt;b&gt;시작 비화:&lt;/b&gt; 무신사 vs 지그재그 '디스전' 벌이더니…둘 다. 무신사·지그재그, 대놓고 붙었다…패션 플랫폼 디스전의 탄생 한국섬유신문.&lt;br&gt;• &lt;b&gt;확산 과정:&lt;/b&gt; 초기에는 특정 매니아층 사이의 호기심으로 시작되었으나, 틱톡·릴스 등 숏폼 영상 알고리즘을 타며 '나도 경험해봐야 한다'는 대중적 열풍으로 급격히 번져나갔습니다.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>소비자들이 기꺼이 시간과 비용을 들여 줄을 서는 심리적 이유를 쉽게 풀어보았습니다.&lt;br&gt;• &lt;b&gt;소비 심리:&lt;/b&gt; AI 안전협약 속 ‘오픈모델 규제’ 부상… 책임 기준 새 쟁점 이코노미톡뉴스. “서버는 해킹·회의실은 도청 위협” 오픈AI 사건 파장, 기업 내부 통제 시험대 The Economy Korea.&lt;br&gt;• &lt;b&gt;심리적 기제:&lt;/b&gt; 단순히 제품의 기능 때문이 아니라, '희소한 트렌드를 남들보다 빠르게 경험하고 인증했다'는 심리적 만족감과 소속감(디토 소비 및 포모 심리)이 지갑을 열게 만드는 핵심 동기입니다.</t>
+          <t>소비자들이 기꺼이 시간과 비용을 들여 줄을 서는 심리적 이유를 쉽게 풀어보았습니다.&lt;br&gt;• &lt;b&gt;소비 심리:&lt;/b&gt; 2030 '가을 산행' 인기 전망…지그재그, '등산' 검색량 폭증 뉴스저널리즘. 지그재그, 슈즈 카테고리 상반기 거래액 15% 성장…직진배송 영향도 Daum.&lt;br&gt;• &lt;b&gt;심리적 기제:&lt;/b&gt; 단순히 제품의 기능 때문이 아니라, '희소한 트렌드를 남들보다 빠르게 경험하고 인증했다'는 심리적 만족감과 소속감(디토 소비 및 포모 심리)이 지갑을 열게 만드는 핵심 동기입니다.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -23105,17 +22328,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>📌 **희소성 마케팅(Scarcity Marketing)**: 수량이나 판매 기간을 극도로 제한하여 '지금 구매하지 않으면 품절된다'는 조급함(FOMO)을 자극하고 소장 가치를 극대화하는 소비 심리 기법입니다.</t>
+          <t>📌 **팝업스토어(Pop-up Store)**: 짧은 기간 동안 임시로 운영되는 매장으로, 단순 물건 판매를 넘어 소비자에게 특별한 브랜드 체험과 인증샷을 유도하는 현대 유통의 핵심 집객 전략입니다.</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>스타패션</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1QVnBDX2JJZVBuYTgzek10UThCUTVMWXFCSGVSNVNSOWFja3lLMVVYRWVBYmlzMVlNZ1VSTDBkMXY3RXpDdG52YjlnYmtvM3BUcHR0WlY0WUV4YXJrYXow?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBOMnU4RDJWWmNmSkhLdU5vcmNsak5IWnhLYldoT0lIbE5kZWRLeGw2Y0JKVl9SNzV1X1hnOUJYbWNmYm5tSHU0WnN4QWt5LU51U1VFTVctVlJYOWZpSnlqQ9IBYEFVX3lxTFBOMnU4RDJWWmNmSkhLdU5vcmNsak5IWnhLYldoT0lIbE5kZWRLeGw2Y0JKVl9SNzV1X1hnOUJYbWNmYm5tSHU0WnN4QWt5LU51U1VFTVctVlJYOWZpSnlqQw?oc=5</t>
         </is>
       </c>
     </row>

--- a/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
+++ b/reports/일자별_누적_데일리_이슈_및_주식_브리핑_마스터.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="종합이슈_누적" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="주식추천_누적" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="시장지표_누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="코인추천_누적" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="공식리포트_누적" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="추천성과_검증누적" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="특수공시_누적" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="스토리딥다이브_누적" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="심층리포트_누적" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종합이슈_누적" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주식추천_누적" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시장지표_누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="코인추천_누적" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공식리포트_누적" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추천성과_검증누적" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="특수공시_누적" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스토리딥다이브_누적" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심층리포트_누적" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G295"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -5227,22 +5227,22 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>[속보] 국회 행안위, 김지용 중수청장 후보자 청문보고서 채택</t>
+          <t>참여연대, 중수·공소청장 국무회의 참석 지시 李대통령에 "공정성 훼손"</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>국회 행안위, 김지용 중수청장 후보자 청문보고서 채택.</t>
+          <t>참여연대, 중수·공소청장 국무회의 참석 지시 李대통령에 "공정성 훼손".</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFB6TFpTSkJPRU52d3hWWEFBcERxdlppUVZ5NlR1QkFlY203S1lvNDhyU3JRV3RWRWt1MS1USWNPUlpvZ3pWVlV0RnJrbXdLTVN5cHp1VjZ5dGlod21HaXZJclJybGRFMUhva0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPbkk3VEdkMk5CakQwZUU5eG0yMmVwVTNTVFlpb1VfTnczWjYtcElZV0pRNVdFd09nS3RlZ2VvNjBpMy1feFV6b2tTMkUxSHppNXNxa2l3aC1za1hZRHV6UVlpQmdsMi1wZGRLeHpwWVpPai04aDVVTHBvUFJDSHRWZXBuOHBndThZUWtVZGM1cXQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5259,27 +5259,27 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 손 들어 준 법제처장‥"대법원장 재제청, 헌법상 책무"</t>
+          <t>강신철, '브런슨 발언 항의해야' 지적에 "그 부분 이미 전달"</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 손 들어 준 법제처장‥"대법원장 재제청, 헌법상 책무".</t>
+          <t>)= 강신철 국방부 장관은 15일 전시작전통제권 전환 조건이 바뀌고 있다는 제이비어 브런슨 주한미군.</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9UdWtaU2FFS0pWMDA0SFdEdy1pcEE2YndTSUNGS1dtZlNDZThKcGN4S2oxMmI4TVprZHZkWVhJX2d2WFdHdzlWZVNtdG55YlRlYzkwSjVfdHU3Mk5Yb0ZIWHBrTk5uV0xaUGVuMnVEVHNnaVNuWG9hN9IBeEFVX3lxTFBwQTVOUklSd3RGUnBsSGgxMnFMdERMSllVWDBGcGEyYV9XZ3RWTDhRdXdPbmZYVVpuYmlydHl2djQ4dlRjekRTaDJ4TEZtN2hyRl9nWmpybUFYc3FQb3RFVTNXb0t6OUdkcnlDNGgxR2Q4SDRZSDJ5SA?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015157900504</t>
         </is>
       </c>
     </row>
@@ -5301,22 +5301,22 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>[속보] 특검, 대법원에 김건희 추가 구속영장 발부 요청</t>
+          <t>광주 군공항 간 국토장관 "반도체 산단 유례없는 속도로 조성"</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>특검, 대법원에 김건희 추가 구속영장 발부 요청. 아울러 범행 전 휴학계 제출·현금 600만 원 소지한 인천 흉기 난동범···경찰 “도피 의혹” 조사.</t>
+          <t>)= 홍지선 국토교통부 장관이 15일 광주 군공항을 방문해 호남권 반도체 첨단 국가산업단지 조성사업의 추진 상황을.</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE5GZm9PYzdLQnMtcVFxbzl5ZElIUG10eWtmajRaRWhnNUFhQmZCVTVBX24weEl6X0hxVUhzbU0yc3lJZG4yT3JxT2x4Ung2Yng5Y3lkag?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015156100003</t>
         </is>
       </c>
     </row>
@@ -5333,27 +5333,27 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>野, 외교·통일·국방 세종행에 "유사시 서울 포기 메시지 될 수도"</t>
+          <t>김민석 "할 것은 다 한다"…최민희 "정청래 '신천지 낙인' 규명"(종합)</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>野, 외교·통일·국방 세종행에 "유사시 서울 포기 메시지 될 수도". 아울러 주호영 “국방·외교부 세종 이전은 국가 안위 흔드는 자해적 결정”.</t>
+          <t>)= 신천지 교인의 더불어민주당 당원 가입 정황이 당 자체 조사에서 확인됐다는 사실이 알려지면서 여당.</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQWgzeDZDRU1meVJxTTVfXzRIWDl6WHdNYmxNVGlhdEtvSW4yc1F3V0ZPR1k3MDM2LUVraWQtRWxaNHZPOFg0R1JFTkl2Tm5TaGpuckczMmozQmsxbF9qTjJTQk1NS2Rxek04NjZXM0p5YVVqUWUxOE9fallDaXFDeXNyYktyUQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015069251001</t>
         </is>
       </c>
     </row>
@@ -5370,27 +5370,27 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>해리스 "트럼프의 한미훈련 중단·징벌적 관세, 동맹 강화에 역행"</t>
+          <t>동해시, 자매결연 해군 '동해함' 견학…관·군 협력 강화</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>해리스 "트럼프의 한미훈련 중단·징벌적 관세, 동맹 강화에 역행". 아울러 아산기념강좌 참석한 정몽준 아산재단 이사장.</t>
+          <t>)= 강원 동해시는 15일 자매결연 함정인 해군 1함대사령부 소속 '동해함'을 방문해 장병들을 격려하고 상호 협력.</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOUWR5dU9nZnV6eHRMMmVGdDJndEZ5Q1pud0xiM2hwU2JOSkxiU1BwaEg4ZVdxUVVwLWNNQng2ek1SOXR2ZXVWQXREZEZpY29KQnQweC1fd3hzNG9LQlpEN2VrX3E3NUhWa2k1QTVwN3VvenFYWVExeUUyNE40eEZ4bWM1VlJrNHdpWVVNTVZJTlhUZw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015157500062</t>
         </is>
       </c>
     </row>
@@ -5407,17 +5407,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>[영상] 로봇·드론·무인체계 총출동…눈앞 다가온 韓육군의 '미래전투'</t>
+          <t>李대통령 "브라질달걀 소량·시험적 수입…'800억 낭비' 허위사실"</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>) 14일 경기도 양평훈련장에서 육군의 '아미 타이거 플러스' 미래전 통합 전투 수행훈련이 진행됐습니다.</t>
+          <t>)= 이재명 대통령은 정부가 브라질산 달걀을 비싼 값에 들여와 싼값에 팔면서 800억원의 혈세를 낭비했다는 일각의.</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015137000704</t>
+          <t>https://www.yna.co.kr/view/AKR20261015152000001</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>韓총리 "창업열풍, 성장으로 이어져야…지역 창업생태계 만들것"</t>
+          <t>국민의힘 강원 "선거 전후 말 바꾸기…우상호 지사는 해명하라"</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>)= 한성숙 국무총리는 15일 "중요한 것은 창업 열풍이 지역으로 이어져 지역에서 기업의 성장으로 이어지고, 이것이.</t>
+          <t>)= 우상호 강원도지사가 강릉 인공지능 데이터센터 유치 과정에서 변전소 문제를 사전에 파악하지 못한 것이.</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015132600001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015154900062</t>
         </is>
       </c>
     </row>
@@ -5481,17 +5481,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>북한 영변 핵시설 내부 3D로 구현한다…정부, 가상모델 구축</t>
+          <t>靑, '李대통령 지시' 이상동기·관계성 범죄 회의…"단호 대응"</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>)= 정부가 영변 핵시설 내 우라늄 농축시설 내부 공간을 3차원 가상공간으로 구현하는 연구에 착수한다.</t>
+          <t>)= 청와대는 최근 잇따르는 강력범죄 대응을 위해 15일 오후 '관계부처 합동 이상동기·관계성·사회적약자 범죄대책회.</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015128600017</t>
+          <t>https://www.yna.co.kr/view/AKR20261015150600001</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>국방부, 軍수사 지휘·감독 '서면으로' 규칙개정…투명성 강화</t>
+          <t>한일 재무장관, 100억달러 규모 통화스와프 3년 연장 합의</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>)= 국방부가 군 수사기관에 대한 지휘·감독의 투명성을 높이기 위한 규정 개정을 추진한다.</t>
+          <t>)= 한국과 일본이 내달 말 만기 예정이었던 통화스와프 를 3년 연장하기로 했다.</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015115100504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015149500002</t>
         </is>
       </c>
     </row>
@@ -5560,12 +5560,12 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>데이터처장, 국토부·국세청 통계 오류에 "신뢰얻는 노력 지속"</t>
+          <t>"경남 남해안 홍수특보지점 0곳"…국감서 재난문자 차별 지적</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>)= 안형준 국가데이터처장은 15일 국토교통부·국세청 통계 오류에 관한 지적에 "오류를 공개해서 바로 잡고 신뢰를.</t>
+          <t>)= 15일 국회 기후에너지환경노동위원회 국정감사에서 경남 남해안에 홍수특보지점이 없어 재난안전문자 발송 체계.</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015133300002</t>
+          <t>https://www.yna.co.kr/view/AKR20261015151400052</t>
         </is>
       </c>
     </row>
@@ -5587,32 +5587,32 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>2025년까지 옮긴다더니 2031년으로…포항 해병대 사격장 갈등</t>
+          <t>국중박 전시 철거된 '친일파' 유묵‥"유홍준 관장 소장품"</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>)= 경북 포항시 오천읍 주민들이 해병대 1사단의 사격장 이전 지연과 부대 내 배수시설 확충 미이행에 반발해 이틀째.</t>
+          <t>국중박 전시 철거된 '친일파' 유묵‥"유홍준 관장 소장품".</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015126100053</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBnN0ZyS3B3MFAydDlQRm41MXNzZ3Nudmh3QkpDTnN6R1pNSnVxdXYwX3dXTmtXY19xakN6VGhVektQSi1mdTZYajRQUE02aTlkd3VPM3RvdFM0YjQ5MzR2Qy1ia2VBb1d5TU1oZzBwNVVNTml4TWcw0gF3QVVfeXFMTTh3SlltMWc2SlByTkQwVDRWb0xvNms5U3dkanJFYmdhU292VFQtVjNqdzZ3dmc2ck5pOUFtV1NSUzNHWkswdkpYcnFQcGxTNDhTTkVpcVNlQlFpaVJYTjFIOWJPUmN0elZGR1RsVW9yNFVKdzh0UTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5634,22 +5634,22 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>국힘, 이진숙 국정감사 제척안 헌재 가처분·권한쟁의 청구</t>
+          <t>주한미군사령관 “전작권 전환…새로운 기준 부합 군사역량 갖춰야”</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>)= 국민의힘은 국회 과학기술정보방송통신위원회가 이진숙 의원을 방송미디어통신위원회 국정감사에서 제척하는 안을 여권.</t>
+          <t>주한미군사령관 “전작권 전환새로운 기준 부합 군사역량 갖춰야”. 아울러 브런슨, 여권에 일침“평화 없는데 어떻게 평화체제 구축하나”.</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015127000001</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1mTkpWeDdCTFFJenltNFR0ZHVzb2xCWjJpRTV2VXI0VWd5SVRvRzlsbjZXRmpVc1drTV84NmhiS0xNeUxjd3FBckRCb29oR25hQmJKRVF1MzlCY1VDVVd2UmxNQ2ZMR2lfcUxvZkx5Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5661,32 +5661,32 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>캠코 선박금융 2조8천억원 중 90% 수도권 해운사에 지원</t>
+          <t>인천 흉기난동범, 범행 때 현금 600만원 소지…"귀금속 팔아 마련"</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>)= 공적 자산관리 전문기관인 한국자산관리공사 가 시행하는 선박금융 지원이 수도권 소재 해운사에 90% 편중돼.</t>
+          <t>인천 흉기난동범, 범행 때 현금 600만원 소지"귀금속 팔아 마련". 아울러 인천 흉기난동 피의자 '모자이크 없는' 사진 확산경찰 "법적 처벌 주의" - 머니투데이.</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015120500051</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE8xUTUyWlNhbEREVmlaNXFMZ1JXMzVtbUNrSkNvQUVfWkxURzNwUnU0aWl4UTB4ODY5eUxnX2VwMG85REs5elF3VmdvN1FuN3NLRlQ0cWs5b2xCTVJ3WG92czJkQzRGaWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5708,22 +5708,22 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>국힘 충북도당 "민주당 선거앱 공짜 이용 의혹 진실 밝혀라"</t>
+          <t>“1년 넘게 감금·폭행에 강제 혼인”…‘장모 살인’ 피해 유족 분노</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>)= 국민의힘 충북도당은 15일 "이강일 국회의원과 더불어민주당 충북도당은 유료 선거앱 공짜 이용 관련 의혹에 대해.</t>
+          <t>“1년 넘게 감금·폭행에 강제 혼인”‘장모 살인’ 피해 유족 분노. 아울러 '장모 살해·아내 납치' 20대 다음 주 신상공개 심의.</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015125900064</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFB0ZS1qbTV4WXZ4UGZSVDRYUWw2RVVhYWRxa0RFT1V1d1kxWWVVTXBCOEVrM3l0bzdHdTJTZ0Z0UnJpejlGZTAzOVFHVTdMNk5wNnpEWTJvMWlQZjAzeXpUZ0NJRTl4WDhVVmdLem04UGxxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5735,32 +5735,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>구속 만기 앞둔 김건희…특검, 대법에 추가 구속영장 발부 요청</t>
+          <t>이 대통령, '브라질 계란 고가 수입' 주장에 "허위사실 시정 바라"</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>)= 민중기 특별검사팀이 구속 만기를 앞둔 김건희 여사에 대한 추가 구속영장을 발부해달라고 15일 대법원에 요청했다.</t>
+          <t>이 대통령, '브라질 계란 고가 수입' 주장에 "허위사실 시정 바라".</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015125500004</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE93b1JOVGp4c1Q1UkNqOTNkNXQ4SUZDeTJpU05aTldlT19HWEIxYzF3b1JyWmVpSW84X3RWRUVtUzROelQ4dHdrOER6SW1WMWo0TjltZ1NtOV82VnRoVnU2dW1JQWEtcHVKVU5zMmliSnZRcllCZU52dtIBeEFVX3lxTFBDbkJmRWhSaVVGREYyZjF4WllJZ0diZGppZ0Nsa0pzdjEyRElrdU1BS2dnR2hwMEFadFNmZG51V3VIU3B4YkdXSG9tcU1IQjIyZjd4RUJvZnkwY0d0cjhsRDhkLWRzaU5QZVlobTRzQ0xRQlVDb0dlSw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5772,32 +5772,32 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>北, 日핵잠 도입 논의에 "핵무장화 노린 것, 열도에 재앙" 주장</t>
+          <t>이 대통령 “국가경제 전체 성과 국민 삶 속 결실로 이어지도록 해야”</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>도입 가능성이 논의되는 일본을 향해 "핵무장화를 노린 것"이라며 "기필코 열도에.</t>
+          <t>이 대통령 “국가경제 전체 성과 국민 삶 속 결실로 이어지도록 해야”. 아울러 이 대통령 "출범 500일‥국민 실생활 호전에 총력".</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>KBS 뉴스</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015120300504</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9SNnJDQVpxeVpUZUlRcmJSdkJhMlFLa2gtcm1CMVJJVU8tLU55QS1tc2pyNW9Oc0NWX1RDN0tSLW0wdm1nVHdmZzhLNmZzbXQ3QkN2UThicTZjeHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5809,32 +5809,32 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>'퇴임' 강훈식 "李대통령, 탁월·좋은 분…모시는 내내 감탄"</t>
+          <t>“소방관 명예 짓밟았다” 분노…‘재정 빨대’ 발언 추미애 지사 규탄</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>)= 강훈식 전 대통령 비서실장은 15일 퇴임하면서 "책임을 지는 것이 옳다는 생각에는 변함이 없다"고 밝혔다.</t>
+          <t>“소방관 명예 짓밟았다” 분노‘재정 빨대’ 발언 추미애 지사 규탄.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015119500001</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE4zZGRMZVhsVXpvLWZ3UlFHNkRyVTFHS3FpcHBWQkVDZXREdDVkQXhVNFBsN2cwbUpiZ3dfeE9vSEhJMzlHbkVyQ3UtTExZX01WT2tJUno1LTZhc3laWGZBVlR1WQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5846,22 +5846,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>경찰, '당원 가입 관여 의혹' 함안군수실·국힘 도당사 압수수색(종합)</t>
+          <t>울산 북구 CCTV 관제센터, 오토바이 절도 용의자 검거 잇단 지원</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>)= 공무원 신분으로 국민의힘 당원 가입에 관여했다는 의혹을 받는 차석호 경남 함안군수에 대해 경찰이 강제수.</t>
+          <t>)= 울산 북구 CCTV 통합관제센터가 심야 시간대 오토바이 절도 의심 정황을 잇달아서 포착해 경찰의 용의자 검거를.</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015070451052</t>
+          <t>https://www.yna.co.kr/view/AKR20261015154700057</t>
         </is>
       </c>
     </row>
@@ -5883,22 +5883,22 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>李대통령 "부마항쟁과 5·18, 내란극복 큰 의미…헌법에 새겨야"</t>
+          <t>경찰, 가정폭력범 조치 '스토킹 수준' 상향…전자발찌도 추진</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>)= 이재명 대통령은 15일 "5·18는 점에 대해서는.</t>
+          <t>)= 경찰이 가정폭력 가해자에 대한 격리 조치와 접근금지 위반 제재를 스토킹 범죄에 준하는 수준으로 강화하기로 했다.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015118700001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015153200004</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>韓총리 "돌봄은 함께 풀 과제…지역별 인프라 격차 큰 문제"</t>
+          <t>유소년 꿈 키우고 환경 지키고…강원랜드 스포츠 선수들 선행</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>)= 한성숙 국무총리는 15일 "우리는 오랫동안 돌봄을 개인의 희생이나 한 가족의 유대관계에 의존해 왔다.</t>
+          <t>)= 강원랜드가 소속 스포츠 선수들의 재능기부를 통해 지역 유소년 꿈나무를 육성하고, 친환경 가치를 확산하는 사회공.</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015117500001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015155100062</t>
         </is>
       </c>
     </row>
@@ -5957,22 +5957,22 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>李대통령 "출범 500일…주요 지표 우수에도 민생회복 속도 더뎌"</t>
+          <t>'명실상부 창업도시 대전'…총리·주무장관 주재 간담회 잇따라</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>)= 이재명 대통령은 15일 "내일은 우리 국민주권정부가 출범 500일을 맞이하는 날"이라며 "어떤 외풍이나.</t>
+          <t>)= 대전시는 15일 한국전자통신연구원 과 나노종합기술원에서 각각 한성숙 국무총리와 이소영 중소벤처기업부.</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015115400001</t>
+          <t>https://www.yna.co.kr/view/AKR20261015154600063</t>
         </is>
       </c>
     </row>
@@ -5994,22 +5994,22 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>美 항모 입항 부산 해군기지 드론 촬영 중국 유학생 2심도 실형</t>
+          <t>부산 영도 앞바다서 50대 남성 숨져</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>등이 입항한 부산 해군기지를 드론으로 불법 촬영한 혐의로 기소된 중국인 유학생이 항소심에서.</t>
+          <t>)= 15일 오후 2시 9분께 부산 영도구 인근 해상에 사람이 떠 있다는 행인의 신고가 해경에 들어왔다.</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015113300051</t>
+          <t>https://www.yna.co.kr/view/AKR20261015154500051</t>
         </is>
       </c>
     </row>
@@ -6031,22 +6031,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>네팔서 관광비자로 종교 활동하다 체포된 한국인 24명 전원 석방</t>
+          <t>"제주 공영주차장 전기차 충전기 28.5% 고장" 대책 촉구</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>)= 네팔에서 관광비자로 입국했다가 종교 프로그램에 참여해 체포됐던 한국인 24명이 전원 석방됐다.</t>
+          <t>)= 제주도가 관리하는 공영주차장 전기차 충전기가 10대 중 3대꼴로 고장 난 상태여서 대책이 시급하다는 지적이.</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015115600504</t>
+          <t>https://www.yna.co.kr/view/AKR20261015155500056</t>
         </is>
       </c>
     </row>
@@ -6068,22 +6068,22 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>정치</t>
+          <t>사회/사건사고</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>특검, '선거물품 독점 특혜' 부산선관위 등 10곳 추가 압수수색</t>
+          <t>경남 시민단체 "거제남부관광단지 지정 무효 판결 내려야"</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>)= 이태한 선거관리위원회 특별검사팀이 선관위의 선거 물품 보관계약 독점 특혜 정황을 포착하고 강제수사에 나섰다.</t>
+          <t>)= 경남 거제 노자산 일대에서 추진되는 거제남부관광단지 개발에 반대하는 시민사회단체들이 15일 법원에 관광단지.</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015115200004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015155300052</t>
         </is>
       </c>
     </row>
@@ -6115,22 +6115,22 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>[영상] 의자 들고 맨몸으로 흉기난동범 맞선 ‘의인 5명’…필사의 2분</t>
+          <t>장세일 영광군수 "인구 늘린 지역에 인센티브 줘야"</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>의자 들고 맨몸으로 흉기난동범 맞선 ‘의인 5명’필사의 2분. 아울러 범행 전 휴학계 제출·현금 600만 원 소지한 인천 흉기 난동범···경찰 “도피 의혹” 조사.</t>
+          <t>)= 장세일 영광군수는 15일 인구 회복 우수 지역에 인센티브를 줘야 한다고 정부에 건의했다.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE53QWdRZGFSYnRLbWNtUVU4cUtQQkdsY0JJTzQ4UWlGYVBXbzJiYXRDVUxvNXAwd04wZFJ0VTAtYUc2T1pxQnM2T0E4Y05LMnVfa3RjcGk4NmszTzJxVGZHcHpzODRDRV9jeFZ0WVlJNFJ6Zw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015154400054</t>
         </is>
       </c>
     </row>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>강선우 “김병기에 원하는 면접 질문 카톡 말고 텔레로 보내라”</t>
+          <t>부산진해경자청·창원시, 상시 협력체계 가동…첫 현안협력 회의</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>강선우 “김병기에 원하는 면접 질문 카톡 말고 텔레로 보내라”.</t>
+          <t>)= 부산진해경제자유구역청 은 15일 경자청 대회의실에서 '2026년 제1회 경자청-창원시 현안협력.</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1KeXNwYVJ2bkt4VFA2RHNESjdnM3dRLWJTR2ZFcHhKcHFQRk1FSEl4TDdlOW11dUVMOWFQZjhVWkZ0VVBjTkVaYVYzaWFWekJ0M1ViVDM0VlVFX3J4SnNzRjVCaUJrZmNmcDJuOUJBV2U5V0tMMlHSAWZBVV95cUxNZzNBd01sSFBxQ1lWZHlyQWdGQmlqWXROZWcycTMwSFZlNmpDUUpFdEhjNWUyclBocTF6NFpXUmRvVEVzdkFacW5ZYmNpSDhoQnFnSnlnOGpWZk1vX2ZfUFRYSHRJU3c?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015153600052</t>
         </is>
       </c>
     </row>
@@ -6184,27 +6184,27 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 지지율 44% 보합‥민주-국힘 지지율 격차 줄어 [NBS]</t>
+          <t>울산 북구, 주택가·강변도로 건설기계 불법주차 집중단속</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 지지율 44% 보합‥민주-국힘 지지율 격차 줄어.</t>
+          <t>)= 울산 북구는 이달 말까지 건설기계 불법주차를 집중 단속한다고 15일 밝혔다.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1IN0k3azRBQ2RJN1l6cTRndUNaRERUWW0zaHFkOFdLZl9MT2owQ1RTQkg1T3pmNzZzbVFqcWpTVkljSkpmTTFkaWNSRDhuQWlnZVZfbWhRNlZSZ3B6S3N0ZUxQblluMmZfeHQtMWNZR3EtejEzZHpCNdIBeEFVX3lxTE9pd3J6U2YxTF82RFNNMzJ4NVlTU1Z3OWpsdGNFQl9qY09TTW93RDRJdnRSSzU2NFJCSTZZTzNHZ3JkdlZYMUJMSzBSQkJKdUdPd3VIdjFxT0NjWVFaTkx0bTFVRHBMcVZPTkdJdldHT0hkNVRkVVRoYQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015154300057</t>
         </is>
       </c>
     </row>
@@ -6226,22 +6226,22 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>토요일까지 포근, 일요일엔 ‘요란한 가을비’…내주부터 ‘쌀쌀’</t>
+          <t>포항 택시호출앱 '타보소' 생활밀착형으로 진화</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>토요일까지 포근, 일요일엔 ‘요란한 가을비’내주부터 ‘쌀쌀’. 아울러 주말 전국 거센 가을비다음주 최고기온 4도 더 ‘뚝’ 더 쌀쌀해진다.</t>
+          <t>)= 경북 포항시의 공공 택시호출앱 '타보소'가 택시 호출 기능뿐만 아니라 교통·생활·관광정보를 종합 제공하는 생활.</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5QUGp6UHhpM2xnSW1DTlZGTzFGN2szZUN4c3IxNkd4V2xvb3BtZmdaYmo1QlZXUTJpei1GQ0VSY1k0ekVDWlQ5d29FeFczVm1XUnpXNjhoYjMyYnU1em0zNGgwM2RSY2hrVHVWRw?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015153700053</t>
         </is>
       </c>
     </row>
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>[속보] 특검, 중앙선관위 등 각급 선관위 7곳 동시다발 압수수색</t>
+          <t>3천400억원대 스캠코인 사기혐의 '존버킴' 1심 무죄 선고</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>특검, 중앙선관위 등 각급 선관위 7곳 동시다발 압수수색.</t>
+          <t>)= 3천400억원대 '스캠 코인' 시세조종을 주도한 혐의로 재판에 넘겨진 '존버킴' 박모.</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5vMXlDcWZUOXp3QVdtUmF1Qm1yWVl2TTFucUxqMUhtWTFRRmdTRW9rRVVPMTdXa3pBMmtJX2d1bmw5RU40X1Z1VHNGWTJYUERfV0NnOXR6R3lEUQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015151200004</t>
         </is>
       </c>
     </row>
@@ -6290,32 +6290,32 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>브라질산 계란 한판 수입가 4만4000원…올해만 16억 썼다, 왜?</t>
+          <t>증시 대폭락에 금융당국 긴급회의…"비상대응 준비"</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>브라질산 계란 한판 수입가 4만4000원올해만 16억 썼다, 왜? 아울러 이 대통령, '브라질 계란 고가 수입' 주장에 "허위사실 시정 바라".</t>
+          <t>증시 대폭락에 금융당국 긴급회의"비상대응 준비". 아울러 공포의 '검은 목요일'‥코스피·코스닥 7%대 급락 마감.</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1NQU5PN1hvTWF5SzNESnVOeG94Z2dvd2R5RjhEclUtd05ueVpiV1NlYkF6RXBnTUJpd3lrTXZueEFkUnBCQVBtbjhEVjlTRWFLQVdZR1RHSDlRbkNjcWZjdmV3YkszR3VBc0lfZURXUml3N210cHfSAWZBVV95cUxQVERObWpHa25ZdDRCYTN0eHY3SmRYUnNXTDdOcndlNWY4MmhIN3FNSDRjeDZKRDlXSzQwZnZzTW9yamRtX0hrNHhFVDFZdGNRcWdrR0tLeWlIekRTcHFGOVV2c1E2Smc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5haFJJbzRxY1VOZFZFXzU1VERPWXRNREJVQUxTUEJPdk9BWDhub2VwNlc1dkpHTVdRSGxYWUpTT0FZQXhkUlJMRkw0SG9ySTY3a2FqRjRtTDFZMkMzZjROdy1iQTBuZ0Q0WUswRG9BNk4?oc=5</t>
         </is>
       </c>
     </row>
@@ -6327,32 +6327,32 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>국힘 최고위 공개 충돌…양향자 "경선 전면 재선거" 정희용 "당 시스템 무력화"</t>
+          <t>OK저축은행 "해킹 정보유출 고객 250명으로 늘어"</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>국힘 최고위 공개 충돌양향자 "경선 전면 재선거" 정희용 "당 시스템 무력화". 아울러 국민의힘, '용인갑 조직위원장 경선 논란'에 지도부간 내부 충돌 계파 갈등 양상으로.</t>
+          <t>OK저축은행 "해킹 정보유출 고객 250명으로 늘어". 아울러 삭제 안 한 테스트 페이지가 해킹 통로산은캐피탈 101시간 뒤 침해 확인.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVGlLbHpDQkxxcVcydTdBOHYzQ080X1pkazN3RGpQekRtazdpR0tMY0w1VmVIMjlVbWt5UjJYQ1hLazFBOFo3Y3JQM2ltWUcyUzIyZmxWV1JZSVZ2TzFEcmptS1N3SjRTaEc2ZHRPMlp1Tldjamk0cHMwd1pwc0R2b1NnWnFGQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE52WVRJaWNBS211OUUzT0QtSUY1SG9qM0NOQThNVmQxT1F4YlBCRkRsR2pUNVVXRVFDWHRuTVRWR29OUG5adWJFV08wNWxrdWx2Zm84SU5EMHVQLWF1OFZrYjBCSkJCZFFFQ0x4UXRGZkQzQUtw0gF0QVVfeXFMTWJRSFVVYlpWeTlzcGlZMTd1M1JIanhOcWk2c0hDajZ5UVdqNGg1V3FyNVRCcmJpU3BubFpxXzZ3bmpyNk1Nc2hleFZKZENiNDkzZ2QtN1hXRjNybldQeUh1UWdqMW45SnBnZko0VW1SNlpiX2Q?oc=5</t>
         </is>
       </c>
     </row>
@@ -6364,32 +6364,32 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>‘접근·연락 금지’ 스토킹 남편, 아내 살해…경찰은 연락두절에도 안 찾아가</t>
+          <t>이헌욱 "통계 생산에 자의적 개입 안 해…모든 외압 차단"</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>‘접근·연락 금지’ 스토킹 남편, 아내 살해경찰은 연락두절에도 안 찾아가. 아울러 8번 경찰에 신고했지만 결국 남편에게 살해됐다.</t>
+          <t>이헌욱 "통계 생산에 자의적 개입 안 해모든 외압 차단".</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBHVUVPXy1zbEhpZHA5dUJSbV9sdE9XQVFnOGRnUzU1Y3FwRUtvcjI5cThLTDVUM2VUNGxDNVcxZ0V4VXR4LVNnbXBKcTMzcnhCNFd0bFphTVY0THlCR3NQcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1mRm5HUlgxRUNub2dSUVlDSlZna0UwaWN6ZTQ0QW9jeERpelNTRE1VSHRRMGZRR05aVFBUMWEyalZSVkYycC1zTHJha1JRQVRDSWpudjlKeFhRaFk?oc=5</t>
         </is>
       </c>
     </row>
@@ -6401,32 +6401,32 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>[단독] 가정폭력도 전자발찌 채운다…경찰, 법 개정 추진</t>
+          <t>[속보] 한일 재무장관, 100억 달러 규모 통화스와프 연장 합의</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>가정폭력도 전자발찌 채운다경찰, 법 개정 추진. 아울러 보호관찰 처분 연간 10만건 쏟아지는데관찰관 2천명도 안돼.</t>
+          <t>한일 재무장관, 100억 달러 규모 통화스와프 연장 합의 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1LQ2FKSHRLZGl6Nm9sZlBMMWVsZVh4Z1hIRVJaLWFDanZyX184bGpqLU5Oa0dGQVZkLVBqRTUzMkdUWGw5c2ZONkh3TFc1ZW1HQkcxZ2UzZjU5bmhhSWoweDBhY1BKcGs?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015142200002</t>
         </is>
       </c>
     </row>
@@ -6438,32 +6438,32 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 “강력범죄에 전쟁 선포 각오로 특단 대책 조속히” [지금뉴스]</t>
+          <t>[표] 당좌거래정지</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>이 대통령 “강력범죄에 전쟁 선포 각오로 특단 대책 조속히”.</t>
+          <t>당좌거래정지 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA0MlNRb0FPb2VKa3BrRkZyRVc0bldsVU8yZ2FaWnRqc3FXOEFsbE42czF0S0cyN0dVZUJfdHBlRDltRTdiZjhVeXdoXzdNbmU1LVZXcDJhbUlod1E?oc=5</t>
+          <t>https://www.mk.co.kr/news/economy/12176947</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>'창원 택시기사 살인' 재심 개시 결정…아크말씨 형집행정지</t>
+          <t>빚투 주춤하자 가계대출 2.2조 뚝</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>)= 17년 전 경남 창원에서 택시기사를 살해한 혐의로 무기징역을 선고받은 우즈베키스탄 국적의 보조로브 아크말(37.</t>
+          <t>금융권 가계대출이 올해 들어 처음으로 감소했다. 증시가 하락하면서 신용대출을 받아 주식에 투자하는 '빚투'가 줄어든 게 원인으로 분석된다. 15일 금융위원회는 지난 9월 말 기준.</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015138500052</t>
+          <t>https://www.mk.co.kr/news/economy/12176943</t>
         </is>
       </c>
     </row>
@@ -6512,22 +6512,22 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>[게시판] 행안부, '사회연대경제 생태계 리더십 국제교류회' 개최</t>
+          <t>[포토] 우리자산신탁, 정비사업 경쟁력 강화</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>행정안전부는 15일 서울 한국고등교육재단에서 SK 사회적가치연구원과 함께 '사회연대경제 생태계 리더십 국제교류회' 세션을 개최했다고 밝혔다.</t>
+          <t>우리자산신탁, 정비사업 경쟁력 강화 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015063300530</t>
+          <t>https://www.mk.co.kr/news/economy/12176945</t>
         </is>
       </c>
     </row>
@@ -6549,22 +6549,22 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>🔥 [언론사 집중 보도 (5개사)]</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>'DMZ 폭발' 李대통령 고발사건 서울중수청 반부패수사국 배당</t>
+          <t>AI 해킹 부정결제 피해땐 '즉시 환불' 추진</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>)= 서부전선 비무장지대 지뢰 폭발 사고와 관련해 일반이적 등 혐의로 고발된 이재명 대통령 사건이 서울지방.</t>
+          <t>금융당국과 전자지급결제대행 업계가 해킹·계정 탈취 등으로 부정결제가 발생했을 때 사업자가 피해액을 먼저 소비자에게 지급하는 '선 구제' 방안을 추진한다.</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015137100004</t>
+          <t>https://www.mk.co.kr/news/economy/12176941</t>
         </is>
       </c>
     </row>
@@ -6586,22 +6586,22 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>울산 야음동 수돗물 공급 차질에 긴급 수도관 공사</t>
+          <t>사옥까지 매각한 신한카드…2년새 네 번째 희망퇴직</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>)= 울산시는 남구 야음동 일대 수돗물 공급 차질과 흐린 물 발생 문제를 해소하기 위해 긴급 수도관 공사를 마쳤다고.</t>
+          <t>국내 신용판매액 1위 카드사인 신한카드가 서울 을지로 본사 사옥을 매각한 데 이어 올해 두 번째 희망퇴직을 실시한다. 2024년 말 이후 2년도 안 돼 네 번째 인력 감축이다.</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015138400057</t>
+          <t>https://www.mk.co.kr/news/economy/12176942</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>"공원등 고장나면 QR코드로 신고" 익산시, 도심공원에 표찰 설치</t>
+          <t>[매부리 라운지] 집주인에 '세뺀다' 미리 안알리면 … 보험 들어도 보증금 못 받을수도</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>)= 전북 익산시는 영등시민공원과 어양공원, 모현공원 등 3개 공원에 '공원등 큐알 코드' 표찰 333개를.</t>
+          <t>전세보증금 반환보증보험에 가입했더라도 집주인에게 계약 종료 의사를 제대로 알리지 않으면 보증금을 돌려받지 못할 수 있어 주의해야 한다.</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015134700055</t>
+          <t>https://www.mk.co.kr/news/economy/12176937</t>
         </is>
       </c>
     </row>
@@ -6660,22 +6660,22 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>서울교육청 "여명학교 건립 예정대로 추진…2028년 착공"</t>
+          <t>[단독] ‘사은품 덫’에 걸린 상조 가입자들…불만 상담접수 1위는 보람상조</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>)= 주민 반발 등으로 북한이탈주민 청소년 대안교육기관인 여명학교의 교사 건립이 지연될 수 있다는 우려에.</t>
+          <t>증가 보람상조, 지난 2002년부터 매년 최다# 상조상품에 가입한 A씨는 가입 당시 납입금을 모두 납부하면 납입금액을 100% 환급받을 수 있다는.</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015135700530</t>
+          <t>https://www.mk.co.kr/news/economy/12176933</t>
         </is>
       </c>
     </row>
@@ -6697,22 +6697,22 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>하동 양보면 야산서 불…1시간 32분 만에 주불 진화</t>
+          <t>용인특례시, 철도기금 1조원 조성…반도체 세수 활용</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>)= 15일 오후 1시 50분께 경남 하동군 양보면 한 야산에서 불이 났다.</t>
+          <t>철도망 반도체 성공에 필수적 내년 하반기부터 단계 적립 이상일 시장 “철도 적기 구축”용인특례시 가 반도체산업 성장에 따른 지방세수 증가분 등을 활용해 2030년까지.</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015137800052</t>
+          <t>https://www.mk.co.kr/news/economy/12176915</t>
         </is>
       </c>
     </row>
@@ -6734,22 +6734,22 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>거시경제/비즈니스</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>경남도, 재선충병 '선제 방제'로…광역방제전략 수립 최종보고회</t>
+          <t>[속보] 한일 재무장관, 100억 달러 규모 통화스와프 연장 합의</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>)= 경남도는 15일 진주시 월아산 숲속의 진주 달음홀에서 '소나무재선충병 광역방제전략 수립.</t>
+          <t>2029년 11월까지 기존 규모 유지 원화·엔화 맡기고 달러 차입 구조 차기 재무장관회의 한국 개최 추진한국과 일본이 100억달러 규모의 통화스와프 계약을 3년 연장한.</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015133200052</t>
+          <t>https://www.mk.co.kr/news/economy/12176914</t>
         </is>
       </c>
     </row>
@@ -6771,32 +6771,32 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (4개사)]</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>서울공소청 불송치심사부에 검사 9명 배치…'사건암장' 통제</t>
+          <t>젤렌스키, 트럼프 압박에도 "러 정유시설 공격 재개…패트리엇 주면 중단"</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>)= 서울중앙지방공소청은 직제 개편에 따라 불송치 사건 및 수사 중지 사건 등을 전담 심사하는 불송치심사 1·2부를.</t>
+          <t>젤렌스키, 트럼프 압박에도 "러 정유시설 공격 재개패트리엇 주면 중단".</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>연합뉴스TV</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015126200004</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9qNkJ5X0hvRmNKMV9DbF8xZnE0QjZib0tuNi10akVwZFN1c1Jta19ZVHVHTWpZRjlremp3Z1ZVTnhSSzlEZW01UEZlX21vV05WVDk4WEY0NFcyQXdQR2huU3hfNnFack0?oc=5</t>
         </is>
       </c>
     </row>
@@ -6808,32 +6808,32 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>폐철도 터널을 스마트팜으로…보령시-건설기술연구원 협약</t>
+          <t>호르무즈서 컨테이너선 침몰…이란 공격에 원유 수송 다시 위축</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>)= 폐철도 터널을 지능형 농장 으로 활용하기 위한 실증사업이 충남 보령에서 진행된다.</t>
+          <t>호르무즈서 컨테이너선 침몰이란 공격에 원유 수송 다시 위축. 아울러 다시 불붙는 호르무즈, 국제 유가 고공행진.</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>파이낸셜뉴스</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015133900063</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5zeDl4S2lQaW5LV3JTQkVIMXFmcGx5NmEtYVBuNm8zVm8yZ3BINDZwLXhQQjk1WDFJRmhrTExxcjZtT0g1Sm8zYXczRDJhWjdhNzUxQlg5REQ1UQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6845,32 +6845,32 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>이철우, 주한 이탈리아 대사와 관광·음식 교류 확대 논의</t>
+          <t>노벨평화상 필라이 “네타냐후, ICC 법정에 설 거라 확신”</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>)= 이철우 경북도지사는 15일 도청을 방문한 에밀리아 가토 주한 이탈리아 대사와 문화, 관광, 음식 분야 교류.</t>
+          <t>노벨평화상 필라이 “네타냐후, ICC 법정에 설 거라 확신”.</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015135000053</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOQ1duOFB6c3pEYU5ObkRabnl0M1phbGdMblRFbEduaDJGQm14S3dSVi1GYkVQSjFhbjhqOGhiM1lTV3RUZHUwRGJvOUhZQ2VCZEE2eW1vN2c2c3dTQUlsMVBNMU5GSThvUk5xN2MyZ1dBTGlLUzBlek5zalZVVmVjeHBB?oc=5</t>
         </is>
       </c>
     </row>
@@ -6882,32 +6882,32 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>경남 공무원노조 "지자체 보조사업 공무원에 떠넘기지 말라"</t>
+          <t>다카이치, 러 체포 기자 간첩 혐의 반박…"국민보호에 총력"</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>)= 전국공무원노조 경남지부는 15회견을 열고 "다수 시·군에서 체육·문화행사 등.</t>
+          <t>다카이치, 러 체포 기자 간첩 혐의 반박"국민보호에 총력".</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015129400052</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5NT3d1ME9OcHc2aHA2WTg1TEdMWHpVUXVhdmZyRmFfN053dWNiRFpzYnhVR2ZINUllZWxiYXJuRWtJc0xCX0wyZG5vaXVIbXROZ29pTENramZoQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6919,32 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>화천군, 강풍 속 산불·문화재 화재 복합재난 대응 30일 훈련</t>
+          <t>“나 지지 안 했으니 예산 깎는다”…다카이치 측근 장관 결국 사퇴</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>)= 강원 화천군이 강풍 속 산불과 문화재 화재 등 복합재난에 대비한 실전 대응훈련을 실시한다.</t>
+          <t>“나 지지 안 했으니 예산 깎는다”다카이치 측근 장관 결국 사퇴. 아울러 예산삭감 발언 논란 일 농림상 사임다카이치 내각 출범 후 처음.</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>서울신문</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015135200062</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1HLWJ3VFBjSUVhNVVJRmZEYkk1TGNFU2laN1VGMjJrMjB4eE5rb1lubk9EaVJVeVgtNjJIaEd4dHlZQ011Nl9tVmI4eDBnS3Y5OVRVV3F0RmRMRFBBeVJoZFZDS0lPQng2SUljNnNBYWdZbzBEZVR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6956,22 +6956,22 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>한강버스 리베이트 공방…"최상층에 오시장" vs "과장된 의혹"(종합)</t>
+          <t>IMF "중동 산유국, 전쟁 후유증에 당분간 성장세 회복 어려워"</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>)= 15일 국회 행정안전위원회가 서울시를 대상으로 한 국정감사에서 한강버스 리베이트 의혹으로 공방이 벌어졌.</t>
+          <t>) 김상훈 특파원 = 국제통화기금 은 이란에서 시작돼 사우디아라비아와 예멘 등으로 번진 중동 전쟁 여파로, 이 지역 산유.</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015090351004</t>
+          <t>https://www.yna.co.kr/view/AKR20261015155400079</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>강원 직업계고, 1학과 1심화동아리로 전공 역량 키운다</t>
+          <t>[영상] '이륙 30분' 선반 뒤진 중국인…여객기서 잠든 승객 카드 노렸다</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>)= 강원특별자치도교육청은 직업계고 학생들의 전공 실무역량과 취업 경쟁력을 높이고, 적성과 소질에 맞는 진로를 주도.</t>
+          <t>) 지난 12일 태국 방콕 돈므앙 국제공항에서 한 중국인이 여객기 안에서 잠든 승객의 신용카드를 훔친 혐의로 체포됐습니다.</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015128200062</t>
+          <t>https://www.yna.co.kr/view/AKR20261015155000704</t>
         </is>
       </c>
     </row>
@@ -7030,22 +7030,22 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>진짜인 줄 알았는데 가짜…사업자 사칭 사이트 71건 적발</t>
+          <t>中업체, 'ASML에 도전' EUV 광원 시제품 공개…"국산화율 90%"</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>)= 방송미디어통신심의위원회는 다른 사업자의 정보를 도용해 공식 사이트인 것처럼 위장한 사칭 사이트에 대해 올해.</t>
+          <t>) 차병섭 특파원 = 미국의 첨단반도체 제조장비 수출 제한에 맞서 중국이 기술 자립을 강조하는 상황과 관련, 한 중국업체가 자체.</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015126400017</t>
+          <t>https://www.yna.co.kr/view/AKR20261015152600089</t>
         </is>
       </c>
     </row>
@@ -7067,22 +7067,22 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>세계/국제</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>신규 이슈</t>
+          <t>🔥 [언론사 집중 보도 (3개사)]</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>[철원소식] 김일남 문화관광해설사, 도 경진대회서 대상</t>
+          <t>이스탄불 41년만의 물폭탄…2명 사망·침수 피해 속출</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>) ▲ 김일남 문화관광해설사, 도 경진대회서 대상 = 강원 철원군은 최근 원주시 오크밸리에서 열린 '2026 강원특별자치도 문화관.</t>
+          <t>) 김동호 특파원 = 튀르키예 최대 도시 이스탄불에 기록적인 폭우가 쏟아져 사망자가 발생하는 등 피해가 잇따랐다.</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015127500062</t>
+          <t>https://www.yna.co.kr/view/AKR20261015153100108</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>사회/사건사고</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -7114,22 +7114,22 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>8개월 아들 리모컨으로 때려 숨지게 한 30대 친모에 징역 12년</t>
+          <t>마이크로소프트 10월 패치로 취약점 1,411건 수정…이미 악용된 제로데이도 포함</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>)= 생후 8개월 된 아들의 머리를 TV 리모컨으로 때려 숨지게 한 30대 친모에게 중형이 선고됐다.</t>
+          <t>마이크로소프트 10월 패치로 취약점 1,411건 수정이미 악용된 제로데이도 포함.</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>주요언론</t>
+          <t>위키트리</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261015132500061</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBWRTRybkFOT1BiMXZwal9vdGxqeHppcmNhcmZkMWxlcE5uYUV0WV9zWGNvT0pTVVBwbjRSZFhLZEdId0x0czAzZDNJdlJIaGNLaklyY0JR?oc=5</t>
         </is>
       </c>
     </row>
@@ -7141,32 +7141,32 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>코스피 8% 넘게 떨어져 서킷 브레이커…‘7월 폭락장’ 이후 처음</t>
+          <t>‘그란 투리스모 7’, 신규 차량 6종 추가</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>코스피 8% 넘게 떨어져 서킷 브레이커‘7월 폭락장’ 이후 처음. 아울러 공포의 '검은 목요일'‥코스피·코스닥 7%대 급락 마감.</t>
+          <t>‘그란 투리스모 7’, 신규 차량 6종 추가.</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>경향게임스</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5mZlRCTlllLTZnVDZHWF9HMHc5T2M2S05la1B6d1ZXbkpSamF3V3F2bjJzU3RnZlZPcVREMmFlRm0yTnJJUWFuQTR5bEhzX1pOVEdJZ1VpdEJXSmh0bFowcmNCallUY2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFA1VzJveTh5YjctUDMxdlVnVkdRQVhIQVdRb0h0SVJHZmlhVVNkU0Y3UnpHa3VZNGxvSXN2ZDg3dTVlWWhaWHRMa2RydGI5dHgzeldSUlJjSWE0eEVJeHdNejNTOHBvbUJVQmxkQw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7178,32 +7178,32 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>"삼성전자, CXMT와 기술격차 최대 7년…시장 우려 과도"</t>
+          <t>테슬라보다 먼저 하늘 날까…드로리안, eVTOL 레이싱 도전</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>"삼성전자, CXMT와 기술격차 최대 7년시장 우려 과도".</t>
+          <t>테슬라보다 먼저 하늘 날까드로리안, eVTOL 레이싱 도전.</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>디지털투데이</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1admhLWjR3QzJUNjFXSldvTXh4Q3NBdlhDWGVldFVjRXBvM1JxWl9YRk5uOF9DZ2VCVXlvTFlud2ViYVFPNlpFLXl2dW9RMjJkWlhPZTFXMGZUZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBwZE9CcjJSSkhqaWJSTHBZaEdlazhjQmlkTDJzcVBTTzVRZmtXY2NvLTNyR29pLUwxb2tDME41LVJhWmZYTGtuN082V25IMHJFWHpPTEtyRmJTZDdzT25xZkxOc3p3ZDR4aDZKcHZSV2N1TzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7215,32 +7215,32 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>지뢰밭 뚫는 로봇·자폭드론 기습‥육군 "2040년까지 전군 유무인복합부대로 전환"</t>
+          <t>왓츠앱, 계정 없는 사람도 링크 하나로 통화 참여</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>지뢰밭 뚫는 로봇·자폭드론 기습‥육군 "2040년까지 전군 유무인복합부대로 전환". 아울러 레이저 대공무기 천광, 드론 요격 시연 성공1회 발사 2천원.</t>
+          <t>왓츠앱, 계정 없는 사람도 링크 하나로 통화 참여.</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>Martin Cid Magazine</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBMMkNldEZtOFJuYmU4Skl3bGZUWnpVOENCa2xmUzVnbER2bnd4OTE5TnptM2xadjYxZlhoWVBTcVpnOHdFZDN6RGtEdzdiT3hTS1ZFQ3hCNE5sWXNBNXNBQTBaXzlFN2VlTjIzZUdMcWtFZGMxWjFCMtIBeEFVX3lxTE9TdjFpZzVZWUlqakZBOTJiaWd4NHY5eWVkdm52cmt5cjRIa3dWMFZGSlQ3T0VQWVBxUGRmaU9FZkJpalZ1NEdhV0szMk9lRTItMDQtcERHLU11RktUeU04TVZHeVBKX3pzNEJ6dnowanFlclBQRFF0Rg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxORWhLUEExWW9mSUVhWkNnNFRJSzlpcFNwTjNYblRLQ2hoTVY0NUI2X3hwSy1GalhOcUJZV2RDQmJTWjFvMVZDMWM4WlNtcU1HNzh1Z0hXb3IyLUZtbDNvSDNQcTAzODRJMnJRTlBuSV80TlNiQmNRZXhiN2JpZmZrR004Q0dMU1dGQWdDc1hPTWRQSmUzNnpLeEhkSjJPNU9RMXotRXdtRXZWMTlla0phYTRTYzZVeTNNZmhzWnRUd0ZwQ180TmpjSE1rSklWel9IMXNDSkJENFgyNXFQQ3RnaWNEekFEWWVqMEplSkFqOWZYQTVhMWR5ZFI1eUZtRmU4ZC1rbHNZaEw3LUpuVDNjaWhxNEMwM19vbnF2Tlh2VEtJNmN5eTVQdmZtZUxJbHdxdkZ3ek42N1dOOEpjYlpV?oc=5</t>
         </is>
       </c>
     </row>
@@ -7252,32 +7252,32 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>OK저축은행 개인정보 유출 고객 규모 183명→250명</t>
+          <t>춘천 시민정원사, 서울국제정원박람회에 '봄내정원' 선보여</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>OK저축은행 개인정보 유출 고객 규모 183명→250명.</t>
+          <t>)= 강원 춘천시 시민정원사들이 서울국제정원박람회에 지역의 독특한 자연경관을 담은 정원을 조성해 눈길을 끌었다.</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBUUkZBTHI5VllFTjFtYVBZMklaQU9oZkVULVlTRFhnQ3I2NE5iSVhhYTQyZlhkUHI1Sl9wbnRRaHlZemdpeGp2Q3hNeW9Hdm5qckw3YzUwUXVNcWVjQmNJV01Pdm5UQTA?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015157000062</t>
         </is>
       </c>
     </row>
@@ -7289,32 +7289,32 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>IT/과학/신상품</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>정부 요청받은 SK·삼성·현대차, 美 웨스팅하우스 지분투자 검토…최대 4조 규모</t>
+          <t>캠코, DIP금융 부실에 "회생기업 지원 한계…개선 필요성 동의"</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>정부 요청받은 SK·삼성·현대차, 美 웨스팅하우스 지분투자 검토최대 4조 규모.</t>
+          <t>)= 정정훈 한국자산관리공사 사장은 15일 회생절차가 진행 중인 기업에 신규 자금을 투입해 경영 정상화를.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>인베스트조선</t>
+          <t>주요언론</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQY3M4MkFsQ1JpMW43Wm9IZ3hqRmFQVUp3M3NDUFlPSzlYSWtJbHIxNGk2V1BZQ1JWaEhWYXZQc182U2NhUHotZHBOZFd4ZXJoVWFIQkczcHlkcXRSUFNFYU1DMDJEbjB5czdJbEw4WkFhaVc2VTRFUEh1ak1lZjRjaXlMRQ?oc=5</t>
+          <t>https://www.yna.co.kr/view/AKR20261015152700002</t>
         </is>
       </c>
     </row>
@@ -7326,32 +7326,32 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
+          <t>연결 이슈 (후속)</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>AI 클라우드업체 코어위브 회사채 가격 급락…'부실영역' 진입</t>
+          <t>이성미, '백일 아기' 있던 故임윤택 위해 기도했었다.."나 대신 살려달라고"</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>AI 클라우드업체 코어위브 회사채 가격 급락'부실영역' 진입. 아울러 "전세계 돈 끌어온다"더니증시 덮친 '15%' 공포의 정체.</t>
+          <t>이성미, '백일 아기' 있던 故임윤택 위해 기도했었다"나 대신 살려달라고".</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1Ud2RXUWZrWFNsejM3Q2J2cUdieXdiSmZVMnk0S2dCU3NrOGRLOEQtQmZ6MWlTcGlSeGU1Y2VEVl90aThINzUwOXRwUEF0d0U2RjlzUGFFU1Rna3VOM3dyRFlLalJPN0Q4R3FRZ3lvU1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNclMzMTZyRk1DNF85TVFKQ0NibDh1bVphaXNlaFBiNWZxS0tFcWV4bXFJU0pHX0hxUUdmR3lVbGZ0Mnh5V0VTWjJlZVBKVDcxZ25PVTd6RHR6QTVhLU5PaTJxalBiVmxiTkE3TUFZN2RFTjFXaVBTbDlBSlNXeU14SHE2OVFpUHJ3cHVwZ2NwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -7373,22 +7373,22 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>믿었던 ‘삼전닉스’에 발목...주요 반도체 ETF 줄줄이 수익률 바닥</t>
+          <t>[인터뷰] 움직이는 그림, 소생하는 우정 - 고레에다 히로카즈 감독</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>믿었던 ‘삼전닉스’에 발목주요 반도체 ETF 줄줄이 수익률 바닥.</t>
+          <t>움직이는 그림, 소생하는 우정 - 고레에다 히로카즈 감독. 아울러 영화 '룩백', 데코팩 엽서 세트 수령 가능 지점?관람객 평점 보니.</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>씨네21</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNRUFoOGM4RW40SVlwck9DR2dPU1VIWHE0VHE3SGFWc2FFZkQ4Z2N0ZlJ5OXBkb3N5QXhhcnVvMzJfdEJjUlVYS25VdUE2MERYQ1VoY1drc0xDWENaQVBFanllVDlhVVEtN05pYnMyTzVVUkRwMEE5VEFqTVVnM3dhXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5hQTkxaXVaTnIyLW4wR2RvdnV3QWhjVkVkMEhWRnM3YlU1WmhHelk1Vl9JU2I4R1ZUSlVxWHVlXzZIRmk0aFZFSXBSX1gtUV9sR2VYUGFR?oc=5</t>
         </is>
       </c>
     </row>
@@ -7400,3991 +7400,32 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>거시경제/비즈니스</t>
+          <t>연예/대중문화</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>연결 이슈 (후속)</t>
+          <t>신규 이슈</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>‘배민 라이더’ 201명 개인정보 노출 정황…로그인 없이 열람 가능</t>
+          <t>'닥터X', 14.9% 대박났는데 의사 반발→심의 민원 '날벼락'..SBS "입장無"</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>‘배민 라이더’ 201명 개인정보 노출 정황로그인 없이 열람 가능.</t>
+          <t>'닥터X', 14.9% 대박났는데 의사 반발→심의 민원 '날벼락'SBS "입장無".</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBBR3JBSlpPZFEyQXpzZWczLVFNMkttZmRPVlhaR3ZtRmdlaGtmN003Wmc4dXNSMlFSdjRNSzFBOHFrd0U5aFE0aGF2Ry1CYTNDVHFYQWVUbks4YlU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>[정신아의 약속 1년②] 카카오 주가 반토막에 인적분할 승부수</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>카카오 주가 반토막에 인적분할 승부수.</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>연합인포맥스</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5pbWNtWko5a2hiY000YzJ2RndTSlJKa0cxOE5RTVNJWnJTc0d0UFlVWHJFVHVDOXliNUk5Z0RUN1RVTUJzbEdjcHY0d1FCenZXdENMa1A1QnhnM0N4OHRYVWotNU1ZYWtMLVVwaHNUblg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 “한국 알래스카 500억달러 투자는 나와 맺은 합의” 또 못박기</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 “한국 알래스카 500억달러 투자는 나와 맺은 합의” 또 못박기.</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>한겨레</t>
-        </is>
-      </c>
-      <c r="G190" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1OYmFhOGZZWDc2UW5JSzBBOHhuNzQ1VWxGY1pmY0ZoNGdIaTZENDU4TWpxMVBVMWNYQ1FteE9NRzVDWGU0SDB2OUx1NEdoS1FuTXdNb1h6TzFRY2k5Z29fSmR6QWFBNnNtOFVPcy1naw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>비트코인, 미국 물가상승 직격탄…8만 1500달러까지 하락</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>비트코인, 미국 물가상승 직격탄8만 1500달러까지 하락. 아울러 코스피 급락 부른 美 CPI 충격"사실상 올해 최악 성적표".</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>지디넷코리아</t>
-        </is>
-      </c>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9Wdkp3aG5zbU9pUXVXaU8xc1M0a2RPbFBlNG1Gci1idDlBWFZFRllzMko3Q3M0YVZ2V0RObWV5bFRIdksxUEZ0TmNBMEZfdW5lWmxQREpn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>“주간 아파트값 통계, 전문가는 조정·국민은 공표 원해…추가 의견수렴 예정”</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>“주간 아파트값 통계, 전문가는 조정·국민은 공표 원해추가 의견수렴 예정”. 아울러 다시 불붙은 ‘주간 집값 통계’ 실효성 논란 부동산원장 “유의미, 검증 강화” - 조선비즈.</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>KBS 뉴스</t>
-        </is>
-      </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAweW1pcXVEcmxTZFotbVYwLUJpaDNNN1J2OHlTa2pCenExNDI2aWVZZDJSVGtGc09sQ2Zza3BtenFpYnRSYXo2QnpMWFp2NkxidDJ0WVRyMzlWZkU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>AI 챗봇과 수다 떨다 성적·폭력 대화까지…정부, 유해 응답 차단 추진</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>AI 챗봇과 수다 떨다 성적·폭력 대화까지정부, 유해 응답 차단 추진.</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>경향신문</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9yQW5TNHlDWXh1OUJFdFl3YU9VWl9BYm5tMU1JY3JSdkFNRDY4TGRteW1hTjRkQW1hRWFEbk50U0RORzNOTEtTSGtuTndkcHdwSFVGVEpzYjMxUdIBX0FVX3lxTE0zZVlrbk1DTDBOb2JtSDJnNDdYTWljNWlCd1NjbG1uaVhjXzFua1k0QzdJVWw1bklheUxZbFV2aEJ5ZWtIeDFOalNBS05XdjZtWjRDckV6dENpRUhobldr?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>서울 아파트값 88주째↑…분당·영통·동탄, 반도체 머니로 ’들썩’</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>서울 아파트값 88주째↑분당·영통·동탄, 반도체 머니로 ’들썩’. 아울러 '88주' 최장 상승 서울 아파트값용산 '상승 전환'에 오름폭도 꿈틀 - 머니투데이.</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스TV</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBTUjZiemJlZlhLeHdnZndBUzVGckN6SllpTFM2bE9UNVZVRUN6SDdiLWdWOEwyVHY4WEM1Zi0tLUVYWGh4WXp5d3IxOEtyUjA5MDhub0lIVGxQUEdINGtDZkpaNzVvZHM?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>아파트 가격 최장 상승에…10월 입주 전망 지수 반등</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>아파트 가격 최장 상승에10월 입주 전망 지수 반등. 아울러 서울·경기 아파트값 상승세 지속에 수도권 입주전망 개선.</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스TV</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5SMDcwSF9HRDY1TnFjd1d1ZEFGQ0Q0V2s0MDBGeFdDQjlueURaTzJvRWRpdGw1dUFpUmM0YVc2eDhpTWpyeWRXVDRwYngwenVmSVZsN3Frc2lXQVVVWmx6aG0ySk0xV1E?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>GM 시절 로봇 6대가 204대로… 현대차가 바꿔놓은 인도 푸네 공장</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>GM 시절 로봇 6대가 204대로 현대차가 바꿔놓은 인도 푸네 공장. 아울러 정의선 '21兆 승부수'인도 車수출 전진기지로.</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPTDlENkJxSnk0UjhyWDlTYkxqR2M4WVk3bXlhVUw5RE9pd1RIM0hPYWtQYlFacG5QOFdwLS1hN3VxZVhFNHlvWkl4b1NXTG41UThJQkE3VTR6VEtUVlFaRVVJNHlBU0NLNE05ZjVUMWRvSjBZRW5jcWtFYkV0VmRubllHQ2oyN2s5WVhyM2pqdw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>'서울디자인위크'에서 내 취향에 딱 맞는 디자인 레시피 찾아볼까?</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>'서울디자인위크'에서 내 취향에 딱 맞는 디자인 레시피 찾아볼까? 아울러 마우로 포르치니 삼성전자 디바이스경험부문 최고디자인책임자 사장.</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>서울특별시</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZNWlZVmU2VTlGX1pUdW85cXQ3ZndNTDJlRnlYTVRJQVhkZzdaWGU5N282UUhjamNSSUdjMGgxYXpoT3dNOHIwV1JOTE5PSWJKUGs4Z2pWdFA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>[심층] 결국 ‘건보 급여화’ 문 두드린 위고비…에페, 출시 전부터 ‘덜덜’</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>결국 ‘건보 급여화’ 문 두드린 위고비에페, 출시 전부터 ‘덜덜’. 아울러 K비만약 ‘에페’ 월12만9800원 마운자로 반값인데주가도 반값될라.</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>농민신문</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1jQWJUWU5QQ3p1WUhKZFRxY3U1V1U0VHJIQ2g1aGFCSk56ZFEwZjhsTEZLbUNYS1hwY1RLcDdLZU12bkJxaWpFN1Q4OXNGR2JuUGFEVF9abk1rUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>내달 5일까지 전국에서 '지역 활성화 투자 펀드 로드쇼'</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>)= 기획예산처는 15일 전북을 시작으로. 달 5일까지 13개 광역·관내 기초 지방정부를 대상으로 '지역 활성화.</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015109500002</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>송미령 장관, 군수협의회 참석…농지조사·기본소득 협력 당부</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>)= 송미령 농림축산식품부 장관은 15일 전북 무주군에서 열린 제16차 전국농어촌지역군수협의회 총회에 참석해 정부의.</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015084300030</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>광주은행, 어르신 치매·실종예방 캠페인…4년간 20억 지원</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>)= 광주은행은 15일 적십자 무료급식소 에서 광주사회복지공동모금회, 대한적십자사 전남광주통합특별.</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015137600054</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>농림축수산단체 "CPTPP 반대 변함없다"…5대 요구안 제시(종합)</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>)= 농업·축산·수산·임업 분야 75개 단체는 15일 포괄적·점진적 환태평양경제동반자협정 가입에 대해.</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G202" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015089951030</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>[특징주] 멜콘, 코스닥 입성 첫날 42% 강세 마감…상승폭은 줄어(종합)</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>)= 반도체 공정용 환경제어 장비 기업 멜콘이 코스닥 시장 상장 첫날인 15일 40%대 강세 마감했다.</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015043951008</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>[바이오스냅] 한미사이언스, '건강한 헌혈문화' 확산에 앞장</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>)= 한미사이언스 가 대한적십자사와 함께 건강한 헌혈문화 확산에 나선다.</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015128500017</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>'검은 목요일' 패닉…코스피·코스닥, 7%대 급락 마감</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>)= 인공지능 투자 수익성 논란이 다시 부각된 가운데 코스피가 15일 7% 넘게 급락했다.</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G205" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015134100008</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>노동부 "DN오토모티브 납 조작 검진기관 개입 의혹도 수사 요청"</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>)= 자동차 부품업체 DN오토모티브의 노동자 혈중 납 농도 조작 의혹과 관련해 고용노동부가 특수건강진단기관이 개입.</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G206" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015129500530</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>코스피 급락에 긴급 점검회의…이억원 "리스크 관리에 만전"</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>)= 코스피가 급락해 장중 5,500선을 밑돈 가운데 금융당국이 긴급 점검회의를 하고 리스크 관리와 투자자 보호를.</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G207" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015130500002</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>[속보] 공포의 '검은 목요일'…코스피·코스닥 7%대 급락 마감</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>공포의 검은 목요일…코스피·코스닥 7%대 급락 마감 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G208" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015131900008</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>[외환] 원/달러 환율 6.3원 오른 1,344.6원(15:30 기준가)</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>원/달러 환율 6.3원 오른 1,344.6원 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G209" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015130900002</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>LH, AI 대전환 선포식…" 주거 혁신 앞당길 것"</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>)= 한국토지주택공사 는 인공지능 을 기반으로 경영을 혁신하고자 15일 'AI 대전환 선포식'을 열었다고.</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G210" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015093200003</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>주담대 변동금리 또 오른다…9월 코픽스 0.25%p↑</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>)= 기준금리와 시장금리 상승 영향으로 은행권 주택담보대출 변동금리의 기준인 코픽스.</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G211" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015126700002</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>[게시판] 소비자원, '한국 ESG 혁신정책 대상' 최우수상</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>한국소비자원은 15일 사단법인 한국정책학회 주관 '제5회 한국 ESG 혁신정책 대상'에서 사회 부문 최우수상을 받았다고 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015127700030</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>관세청장 "세관 '수사심사과' 신설 추진…공소청과 많은 협력"</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>)= 이종욱 관세청장은 검찰청 폐지 후 특별사법경찰관 수사 시스템을 보완하도록 "수사 심사과.</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015112900002</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>캠코 선박금융 90% 수도권에 집중…“해양수도 육성과 엇박자”</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>올해 선박금융 총 2조8000억원 달해 부울경 지원 규모는 2854억원 그쳐한국자산관리공사 가 시행하는 선박금융 지원이 수도권 소재 해운사에 90% 편중돼 개선해야 한다는.</t>
-        </is>
-      </c>
-      <c r="F214" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/politics/12176819</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>코스피 급락에…이억원 “투자자 보호에 적극 대응하라” 주문</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>7%대 ‘뚝’5500선 마감하며 하락세 금융당국, 대내외 경제 여건 영향 분석 투자자에 “기업 본질적 가치 판단 필요”코스피가 15일 급락하며 하루에만 7%대 빠지며 5500선에.</t>
-        </is>
-      </c>
-      <c r="F215" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12176796</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 펄펄 끓는 바다, 양식장 1747만마리 폐사…‘고수온경보’ 역대최다</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>정부 양식장 이전지원 해상 1곳 그쳐 피해 반복에 육상양식 대안 부상올 여름 고수온 경보가 내려진 해역이 역대 최다인 27곳으로 늘면서 양식어류 1747만마리가 폐사한 것으로 나타.</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12176779</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>“주식은 빠지는데 주담대 이자는”…코픽스, 3년 10개월만에 최대폭 상승</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>8월 신규취급액 코픽스 연 3.45% 지난달 숨고르기 후 0.25%P 급등 5대銀 변동형 금리 상단은 6.46%은행권 주택담보대출 변동금리의 기준이 되는 코픽스(COFIX·자금조달.</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12176776</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>최형욱 행복청 차장 “사람 옮기는 건 기관, 눌러앉게 하는 건 정주환경”</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>행복도시 현장 누빈 첫 내부 승진 차장 첫마을 입주 때 상수관·이삿짐까지 챙겨 44개 기관 이전 앞두고 “청사만으론 부족” 병원·대학 갖추고 국가 장기계획 세워야최근 행정중심복합도.</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12176769</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>“내가 손절만 하면 다시 오르네”…하루 만에 반등한 금값 이유는?</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>4084달러까지 하락한 국제금값, 15일 4158달러 美 CPI 3.7% ↑고금리 장기화 우려에 금값 출렁 국내 금 투자 수익률도 국제 금값·원달러 환율 영향미국의 물가 상승률.</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12176754</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>[Visual] ‘AI 해킹’ 금융권이 뚫렸다</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>연초부터 금융권 해킹 시도 포착 신한은행 시작으로 피해 확산 금융사 16곳·정보 10만건 유출 中 AI 해킹 도구 사용 정황 당국, 동일범·AI 활용 여부 조사국내 금융권을 겨냥한.</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12176706</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>거시경제/비즈니스</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>[속보] 다시 오르는 용산 집값…상봉·신내동 소형아파트까지 ‘들썩’</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>서울 아파트값 88주 연속 상승 중랑·성북 등 강북권 상승세 주도 강남3구 하락 지속용산은 반등 경기 0.26% 상승, 세종 상승 전환강남3구의 아파트값 하락세에도 서울 집값.</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/economy/12176569</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="inlineStr">
-        <is>
-          <t>AFC, 중동 정세 불안에‥"1월 사우디 아시안컵, 1년 연기 검토"</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>AFC, 중동 정세 불안에‥"1월 사우디 아시안컵, 1년 연기 검토".</t>
-        </is>
-      </c>
-      <c r="F222" s="3" t="inlineStr">
-        <is>
-          <t>MBC 뉴스</t>
-        </is>
-      </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE82M05tbUctTmVxaGdlY1VWdDdtNTRyS1Y2eFU4bFVNRTg4ZmljVHgxVWhCWTlOWGRkLXZ6QTlJR0xMNldpWTBNaE93ZWN2NkUyc1FZbmZXLVJVYzNQNGd6TkpybTItQklHVnR2QWlMakhQU3hBcEHSAXZBVV95cUxOSzJsR2NHTnBNM1MxLWdRTjRySnFmZm1WUWgzZzBMdXprb29YS3JCYzdObUppZUl5U0VXaUxfQ2VSUXJJaDNLd0VWaUVVS3J6akdsbGRQM2huTXNZSUhNRDF2RTNYWFJTYThTaHpaNnBmOWFiUkln?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 새 대변인, 美변호사시험 불합격…경력 논란 확산</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 새 대변인, 美변호사시험 불합격경력 논란 확산.</t>
-        </is>
-      </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스TV</t>
-        </is>
-      </c>
-      <c r="G223" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9hTW9HYWFBTWpib1Fnd1hMY0l4VjhhanNmcWVDc1luWnlCNEFQelItWG5JX2E2dHE3ai1UVVFuVnVocW1PWDNJSFA3Y25wN0R3VW1kSnVsSkUtNk91allsTmJZOFJOWVk?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>노벨평화상 필라이, 트럼프 ICC 제재 비판</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>노벨평화상 필라이, 트럼프 ICC 제재 비판.</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>MBC 뉴스</t>
-        </is>
-      </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB1eURfdmF4ZTVVbE8wVzVKVkItdHhSWERSWkhpN2ppYWJDUVNreVJVLTAxREJTVlB5bmRWdHQ4ZThYckxhbWpPbW4ySDZvbnNEZlcwdjYybDZuVTdKUDk1MHFfa1haLURUVHRaRDhyRFdBOUl30gF0QVVfeXFMT0lwcEtUT3ptY3FZLXdIZVd6MWdiMUlVanZxbmgzTUI4NHZfSlFreElCWG85VUhzNE9tQmdRMTNza05za0pnTXdPbXlqNUJwTXhleHJQZ1VLTDVSTnRmYmJmd3o1RE9TYjBJLVdDaEVTZTRTMU0?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>미국, 이란 공격에 ‘비핵무기 중 최강’ MOAB 투하 검토 - CNN</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>미국, 이란 공격에 ‘비핵무기 중 최강’ MOAB 투하 검토 - CNN. 아울러 총선 앞 네타냐후, 전쟁 불씨 만지작트럼프는 멈칫.</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>경향신문</t>
-        </is>
-      </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE8wYnV4dFRLNVlTUC1EdEE3QlBBUHNaWVF1SGJKUnZqSFg3bDNaWDN3dGZsQ1dnLWFZREhDSVVmVEJwQnZxa1JVN1RXbHBqbHhTUkROeDZLZUN1UdIBX0FVX3lxTE1xVEZFM3luMGg1QnhEN1JhdjRXRnlRVTZRaFhiUE5hVm1QZk5VaVFBVGRKemFUVGFIWFhMS0FaMkx1LXpONU5BdGVFS0xtY2ZtTDlaMzllLUxIdk4zZmhn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>[포착] “5000년 만에 처음 만졌다”…‘세계서 가장 오래된 난파선’ 튀르키예서 발견</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>“5000년 만에 처음 만졌다”‘세계서 가장 오래된 난파선’ 튀르키예서 발견.</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>나우뉴스</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFAxTEY1bTQ2Q2Y2QmRpY2JfUGo5M1c2Y01pV2lfYUF6ZmZxYzRlbXBYYzNuMzk4UTZQTC1rb0JzTFBQUVl3SXZhd0VQazgxVGo0OHNyaTFfRkdSd1JkOWw5YWp3LXBDVjhVdHV3OVNjMVk?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>“북한, 러시아서 드론 대량생산 기술 습득…한국·일본에 새 위협”</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>“북한, 러시아서 드론 대량생산 기술 습득한국·일본에 새 위협”. 아울러 “北, 러 드론 공장에 1.2만명 파견대량생산 노하우 갖고 평양으로”.</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>한겨레</t>
-        </is>
-      </c>
-      <c r="G227" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOczVHZ1RfWklZTWcwOWI4d2xnS1lLOFRuUE5iVm1tcVkzaXRZb05Oa3lnOEE5LVE1ZzJvcXpKd1ZDUFQyYUM2eUJUQnFPOW85R3pGXzYzOWRIdVdVa2loVEZwcUJDTkV4dFVQVzdna213eGc1MUE1X0tFTmVkakxZV1FR?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>중간선거앞 '사익추구' 불똥튈라…트럼프, 그리스 대사 경질</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>중간선거앞 '사익추구' 불똥튈라트럼프, 그리스 대사 경질.</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFB6M3AtNHdfanMxZXZVb2RCN2l6U2ZCcEhkMjBqeklYb3VoRGsxcnpCeXg3SWYyUUlfbTRJS1llMW9ZT0Q4ZmxhY2x4UXVITjhHYXFnVS1yYlZ3cWfSAWBBVV95cUxQNjlNV2NaT0pWWTMwMUF3OXNhZUR5OE1WV2lkVVRHR25WOW0wYTlNV0VrSGlSMU9CWFdpT0V3MmVuSTF1djZSXzNEVFlQQ3lRcENubmtBMkdIdWpEM3J6N3o?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>[사진] 영국 총리관저 앞에서 만난 버넘과 젤렌스키</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>영국 총리관저 앞에서 만난 버넘과 젤렌스키. 아울러 "미 압박 막아주겠다"트럼프 빈자리 채우고 나선 유럽 각국.</t>
-        </is>
-      </c>
-      <c r="F229" s="3" t="inlineStr">
-        <is>
-          <t>뉴스핌</t>
-        </is>
-      </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBkUHFoU1lLTlFhSHlpZ09VMU9vZ2JTVXhzRW1teHJiQ2NQemJsUGt5QXprS2MxUFNWN1pVZTVBbzAxbXVZOE9RejROdzRSektQcVBrM2VqX24zcDFv?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>미군 "이란 연계 선박 격침…미 해군 함정 표적 삼았다"</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>미군 "이란 연계 선박 격침미 해군 함정 표적 삼았다".</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>한국경제</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1qMVh5Tmh6WWRaRk4xMjFxZ3BLVXFIc0V4ZGpaYVFjdHg2cllFNTc4OVBnbXBJSGhrbHVvc3ZIUFA4SDZ4UUdBRUhydXh0bEdGRlVkbHg1U1A1Zw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>美 건국 최초 '총살형 생중계' 논란…어떤 방식으로 집행되나</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>美 건국 최초 '총살형 생중계' 논란어떤 방식으로 집행되나.</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>광주타임즈</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9aTUcwZmdWMzVzSUdVRXVseDBHRVJPakR6eGlIZDNYRVlUc0pQek5nLUpZN0VISFpxN25xR2JWRzVVOHVtenRXZ3RvZ3pFMUJTUmQzWExlVkp5NXJYM09OSHRnMEdHYlR2Nmc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>그린란드 정부, 트럼프 ‘대규모 석유·가스 탐사 임박’ 주장 반박 - 조선비즈</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>그린란드 정부, 트럼프 ‘대규모 석유·가스 탐사 임박’ 주장 반박 - 조선비즈.</t>
-        </is>
-      </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPZXIwSlFQWi02cEl1UkU3cGNUSkQxdjV1aTVlQ0VRYVI1dVR0MVBuNEk3WmdUX0R0ZHpSa2ppVzdHcnNkbnJLS3AyMnBZbEhRWWZZVGdabVJDc0hYdko3Q1EwbmJTOUhTZmd2OEZ0ejlIbUtIZDhFMUFjOF9SS3FJTUEtNjRKRmF1YWxMVU1iVU95ZUZuNjQzbWZWZ2hwQdIBsgFBVV95cUxOR0FMWjlCb0pEcjJVYllMZlY3ejZ0RjRzM3RjOEFDNkwtOWZWUnQzRmZ1TXk2UkRpMEtyS3JpQ1ZDREF1RXU0dEI5eC1hYTV5YWFyTGZwSHBKN3NXVEYtUHNhMUJuelk5NkZPRXhnV2gwNldTRFFaUnZFX0dkV1JuQ0FoX3dGaGFHcnR2MlRyNVF1TGdQRmJQaVdUSDVoNWllSE4xdHhxVS1BbVU1VE9mOGZB?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>노르트스트림 폭파 4년만에 재판…전직 우크라 장교 법정에</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>노르트스트림 폭파 4년만에 재판전직 우크라 장교 법정에.</t>
-        </is>
-      </c>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>KBS 뉴스</t>
-        </is>
-      </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1DY0NGMTlFY2JJTGYyNHBtUjh5ZW51SjR2ZFZEOEhUYnV0Ym15anptZTN4RklEUEFudS1rVlVjQ2tyOE82UEkyWVhvbEJrNF90MXkycjRBd1Z6d00?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>젤렌스키 "러 정유시설 공격 재개"…트럼프 압박 정면돌파 시사</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>)= 볼로디미르 젤렌스키 우크라이나 대통령이 미국 트럼프 행정부의 압박에도 러시아의 정유시설에 대한 공격을 재개한다.</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015138100009</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>인니 대규모 산불로 연무 확산…이웃국들 대기질 악화로 골머리</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>) 손현규 특파원 = 인도네시아에서 11년 만에 발생한 최악의 산불로 연무가 계속 확산하면서 대기질이 악화한 이웃국들이 골머리.</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015136700104</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>[쇼츠] 새벽하늘 푸른색 괴생명체?…팰컨9이 만든 '우주 해파리'</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>) 아직 동이 트지 않은 새벽 시간, 미국 동부 연안 상공에서 정체불명의 거대한 불빛 덩어리가 목격돼 시민들을 놀라게 했습니다.</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015130100704</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>[쇼츠] 그리펜 전투기 360도 돌리더니…태국 왕비, 여객기 몰고 일본행</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>) 14일 방콕비즈뉴스 등 태국 매체에 따르면 수티다. 왕비가 이날 전용기를 직접 조종해 태국에서 약 7시간의 비행 끝에.</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015135500704</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>'트럼프 구상' 가자 다국적군기지, 이스라엘 불허에 첫삽도 못떠</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>)= 도널드 트럼프 미국 대통령 주도로 만들어진 가자 평화위원회가 이스라엘의 불허로 가자지구 내 임무지원 기지 건립.</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015136500009</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>대만 "中, 타이베이시장 후보 부친 기업 제재로 지방선거 개입"</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>) 김철문 통신원 = 중국이 집권 여당 타이베이시장 후보의 부친 회사에 대한 제재를 가해 지방선거 개입에 나섰다고 대만 당국이.</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015124000009</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>[영상] 컨테이너 2천500개 물에 둥둥…호르무즈 해협서 화물선 침몰</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>컨테이너 2천500개 물에 둥둥…호르무즈 해협서 화물선 침몰 소식이 전해진 가운데, 관련 당사자들의 공식 입장과 향후 대응 방향 및 일정에 대한 심층 보도가 이어지고 있습니다.</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015132100704</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>佛 극우 르펜 "대통령 되면 EU와 힘겨루기"…정면충돌 예고</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>)= 프랑스의 유력 대선 후보인 극우 국민연합 의 마린 르펜 의원이 내년 대선에서 승리하면 프랑스가 유럽연합(.</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015131100009</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>[게시판] 주오사카총영사관, '코리아타운의 미래' 세미나 개최</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>주오사카총영사관은 지난 14일 오사카 뉴오타니 호텔에서 '다문화 공생 플랫폼, 오사카 코리아타운의 도전과 미래'라는 주제로 재일동포, 오사카.</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015127800073</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>4천400억원 투입된 北中신압록강대교…왕복 4차로·3㎞ 사장교</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>)= 압록강을 가로질러 북한과 중국을 연결하는 신압록강대교는 폭 33ｍ, 총연장 3천26ｍ의 왕복 4차로로 건설됐다.</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015124500009</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>손주 자랑하려 사진 올렸는데…신상 털린 日 운동회</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>)= 가을 운동회 시즌을 맞은 일본에서 자녀나 손주 사진을 사회관계망서비스 에 올렸다가 타인의 신상 정보까지.</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015126600009</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>'소니 산하 애니 OTT' 크런치롤 "번역에 AI 안쓴다…창작 영역"</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>) 이도연 특파원 = 소니 그룹 산하의 애니메이션 전문 온라인 동영상서비스 가 일본 애니메이션의 해외 서비스용 자막·더빙.</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015124100073</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 지지율 폭스뉴스 조사 36%…1·2기 통틀어 최저</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>)= 우파·친 공화당 성향 미국 뉴스채널 폭스뉴스에서 도널드 트럼프 미국 대통령의 국정 수행 지지율이 트럼프.</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015121200009</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>TSMC, 3분기 순이익 68.7% 늘어…6분기 연속 신기록</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>) 차병섭 특파원 = 세계 최대 파운드리 업체인 대만 TSMC가 인공지능 붐에 힘입어 올해 3분기에.</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015124300089</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>[게시판] 서강대 유로메나연구소, '수에즈 운하' 국제학술대회</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>서강대학교 유로메나연구소 와 사학과는 16∼17일 학내 정하상관에서 '수에즈 위기 70주년, 역사 유산과 세계질서 재편'을 주제로.</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015122000009</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>[르포] 12년만에 이어진 北中신압록강대교…긴장속 中주민 수천명 운집</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>) 정성조 특파원 = "개방하고 무역하면 모두에게 좋아요. 조선 뿐만 아니라 조선반도 , 동아시아 전체를 연결하는.</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015115700083</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (6개사)]</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>트럼프 새 대변인, 美변호사시험 불합격 확인…경력 논란 확산</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>)= 변호사 경력을 내세우고 활동했던 케이티 재커라이어 백악관 대변인이 미국 변호사시험에 합격하지 못한 것으로 확인.</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015117600009</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>세계/국제</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>"미군, 이란 추가공격에 '모든 폭탄의 어머니' 투하 검토"</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>)= 중간선거 전후 도널드 트럼프 미 대통령이 이란 공격 재개를 명령할 때를 대비해 미군이 이란의 에너지 인프라.</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015116600009</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>GTA6, 'NPC 대사를 위한 작가 팀'이 별도 존재한다</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>GTA6, 'NPC 대사를 위한 작가 팀'이 별도 존재한다. 아울러 GTA 6 최신 정보 총정리: 현실적인 강도·수배 시스템 완벽 분석.</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>인벤</t>
-        </is>
-      </c>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yTUpmS0daaV9EVTVVM25TM25xT2sxUW9aWWlFNUQyMXR4UTI3NE9yVnFDdDh5dW9MY3pwQUl5amVzazV3TXdvcGRIMW85ZzVtakxxd3JiWmZlSU5LdDBuNGZyOWNLeUFqamV3S1k2NA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>조지아 새벽하늘에 신비한 빛줄기…“우주 해파리 현상”</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>조지아 새벽하늘에 신비한 빛줄기“우주 해파리 현상”.</t>
-        </is>
-      </c>
-      <c r="F253" s="3" t="inlineStr">
-        <is>
-          <t>애틀랜타 중앙일보</t>
-        </is>
-      </c>
-      <c r="G253" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5vX1dFOWFNNkg2Yk95dFFMZVhZdnRPSUZhdHBBSER4bkVNVW9jWlZnU2cxRlVOdVNQSHZyQmpTaEdnOG5jdXBEc3N3eEc0U28?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>[정보] 린델 나인 코어 시세 반등? 거래소 시세 살펴보기</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>린델 나인 코어 시세 반등? 거래소 시세 살펴보기.</t>
-        </is>
-      </c>
-      <c r="F254" s="3" t="inlineStr">
-        <is>
-          <t>인벤</t>
-        </is>
-      </c>
-      <c r="G254" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE8xeFVqNGtidm5vWDh1TnpORkxoeUVyUVVURXI2M2M1Z0p2OHJUb0ltZGVVOUVpSTJXd2VmLWxYcUZlY1lCRU1RV2l2OTktelltU1RGWkNjazBIY05sd0E?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>갤럭시S23·갤Z폴드5도 원UI 9 업데이트 받는다</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>갤럭시S23·갤Z폴드5도 원UI 9 업데이트 받는다.</t>
-        </is>
-      </c>
-      <c r="F255" s="3" t="inlineStr">
-        <is>
-          <t>지디넷코리아</t>
-        </is>
-      </c>
-      <c r="G255" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBtSVVidk5hR284U29DeDRuZFZzVFJoaVFrWE1RRko4bWx2bWktbFVGam5kRTFLUWJDQUt6RG1IVk03ZlI5NnJBbFhoV2RibFgtb1VkZllB?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>연결 이슈 (후속)</t>
-        </is>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>코나미, '캐슬바니아: 벨몬트의 저주' 정식 출시</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>코나미, '캐슬바니아: 벨몬트의 저주' 정식 출시.</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="inlineStr">
-        <is>
-          <t>전자신문</t>
-        </is>
-      </c>
-      <c r="G256" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE1PY2M3anFfTTBzeGVzT283eFgxRE0wdnRaYzBzMjFEUnJqQ2Q4TDJZQUVNUFd2dzRHWnpTYzJOQlNTREZqUWFGOHJyRV9mUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D257" s="3" t="inlineStr">
-        <is>
-          <t>다시 만나는 인페리아와 셀레스티아의 모험 ‘테일즈 오브 이터니아 리마스터’</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="inlineStr">
-        <is>
-          <t>다시 만나는 인페리아와 셀레스티아의 모험 ‘테일즈 오브 이터니아 리마스터’. 아울러 리마스터부터 신작까지 콘솔·PC 게임 5종 15일 대격돌.</t>
-        </is>
-      </c>
-      <c r="F257" s="3" t="inlineStr">
-        <is>
-          <t>디지털포스트</t>
-        </is>
-      </c>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBQbUlKekZEYWYxT1RUcmZmRE4ycUYwNlRESzdiOXJZVlRsVVZYVGRSQWVjT0dpWVlkRzB0UGhCSEM2NjZVZE1TdTlkaUhLMWpnMmFISjJMQkxqeEYtNmZ4Wnl3dXVqTWxtY3J3?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="inlineStr">
-        <is>
-          <t>SIE, 30주년 맞은 '그란 투리스모' 한정판 컨트롤러 공개</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>SIE, 30주년 맞은 '그란 투리스모' 한정판 컨트롤러 공개.</t>
-        </is>
-      </c>
-      <c r="F258" s="3" t="inlineStr">
-        <is>
-          <t>게임뷰</t>
-        </is>
-      </c>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE8zVEg3cEl1QTNhanZybURWRTdfVFp0SUZDbVUxbjdwbmJvS2xPM042czRwalVXWXc1QU81LW13WWFHdDlfM1dCbkwzaklNbFgtZkdTQmVGRWdxemNQbXkwY25XM3JabnpmREE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D259" s="3" t="inlineStr">
-        <is>
-          <t>엑스박스, AI 게임 디컴파일 확산에 실험 조직 ‘엑스박스 랩스’ 신설</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="inlineStr">
-        <is>
-          <t>엑스박스, AI 게임 디컴파일 확산에 실험 조직 ‘엑스박스 랩스’ 신설.</t>
-        </is>
-      </c>
-      <c r="F259" s="3" t="inlineStr">
-        <is>
-          <t>AI 매터스</t>
-        </is>
-      </c>
-      <c r="G259" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE03VUVQVGI3eEhXc2pBYmhUcFprZUNtMm00Uld4NmJnamUtQno5cThDeGtiV0EtNkI4MW85MVk3dENOLWVZRVhNZndjck1XLU9FaGNwcg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D260" s="3" t="inlineStr">
-        <is>
-          <t>마비노기 영웅전 시즌4 대단원 에피소드16 "운명의 권좌 열렸다"</t>
-        </is>
-      </c>
-      <c r="E260" s="3" t="inlineStr">
-        <is>
-          <t>마비노기 영웅전 시즌4 대단원 에피소드16 "운명의 권좌 열렸다".</t>
-        </is>
-      </c>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>ER 이코노믹리뷰</t>
-        </is>
-      </c>
-      <c r="G260" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1lZUZlVEQzU0RGSkpiNW1yZEVmeklRVEVETUZIdUZGRERjdW9vbnQxQi1VYVdJS09RelBMTlNjbGxGQzhiQ29QOUtrRVBpdS1sd0g4NmZPM1h2UlR4cVR1SkFVX3lWbS1yZjVEQg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D261" s="3" t="inlineStr">
-        <is>
-          <t>아디다스 오리지널스와 에디슨 진, 클롯 슈퍼스타 컬렉션 공개</t>
-        </is>
-      </c>
-      <c r="E261" s="3" t="inlineStr">
-        <is>
-          <t>아디다스 오리지널스와 에디슨 진, 클롯 슈퍼스타 컬렉션 공개.</t>
-        </is>
-      </c>
-      <c r="F261" s="3" t="inlineStr">
-        <is>
-          <t>Hypebeast.KR</t>
-        </is>
-      </c>
-      <c r="G261" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNGlTaDBZWjZfWnV0QjBEdWhGb3Z3V3RlaFRlN3VlT2p2blhsdU13TjhQTTJjNThvVXh4ZWtWaktfR21aNWdjbWJITWc2el8tSjNOeHpXdGNLZktGYnhSZnRFWmhaUzFpY1o0Q01UM0gxVmRKRjFBWmJkajhMNWlzeG9HempxMVRheTQyMy1tLWRVaGxiOXRnc3VwMHdTNWpQQXh4d1hSNGxUZ1h2bHoxU0tCUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D262" s="3" t="inlineStr">
-        <is>
-          <t>DLSS 5 테스트 S.T.A.L.K.E.R. 2: Heart of Chornobyl그래픽, FPS 및 이미지 품질</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>DLSS 5 테스트 S.T.A.L.K.E.R. 2: Heart of Chornobyl그래픽, FPS 및 이미지 품질.</t>
-        </is>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>GameGPU</t>
-        </is>
-      </c>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNZWFlWl8yVmlybDkxNFc3TW1PUjVvSmlHNlVIdTFQSVk4R1F5QjlnU05CMWNQVVc2WG5fQkhwMGJOUkdQa0h6Z3dTMVd5TkFVRVAyUWdWcm5VSmNhYnY1ajBoNzJiN1Bwb2RuQlo3OW5oQ3N1UWUzanVFelgxQmE5VXprU3JnTXdrUHZpcnZmRXlMVUl6Y2p6V1ZJeENXYmVqMlM5TktNaWd0RVB6WXZfalpiTWJSd1p0cTJhWTA5SkpfMDhMRUZ6Q0Rnc1hUZGI0VnRONDZRSjI?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D263" s="3" t="inlineStr">
-        <is>
-          <t>'디아블로2' 팬게임 'D2서바이버' 인터넷 강타 … '뱀서'와 '디아블로2' 조합 성공적</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="inlineStr">
-        <is>
-          <t>'디아블로2' 팬게임 'D2서바이버' 인터넷 강타  '뱀서'와 '디아블로2' 조합 성공적.</t>
-        </is>
-      </c>
-      <c r="F263" s="3" t="inlineStr">
-        <is>
-          <t>경향게임스</t>
-        </is>
-      </c>
-      <c r="G263" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBWUnFGbkk0b1dxSDZ3MVB0QUV4dnFuZ3Npd09USzA5NEEzX0JjbzJ0a2xQWnVRTVd0SzJyWkt5UDBzLUROOTY5RjBMRzhKbFAtelBGcE9zYkw1cy16TF9LMDhIRENfMVRNSE40bw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>건담 블리츠 오더 첫 공개, 테스트 참가자 모집</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>건담 블리츠 오더 첫 공개, 테스트 참가자 모집.</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>인벤</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1hdFhLWnJXbVJ4UHJaaDZUYlpXTHZxa1pCZllfSGVkekxDTVlpUHEtZ1ZxcUk5NHdyaWhCZUFnZmNZWmNfQ3Q2cTZERVpsckpRWWd4UE5nS3A2dFV1X3c?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>드로리안, 에어스피더 전기 플라잉 카 레이싱 시리즈에 참가하는 최초의 미국 팀이 되다</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="inlineStr">
-        <is>
-          <t>드로리안, 에어스피더 전기 플라잉 카 레이싱 시리즈에 참가하는 최초의 미국 팀이 되다.</t>
-        </is>
-      </c>
-      <c r="F265" s="3" t="inlineStr">
-        <is>
-          <t>Hypebeast.KR</t>
-        </is>
-      </c>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNMUVlU3NSNTFzU0JITFVYaFdrVU5tOVZ5Tng5cDYteTFPSE1BMnVFVXlucjY5WlNYT3RFSzhsR2Q3bDZaSjdkeUpINUdKUllTc1RudlpYUkRhdUJZbkNURWw5RXEzRXJIQTZlSExEZ0lNbm5TX0xack8yRGs3UUROOHExUE54NVpxS0RhQ0pB?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D266" s="3" t="inlineStr">
-        <is>
-          <t>최휘영 "문화가 AI 기술 주도해야…기업·창작자·연구자 협력"</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="inlineStr">
-        <is>
-          <t>)= 최휘영 문화체육관광부 장관은 15일 "문화가 인공지능 기술개발을 주도해야 한다"고 강조했다.</t>
-        </is>
-      </c>
-      <c r="F266" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G266" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015120100005</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D267" s="3" t="inlineStr">
-        <is>
-          <t>"세계인이 즐기는 K푸드 축제로"…순창장류축제 개막</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="inlineStr">
-        <is>
-          <t>)= 전북 순창군의 대표 축제인 제21회 순창장류축제가 15일 순창읍 전통고추장민속마을과 순창발효테마파크 일원에서.</t>
-        </is>
-      </c>
-      <c r="F267" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G267" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015130300055</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (5개사)]</t>
-        </is>
-      </c>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>이마트, 758억원 규모 자사주 소각 결정…"주주가치 제고"</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="inlineStr">
-        <is>
-          <t>)= 이마트는 758억5천만원 규모의 자사주를 소각한다고 15일 공시했다.</t>
-        </is>
-      </c>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015138800030</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>어기구 "수자원공사 해외사업 손실 눈덩이…목표액 5.7%만 회수"</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="inlineStr">
-        <is>
-          <t>)= 한국수자원공사가 해외사업에 수천억 원 투자하고도 당초 계획의 5.7%만 회수했다는 지적이 나왔다.</t>
-        </is>
-      </c>
-      <c r="F269" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015138200063</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>우주태양광 필름 쥔 이소영 장관…"중소기업, 성장엔진으로 육성"(종합2보)</t>
-        </is>
-      </c>
-      <c r="E270" s="3" t="inlineStr">
-        <is>
-          <t>)= "반도체에 이어 태양광 소재를 연구개발하고 있는데 인상적입니다.".</t>
-        </is>
-      </c>
-      <c r="F270" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G270" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261014190352030</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D271" s="3" t="inlineStr">
-        <is>
-          <t>한국전기공사협회, 한국전력과 상생협력 업무협약</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="inlineStr">
-        <is>
-          <t>)= 한국전기공사협회는 한전 아트센터에서 한국전력과 상생협력 업무협약을 체결했다고 15일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F271" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G271" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015134900064</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D272" s="3" t="inlineStr">
-        <is>
-          <t>양평 농가 한우, 올해 경기지역 최고급육 선정</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="inlineStr">
-        <is>
-          <t>)= 올해 경기지역 최고급육으로 양평 농가 한우가 선정됐다.</t>
-        </is>
-      </c>
-      <c r="F272" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015136800060</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>IT/과학/신상품</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D273" s="3" t="inlineStr">
-        <is>
-          <t>충남 산하기관 평가서 신용보증재단 최고등급…일부 기관 하락</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="inlineStr">
-        <is>
-          <t>)= 충남도 산하 공공기관 경영평가에서 충남신용보증재단이 2년 연속 최고 등급을 받았지만, 한국 유교문화 진흥원은년.</t>
-        </is>
-      </c>
-      <c r="F273" s="3" t="inlineStr">
-        <is>
-          <t>주요언론</t>
-        </is>
-      </c>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yna.co.kr/view/AKR20261015134800063</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D274" s="3" t="inlineStr">
-        <is>
-          <t>장영란, 中 진출 안 한 것 후회 “인기 엄청 나, 채연처럼 나갈걸"···김영철 증인(‘A급 장영란’)</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>장영란, 中 진출 안 한 것 후회 “인기 엄청 나, 채연처럼 나갈걸"···김영철 증인.</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPM3NPcXpzaUVteWRodXpQVEpoVkRaZG12VEsycHRrWHhaTEYzV19wWUJISDg1bkhuSGFHaVQ0WmZyZTlpVmpWWkRsLXVHYVNfMlJ5S0ZfRWlkd0RJZzNnYXRiMEhrRl90OUNKZ0FmVVRBdmtCQ1JaWWFRYzhZcW5sTllLa1paM092c3VWRHR5bw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D275" s="3" t="inlineStr">
-        <is>
-          <t>하희라 “♥최수종, 술 마시고 나 때린다는 소문까지”…33년 잉꼬부부의 해명 (유퀴즈)</t>
-        </is>
-      </c>
-      <c r="E275" s="3" t="inlineStr">
-        <is>
-          <t>하희라 “♥최수종, 술 마시고 나 때린다는 소문까지”33년 잉꼬부부의 해명.</t>
-        </is>
-      </c>
-      <c r="F275" s="3" t="inlineStr">
-        <is>
-          <t>스포츠경향</t>
-        </is>
-      </c>
-      <c r="G275" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1IakJHX1U3bnNKaGtyYl81eDN5Yl9uUTJZb2s2cjcwVmpuem9jRnRqZG1jZFo4dkhXM0hwSm5SWXpZQm53UVpyWFViaExhaF91VmU0MmNhencwQ1pBdUHSAWNBVV95cUxNM3ZXSEpYcU1ZUFlaN1VmMU9RUWlITk5wVVhuWDJfMl90dlBEZGtsZEdwWjJhTTlaN0czbkVSVHJZZ0pNeC1aVEdPMk5SWWJkcTd2YnBwdk96VDlXeVFLYlVfUlE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D276" s="3" t="inlineStr">
-        <is>
-          <t>이수만 신인 걸그룹 아이찡 부모에 임금체불 의혹…모친 사과</t>
-        </is>
-      </c>
-      <c r="E276" s="3" t="inlineStr">
-        <is>
-          <t>이수만 신인 걸그룹 아이찡 부모에 임금체불 의혹모친 사과. 아울러 이수만이 다시 꺼낸 K팝 DNAA20라이트, 데뷔 직후 '멜론 1위'.</t>
-        </is>
-      </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>경기일보</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE4yWUlSaTFLeWVvMUI0Q1o2bFJzVGRZWldocjVVQmxDdmM0RW5ITlVJYzBCTnNQdVV2WGdTQWtKellRZWo1NDBxdUx6UUhSSF91dDdJUmFTZjY3dTQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D277" s="3" t="inlineStr">
-        <is>
-          <t>‘개과천선’ 서인영 “일본인과 3년 연애…번역기 썼다”</t>
-        </is>
-      </c>
-      <c r="E277" s="3" t="inlineStr">
-        <is>
-          <t>‘개과천선’ 서인영 “일본인과 3년 연애번역기 썼다”.</t>
-        </is>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>동아일보</t>
-        </is>
-      </c>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE92cXFLcERXbmkxeG1xNWYyN05QTGNwWURDcld6NHd0dTRORVpGU0xxalAtbzFUc1B1bFhzck9lUjJQUU9YZUVkaTRxR19VVnp5RkFxSHNwZ2lnZDN0YndmczJpMlEtMzVmMDNrZktRNnRZSFEyNTFjN0F3LVdaZ9IBZkFVX3lxTE44M3RXZzBOYVlDT2h0aEpCR1RBQnBHVHY0eF9PWno2Qk44NGNzUXRsbnNxcjhDNHpkNGhHN1JDVXUzTjhKUFlDc0lDbnhnT3FHbDBBYlFwbE5NTDlndHNFSkdTUk9xUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (4개사)]</t>
-        </is>
-      </c>
-      <c r="D278" s="3" t="inlineStr">
-        <is>
-          <t>부산국제영화제, 관객 20만 명 넘어...2015년 이후 처음</t>
-        </is>
-      </c>
-      <c r="E278" s="3" t="inlineStr">
-        <is>
-          <t>부산국제영화제, 관객 20만 명 넘어2015년 이후 처음.</t>
-        </is>
-      </c>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>YTN</t>
-        </is>
-      </c>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE42MXpmdWtqdzZnVV9YSjZfZTNQZWpFVWlSODRfRTJMWms2dm1OZGhBa0FHTUlSUjYwR19qRzF6MFlvQWFlTExHanBKcjUxcU1oQVFHZ1BKeV92MnVQQlE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B279" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D279" s="3" t="inlineStr">
-        <is>
-          <t>김세의 "독방이 정신건강 해쳐"…검사 "보석을 무죄로 왜곡할것"</t>
-        </is>
-      </c>
-      <c r="E279" s="3" t="inlineStr">
-        <is>
-          <t>김세의 "독방이 정신건강 해쳐"검사 "보석을 무죄로 왜곡할것". 아울러 "김새론 안고 자고 싶다" 카톡 보낸 인물은 연예인 A 씨조작 진술 확보.</t>
-        </is>
-      </c>
-      <c r="F279" s="3" t="inlineStr">
-        <is>
-          <t>연합뉴스</t>
-        </is>
-      </c>
-      <c r="G279" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBuSHp6cm1lR1hIUmRLZGxhU1hhaHIxSVRnb2h5dnBRdmhxUjEtb0ctWDJDVXQxXzhIUHhSSW9kMGFCdkNDZng2Wk5lN0ZRMDg1ZlRKRXNSWnRZYk3SAWBBVV95cUxOdkdSOVlKN1VqNHBtMi1hVjF6SU41SVY0WTNQTVczQ0FIR1hsWG80RzVYVUJVRndPNm90QjZha0lkYkQyR2pVY3RuVjJMWnlvZ19McWVwVmZIcWhxdTFKaTk?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="inlineStr">
-        <is>
-          <t>‘편스토랑’ 이정현, 남편 위한 몰래 카메라</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="inlineStr">
-        <is>
-          <t>‘편스토랑’ 이정현, 남편 위한 몰래 카메라.</t>
-        </is>
-      </c>
-      <c r="F280" s="3" t="inlineStr">
-        <is>
-          <t>BNT뉴스</t>
-        </is>
-      </c>
-      <c r="G280" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9FUVV5YTlmaEY4ZjNyWjVQRXc5VWVMZTg4UmRaSWJQTjBGRTdJc0JzX29GaWFNQnpBMm5sLUltVEhzYW5HRFdHWElrSld2cGVXcEJOdWdZdWpFcmpzMHh4QlctbHU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B281" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>🔥 [언론사 집중 보도 (3개사)]</t>
-        </is>
-      </c>
-      <c r="D281" s="3" t="inlineStr">
-        <is>
-          <t>“민희진, 전 어도어 직원 명예훼손 사건 불송치·불기소 처분 받아”</t>
-        </is>
-      </c>
-      <c r="E281" s="3" t="inlineStr">
-        <is>
-          <t>“민희진, 전 어도어 직원 명예훼손 사건 불송치·불기소 처분 받아”.</t>
-        </is>
-      </c>
-      <c r="F281" s="3" t="inlineStr">
-        <is>
-          <t>한겨레</t>
-        </is>
-      </c>
-      <c r="G281" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5XZ2owc2NfT3hDeUk3Unpia0pxRWxfT3EyZnYtSHRISU5FRU9kMXdkSXFIa3N6SHFhVWppV1lxT0Y2R28ycFRuMi05Q3NCLXM0RDhyTUtvQ1UyS3VNUmRHcnFBaUJXQUtQcGhIaDAwN2MzQQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>연예/대중문화</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>신규 이슈</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="inlineStr">
-        <is>
-          <t>김유신 된 박성웅의 든든한 리더십…신라의 운명 짊어졌다(‘문무’)</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="inlineStr">
-        <is>
-          <t>김유신 된 박성웅의 든든한 리더십신라의 운명 짊어졌다. 아울러 KBS 대하드라마 ‘문무’다음 달 14일 첫 방송.</t>
-        </is>
-      </c>
-      <c r="F282" s="3" t="inlineStr">
-        <is>